--- a/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
@@ -586,82 +586,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.9980797418832</v>
+        <v>39.99807974188317</v>
       </c>
       <c r="C2" t="n">
-        <v>42.67289011868515</v>
+        <v>42.67289011868514</v>
       </c>
       <c r="D2" t="n">
-        <v>39.82622113669218</v>
+        <v>39.82622113669213</v>
       </c>
       <c r="E2" t="n">
-        <v>39.85385363729281</v>
+        <v>39.85385363729279</v>
       </c>
       <c r="F2" t="n">
-        <v>39.84486075689934</v>
+        <v>39.84486075689929</v>
       </c>
       <c r="G2" t="n">
-        <v>40.13009998170717</v>
+        <v>40.13009998170715</v>
       </c>
       <c r="H2" t="n">
-        <v>40.03591457761061</v>
+        <v>40.03591457761055</v>
       </c>
       <c r="I2" t="n">
         <v>39.819850735511</v>
       </c>
       <c r="J2" t="n">
-        <v>40.07509667076752</v>
+        <v>40.0750966707675</v>
       </c>
       <c r="K2" t="n">
-        <v>39.99132032368851</v>
+        <v>39.9913203236885</v>
       </c>
       <c r="L2" t="n">
-        <v>40.06145167059997</v>
+        <v>40.06145167059994</v>
       </c>
       <c r="M2" t="n">
-        <v>40.33198090686854</v>
+        <v>40.3319809068685</v>
       </c>
       <c r="N2" t="n">
-        <v>40.06991348400537</v>
+        <v>40.06991348400534</v>
       </c>
       <c r="O2" t="n">
-        <v>44.20916049915471</v>
+        <v>44.2091604991547</v>
       </c>
       <c r="P2" t="n">
-        <v>40.1652041085642</v>
+        <v>40.16520410856416</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.95439138243957</v>
+        <v>39.95439138243952</v>
       </c>
       <c r="R2" t="n">
-        <v>39.87337331060424</v>
+        <v>39.8733733106042</v>
       </c>
       <c r="S2" t="n">
-        <v>40.05064264061194</v>
+        <v>40.0506426406119</v>
       </c>
       <c r="T2" t="n">
-        <v>40.0060035351282</v>
+        <v>40.00600353512817</v>
       </c>
       <c r="U2" t="n">
-        <v>43.83187745594133</v>
+        <v>43.83187745594135</v>
       </c>
       <c r="V2" t="n">
-        <v>39.97858007093162</v>
+        <v>39.97858007093157</v>
       </c>
       <c r="W2" t="n">
-        <v>46.33714823440368</v>
+        <v>46.33714823440372</v>
       </c>
       <c r="X2" t="n">
-        <v>39.93222034211363</v>
+        <v>39.9322203421136</v>
       </c>
       <c r="Y2" t="n">
-        <v>40.26786975731439</v>
+        <v>40.26786975731436</v>
       </c>
       <c r="Z2" t="n">
-        <v>41.45464129667145</v>
+        <v>41.45464129667144</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.97347290082378</v>
+        <v>39.97347290082377</v>
       </c>
       <c r="AB2" t="n">
         <v>40.18591906313062</v>
@@ -674,37 +674,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.91812281726034</v>
+        <v>41.91812281726035</v>
       </c>
       <c r="C3" t="n">
         <v>44.74633642761335</v>
       </c>
       <c r="D3" t="n">
-        <v>40.70791935247919</v>
+        <v>40.70791935247918</v>
       </c>
       <c r="E3" t="n">
-        <v>40.89978126488997</v>
+        <v>40.89978126488996</v>
       </c>
       <c r="F3" t="n">
         <v>40.84387738059343</v>
       </c>
       <c r="G3" t="n">
-        <v>42.86213344975794</v>
+        <v>42.86213344975791</v>
       </c>
       <c r="H3" t="n">
-        <v>42.21691269644145</v>
+        <v>42.2169126964415</v>
       </c>
       <c r="I3" t="n">
-        <v>40.66343368561802</v>
+        <v>40.66343368561804</v>
       </c>
       <c r="J3" t="n">
-        <v>42.47533625866584</v>
+        <v>42.47533625866581</v>
       </c>
       <c r="K3" t="n">
-        <v>41.88844220004103</v>
+        <v>41.88844220004102</v>
       </c>
       <c r="L3" t="n">
-        <v>42.3810589345558</v>
+        <v>42.38105893455577</v>
       </c>
       <c r="M3" t="n">
         <v>44.32888909702822</v>
@@ -716,43 +716,43 @@
         <v>48.90476797516575</v>
       </c>
       <c r="P3" t="n">
-        <v>43.10962679865452</v>
+        <v>43.10962679865449</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.6222211631851</v>
+        <v>41.62222116318509</v>
       </c>
       <c r="R3" t="n">
-        <v>41.04841969041292</v>
+        <v>41.04841969041294</v>
       </c>
       <c r="S3" t="n">
-        <v>42.29701496453391</v>
+        <v>42.29701496453389</v>
       </c>
       <c r="T3" t="n">
-        <v>41.99561374630451</v>
+        <v>41.99561374630449</v>
       </c>
       <c r="U3" t="n">
-        <v>49.34998642411141</v>
+        <v>49.34998642411142</v>
       </c>
       <c r="V3" t="n">
-        <v>41.78075786151693</v>
+        <v>41.78075786151696</v>
       </c>
       <c r="W3" t="n">
         <v>53.55597555875507</v>
       </c>
       <c r="X3" t="n">
-        <v>41.46485064159549</v>
+        <v>41.46485064159545</v>
       </c>
       <c r="Y3" t="n">
         <v>43.85631037148435</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.60507382144927</v>
+        <v>44.60507382144925</v>
       </c>
       <c r="AA3" t="n">
         <v>41.75557064310686</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.28996778698482</v>
+        <v>43.28996778698476</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.151760975869019</v>
+        <v>7.151760975869013</v>
       </c>
       <c r="C4" t="n">
         <v>3.85060569686131</v>
       </c>
       <c r="D4" t="n">
-        <v>5.210538971371824</v>
+        <v>5.210538971371826</v>
       </c>
       <c r="E4" t="n">
-        <v>5.522660777234393</v>
+        <v>5.522660777234391</v>
       </c>
       <c r="F4" t="n">
-        <v>5.421082056260695</v>
+        <v>5.421082056260701</v>
       </c>
       <c r="G4" t="n">
-        <v>8.64299031699163</v>
+        <v>8.642990316991636</v>
       </c>
       <c r="H4" t="n">
-        <v>7.579122850294405</v>
+        <v>7.57912285029441</v>
       </c>
       <c r="I4" t="n">
-        <v>5.138582359501588</v>
+        <v>5.13858235950159</v>
       </c>
       <c r="J4" t="n">
         <v>8.021880397373661</v>
       </c>
       <c r="K4" t="n">
-        <v>7.075410237874196</v>
+        <v>7.075410237874195</v>
       </c>
       <c r="L4" t="n">
-        <v>7.867576063252202</v>
+        <v>7.867576063252205</v>
       </c>
       <c r="M4" t="n">
         <v>10.91713548017885</v>
       </c>
       <c r="N4" t="n">
-        <v>7.963156138292883</v>
+        <v>7.963156138292893</v>
       </c>
       <c r="O4" t="n">
-        <v>7.232338844863492</v>
+        <v>7.232338844863489</v>
       </c>
       <c r="P4" t="n">
-        <v>9.039507578537929</v>
+        <v>9.039507578537936</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.658280858314721</v>
+        <v>6.658280858314717</v>
       </c>
       <c r="R4" t="n">
-        <v>5.7431444667804</v>
+        <v>5.743144466780399</v>
       </c>
       <c r="S4" t="n">
-        <v>7.745483097138208</v>
+        <v>7.745483097138205</v>
       </c>
       <c r="T4" t="n">
-        <v>7.24126386569635</v>
+        <v>7.241263865696351</v>
       </c>
       <c r="U4" t="n">
-        <v>9.391743797250712</v>
+        <v>9.391743797250694</v>
       </c>
       <c r="V4" t="n">
-        <v>6.932406243063376</v>
+        <v>6.932406243063371</v>
       </c>
       <c r="W4" t="n">
-        <v>9.543284237633571</v>
+        <v>9.543284237633568</v>
       </c>
       <c r="X4" t="n">
-        <v>6.407848758651247</v>
+        <v>6.407848758651241</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.1793763035508</v>
+        <v>10.17937630355079</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.727032676486676</v>
+        <v>7.727032676486667</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.873815386397025</v>
+        <v>6.873815386397024</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.266476630854463</v>
+        <v>9.266476630854452</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>87.95426209421106</v>
+        <v>87.95426209421117</v>
       </c>
       <c r="C5" t="n">
-        <v>29.28448237000413</v>
+        <v>29.28448237000412</v>
       </c>
       <c r="D5" t="n">
-        <v>58.585768597494</v>
+        <v>58.58576859749389</v>
       </c>
       <c r="E5" t="n">
-        <v>61.68990113118596</v>
+        <v>61.68990113118592</v>
       </c>
       <c r="F5" t="n">
-        <v>64.56479766306826</v>
+        <v>64.56479766306792</v>
       </c>
       <c r="G5" t="n">
-        <v>119.0397404577808</v>
+        <v>119.0397404577807</v>
       </c>
       <c r="H5" t="n">
         <v>113.6543665803669</v>
       </c>
       <c r="I5" t="n">
-        <v>57.71930113986657</v>
+        <v>57.71930113986642</v>
       </c>
       <c r="J5" t="n">
         <v>109.9544596887862</v>
       </c>
       <c r="K5" t="n">
-        <v>97.44885597818954</v>
+        <v>97.44885597818958</v>
       </c>
       <c r="L5" t="n">
         <v>108.6975784874728</v>
       </c>
       <c r="M5" t="n">
-        <v>182.2422990105713</v>
+        <v>182.2422990105716</v>
       </c>
       <c r="N5" t="n">
-        <v>135.524214989485</v>
+        <v>135.5242149894848</v>
       </c>
       <c r="O5" t="n">
-        <v>87.40613600125094</v>
+        <v>87.40613600125107</v>
       </c>
       <c r="P5" t="n">
         <v>125.2140264393936</v>
       </c>
       <c r="Q5" t="n">
-        <v>87.46937694359494</v>
+        <v>87.46937694359485</v>
       </c>
       <c r="R5" t="n">
         <v>71.67260276142881</v>
       </c>
       <c r="S5" t="n">
-        <v>102.1382418016025</v>
+        <v>102.1382418016023</v>
       </c>
       <c r="T5" t="n">
         <v>102.2014026003562</v>
       </c>
       <c r="U5" t="n">
-        <v>136.9725896545946</v>
+        <v>136.9725896545944</v>
       </c>
       <c r="V5" t="n">
-        <v>84.59254876448219</v>
+        <v>84.59254876448216</v>
       </c>
       <c r="W5" t="n">
-        <v>143.5215307226316</v>
+        <v>143.5215307226315</v>
       </c>
       <c r="X5" t="n">
-        <v>82.94050302704926</v>
+        <v>82.94050302704915</v>
       </c>
       <c r="Y5" t="n">
-        <v>156.8603877073068</v>
+        <v>156.8603877073066</v>
       </c>
       <c r="Z5" t="n">
-        <v>101.4479276206044</v>
+        <v>101.4479276206042</v>
       </c>
       <c r="AA5" t="n">
-        <v>90.12404365067917</v>
+        <v>90.12404365067916</v>
       </c>
       <c r="AB5" t="n">
-        <v>151.3650562213689</v>
+        <v>151.3650562213685</v>
       </c>
     </row>
     <row r="6">
@@ -938,70 +938,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.895636652097</v>
+        <v>160.5296666582973</v>
       </c>
       <c r="C6" t="n">
-        <v>157.2285113792898</v>
+        <v>157.2285113792897</v>
       </c>
       <c r="D6" t="n">
         <v>132.9544146475999</v>
       </c>
       <c r="E6" t="n">
-        <v>158.9005664596628</v>
+        <v>133.2665364534622</v>
       </c>
       <c r="F6" t="n">
-        <v>133.1649577324887</v>
+        <v>158.798987738689</v>
       </c>
       <c r="G6" t="n">
-        <v>136.3868659932197</v>
+        <v>162.02089599942</v>
       </c>
       <c r="H6" t="n">
         <v>160.9570285327227</v>
       </c>
       <c r="I6" t="n">
-        <v>158.51648804193</v>
+        <v>132.8824580357295</v>
       </c>
       <c r="J6" t="n">
-        <v>135.7657560736016</v>
+        <v>161.3997860798021</v>
       </c>
       <c r="K6" t="n">
-        <v>134.819285914102</v>
+        <v>134.8192859141022</v>
       </c>
       <c r="L6" t="n">
-        <v>161.2454817456807</v>
+        <v>135.6114517394801</v>
       </c>
       <c r="M6" t="n">
-        <v>138.6610111564069</v>
+        <v>138.661011156407</v>
       </c>
       <c r="N6" t="n">
-        <v>135.720430696095</v>
+        <v>135.7204306960951</v>
       </c>
       <c r="O6" t="n">
-        <v>160.6816259876682</v>
+        <v>160.6816259876683</v>
       </c>
       <c r="P6" t="n">
         <v>162.488808720769</v>
       </c>
       <c r="Q6" t="n">
-        <v>134.4021565345428</v>
+        <v>134.4021565345427</v>
       </c>
       <c r="R6" t="n">
-        <v>159.1210501492089</v>
+        <v>133.4870201430084</v>
       </c>
       <c r="S6" t="n">
-        <v>161.1233887795666</v>
+        <v>161.1233887795667</v>
       </c>
       <c r="T6" t="n">
         <v>134.9851395419244</v>
       </c>
       <c r="U6" t="n">
-        <v>137.1554064796307</v>
+        <v>137.1554064796308</v>
       </c>
       <c r="V6" t="n">
-        <v>160.3103119254918</v>
+        <v>160.3103119254917</v>
       </c>
       <c r="W6" t="n">
-        <v>143.8269234086326</v>
+        <v>162.9925801137932</v>
       </c>
       <c r="X6" t="n">
         <v>159.7857544410797</v>
@@ -1010,13 +1010,13 @@
         <v>143.5614134412847</v>
       </c>
       <c r="Z6" t="n">
-        <v>135.4709083527148</v>
+        <v>135.4709083527147</v>
       </c>
       <c r="AA6" t="n">
-        <v>160.2517210688254</v>
+        <v>134.6176910626249</v>
       </c>
       <c r="AB6" t="n">
-        <v>137.0343038972036</v>
+        <v>137.0343038972037</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.549746102286914</v>
+        <v>8.549746102286903</v>
       </c>
       <c r="C7" t="n">
-        <v>5.248590823279207</v>
+        <v>5.248590823279206</v>
       </c>
       <c r="D7" t="n">
-        <v>6.60852409778972</v>
+        <v>6.608524097789719</v>
       </c>
       <c r="E7" t="n">
         <v>6.920645903652286</v>
       </c>
       <c r="F7" t="n">
-        <v>6.819067182678593</v>
+        <v>6.819067182678591</v>
       </c>
       <c r="G7" t="n">
-        <v>10.04097544340952</v>
+        <v>10.04097544340953</v>
       </c>
       <c r="H7" t="n">
-        <v>8.977107976712293</v>
+        <v>8.977107976712302</v>
       </c>
       <c r="I7" t="n">
-        <v>6.536567485919484</v>
+        <v>6.536567485919481</v>
       </c>
       <c r="J7" t="n">
-        <v>9.419865523791557</v>
+        <v>9.419865523791556</v>
       </c>
       <c r="K7" t="n">
-        <v>8.473395364292099</v>
+        <v>8.473395364292092</v>
       </c>
       <c r="L7" t="n">
-        <v>9.265561189670091</v>
+        <v>9.265561189670095</v>
       </c>
       <c r="M7" t="n">
         <v>12.31512060659674</v>
       </c>
       <c r="N7" t="n">
-        <v>9.361141264710783</v>
+        <v>9.361141264710788</v>
       </c>
       <c r="O7" t="n">
-        <v>8.630309387388106</v>
+        <v>8.630309387388104</v>
       </c>
       <c r="P7" t="n">
         <v>10.43747812106255</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.056265984732608</v>
+        <v>8.056265984732612</v>
       </c>
       <c r="R7" t="n">
-        <v>7.141129593198293</v>
+        <v>7.141129593198291</v>
       </c>
       <c r="S7" t="n">
-        <v>9.143468223556104</v>
+        <v>9.143468223556097</v>
       </c>
       <c r="T7" t="n">
-        <v>8.639248992114245</v>
+        <v>8.639248992114243</v>
       </c>
       <c r="U7" t="n">
         <v>10.80937925032173</v>
       </c>
       <c r="V7" t="n">
-        <v>8.330391369481271</v>
+        <v>8.330391369481266</v>
       </c>
       <c r="W7" t="n">
-        <v>10.94126936405147</v>
+        <v>10.94126936405146</v>
       </c>
       <c r="X7" t="n">
-        <v>7.805833885069137</v>
+        <v>7.805833885069134</v>
       </c>
       <c r="Y7" t="n">
         <v>11.59714843612065</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.125017802904573</v>
+        <v>9.125017802904569</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.27180051281492</v>
+        <v>8.271800512814918</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.66446175727236</v>
+        <v>10.66446175727234</v>
       </c>
     </row>
     <row r="8">
@@ -1123,19 +1123,19 @@
         <v>8.739883668288586</v>
       </c>
       <c r="E8" t="n">
-        <v>9.052005474151148</v>
+        <v>8.238563614520713</v>
       </c>
       <c r="F8" t="n">
-        <v>7.660745685546337</v>
+        <v>7.66074568554634</v>
       </c>
       <c r="G8" t="n">
-        <v>12.17233501390841</v>
+        <v>12.48910837149089</v>
       </c>
       <c r="H8" t="n">
-        <v>11.10846754721116</v>
+        <v>11.10846754721118</v>
       </c>
       <c r="I8" t="n">
-        <v>8.667927056418351</v>
+        <v>8.667927056418355</v>
       </c>
       <c r="J8" t="n">
         <v>11.55122509429043</v>
@@ -1144,55 +1144,55 @@
         <v>10.60475493479096</v>
       </c>
       <c r="L8" t="n">
-        <v>11.39692076016896</v>
+        <v>11.39692076016897</v>
       </c>
       <c r="M8" t="n">
-        <v>14.44648017709562</v>
+        <v>14.44648017709575</v>
       </c>
       <c r="N8" t="n">
-        <v>10.30829715533755</v>
+        <v>10.30829715533756</v>
       </c>
       <c r="O8" t="n">
-        <v>9.902909314281018</v>
+        <v>9.902909314281017</v>
       </c>
       <c r="P8" t="n">
-        <v>11.63030742582072</v>
+        <v>11.63030742582073</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.359727581928164</v>
+        <v>8.359727581928157</v>
       </c>
       <c r="R8" t="n">
-        <v>9.272489163697157</v>
+        <v>9.272489163697163</v>
       </c>
       <c r="S8" t="n">
         <v>11.27482779405496</v>
       </c>
       <c r="T8" t="n">
-        <v>10.7706085626131</v>
+        <v>10.77060856261311</v>
       </c>
       <c r="U8" t="n">
-        <v>12.00073501589414</v>
+        <v>12.19514311276066</v>
       </c>
       <c r="V8" t="n">
-        <v>10.46175093998014</v>
+        <v>10.04410996945431</v>
       </c>
       <c r="W8" t="n">
         <v>13.07292916428793</v>
       </c>
       <c r="X8" t="n">
-        <v>8.249309927837405</v>
+        <v>8.249309927837407</v>
       </c>
       <c r="Y8" t="n">
         <v>15.24727859138449</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.25637737340343</v>
+        <v>9.700325052623576</v>
       </c>
       <c r="AA8" t="n">
         <v>10.40316008331379</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.39160557820946</v>
+        <v>14.39160557820944</v>
       </c>
     </row>
     <row r="9">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.99795394953238</v>
+        <v>12.99795394953239</v>
       </c>
       <c r="C9" t="n">
-        <v>11.42494658793265</v>
+        <v>11.42494658793264</v>
       </c>
       <c r="D9" t="n">
-        <v>12.78487986244315</v>
+        <v>12.78487986244316</v>
       </c>
       <c r="E9" t="n">
-        <v>13.09700166830572</v>
+        <v>12.69815254082712</v>
       </c>
       <c r="F9" t="n">
-        <v>12.99542294733204</v>
+        <v>9.011569725628618</v>
       </c>
       <c r="G9" t="n">
-        <v>16.21733120806298</v>
+        <v>16.21733167981307</v>
       </c>
       <c r="H9" t="n">
-        <v>15.15346374136574</v>
+        <v>15.15346374136573</v>
       </c>
       <c r="I9" t="n">
         <v>12.71292325057293</v>
@@ -1229,10 +1229,10 @@
         <v>15.59622128844499</v>
       </c>
       <c r="K9" t="n">
-        <v>14.64975112894554</v>
+        <v>14.64975112894553</v>
       </c>
       <c r="L9" t="n">
-        <v>15.44191695432353</v>
+        <v>15.44191695432354</v>
       </c>
       <c r="M9" t="n">
         <v>18.49147637125018</v>
@@ -1241,46 +1241,46 @@
         <v>15.53749702936422</v>
       </c>
       <c r="O9" t="n">
-        <v>15.37938632103474</v>
+        <v>15.37938632103472</v>
       </c>
       <c r="P9" t="n">
-        <v>17.31110880838071</v>
+        <v>17.3111088083807</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.23262222113617</v>
+        <v>14.23262222113616</v>
       </c>
       <c r="R9" t="n">
         <v>13.31748535785173</v>
       </c>
       <c r="S9" t="n">
-        <v>15.31982398820955</v>
+        <v>15.31982398820954</v>
       </c>
       <c r="T9" t="n">
-        <v>14.81560475676769</v>
+        <v>14.81560475676768</v>
       </c>
       <c r="U9" t="n">
-        <v>16.985871694474</v>
+        <v>16.98587169447399</v>
       </c>
       <c r="V9" t="n">
-        <v>14.50674713413472</v>
+        <v>16.50099125796267</v>
       </c>
       <c r="W9" t="n">
-        <v>17.1176251287049</v>
+        <v>17.11762512870491</v>
       </c>
       <c r="X9" t="n">
         <v>13.98218964972258</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.7735042007741</v>
+        <v>17.77350420077409</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.301373567558</v>
+        <v>14.2594542335965</v>
       </c>
       <c r="AA9" t="n">
         <v>14.44815627746836</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.8408175219258</v>
+        <v>16.84081752192578</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.82042167757415</v>
+        <v>38.82042167757412</v>
       </c>
       <c r="C2" t="n">
-        <v>41.81481548691188</v>
+        <v>41.81481548691185</v>
       </c>
       <c r="D2" t="n">
-        <v>38.89397931956863</v>
+        <v>38.89397931956858</v>
       </c>
       <c r="E2" t="n">
-        <v>38.84838301845765</v>
+        <v>38.8483830184576</v>
       </c>
       <c r="F2" t="n">
-        <v>38.96218565438262</v>
+        <v>38.96218565438257</v>
       </c>
       <c r="G2" t="n">
-        <v>39.01226997208033</v>
+        <v>39.01226997208029</v>
       </c>
       <c r="H2" t="n">
-        <v>38.99593715792247</v>
+        <v>38.99593715792241</v>
       </c>
       <c r="I2" t="n">
-        <v>38.88340250328905</v>
+        <v>38.88340250328901</v>
       </c>
       <c r="J2" t="n">
-        <v>38.98579920688287</v>
+        <v>38.98579920688285</v>
       </c>
       <c r="K2" t="n">
         <v>39.02917331812436</v>
       </c>
       <c r="L2" t="n">
-        <v>38.95456630060934</v>
+        <v>38.95456630060931</v>
       </c>
       <c r="M2" t="n">
-        <v>38.95665718320243</v>
+        <v>38.9566571832024</v>
       </c>
       <c r="N2" t="n">
-        <v>39.04913387708802</v>
+        <v>39.04913387708799</v>
       </c>
       <c r="O2" t="n">
-        <v>42.84027690660583</v>
+        <v>42.84027690660581</v>
       </c>
       <c r="P2" t="n">
-        <v>39.19854140005503</v>
+        <v>39.198541400055</v>
       </c>
       <c r="Q2" t="n">
-        <v>38.8904196199713</v>
+        <v>38.89041961997125</v>
       </c>
       <c r="R2" t="n">
-        <v>38.87639673208587</v>
+        <v>38.87639673208581</v>
       </c>
       <c r="S2" t="n">
-        <v>39.02260617650404</v>
+        <v>39.02260617650401</v>
       </c>
       <c r="T2" t="n">
-        <v>39.000564843771</v>
+        <v>39.00056484377097</v>
       </c>
       <c r="U2" t="n">
         <v>42.44642589783226</v>
       </c>
       <c r="V2" t="n">
-        <v>38.92862687638537</v>
+        <v>38.92862687638534</v>
       </c>
       <c r="W2" t="n">
-        <v>45.07851105920369</v>
+        <v>45.07851105920366</v>
       </c>
       <c r="X2" t="n">
-        <v>39.19324788346734</v>
+        <v>39.19324788346732</v>
       </c>
       <c r="Y2" t="n">
         <v>39.14872771998019</v>
       </c>
       <c r="Z2" t="n">
-        <v>39.99846529400023</v>
+        <v>39.99846529400021</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.11392084505265</v>
+        <v>39.11392084505258</v>
       </c>
       <c r="AB2" t="n">
-        <v>38.96123114637845</v>
+        <v>38.96123114637843</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.52143930804844</v>
+        <v>38.52143930804848</v>
       </c>
       <c r="C3" t="n">
-        <v>43.68647952399669</v>
+        <v>43.68647952399665</v>
       </c>
       <c r="D3" t="n">
-        <v>39.04668365425515</v>
+        <v>39.04668365425513</v>
       </c>
       <c r="E3" t="n">
-        <v>38.72034724547448</v>
+        <v>38.72034724547443</v>
       </c>
       <c r="F3" t="n">
-        <v>39.53489964356361</v>
+        <v>39.53489964356359</v>
       </c>
       <c r="G3" t="n">
-        <v>39.88169925216769</v>
+        <v>39.88169925216765</v>
       </c>
       <c r="H3" t="n">
-        <v>39.78006204614428</v>
+        <v>39.78006204614427</v>
       </c>
       <c r="I3" t="n">
-        <v>38.9723920232036</v>
+        <v>38.97239202320364</v>
       </c>
       <c r="J3" t="n">
-        <v>39.69806751107503</v>
+        <v>39.69806751107502</v>
       </c>
       <c r="K3" t="n">
-        <v>40.00451496380695</v>
+        <v>40.00451496380693</v>
       </c>
       <c r="L3" t="n">
-        <v>39.47409026209399</v>
+        <v>39.47409026209401</v>
       </c>
       <c r="M3" t="n">
-        <v>39.50040494050671</v>
+        <v>39.50040494050674</v>
       </c>
       <c r="N3" t="n">
         <v>40.1566886116325</v>
       </c>
       <c r="O3" t="n">
-        <v>46.5068463672205</v>
+        <v>46.50684636722055</v>
       </c>
       <c r="P3" t="n">
-        <v>41.2040018926219</v>
+        <v>41.20400189262187</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.0202029260947</v>
+        <v>39.02020292609468</v>
       </c>
       <c r="R3" t="n">
         <v>38.92311622110554</v>
       </c>
       <c r="S3" t="n">
-        <v>39.95620283727498</v>
+        <v>39.956202837275</v>
       </c>
       <c r="T3" t="n">
-        <v>39.81085917339233</v>
+        <v>39.81085917339229</v>
       </c>
       <c r="U3" t="n">
-        <v>45.67621918489813</v>
+        <v>45.67621918489814</v>
       </c>
       <c r="V3" t="n">
-        <v>39.28916698892567</v>
+        <v>39.28916698892568</v>
       </c>
       <c r="W3" t="n">
-        <v>50.91003639210928</v>
+        <v>50.91003639210933</v>
       </c>
       <c r="X3" t="n">
-        <v>41.17904112605559</v>
+        <v>41.17904112605563</v>
       </c>
       <c r="Y3" t="n">
-        <v>40.86711318503333</v>
+        <v>40.86711318503332</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.91074459477136</v>
+        <v>40.91074459477137</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.61787300524974</v>
+        <v>40.61787300524976</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.53222792136643</v>
+        <v>39.53222792136648</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.436337953835211</v>
+        <v>1.436337953835241</v>
       </c>
       <c r="C4" t="n">
-        <v>1.892590663596865</v>
+        <v>1.892590663596843</v>
       </c>
       <c r="D4" t="n">
-        <v>2.267205358349669</v>
+        <v>2.267205358349709</v>
       </c>
       <c r="E4" t="n">
-        <v>1.752174161966787</v>
+        <v>1.752174161966826</v>
       </c>
       <c r="F4" t="n">
-        <v>3.037627286537773</v>
+        <v>3.037627286537803</v>
       </c>
       <c r="G4" t="n">
-        <v>3.603352694858297</v>
+        <v>3.603352694858379</v>
       </c>
       <c r="H4" t="n">
-        <v>3.418866045479334</v>
+        <v>3.418866045479377</v>
       </c>
       <c r="I4" t="n">
-        <v>2.147735352896174</v>
+        <v>2.147735352896206</v>
       </c>
       <c r="J4" t="n">
-        <v>3.30489256701313</v>
+        <v>3.304892567013147</v>
       </c>
       <c r="K4" t="n">
-        <v>3.794283764349313</v>
+        <v>3.794283764349348</v>
       </c>
       <c r="L4" t="n">
-        <v>2.951563180592951</v>
+        <v>2.951563180592988</v>
       </c>
       <c r="M4" t="n">
-        <v>2.985642064800699</v>
+        <v>2.985642064800731</v>
       </c>
       <c r="N4" t="n">
-        <v>51.07886759202057</v>
+        <v>51.07886759202032</v>
       </c>
       <c r="O4" t="n">
-        <v>4.239176117330143</v>
+        <v>4.239176117330177</v>
       </c>
       <c r="P4" t="n">
-        <v>5.707374162923047</v>
+        <v>5.707374162923065</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.226996913855249</v>
+        <v>2.226996913855224</v>
       </c>
       <c r="R4" t="n">
-        <v>2.068601944342128</v>
+        <v>2.068601944342168</v>
       </c>
       <c r="S4" t="n">
-        <v>3.720104878713178</v>
+        <v>3.720104878713196</v>
       </c>
       <c r="T4" t="n">
-        <v>3.471137885979453</v>
+        <v>3.471137885979445</v>
       </c>
       <c r="U4" t="n">
-        <v>3.810025788985158</v>
+        <v>3.810025788985167</v>
       </c>
       <c r="V4" t="n">
-        <v>2.661882068723762</v>
+        <v>2.661882068723766</v>
       </c>
       <c r="W4" t="n">
-        <v>5.674541992762491</v>
+        <v>5.674541992762533</v>
       </c>
       <c r="X4" t="n">
-        <v>5.647581457926736</v>
+        <v>5.647581457926812</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.091568819171748</v>
+        <v>5.091568819171741</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.36163639545381</v>
+        <v>2.36163639545385</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.751546066792328</v>
+        <v>4.751546066792386</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.028457142600965</v>
+        <v>3.028457142601038</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.874343928064382</v>
+        <v>3.874343928064416</v>
       </c>
       <c r="C5" t="n">
-        <v>11.98633145759585</v>
+        <v>11.98633145759584</v>
       </c>
       <c r="D5" t="n">
-        <v>18.70423372467656</v>
+        <v>18.70423372467661</v>
       </c>
       <c r="E5" t="n">
-        <v>9.121744573868282</v>
+        <v>9.121744573868305</v>
       </c>
       <c r="F5" t="n">
         <v>33.06835711406274</v>
       </c>
       <c r="G5" t="n">
-        <v>37.55263486559005</v>
+        <v>37.55263486559007</v>
       </c>
       <c r="H5" t="n">
-        <v>42.02724636154448</v>
+        <v>42.02724636154454</v>
       </c>
       <c r="I5" t="n">
-        <v>17.2108165871843</v>
+        <v>17.21081658718429</v>
       </c>
       <c r="J5" t="n">
-        <v>35.00702466481813</v>
+        <v>35.0070246648181</v>
       </c>
       <c r="K5" t="n">
-        <v>42.05706123741763</v>
+        <v>42.05706123741766</v>
       </c>
       <c r="L5" t="n">
-        <v>28.21415577516765</v>
+        <v>28.21415577516761</v>
       </c>
       <c r="M5" t="n">
-        <v>31.77495199209524</v>
+        <v>31.77495199209526</v>
       </c>
       <c r="N5" t="n">
-        <v>51.07886759202057</v>
+        <v>51.07886759202032</v>
       </c>
       <c r="O5" t="n">
-        <v>47.49868457655614</v>
+        <v>47.49868457655611</v>
       </c>
       <c r="P5" t="n">
-        <v>71.07294703845724</v>
+        <v>71.07294703845696</v>
       </c>
       <c r="Q5" t="n">
         <v>17.43600262918956</v>
       </c>
       <c r="R5" t="n">
-        <v>16.18678787609634</v>
+        <v>16.18678787609638</v>
       </c>
       <c r="S5" t="n">
-        <v>39.99774855936198</v>
+        <v>39.99774855936191</v>
       </c>
       <c r="T5" t="n">
-        <v>41.79565405430119</v>
+        <v>41.79565405430122</v>
       </c>
       <c r="U5" t="n">
-        <v>41.96435661540603</v>
+        <v>41.96435661540599</v>
       </c>
       <c r="V5" t="n">
-        <v>23.14295448911491</v>
+        <v>23.14295448911496</v>
       </c>
       <c r="W5" t="n">
-        <v>78.79172077385454</v>
+        <v>78.79172077385456</v>
       </c>
       <c r="X5" t="n">
-        <v>76.65870506403105</v>
+        <v>76.65870506403094</v>
       </c>
       <c r="Y5" t="n">
         <v>70.77783139002238</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.80304085735406</v>
+        <v>17.8030408573541</v>
       </c>
       <c r="AA5" t="n">
-        <v>63.39828820164848</v>
+        <v>63.39828820164858</v>
       </c>
       <c r="AB5" t="n">
-        <v>34.59822795670176</v>
+        <v>34.59822795670191</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.5615157006748</v>
+        <v>112.6196404332074</v>
       </c>
       <c r="C6" t="n">
-        <v>135.0177684104363</v>
+        <v>113.0758931429691</v>
       </c>
       <c r="D6" t="n">
-        <v>135.3923831051892</v>
+        <v>135.3923831051893</v>
       </c>
       <c r="E6" t="n">
-        <v>134.8773519088064</v>
+        <v>112.935476641339</v>
       </c>
       <c r="F6" t="n">
-        <v>136.1628050333773</v>
+        <v>114.2209297659099</v>
       </c>
       <c r="G6" t="n">
-        <v>114.7866551742303</v>
+        <v>136.7285304416979</v>
       </c>
       <c r="H6" t="n">
-        <v>114.6021685248514</v>
+        <v>136.544043792319</v>
       </c>
       <c r="I6" t="n">
-        <v>113.3310378322682</v>
+        <v>135.2729130997358</v>
       </c>
       <c r="J6" t="n">
-        <v>114.488195046385</v>
+        <v>136.4300703138528</v>
       </c>
       <c r="K6" t="n">
-        <v>136.9194615111888</v>
+        <v>114.9775862437215</v>
       </c>
       <c r="L6" t="n">
-        <v>114.134865659965</v>
+        <v>136.0767409274325</v>
       </c>
       <c r="M6" t="n">
-        <v>114.1689445441727</v>
+        <v>136.1108198116404</v>
       </c>
       <c r="N6" t="n">
-        <v>51.07886759202057</v>
+        <v>51.07886759202032</v>
       </c>
       <c r="O6" t="n">
-        <v>137.4384876522866</v>
+        <v>137.4384876522864</v>
       </c>
       <c r="P6" t="n">
-        <v>110.4620841077715</v>
+        <v>138.9061077776216</v>
       </c>
       <c r="Q6" t="n">
-        <v>135.3521746606947</v>
+        <v>135.3521746606948</v>
       </c>
       <c r="R6" t="n">
-        <v>113.2519044237142</v>
+        <v>135.1937796911818</v>
       </c>
       <c r="S6" t="n">
-        <v>114.9034073580852</v>
+        <v>136.8452826255528</v>
       </c>
       <c r="T6" t="n">
-        <v>136.5963156328191</v>
+        <v>114.6544403653516</v>
       </c>
       <c r="U6" t="n">
-        <v>115.0464651802378</v>
+        <v>136.9883404477054</v>
       </c>
       <c r="V6" t="n">
-        <v>113.8451845480958</v>
+        <v>135.7870598155634</v>
       </c>
       <c r="W6" t="n">
-        <v>122.5441006226811</v>
+        <v>122.544100622681</v>
       </c>
       <c r="X6" t="n">
-        <v>116.8308839372987</v>
+        <v>116.8308839372989</v>
       </c>
       <c r="Y6" t="n">
-        <v>121.2097881211392</v>
+        <v>121.2097881211394</v>
       </c>
       <c r="Z6" t="n">
-        <v>135.4868141422934</v>
+        <v>113.544938874826</v>
       </c>
       <c r="AA6" t="n">
-        <v>115.9348485461643</v>
+        <v>115.9348485461645</v>
       </c>
       <c r="AB6" t="n">
-        <v>114.2191388131882</v>
+        <v>114.2191388131883</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.279347977044947</v>
+        <v>2.279347977044986</v>
       </c>
       <c r="C7" t="n">
-        <v>2.735600686806593</v>
+        <v>2.735600686806575</v>
       </c>
       <c r="D7" t="n">
-        <v>3.110215381559396</v>
+        <v>3.110215381559437</v>
       </c>
       <c r="E7" t="n">
-        <v>2.59518418517652</v>
+        <v>2.595184185176552</v>
       </c>
       <c r="F7" t="n">
-        <v>3.880637309747514</v>
+        <v>3.880637309747547</v>
       </c>
       <c r="G7" t="n">
-        <v>4.446362718068015</v>
+        <v>4.446362718068105</v>
       </c>
       <c r="H7" t="n">
-        <v>4.26187606868907</v>
+        <v>4.2618760686891</v>
       </c>
       <c r="I7" t="n">
-        <v>2.990745376105898</v>
+        <v>2.990745376105931</v>
       </c>
       <c r="J7" t="n">
-        <v>4.147902590222857</v>
+        <v>4.147902590222872</v>
       </c>
       <c r="K7" t="n">
-        <v>4.637293787559038</v>
+        <v>4.637293787559081</v>
       </c>
       <c r="L7" t="n">
-        <v>3.794573203802675</v>
+        <v>3.794573203802714</v>
       </c>
       <c r="M7" t="n">
-        <v>3.828652088010423</v>
+        <v>3.828652088010463</v>
       </c>
       <c r="N7" t="n">
-        <v>51.07886759202057</v>
+        <v>51.07886759202032</v>
       </c>
       <c r="O7" t="n">
-        <v>5.082188460348561</v>
+        <v>5.082188460348599</v>
       </c>
       <c r="P7" t="n">
-        <v>6.550386505941452</v>
+        <v>6.550386505941489</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.070006937064943</v>
+        <v>3.070006937064967</v>
       </c>
       <c r="R7" t="n">
-        <v>2.911611967551852</v>
+        <v>2.911611967551887</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5631149019229</v>
+        <v>4.563114901922916</v>
       </c>
       <c r="T7" t="n">
-        <v>4.314147909189177</v>
+        <v>4.314147909189166</v>
       </c>
       <c r="U7" t="n">
-        <v>4.693593347981348</v>
+        <v>4.693593347981378</v>
       </c>
       <c r="V7" t="n">
-        <v>3.504892091933487</v>
+        <v>3.504892091933493</v>
       </c>
       <c r="W7" t="n">
-        <v>6.517552015972229</v>
+        <v>6.517552015972271</v>
       </c>
       <c r="X7" t="n">
-        <v>6.490591481136497</v>
+        <v>6.490591481136536</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.987715754262064</v>
+        <v>5.987715754262078</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.204646418663538</v>
+        <v>3.204646418663575</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.594556090002054</v>
+        <v>5.594556090002101</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.871467165810706</v>
+        <v>3.871467165810772</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.52838402908393</v>
+        <v>2.528384029083981</v>
       </c>
       <c r="C8" t="n">
-        <v>3.822712537051395</v>
+        <v>3.822712537051417</v>
       </c>
       <c r="D8" t="n">
-        <v>4.197327231804206</v>
+        <v>4.19732723180427</v>
       </c>
       <c r="E8" t="n">
-        <v>3.682296035421317</v>
+        <v>3.23604539490969</v>
       </c>
       <c r="F8" t="n">
-        <v>4.260235776158982</v>
+        <v>4.260235776158989</v>
       </c>
       <c r="G8" t="n">
-        <v>5.533474568312845</v>
+        <v>5.707255044495099</v>
       </c>
       <c r="H8" t="n">
-        <v>5.348987918933857</v>
+        <v>5.34898791893391</v>
       </c>
       <c r="I8" t="n">
-        <v>4.077857226350706</v>
+        <v>4.077857226350766</v>
       </c>
       <c r="J8" t="n">
-        <v>5.235014440467655</v>
+        <v>5.235014440467666</v>
       </c>
       <c r="K8" t="n">
-        <v>5.724405637803837</v>
+        <v>5.724405637803904</v>
       </c>
       <c r="L8" t="n">
-        <v>4.88168505404748</v>
+        <v>4.881685054047529</v>
       </c>
       <c r="M8" t="n">
-        <v>4.91576393825523</v>
+        <v>4.915763938254546</v>
       </c>
       <c r="N8" t="n">
-        <v>51.07886759202057</v>
+        <v>51.07886759202032</v>
       </c>
       <c r="O8" t="n">
-        <v>5.698178211407187</v>
+        <v>5.698178211407238</v>
       </c>
       <c r="P8" t="n">
-        <v>7.12261444324175</v>
+        <v>7.122614443241813</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.154341967074233</v>
+        <v>3.154341967074261</v>
       </c>
       <c r="R8" t="n">
-        <v>3.998723817796655</v>
+        <v>3.998723817796718</v>
       </c>
       <c r="S8" t="n">
-        <v>5.650226752167709</v>
+        <v>5.650226752167741</v>
       </c>
       <c r="T8" t="n">
-        <v>5.401259759433964</v>
+        <v>5.401259759434003</v>
       </c>
       <c r="U8" t="n">
-        <v>5.268420781356897</v>
+        <v>5.37448045642188</v>
       </c>
       <c r="V8" t="n">
-        <v>4.592003942178289</v>
+        <v>4.352190666713055</v>
       </c>
       <c r="W8" t="n">
-        <v>7.604828570442124</v>
+        <v>7.604828570442178</v>
       </c>
       <c r="X8" t="n">
-        <v>6.651737822297189</v>
+        <v>6.651737822297208</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.891427016365679</v>
+        <v>7.891427016365726</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.291758268908358</v>
+        <v>3.438114782635904</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.681667940246875</v>
+        <v>6.681667940246918</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.834019264455186</v>
+        <v>5.834019264455215</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.589800640749744</v>
+        <v>3.589800640749739</v>
       </c>
       <c r="C9" t="n">
-        <v>4.704368540308447</v>
+        <v>4.704368540308464</v>
       </c>
       <c r="D9" t="n">
-        <v>5.078983235061281</v>
+        <v>5.078983235061288</v>
       </c>
       <c r="E9" t="n">
-        <v>4.563952038678408</v>
+        <v>4.412015912648728</v>
       </c>
       <c r="F9" t="n">
-        <v>5.849405163249401</v>
+        <v>4.331808411791503</v>
       </c>
       <c r="G9" t="n">
-        <v>6.415130571569902</v>
+        <v>6.415131006508741</v>
       </c>
       <c r="H9" t="n">
-        <v>6.230643922190955</v>
+        <v>6.230643922190944</v>
       </c>
       <c r="I9" t="n">
-        <v>4.959513229607788</v>
+        <v>4.959513229607801</v>
       </c>
       <c r="J9" t="n">
-        <v>6.116670443724723</v>
+        <v>6.116670443724743</v>
       </c>
       <c r="K9" t="n">
-        <v>6.606061641060925</v>
+        <v>6.606061641060947</v>
       </c>
       <c r="L9" t="n">
-        <v>5.763341057304561</v>
+        <v>5.76334105730457</v>
       </c>
       <c r="M9" t="n">
-        <v>5.79741994151231</v>
+        <v>5.797419941512308</v>
       </c>
       <c r="N9" t="n">
-        <v>51.07886759202057</v>
+        <v>51.07886759202032</v>
       </c>
       <c r="O9" t="n">
-        <v>7.269119365027335</v>
+        <v>7.26911936502737</v>
       </c>
       <c r="P9" t="n">
-        <v>8.784764541130478</v>
+        <v>8.784764541130517</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.03877522550568</v>
+        <v>5.038775225505687</v>
       </c>
       <c r="R9" t="n">
-        <v>4.880379821053747</v>
+        <v>4.880379821053765</v>
       </c>
       <c r="S9" t="n">
-        <v>6.531882755424795</v>
+        <v>6.531882755424811</v>
       </c>
       <c r="T9" t="n">
-        <v>6.282915762691021</v>
+        <v>6.282915762691047</v>
       </c>
       <c r="U9" t="n">
-        <v>6.674940577577414</v>
+        <v>6.674940577577411</v>
       </c>
       <c r="V9" t="n">
-        <v>5.473659945435349</v>
+        <v>6.233341685624834</v>
       </c>
       <c r="W9" t="n">
-        <v>8.486319869474119</v>
+        <v>8.486319869474125</v>
       </c>
       <c r="X9" t="n">
-        <v>8.459359334638357</v>
+        <v>8.459359334638364</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.956483607763927</v>
+        <v>7.956483607763943</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.173414272165393</v>
+        <v>4.776508925097907</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.563323943503943</v>
+        <v>7.563323943503962</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.840235019312594</v>
+        <v>5.840235019312605</v>
       </c>
     </row>
   </sheetData>
@@ -2306,19 +2306,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.83583034254408</v>
+        <v>39.83583034254409</v>
       </c>
       <c r="C2" t="n">
-        <v>42.57620033197403</v>
+        <v>42.57620033197401</v>
       </c>
       <c r="D2" t="n">
-        <v>39.75687580323837</v>
+        <v>39.75687580323839</v>
       </c>
       <c r="E2" t="n">
-        <v>39.75875694247253</v>
+        <v>39.75875694247251</v>
       </c>
       <c r="F2" t="n">
-        <v>39.72749755775747</v>
+        <v>39.7274975577575</v>
       </c>
       <c r="G2" t="n">
         <v>40.02371054570597</v>
@@ -2330,25 +2330,25 @@
         <v>39.69891935782336</v>
       </c>
       <c r="J2" t="n">
-        <v>39.96711203454781</v>
+        <v>39.96711203454784</v>
       </c>
       <c r="K2" t="n">
         <v>39.8394456210986</v>
       </c>
       <c r="L2" t="n">
-        <v>39.91430612455409</v>
+        <v>39.91430612455408</v>
       </c>
       <c r="M2" t="n">
         <v>40.18603263417679</v>
       </c>
       <c r="N2" t="n">
-        <v>39.9410055357511</v>
+        <v>39.94100553575112</v>
       </c>
       <c r="O2" t="n">
         <v>44.10986533167497</v>
       </c>
       <c r="P2" t="n">
-        <v>40.10131605824851</v>
+        <v>40.10131605824854</v>
       </c>
       <c r="Q2" t="n">
         <v>39.83429821919813</v>
@@ -2357,31 +2357,31 @@
         <v>39.76733455105744</v>
       </c>
       <c r="S2" t="n">
-        <v>39.93607952856475</v>
+        <v>39.93607952856477</v>
       </c>
       <c r="T2" t="n">
-        <v>39.84303310872756</v>
+        <v>39.84303310872758</v>
       </c>
       <c r="U2" t="n">
         <v>43.62596333629708</v>
       </c>
       <c r="V2" t="n">
-        <v>39.85806465648854</v>
+        <v>39.85806465648855</v>
       </c>
       <c r="W2" t="n">
-        <v>46.22015569850177</v>
+        <v>46.22015569850176</v>
       </c>
       <c r="X2" t="n">
-        <v>39.86668786766842</v>
+        <v>39.86668786766843</v>
       </c>
       <c r="Y2" t="n">
         <v>40.17273335803421</v>
       </c>
       <c r="Z2" t="n">
-        <v>41.2670500400186</v>
+        <v>41.26705004001864</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.83541872336387</v>
+        <v>39.83541872336389</v>
       </c>
       <c r="AB2" t="n">
         <v>40.08947407011924</v>
@@ -2394,31 +2394,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.30875722035801</v>
+        <v>41.30875722035805</v>
       </c>
       <c r="C3" t="n">
-        <v>44.6055181860567</v>
+        <v>44.60551818605671</v>
       </c>
       <c r="D3" t="n">
-        <v>40.76054160804917</v>
+        <v>40.7605416080492</v>
       </c>
       <c r="E3" t="n">
-        <v>40.76797108579635</v>
+        <v>40.76797108579633</v>
       </c>
       <c r="F3" t="n">
-        <v>40.55052032249609</v>
+        <v>40.55052032249613</v>
       </c>
       <c r="G3" t="n">
-        <v>42.64860126311736</v>
+        <v>42.64860126311739</v>
       </c>
       <c r="H3" t="n">
-        <v>41.61836202622591</v>
+        <v>41.6183620262259</v>
       </c>
       <c r="I3" t="n">
-        <v>40.34659609729722</v>
+        <v>40.34659609729727</v>
       </c>
       <c r="J3" t="n">
-        <v>42.25124184202213</v>
+        <v>42.25124184202211</v>
       </c>
       <c r="K3" t="n">
         <v>41.34193391811797</v>
@@ -2427,49 +2427,49 @@
         <v>41.87814452987799</v>
       </c>
       <c r="M3" t="n">
-        <v>43.83119790305864</v>
+        <v>43.8311979030587</v>
       </c>
       <c r="N3" t="n">
-        <v>42.07328736623683</v>
+        <v>42.07328736623685</v>
       </c>
       <c r="O3" t="n">
-        <v>48.9013123756559</v>
+        <v>48.90131237565587</v>
       </c>
       <c r="P3" t="n">
-        <v>43.19977630585948</v>
+        <v>43.19977630585956</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.3111578331478</v>
+        <v>41.31115783314782</v>
       </c>
       <c r="R3" t="n">
-        <v>40.83815380859929</v>
+        <v>40.83815380859927</v>
       </c>
       <c r="S3" t="n">
-        <v>42.02552661064605</v>
+        <v>42.02552661064609</v>
       </c>
       <c r="T3" t="n">
-        <v>41.37713875922041</v>
+        <v>41.37713875922042</v>
       </c>
       <c r="U3" t="n">
-        <v>48.68191698440831</v>
+        <v>48.68191698440832</v>
       </c>
       <c r="V3" t="n">
-        <v>41.46419901786842</v>
+        <v>41.46419901786849</v>
       </c>
       <c r="W3" t="n">
-        <v>53.5315466949622</v>
+        <v>53.53154669496217</v>
       </c>
       <c r="X3" t="n">
-        <v>41.54394240877481</v>
+        <v>41.54394240877477</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.72166871237665</v>
+        <v>43.72166871237663</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.06818751551229</v>
+        <v>44.06818751551228</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.3161814458726</v>
+        <v>41.31618144587265</v>
       </c>
       <c r="AB3" t="n">
         <v>43.14507458427327</v>
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.155242207961408</v>
+        <v>6.155242207961414</v>
       </c>
       <c r="C4" t="n">
-        <v>3.60162312084804</v>
+        <v>3.601623120848047</v>
       </c>
       <c r="D4" t="n">
-        <v>5.263414365621397</v>
+        <v>5.263414365621415</v>
       </c>
       <c r="E4" t="n">
-        <v>5.284662698637447</v>
+        <v>5.284662698637454</v>
       </c>
       <c r="F4" t="n">
         <v>4.931573568254043</v>
       </c>
       <c r="G4" t="n">
-        <v>8.277435531838679</v>
+        <v>8.27743553183867</v>
       </c>
       <c r="H4" t="n">
-        <v>6.607625004621103</v>
+        <v>6.607625004621114</v>
       </c>
       <c r="I4" t="n">
-        <v>4.608769653376608</v>
+        <v>4.608769653376616</v>
       </c>
       <c r="J4" t="n">
-        <v>7.638275330465383</v>
+        <v>7.638275330465388</v>
       </c>
       <c r="K4" t="n">
-        <v>6.196078442345464</v>
+        <v>6.196078442345472</v>
       </c>
       <c r="L4" t="n">
-        <v>7.041662266407836</v>
+        <v>7.041662266407846</v>
       </c>
       <c r="M4" t="n">
-        <v>10.10446356932529</v>
+        <v>10.1044635693253</v>
       </c>
       <c r="N4" t="n">
-        <v>7.343244398214409</v>
+        <v>7.343244398214406</v>
       </c>
       <c r="O4" t="n">
-        <v>7.276350903003605</v>
+        <v>7.276350903003609</v>
       </c>
       <c r="P4" t="n">
-        <v>9.154025496306598</v>
+        <v>9.154025496306616</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.137936169957598</v>
+        <v>6.137936169957607</v>
       </c>
       <c r="R4" t="n">
-        <v>5.381550733499131</v>
+        <v>5.38155073349914</v>
       </c>
       <c r="S4" t="n">
-        <v>7.287602880969288</v>
+        <v>7.28760288096931</v>
       </c>
       <c r="T4" t="n">
-        <v>6.236600765440556</v>
+        <v>6.236600765440564</v>
       </c>
       <c r="U4" t="n">
-        <v>8.425362461762488</v>
+        <v>8.4253624617625</v>
       </c>
       <c r="V4" t="n">
-        <v>6.407071747987704</v>
+        <v>6.407071747987708</v>
       </c>
       <c r="W4" t="n">
-        <v>9.600089767962345</v>
+        <v>9.600089767962334</v>
       </c>
       <c r="X4" t="n">
-        <v>6.503792149404046</v>
+        <v>6.503792149404055</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.941029358292697</v>
+        <v>9.941029358292703</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.96904829161423</v>
+        <v>6.969048291614241</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.150592779967141</v>
+        <v>6.150592779967139</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.006820148384744</v>
+        <v>9.006820148384733</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.11922411012935</v>
+        <v>67.11922411012932</v>
       </c>
       <c r="C5" t="n">
-        <v>24.80227628112812</v>
+        <v>24.80227628112808</v>
       </c>
       <c r="D5" t="n">
-        <v>58.75845602341132</v>
+        <v>58.75845602341119</v>
       </c>
       <c r="E5" t="n">
-        <v>55.82535797624915</v>
+        <v>55.82535797624919</v>
       </c>
       <c r="F5" t="n">
-        <v>52.29089969682663</v>
+        <v>52.29089969682666</v>
       </c>
       <c r="G5" t="n">
         <v>106.6524090997544</v>
       </c>
       <c r="H5" t="n">
-        <v>88.89045917693483</v>
+        <v>88.89045917693485</v>
       </c>
       <c r="I5" t="n">
-        <v>46.20949586149738</v>
+        <v>46.2094958614974</v>
       </c>
       <c r="J5" t="n">
-        <v>98.22797490665995</v>
+        <v>98.22797490666004</v>
       </c>
       <c r="K5" t="n">
-        <v>71.99257109178697</v>
+        <v>71.99257109178687</v>
       </c>
       <c r="L5" t="n">
-        <v>89.0527542105241</v>
+        <v>89.05275421052424</v>
       </c>
       <c r="M5" t="n">
-        <v>156.5550439487515</v>
+        <v>156.5550439487519</v>
       </c>
       <c r="N5" t="n">
-        <v>111.9211976713966</v>
+        <v>111.9211976713965</v>
       </c>
       <c r="O5" t="n">
-        <v>84.39027218998694</v>
+        <v>84.390272189987</v>
       </c>
       <c r="P5" t="n">
-        <v>121.7256282579152</v>
+        <v>121.7256282579155</v>
       </c>
       <c r="Q5" t="n">
         <v>74.20854568279309</v>
       </c>
       <c r="R5" t="n">
-        <v>62.64260237080189</v>
+        <v>62.64260237080197</v>
       </c>
       <c r="S5" t="n">
-        <v>89.24497670546471</v>
+        <v>89.24497670546508</v>
       </c>
       <c r="T5" t="n">
-        <v>78.09824929713858</v>
+        <v>78.09824929713852</v>
       </c>
       <c r="U5" t="n">
-        <v>113.0230031276186</v>
+        <v>113.0230031276185</v>
       </c>
       <c r="V5" t="n">
-        <v>70.06351359425274</v>
+        <v>70.06351359425261</v>
       </c>
       <c r="W5" t="n">
         <v>138.4161708713941</v>
       </c>
       <c r="X5" t="n">
-        <v>82.02599208764509</v>
+        <v>82.02599208764545</v>
       </c>
       <c r="Y5" t="n">
-        <v>143.7543936150537</v>
+        <v>143.754393615054</v>
       </c>
       <c r="Z5" t="n">
-        <v>83.43141489361511</v>
+        <v>83.43141489361498</v>
       </c>
       <c r="AA5" t="n">
-        <v>72.79414729917978</v>
+        <v>72.79414729917991</v>
       </c>
       <c r="AB5" t="n">
-        <v>139.5865900320196</v>
+        <v>139.5865900320194</v>
       </c>
     </row>
     <row r="6">
@@ -2658,34 +2658,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>149.6131408799583</v>
+        <v>125.670541972539</v>
       </c>
       <c r="C6" t="n">
         <v>147.0595217928449</v>
       </c>
       <c r="D6" t="n">
-        <v>124.778714130199</v>
+        <v>148.7213130376183</v>
       </c>
       <c r="E6" t="n">
         <v>124.7999624632151</v>
       </c>
       <c r="F6" t="n">
-        <v>148.3894722402508</v>
+        <v>124.4468733328317</v>
       </c>
       <c r="G6" t="n">
-        <v>151.7353342038355</v>
+        <v>127.7927352964164</v>
       </c>
       <c r="H6" t="n">
-        <v>126.1229247691987</v>
+        <v>150.065523676618</v>
       </c>
       <c r="I6" t="n">
-        <v>124.1240694179542</v>
+        <v>124.1240694179543</v>
       </c>
       <c r="J6" t="n">
         <v>151.0961740024621</v>
       </c>
       <c r="K6" t="n">
-        <v>125.7113782069231</v>
+        <v>149.6539771143424</v>
       </c>
       <c r="L6" t="n">
         <v>126.5569620309855</v>
@@ -2697,43 +2697,43 @@
         <v>126.8684907339696</v>
       </c>
       <c r="O6" t="n">
-        <v>150.8003070305169</v>
+        <v>150.8003070305168</v>
       </c>
       <c r="P6" t="n">
-        <v>152.6778797577499</v>
+        <v>152.67787975775</v>
       </c>
       <c r="Q6" t="n">
-        <v>125.6532359345352</v>
+        <v>149.5958348419544</v>
       </c>
       <c r="R6" t="n">
-        <v>124.8968504980768</v>
+        <v>148.8394494054959</v>
       </c>
       <c r="S6" t="n">
-        <v>126.8029026455469</v>
+        <v>150.7455015529661</v>
       </c>
       <c r="T6" t="n">
-        <v>149.6944994374373</v>
+        <v>125.7519005300183</v>
       </c>
       <c r="U6" t="n">
-        <v>151.9029485264332</v>
+        <v>127.9603496190142</v>
       </c>
       <c r="V6" t="n">
-        <v>149.8649704199844</v>
+        <v>149.8649704199845</v>
       </c>
       <c r="W6" t="n">
         <v>153.1240718382445</v>
       </c>
       <c r="X6" t="n">
-        <v>126.0190919139816</v>
+        <v>149.9616908214009</v>
       </c>
       <c r="Y6" t="n">
         <v>134.7290106129945</v>
       </c>
       <c r="Z6" t="n">
-        <v>126.4843480561918</v>
+        <v>150.426946963611</v>
       </c>
       <c r="AA6" t="n">
-        <v>149.6084914519639</v>
+        <v>125.6658925445448</v>
       </c>
       <c r="AB6" t="n">
         <v>128.544399401284</v>
@@ -2746,34 +2746,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.40737661928378</v>
+        <v>7.407376619283772</v>
       </c>
       <c r="C7" t="n">
-        <v>4.853757532170417</v>
+        <v>4.853757532170413</v>
       </c>
       <c r="D7" t="n">
-        <v>6.515548776943777</v>
+        <v>6.515548776943779</v>
       </c>
       <c r="E7" t="n">
-        <v>6.536797109959823</v>
+        <v>6.53679710995982</v>
       </c>
       <c r="F7" t="n">
         <v>6.183707979576412</v>
       </c>
       <c r="G7" t="n">
-        <v>9.529569943161048</v>
+        <v>9.529569943161038</v>
       </c>
       <c r="H7" t="n">
-        <v>7.859759415943481</v>
+        <v>7.859759415943484</v>
       </c>
       <c r="I7" t="n">
-        <v>5.860904064698985</v>
+        <v>5.860904064698983</v>
       </c>
       <c r="J7" t="n">
-        <v>8.890409741787764</v>
+        <v>8.890409741787757</v>
       </c>
       <c r="K7" t="n">
-        <v>7.448212853667845</v>
+        <v>7.448212853667836</v>
       </c>
       <c r="L7" t="n">
         <v>8.293796677730212</v>
@@ -2785,46 +2785,46 @@
         <v>8.595378809536779</v>
       </c>
       <c r="O7" t="n">
-        <v>8.528472717512843</v>
+        <v>8.528472717512841</v>
       </c>
       <c r="P7" t="n">
-        <v>10.40614731081582</v>
+        <v>10.40614731081585</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.390070581279978</v>
+        <v>7.390070581279968</v>
       </c>
       <c r="R7" t="n">
-        <v>6.633685144821511</v>
+        <v>6.633685144821509</v>
       </c>
       <c r="S7" t="n">
-        <v>8.539737292291665</v>
+        <v>8.539737292291676</v>
       </c>
       <c r="T7" t="n">
-        <v>7.488735176762925</v>
+        <v>7.488735176762928</v>
       </c>
       <c r="U7" t="n">
-        <v>9.696607934016976</v>
+        <v>9.696607934016987</v>
       </c>
       <c r="V7" t="n">
         <v>7.659206159310072</v>
       </c>
       <c r="W7" t="n">
-        <v>10.85222417928472</v>
+        <v>10.8522241792847</v>
       </c>
       <c r="X7" t="n">
-        <v>7.755926560726418</v>
+        <v>7.755926560726422</v>
       </c>
       <c r="Y7" t="n">
         <v>11.21285116228903</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.221182702936609</v>
+        <v>8.221182702936607</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.402727191289509</v>
+        <v>7.402727191289508</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.25895455970712</v>
+        <v>10.2589545597071</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.936062956553239</v>
+        <v>7.936062956553231</v>
       </c>
       <c r="C8" t="n">
-        <v>6.74268783037297</v>
+        <v>6.742687830372969</v>
       </c>
       <c r="D8" t="n">
-        <v>8.404479075146332</v>
+        <v>8.404479075146336</v>
       </c>
       <c r="E8" t="n">
-        <v>8.425727408162377</v>
+        <v>7.701437624061382</v>
       </c>
       <c r="F8" t="n">
-        <v>6.924304428220563</v>
+        <v>6.924304428220567</v>
       </c>
       <c r="G8" t="n">
-        <v>11.41850024136361</v>
+        <v>11.70055568767426</v>
       </c>
       <c r="H8" t="n">
-        <v>9.748689714146037</v>
+        <v>9.748689714146032</v>
       </c>
       <c r="I8" t="n">
-        <v>7.749834362901537</v>
+        <v>7.749834362901531</v>
       </c>
       <c r="J8" t="n">
         <v>10.77934003999031</v>
       </c>
       <c r="K8" t="n">
-        <v>9.337143151870398</v>
+        <v>9.337143151870404</v>
       </c>
       <c r="L8" t="n">
-        <v>10.18272697593277</v>
+        <v>10.18272697593276</v>
       </c>
       <c r="M8" t="n">
-        <v>13.24552827885023</v>
+        <v>13.24552827885002</v>
       </c>
       <c r="N8" t="n">
-        <v>9.429892473643248</v>
+        <v>9.429892473643235</v>
       </c>
       <c r="O8" t="n">
         <v>9.652761823784246</v>
       </c>
       <c r="P8" t="n">
-        <v>11.45940854215056</v>
+        <v>11.45940854215058</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.651437934722532</v>
+        <v>7.651437934722538</v>
       </c>
       <c r="R8" t="n">
-        <v>8.522615443024064</v>
+        <v>8.522615443024051</v>
       </c>
       <c r="S8" t="n">
-        <v>10.42866759049422</v>
+        <v>10.42866759049423</v>
       </c>
       <c r="T8" t="n">
-        <v>9.377665474965488</v>
+        <v>9.377665474965479</v>
       </c>
       <c r="U8" t="n">
-        <v>10.74868103039763</v>
+        <v>10.92176075966978</v>
       </c>
       <c r="V8" t="n">
-        <v>9.54813645751263</v>
+        <v>9.175879405146745</v>
       </c>
       <c r="W8" t="n">
         <v>12.74142180238525</v>
       </c>
       <c r="X8" t="n">
-        <v>8.141962974794529</v>
+        <v>8.141962974794543</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.45349369330802</v>
+        <v>14.45349369330803</v>
       </c>
       <c r="Z8" t="n">
-        <v>10.11011300113917</v>
+        <v>8.724601810459863</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.29165748949206</v>
+        <v>9.291657489492055</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.56877341496665</v>
+        <v>13.56877341496663</v>
       </c>
     </row>
     <row r="9">
@@ -2928,16 +2928,16 @@
         <v>9.751279912490292</v>
       </c>
       <c r="D9" t="n">
-        <v>11.41307115726364</v>
+        <v>11.41307115726365</v>
       </c>
       <c r="E9" t="n">
-        <v>11.43431949027969</v>
+        <v>11.10883756904192</v>
       </c>
       <c r="F9" t="n">
-        <v>11.08123035989628</v>
+        <v>7.83019591690352</v>
       </c>
       <c r="G9" t="n">
-        <v>14.42709232348091</v>
+        <v>14.42709272252951</v>
       </c>
       <c r="H9" t="n">
         <v>12.75728179626335</v>
@@ -2946,58 +2946,58 @@
         <v>10.75842644501885</v>
       </c>
       <c r="J9" t="n">
-        <v>13.78793212210763</v>
+        <v>13.78793212210762</v>
       </c>
       <c r="K9" t="n">
         <v>12.34573523398771</v>
       </c>
       <c r="L9" t="n">
-        <v>13.19131905805008</v>
+        <v>13.1913190580501</v>
       </c>
       <c r="M9" t="n">
-        <v>16.25412036096754</v>
+        <v>16.25412036096753</v>
       </c>
       <c r="N9" t="n">
-        <v>13.49290118985666</v>
+        <v>13.49290118985665</v>
       </c>
       <c r="O9" t="n">
         <v>13.8933665039217</v>
       </c>
       <c r="P9" t="n">
-        <v>15.87268353292924</v>
+        <v>15.87268353292926</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.28759336064847</v>
+        <v>12.28759336064845</v>
       </c>
       <c r="R9" t="n">
         <v>11.53120752514138</v>
       </c>
       <c r="S9" t="n">
-        <v>13.43725967261154</v>
+        <v>13.43725967261155</v>
       </c>
       <c r="T9" t="n">
         <v>12.3862575570828</v>
       </c>
       <c r="U9" t="n">
-        <v>14.59470664607869</v>
+        <v>14.59470664607871</v>
       </c>
       <c r="V9" t="n">
-        <v>12.55672853962996</v>
+        <v>14.18413687408953</v>
       </c>
       <c r="W9" t="n">
-        <v>15.74974655960458</v>
+        <v>15.74974655960459</v>
       </c>
       <c r="X9" t="n">
         <v>12.65344894104629</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.11037354260892</v>
+        <v>16.11037354260891</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.11870508325648</v>
+        <v>12.26844393867772</v>
       </c>
       <c r="AA9" t="n">
-        <v>12.30024957160939</v>
+        <v>12.30024957160938</v>
       </c>
       <c r="AB9" t="n">
         <v>15.15647694002699</v>
@@ -3166,49 +3166,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.6811195977368</v>
+        <v>39.68111959773678</v>
       </c>
       <c r="C2" t="n">
-        <v>42.53375649812867</v>
+        <v>42.5337564981287</v>
       </c>
       <c r="D2" t="n">
         <v>39.70815636860006</v>
       </c>
       <c r="E2" t="n">
-        <v>39.62761023782727</v>
+        <v>39.62761023782725</v>
       </c>
       <c r="F2" t="n">
-        <v>39.6296258768629</v>
+        <v>39.62962587686292</v>
       </c>
       <c r="G2" t="n">
-        <v>39.905434979878</v>
+        <v>39.90543497987802</v>
       </c>
       <c r="H2" t="n">
-        <v>39.74577652075352</v>
+        <v>39.74577652075353</v>
       </c>
       <c r="I2" t="n">
-        <v>39.65284841847647</v>
+        <v>39.65284841847644</v>
       </c>
       <c r="J2" t="n">
         <v>39.84135810699775</v>
       </c>
       <c r="K2" t="n">
-        <v>39.69258601115407</v>
+        <v>39.69258601115406</v>
       </c>
       <c r="L2" t="n">
-        <v>39.77136953221928</v>
+        <v>39.7713695322193</v>
       </c>
       <c r="M2" t="n">
-        <v>40.02567265297894</v>
+        <v>40.02567265297897</v>
       </c>
       <c r="N2" t="n">
-        <v>39.76732752906173</v>
+        <v>39.76732752906171</v>
       </c>
       <c r="O2" t="n">
         <v>43.92218381852712</v>
       </c>
       <c r="P2" t="n">
-        <v>39.98976210041658</v>
+        <v>39.9897621004166</v>
       </c>
       <c r="Q2" t="n">
         <v>39.69551760920189</v>
@@ -3217,31 +3217,31 @@
         <v>39.63589320337469</v>
       </c>
       <c r="S2" t="n">
-        <v>39.81426140833877</v>
+        <v>39.81426140833879</v>
       </c>
       <c r="T2" t="n">
-        <v>39.75362163601462</v>
+        <v>39.75362163601464</v>
       </c>
       <c r="U2" t="n">
-        <v>43.36364630624843</v>
+        <v>43.36364630624847</v>
       </c>
       <c r="V2" t="n">
-        <v>39.7537613367642</v>
+        <v>39.75376133676419</v>
       </c>
       <c r="W2" t="n">
-        <v>45.99988190814981</v>
+        <v>45.99988190814985</v>
       </c>
       <c r="X2" t="n">
-        <v>39.83644516998638</v>
+        <v>39.83644516998643</v>
       </c>
       <c r="Y2" t="n">
-        <v>40.07623016177869</v>
+        <v>40.07623016177872</v>
       </c>
       <c r="Z2" t="n">
-        <v>41.06033236737354</v>
+        <v>41.06033236737353</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.74460360177578</v>
+        <v>39.74460360177577</v>
       </c>
       <c r="AB2" t="n">
         <v>39.96428634312679</v>
@@ -3254,31 +3254,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.81075123235859</v>
+        <v>40.81075123235858</v>
       </c>
       <c r="C3" t="n">
-        <v>44.88551156421224</v>
+        <v>44.88551156421227</v>
       </c>
       <c r="D3" t="n">
-        <v>41.01545750182925</v>
+        <v>41.01545750182927</v>
       </c>
       <c r="E3" t="n">
         <v>40.4350867665943</v>
       </c>
       <c r="F3" t="n">
-        <v>40.45340211753512</v>
+        <v>40.45340211753515</v>
       </c>
       <c r="G3" t="n">
-        <v>42.40489207698045</v>
+        <v>42.40489207698049</v>
       </c>
       <c r="H3" t="n">
-        <v>41.2921422736158</v>
+        <v>41.29214227361586</v>
       </c>
       <c r="I3" t="n">
-        <v>40.62143190072875</v>
+        <v>40.62143190072882</v>
       </c>
       <c r="J3" t="n">
-        <v>41.95577353184597</v>
+        <v>41.95577353184598</v>
       </c>
       <c r="K3" t="n">
         <v>40.89244244678287</v>
@@ -3287,52 +3287,52 @@
         <v>41.46014815372749</v>
       </c>
       <c r="M3" t="n">
-        <v>43.28910149021416</v>
+        <v>43.28910149021417</v>
       </c>
       <c r="N3" t="n">
-        <v>41.43602945871064</v>
+        <v>41.43602945871062</v>
       </c>
       <c r="O3" t="n">
-        <v>48.59679525210936</v>
+        <v>48.59679525210935</v>
       </c>
       <c r="P3" t="n">
-        <v>43.00420837162475</v>
+        <v>43.00420837162478</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.92066492364869</v>
+        <v>40.92066492364867</v>
       </c>
       <c r="R3" t="n">
         <v>40.50160942478644</v>
       </c>
       <c r="S3" t="n">
-        <v>41.75814733851804</v>
+        <v>41.75814733851809</v>
       </c>
       <c r="T3" t="n">
         <v>41.34216866471559</v>
       </c>
       <c r="U3" t="n">
-        <v>47.78053818712727</v>
+        <v>47.78053818712729</v>
       </c>
       <c r="V3" t="n">
-        <v>41.32128833027399</v>
+        <v>41.32128833027398</v>
       </c>
       <c r="W3" t="n">
-        <v>52.96506302916258</v>
+        <v>52.9650630291626</v>
       </c>
       <c r="X3" t="n">
-        <v>41.93092341075098</v>
+        <v>41.93092341075095</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.63640715648472</v>
+        <v>43.63640715648477</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.52048994471276</v>
+        <v>43.52048994471277</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.27112562375428</v>
+        <v>41.27112562375426</v>
       </c>
       <c r="AB3" t="n">
-        <v>42.85282770329669</v>
+        <v>42.8528277032967</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.303407180493444</v>
+        <v>5.303407180493443</v>
       </c>
       <c r="C4" t="n">
-        <v>3.981369745139892</v>
+        <v>3.981369745139888</v>
       </c>
       <c r="D4" t="n">
-        <v>5.608799944922933</v>
+        <v>5.608799944922935</v>
       </c>
       <c r="E4" t="n">
-        <v>4.698994344793722</v>
+        <v>4.698994344793723</v>
       </c>
       <c r="F4" t="n">
-        <v>4.721761914941344</v>
+        <v>4.721761914941345</v>
       </c>
       <c r="G4" t="n">
-        <v>7.837152611952565</v>
+        <v>7.837152611952563</v>
       </c>
       <c r="H4" t="n">
-        <v>6.033736869621817</v>
+        <v>6.03373686962181</v>
       </c>
       <c r="I4" t="n">
-        <v>4.984071205362678</v>
+        <v>4.984071205362687</v>
       </c>
       <c r="J4" t="n">
-        <v>7.113621360476089</v>
+        <v>7.113621360476093</v>
       </c>
       <c r="K4" t="n">
-        <v>5.432925594852517</v>
+        <v>5.432925594852524</v>
       </c>
       <c r="L4" t="n">
-        <v>6.322821707494128</v>
+        <v>6.322821707494127</v>
       </c>
       <c r="M4" t="n">
-        <v>9.190345647715063</v>
+        <v>9.190345647715064</v>
       </c>
       <c r="N4" t="n">
-        <v>6.277165422416353</v>
+        <v>6.277165422416345</v>
       </c>
       <c r="O4" t="n">
-        <v>6.943657542893034</v>
+        <v>6.94365754289305</v>
       </c>
       <c r="P4" t="n">
-        <v>8.789666230828022</v>
+        <v>8.78966623082805</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.466039343404096</v>
+        <v>5.466039343404093</v>
       </c>
       <c r="R4" t="n">
-        <v>4.792554251004198</v>
+        <v>4.79255425100419</v>
       </c>
       <c r="S4" t="n">
-        <v>6.807305179501909</v>
+        <v>6.807305179501916</v>
       </c>
       <c r="T4" t="n">
-        <v>6.122351055427123</v>
+        <v>6.122351055427131</v>
       </c>
       <c r="U4" t="n">
-        <v>7.118342214337422</v>
+        <v>7.11834221433744</v>
       </c>
       <c r="V4" t="n">
-        <v>6.125293606505562</v>
+        <v>6.125293606505565</v>
       </c>
       <c r="W4" t="n">
-        <v>8.837149125368455</v>
+        <v>8.837149125368445</v>
       </c>
       <c r="X4" t="n">
-        <v>7.057880972346379</v>
+        <v>7.057880972346396</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.747410671462726</v>
+        <v>9.747410671462731</v>
       </c>
       <c r="Z4" t="n">
         <v>6.21190976178495</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.020488210198535</v>
+        <v>6.020488210198542</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.486410897611497</v>
+        <v>8.486410897611501</v>
       </c>
     </row>
     <row r="5">
@@ -3430,82 +3430,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.47037193772566</v>
+        <v>52.47037193772577</v>
       </c>
       <c r="C5" t="n">
-        <v>32.13369303971805</v>
+        <v>32.13369303971807</v>
       </c>
       <c r="D5" t="n">
-        <v>63.95751219251086</v>
+        <v>63.957512192511</v>
       </c>
       <c r="E5" t="n">
-        <v>45.01120712379119</v>
+        <v>45.01120712379123</v>
       </c>
       <c r="F5" t="n">
-        <v>47.45032282716665</v>
+        <v>47.45032282716662</v>
       </c>
       <c r="G5" t="n">
-        <v>93.75513491715279</v>
+        <v>93.75513491715274</v>
       </c>
       <c r="H5" t="n">
-        <v>75.71637942294838</v>
+        <v>75.71637942294825</v>
       </c>
       <c r="I5" t="n">
-        <v>53.27609107100957</v>
+        <v>53.27609107100969</v>
       </c>
       <c r="J5" t="n">
-        <v>85.20428884989258</v>
+        <v>85.20428884989265</v>
       </c>
       <c r="K5" t="n">
-        <v>54.68589863134853</v>
+        <v>54.68589863134866</v>
       </c>
       <c r="L5" t="n">
-        <v>73.2359214413833</v>
+        <v>73.23592144138341</v>
       </c>
       <c r="M5" t="n">
-        <v>132.5900536488055</v>
+        <v>132.5900536488056</v>
       </c>
       <c r="N5" t="n">
-        <v>84.24513619444355</v>
+        <v>84.24513619444382</v>
       </c>
       <c r="O5" t="n">
-        <v>75.62393508636629</v>
+        <v>75.6239350863664</v>
       </c>
       <c r="P5" t="n">
-        <v>109.2905069869407</v>
+        <v>109.2905069869414</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.05435896091245</v>
+        <v>59.05435896091251</v>
       </c>
       <c r="R5" t="n">
-        <v>50.50431361954508</v>
+        <v>50.50431361954506</v>
       </c>
       <c r="S5" t="n">
-        <v>77.59564863053743</v>
+        <v>77.59564863053762</v>
       </c>
       <c r="T5" t="n">
-        <v>74.19267102930529</v>
+        <v>74.19267102930549</v>
       </c>
       <c r="U5" t="n">
-        <v>85.10526507608786</v>
+        <v>85.10526507608829</v>
       </c>
       <c r="V5" t="n">
-        <v>62.88454372217119</v>
+        <v>62.88454372217106</v>
       </c>
       <c r="W5" t="n">
-        <v>118.934190606066</v>
+        <v>118.9341906060658</v>
       </c>
       <c r="X5" t="n">
-        <v>89.51556147916182</v>
+        <v>89.51556147916206</v>
       </c>
       <c r="Y5" t="n">
-        <v>134.3756378548454</v>
+        <v>134.3756378548456</v>
       </c>
       <c r="Z5" t="n">
-        <v>64.30112390878763</v>
+        <v>64.3011239087877</v>
       </c>
       <c r="AA5" t="n">
-        <v>68.92886110351422</v>
+        <v>68.92886110351424</v>
       </c>
       <c r="AB5" t="n">
         <v>124.0650383520079</v>
@@ -3518,37 +3518,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>138.9151305120827</v>
+        <v>116.6559632266844</v>
       </c>
       <c r="C6" t="n">
         <v>115.3339257913309</v>
       </c>
       <c r="D6" t="n">
-        <v>139.2205232765122</v>
+        <v>139.2205232765123</v>
       </c>
       <c r="E6" t="n">
         <v>116.0515503909847</v>
       </c>
       <c r="F6" t="n">
-        <v>116.0743179611323</v>
+        <v>138.3334852465308</v>
       </c>
       <c r="G6" t="n">
-        <v>141.448875943542</v>
+        <v>119.1897086581436</v>
       </c>
       <c r="H6" t="n">
-        <v>117.3862929158127</v>
+        <v>117.3862929158128</v>
       </c>
       <c r="I6" t="n">
-        <v>138.5957945369521</v>
+        <v>116.3366272515536</v>
       </c>
       <c r="J6" t="n">
-        <v>140.7253446920656</v>
+        <v>140.7253446920655</v>
       </c>
       <c r="K6" t="n">
-        <v>116.7854816410436</v>
+        <v>139.0446489264419</v>
       </c>
       <c r="L6" t="n">
-        <v>139.9345450390836</v>
+        <v>117.6753777536851</v>
       </c>
       <c r="M6" t="n">
         <v>142.8020689793044</v>
@@ -3557,43 +3557,43 @@
         <v>117.6391302138932</v>
       </c>
       <c r="O6" t="n">
-        <v>140.6188678225435</v>
+        <v>118.3056223343699</v>
       </c>
       <c r="P6" t="n">
-        <v>142.4646413033338</v>
+        <v>142.4646413033337</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.0777626749934</v>
+        <v>139.0777626749935</v>
       </c>
       <c r="R6" t="n">
-        <v>138.4042775825937</v>
+        <v>138.4042775825936</v>
       </c>
       <c r="S6" t="n">
         <v>118.1598612256929</v>
       </c>
       <c r="T6" t="n">
-        <v>117.474907101618</v>
+        <v>117.4749071016181</v>
       </c>
       <c r="U6" t="n">
-        <v>140.74901763565</v>
+        <v>118.4898503502518</v>
       </c>
       <c r="V6" t="n">
         <v>139.7370169380949</v>
       </c>
       <c r="W6" t="n">
-        <v>142.5123908397238</v>
+        <v>125.8891788411457</v>
       </c>
       <c r="X6" t="n">
-        <v>118.4104370185373</v>
+        <v>118.4104370185374</v>
       </c>
       <c r="Y6" t="n">
-        <v>126.0127404354663</v>
+        <v>126.0127404354664</v>
       </c>
       <c r="Z6" t="n">
-        <v>139.8236330933744</v>
+        <v>117.5644658079759</v>
       </c>
       <c r="AA6" t="n">
-        <v>117.3730442563895</v>
+        <v>139.632211541788</v>
       </c>
       <c r="AB6" t="n">
         <v>119.8600615887886</v>
@@ -3606,37 +3606,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.397264144282526</v>
+        <v>6.39726414428253</v>
       </c>
       <c r="C7" t="n">
-        <v>5.07522670892898</v>
+        <v>5.075226708928978</v>
       </c>
       <c r="D7" t="n">
-        <v>6.702656908712024</v>
+        <v>6.702656908712026</v>
       </c>
       <c r="E7" t="n">
         <v>5.792851308582811</v>
       </c>
       <c r="F7" t="n">
-        <v>5.815618878730429</v>
+        <v>5.815618878730431</v>
       </c>
       <c r="G7" t="n">
-        <v>8.931009575741642</v>
+        <v>8.931009575741649</v>
       </c>
       <c r="H7" t="n">
-        <v>7.127593833410902</v>
+        <v>7.127593833410899</v>
       </c>
       <c r="I7" t="n">
-        <v>6.077928169151766</v>
+        <v>6.077928169151776</v>
       </c>
       <c r="J7" t="n">
-        <v>8.207478324265173</v>
+        <v>8.20747832426518</v>
       </c>
       <c r="K7" t="n">
-        <v>6.526782558641601</v>
+        <v>6.526782558641611</v>
       </c>
       <c r="L7" t="n">
-        <v>7.416678671283208</v>
+        <v>7.416678671283207</v>
       </c>
       <c r="M7" t="n">
         <v>10.28420261150415</v>
@@ -3645,46 +3645,46 @@
         <v>7.371022386205438</v>
       </c>
       <c r="O7" t="n">
-        <v>8.037507084590278</v>
+        <v>8.037507084590281</v>
       </c>
       <c r="P7" t="n">
-        <v>9.88351577252525</v>
+        <v>9.883515772525289</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.559896307193185</v>
+        <v>6.559896307193183</v>
       </c>
       <c r="R7" t="n">
-        <v>5.886411214793283</v>
+        <v>5.886411214793282</v>
       </c>
       <c r="S7" t="n">
-        <v>7.901162143290989</v>
+        <v>7.901162143291002</v>
       </c>
       <c r="T7" t="n">
-        <v>7.216208019216211</v>
+        <v>7.216208019216221</v>
       </c>
       <c r="U7" t="n">
-        <v>8.225994639174623</v>
+        <v>8.225994639174642</v>
       </c>
       <c r="V7" t="n">
-        <v>7.219150570294655</v>
+        <v>7.219150570294652</v>
       </c>
       <c r="W7" t="n">
-        <v>9.931006089157544</v>
+        <v>9.931006089157538</v>
       </c>
       <c r="X7" t="n">
-        <v>8.15173793613547</v>
+        <v>8.151737936135477</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.86021972497513</v>
+        <v>10.86021972497514</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.305766725574033</v>
+        <v>7.305766725574037</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.114345173987622</v>
+        <v>7.114345173987624</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.580267861400596</v>
+        <v>9.580267861400587</v>
       </c>
     </row>
     <row r="8">
@@ -3694,82 +3694,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.845444930273985</v>
+        <v>6.845444930273979</v>
       </c>
       <c r="C8" t="n">
         <v>6.701681640551943</v>
       </c>
       <c r="D8" t="n">
-        <v>8.329111840334987</v>
+        <v>8.329111840334994</v>
       </c>
       <c r="E8" t="n">
-        <v>7.419306240205778</v>
+        <v>6.791910014949115</v>
       </c>
       <c r="F8" t="n">
-        <v>6.447361005620421</v>
+        <v>6.447361005620422</v>
       </c>
       <c r="G8" t="n">
-        <v>10.55746450736462</v>
+        <v>10.80178732706023</v>
       </c>
       <c r="H8" t="n">
-        <v>8.754048765033865</v>
+        <v>8.754048765033863</v>
       </c>
       <c r="I8" t="n">
-        <v>7.704383100774735</v>
+        <v>7.70438310077474</v>
       </c>
       <c r="J8" t="n">
-        <v>9.833933255888136</v>
+        <v>9.833933255888139</v>
       </c>
       <c r="K8" t="n">
-        <v>8.153237490264564</v>
+        <v>8.153237490264578</v>
       </c>
       <c r="L8" t="n">
-        <v>9.043133602906176</v>
+        <v>9.043133602906178</v>
       </c>
       <c r="M8" t="n">
-        <v>11.91065754312711</v>
+        <v>11.91065754312686</v>
       </c>
       <c r="N8" t="n">
-        <v>8.084117733521179</v>
+        <v>8.08411773352117</v>
       </c>
       <c r="O8" t="n">
-        <v>9.001608997370358</v>
+        <v>9.00160899737037</v>
       </c>
       <c r="P8" t="n">
-        <v>10.78609173037623</v>
+        <v>10.78609173037625</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.77651933128433</v>
+        <v>6.776519331284332</v>
       </c>
       <c r="R8" t="n">
-        <v>7.51286614641625</v>
+        <v>7.512866146416256</v>
       </c>
       <c r="S8" t="n">
-        <v>9.527617074913948</v>
+        <v>9.527617074913975</v>
       </c>
       <c r="T8" t="n">
-        <v>8.842662950839172</v>
+        <v>8.842662950839182</v>
       </c>
       <c r="U8" t="n">
-        <v>9.128810610350076</v>
+        <v>9.2785158054345</v>
       </c>
       <c r="V8" t="n">
-        <v>8.845605501917614</v>
+        <v>8.519163996291667</v>
       </c>
       <c r="W8" t="n">
         <v>11.55769258355431</v>
       </c>
       <c r="X8" t="n">
-        <v>8.476352125796801</v>
+        <v>8.47635212579681</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.65137922046071</v>
+        <v>13.65137922046073</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.932221657196999</v>
+        <v>7.732060464552713</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.740800105610585</v>
+        <v>8.740800105610592</v>
       </c>
       <c r="AB8" t="n">
         <v>12.43752866206957</v>
@@ -3785,34 +3785,34 @@
         <v>9.20210858574997</v>
       </c>
       <c r="C9" t="n">
-        <v>9.04466614847405</v>
+        <v>9.044666148474043</v>
       </c>
       <c r="D9" t="n">
-        <v>10.67209634825709</v>
+        <v>10.6720963482571</v>
       </c>
       <c r="E9" t="n">
-        <v>9.762290748127878</v>
+        <v>9.493507213714873</v>
       </c>
       <c r="F9" t="n">
-        <v>9.785058318275505</v>
+        <v>7.1003485908793</v>
       </c>
       <c r="G9" t="n">
-        <v>12.90044901528672</v>
+        <v>12.90044932839838</v>
       </c>
       <c r="H9" t="n">
-        <v>11.09703327295598</v>
+        <v>11.09703327295597</v>
       </c>
       <c r="I9" t="n">
         <v>10.04736760869684</v>
       </c>
       <c r="J9" t="n">
-        <v>12.17691776381025</v>
+        <v>12.17691776381024</v>
       </c>
       <c r="K9" t="n">
         <v>10.49622199818668</v>
       </c>
       <c r="L9" t="n">
-        <v>11.38611811082829</v>
+        <v>11.38611811082828</v>
       </c>
       <c r="M9" t="n">
         <v>14.25364205104922</v>
@@ -3824,25 +3824,25 @@
         <v>12.39289962055963</v>
       </c>
       <c r="P9" t="n">
-        <v>14.32284480285291</v>
+        <v>14.32284480285294</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.52933605984992</v>
+        <v>10.52933605984991</v>
       </c>
       <c r="R9" t="n">
-        <v>9.855850654338358</v>
+        <v>9.855850654338354</v>
       </c>
       <c r="S9" t="n">
         <v>11.87060158283608</v>
       </c>
       <c r="T9" t="n">
-        <v>11.18564745876129</v>
+        <v>11.18564745876128</v>
       </c>
       <c r="U9" t="n">
-        <v>12.2005907073949</v>
+        <v>12.20059070739491</v>
       </c>
       <c r="V9" t="n">
-        <v>11.18859000983973</v>
+        <v>12.53250651738466</v>
       </c>
       <c r="W9" t="n">
         <v>13.90044552870261</v>
@@ -3851,13 +3851,13 @@
         <v>12.12117737568054</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.8296591645202</v>
+        <v>14.82965916452021</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.27520616511911</v>
+        <v>10.57305906543934</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.0837846135327</v>
+        <v>11.08378461353269</v>
       </c>
       <c r="AB9" t="n">
         <v>13.54970730094565</v>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.55116932215856</v>
+        <v>39.55116932215855</v>
       </c>
       <c r="C2" t="n">
-        <v>42.43075787621282</v>
+        <v>42.43075787621281</v>
       </c>
       <c r="D2" t="n">
         <v>39.53128712652673</v>
       </c>
       <c r="E2" t="n">
-        <v>39.42625125518244</v>
+        <v>39.42625125518245</v>
       </c>
       <c r="F2" t="n">
-        <v>39.58787257764131</v>
+        <v>39.58787257764134</v>
       </c>
       <c r="G2" t="n">
         <v>39.75269807471044</v>
       </c>
       <c r="H2" t="n">
-        <v>39.6149835858381</v>
+        <v>39.61498358583808</v>
       </c>
       <c r="I2" t="n">
-        <v>39.60190185692143</v>
+        <v>39.60190185692144</v>
       </c>
       <c r="J2" t="n">
-        <v>39.70016934504866</v>
+        <v>39.70016934504865</v>
       </c>
       <c r="K2" t="n">
-        <v>39.68535783760335</v>
+        <v>39.68535783760336</v>
       </c>
       <c r="L2" t="n">
-        <v>39.67922359995872</v>
+        <v>39.67922359995873</v>
       </c>
       <c r="M2" t="n">
-        <v>39.86384971178413</v>
+        <v>39.86384971178415</v>
       </c>
       <c r="N2" t="n">
-        <v>39.61629221261318</v>
+        <v>39.61629221261319</v>
       </c>
       <c r="O2" t="n">
         <v>43.62495850344184</v>
       </c>
       <c r="P2" t="n">
-        <v>39.81935787910054</v>
+        <v>39.81935787910052</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.62009535857246</v>
+        <v>39.62009535857244</v>
       </c>
       <c r="R2" t="n">
-        <v>39.55521311781045</v>
+        <v>39.55521311781044</v>
       </c>
       <c r="S2" t="n">
-        <v>39.72322564010337</v>
+        <v>39.72322564010339</v>
       </c>
       <c r="T2" t="n">
-        <v>39.65819676459632</v>
+        <v>39.65819676459633</v>
       </c>
       <c r="U2" t="n">
-        <v>43.16826630352689</v>
+        <v>43.1682663035269</v>
       </c>
       <c r="V2" t="n">
         <v>39.62449604503279</v>
       </c>
       <c r="W2" t="n">
-        <v>45.79118644628655</v>
+        <v>45.79118644628656</v>
       </c>
       <c r="X2" t="n">
-        <v>39.7496695450656</v>
+        <v>39.74966954506557</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.93352490983063</v>
+        <v>39.93352490983062</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.77918161553993</v>
+        <v>40.7791816155399</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.67061542956781</v>
+        <v>39.67061542956782</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.81014102105218</v>
+        <v>39.81014102105216</v>
       </c>
     </row>
     <row r="3">
@@ -4114,55 +4114,55 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.58222308217109</v>
+        <v>40.5822230821711</v>
       </c>
       <c r="C3" t="n">
         <v>44.8571240498696</v>
       </c>
       <c r="D3" t="n">
-        <v>40.44950655511338</v>
+        <v>40.44950655511339</v>
       </c>
       <c r="E3" t="n">
-        <v>39.69672993112599</v>
+        <v>39.69672993112596</v>
       </c>
       <c r="F3" t="n">
-        <v>40.85659501484557</v>
+        <v>40.85659501484559</v>
       </c>
       <c r="G3" t="n">
-        <v>42.01185205618052</v>
+        <v>42.01185205618046</v>
       </c>
       <c r="H3" t="n">
-        <v>41.05928582903901</v>
+        <v>41.05928582903898</v>
       </c>
       <c r="I3" t="n">
-        <v>40.95821766083094</v>
+        <v>40.95821766083093</v>
       </c>
       <c r="J3" t="n">
-        <v>41.64716176518152</v>
+        <v>41.64716176518153</v>
       </c>
       <c r="K3" t="n">
         <v>41.53929934674007</v>
       </c>
       <c r="L3" t="n">
-        <v>41.49817279627681</v>
+        <v>41.4981727962768</v>
       </c>
       <c r="M3" t="n">
-        <v>42.82246766158298</v>
+        <v>42.82246766158296</v>
       </c>
       <c r="N3" t="n">
-        <v>41.05912685884304</v>
+        <v>41.05912685884305</v>
       </c>
       <c r="O3" t="n">
         <v>47.78407740531494</v>
       </c>
       <c r="P3" t="n">
-        <v>42.48460025668006</v>
+        <v>42.48460025668007</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.08049865903087</v>
+        <v>41.08049865903088</v>
       </c>
       <c r="R3" t="n">
-        <v>40.62778121384373</v>
+        <v>40.62778121384375</v>
       </c>
       <c r="S3" t="n">
         <v>41.80707490881449</v>
@@ -4177,22 +4177,22 @@
         <v>41.09970158398836</v>
       </c>
       <c r="W3" t="n">
-        <v>52.54985921731281</v>
+        <v>52.54985921731285</v>
       </c>
       <c r="X3" t="n">
-        <v>42.00760416207029</v>
+        <v>42.00760416207025</v>
       </c>
       <c r="Y3" t="n">
         <v>43.32387751521102</v>
       </c>
       <c r="Z3" t="n">
-        <v>42.68647310280203</v>
+        <v>42.68647310280201</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.44504503996514</v>
+        <v>41.44504503996515</v>
       </c>
       <c r="AB3" t="n">
-        <v>42.44683482887159</v>
+        <v>42.44683482887154</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.908881428121437</v>
+        <v>4.908881428121434</v>
       </c>
       <c r="C4" t="n">
         <v>3.905124512575779</v>
       </c>
       <c r="D4" t="n">
-        <v>4.684302882198167</v>
+        <v>4.684302882198168</v>
       </c>
       <c r="E4" t="n">
         <v>3.497874396476591</v>
       </c>
       <c r="F4" t="n">
-        <v>5.323461583131253</v>
+        <v>5.323461583131252</v>
       </c>
       <c r="G4" t="n">
-        <v>7.185241396001481</v>
+        <v>7.185241396001478</v>
       </c>
       <c r="H4" t="n">
-        <v>5.629692892393514</v>
+        <v>5.629692892393518</v>
       </c>
       <c r="I4" t="n">
-        <v>5.481928746387341</v>
+        <v>5.481928746387342</v>
       </c>
       <c r="J4" t="n">
-        <v>6.592293479170471</v>
+        <v>6.592293479170472</v>
       </c>
       <c r="K4" t="n">
-        <v>6.424602439837437</v>
+        <v>6.424602439837448</v>
       </c>
       <c r="L4" t="n">
-        <v>6.355313403752728</v>
+        <v>6.355313403752726</v>
       </c>
       <c r="M4" t="n">
-        <v>8.432144432076081</v>
+        <v>8.432144432076075</v>
       </c>
       <c r="N4" t="n">
-        <v>5.64447443381624</v>
+        <v>5.644474433816235</v>
       </c>
       <c r="O4" t="n">
-        <v>5.902772749089437</v>
+        <v>5.902772749089438</v>
       </c>
       <c r="P4" t="n">
-        <v>7.938194551612627</v>
+        <v>7.93819455161263</v>
       </c>
       <c r="Q4" t="n">
         <v>5.687432716959751</v>
       </c>
       <c r="R4" t="n">
-        <v>4.954557960247468</v>
+        <v>4.954557960247466</v>
       </c>
       <c r="S4" t="n">
-        <v>6.852336689124944</v>
+        <v>6.852336689124948</v>
       </c>
       <c r="T4" t="n">
-        <v>6.117805625512116</v>
+        <v>6.117805625512105</v>
       </c>
       <c r="U4" t="n">
-        <v>6.671590264895595</v>
+        <v>6.671590264895596</v>
       </c>
       <c r="V4" t="n">
         <v>5.739482595945782</v>
       </c>
       <c r="W4" t="n">
-        <v>8.320826982752308</v>
+        <v>8.320826982752314</v>
       </c>
       <c r="X4" t="n">
-        <v>7.151032760470221</v>
+        <v>7.151032760470227</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.206008395569501</v>
+        <v>9.206008395569516</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.082019077658916</v>
+        <v>5.082019077658915</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.258080159233038</v>
+        <v>6.258080159233048</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.814968749032299</v>
+        <v>7.814968749032301</v>
       </c>
     </row>
     <row r="5">
@@ -4293,82 +4293,82 @@
         <v>46.85342314777831</v>
       </c>
       <c r="C5" t="n">
-        <v>33.00738281984988</v>
+        <v>33.00738281984992</v>
       </c>
       <c r="D5" t="n">
-        <v>47.64059801691009</v>
+        <v>47.64059801691015</v>
       </c>
       <c r="E5" t="n">
-        <v>25.03441544797988</v>
+        <v>25.03441544797996</v>
       </c>
       <c r="F5" t="n">
-        <v>60.62177328492973</v>
+        <v>60.62177328492977</v>
       </c>
       <c r="G5" t="n">
-        <v>82.61031081006128</v>
+        <v>82.61031081006145</v>
       </c>
       <c r="H5" t="n">
-        <v>70.80471206960969</v>
+        <v>70.80471206960985</v>
       </c>
       <c r="I5" t="n">
-        <v>64.19926228258872</v>
+        <v>64.19926228258871</v>
       </c>
       <c r="J5" t="n">
-        <v>77.40757712602137</v>
+        <v>77.40757712602141</v>
       </c>
       <c r="K5" t="n">
-        <v>73.3329686279842</v>
+        <v>73.3329686279844</v>
       </c>
       <c r="L5" t="n">
-        <v>73.48274721569678</v>
+        <v>73.4827472156969</v>
       </c>
       <c r="M5" t="n">
         <v>116.0630057734272</v>
       </c>
       <c r="N5" t="n">
-        <v>76.20402381635024</v>
+        <v>76.20402381635041</v>
       </c>
       <c r="O5" t="n">
-        <v>61.61922948273347</v>
+        <v>61.61922948273353</v>
       </c>
       <c r="P5" t="n">
-        <v>94.3696705082917</v>
+        <v>94.36967050829188</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.91256921487506</v>
+        <v>63.91256921487511</v>
       </c>
       <c r="R5" t="n">
-        <v>56.31427226494915</v>
+        <v>56.31427226494922</v>
       </c>
       <c r="S5" t="n">
-        <v>79.60838040355587</v>
+        <v>79.60838040355601</v>
       </c>
       <c r="T5" t="n">
-        <v>76.83470050976207</v>
+        <v>76.83470050976216</v>
       </c>
       <c r="U5" t="n">
-        <v>77.25289493499845</v>
+        <v>77.25289493499766</v>
       </c>
       <c r="V5" t="n">
-        <v>58.46914647366133</v>
+        <v>58.46914647366135</v>
       </c>
       <c r="W5" t="n">
         <v>112.4409806183878</v>
       </c>
       <c r="X5" t="n">
-        <v>91.00521677933908</v>
+        <v>91.00521677933935</v>
       </c>
       <c r="Y5" t="n">
-        <v>129.8543653263106</v>
+        <v>129.854365326311</v>
       </c>
       <c r="Z5" t="n">
-        <v>46.3375560298631</v>
+        <v>46.33755602986308</v>
       </c>
       <c r="AA5" t="n">
-        <v>76.06904150865053</v>
+        <v>76.0690415086507</v>
       </c>
       <c r="AB5" t="n">
-        <v>112.0913311035702</v>
+        <v>112.0913311035705</v>
       </c>
     </row>
     <row r="6">
@@ -4378,67 +4378,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116.2388220467051</v>
+        <v>138.4378398939894</v>
       </c>
       <c r="C6" t="n">
-        <v>115.2350651311595</v>
+        <v>115.2350651311596</v>
       </c>
       <c r="D6" t="n">
-        <v>116.0142435007819</v>
+        <v>116.0142435007818</v>
       </c>
       <c r="E6" t="n">
-        <v>114.8278150150603</v>
+        <v>137.0268328623446</v>
       </c>
       <c r="F6" t="n">
-        <v>116.653402201715</v>
+        <v>116.6534022017149</v>
       </c>
       <c r="G6" t="n">
-        <v>118.5151820145852</v>
+        <v>140.7141998618694</v>
       </c>
       <c r="H6" t="n">
-        <v>139.1586513582615</v>
+        <v>116.9596335109772</v>
       </c>
       <c r="I6" t="n">
         <v>116.811869364971</v>
       </c>
       <c r="J6" t="n">
-        <v>117.9222340977541</v>
+        <v>140.1212519450384</v>
       </c>
       <c r="K6" t="n">
-        <v>139.9535609057055</v>
+        <v>139.9535609057054</v>
       </c>
       <c r="L6" t="n">
-        <v>117.6852540223365</v>
+        <v>139.8842718696208</v>
       </c>
       <c r="M6" t="n">
-        <v>119.7620850506597</v>
+        <v>119.7620850506598</v>
       </c>
       <c r="N6" t="n">
-        <v>116.9882118780724</v>
+        <v>116.9882118780725</v>
       </c>
       <c r="O6" t="n">
-        <v>117.2465101933456</v>
+        <v>139.4984921617417</v>
       </c>
       <c r="P6" t="n">
-        <v>141.5335975207544</v>
+        <v>112.8362687667971</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.2163911828278</v>
+        <v>139.2163911828277</v>
       </c>
       <c r="R6" t="n">
-        <v>138.4835164261154</v>
+        <v>138.4835164261153</v>
       </c>
       <c r="S6" t="n">
-        <v>140.3812951549928</v>
+        <v>140.3812951549929</v>
       </c>
       <c r="T6" t="n">
-        <v>117.4477462440958</v>
+        <v>139.6467640913801</v>
       </c>
       <c r="U6" t="n">
-        <v>140.222304018332</v>
+        <v>118.0232861710479</v>
       </c>
       <c r="V6" t="n">
-        <v>139.2684410618138</v>
+        <v>117.0694232145294</v>
       </c>
       <c r="W6" t="n">
         <v>141.9165939528989</v>
@@ -4453,7 +4453,7 @@
         <v>138.6109775435268</v>
       </c>
       <c r="AA6" t="n">
-        <v>139.787038625101</v>
+        <v>139.7870386251011</v>
       </c>
       <c r="AB6" t="n">
         <v>119.1688620537379</v>
@@ -4472,79 +4472,79 @@
         <v>4.947276562171521</v>
       </c>
       <c r="D7" t="n">
-        <v>5.726454931793912</v>
+        <v>5.726454931793911</v>
       </c>
       <c r="E7" t="n">
-        <v>4.540026446072336</v>
+        <v>4.540026446072333</v>
       </c>
       <c r="F7" t="n">
-        <v>6.365613632726998</v>
+        <v>6.365613632726999</v>
       </c>
       <c r="G7" t="n">
-        <v>8.227393445597219</v>
+        <v>8.227393445597224</v>
       </c>
       <c r="H7" t="n">
-        <v>6.671844941989261</v>
+        <v>6.671844941989257</v>
       </c>
       <c r="I7" t="n">
-        <v>6.524080795983083</v>
+        <v>6.524080795983087</v>
       </c>
       <c r="J7" t="n">
         <v>7.634445528766215</v>
       </c>
       <c r="K7" t="n">
-        <v>7.466754489433186</v>
+        <v>7.46675448943319</v>
       </c>
       <c r="L7" t="n">
-        <v>7.397465453348468</v>
+        <v>7.397465453348472</v>
       </c>
       <c r="M7" t="n">
-        <v>9.474296481671823</v>
+        <v>9.474296481671821</v>
       </c>
       <c r="N7" t="n">
-        <v>6.686626483411982</v>
+        <v>6.686626483411975</v>
       </c>
       <c r="O7" t="n">
-        <v>6.944923404402122</v>
+        <v>6.944923404402116</v>
       </c>
       <c r="P7" t="n">
-        <v>8.980345206925307</v>
+        <v>8.980345206925323</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.729584766555496</v>
+        <v>6.729584766555494</v>
       </c>
       <c r="R7" t="n">
-        <v>5.996710009843214</v>
+        <v>5.996710009843209</v>
       </c>
       <c r="S7" t="n">
-        <v>7.89448873872069</v>
+        <v>7.894488738720691</v>
       </c>
       <c r="T7" t="n">
-        <v>7.159957675107846</v>
+        <v>7.159957675107845</v>
       </c>
       <c r="U7" t="n">
-        <v>7.721822846118712</v>
+        <v>7.721822846118717</v>
       </c>
       <c r="V7" t="n">
-        <v>6.781634645541526</v>
+        <v>6.781634645541519</v>
       </c>
       <c r="W7" t="n">
-        <v>9.362979032348056</v>
+        <v>9.362979032348058</v>
       </c>
       <c r="X7" t="n">
         <v>8.193184810065963</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.26991573273374</v>
+        <v>10.26991573273376</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.124171127254663</v>
+        <v>6.124171127254654</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.30023220882878</v>
+        <v>7.300232208828787</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.857120798628042</v>
+        <v>8.857120798628044</v>
       </c>
     </row>
     <row r="8">
@@ -4554,82 +4554,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.366536651011298</v>
+        <v>6.366536651011295</v>
       </c>
       <c r="C8" t="n">
-        <v>6.477694738397127</v>
+        <v>6.477694738397123</v>
       </c>
       <c r="D8" t="n">
         <v>7.256873108019517</v>
       </c>
       <c r="E8" t="n">
-        <v>6.070444622297934</v>
+        <v>5.476785271544111</v>
       </c>
       <c r="F8" t="n">
-        <v>6.95480753298566</v>
+        <v>6.954807532985662</v>
       </c>
       <c r="G8" t="n">
-        <v>9.757811621822835</v>
+        <v>9.988996510534667</v>
       </c>
       <c r="H8" t="n">
-        <v>8.202263118214862</v>
+        <v>8.20226311821486</v>
       </c>
       <c r="I8" t="n">
-        <v>8.054498972208686</v>
+        <v>8.054498972208689</v>
       </c>
       <c r="J8" t="n">
-        <v>9.164863704991822</v>
+        <v>9.164863704991815</v>
       </c>
       <c r="K8" t="n">
-        <v>8.997172665658786</v>
+        <v>8.997172665658795</v>
       </c>
       <c r="L8" t="n">
-        <v>8.927883629574083</v>
+        <v>8.927883629574074</v>
       </c>
       <c r="M8" t="n">
-        <v>11.00471465789743</v>
+        <v>11.00471465789699</v>
       </c>
       <c r="N8" t="n">
-        <v>7.352799010687129</v>
+        <v>7.352799010687123</v>
       </c>
       <c r="O8" t="n">
-        <v>7.848599533466214</v>
+        <v>7.848599533466212</v>
       </c>
       <c r="P8" t="n">
-        <v>9.825803806169789</v>
+        <v>9.825803806169795</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.925981695581437</v>
+        <v>6.925981695581441</v>
       </c>
       <c r="R8" t="n">
-        <v>7.527128186068819</v>
+        <v>7.527128186068814</v>
       </c>
       <c r="S8" t="n">
-        <v>9.424906914946295</v>
+        <v>9.4249069149463</v>
       </c>
       <c r="T8" t="n">
-        <v>8.690375851333457</v>
+        <v>8.690375851333451</v>
       </c>
       <c r="U8" t="n">
-        <v>8.569905158126872</v>
+        <v>8.71114412524647</v>
       </c>
       <c r="V8" t="n">
-        <v>8.312052821767127</v>
+        <v>7.995642088478673</v>
       </c>
       <c r="W8" t="n">
         <v>10.89361631949784</v>
       </c>
       <c r="X8" t="n">
-        <v>8.491765913360227</v>
+        <v>8.491765913360236</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.89074095668317</v>
+        <v>12.8907409566832</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.654589303480268</v>
+        <v>6.518964182137343</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.830650385054387</v>
+        <v>8.83065038505439</v>
       </c>
       <c r="AB8" t="n">
         <v>11.55216092137846</v>
@@ -4642,28 +4642,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.333701108453992</v>
+        <v>8.333701108453983</v>
       </c>
       <c r="C9" t="n">
-        <v>8.359244102637655</v>
+        <v>8.359244102637659</v>
       </c>
       <c r="D9" t="n">
-        <v>9.138422472260043</v>
+        <v>9.138422472260041</v>
       </c>
       <c r="E9" t="n">
-        <v>7.951993986538465</v>
+        <v>7.714435864747705</v>
       </c>
       <c r="F9" t="n">
-        <v>9.777581173193123</v>
+        <v>7.404763790781602</v>
       </c>
       <c r="G9" t="n">
-        <v>11.63936098606335</v>
+        <v>11.63936111468572</v>
       </c>
       <c r="H9" t="n">
         <v>10.08381248245539</v>
       </c>
       <c r="I9" t="n">
-        <v>9.936048336449216</v>
+        <v>9.936048336449209</v>
       </c>
       <c r="J9" t="n">
         <v>11.04641306923235</v>
@@ -4675,52 +4675,52 @@
         <v>10.8094329938146</v>
       </c>
       <c r="M9" t="n">
-        <v>12.88626402213796</v>
+        <v>12.88626402213795</v>
       </c>
       <c r="N9" t="n">
         <v>10.09859402387811</v>
       </c>
       <c r="O9" t="n">
-        <v>10.6980011527301</v>
+        <v>10.69800115273011</v>
       </c>
       <c r="P9" t="n">
         <v>12.80760824179191</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.14155243564401</v>
+        <v>10.141552435644</v>
       </c>
       <c r="R9" t="n">
-        <v>9.408677550309347</v>
+        <v>9.408677550309335</v>
       </c>
       <c r="S9" t="n">
         <v>11.30645627918682</v>
       </c>
       <c r="T9" t="n">
-        <v>10.57192521557395</v>
+        <v>10.57192521557398</v>
       </c>
       <c r="U9" t="n">
-        <v>11.14746514252597</v>
+        <v>11.14746514252598</v>
       </c>
       <c r="V9" t="n">
-        <v>10.19360218600765</v>
+        <v>11.38139098678458</v>
       </c>
       <c r="W9" t="n">
         <v>12.77494657281419</v>
       </c>
       <c r="X9" t="n">
-        <v>11.60515235053209</v>
+        <v>11.6051523505321</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.68188327319987</v>
+        <v>13.68188327319989</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.536138667720794</v>
+        <v>8.915562402147739</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.71219974929491</v>
+        <v>10.71219974929492</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.26908833909417</v>
+        <v>12.26908833909418</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.1842893588482</v>
+        <v>39.18428935884818</v>
       </c>
       <c r="C2" t="n">
-        <v>42.11067217972032</v>
+        <v>42.11067217972031</v>
       </c>
       <c r="D2" t="n">
-        <v>39.22304562785089</v>
+        <v>39.2230456278509</v>
       </c>
       <c r="E2" t="n">
-        <v>39.28580122762035</v>
+        <v>39.28580122762036</v>
       </c>
       <c r="F2" t="n">
-        <v>39.19987902857064</v>
+        <v>39.19987902857061</v>
       </c>
       <c r="G2" t="n">
-        <v>39.37446243682653</v>
+        <v>39.37446243682649</v>
       </c>
       <c r="H2" t="n">
-        <v>39.32727036990336</v>
+        <v>39.32727036990335</v>
       </c>
       <c r="I2" t="n">
-        <v>39.22699230665019</v>
+        <v>39.22699230665016</v>
       </c>
       <c r="J2" t="n">
-        <v>39.39689074180664</v>
+        <v>39.39689074180662</v>
       </c>
       <c r="K2" t="n">
-        <v>39.29773907873349</v>
+        <v>39.29773907873348</v>
       </c>
       <c r="L2" t="n">
-        <v>39.33416971523591</v>
+        <v>39.33416971523593</v>
       </c>
       <c r="M2" t="n">
-        <v>39.43879060460087</v>
+        <v>39.43879060460084</v>
       </c>
       <c r="N2" t="n">
-        <v>39.47612306361047</v>
+        <v>39.47612306361044</v>
       </c>
       <c r="O2" t="n">
-        <v>43.47489660471768</v>
+        <v>43.47489660471769</v>
       </c>
       <c r="P2" t="n">
-        <v>39.6228265327743</v>
+        <v>39.62282653277428</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.32152504135556</v>
+        <v>39.32152504135554</v>
       </c>
       <c r="R2" t="n">
-        <v>39.23324489577477</v>
+        <v>39.23324489577472</v>
       </c>
       <c r="S2" t="n">
-        <v>39.31595280438706</v>
+        <v>39.31595280438703</v>
       </c>
       <c r="T2" t="n">
         <v>39.3579967768711</v>
       </c>
       <c r="U2" t="n">
-        <v>42.96143257781122</v>
+        <v>42.96143257781124</v>
       </c>
       <c r="V2" t="n">
-        <v>39.40468589340643</v>
+        <v>39.40468589340645</v>
       </c>
       <c r="W2" t="n">
-        <v>45.76828661384923</v>
+        <v>45.76828661384928</v>
       </c>
       <c r="X2" t="n">
-        <v>39.34345466654729</v>
+        <v>39.3434546665473</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.68166985031176</v>
+        <v>39.68166985031174</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.6356475447919</v>
+        <v>40.63564754479187</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.33900175919526</v>
+        <v>39.33900175919523</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.51112839294412</v>
+        <v>39.51112839294409</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.17579494363223</v>
+        <v>39.17579494363216</v>
       </c>
       <c r="C3" t="n">
-        <v>43.82058047715421</v>
+        <v>43.82058047715417</v>
       </c>
       <c r="D3" t="n">
         <v>39.45631807161678</v>
       </c>
       <c r="E3" t="n">
-        <v>39.90207183631207</v>
+        <v>39.902071836312</v>
       </c>
       <c r="F3" t="n">
-        <v>39.29061120712937</v>
+        <v>39.29061120712934</v>
       </c>
       <c r="G3" t="n">
-        <v>40.52142186608598</v>
+        <v>40.52142186608597</v>
       </c>
       <c r="H3" t="n">
-        <v>40.20612971455667</v>
+        <v>40.20612971455659</v>
       </c>
       <c r="I3" t="n">
-        <v>39.48522363255686</v>
+        <v>39.48522363255683</v>
       </c>
       <c r="J3" t="n">
-        <v>40.68679193706647</v>
+        <v>40.68679193706646</v>
       </c>
       <c r="K3" t="n">
-        <v>39.9843183212476</v>
+        <v>39.98431832124754</v>
       </c>
       <c r="L3" t="n">
         <v>40.23813893362328</v>
       </c>
       <c r="M3" t="n">
-        <v>40.99468606358707</v>
+        <v>40.99468606358708</v>
       </c>
       <c r="N3" t="n">
         <v>41.25967458473046</v>
       </c>
       <c r="O3" t="n">
-        <v>47.95746887826533</v>
+        <v>47.95746887826532</v>
       </c>
       <c r="P3" t="n">
-        <v>42.29419639823595</v>
+        <v>42.29419639823596</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.1558199659485</v>
+        <v>40.15581996594847</v>
       </c>
       <c r="R3" t="n">
-        <v>39.53118093370379</v>
+        <v>39.53118093370376</v>
       </c>
       <c r="S3" t="n">
-        <v>40.1046757383773</v>
+        <v>40.10467573837732</v>
       </c>
       <c r="T3" t="n">
-        <v>40.41793166182622</v>
+        <v>40.41793166182626</v>
       </c>
       <c r="U3" t="n">
-        <v>47.07717340577696</v>
+        <v>47.07717340577697</v>
       </c>
       <c r="V3" t="n">
-        <v>40.73952621563055</v>
+        <v>40.73952621563056</v>
       </c>
       <c r="W3" t="n">
-        <v>53.49401191863942</v>
+        <v>53.49401191863946</v>
       </c>
       <c r="X3" t="n">
-        <v>40.31623096302914</v>
+        <v>40.31623096302911</v>
       </c>
       <c r="Y3" t="n">
-        <v>42.72596232396105</v>
+        <v>42.72596232396103</v>
       </c>
       <c r="Z3" t="n">
         <v>42.65128754865604</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.2823677563257</v>
+        <v>40.28236775632566</v>
       </c>
       <c r="AB3" t="n">
-        <v>41.5114811069415</v>
+        <v>41.51148110694145</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.622885273735149</v>
+        <v>2.622885273735148</v>
       </c>
       <c r="C4" t="n">
         <v>2.231487405948784</v>
       </c>
       <c r="D4" t="n">
-        <v>3.060655160885274</v>
+        <v>3.060655160885275</v>
       </c>
       <c r="E4" t="n">
         <v>3.769508529283285</v>
       </c>
       <c r="F4" t="n">
-        <v>2.798977764852081</v>
+        <v>2.798977764852082</v>
       </c>
       <c r="G4" t="n">
-        <v>4.770977673438048</v>
+        <v>4.770977673438043</v>
       </c>
       <c r="H4" t="n">
-        <v>4.237921568117754</v>
+        <v>4.237921568117756</v>
       </c>
       <c r="I4" t="n">
-        <v>3.105234713485111</v>
+        <v>3.105234713485113</v>
       </c>
       <c r="J4" t="n">
-        <v>5.025454513683461</v>
+        <v>5.025454513683464</v>
       </c>
       <c r="K4" t="n">
-        <v>3.904352049289399</v>
+        <v>3.904352049289397</v>
       </c>
       <c r="L4" t="n">
-        <v>4.315852847504837</v>
+        <v>4.315852847504843</v>
       </c>
       <c r="M4" t="n">
-        <v>5.506668469557555</v>
+        <v>5.506668469557567</v>
       </c>
       <c r="N4" t="n">
-        <v>5.919281219161553</v>
+        <v>5.919281219161554</v>
       </c>
       <c r="O4" t="n">
-        <v>6.152745714155573</v>
+        <v>6.152745714155576</v>
       </c>
       <c r="P4" t="n">
-        <v>7.576364390297483</v>
+        <v>7.576364390297489</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.173025439188518</v>
+        <v>4.173025439188516</v>
       </c>
       <c r="R4" t="n">
-        <v>3.175860583980138</v>
+        <v>3.175860583980136</v>
       </c>
       <c r="S4" t="n">
-        <v>4.110084459273417</v>
+        <v>4.110084459273415</v>
       </c>
       <c r="T4" t="n">
         <v>4.584990469664277</v>
       </c>
       <c r="U4" t="n">
-        <v>6.065473812257292</v>
+        <v>6.065473812257299</v>
       </c>
       <c r="V4" t="n">
-        <v>5.11976846150492</v>
+        <v>5.119768461504913</v>
       </c>
       <c r="W4" t="n">
-        <v>9.719192398537976</v>
+        <v>9.719192398537981</v>
       </c>
       <c r="X4" t="n">
-        <v>4.420730643855432</v>
+        <v>4.420730643855429</v>
       </c>
       <c r="Y4" t="n">
         <v>8.241642754259628</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.865024908868834</v>
+        <v>4.865024908868838</v>
       </c>
       <c r="AA4" t="n">
         <v>4.370433006875511</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.298995271585127</v>
+        <v>6.298995271585133</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.58503908685087</v>
+        <v>15.58503908685091</v>
       </c>
       <c r="C5" t="n">
-        <v>9.619013544519596</v>
+        <v>9.619013544519589</v>
       </c>
       <c r="D5" t="n">
-        <v>26.04119023072628</v>
+        <v>26.0411902307263</v>
       </c>
       <c r="E5" t="n">
-        <v>38.25613668992636</v>
+        <v>38.25613668992637</v>
       </c>
       <c r="F5" t="n">
-        <v>20.89003940679289</v>
+        <v>20.89003940679322</v>
       </c>
       <c r="G5" t="n">
-        <v>49.72300619029623</v>
+        <v>49.72300619029629</v>
       </c>
       <c r="H5" t="n">
-        <v>51.61241910136297</v>
+        <v>51.612419101363</v>
       </c>
       <c r="I5" t="n">
-        <v>27.29449068908504</v>
+        <v>27.29449068908505</v>
       </c>
       <c r="J5" t="n">
         <v>57.46080876755175</v>
       </c>
       <c r="K5" t="n">
-        <v>39.16256346053857</v>
+        <v>39.16256346053849</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50245832494168</v>
+        <v>43.50245832494169</v>
       </c>
       <c r="M5" t="n">
-        <v>68.76136433427682</v>
+        <v>68.76136433427685</v>
       </c>
       <c r="N5" t="n">
-        <v>77.58574341552179</v>
+        <v>77.58574341552196</v>
       </c>
       <c r="O5" t="n">
-        <v>73.83897369452235</v>
+        <v>73.83897369452239</v>
       </c>
       <c r="P5" t="n">
         <v>102.8713233508487</v>
       </c>
       <c r="Q5" t="n">
-        <v>45.21034347712393</v>
+        <v>45.21034347712395</v>
       </c>
       <c r="R5" t="n">
         <v>29.37081778201476</v>
       </c>
       <c r="S5" t="n">
-        <v>37.69408822699821</v>
+        <v>37.6940882269982</v>
       </c>
       <c r="T5" t="n">
-        <v>54.0069870084175</v>
+        <v>54.00698700841747</v>
       </c>
       <c r="U5" t="n">
-        <v>77.73131998550426</v>
+        <v>77.73131998550427</v>
       </c>
       <c r="V5" t="n">
-        <v>57.51900950121739</v>
+        <v>57.51900950121725</v>
       </c>
       <c r="W5" t="n">
-        <v>151.6222898607923</v>
+        <v>151.6222898607922</v>
       </c>
       <c r="X5" t="n">
-        <v>52.06190521791069</v>
+        <v>52.06190521791065</v>
       </c>
       <c r="Y5" t="n">
         <v>122.0003103866014</v>
       </c>
       <c r="Z5" t="n">
-        <v>52.81859288136545</v>
+        <v>52.81859288136538</v>
       </c>
       <c r="AA5" t="n">
         <v>49.95264799383916</v>
       </c>
       <c r="AB5" t="n">
-        <v>91.51217370702437</v>
+        <v>91.51217370702426</v>
       </c>
     </row>
     <row r="6">
@@ -5238,82 +5238,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>122.0937777272174</v>
+        <v>122.0937777272173</v>
       </c>
       <c r="C6" t="n">
-        <v>145.3852007234096</v>
+        <v>145.3852007234095</v>
       </c>
       <c r="D6" t="n">
-        <v>146.2143684783461</v>
+        <v>122.5315476143673</v>
       </c>
       <c r="E6" t="n">
-        <v>146.923221846744</v>
+        <v>123.2404009827654</v>
       </c>
       <c r="F6" t="n">
-        <v>145.9526910823128</v>
+        <v>145.9526910823127</v>
       </c>
       <c r="G6" t="n">
-        <v>124.2418701269203</v>
+        <v>147.9246909908986</v>
       </c>
       <c r="H6" t="n">
         <v>123.7088140216</v>
       </c>
       <c r="I6" t="n">
-        <v>146.2589480309458</v>
+        <v>122.5761271669672</v>
       </c>
       <c r="J6" t="n">
-        <v>124.4963469671657</v>
+        <v>124.4963469671656</v>
       </c>
       <c r="K6" t="n">
-        <v>147.0580653667502</v>
+        <v>123.3752445027715</v>
       </c>
       <c r="L6" t="n">
-        <v>147.4695661649656</v>
+        <v>123.786745300987</v>
       </c>
       <c r="M6" t="n">
-        <v>124.9775609230398</v>
+        <v>148.6603817870182</v>
       </c>
       <c r="N6" t="n">
-        <v>125.3974748298762</v>
+        <v>125.3974748298761</v>
       </c>
       <c r="O6" t="n">
-        <v>149.3782131115472</v>
+        <v>149.3782131115473</v>
       </c>
       <c r="P6" t="n">
-        <v>150.8017267373281</v>
+        <v>120.1396462748172</v>
       </c>
       <c r="Q6" t="n">
-        <v>147.3267387566491</v>
+        <v>147.326738756649</v>
       </c>
       <c r="R6" t="n">
-        <v>146.3295739014408</v>
+        <v>122.6467530374623</v>
       </c>
       <c r="S6" t="n">
-        <v>147.2637977767342</v>
+        <v>123.5809769127556</v>
       </c>
       <c r="T6" t="n">
-        <v>124.0558829231466</v>
+        <v>147.738703787125</v>
       </c>
       <c r="U6" t="n">
-        <v>149.2185711066048</v>
+        <v>125.5357502426261</v>
       </c>
       <c r="V6" t="n">
-        <v>124.5906609149871</v>
+        <v>148.2734817789655</v>
       </c>
       <c r="W6" t="n">
-        <v>135.3133819106799</v>
+        <v>135.31338191068</v>
       </c>
       <c r="X6" t="n">
-        <v>123.8916230973377</v>
+        <v>123.8916230973376</v>
       </c>
       <c r="Y6" t="n">
-        <v>132.961712609745</v>
+        <v>132.9617126097449</v>
       </c>
       <c r="Z6" t="n">
-        <v>124.335917362351</v>
+        <v>148.0187382263294</v>
       </c>
       <c r="AA6" t="n">
-        <v>123.8413254603577</v>
+        <v>147.5241463243361</v>
       </c>
       <c r="AB6" t="n">
         <v>125.7850413728566</v>
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.667376928909045</v>
+        <v>3.667376928909054</v>
       </c>
       <c r="C7" t="n">
-        <v>3.27597906112268</v>
+        <v>3.275979061122681</v>
       </c>
       <c r="D7" t="n">
-        <v>4.10514681605917</v>
+        <v>4.105146816059175</v>
       </c>
       <c r="E7" t="n">
         <v>4.814000184457182</v>
       </c>
       <c r="F7" t="n">
-        <v>3.843469420025976</v>
+        <v>3.843469420025967</v>
       </c>
       <c r="G7" t="n">
-        <v>5.815469328611947</v>
+        <v>5.815469328611941</v>
       </c>
       <c r="H7" t="n">
         <v>5.282413223291649</v>
       </c>
       <c r="I7" t="n">
-        <v>4.149726368659009</v>
+        <v>4.149726368659008</v>
       </c>
       <c r="J7" t="n">
-        <v>6.069946168857358</v>
+        <v>6.069946168857356</v>
       </c>
       <c r="K7" t="n">
-        <v>4.948843704463292</v>
+        <v>4.948843704463291</v>
       </c>
       <c r="L7" t="n">
-        <v>5.360344502678731</v>
+        <v>5.360344502678739</v>
       </c>
       <c r="M7" t="n">
-        <v>6.551160124731454</v>
+        <v>6.551160124731457</v>
       </c>
       <c r="N7" t="n">
         <v>6.963772874335449</v>
       </c>
       <c r="O7" t="n">
-        <v>7.197232513451038</v>
+        <v>7.197232513451041</v>
       </c>
       <c r="P7" t="n">
-        <v>8.620851189592951</v>
+        <v>8.620851189592965</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.217517094362416</v>
+        <v>5.217517094362417</v>
       </c>
       <c r="R7" t="n">
-        <v>4.220352239154036</v>
+        <v>4.220352239154034</v>
       </c>
       <c r="S7" t="n">
         <v>5.154576114447313</v>
       </c>
       <c r="T7" t="n">
-        <v>5.629482124838169</v>
+        <v>5.629482124838176</v>
       </c>
       <c r="U7" t="n">
-        <v>7.102923599322107</v>
+        <v>7.102923599322109</v>
       </c>
       <c r="V7" t="n">
-        <v>6.164260116678813</v>
+        <v>6.164260116678809</v>
       </c>
       <c r="W7" t="n">
-        <v>10.76368405371187</v>
+        <v>10.76368405371188</v>
       </c>
       <c r="X7" t="n">
-        <v>5.465222299029326</v>
+        <v>5.465222299029325</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.285518386320229</v>
+        <v>9.285518386320222</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.909516564042734</v>
+        <v>5.909516564042738</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.41492466204941</v>
+        <v>5.414924662049412</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.343486926759022</v>
+        <v>7.343486926759006</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.029028263103302</v>
+        <v>4.029028263103317</v>
       </c>
       <c r="C8" t="n">
-        <v>4.712736585393811</v>
+        <v>4.712736585393814</v>
       </c>
       <c r="D8" t="n">
-        <v>5.541904340330302</v>
+        <v>5.5419043403303</v>
       </c>
       <c r="E8" t="n">
-        <v>6.250757708728312</v>
+        <v>5.678295376547164</v>
       </c>
       <c r="F8" t="n">
-        <v>4.372609733380559</v>
+        <v>4.372609733380584</v>
       </c>
       <c r="G8" t="n">
-        <v>7.252226852883073</v>
+        <v>7.475157124909916</v>
       </c>
       <c r="H8" t="n">
-        <v>6.719170747562782</v>
+        <v>6.719170747562786</v>
       </c>
       <c r="I8" t="n">
-        <v>5.586483892930138</v>
+        <v>5.58648389293014</v>
       </c>
       <c r="J8" t="n">
         <v>7.50670369312849</v>
       </c>
       <c r="K8" t="n">
-        <v>6.385601228734423</v>
+        <v>6.385601228734419</v>
       </c>
       <c r="L8" t="n">
-        <v>6.797102026949863</v>
+        <v>6.797102026949875</v>
       </c>
       <c r="M8" t="n">
-        <v>7.987917649002577</v>
+        <v>7.987917649001752</v>
       </c>
       <c r="N8" t="n">
-        <v>7.567143239454968</v>
+        <v>7.567143239454971</v>
       </c>
       <c r="O8" t="n">
-        <v>8.029629760968236</v>
+        <v>8.029629760968238</v>
       </c>
       <c r="P8" t="n">
         <v>9.397109604568548</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.36788552462574</v>
+        <v>5.367885524625741</v>
       </c>
       <c r="R8" t="n">
-        <v>5.657109763425164</v>
+        <v>5.657109763425167</v>
       </c>
       <c r="S8" t="n">
-        <v>6.591333638718444</v>
+        <v>6.591333638718449</v>
       </c>
       <c r="T8" t="n">
-        <v>7.066239649109304</v>
+        <v>7.066239649109301</v>
       </c>
       <c r="U8" t="n">
-        <v>7.879870103209572</v>
+        <v>8.016385876405725</v>
       </c>
       <c r="V8" t="n">
-        <v>7.601017640949946</v>
+        <v>7.301686404897199</v>
       </c>
       <c r="W8" t="n">
-        <v>12.20065286523118</v>
+        <v>12.20065286523119</v>
       </c>
       <c r="X8" t="n">
-        <v>5.714126346700649</v>
+        <v>5.714126346700644</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.78271684922957</v>
+        <v>11.78271684922955</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.346274088313862</v>
+        <v>6.251197248964061</v>
       </c>
       <c r="AA8" t="n">
         <v>6.85168218632054</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.903282763684347</v>
+        <v>9.903282763684359</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.331140906386914</v>
+        <v>6.331140906386927</v>
       </c>
       <c r="C9" t="n">
-        <v>7.044347316671104</v>
+        <v>7.044347316671105</v>
       </c>
       <c r="D9" t="n">
-        <v>7.873515071607595</v>
+        <v>7.8735150716076</v>
       </c>
       <c r="E9" t="n">
-        <v>8.582368440005602</v>
+        <v>8.327430627522933</v>
       </c>
       <c r="F9" t="n">
-        <v>7.611837675574403</v>
+        <v>5.065422746784447</v>
       </c>
       <c r="G9" t="n">
-        <v>9.583837584160365</v>
+        <v>9.583838038262492</v>
       </c>
       <c r="H9" t="n">
-        <v>9.050781478840072</v>
+        <v>9.050781478840083</v>
       </c>
       <c r="I9" t="n">
-        <v>7.918094624207432</v>
+        <v>7.918094624207439</v>
       </c>
       <c r="J9" t="n">
-        <v>9.838314424405782</v>
+        <v>9.838314424405779</v>
       </c>
       <c r="K9" t="n">
         <v>8.717211960011717</v>
       </c>
       <c r="L9" t="n">
-        <v>9.128712758227163</v>
+        <v>9.128712758227175</v>
       </c>
       <c r="M9" t="n">
-        <v>10.31952838027987</v>
+        <v>10.31952838027988</v>
       </c>
       <c r="N9" t="n">
-        <v>10.73214112988387</v>
+        <v>10.73214112988388</v>
       </c>
       <c r="O9" t="n">
-        <v>11.33167064086554</v>
+        <v>11.33167064086556</v>
       </c>
       <c r="P9" t="n">
-        <v>12.83490207860744</v>
+        <v>12.83490207860745</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.985885804012952</v>
+        <v>8.985885804012961</v>
       </c>
       <c r="R9" t="n">
-        <v>7.98872049470246</v>
+        <v>7.988720494702465</v>
       </c>
       <c r="S9" t="n">
-        <v>8.922944369995738</v>
+        <v>8.922944369995742</v>
       </c>
       <c r="T9" t="n">
-        <v>9.3978503803866</v>
+        <v>9.397850380386606</v>
       </c>
       <c r="U9" t="n">
-        <v>10.87771769986632</v>
+        <v>10.87771769986633</v>
       </c>
       <c r="V9" t="n">
-        <v>9.932628372227242</v>
+        <v>11.20731787495555</v>
       </c>
       <c r="W9" t="n">
-        <v>14.53205230926031</v>
+        <v>14.53205230926032</v>
       </c>
       <c r="X9" t="n">
-        <v>9.233590554577757</v>
+        <v>9.233590554577761</v>
       </c>
       <c r="Y9" t="n">
         <v>13.05388664186864</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.677884819591158</v>
+        <v>9.011906845478435</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.183292917597834</v>
+        <v>9.183292917597843</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.11185518230744</v>
+        <v>11.11185518230747</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.89562720007461</v>
+        <v>38.89562720007466</v>
       </c>
       <c r="C2" t="n">
-        <v>41.88777994697599</v>
+        <v>41.88777994697603</v>
       </c>
       <c r="D2" t="n">
-        <v>38.91536827063064</v>
+        <v>38.91536827063065</v>
       </c>
       <c r="E2" t="n">
-        <v>38.94245682634137</v>
+        <v>38.94245682634143</v>
       </c>
       <c r="F2" t="n">
-        <v>38.97006941619549</v>
+        <v>38.97006941619556</v>
       </c>
       <c r="G2" t="n">
-        <v>39.07168208130357</v>
+        <v>39.07168208130361</v>
       </c>
       <c r="H2" t="n">
-        <v>39.05009854660321</v>
+        <v>39.05009854660324</v>
       </c>
       <c r="I2" t="n">
-        <v>38.95466883517143</v>
+        <v>38.95466883517148</v>
       </c>
       <c r="J2" t="n">
-        <v>39.05996851413006</v>
+        <v>39.05996851413012</v>
       </c>
       <c r="K2" t="n">
-        <v>38.94641334617886</v>
+        <v>38.94641334617889</v>
       </c>
       <c r="L2" t="n">
-        <v>38.91408697639318</v>
+        <v>38.91408697639319</v>
       </c>
       <c r="M2" t="n">
-        <v>39.00561718719262</v>
+        <v>39.00561718719268</v>
       </c>
       <c r="N2" t="n">
-        <v>39.15146670145087</v>
+        <v>39.15146670145096</v>
       </c>
       <c r="O2" t="n">
-        <v>43.03876210519868</v>
+        <v>43.03876210519869</v>
       </c>
       <c r="P2" t="n">
-        <v>39.3075545851414</v>
+        <v>39.30755458514144</v>
       </c>
       <c r="Q2" t="n">
-        <v>38.96955331541696</v>
+        <v>38.96955331541702</v>
       </c>
       <c r="R2" t="n">
-        <v>38.92780611236679</v>
+        <v>38.92780611236685</v>
       </c>
       <c r="S2" t="n">
-        <v>39.00658632358374</v>
+        <v>39.0065863235838</v>
       </c>
       <c r="T2" t="n">
-        <v>39.04039400780255</v>
+        <v>39.04039400780258</v>
       </c>
       <c r="U2" t="n">
-        <v>42.42814202574774</v>
+        <v>42.42814202574775</v>
       </c>
       <c r="V2" t="n">
-        <v>39.08967739445876</v>
+        <v>39.08967739445885</v>
       </c>
       <c r="W2" t="n">
         <v>45.14168873592195</v>
       </c>
       <c r="X2" t="n">
-        <v>39.21967913290123</v>
+        <v>39.21967913290131</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.32890419909677</v>
+        <v>39.32890419909682</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.12863726988343</v>
+        <v>40.12863726988346</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.14460104089238</v>
+        <v>39.14460104089242</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.14559980216772</v>
+        <v>39.14559980216777</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.6273325134843</v>
+        <v>38.62733251348433</v>
       </c>
       <c r="C3" t="n">
         <v>43.73351846947249</v>
       </c>
       <c r="D3" t="n">
-        <v>38.76873454556964</v>
+        <v>38.76873454556972</v>
       </c>
       <c r="E3" t="n">
-        <v>38.96177029874114</v>
+        <v>38.96177029874116</v>
       </c>
       <c r="F3" t="n">
-        <v>39.15956899963249</v>
+        <v>39.15956899963252</v>
       </c>
       <c r="G3" t="n">
-        <v>39.87203269465699</v>
+        <v>39.87203269465704</v>
       </c>
       <c r="H3" t="n">
-        <v>39.73552803874092</v>
+        <v>39.73552803874095</v>
       </c>
       <c r="I3" t="n">
         <v>39.05009248889358</v>
       </c>
       <c r="J3" t="n">
-        <v>39.79371168009622</v>
+        <v>39.79371168009627</v>
       </c>
       <c r="K3" t="n">
-        <v>38.98872369687604</v>
+        <v>38.98872369687607</v>
       </c>
       <c r="L3" t="n">
-        <v>38.75772870277303</v>
+        <v>38.75772870277306</v>
       </c>
       <c r="M3" t="n">
-        <v>39.41591659659802</v>
+        <v>39.41591659659809</v>
       </c>
       <c r="N3" t="n">
-        <v>40.45070480965076</v>
+        <v>40.45070480965078</v>
       </c>
       <c r="O3" t="n">
-        <v>47.15448346016358</v>
+        <v>47.15448346016359</v>
       </c>
       <c r="P3" t="n">
-        <v>41.55350935055388</v>
+        <v>41.55350935055395</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.1520216969315</v>
+        <v>39.15202169693153</v>
       </c>
       <c r="R3" t="n">
-        <v>38.85857953666046</v>
+        <v>38.85857953666049</v>
       </c>
       <c r="S3" t="n">
-        <v>39.41187866329315</v>
+        <v>39.41187866329317</v>
       </c>
       <c r="T3" t="n">
-        <v>39.6595876797593</v>
+        <v>39.65958767975933</v>
       </c>
       <c r="U3" t="n">
-        <v>45.41873041201071</v>
+        <v>45.41873041201069</v>
       </c>
       <c r="V3" t="n">
-        <v>40.00251510550862</v>
+        <v>40.00251510550866</v>
       </c>
       <c r="W3" t="n">
-        <v>51.26058970929783</v>
+        <v>51.26058970929781</v>
       </c>
       <c r="X3" t="n">
-        <v>40.93612196809781</v>
+        <v>40.93612196809782</v>
       </c>
       <c r="Y3" t="n">
-        <v>41.72072174588472</v>
+        <v>41.72072174588475</v>
       </c>
       <c r="Z3" t="n">
         <v>41.22517503969029</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.40485856362695</v>
+        <v>40.40485856362697</v>
       </c>
       <c r="AB3" t="n">
-        <v>40.40486403137173</v>
+        <v>40.40486403137177</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.676670834219327</v>
+        <v>1.676670834219329</v>
       </c>
       <c r="C4" t="n">
-        <v>2.018678689634593</v>
+        <v>2.018678689634577</v>
       </c>
       <c r="D4" t="n">
-        <v>1.899655307490384</v>
+        <v>1.899655307490386</v>
       </c>
       <c r="E4" t="n">
-        <v>2.205633005595041</v>
+        <v>2.205633005595028</v>
       </c>
       <c r="F4" t="n">
-        <v>2.517529910415939</v>
+        <v>2.517529910415955</v>
       </c>
       <c r="G4" t="n">
-        <v>3.665291706946818</v>
+        <v>3.66529170694681</v>
       </c>
       <c r="H4" t="n">
-        <v>3.421495753589822</v>
+        <v>3.421495753589807</v>
       </c>
       <c r="I4" t="n">
-        <v>2.343573263131649</v>
+        <v>2.343573263131646</v>
       </c>
       <c r="J4" t="n">
-        <v>3.534129146187819</v>
+        <v>3.534129146187817</v>
       </c>
       <c r="K4" t="n">
-        <v>2.250323717247919</v>
+        <v>2.250323717247899</v>
       </c>
       <c r="L4" t="n">
         <v>1.885182499653941</v>
       </c>
       <c r="M4" t="n">
-        <v>2.932996617772258</v>
+        <v>2.932996617772247</v>
       </c>
       <c r="N4" t="n">
-        <v>4.566495694249539</v>
+        <v>4.566495694249554</v>
       </c>
       <c r="O4" t="n">
-        <v>5.183371669679966</v>
+        <v>5.183371669679984</v>
       </c>
       <c r="P4" t="n">
-        <v>6.329580144507862</v>
+        <v>6.329580144507853</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.511700314704497</v>
+        <v>2.511700314704499</v>
       </c>
       <c r="R4" t="n">
-        <v>2.04014645159034</v>
+        <v>2.04014645159033</v>
       </c>
       <c r="S4" t="n">
-        <v>2.930005177973524</v>
+        <v>2.93000517797351</v>
       </c>
       <c r="T4" t="n">
-        <v>3.311878523527983</v>
+        <v>3.311878523527978</v>
       </c>
       <c r="U4" t="n">
-        <v>3.675350919218087</v>
+        <v>3.67535091921809</v>
       </c>
       <c r="V4" t="n">
-        <v>3.875995585856504</v>
+        <v>3.875995585856508</v>
       </c>
       <c r="W4" t="n">
-        <v>6.477939538563151</v>
+        <v>6.47793953856313</v>
       </c>
       <c r="X4" t="n">
-        <v>5.336986486749961</v>
+        <v>5.336986486749979</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.569367145723978</v>
+        <v>6.569367145723989</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.845509476274607</v>
+        <v>2.84550947627459</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.488944899881171</v>
+        <v>4.488944899881157</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.484206752491981</v>
+        <v>4.484206752492002</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.094531305758323</v>
+        <v>5.094531305758341</v>
       </c>
       <c r="C5" t="n">
-        <v>11.31911599411266</v>
+        <v>11.31911599411265</v>
       </c>
       <c r="D5" t="n">
-        <v>9.302170227551727</v>
+        <v>9.302170227551706</v>
       </c>
       <c r="E5" t="n">
-        <v>14.56017525251249</v>
+        <v>14.5601752525125</v>
       </c>
       <c r="F5" t="n">
-        <v>20.45295801246217</v>
+        <v>20.45295801246215</v>
       </c>
       <c r="G5" t="n">
-        <v>34.14515645473799</v>
+        <v>34.14515645473797</v>
       </c>
       <c r="H5" t="n">
-        <v>38.92190269060197</v>
+        <v>38.92190269060191</v>
       </c>
       <c r="I5" t="n">
-        <v>17.60333566631848</v>
+        <v>17.60333566631864</v>
       </c>
       <c r="J5" t="n">
-        <v>34.54204371183126</v>
+        <v>34.54204371183124</v>
       </c>
       <c r="K5" t="n">
-        <v>14.68495438520137</v>
+        <v>14.68495438520135</v>
       </c>
       <c r="L5" t="n">
-        <v>8.081684322918608</v>
+        <v>8.081684322918626</v>
       </c>
       <c r="M5" t="n">
         <v>25.24551397522624</v>
       </c>
       <c r="N5" t="n">
-        <v>35.61009086146105</v>
+        <v>35.61009086146102</v>
       </c>
       <c r="O5" t="n">
-        <v>59.28774021241821</v>
+        <v>59.28774021241816</v>
       </c>
       <c r="P5" t="n">
-        <v>80.25324388726827</v>
+        <v>80.25324388726831</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.34750142652436</v>
+        <v>18.34750142652435</v>
       </c>
       <c r="R5" t="n">
         <v>12.34433576628536</v>
       </c>
       <c r="S5" t="n">
-        <v>23.44009368603222</v>
+        <v>23.4400936860322</v>
       </c>
       <c r="T5" t="n">
-        <v>33.52213520700272</v>
+        <v>33.52213520700269</v>
       </c>
       <c r="U5" t="n">
         <v>34.72031279614713</v>
       </c>
       <c r="V5" t="n">
-        <v>38.80950153773736</v>
+        <v>38.80950153773746</v>
       </c>
       <c r="W5" t="n">
-        <v>85.31993070859787</v>
+        <v>85.31993070859792</v>
       </c>
       <c r="X5" t="n">
-        <v>67.76794970158178</v>
+        <v>67.7679497015818</v>
       </c>
       <c r="Y5" t="n">
-        <v>92.20845178373332</v>
+        <v>92.20845178373352</v>
       </c>
       <c r="Z5" t="n">
         <v>23.0788230800197</v>
       </c>
       <c r="AA5" t="n">
-        <v>55.13861098970615</v>
+        <v>55.13861098970607</v>
       </c>
       <c r="AB5" t="n">
-        <v>55.87414138519364</v>
+        <v>55.87414138519355</v>
       </c>
     </row>
     <row r="6">
@@ -6101,64 +6101,64 @@
         <v>112.9120644993154</v>
       </c>
       <c r="C6" t="n">
-        <v>135.222760946409</v>
+        <v>113.2540723547306</v>
       </c>
       <c r="D6" t="n">
-        <v>113.1350489725865</v>
+        <v>113.1350489725864</v>
       </c>
       <c r="E6" t="n">
-        <v>135.4097152623693</v>
+        <v>135.4097152623695</v>
       </c>
       <c r="F6" t="n">
-        <v>135.7216121671903</v>
+        <v>135.7216121671904</v>
       </c>
       <c r="G6" t="n">
-        <v>136.8693739637212</v>
+        <v>114.9006853720429</v>
       </c>
       <c r="H6" t="n">
-        <v>136.6255780103642</v>
+        <v>114.6568894186858</v>
       </c>
       <c r="I6" t="n">
         <v>113.5789669282277</v>
       </c>
       <c r="J6" t="n">
-        <v>136.7382114029623</v>
+        <v>114.7695228112839</v>
       </c>
       <c r="K6" t="n">
-        <v>113.4857173823441</v>
+        <v>113.485717382344</v>
       </c>
       <c r="L6" t="n">
-        <v>135.0892647564284</v>
+        <v>135.0892647564283</v>
       </c>
       <c r="M6" t="n">
-        <v>114.1683902828683</v>
+        <v>136.1370788745467</v>
       </c>
       <c r="N6" t="n">
-        <v>115.8095640644489</v>
+        <v>115.809564064449</v>
       </c>
       <c r="O6" t="n">
         <v>116.4264400398796</v>
       </c>
       <c r="P6" t="n">
-        <v>139.5966481722991</v>
+        <v>111.1365297662524</v>
       </c>
       <c r="Q6" t="n">
-        <v>135.7157825714789</v>
+        <v>113.7470939798005</v>
       </c>
       <c r="R6" t="n">
-        <v>135.2442287083647</v>
+        <v>135.2442287083648</v>
       </c>
       <c r="S6" t="n">
-        <v>136.1340874347479</v>
+        <v>114.1653988430696</v>
       </c>
       <c r="T6" t="n">
         <v>136.5159607803024</v>
       </c>
       <c r="U6" t="n">
-        <v>114.9121112940317</v>
+        <v>114.9121112940318</v>
       </c>
       <c r="V6" t="n">
-        <v>115.1113892509526</v>
+        <v>137.0800778426309</v>
       </c>
       <c r="W6" t="n">
         <v>123.4034938779567</v>
@@ -6167,13 +6167,13 @@
         <v>116.5723801518461</v>
       </c>
       <c r="Y6" t="n">
-        <v>122.6932694750021</v>
+        <v>122.6932694750022</v>
       </c>
       <c r="Z6" t="n">
-        <v>136.049591733049</v>
+        <v>136.0495917330491</v>
       </c>
       <c r="AA6" t="n">
-        <v>115.7243385649773</v>
+        <v>137.6930271566555</v>
       </c>
       <c r="AB6" t="n">
         <v>115.7322620934786</v>
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.532394258583277</v>
+        <v>2.532394258583275</v>
       </c>
       <c r="C7" t="n">
-        <v>2.874402113998523</v>
+        <v>2.874402113998521</v>
       </c>
       <c r="D7" t="n">
-        <v>2.755378731854325</v>
+        <v>2.75537873185433</v>
       </c>
       <c r="E7" t="n">
-        <v>3.061356429958975</v>
+        <v>3.06135642995898</v>
       </c>
       <c r="F7" t="n">
-        <v>3.373253334779893</v>
+        <v>3.373253334779903</v>
       </c>
       <c r="G7" t="n">
-        <v>4.521015131310756</v>
+        <v>4.521015131310749</v>
       </c>
       <c r="H7" t="n">
-        <v>4.277219177953745</v>
+        <v>4.277219177953752</v>
       </c>
       <c r="I7" t="n">
         <v>3.199296687495587</v>
       </c>
       <c r="J7" t="n">
-        <v>4.389852570551763</v>
+        <v>4.389852570551765</v>
       </c>
       <c r="K7" t="n">
-        <v>3.106047141611843</v>
+        <v>3.106047141611846</v>
       </c>
       <c r="L7" t="n">
-        <v>2.740905924017887</v>
+        <v>2.740905924017883</v>
       </c>
       <c r="M7" t="n">
-        <v>3.788720042136187</v>
+        <v>3.788720042136196</v>
       </c>
       <c r="N7" t="n">
-        <v>5.422219118613492</v>
+        <v>5.4222191186135</v>
       </c>
       <c r="O7" t="n">
-        <v>6.03909376320847</v>
+        <v>6.039093763208456</v>
       </c>
       <c r="P7" t="n">
-        <v>7.185302238036332</v>
+        <v>7.185302238036321</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.36742373906845</v>
+        <v>3.367423739068448</v>
       </c>
       <c r="R7" t="n">
-        <v>2.89586987595427</v>
+        <v>2.895869875954279</v>
       </c>
       <c r="S7" t="n">
-        <v>3.785728602337457</v>
+        <v>3.785728602337463</v>
       </c>
       <c r="T7" t="n">
-        <v>4.167601947891919</v>
+        <v>4.167601947891928</v>
       </c>
       <c r="U7" t="n">
-        <v>4.52289627722072</v>
+        <v>4.522896277220708</v>
       </c>
       <c r="V7" t="n">
-        <v>4.731719010220454</v>
+        <v>4.73171901022045</v>
       </c>
       <c r="W7" t="n">
-        <v>7.333662962927098</v>
+        <v>7.33366296292708</v>
       </c>
       <c r="X7" t="n">
-        <v>6.192709911113917</v>
+        <v>6.192709911113928</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.426457279805471</v>
+        <v>7.426457279805483</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.701232900638534</v>
+        <v>3.70123290063854</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.344668324245102</v>
+        <v>5.344668324245114</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.339930176855951</v>
+        <v>5.339930176855948</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.768372346919656</v>
+        <v>2.768372346919675</v>
       </c>
       <c r="C8" t="n">
-        <v>3.945184963582273</v>
+        <v>3.94518496358228</v>
       </c>
       <c r="D8" t="n">
-        <v>3.826161581438082</v>
+        <v>3.826161581438073</v>
       </c>
       <c r="E8" t="n">
-        <v>4.132139279542719</v>
+        <v>3.687630369702899</v>
       </c>
       <c r="F8" t="n">
-        <v>3.73928424816682</v>
+        <v>3.739284248166838</v>
       </c>
       <c r="G8" t="n">
-        <v>5.591797980894512</v>
+        <v>5.764900186261099</v>
       </c>
       <c r="H8" t="n">
-        <v>5.348002027537502</v>
+        <v>5.348002027537497</v>
       </c>
       <c r="I8" t="n">
-        <v>4.270079537079336</v>
+        <v>4.270079537079342</v>
       </c>
       <c r="J8" t="n">
-        <v>5.460635420135513</v>
+        <v>5.460635420135509</v>
       </c>
       <c r="K8" t="n">
-        <v>4.176829991195611</v>
+        <v>4.176829991195591</v>
       </c>
       <c r="L8" t="n">
-        <v>3.811688773601627</v>
+        <v>3.811688773601637</v>
       </c>
       <c r="M8" t="n">
-        <v>4.859502891719934</v>
+        <v>4.859502891717919</v>
       </c>
       <c r="N8" t="n">
-        <v>5.845888618026938</v>
+        <v>5.845888618026932</v>
       </c>
       <c r="O8" t="n">
-        <v>6.640596960045036</v>
+        <v>6.64059696004505</v>
       </c>
       <c r="P8" t="n">
-        <v>7.743214424878498</v>
+        <v>7.74321442487849</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.439343638769743</v>
+        <v>3.439343638769749</v>
       </c>
       <c r="R8" t="n">
-        <v>3.966652725538018</v>
+        <v>3.966652725538021</v>
       </c>
       <c r="S8" t="n">
-        <v>4.856511451921196</v>
+        <v>4.856511451921206</v>
       </c>
       <c r="T8" t="n">
-        <v>5.238384797475665</v>
+        <v>5.238384797475675</v>
       </c>
       <c r="U8" t="n">
-        <v>5.082583842553223</v>
+        <v>5.188370904190805</v>
       </c>
       <c r="V8" t="n">
-        <v>5.802501859804201</v>
+        <v>5.566179629553556</v>
       </c>
       <c r="W8" t="n">
-        <v>8.404609873964432</v>
+        <v>8.404609873964416</v>
       </c>
       <c r="X8" t="n">
-        <v>6.341141324979823</v>
+        <v>6.341141324979841</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.314615207346014</v>
+        <v>9.314615207346019</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.772015750222279</v>
+        <v>3.921704062088245</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.415451173828844</v>
+        <v>6.415451173828847</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.282736403297934</v>
+        <v>7.282736403297926</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.43118014856235</v>
+        <v>4.431180148562345</v>
       </c>
       <c r="C9" t="n">
-        <v>5.596397303961004</v>
+        <v>5.596397303961</v>
       </c>
       <c r="D9" t="n">
-        <v>5.477373921816799</v>
+        <v>5.477373921816796</v>
       </c>
       <c r="E9" t="n">
-        <v>5.783351619921455</v>
+        <v>5.593358564341633</v>
       </c>
       <c r="F9" t="n">
-        <v>6.095248524742376</v>
+        <v>4.197525915871415</v>
       </c>
       <c r="G9" t="n">
-        <v>7.243010321273232</v>
+        <v>7.243010702247252</v>
       </c>
       <c r="H9" t="n">
-        <v>6.999214367916227</v>
+        <v>6.999214367916217</v>
       </c>
       <c r="I9" t="n">
-        <v>5.921291877458085</v>
+        <v>5.921291877458067</v>
       </c>
       <c r="J9" t="n">
-        <v>7.111847760514237</v>
+        <v>7.111847760514229</v>
       </c>
       <c r="K9" t="n">
-        <v>5.828042331574325</v>
+        <v>5.828042331574303</v>
       </c>
       <c r="L9" t="n">
-        <v>5.46290111398037</v>
+        <v>5.462901113980362</v>
       </c>
       <c r="M9" t="n">
-        <v>6.510715232098659</v>
+        <v>6.510715232098653</v>
       </c>
       <c r="N9" t="n">
-        <v>8.144214308575974</v>
+        <v>8.144214308575958</v>
       </c>
       <c r="O9" t="n">
-        <v>9.033901275348594</v>
+        <v>9.033901275348587</v>
       </c>
       <c r="P9" t="n">
         <v>10.23944137728976</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.089419310004946</v>
+        <v>6.089419310004935</v>
       </c>
       <c r="R9" t="n">
-        <v>5.617865065916746</v>
+        <v>5.617865065916737</v>
       </c>
       <c r="S9" t="n">
-        <v>6.507723792299926</v>
+        <v>6.507723792299919</v>
       </c>
       <c r="T9" t="n">
         <v>6.889597137854391</v>
       </c>
       <c r="U9" t="n">
-        <v>7.254436243262061</v>
+        <v>7.254436243262049</v>
       </c>
       <c r="V9" t="n">
-        <v>7.453714200182929</v>
+        <v>8.403680377286818</v>
       </c>
       <c r="W9" t="n">
-        <v>10.05565815288957</v>
+        <v>10.05565815288955</v>
       </c>
       <c r="X9" t="n">
-        <v>8.914705101076398</v>
+        <v>8.914705101076382</v>
       </c>
       <c r="Y9" t="n">
         <v>10.14845246976795</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.423228090601005</v>
+        <v>5.92690623661869</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.066663514207574</v>
+        <v>8.066663514207564</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.061925366818421</v>
+        <v>8.061925366818414</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.74068069772324</v>
+        <v>38.74068069772322</v>
       </c>
       <c r="C2" t="n">
         <v>41.71248924242067</v>
       </c>
       <c r="D2" t="n">
-        <v>38.78445088964715</v>
+        <v>38.7844508896471</v>
       </c>
       <c r="E2" t="n">
-        <v>38.74357278028445</v>
+        <v>38.74357278028446</v>
       </c>
       <c r="F2" t="n">
-        <v>38.85590356427712</v>
+        <v>38.85590356427711</v>
       </c>
       <c r="G2" t="n">
         <v>38.83419627692015</v>
       </c>
       <c r="H2" t="n">
-        <v>38.89044966425655</v>
+        <v>38.89044966425656</v>
       </c>
       <c r="I2" t="n">
-        <v>38.79893008260571</v>
+        <v>38.7989300826057</v>
       </c>
       <c r="J2" t="n">
-        <v>38.85478055914813</v>
+        <v>38.85478055914814</v>
       </c>
       <c r="K2" t="n">
-        <v>38.80184700695996</v>
+        <v>38.80184700695997</v>
       </c>
       <c r="L2" t="n">
-        <v>38.76647434972876</v>
+        <v>38.76647434972877</v>
       </c>
       <c r="M2" t="n">
-        <v>38.85018683180322</v>
+        <v>38.85018683180314</v>
       </c>
       <c r="N2" t="n">
-        <v>38.91206937734493</v>
+        <v>38.91206937734496</v>
       </c>
       <c r="O2" t="n">
         <v>42.68021168322561</v>
       </c>
       <c r="P2" t="n">
-        <v>39.09962847556434</v>
+        <v>39.09962847556432</v>
       </c>
       <c r="Q2" t="n">
-        <v>38.78569998408374</v>
+        <v>38.78569998408373</v>
       </c>
       <c r="R2" t="n">
-        <v>38.76825986985776</v>
+        <v>38.76825986985772</v>
       </c>
       <c r="S2" t="n">
-        <v>38.89146759053195</v>
+        <v>38.8914675905319</v>
       </c>
       <c r="T2" t="n">
-        <v>38.87179905617016</v>
+        <v>38.87179905617017</v>
       </c>
       <c r="U2" t="n">
-        <v>42.20499122205365</v>
+        <v>42.20499122205362</v>
       </c>
       <c r="V2" t="n">
-        <v>38.8693552443381</v>
+        <v>38.86935524433809</v>
       </c>
       <c r="W2" t="n">
-        <v>44.72133906469502</v>
+        <v>44.72133906469504</v>
       </c>
       <c r="X2" t="n">
-        <v>39.09878440562591</v>
+        <v>39.09878440562589</v>
       </c>
       <c r="Y2" t="n">
         <v>39.03926711571361</v>
       </c>
       <c r="Z2" t="n">
-        <v>39.84889497996841</v>
+        <v>39.84889497996843</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.00801313739741</v>
+        <v>39.00801313739743</v>
       </c>
       <c r="AB2" t="n">
-        <v>38.94913924149516</v>
+        <v>38.94913924149515</v>
       </c>
     </row>
     <row r="3">
@@ -6694,10 +6694,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.49968387431982</v>
+        <v>38.49968387431985</v>
       </c>
       <c r="C3" t="n">
-        <v>43.49977870817984</v>
+        <v>43.49977870817978</v>
       </c>
       <c r="D3" t="n">
         <v>38.81272051926516</v>
@@ -6706,16 +6706,16 @@
         <v>38.52057584316117</v>
       </c>
       <c r="F3" t="n">
-        <v>39.32438653225964</v>
+        <v>39.32438653225962</v>
       </c>
       <c r="G3" t="n">
-        <v>39.16256889983142</v>
+        <v>39.16256889983141</v>
       </c>
       <c r="H3" t="n">
-        <v>39.57353850901956</v>
+        <v>39.57353850901957</v>
       </c>
       <c r="I3" t="n">
-        <v>38.9171065463608</v>
+        <v>38.91710654636076</v>
       </c>
       <c r="J3" t="n">
         <v>39.31159868139461</v>
@@ -6727,52 +6727,52 @@
         <v>38.6824113800784</v>
       </c>
       <c r="M3" t="n">
-        <v>39.28400145698094</v>
+        <v>39.28400145698092</v>
       </c>
       <c r="N3" t="n">
-        <v>39.72296520088518</v>
+        <v>39.7229652008852</v>
       </c>
       <c r="O3" t="n">
-        <v>46.24609477104305</v>
+        <v>46.24609477104302</v>
       </c>
       <c r="P3" t="n">
         <v>41.04592427454671</v>
       </c>
       <c r="Q3" t="n">
-        <v>38.8204775974113</v>
+        <v>38.82047759741132</v>
       </c>
       <c r="R3" t="n">
         <v>38.69819061561837</v>
       </c>
       <c r="S3" t="n">
-        <v>39.56933332623456</v>
+        <v>39.5693333262345</v>
       </c>
       <c r="T3" t="n">
-        <v>39.4367818550567</v>
+        <v>39.43678185505664</v>
       </c>
       <c r="U3" t="n">
-        <v>45.1806048807194</v>
+        <v>45.18060488071941</v>
       </c>
       <c r="V3" t="n">
-        <v>39.41277602644666</v>
+        <v>39.41277602644663</v>
       </c>
       <c r="W3" t="n">
-        <v>49.71071054320629</v>
+        <v>49.71071054320632</v>
       </c>
       <c r="X3" t="n">
-        <v>41.04895462593351</v>
+        <v>41.04895462593347</v>
       </c>
       <c r="Y3" t="n">
-        <v>40.63324197074098</v>
+        <v>40.63324197074095</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.54908487687777</v>
+        <v>40.54908487687774</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.40870390993957</v>
+        <v>40.40870390993958</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.98293234464252</v>
+        <v>39.98293234464249</v>
       </c>
     </row>
     <row r="4">
@@ -6785,52 +6785,52 @@
         <v>1.471978440301808</v>
       </c>
       <c r="C4" t="n">
-        <v>1.664970398176601</v>
+        <v>1.664970398176602</v>
       </c>
       <c r="D4" t="n">
-        <v>1.966382893365718</v>
+        <v>1.966382893365719</v>
       </c>
       <c r="E4" t="n">
-        <v>1.504645843255035</v>
+        <v>1.504645843255036</v>
       </c>
       <c r="F4" t="n">
-        <v>2.773473723165501</v>
+        <v>2.773473723165498</v>
       </c>
       <c r="G4" t="n">
-        <v>2.528279926623383</v>
+        <v>2.528279926623389</v>
       </c>
       <c r="H4" t="n">
-        <v>3.163687814424699</v>
+        <v>3.1636878144247</v>
       </c>
       <c r="I4" t="n">
         <v>2.129932038590559</v>
       </c>
       <c r="J4" t="n">
-        <v>2.761908279504506</v>
+        <v>2.761908279504509</v>
       </c>
       <c r="K4" t="n">
         <v>2.162880041023635</v>
       </c>
       <c r="L4" t="n">
-        <v>1.763329605371084</v>
+        <v>1.763329605371085</v>
       </c>
       <c r="M4" t="n">
-        <v>2.714087037073948</v>
+        <v>2.714087037073951</v>
       </c>
       <c r="N4" t="n">
         <v>3.407892419317595</v>
       </c>
       <c r="O4" t="n">
-        <v>4.053981984482209</v>
+        <v>4.053981984482212</v>
       </c>
       <c r="P4" t="n">
-        <v>5.526458715153378</v>
+        <v>5.526458715153376</v>
       </c>
       <c r="Q4" t="n">
         <v>1.980491989638682</v>
       </c>
       <c r="R4" t="n">
-        <v>1.783497876607497</v>
+        <v>1.783497876607498</v>
       </c>
       <c r="S4" t="n">
         <v>3.175185759973957</v>
@@ -6839,28 +6839,28 @@
         <v>2.953020616385223</v>
       </c>
       <c r="U4" t="n">
-        <v>3.470096145377472</v>
+        <v>3.470096145377476</v>
       </c>
       <c r="V4" t="n">
-        <v>2.932650841082728</v>
+        <v>2.932650841082727</v>
       </c>
       <c r="W4" t="n">
-        <v>4.235070673023946</v>
+        <v>4.235070673023951</v>
       </c>
       <c r="X4" t="n">
-        <v>5.51692455690725</v>
+        <v>5.516924556907252</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.843484611276227</v>
+        <v>4.84348461127623</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.930202164977501</v>
+        <v>1.930202164977502</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.491621325420163</v>
+        <v>4.491621325420159</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.807763176811536</v>
+        <v>3.807763176811534</v>
       </c>
     </row>
     <row r="5">
@@ -6870,37 +6870,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.814768462323487</v>
+        <v>4.814768462323481</v>
       </c>
       <c r="C5" t="n">
-        <v>8.521670434933537</v>
+        <v>8.52167043493354</v>
       </c>
       <c r="D5" t="n">
-        <v>13.89421275815066</v>
+        <v>13.89421275815065</v>
       </c>
       <c r="E5" t="n">
         <v>5.522636068696096</v>
       </c>
       <c r="F5" t="n">
-        <v>29.05236976983164</v>
+        <v>29.05236976983163</v>
       </c>
       <c r="G5" t="n">
-        <v>21.14429474394049</v>
+        <v>21.14429474394046</v>
       </c>
       <c r="H5" t="n">
-        <v>37.29860766871438</v>
+        <v>37.29860766871434</v>
       </c>
       <c r="I5" t="n">
-        <v>17.32958863476046</v>
+        <v>17.32958863476034</v>
       </c>
       <c r="J5" t="n">
-        <v>26.35569817740621</v>
+        <v>26.35569817740623</v>
       </c>
       <c r="K5" t="n">
         <v>16.82954608482108</v>
       </c>
       <c r="L5" t="n">
-        <v>9.261415756193067</v>
+        <v>9.261415756193053</v>
       </c>
       <c r="M5" t="n">
         <v>26.75705297542314</v>
@@ -6909,46 +6909,46 @@
         <v>35.64659257932351</v>
       </c>
       <c r="O5" t="n">
-        <v>44.97701191919839</v>
+        <v>44.97701191919835</v>
       </c>
       <c r="P5" t="n">
-        <v>68.44696795645393</v>
+        <v>68.4469679564538</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.5437698431192</v>
+        <v>13.54376984311921</v>
       </c>
       <c r="R5" t="n">
-        <v>11.19139770315962</v>
+        <v>11.19139770315963</v>
       </c>
       <c r="S5" t="n">
-        <v>31.55784091496638</v>
+        <v>31.55784091496636</v>
       </c>
       <c r="T5" t="n">
-        <v>31.68299023469861</v>
+        <v>31.68299023469863</v>
       </c>
       <c r="U5" t="n">
-        <v>35.70996108214889</v>
+        <v>35.70996108214897</v>
       </c>
       <c r="V5" t="n">
-        <v>27.80026082818731</v>
+        <v>27.80026082818735</v>
       </c>
       <c r="W5" t="n">
-        <v>52.01679403984674</v>
+        <v>52.01679403984667</v>
       </c>
       <c r="X5" t="n">
-        <v>72.97061666512977</v>
+        <v>72.9706166651298</v>
       </c>
       <c r="Y5" t="n">
-        <v>65.77813647616797</v>
+        <v>65.77813647616803</v>
       </c>
       <c r="Z5" t="n">
         <v>11.63640821232751</v>
       </c>
       <c r="AA5" t="n">
-        <v>58.76890761442382</v>
+        <v>58.76890761442368</v>
       </c>
       <c r="AB5" t="n">
-        <v>49.0866904814109</v>
+        <v>49.08669048141097</v>
       </c>
     </row>
     <row r="6">
@@ -6958,34 +6958,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.5408810361793</v>
+        <v>134.5408810361794</v>
       </c>
       <c r="C6" t="n">
-        <v>134.7338729940542</v>
+        <v>134.7338729940543</v>
       </c>
       <c r="D6" t="n">
-        <v>135.0352854892433</v>
+        <v>135.0352854892432</v>
       </c>
       <c r="E6" t="n">
-        <v>134.5735484391326</v>
+        <v>134.5735484391325</v>
       </c>
       <c r="F6" t="n">
-        <v>113.9473674995399</v>
+        <v>135.8423763190431</v>
       </c>
       <c r="G6" t="n">
-        <v>113.7021737029979</v>
+        <v>135.597182522501</v>
       </c>
       <c r="H6" t="n">
-        <v>114.3375815907992</v>
+        <v>114.3375815907991</v>
       </c>
       <c r="I6" t="n">
-        <v>135.1988346344681</v>
+        <v>113.303825814965</v>
       </c>
       <c r="J6" t="n">
-        <v>135.830810875382</v>
+        <v>113.935802055879</v>
       </c>
       <c r="K6" t="n">
-        <v>113.3367738173982</v>
+        <v>135.2317826369012</v>
       </c>
       <c r="L6" t="n">
         <v>134.8322322012486</v>
@@ -6997,46 +6997,46 @@
         <v>114.5898307252417</v>
       </c>
       <c r="O6" t="n">
-        <v>115.2359202904062</v>
+        <v>137.1772937572839</v>
       </c>
       <c r="P6" t="n">
-        <v>138.649652967648</v>
+        <v>138.6496529676479</v>
       </c>
       <c r="Q6" t="n">
         <v>135.0493945855163</v>
       </c>
       <c r="R6" t="n">
-        <v>134.8524004724851</v>
+        <v>112.9573916529819</v>
       </c>
       <c r="S6" t="n">
-        <v>114.3490795363485</v>
+        <v>114.3490795363484</v>
       </c>
       <c r="T6" t="n">
         <v>136.0219232122628</v>
       </c>
       <c r="U6" t="n">
-        <v>136.5401635180207</v>
+        <v>136.5401635180206</v>
       </c>
       <c r="V6" t="n">
-        <v>114.1065446174572</v>
+        <v>114.1065446174573</v>
       </c>
       <c r="W6" t="n">
-        <v>137.3585221343326</v>
+        <v>137.3585221343325</v>
       </c>
       <c r="X6" t="n">
-        <v>138.5858271527848</v>
+        <v>116.6908183332818</v>
       </c>
       <c r="Y6" t="n">
-        <v>120.9019163506033</v>
+        <v>120.9019163506032</v>
       </c>
       <c r="Z6" t="n">
-        <v>134.999104760855</v>
+        <v>113.104095941352</v>
       </c>
       <c r="AA6" t="n">
-        <v>137.5605239212977</v>
+        <v>115.6655151017947</v>
       </c>
       <c r="AB6" t="n">
-        <v>114.9944083536233</v>
+        <v>114.9944083536234</v>
       </c>
     </row>
     <row r="7">
@@ -7046,52 +7046,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.269847158840897</v>
+        <v>2.269847158840896</v>
       </c>
       <c r="C7" t="n">
-        <v>2.46283911671569</v>
+        <v>2.462839116715688</v>
       </c>
       <c r="D7" t="n">
-        <v>2.764251611904809</v>
+        <v>2.764251611904807</v>
       </c>
       <c r="E7" t="n">
-        <v>2.302514561794125</v>
+        <v>2.302514561794122</v>
       </c>
       <c r="F7" t="n">
-        <v>3.571342441704573</v>
+        <v>3.571342441704583</v>
       </c>
       <c r="G7" t="n">
-        <v>3.326148645162472</v>
+        <v>3.326148645162479</v>
       </c>
       <c r="H7" t="n">
-        <v>3.961556532963787</v>
+        <v>3.961556532963786</v>
       </c>
       <c r="I7" t="n">
-        <v>2.92780075712965</v>
+        <v>2.927800757129646</v>
       </c>
       <c r="J7" t="n">
-        <v>3.559776998043596</v>
+        <v>3.559776998043593</v>
       </c>
       <c r="K7" t="n">
-        <v>2.960748759562724</v>
+        <v>2.960748759562722</v>
       </c>
       <c r="L7" t="n">
-        <v>2.561198323910175</v>
+        <v>2.561198323910172</v>
       </c>
       <c r="M7" t="n">
-        <v>3.511955755613039</v>
+        <v>3.511955755613037</v>
       </c>
       <c r="N7" t="n">
-        <v>4.205761137856686</v>
+        <v>4.205761137856681</v>
       </c>
       <c r="O7" t="n">
-        <v>4.851850785460574</v>
+        <v>4.851850785460572</v>
       </c>
       <c r="P7" t="n">
-        <v>6.324327516131742</v>
+        <v>6.324327516131738</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.778360708177773</v>
+        <v>2.77836070817777</v>
       </c>
       <c r="R7" t="n">
         <v>2.581366595146585</v>
@@ -7103,28 +7103,28 @@
         <v>3.750889334924313</v>
       </c>
       <c r="U7" t="n">
-        <v>4.259182669104081</v>
+        <v>4.259182669104083</v>
       </c>
       <c r="V7" t="n">
         <v>3.730519559621816</v>
       </c>
       <c r="W7" t="n">
-        <v>5.032939391563038</v>
+        <v>5.032939391563037</v>
       </c>
       <c r="X7" t="n">
-        <v>6.314793275446334</v>
+        <v>6.314793275446339</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.642518106580884</v>
+        <v>5.642518106580879</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.72807088351659</v>
+        <v>2.728070883516589</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.289490043959253</v>
+        <v>5.289490043959248</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.605631895350622</v>
+        <v>4.605631895350627</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.452891018910588</v>
+        <v>2.452891018910586</v>
       </c>
       <c r="C8" t="n">
-        <v>3.389265609349818</v>
+        <v>3.389265609349811</v>
       </c>
       <c r="D8" t="n">
-        <v>3.690678104538935</v>
+        <v>3.690678104538933</v>
       </c>
       <c r="E8" t="n">
-        <v>3.228941054428251</v>
+        <v>2.833111731275018</v>
       </c>
       <c r="F8" t="n">
-        <v>3.870196627677029</v>
+        <v>3.870196627677038</v>
       </c>
       <c r="G8" t="n">
-        <v>4.252575137796598</v>
+        <v>4.406720369242101</v>
       </c>
       <c r="H8" t="n">
-        <v>4.887983025597916</v>
+        <v>4.88798302559791</v>
       </c>
       <c r="I8" t="n">
-        <v>3.854227249763774</v>
+        <v>3.85422724976377</v>
       </c>
       <c r="J8" t="n">
-        <v>4.48620349067773</v>
+        <v>4.486203490677717</v>
       </c>
       <c r="K8" t="n">
-        <v>3.887175252196849</v>
+        <v>3.887175252196842</v>
       </c>
       <c r="L8" t="n">
-        <v>3.487624816544299</v>
+        <v>3.487624816544295</v>
       </c>
       <c r="M8" t="n">
-        <v>4.438382248247168</v>
+        <v>4.43838224824451</v>
       </c>
       <c r="N8" t="n">
-        <v>4.555941724703844</v>
+        <v>4.555941724703841</v>
       </c>
       <c r="O8" t="n">
         <v>5.360388667542582</v>
       </c>
       <c r="P8" t="n">
-        <v>6.794048178569057</v>
+        <v>6.79404817856905</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.815312914433902</v>
+        <v>2.8153129144339</v>
       </c>
       <c r="R8" t="n">
-        <v>3.507793087780714</v>
+        <v>3.507793087780708</v>
       </c>
       <c r="S8" t="n">
-        <v>4.899480971147171</v>
+        <v>4.899480971147166</v>
       </c>
       <c r="T8" t="n">
-        <v>4.677315827558441</v>
+        <v>4.677315827558436</v>
       </c>
       <c r="U8" t="n">
-        <v>4.730878788518301</v>
+        <v>4.825012268698634</v>
       </c>
       <c r="V8" t="n">
-        <v>4.656946052255945</v>
+        <v>4.445265873617754</v>
       </c>
       <c r="W8" t="n">
-        <v>5.959511978842539</v>
+        <v>5.959511978842533</v>
       </c>
       <c r="X8" t="n">
-        <v>6.41987797627446</v>
+        <v>6.419877976274468</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.294885648234013</v>
+        <v>7.294885648234001</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.654497376150719</v>
+        <v>2.897306029651242</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.21591653659338</v>
+        <v>6.215916536593371</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.308583707087303</v>
+        <v>6.308583707087298</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.765776986822469</v>
+        <v>3.765776986822472</v>
       </c>
       <c r="C9" t="n">
-        <v>4.645414021518381</v>
+        <v>4.645414021518382</v>
       </c>
       <c r="D9" t="n">
-        <v>4.946826516707504</v>
+        <v>4.946826516707501</v>
       </c>
       <c r="E9" t="n">
-        <v>4.485089466596814</v>
+        <v>4.32661468968854</v>
       </c>
       <c r="F9" t="n">
-        <v>5.753917346507258</v>
+        <v>4.171012861259254</v>
       </c>
       <c r="G9" t="n">
-        <v>5.508723549965164</v>
+        <v>5.508723687832056</v>
       </c>
       <c r="H9" t="n">
-        <v>6.144131437766482</v>
+        <v>6.14413143776648</v>
       </c>
       <c r="I9" t="n">
-        <v>5.110375661932341</v>
+        <v>5.110375661932342</v>
       </c>
       <c r="J9" t="n">
-        <v>5.742351902846292</v>
+        <v>5.742351902846287</v>
       </c>
       <c r="K9" t="n">
-        <v>5.143323664365417</v>
+        <v>5.14332366436542</v>
       </c>
       <c r="L9" t="n">
-        <v>4.743773228712865</v>
+        <v>4.743773228712866</v>
       </c>
       <c r="M9" t="n">
-        <v>5.69453066041573</v>
+        <v>5.694530660415728</v>
       </c>
       <c r="N9" t="n">
-        <v>6.388336042659378</v>
+        <v>6.38833604265937</v>
       </c>
       <c r="O9" t="n">
-        <v>7.26197907075326</v>
+        <v>7.261979070753261</v>
       </c>
       <c r="P9" t="n">
-        <v>8.783944745467986</v>
+        <v>8.783944745467975</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.960935750847358</v>
+        <v>4.960935750847361</v>
       </c>
       <c r="R9" t="n">
-        <v>4.763941499949286</v>
+        <v>4.763941499949279</v>
       </c>
       <c r="S9" t="n">
         <v>6.155629383315735</v>
       </c>
       <c r="T9" t="n">
-        <v>5.933464239727017</v>
+        <v>5.933464239727004</v>
       </c>
       <c r="U9" t="n">
-        <v>6.451704545484823</v>
+        <v>6.451704545484821</v>
       </c>
       <c r="V9" t="n">
-        <v>5.913094464424511</v>
+        <v>6.705468081326623</v>
       </c>
       <c r="W9" t="n">
-        <v>7.215514296365736</v>
+        <v>7.215514296365737</v>
       </c>
       <c r="X9" t="n">
-        <v>8.497368180249033</v>
+        <v>8.497368180249039</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.82509301138357</v>
+        <v>7.825093011383577</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.910645788319276</v>
+        <v>4.496659920604134</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.472064948761944</v>
+        <v>7.472064948761943</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.78820680015332</v>
+        <v>6.788206800153322</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.62780535359531</v>
+        <v>39.62780535359527</v>
       </c>
       <c r="C2" t="n">
-        <v>42.42897767731513</v>
+        <v>42.42897767731518</v>
       </c>
       <c r="D2" t="n">
-        <v>39.599701921459</v>
+        <v>39.59970192145899</v>
       </c>
       <c r="E2" t="n">
-        <v>39.62452743273987</v>
+        <v>39.62452743273985</v>
       </c>
       <c r="F2" t="n">
-        <v>39.55369666745759</v>
+        <v>39.55369666745757</v>
       </c>
       <c r="G2" t="n">
-        <v>39.90855647702611</v>
+        <v>39.90855647702609</v>
       </c>
       <c r="H2" t="n">
-        <v>39.74035433896784</v>
+        <v>39.74035433896783</v>
       </c>
       <c r="I2" t="n">
-        <v>39.58269083639091</v>
+        <v>39.5826908363909</v>
       </c>
       <c r="J2" t="n">
-        <v>39.8312395476548</v>
+        <v>39.83123954765473</v>
       </c>
       <c r="K2" t="n">
-        <v>39.6447447273021</v>
+        <v>39.64474472730206</v>
       </c>
       <c r="L2" t="n">
-        <v>39.77398472797594</v>
+        <v>39.7739847279759</v>
       </c>
       <c r="M2" t="n">
-        <v>40.07409185397335</v>
+        <v>40.07409185397333</v>
       </c>
       <c r="N2" t="n">
-        <v>39.78703596940316</v>
+        <v>39.78703596940313</v>
       </c>
       <c r="O2" t="n">
-        <v>43.85666173165723</v>
+        <v>43.85666173165733</v>
       </c>
       <c r="P2" t="n">
         <v>39.93554293972279</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.65497346321664</v>
+        <v>39.65497346321663</v>
       </c>
       <c r="R2" t="n">
         <v>39.61178445983789</v>
       </c>
       <c r="S2" t="n">
-        <v>39.72578793775206</v>
+        <v>39.72578793775203</v>
       </c>
       <c r="T2" t="n">
-        <v>39.66646276315426</v>
+        <v>39.66646276315422</v>
       </c>
       <c r="U2" t="n">
-        <v>43.41411216989278</v>
+        <v>43.41411216989282</v>
       </c>
       <c r="V2" t="n">
-        <v>39.74794458217399</v>
+        <v>39.74794458217396</v>
       </c>
       <c r="W2" t="n">
-        <v>46.08165313274223</v>
+        <v>46.08165313274222</v>
       </c>
       <c r="X2" t="n">
-        <v>39.74822920439446</v>
+        <v>39.74822920439443</v>
       </c>
       <c r="Y2" t="n">
-        <v>40.06474610469414</v>
+        <v>40.06474610469418</v>
       </c>
       <c r="Z2" t="n">
-        <v>41.08666926668123</v>
+        <v>41.08666926668122</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.70590035324391</v>
+        <v>39.70590035324388</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.94177378170823</v>
+        <v>39.9417737817082</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.45097487424883</v>
+        <v>40.45097487424877</v>
       </c>
       <c r="C3" t="n">
-        <v>44.20048411866664</v>
+        <v>44.20048411866667</v>
       </c>
       <c r="D3" t="n">
-        <v>40.26146647902084</v>
+        <v>40.2614664790208</v>
       </c>
       <c r="E3" t="n">
         <v>40.43402944583197</v>
       </c>
       <c r="F3" t="n">
-        <v>39.93170258396653</v>
+        <v>39.93170258396652</v>
       </c>
       <c r="G3" t="n">
         <v>42.44331769283207</v>
       </c>
       <c r="H3" t="n">
-        <v>41.27343246382681</v>
+        <v>41.27343246382694</v>
       </c>
       <c r="I3" t="n">
-        <v>40.13977739801614</v>
+        <v>40.13977739801616</v>
       </c>
       <c r="J3" t="n">
-        <v>41.90036194552675</v>
+        <v>41.90036194552678</v>
       </c>
       <c r="K3" t="n">
-        <v>40.5742408488531</v>
+        <v>40.57424084885312</v>
       </c>
       <c r="L3" t="n">
-        <v>41.49586428993005</v>
+        <v>41.49586428993013</v>
       </c>
       <c r="M3" t="n">
-        <v>43.63075137593528</v>
+        <v>43.63075137593526</v>
       </c>
       <c r="N3" t="n">
-        <v>41.597701361672</v>
+        <v>41.59770136167199</v>
       </c>
       <c r="O3" t="n">
-        <v>48.24570773055077</v>
+        <v>48.24570773055075</v>
       </c>
       <c r="P3" t="n">
-        <v>42.64196695305375</v>
+        <v>42.64196695305372</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.65212359622695</v>
+        <v>40.65212359622691</v>
       </c>
       <c r="R3" t="n">
-        <v>40.35009231198347</v>
+        <v>40.35009231198342</v>
       </c>
       <c r="S3" t="n">
-        <v>41.14385253628635</v>
+        <v>41.14385253628648</v>
       </c>
       <c r="T3" t="n">
-        <v>40.73915872486352</v>
+        <v>40.73915872486353</v>
       </c>
       <c r="U3" t="n">
-        <v>48.07784639508208</v>
+        <v>48.07784639508227</v>
       </c>
       <c r="V3" t="n">
-        <v>41.3022284302408</v>
+        <v>41.30222843024082</v>
       </c>
       <c r="W3" t="n">
-        <v>53.46988656095328</v>
+        <v>53.4698865609533</v>
       </c>
       <c r="X3" t="n">
-        <v>41.32205080410918</v>
+        <v>41.32205080410909</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.57413803159822</v>
+        <v>43.57413803159886</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.62922251472772</v>
+        <v>43.62922251472769</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.01558290507247</v>
+        <v>41.01558290507251</v>
       </c>
       <c r="AB3" t="n">
-        <v>42.71143754667668</v>
+        <v>42.71143754667674</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.746372723751612</v>
+        <v>4.746372723751751</v>
       </c>
       <c r="C4" t="n">
-        <v>2.925177343542069</v>
+        <v>2.925177343542077</v>
       </c>
       <c r="D4" t="n">
-        <v>4.428931529554578</v>
+        <v>4.428931529554637</v>
       </c>
       <c r="E4" t="n">
-        <v>4.709347099771517</v>
+        <v>4.709347099771519</v>
       </c>
       <c r="F4" t="n">
-        <v>3.909281022146353</v>
+        <v>3.909281022146371</v>
       </c>
       <c r="G4" t="n">
-        <v>7.917585814800334</v>
+        <v>7.917585814800378</v>
       </c>
       <c r="H4" t="n">
-        <v>6.017665288625871</v>
+        <v>6.017665288625948</v>
       </c>
       <c r="I4" t="n">
-        <v>4.236783498225018</v>
+        <v>4.236783498225046</v>
       </c>
       <c r="J4" t="n">
-        <v>7.044532879480905</v>
+        <v>7.044532879480929</v>
       </c>
       <c r="K4" t="n">
-        <v>4.937710742267057</v>
+        <v>4.937710742267075</v>
       </c>
       <c r="L4" t="n">
-        <v>6.397536003215449</v>
+        <v>6.397536003215518</v>
       </c>
       <c r="M4" t="n">
-        <v>9.773732465895236</v>
+        <v>9.773732465895261</v>
       </c>
       <c r="N4" t="n">
-        <v>6.544955779003569</v>
+        <v>6.544955779003386</v>
       </c>
       <c r="O4" t="n">
-        <v>6.440292482152318</v>
+        <v>6.440292482152731</v>
       </c>
       <c r="P4" t="n">
-        <v>8.22241032534539</v>
+        <v>8.222410325345503</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.053249019872613</v>
+        <v>5.053249019872773</v>
       </c>
       <c r="R4" t="n">
-        <v>4.565409358786291</v>
+        <v>4.56540935878639</v>
       </c>
       <c r="S4" t="n">
-        <v>5.85313108601788</v>
+        <v>5.853131086017848</v>
       </c>
       <c r="T4" t="n">
-        <v>5.183025948007153</v>
+        <v>5.183025948007162</v>
       </c>
       <c r="U4" t="n">
-        <v>7.561067205190076</v>
+        <v>7.561067205190528</v>
       </c>
       <c r="V4" t="n">
-        <v>6.10496515343218</v>
+        <v>6.104965153432207</v>
       </c>
       <c r="W4" t="n">
-        <v>9.600188775337818</v>
+        <v>9.600188775337829</v>
       </c>
       <c r="X4" t="n">
-        <v>6.106615516236681</v>
+        <v>6.106615516236651</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.664156839585772</v>
+        <v>9.664156839585539</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.339279982964366</v>
+        <v>6.339279982964381</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.628491670257571</v>
+        <v>5.628491670257715</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.27830752310461</v>
+        <v>8.278307523104615</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.96825481808173</v>
+        <v>44.96825481808193</v>
       </c>
       <c r="C5" t="n">
         <v>14.72283998096817</v>
       </c>
       <c r="D5" t="n">
-        <v>45.12115575548498</v>
+        <v>45.12115575548403</v>
       </c>
       <c r="E5" t="n">
-        <v>47.85494617968618</v>
+        <v>47.85494617968625</v>
       </c>
       <c r="F5" t="n">
-        <v>34.5047473569584</v>
+        <v>34.50474735695848</v>
       </c>
       <c r="G5" t="n">
-        <v>98.5935930636779</v>
+        <v>98.5935930636778</v>
       </c>
       <c r="H5" t="n">
-        <v>79.67822275102243</v>
+        <v>79.67822275102421</v>
       </c>
       <c r="I5" t="n">
-        <v>41.33225040539462</v>
+        <v>41.33225040539546</v>
       </c>
       <c r="J5" t="n">
-        <v>87.00799539100831</v>
+        <v>87.00799539100908</v>
       </c>
       <c r="K5" t="n">
-        <v>49.90348037654734</v>
+        <v>49.9034803765491</v>
       </c>
       <c r="L5" t="n">
-        <v>77.07809899375046</v>
+        <v>77.07809899374961</v>
       </c>
       <c r="M5" t="n">
         <v>141.1511220534268</v>
       </c>
       <c r="N5" t="n">
-        <v>98.15180889631306</v>
+        <v>98.15180889631944</v>
       </c>
       <c r="O5" t="n">
-        <v>72.25282103588287</v>
+        <v>72.25282103588934</v>
       </c>
       <c r="P5" t="n">
-        <v>107.7194212722261</v>
+        <v>107.7194212722257</v>
       </c>
       <c r="Q5" t="n">
-        <v>54.80195061849356</v>
+        <v>54.80195061849656</v>
       </c>
       <c r="R5" t="n">
-        <v>49.03206747086284</v>
+        <v>49.03206747086459</v>
       </c>
       <c r="S5" t="n">
-        <v>62.31927473206441</v>
+        <v>62.31927473206189</v>
       </c>
       <c r="T5" t="n">
-        <v>60.05622178794918</v>
+        <v>60.05622178795033</v>
       </c>
       <c r="U5" t="n">
-        <v>99.18558299300297</v>
+        <v>99.18558299300867</v>
       </c>
       <c r="V5" t="n">
-        <v>67.18795482484006</v>
+        <v>67.18795482484052</v>
       </c>
       <c r="W5" t="n">
-        <v>141.2410238348072</v>
+        <v>141.2410238348073</v>
       </c>
       <c r="X5" t="n">
-        <v>77.1416887699595</v>
+        <v>77.14168876995812</v>
       </c>
       <c r="Y5" t="n">
-        <v>140.8984765397776</v>
+        <v>140.8984765397742</v>
       </c>
       <c r="Z5" t="n">
-        <v>73.10010478856184</v>
+        <v>73.10010478856186</v>
       </c>
       <c r="AA5" t="n">
-        <v>65.67388752374772</v>
+        <v>65.6738875237471</v>
       </c>
       <c r="AB5" t="n">
-        <v>127.0568687080795</v>
+        <v>127.0568687080792</v>
       </c>
     </row>
     <row r="6">
@@ -7824,79 +7824,79 @@
         <v>122.4252960494671</v>
       </c>
       <c r="D6" t="n">
-        <v>147.8228387851368</v>
+        <v>147.8228387851369</v>
       </c>
       <c r="E6" t="n">
-        <v>148.1032543553536</v>
+        <v>148.1032543553537</v>
       </c>
       <c r="F6" t="n">
-        <v>147.3031882777284</v>
+        <v>147.3031882777286</v>
       </c>
       <c r="G6" t="n">
         <v>127.4177045207253</v>
       </c>
       <c r="H6" t="n">
-        <v>149.4115725442079</v>
+        <v>149.4115725442083</v>
       </c>
       <c r="I6" t="n">
-        <v>123.73690220415</v>
+        <v>123.7369022041502</v>
       </c>
       <c r="J6" t="n">
-        <v>150.4384401350631</v>
+        <v>126.544651585406</v>
       </c>
       <c r="K6" t="n">
         <v>124.437829448192</v>
       </c>
       <c r="L6" t="n">
-        <v>125.8976547091404</v>
+        <v>149.7914432587975</v>
       </c>
       <c r="M6" t="n">
-        <v>153.1676397214775</v>
+        <v>153.1676397214774</v>
       </c>
       <c r="N6" t="n">
-        <v>126.0549156754662</v>
+        <v>126.0549156754726</v>
       </c>
       <c r="O6" t="n">
-        <v>125.9502523786149</v>
+        <v>125.9502523786241</v>
       </c>
       <c r="P6" t="n">
         <v>151.6864551055892</v>
       </c>
       <c r="Q6" t="n">
-        <v>124.5533677257976</v>
+        <v>148.4471562754548</v>
       </c>
       <c r="R6" t="n">
-        <v>147.9593166143684</v>
+        <v>147.9593166143687</v>
       </c>
       <c r="S6" t="n">
-        <v>149.2470383416</v>
+        <v>149.2470383416001</v>
       </c>
       <c r="T6" t="n">
-        <v>148.5769332035894</v>
+        <v>124.6831446539321</v>
       </c>
       <c r="U6" t="n">
-        <v>150.9726371312757</v>
+        <v>150.972637131276</v>
       </c>
       <c r="V6" t="n">
-        <v>125.6050838593571</v>
+        <v>149.4988724090146</v>
       </c>
       <c r="W6" t="n">
-        <v>135.2214215027483</v>
+        <v>135.2214215027482</v>
       </c>
       <c r="X6" t="n">
-        <v>149.5005227718189</v>
+        <v>125.606734222162</v>
       </c>
       <c r="Y6" t="n">
-        <v>134.4339108101481</v>
+        <v>134.4339108101659</v>
       </c>
       <c r="Z6" t="n">
         <v>125.8393986888893</v>
       </c>
       <c r="AA6" t="n">
-        <v>149.0223989258398</v>
+        <v>149.02239892584</v>
       </c>
       <c r="AB6" t="n">
-        <v>127.799777777638</v>
+        <v>127.7997777776382</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.928118753529964</v>
+        <v>5.928118753529976</v>
       </c>
       <c r="C7" t="n">
-        <v>4.106923373320421</v>
+        <v>4.106923373320439</v>
       </c>
       <c r="D7" t="n">
-        <v>5.610677559332935</v>
+        <v>5.610677559332926</v>
       </c>
       <c r="E7" t="n">
-        <v>5.891093129549872</v>
+        <v>5.891093129549884</v>
       </c>
       <c r="F7" t="n">
-        <v>5.091027051924707</v>
+        <v>5.091027051924674</v>
       </c>
       <c r="G7" t="n">
-        <v>9.099331844578687</v>
+        <v>9.099331844578726</v>
       </c>
       <c r="H7" t="n">
-        <v>7.199411318404223</v>
+        <v>7.199411318404335</v>
       </c>
       <c r="I7" t="n">
-        <v>5.418529528003375</v>
+        <v>5.418529528003451</v>
       </c>
       <c r="J7" t="n">
-        <v>8.226278909259253</v>
+        <v>8.226278909259314</v>
       </c>
       <c r="K7" t="n">
-        <v>6.119456772045406</v>
+        <v>6.119456772045408</v>
       </c>
       <c r="L7" t="n">
-        <v>7.579282032993802</v>
+        <v>7.579282032993814</v>
       </c>
       <c r="M7" t="n">
-        <v>10.95547849567359</v>
+        <v>10.95547849567361</v>
       </c>
       <c r="N7" t="n">
-        <v>7.726701808781921</v>
+        <v>7.726701808781836</v>
       </c>
       <c r="O7" t="n">
-        <v>7.622028175339446</v>
+        <v>7.622028175339821</v>
       </c>
       <c r="P7" t="n">
-        <v>9.404146018532522</v>
+        <v>9.404146018532742</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.234995049650965</v>
+        <v>6.23499504965103</v>
       </c>
       <c r="R7" t="n">
-        <v>5.747155388564646</v>
+        <v>5.74715538856455</v>
       </c>
       <c r="S7" t="n">
-        <v>7.034877115796241</v>
+        <v>7.034877115796426</v>
       </c>
       <c r="T7" t="n">
-        <v>6.364771977785508</v>
+        <v>6.36477197778555</v>
       </c>
       <c r="U7" t="n">
-        <v>8.758204090832026</v>
+        <v>8.758204090832157</v>
       </c>
       <c r="V7" t="n">
-        <v>7.286711183210533</v>
+        <v>7.286711183210641</v>
       </c>
       <c r="W7" t="n">
-        <v>10.78193480511617</v>
+        <v>10.78193480511618</v>
       </c>
       <c r="X7" t="n">
-        <v>7.288361546015039</v>
+        <v>7.288361546015049</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.86356553986758</v>
+        <v>10.86356553986812</v>
       </c>
       <c r="Z7" t="n">
         <v>7.521026012742729</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.810237700035927</v>
+        <v>6.810237700035798</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.460053552882957</v>
+        <v>9.460053552882954</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.403079327219083</v>
+        <v>6.403079327219016</v>
       </c>
       <c r="C8" t="n">
-        <v>5.849947282378545</v>
+        <v>5.849947282378585</v>
       </c>
       <c r="D8" t="n">
-        <v>7.353701468391055</v>
+        <v>7.353701468391072</v>
       </c>
       <c r="E8" t="n">
-        <v>7.63411703860799</v>
+        <v>6.958910718456579</v>
       </c>
       <c r="F8" t="n">
-        <v>5.763537072864393</v>
+        <v>5.763537072864409</v>
       </c>
       <c r="G8" t="n">
-        <v>10.8423557536368</v>
+        <v>11.10529694673455</v>
       </c>
       <c r="H8" t="n">
-        <v>8.942435227462347</v>
+        <v>8.942435227462342</v>
       </c>
       <c r="I8" t="n">
-        <v>7.161553437061492</v>
+        <v>7.161553437061593</v>
       </c>
       <c r="J8" t="n">
-        <v>9.969302818317381</v>
+        <v>9.969302818317438</v>
       </c>
       <c r="K8" t="n">
-        <v>7.862480681103534</v>
+        <v>7.862480681103536</v>
       </c>
       <c r="L8" t="n">
-        <v>9.322305942051923</v>
+        <v>9.322305942051853</v>
       </c>
       <c r="M8" t="n">
-        <v>12.69850240473172</v>
+        <v>12.69850240473114</v>
       </c>
       <c r="N8" t="n">
-        <v>8.486764490041317</v>
+        <v>8.486764490041718</v>
       </c>
       <c r="O8" t="n">
-        <v>8.652227472459771</v>
+        <v>8.652227472459559</v>
       </c>
       <c r="P8" t="n">
-        <v>10.3681308375483</v>
+        <v>10.36813083754851</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.460752236353435</v>
+        <v>6.460752236353633</v>
       </c>
       <c r="R8" t="n">
-        <v>7.490179297622768</v>
+        <v>7.490179297622854</v>
       </c>
       <c r="S8" t="n">
-        <v>8.777901024854353</v>
+        <v>8.77790102485425</v>
       </c>
       <c r="T8" t="n">
-        <v>8.107795886843633</v>
+        <v>8.107795886843627</v>
       </c>
       <c r="U8" t="n">
-        <v>9.721554006381101</v>
+        <v>9.882822434020726</v>
       </c>
       <c r="V8" t="n">
-        <v>9.029735092268648</v>
+        <v>8.681221206003094</v>
       </c>
       <c r="W8" t="n">
-        <v>12.52520792294852</v>
+        <v>12.52520792294854</v>
       </c>
       <c r="X8" t="n">
-        <v>7.630339255850592</v>
+        <v>7.630339255850597</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.86439778820211</v>
+        <v>13.86439778820229</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.264049921800837</v>
+        <v>7.972431659129762</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.553261609094049</v>
+        <v>8.55326160909406</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.52767564758813</v>
+        <v>12.52767564758815</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.290447625379633</v>
+        <v>9.290447625379665</v>
       </c>
       <c r="C9" t="n">
-        <v>8.819697494130603</v>
+        <v>8.819697494130635</v>
       </c>
       <c r="D9" t="n">
-        <v>10.32345168014312</v>
+        <v>10.32345168014308</v>
       </c>
       <c r="E9" t="n">
-        <v>10.60386725036005</v>
+        <v>10.29219014112949</v>
       </c>
       <c r="F9" t="n">
-        <v>9.803801172734886</v>
+        <v>6.690656054886064</v>
       </c>
       <c r="G9" t="n">
-        <v>13.81210596538885</v>
+        <v>13.81210615501812</v>
       </c>
       <c r="H9" t="n">
-        <v>11.91218543921441</v>
+        <v>11.91218543921443</v>
       </c>
       <c r="I9" t="n">
-        <v>10.13130364881355</v>
+        <v>10.13130364881357</v>
       </c>
       <c r="J9" t="n">
-        <v>12.93905303006944</v>
+        <v>12.93905303006953</v>
       </c>
       <c r="K9" t="n">
-        <v>10.83223089285559</v>
+        <v>10.83223089285558</v>
       </c>
       <c r="L9" t="n">
-        <v>12.29205615380398</v>
+        <v>12.29205615380386</v>
       </c>
       <c r="M9" t="n">
-        <v>15.66825261648377</v>
+        <v>15.66825261648381</v>
       </c>
       <c r="N9" t="n">
-        <v>12.4394759295921</v>
+        <v>12.43947592959186</v>
       </c>
       <c r="O9" t="n">
-        <v>12.7823486724614</v>
+        <v>12.78234867246207</v>
       </c>
       <c r="P9" t="n">
-        <v>14.6617978846273</v>
+        <v>14.66179788462744</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.94776936009042</v>
+        <v>10.94776936009058</v>
       </c>
       <c r="R9" t="n">
-        <v>10.45992950937483</v>
+        <v>10.45992950937497</v>
       </c>
       <c r="S9" t="n">
-        <v>11.74765123660642</v>
+        <v>11.74765123660653</v>
       </c>
       <c r="T9" t="n">
-        <v>11.07754609859569</v>
+        <v>11.07754609859577</v>
       </c>
       <c r="U9" t="n">
-        <v>13.47325002628206</v>
+        <v>13.47325002628225</v>
       </c>
       <c r="V9" t="n">
-        <v>11.99948530402072</v>
+        <v>13.55786871626831</v>
       </c>
       <c r="W9" t="n">
-        <v>15.49470892592635</v>
+        <v>15.49470892592636</v>
       </c>
       <c r="X9" t="n">
-        <v>12.00113566682522</v>
+        <v>12.00113566682532</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.57633966067776</v>
+        <v>15.57633966067801</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.23380013355291</v>
+        <v>11.41960181000639</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.52301182084611</v>
+        <v>11.52301182084623</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.17282767369314</v>
+        <v>14.17282767369318</v>
       </c>
     </row>
   </sheetData>
@@ -8326,19 +8326,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.12384717844134</v>
+        <v>39.12384717844137</v>
       </c>
       <c r="C2" t="n">
         <v>42.11664454293246</v>
       </c>
       <c r="D2" t="n">
-        <v>39.17871795181071</v>
+        <v>39.17871795181073</v>
       </c>
       <c r="E2" t="n">
-        <v>39.21435283400168</v>
+        <v>39.21435283400169</v>
       </c>
       <c r="F2" t="n">
-        <v>39.1909588529766</v>
+        <v>39.19095885297659</v>
       </c>
       <c r="G2" t="n">
         <v>39.52958573128264</v>
@@ -8347,34 +8347,34 @@
         <v>39.3703157582039</v>
       </c>
       <c r="I2" t="n">
-        <v>39.15875948471033</v>
+        <v>39.15875948471034</v>
       </c>
       <c r="J2" t="n">
-        <v>39.37678748761557</v>
+        <v>39.37678748761559</v>
       </c>
       <c r="K2" t="n">
-        <v>39.22608729596771</v>
+        <v>39.22608729596774</v>
       </c>
       <c r="L2" t="n">
-        <v>39.23359523199596</v>
+        <v>39.23359523199597</v>
       </c>
       <c r="M2" t="n">
-        <v>39.3428399610267</v>
+        <v>39.34283996102673</v>
       </c>
       <c r="N2" t="n">
-        <v>39.36102472624997</v>
+        <v>39.36102472625001</v>
       </c>
       <c r="O2" t="n">
         <v>43.32787534108692</v>
       </c>
       <c r="P2" t="n">
-        <v>39.55055949586475</v>
+        <v>39.55055949586473</v>
       </c>
       <c r="Q2" t="n">
         <v>39.23162263296408</v>
       </c>
       <c r="R2" t="n">
-        <v>39.17541807078082</v>
+        <v>39.17541807078084</v>
       </c>
       <c r="S2" t="n">
         <v>39.23846230477346</v>
@@ -8383,25 +8383,25 @@
         <v>39.25961384981365</v>
       </c>
       <c r="U2" t="n">
-        <v>42.78391163673516</v>
+        <v>42.78391163673513</v>
       </c>
       <c r="V2" t="n">
-        <v>39.31740309458157</v>
+        <v>39.31740309458161</v>
       </c>
       <c r="W2" t="n">
-        <v>45.49802111322249</v>
+        <v>45.49802111322253</v>
       </c>
       <c r="X2" t="n">
         <v>39.44842444762973</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.71570541034198</v>
+        <v>39.715705410342</v>
       </c>
       <c r="Z2" t="n">
         <v>40.42062655448035</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.28374330056509</v>
+        <v>39.28374330056511</v>
       </c>
       <c r="AB2" t="n">
         <v>39.54248256743843</v>
@@ -8414,13 +8414,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.83637666694626</v>
+        <v>38.83637666694629</v>
       </c>
       <c r="C3" t="n">
         <v>43.91215837502723</v>
       </c>
       <c r="D3" t="n">
-        <v>39.22935709487688</v>
+        <v>39.2293570948769</v>
       </c>
       <c r="E3" t="n">
         <v>39.48266164744251</v>
@@ -8429,7 +8429,7 @@
         <v>39.31688747746517</v>
       </c>
       <c r="G3" t="n">
-        <v>41.71078385986695</v>
+        <v>41.71078385986696</v>
       </c>
       <c r="H3" t="n">
         <v>40.60688493357185</v>
@@ -8438,61 +8438,61 @@
         <v>39.08752321647422</v>
       </c>
       <c r="J3" t="n">
-        <v>40.63336446408847</v>
+        <v>40.63336446408849</v>
       </c>
       <c r="K3" t="n">
-        <v>39.56320877516193</v>
+        <v>39.56320877516188</v>
       </c>
       <c r="L3" t="n">
-        <v>39.61572485320135</v>
+        <v>39.61572485320136</v>
       </c>
       <c r="M3" t="n">
-        <v>40.4027897282804</v>
+        <v>40.40278972828034</v>
       </c>
       <c r="N3" t="n">
         <v>40.53221691177359</v>
       </c>
       <c r="O3" t="n">
-        <v>47.35621740196846</v>
+        <v>47.35621740196849</v>
       </c>
       <c r="P3" t="n">
-        <v>41.86767326082256</v>
+        <v>41.86767326082254</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.60296573589879</v>
+        <v>39.60296573589877</v>
       </c>
       <c r="R3" t="n">
-        <v>39.20732980751943</v>
+        <v>39.20732980751938</v>
       </c>
       <c r="S3" t="n">
-        <v>39.64884978745271</v>
+        <v>39.64884978745268</v>
       </c>
       <c r="T3" t="n">
-        <v>39.80847848675856</v>
+        <v>39.80847848675855</v>
       </c>
       <c r="U3" t="n">
-        <v>46.19564927486731</v>
+        <v>46.19564927486729</v>
       </c>
       <c r="V3" t="n">
-        <v>40.20879768420929</v>
+        <v>40.20879768420931</v>
       </c>
       <c r="W3" t="n">
-        <v>51.99465384872511</v>
+        <v>51.99465384872513</v>
       </c>
       <c r="X3" t="n">
-        <v>41.15376353795579</v>
+        <v>41.15376353795585</v>
       </c>
       <c r="Y3" t="n">
         <v>43.05948968395287</v>
       </c>
       <c r="Z3" t="n">
-        <v>41.68845812591289</v>
+        <v>41.68845812591286</v>
       </c>
       <c r="AA3" t="n">
-        <v>39.97850103511617</v>
+        <v>39.97850103511615</v>
       </c>
       <c r="AB3" t="n">
-        <v>41.82123346035706</v>
+        <v>41.82123346035704</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.062176236610326</v>
+        <v>2.062176236610334</v>
       </c>
       <c r="C4" t="n">
-        <v>2.337681514150317</v>
+        <v>2.337681514150295</v>
       </c>
       <c r="D4" t="n">
-        <v>2.681966863619872</v>
+        <v>2.681966863619856</v>
       </c>
       <c r="E4" t="n">
-        <v>3.084479250822616</v>
+        <v>3.084479250822596</v>
       </c>
       <c r="F4" t="n">
-        <v>2.82023347338136</v>
+        <v>2.820233473381339</v>
       </c>
       <c r="G4" t="n">
-        <v>6.645179839908221</v>
+        <v>6.645179839908174</v>
       </c>
       <c r="H4" t="n">
-        <v>4.846152226176707</v>
+        <v>4.846152226176698</v>
       </c>
       <c r="I4" t="n">
-        <v>2.456526796372418</v>
+        <v>2.456526796372423</v>
       </c>
       <c r="J4" t="n">
-        <v>4.919449671972986</v>
+        <v>4.91944967197299</v>
       </c>
       <c r="K4" t="n">
-        <v>3.217025396848166</v>
+        <v>3.21702539684815</v>
       </c>
       <c r="L4" t="n">
-        <v>3.301830988108375</v>
+        <v>3.301830988108342</v>
       </c>
       <c r="M4" t="n">
-        <v>4.54723875036726</v>
+        <v>4.547238750367237</v>
       </c>
       <c r="N4" t="n">
-        <v>4.74120574617078</v>
+        <v>4.741205746170785</v>
       </c>
       <c r="O4" t="n">
-        <v>5.344334171311009</v>
+        <v>5.344334171310978</v>
       </c>
       <c r="P4" t="n">
-        <v>6.882088159271723</v>
+        <v>6.882088159271738</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.279549574602944</v>
+        <v>3.279549574602937</v>
       </c>
       <c r="R4" t="n">
-        <v>2.644693189366807</v>
+        <v>2.644693189366815</v>
       </c>
       <c r="S4" t="n">
-        <v>3.356806814094277</v>
+        <v>3.356806814094286</v>
       </c>
       <c r="T4" t="n">
-        <v>3.595723245514729</v>
+        <v>3.595723245514735</v>
       </c>
       <c r="U4" t="n">
-        <v>4.769968993016224</v>
+        <v>4.76996899301622</v>
       </c>
       <c r="V4" t="n">
-        <v>4.249474080606404</v>
+        <v>4.249474080606403</v>
       </c>
       <c r="W4" t="n">
-        <v>7.487171260028173</v>
+        <v>7.48717126002818</v>
       </c>
       <c r="X4" t="n">
-        <v>5.728425805013782</v>
+        <v>5.728425805013771</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.725722890572671</v>
+        <v>8.72572289057265</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.540261341893184</v>
+        <v>3.540261341893163</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.868276491848072</v>
+        <v>3.868276491848073</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.760856480985105</v>
+        <v>6.760856480985115</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.48411635474995</v>
+        <v>6.484116354749934</v>
       </c>
       <c r="C5" t="n">
-        <v>11.65828659160805</v>
+        <v>11.65828659160802</v>
       </c>
       <c r="D5" t="n">
-        <v>18.15350419311615</v>
+        <v>18.1535041931161</v>
       </c>
       <c r="E5" t="n">
-        <v>24.74226017259319</v>
+        <v>24.74226017259321</v>
       </c>
       <c r="F5" t="n">
-        <v>20.68524140521782</v>
+        <v>20.68524140521785</v>
       </c>
       <c r="G5" t="n">
-        <v>76.46811014776776</v>
+        <v>76.46811014776738</v>
       </c>
       <c r="H5" t="n">
-        <v>61.65685618088651</v>
+        <v>61.65685618088639</v>
       </c>
       <c r="I5" t="n">
         <v>14.48270247170939</v>
       </c>
       <c r="J5" t="n">
-        <v>52.73600491698853</v>
+        <v>52.73600491698841</v>
       </c>
       <c r="K5" t="n">
-        <v>25.42704021389233</v>
+        <v>25.42704021389238</v>
       </c>
       <c r="L5" t="n">
-        <v>26.37327729980016</v>
+        <v>26.37327729980012</v>
       </c>
       <c r="M5" t="n">
-        <v>49.00417511835839</v>
+        <v>49.00417511835832</v>
       </c>
       <c r="N5" t="n">
-        <v>50.51609787791905</v>
+        <v>50.51609787791914</v>
       </c>
       <c r="O5" t="n">
-        <v>57.34748780083397</v>
+        <v>57.34748780083405</v>
       </c>
       <c r="P5" t="n">
-        <v>84.38871560201076</v>
+        <v>84.38871560201082</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.66294990810227</v>
+        <v>26.66294990810224</v>
       </c>
       <c r="R5" t="n">
-        <v>18.28409852971618</v>
+        <v>18.28409852971608</v>
       </c>
       <c r="S5" t="n">
-        <v>26.51044108750296</v>
+        <v>26.51044108750297</v>
       </c>
       <c r="T5" t="n">
-        <v>35.22859734494772</v>
+        <v>35.22859734494767</v>
       </c>
       <c r="U5" t="n">
-        <v>50.56662546835773</v>
+        <v>50.56662546835778</v>
       </c>
       <c r="V5" t="n">
-        <v>40.4909154733284</v>
+        <v>40.49091547332844</v>
       </c>
       <c r="W5" t="n">
         <v>103.2313247846855</v>
       </c>
       <c r="X5" t="n">
-        <v>71.77487255674862</v>
+        <v>71.7748725567486</v>
       </c>
       <c r="Y5" t="n">
-        <v>124.2021452646126</v>
+        <v>124.2021452646122</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.30082650038939</v>
+        <v>29.30082650038933</v>
       </c>
       <c r="AA5" t="n">
-        <v>38.91395700791563</v>
+        <v>38.91395700791568</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.49816260224245</v>
+        <v>96.49816260224225</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>135.4453441560183</v>
+        <v>113.3144745113888</v>
       </c>
       <c r="C6" t="n">
-        <v>135.7208494335583</v>
+        <v>135.7208494335582</v>
       </c>
       <c r="D6" t="n">
-        <v>113.9342651383985</v>
+        <v>113.9342651383983</v>
       </c>
       <c r="E6" t="n">
-        <v>114.3367775256012</v>
+        <v>136.4676471702304</v>
       </c>
       <c r="F6" t="n">
-        <v>114.07253174816</v>
+        <v>136.2034013927891</v>
       </c>
       <c r="G6" t="n">
-        <v>140.028347759316</v>
+        <v>117.8974781146866</v>
       </c>
       <c r="H6" t="n">
-        <v>116.0984505009553</v>
+        <v>138.2293201455846</v>
       </c>
       <c r="I6" t="n">
-        <v>113.7088250711508</v>
+        <v>135.8396947157804</v>
       </c>
       <c r="J6" t="n">
-        <v>138.3026175913811</v>
+        <v>116.1717479467514</v>
       </c>
       <c r="K6" t="n">
-        <v>114.4693236716266</v>
+        <v>136.600193316256</v>
       </c>
       <c r="L6" t="n">
-        <v>136.6849989075162</v>
+        <v>114.5541292628868</v>
       </c>
       <c r="M6" t="n">
-        <v>115.7995370251459</v>
+        <v>137.930406669775</v>
       </c>
       <c r="N6" t="n">
-        <v>116.0007806945644</v>
+        <v>116.0007806945642</v>
       </c>
       <c r="O6" t="n">
-        <v>138.79553915582</v>
+        <v>116.6039091197044</v>
       </c>
       <c r="P6" t="n">
-        <v>111.7019702560929</v>
+        <v>111.7019702560927</v>
       </c>
       <c r="Q6" t="n">
-        <v>114.5318478493816</v>
+        <v>136.6627174940109</v>
       </c>
       <c r="R6" t="n">
-        <v>136.0278611087748</v>
+        <v>136.0278611087747</v>
       </c>
       <c r="S6" t="n">
-        <v>114.6091050888729</v>
+        <v>114.6091050888728</v>
       </c>
       <c r="T6" t="n">
-        <v>114.8480215202934</v>
+        <v>114.8480215202932</v>
       </c>
       <c r="U6" t="n">
-        <v>138.1749012560175</v>
+        <v>116.044031611388</v>
       </c>
       <c r="V6" t="n">
-        <v>137.6326420000144</v>
+        <v>137.6326420000143</v>
       </c>
       <c r="W6" t="n">
-        <v>124.4335050355528</v>
+        <v>124.4335050355529</v>
       </c>
       <c r="X6" t="n">
-        <v>139.1115937244218</v>
+        <v>116.9807240797923</v>
       </c>
       <c r="Y6" t="n">
-        <v>124.8850989918216</v>
+        <v>124.8850989918215</v>
       </c>
       <c r="Z6" t="n">
-        <v>114.7925596166718</v>
+        <v>114.7925596166717</v>
       </c>
       <c r="AA6" t="n">
-        <v>137.2514444112561</v>
+        <v>137.251444411256</v>
       </c>
       <c r="AB6" t="n">
-        <v>118.0335777792343</v>
+        <v>118.0335777792342</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.005950187686251</v>
+        <v>3.005950187686247</v>
       </c>
       <c r="C7" t="n">
-        <v>3.281455465226219</v>
+        <v>3.281455465226207</v>
       </c>
       <c r="D7" t="n">
-        <v>3.625740814695776</v>
+        <v>3.625740814695766</v>
       </c>
       <c r="E7" t="n">
-        <v>4.028253201898515</v>
+        <v>4.028253201898508</v>
       </c>
       <c r="F7" t="n">
-        <v>3.764007424457286</v>
+        <v>3.764007424457248</v>
       </c>
       <c r="G7" t="n">
-        <v>7.588953790984118</v>
+        <v>7.588953790984073</v>
       </c>
       <c r="H7" t="n">
-        <v>5.789926177252606</v>
+        <v>5.789926177252609</v>
       </c>
       <c r="I7" t="n">
-        <v>3.400300747448327</v>
+        <v>3.400300747448336</v>
       </c>
       <c r="J7" t="n">
-        <v>5.863223623048914</v>
+        <v>5.863223623048897</v>
       </c>
       <c r="K7" t="n">
-        <v>4.160799347924071</v>
+        <v>4.160799347924064</v>
       </c>
       <c r="L7" t="n">
-        <v>4.245604939184279</v>
+        <v>4.245604939184252</v>
       </c>
       <c r="M7" t="n">
-        <v>5.491012701443163</v>
+        <v>5.49101270144315</v>
       </c>
       <c r="N7" t="n">
-        <v>5.68497969724671</v>
+        <v>5.684979697246693</v>
       </c>
       <c r="O7" t="n">
-        <v>6.288104219851242</v>
+        <v>6.288104219851236</v>
       </c>
       <c r="P7" t="n">
-        <v>7.825858207812007</v>
+        <v>7.825858207812002</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.223323525678881</v>
+        <v>4.223323525678849</v>
       </c>
       <c r="R7" t="n">
-        <v>3.588467140442733</v>
+        <v>3.588467140442728</v>
       </c>
       <c r="S7" t="n">
-        <v>4.300580765170186</v>
+        <v>4.300580765170197</v>
       </c>
       <c r="T7" t="n">
-        <v>4.539497196590633</v>
+        <v>4.539497196590648</v>
       </c>
       <c r="U7" t="n">
-        <v>5.728202795787406</v>
+        <v>5.72820279578742</v>
       </c>
       <c r="V7" t="n">
-        <v>5.193248031682313</v>
+        <v>5.193248031682316</v>
       </c>
       <c r="W7" t="n">
-        <v>8.430945211104104</v>
+        <v>8.430945211104092</v>
       </c>
       <c r="X7" t="n">
-        <v>6.672199756089722</v>
+        <v>6.672199756089682</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.691261185241858</v>
+        <v>9.691261185241832</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.484035292969084</v>
+        <v>4.484035292969074</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.812050442923953</v>
+        <v>4.812050442923984</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.704630432061041</v>
+        <v>7.704630432061029</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.334572972053842</v>
+        <v>3.334572972053858</v>
       </c>
       <c r="C8" t="n">
-        <v>4.590549981106398</v>
+        <v>4.590549981106368</v>
       </c>
       <c r="D8" t="n">
-        <v>4.934835330575962</v>
+        <v>4.934835330575929</v>
       </c>
       <c r="E8" t="n">
-        <v>5.337347717778707</v>
+        <v>4.815275443220981</v>
       </c>
       <c r="F8" t="n">
-        <v>4.245376245376413</v>
+        <v>4.245376245376391</v>
       </c>
       <c r="G8" t="n">
-        <v>8.89804830686426</v>
+        <v>9.101355507432489</v>
       </c>
       <c r="H8" t="n">
-        <v>7.099020693132779</v>
+        <v>7.099020693132772</v>
       </c>
       <c r="I8" t="n">
-        <v>4.709395263328524</v>
+        <v>4.709395263328495</v>
       </c>
       <c r="J8" t="n">
-        <v>7.172318138929078</v>
+        <v>7.172318138929057</v>
       </c>
       <c r="K8" t="n">
-        <v>5.469893863804227</v>
+        <v>5.469893863804223</v>
       </c>
       <c r="L8" t="n">
-        <v>5.554699455064433</v>
+        <v>5.554699455064416</v>
       </c>
       <c r="M8" t="n">
-        <v>6.800107217323349</v>
+        <v>6.800107217322461</v>
       </c>
       <c r="N8" t="n">
-        <v>6.23404459139949</v>
+        <v>6.234044591399478</v>
       </c>
       <c r="O8" t="n">
-        <v>7.046035754884764</v>
+        <v>7.046035754884761</v>
       </c>
       <c r="P8" t="n">
-        <v>8.532592438944091</v>
+        <v>8.532592438944047</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.359261237123398</v>
+        <v>4.359261237123375</v>
       </c>
       <c r="R8" t="n">
-        <v>4.897561656322912</v>
+        <v>4.897561656322886</v>
       </c>
       <c r="S8" t="n">
-        <v>5.609675281050365</v>
+        <v>5.609675281050354</v>
       </c>
       <c r="T8" t="n">
-        <v>5.848591712470842</v>
+        <v>5.84859171247081</v>
       </c>
       <c r="U8" t="n">
-        <v>6.435957979666243</v>
+        <v>6.560388859014745</v>
       </c>
       <c r="V8" t="n">
-        <v>6.502342547562472</v>
+        <v>6.228124475512439</v>
       </c>
       <c r="W8" t="n">
-        <v>9.740232415976037</v>
+        <v>9.740232415976035</v>
       </c>
       <c r="X8" t="n">
-        <v>6.897999648848196</v>
+        <v>6.897999648848183</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.96553761501531</v>
+        <v>11.96553761501535</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.793129808849275</v>
+        <v>4.794445311712317</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.121144958804158</v>
+        <v>6.121144958804144</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.03790965552781</v>
+        <v>10.03790965552778</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.377737821468175</v>
+        <v>5.377737821468171</v>
       </c>
       <c r="C9" t="n">
-        <v>6.645044002933245</v>
+        <v>6.645044002933218</v>
       </c>
       <c r="D9" t="n">
-        <v>6.989329352402813</v>
+        <v>6.989329352402781</v>
       </c>
       <c r="E9" t="n">
-        <v>7.391841739605551</v>
+        <v>7.162938533774889</v>
       </c>
       <c r="F9" t="n">
-        <v>7.127595962164268</v>
+        <v>4.841223516262607</v>
       </c>
       <c r="G9" t="n">
-        <v>10.95254232869112</v>
+        <v>10.95254284521598</v>
       </c>
       <c r="H9" t="n">
-        <v>9.153514714959627</v>
+        <v>9.153514714959625</v>
       </c>
       <c r="I9" t="n">
-        <v>6.763889285155376</v>
+        <v>6.76388928515534</v>
       </c>
       <c r="J9" t="n">
-        <v>9.226812160755927</v>
+        <v>9.226812160755916</v>
       </c>
       <c r="K9" t="n">
-        <v>7.524387885631071</v>
+        <v>7.524387885631072</v>
       </c>
       <c r="L9" t="n">
-        <v>7.60919347689131</v>
+        <v>7.609193476891269</v>
       </c>
       <c r="M9" t="n">
-        <v>8.854601239150195</v>
+        <v>8.854601239150167</v>
       </c>
       <c r="N9" t="n">
-        <v>9.048568234953736</v>
+        <v>9.0485682349537</v>
       </c>
       <c r="O9" t="n">
-        <v>9.980378868702749</v>
+        <v>9.980378868702751</v>
       </c>
       <c r="P9" t="n">
-        <v>11.58961548546371</v>
+        <v>11.58961548546369</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.586912579910774</v>
+        <v>7.586912579910756</v>
       </c>
       <c r="R9" t="n">
-        <v>6.952055678149792</v>
+        <v>6.952055678149741</v>
       </c>
       <c r="S9" t="n">
-        <v>7.664169302877252</v>
+        <v>7.664169302877212</v>
       </c>
       <c r="T9" t="n">
-        <v>7.903085734297673</v>
+        <v>7.90308573429766</v>
       </c>
       <c r="U9" t="n">
-        <v>9.099095825392428</v>
+        <v>9.099095825392411</v>
       </c>
       <c r="V9" t="n">
-        <v>8.556836569389336</v>
+        <v>9.701353636153257</v>
       </c>
       <c r="W9" t="n">
-        <v>11.79453374881111</v>
+        <v>11.7945337488111</v>
       </c>
       <c r="X9" t="n">
-        <v>10.0357882937967</v>
+        <v>10.03578829379669</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.05484972294885</v>
+        <v>13.05484972294884</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.84762383067611</v>
+        <v>7.249656285093059</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.175638980631028</v>
+        <v>8.175638980630996</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.06821896976808</v>
+        <v>11.06821896976804</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.99807974188317</v>
+        <v>39.86558020822903</v>
       </c>
       <c r="C2" t="n">
-        <v>42.67289011868514</v>
+        <v>42.57319409382514</v>
       </c>
       <c r="D2" t="n">
-        <v>39.82622113669213</v>
+        <v>39.74379697887208</v>
       </c>
       <c r="E2" t="n">
-        <v>39.85385363729279</v>
+        <v>39.73571265549226</v>
       </c>
       <c r="F2" t="n">
-        <v>39.84486075689929</v>
+        <v>39.74936597682419</v>
       </c>
       <c r="G2" t="n">
-        <v>40.13009998170715</v>
+        <v>39.92563869640193</v>
       </c>
       <c r="H2" t="n">
-        <v>40.03591457761055</v>
+        <v>39.92338634207723</v>
       </c>
       <c r="I2" t="n">
-        <v>39.819850735511</v>
+        <v>39.70996203503856</v>
       </c>
       <c r="J2" t="n">
-        <v>40.0750966707675</v>
+        <v>39.94209255405192</v>
       </c>
       <c r="K2" t="n">
-        <v>39.9913203236885</v>
+        <v>39.89178481684849</v>
       </c>
       <c r="L2" t="n">
-        <v>40.06145167059994</v>
+        <v>40.0200402595998</v>
       </c>
       <c r="M2" t="n">
-        <v>40.3319809068685</v>
+        <v>40.2099958901585</v>
       </c>
       <c r="N2" t="n">
-        <v>40.06991348400534</v>
+        <v>39.97294740999753</v>
       </c>
       <c r="O2" t="n">
-        <v>44.2091604991547</v>
+        <v>44.0647283889531</v>
       </c>
       <c r="P2" t="n">
-        <v>40.16520410856416</v>
+        <v>40.03532099705399</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.95439138243952</v>
+        <v>39.84917345479597</v>
       </c>
       <c r="R2" t="n">
-        <v>39.8733733106042</v>
+        <v>39.76836775620612</v>
       </c>
       <c r="S2" t="n">
-        <v>40.0506426406119</v>
+        <v>39.91121268372182</v>
       </c>
       <c r="T2" t="n">
-        <v>40.00600353512817</v>
+        <v>39.8933557817838</v>
       </c>
       <c r="U2" t="n">
-        <v>43.83187745594135</v>
+        <v>43.74458627711367</v>
       </c>
       <c r="V2" t="n">
-        <v>39.97858007093157</v>
+        <v>39.87922973880492</v>
       </c>
       <c r="W2" t="n">
-        <v>46.33714823440372</v>
+        <v>46.24781264865615</v>
       </c>
       <c r="X2" t="n">
-        <v>39.9322203421136</v>
+        <v>39.83098976852254</v>
       </c>
       <c r="Y2" t="n">
-        <v>40.26786975731436</v>
+        <v>40.15672860280745</v>
       </c>
       <c r="Z2" t="n">
-        <v>41.45464129667144</v>
+        <v>41.34106150211278</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.97347290082377</v>
+        <v>39.8731527723793</v>
       </c>
       <c r="AB2" t="n">
-        <v>40.18591906313062</v>
+        <v>40.21119741395757</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.91812281726035</v>
+        <v>41.59003225759685</v>
       </c>
       <c r="C3" t="n">
-        <v>44.74633642761335</v>
+        <v>44.66813516894263</v>
       </c>
       <c r="D3" t="n">
-        <v>40.70791935247918</v>
+        <v>40.73652099874683</v>
       </c>
       <c r="E3" t="n">
-        <v>40.89978126488996</v>
+        <v>40.6731996817472</v>
       </c>
       <c r="F3" t="n">
-        <v>40.84387738059343</v>
+        <v>40.77891345547659</v>
       </c>
       <c r="G3" t="n">
-        <v>42.86213344975791</v>
+        <v>42.02136842120964</v>
       </c>
       <c r="H3" t="n">
-        <v>42.2169126964415</v>
+        <v>42.02971977390121</v>
       </c>
       <c r="I3" t="n">
-        <v>40.66343368561804</v>
+        <v>40.49535967140321</v>
       </c>
       <c r="J3" t="n">
-        <v>42.47533625866581</v>
+        <v>42.14326094593921</v>
       </c>
       <c r="K3" t="n">
-        <v>41.88844220004102</v>
+        <v>41.79455978800009</v>
       </c>
       <c r="L3" t="n">
-        <v>42.38105893455577</v>
+        <v>42.70199130034279</v>
       </c>
       <c r="M3" t="n">
-        <v>44.32888909702822</v>
+        <v>44.07343409629516</v>
       </c>
       <c r="N3" t="n">
-        <v>42.4465708053076</v>
+        <v>42.37107455390974</v>
       </c>
       <c r="O3" t="n">
-        <v>48.90476797516575</v>
+        <v>48.72350244181498</v>
       </c>
       <c r="P3" t="n">
-        <v>43.10962679865449</v>
+        <v>42.79993913720786</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.62222116318509</v>
+        <v>41.48772405002578</v>
       </c>
       <c r="R3" t="n">
-        <v>41.04841969041294</v>
+        <v>40.91527871138069</v>
       </c>
       <c r="S3" t="n">
-        <v>42.29701496453389</v>
+        <v>41.9191675097569</v>
       </c>
       <c r="T3" t="n">
-        <v>41.99561374630449</v>
+        <v>41.8078274654559</v>
       </c>
       <c r="U3" t="n">
-        <v>49.34998642411142</v>
+        <v>49.32064072718993</v>
       </c>
       <c r="V3" t="n">
-        <v>41.78075786151696</v>
+        <v>41.6882860294765</v>
       </c>
       <c r="W3" t="n">
-        <v>53.55597555875507</v>
+        <v>53.49348608030591</v>
       </c>
       <c r="X3" t="n">
-        <v>41.46485064159545</v>
+        <v>41.35884397933955</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.85631037148435</v>
+        <v>43.67961306704692</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.60507382144925</v>
+        <v>44.45484910854751</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.75557064310686</v>
+        <v>41.65612642825275</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.28996778698476</v>
+        <v>44.07810035166606</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.151760975869013</v>
+        <v>5.958771451649437</v>
       </c>
       <c r="C4" t="n">
-        <v>3.85060569686131</v>
+        <v>3.063154130162663</v>
       </c>
       <c r="D4" t="n">
-        <v>5.210538971371826</v>
+        <v>4.583173853009286</v>
       </c>
       <c r="E4" t="n">
-        <v>5.522660777234391</v>
+        <v>4.491857701461445</v>
       </c>
       <c r="F4" t="n">
-        <v>5.421082056260701</v>
+        <v>4.646078246743581</v>
       </c>
       <c r="G4" t="n">
-        <v>8.642990316991636</v>
+        <v>6.637159703831425</v>
       </c>
       <c r="H4" t="n">
-        <v>7.57912285029441</v>
+        <v>6.611718325599921</v>
       </c>
       <c r="I4" t="n">
-        <v>5.13858235950159</v>
+        <v>4.200992597566137</v>
       </c>
       <c r="J4" t="n">
-        <v>8.021880397373661</v>
+        <v>6.823608014778772</v>
       </c>
       <c r="K4" t="n">
-        <v>7.075410237874195</v>
+        <v>6.254764560721542</v>
       </c>
       <c r="L4" t="n">
-        <v>7.867576063252205</v>
+        <v>7.703468787016422</v>
       </c>
       <c r="M4" t="n">
-        <v>10.91713548017885</v>
+        <v>9.841604237983002</v>
       </c>
       <c r="N4" t="n">
-        <v>7.963156138292893</v>
+        <v>112.7863197477354</v>
       </c>
       <c r="O4" t="n">
-        <v>7.232338844863489</v>
+        <v>6.383930261660264</v>
       </c>
       <c r="P4" t="n">
-        <v>9.039507578537936</v>
+        <v>7.87607174604783</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.658280858314717</v>
+        <v>5.77344962414326</v>
       </c>
       <c r="R4" t="n">
-        <v>5.743144466780399</v>
+        <v>4.860712086113234</v>
       </c>
       <c r="S4" t="n">
-        <v>7.745483097138205</v>
+        <v>6.474211254316091</v>
       </c>
       <c r="T4" t="n">
-        <v>7.241263865696351</v>
+        <v>6.272509332345686</v>
       </c>
       <c r="U4" t="n">
-        <v>9.391743797250694</v>
+        <v>8.68009087306465</v>
       </c>
       <c r="V4" t="n">
-        <v>6.932406243063371</v>
+        <v>6.116671802223239</v>
       </c>
       <c r="W4" t="n">
-        <v>9.543284237633568</v>
+        <v>8.752498563223481</v>
       </c>
       <c r="X4" t="n">
-        <v>6.407848758651241</v>
+        <v>5.568056522775903</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.17937630355079</v>
+        <v>9.245363694056401</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.727032676486667</v>
+        <v>6.837684138097909</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.873815386397024</v>
+        <v>6.044307047278175</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.266476630854452</v>
+        <v>9.830662539209808</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>87.95426209421117</v>
+        <v>79.59295066876508</v>
       </c>
       <c r="C5" t="n">
-        <v>29.28448237000412</v>
+        <v>28.48735538111602</v>
       </c>
       <c r="D5" t="n">
-        <v>58.58576859749389</v>
+        <v>61.19991272789832</v>
       </c>
       <c r="E5" t="n">
-        <v>61.68990113118592</v>
+        <v>56.01891517752794</v>
       </c>
       <c r="F5" t="n">
-        <v>64.56479766306792</v>
+        <v>64.03946431738021</v>
       </c>
       <c r="G5" t="n">
-        <v>119.0397404577807</v>
+        <v>94.85644287227058</v>
       </c>
       <c r="H5" t="n">
-        <v>113.6543665803669</v>
+        <v>108.8620019948882</v>
       </c>
       <c r="I5" t="n">
-        <v>57.71930113986642</v>
+        <v>53.69400632597093</v>
       </c>
       <c r="J5" t="n">
-        <v>109.9544596887862</v>
+        <v>101.2508451083561</v>
       </c>
       <c r="K5" t="n">
-        <v>97.44885597818958</v>
+        <v>95.95707232069437</v>
       </c>
       <c r="L5" t="n">
-        <v>108.6975784874728</v>
+        <v>120.4153028042077</v>
       </c>
       <c r="M5" t="n">
-        <v>182.2422990105716</v>
+        <v>175.2380915959088</v>
       </c>
       <c r="N5" t="n">
-        <v>135.5242149894848</v>
+        <v>112.7863197477354</v>
       </c>
       <c r="O5" t="n">
-        <v>87.40613600125107</v>
+        <v>85.48114031744191</v>
       </c>
       <c r="P5" t="n">
-        <v>125.2140264393936</v>
+        <v>117.2870097399863</v>
       </c>
       <c r="Q5" t="n">
-        <v>87.46937694359485</v>
+        <v>84.64997914673984</v>
       </c>
       <c r="R5" t="n">
-        <v>71.67260276142881</v>
+        <v>68.80666382409234</v>
       </c>
       <c r="S5" t="n">
-        <v>102.1382418016023</v>
+        <v>92.02568332854516</v>
       </c>
       <c r="T5" t="n">
-        <v>102.2014026003562</v>
+        <v>97.53617242777239</v>
       </c>
       <c r="U5" t="n">
-        <v>136.9725896545944</v>
+        <v>137.315353078078</v>
       </c>
       <c r="V5" t="n">
-        <v>84.59254876448216</v>
+        <v>83.19859025623199</v>
       </c>
       <c r="W5" t="n">
-        <v>143.5215307226315</v>
+        <v>142.6623649242607</v>
       </c>
       <c r="X5" t="n">
-        <v>82.94050302704915</v>
+        <v>81.04741386160957</v>
       </c>
       <c r="Y5" t="n">
-        <v>156.8603877073066</v>
+        <v>152.7377409684672</v>
       </c>
       <c r="Z5" t="n">
-        <v>101.4479276206042</v>
+        <v>98.69762641940274</v>
       </c>
       <c r="AA5" t="n">
-        <v>90.12404365067916</v>
+        <v>88.47641829302817</v>
       </c>
       <c r="AB5" t="n">
-        <v>151.3650562213685</v>
+        <v>180.6103279895025</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>160.5296666582973</v>
+        <v>133.7113716979431</v>
       </c>
       <c r="C6" t="n">
-        <v>157.2285113792897</v>
+        <v>156.3763591790596</v>
       </c>
       <c r="D6" t="n">
-        <v>132.9544146475999</v>
+        <v>157.8963789019063</v>
       </c>
       <c r="E6" t="n">
-        <v>133.2665364534622</v>
+        <v>157.8050627503584</v>
       </c>
       <c r="F6" t="n">
-        <v>158.798987738689</v>
+        <v>132.3986784930372</v>
       </c>
       <c r="G6" t="n">
-        <v>162.02089599942</v>
+        <v>159.9503647527284</v>
       </c>
       <c r="H6" t="n">
-        <v>160.9570285327227</v>
+        <v>159.924923374497</v>
       </c>
       <c r="I6" t="n">
-        <v>132.8824580357295</v>
+        <v>131.9535928438598</v>
       </c>
       <c r="J6" t="n">
-        <v>161.3997860798021</v>
+        <v>134.5762082610723</v>
       </c>
       <c r="K6" t="n">
-        <v>134.8192859141022</v>
+        <v>159.5679696096185</v>
       </c>
       <c r="L6" t="n">
-        <v>135.6114517394801</v>
+        <v>161.0166738359135</v>
       </c>
       <c r="M6" t="n">
-        <v>138.661011156407</v>
+        <v>163.1548092868801</v>
       </c>
       <c r="N6" t="n">
-        <v>135.7204306960951</v>
+        <v>112.7863197477354</v>
       </c>
       <c r="O6" t="n">
-        <v>160.6816259876683</v>
+        <v>134.1510834482693</v>
       </c>
       <c r="P6" t="n">
-        <v>162.488808720769</v>
+        <v>161.2542468551927</v>
       </c>
       <c r="Q6" t="n">
-        <v>134.4021565345427</v>
+        <v>159.0866546730404</v>
       </c>
       <c r="R6" t="n">
-        <v>133.4870201430084</v>
+        <v>158.1739171350102</v>
       </c>
       <c r="S6" t="n">
-        <v>161.1233887795667</v>
+        <v>134.2268115006097</v>
       </c>
       <c r="T6" t="n">
-        <v>134.9851395419244</v>
+        <v>134.0251095786393</v>
       </c>
       <c r="U6" t="n">
-        <v>137.1554064796308</v>
+        <v>136.4347539285932</v>
       </c>
       <c r="V6" t="n">
-        <v>160.3103119254917</v>
+        <v>159.4298768511202</v>
       </c>
       <c r="W6" t="n">
-        <v>162.9925801137932</v>
+        <v>162.1306688099944</v>
       </c>
       <c r="X6" t="n">
-        <v>159.7857544410797</v>
+        <v>158.881261571673</v>
       </c>
       <c r="Y6" t="n">
-        <v>143.5614134412847</v>
+        <v>142.6207229350815</v>
       </c>
       <c r="Z6" t="n">
-        <v>135.4709083527147</v>
+        <v>134.5902843843916</v>
       </c>
       <c r="AA6" t="n">
-        <v>134.6176910626249</v>
+        <v>159.3575120961754</v>
       </c>
       <c r="AB6" t="n">
-        <v>137.0343038972037</v>
+        <v>137.6174078246913</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.549746102286903</v>
+        <v>7.302718952914929</v>
       </c>
       <c r="C7" t="n">
-        <v>5.248590823279206</v>
+        <v>4.407101631428175</v>
       </c>
       <c r="D7" t="n">
-        <v>6.608524097789719</v>
+        <v>5.927121354274782</v>
       </c>
       <c r="E7" t="n">
-        <v>6.920645903652286</v>
+        <v>5.835805202726942</v>
       </c>
       <c r="F7" t="n">
-        <v>6.819067182678591</v>
+        <v>5.990025748009049</v>
       </c>
       <c r="G7" t="n">
-        <v>10.04097544340953</v>
+        <v>7.981107205096929</v>
       </c>
       <c r="H7" t="n">
-        <v>8.977107976712302</v>
+        <v>7.955665826865429</v>
       </c>
       <c r="I7" t="n">
-        <v>6.536567485919481</v>
+        <v>5.544940098831651</v>
       </c>
       <c r="J7" t="n">
-        <v>9.419865523791556</v>
+        <v>8.167555516044278</v>
       </c>
       <c r="K7" t="n">
-        <v>8.473395364292092</v>
+        <v>7.598712061987051</v>
       </c>
       <c r="L7" t="n">
-        <v>9.265561189670095</v>
+        <v>9.047416288281962</v>
       </c>
       <c r="M7" t="n">
-        <v>12.31512060659674</v>
+        <v>11.18555173924851</v>
       </c>
       <c r="N7" t="n">
-        <v>9.361141264710788</v>
+        <v>112.7863197477354</v>
       </c>
       <c r="O7" t="n">
-        <v>8.630309387388104</v>
+        <v>7.727862772552006</v>
       </c>
       <c r="P7" t="n">
-        <v>10.43747812106255</v>
+        <v>9.220004256939564</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.056265984732612</v>
+        <v>7.117397125408734</v>
       </c>
       <c r="R7" t="n">
-        <v>7.141129593198291</v>
+        <v>6.204659587378751</v>
       </c>
       <c r="S7" t="n">
-        <v>9.143468223556097</v>
+        <v>7.81815875558158</v>
       </c>
       <c r="T7" t="n">
-        <v>8.639248992114243</v>
+        <v>7.6164568336112</v>
       </c>
       <c r="U7" t="n">
-        <v>10.80937925032173</v>
+        <v>10.02680514579375</v>
       </c>
       <c r="V7" t="n">
-        <v>8.330391369481266</v>
+        <v>7.460619303488736</v>
       </c>
       <c r="W7" t="n">
-        <v>10.94126936405146</v>
+        <v>10.09644606448895</v>
       </c>
       <c r="X7" t="n">
-        <v>7.805833885069134</v>
+        <v>6.912004024041419</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.59714843612065</v>
+        <v>10.5913740045568</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.125017802904569</v>
+        <v>8.181631639363424</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.271800512814918</v>
+        <v>7.388254548543685</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.66446175727234</v>
+        <v>11.17461004047529</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.153430698767234</v>
+        <v>7.87715136980653</v>
       </c>
       <c r="C8" t="n">
-        <v>7.379950393778072</v>
+        <v>6.435161644917458</v>
       </c>
       <c r="D8" t="n">
-        <v>8.739883668288586</v>
+        <v>7.955181367764093</v>
       </c>
       <c r="E8" t="n">
-        <v>8.238563614520713</v>
+        <v>7.08985140078806</v>
       </c>
       <c r="F8" t="n">
-        <v>7.66074568554634</v>
+        <v>6.790916355302614</v>
       </c>
       <c r="G8" t="n">
-        <v>12.48910837149089</v>
+        <v>10.31058637009214</v>
       </c>
       <c r="H8" t="n">
-        <v>11.10846754721118</v>
+        <v>9.98372584035471</v>
       </c>
       <c r="I8" t="n">
-        <v>8.667927056418355</v>
+        <v>7.573000112320932</v>
       </c>
       <c r="J8" t="n">
-        <v>11.55122509429043</v>
+        <v>10.19561552953358</v>
       </c>
       <c r="K8" t="n">
-        <v>10.60475493479096</v>
+        <v>9.626772075476334</v>
       </c>
       <c r="L8" t="n">
-        <v>11.39692076016897</v>
+        <v>11.07547630177124</v>
       </c>
       <c r="M8" t="n">
-        <v>14.44648017709575</v>
+        <v>13.21361175273829</v>
       </c>
       <c r="N8" t="n">
-        <v>10.30829715533756</v>
+        <v>112.7863197477354</v>
       </c>
       <c r="O8" t="n">
-        <v>9.902909314281017</v>
+        <v>8.938788881777811</v>
       </c>
       <c r="P8" t="n">
-        <v>11.63030742582073</v>
+        <v>10.3550262768174</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.359727581928157</v>
+        <v>7.406158542709045</v>
       </c>
       <c r="R8" t="n">
-        <v>9.272489163697163</v>
+        <v>8.232719600868032</v>
       </c>
       <c r="S8" t="n">
-        <v>11.27482779405496</v>
+        <v>9.846218769070877</v>
       </c>
       <c r="T8" t="n">
-        <v>10.77060856261311</v>
+        <v>9.644516847100498</v>
       </c>
       <c r="U8" t="n">
-        <v>12.19514311276066</v>
+        <v>11.34522213786832</v>
       </c>
       <c r="V8" t="n">
-        <v>10.04410996945431</v>
+        <v>9.091995518424474</v>
       </c>
       <c r="W8" t="n">
-        <v>13.07292916428793</v>
+        <v>12.12479175534861</v>
       </c>
       <c r="X8" t="n">
-        <v>8.249309927837407</v>
+        <v>7.333993297679033</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.24727859138449</v>
+        <v>14.06569600687694</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.700325052623576</v>
+        <v>8.729062177538697</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.40316008331379</v>
+        <v>9.416314562032982</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.39160557820944</v>
+        <v>14.72110562700791</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.99795394953239</v>
+        <v>11.4492379981237</v>
       </c>
       <c r="C9" t="n">
-        <v>11.42494658793264</v>
+        <v>10.17419565914791</v>
       </c>
       <c r="D9" t="n">
-        <v>12.78487986244316</v>
+        <v>11.69421538199454</v>
       </c>
       <c r="E9" t="n">
-        <v>12.69815254082712</v>
+        <v>11.22887735868203</v>
       </c>
       <c r="F9" t="n">
-        <v>9.011569725628618</v>
+        <v>8.021251764066756</v>
       </c>
       <c r="G9" t="n">
-        <v>16.21733167981307</v>
+        <v>13.7482015240188</v>
       </c>
       <c r="H9" t="n">
-        <v>15.15346374136573</v>
+        <v>13.72275985458518</v>
       </c>
       <c r="I9" t="n">
-        <v>12.71292325057293</v>
+        <v>11.31203412655138</v>
       </c>
       <c r="J9" t="n">
-        <v>15.59622128844499</v>
+        <v>13.93464954376402</v>
       </c>
       <c r="K9" t="n">
-        <v>14.64975112894553</v>
+        <v>13.36580608970679</v>
       </c>
       <c r="L9" t="n">
-        <v>15.44191695432354</v>
+        <v>14.81451031600172</v>
       </c>
       <c r="M9" t="n">
-        <v>18.49147637125018</v>
+        <v>16.95264576696825</v>
       </c>
       <c r="N9" t="n">
-        <v>15.53749702936422</v>
+        <v>112.7863197477354</v>
       </c>
       <c r="O9" t="n">
-        <v>15.37938632103472</v>
+        <v>14.03202860559393</v>
       </c>
       <c r="P9" t="n">
-        <v>17.3111088083807</v>
+        <v>15.64097066955822</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.23262222113616</v>
+        <v>12.88449144433062</v>
       </c>
       <c r="R9" t="n">
-        <v>13.31748535785173</v>
+        <v>11.97175361509848</v>
       </c>
       <c r="S9" t="n">
-        <v>15.31982398820954</v>
+        <v>13.58525278330133</v>
       </c>
       <c r="T9" t="n">
-        <v>14.81560475676768</v>
+        <v>13.38355086133096</v>
       </c>
       <c r="U9" t="n">
-        <v>16.98587169447399</v>
+        <v>15.7931952112848</v>
       </c>
       <c r="V9" t="n">
-        <v>16.50099125796267</v>
+        <v>15.09782041297532</v>
       </c>
       <c r="W9" t="n">
-        <v>17.11762512870491</v>
+        <v>15.8635400922087</v>
       </c>
       <c r="X9" t="n">
-        <v>13.98218964972258</v>
+        <v>12.67909805176116</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.77350420077409</v>
+        <v>16.35846803227654</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.2594542335965</v>
+        <v>12.97166317541233</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.44815627746836</v>
+        <v>13.15534857626343</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.84081752192578</v>
+        <v>16.94170406819504</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.82042167757412</v>
+        <v>38.79767279880322</v>
       </c>
       <c r="C2" t="n">
-        <v>41.81481548691185</v>
+        <v>41.7832252513118</v>
       </c>
       <c r="D2" t="n">
-        <v>38.89397931956858</v>
+        <v>38.87096952041478</v>
       </c>
       <c r="E2" t="n">
-        <v>38.8483830184576</v>
+        <v>38.82519896262243</v>
       </c>
       <c r="F2" t="n">
-        <v>38.96218565438257</v>
+        <v>38.93888780294378</v>
       </c>
       <c r="G2" t="n">
-        <v>39.01226997208029</v>
+        <v>38.98457544179062</v>
       </c>
       <c r="H2" t="n">
-        <v>38.99593715792241</v>
+        <v>38.97324814550442</v>
       </c>
       <c r="I2" t="n">
-        <v>38.88340250328901</v>
+        <v>38.86908781616912</v>
       </c>
       <c r="J2" t="n">
-        <v>38.98579920688285</v>
+        <v>38.96219847616745</v>
       </c>
       <c r="K2" t="n">
-        <v>39.02917331812436</v>
+        <v>39.01754417691996</v>
       </c>
       <c r="L2" t="n">
-        <v>38.95456630060931</v>
+        <v>38.93175487760107</v>
       </c>
       <c r="M2" t="n">
-        <v>38.9566571832024</v>
+        <v>38.93490611117453</v>
       </c>
       <c r="N2" t="n">
-        <v>39.04913387708799</v>
+        <v>39.02692214176368</v>
       </c>
       <c r="O2" t="n">
-        <v>42.84027690660581</v>
+        <v>42.77805981120951</v>
       </c>
       <c r="P2" t="n">
-        <v>39.198541400055</v>
+        <v>39.17523058394656</v>
       </c>
       <c r="Q2" t="n">
-        <v>38.89041961997125</v>
+        <v>38.86757583564978</v>
       </c>
       <c r="R2" t="n">
-        <v>38.87639673208581</v>
+        <v>38.85575154832134</v>
       </c>
       <c r="S2" t="n">
-        <v>39.02260617650401</v>
+        <v>38.99460269978464</v>
       </c>
       <c r="T2" t="n">
-        <v>39.00056484377097</v>
+        <v>38.98869322774883</v>
       </c>
       <c r="U2" t="n">
-        <v>42.44642589783226</v>
+        <v>42.36330489084965</v>
       </c>
       <c r="V2" t="n">
-        <v>38.92862687638534</v>
+        <v>38.90541315723291</v>
       </c>
       <c r="W2" t="n">
-        <v>45.07851105920366</v>
+        <v>44.98574370532948</v>
       </c>
       <c r="X2" t="n">
-        <v>39.19324788346732</v>
+        <v>39.16914714456269</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.14872771998019</v>
+        <v>39.12508096030318</v>
       </c>
       <c r="Z2" t="n">
-        <v>39.99846529400021</v>
+        <v>39.95932211852326</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.11392084505258</v>
+        <v>39.09284144629075</v>
       </c>
       <c r="AB2" t="n">
-        <v>38.96123114637843</v>
+        <v>38.94229044815238</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.52143930804848</v>
+        <v>38.50376106155622</v>
       </c>
       <c r="C3" t="n">
-        <v>43.68647952399665</v>
+        <v>43.65229972366941</v>
       </c>
       <c r="D3" t="n">
-        <v>39.04668365425513</v>
+        <v>39.02715485099089</v>
       </c>
       <c r="E3" t="n">
-        <v>38.72034724547443</v>
+        <v>38.69966036024099</v>
       </c>
       <c r="F3" t="n">
-        <v>39.53489964356359</v>
+        <v>39.51330217221511</v>
       </c>
       <c r="G3" t="n">
-        <v>39.88169925216765</v>
+        <v>39.82897601903489</v>
       </c>
       <c r="H3" t="n">
-        <v>39.78006204614427</v>
+        <v>39.76281154299256</v>
       </c>
       <c r="I3" t="n">
-        <v>38.97239202320364</v>
+        <v>39.01501434053375</v>
       </c>
       <c r="J3" t="n">
-        <v>39.69806751107502</v>
+        <v>39.67439755717765</v>
       </c>
       <c r="K3" t="n">
-        <v>40.00451496380693</v>
+        <v>40.06584519772085</v>
       </c>
       <c r="L3" t="n">
-        <v>39.47409026209401</v>
+        <v>39.45598775250475</v>
       </c>
       <c r="M3" t="n">
-        <v>39.50040494050674</v>
+        <v>39.4894070050144</v>
       </c>
       <c r="N3" t="n">
-        <v>40.1566886116325</v>
+        <v>40.14283495315444</v>
       </c>
       <c r="O3" t="n">
-        <v>46.50684636722055</v>
+        <v>46.4213369137717</v>
       </c>
       <c r="P3" t="n">
-        <v>41.20400189262187</v>
+        <v>41.1823404403031</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.02020292609468</v>
+        <v>39.001853418548</v>
       </c>
       <c r="R3" t="n">
-        <v>38.92311622110554</v>
+        <v>38.92049835784486</v>
       </c>
       <c r="S3" t="n">
-        <v>39.956202837275</v>
+        <v>39.90124493755184</v>
       </c>
       <c r="T3" t="n">
-        <v>39.81085917339229</v>
+        <v>39.87099168448707</v>
       </c>
       <c r="U3" t="n">
-        <v>45.67621918489814</v>
+        <v>45.5631726567054</v>
       </c>
       <c r="V3" t="n">
-        <v>39.28916698892568</v>
+        <v>39.26820899589327</v>
       </c>
       <c r="W3" t="n">
-        <v>50.91003639210933</v>
+        <v>50.77021166782205</v>
       </c>
       <c r="X3" t="n">
-        <v>41.17904112605563</v>
+        <v>41.15173433708225</v>
       </c>
       <c r="Y3" t="n">
-        <v>40.86711318503332</v>
+        <v>40.84300548747163</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.91074459477137</v>
+        <v>40.86708536001722</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.61787300524976</v>
+        <v>40.61210223970389</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.53222792136648</v>
+        <v>39.54120770839887</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.436337953835241</v>
+        <v>1.231913899733783</v>
       </c>
       <c r="C4" t="n">
-        <v>1.892590663596843</v>
+        <v>1.684204024660515</v>
       </c>
       <c r="D4" t="n">
-        <v>2.267205358349709</v>
+        <v>2.059834088493855</v>
       </c>
       <c r="E4" t="n">
-        <v>1.752174161966826</v>
+        <v>1.542834582733042</v>
       </c>
       <c r="F4" t="n">
-        <v>3.037627286537803</v>
+        <v>2.827002333612737</v>
       </c>
       <c r="G4" t="n">
-        <v>3.603352694858379</v>
+        <v>3.343065231740045</v>
       </c>
       <c r="H4" t="n">
-        <v>3.418866045479377</v>
+        <v>3.215118209373704</v>
       </c>
       <c r="I4" t="n">
-        <v>2.147735352896206</v>
+        <v>2.038579373412538</v>
       </c>
       <c r="J4" t="n">
-        <v>3.304892567013147</v>
+        <v>3.090864016999223</v>
       </c>
       <c r="K4" t="n">
-        <v>3.794283764349348</v>
+        <v>3.715462261393433</v>
       </c>
       <c r="L4" t="n">
-        <v>2.951563180592988</v>
+        <v>2.74643266055907</v>
       </c>
       <c r="M4" t="n">
-        <v>2.985642064800731</v>
+        <v>2.791647448925112</v>
       </c>
       <c r="N4" t="n">
-        <v>51.07886759202032</v>
+        <v>51.02917605539093</v>
       </c>
       <c r="O4" t="n">
-        <v>4.239176117330177</v>
+        <v>4.029151129765974</v>
       </c>
       <c r="P4" t="n">
-        <v>5.707374162923065</v>
+        <v>5.496602768089915</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.226996913855224</v>
+        <v>2.021500857901084</v>
       </c>
       <c r="R4" t="n">
-        <v>2.068601944342168</v>
+        <v>1.887940093085597</v>
       </c>
       <c r="S4" t="n">
-        <v>3.720104878713196</v>
+        <v>3.456327723549018</v>
       </c>
       <c r="T4" t="n">
-        <v>3.471137885979445</v>
+        <v>3.389577518413202</v>
       </c>
       <c r="U4" t="n">
-        <v>3.810025788985167</v>
+        <v>3.634438463141649</v>
       </c>
       <c r="V4" t="n">
-        <v>2.661882068723766</v>
+        <v>2.452298180244605</v>
       </c>
       <c r="W4" t="n">
-        <v>5.674541992762533</v>
+        <v>5.456616956968288</v>
       </c>
       <c r="X4" t="n">
-        <v>5.647581457926812</v>
+        <v>5.427887521728737</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.091568819171741</v>
+        <v>4.896997334888393</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.36163639545385</v>
+        <v>2.159428864555268</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.751546066792386</v>
+        <v>4.565979557391797</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.028457142601038</v>
+        <v>2.865895163200152</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.874343928064416</v>
+        <v>3.72202285942897</v>
       </c>
       <c r="C5" t="n">
-        <v>11.98633145759584</v>
+        <v>11.77338069445656</v>
       </c>
       <c r="D5" t="n">
-        <v>18.70423372467661</v>
+        <v>18.50582101282184</v>
       </c>
       <c r="E5" t="n">
-        <v>9.121744573868305</v>
+        <v>8.932877360417882</v>
       </c>
       <c r="F5" t="n">
-        <v>33.06835711406274</v>
+        <v>32.80575164126046</v>
       </c>
       <c r="G5" t="n">
-        <v>37.55263486559007</v>
+        <v>36.54306407574137</v>
       </c>
       <c r="H5" t="n">
-        <v>42.02724636154454</v>
+        <v>41.88713106378827</v>
       </c>
       <c r="I5" t="n">
-        <v>17.21081658718429</v>
+        <v>18.79804677550249</v>
       </c>
       <c r="J5" t="n">
-        <v>35.0070246648181</v>
+        <v>34.73014416819943</v>
       </c>
       <c r="K5" t="n">
-        <v>42.05706123741766</v>
+        <v>43.94296308073689</v>
       </c>
       <c r="L5" t="n">
-        <v>28.21415577516761</v>
+        <v>28.06080191001574</v>
       </c>
       <c r="M5" t="n">
-        <v>31.77495199209526</v>
+        <v>31.81537470788103</v>
       </c>
       <c r="N5" t="n">
-        <v>51.07886759202032</v>
+        <v>51.02917605539093</v>
       </c>
       <c r="O5" t="n">
-        <v>47.49868457655611</v>
+        <v>47.26739004629542</v>
       </c>
       <c r="P5" t="n">
-        <v>71.07294703845696</v>
+        <v>70.82254604826761</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.43600262918956</v>
+        <v>17.26787462422494</v>
       </c>
       <c r="R5" t="n">
-        <v>16.18678787609638</v>
+        <v>16.47868623370214</v>
       </c>
       <c r="S5" t="n">
-        <v>39.99774855936191</v>
+        <v>38.91106526482577</v>
       </c>
       <c r="T5" t="n">
-        <v>41.79565405430122</v>
+        <v>43.90924127135468</v>
       </c>
       <c r="U5" t="n">
-        <v>41.96435661540599</v>
+        <v>41.96417205804574</v>
       </c>
       <c r="V5" t="n">
-        <v>23.14295448911496</v>
+        <v>22.91746977870998</v>
       </c>
       <c r="W5" t="n">
-        <v>78.79172077385456</v>
+        <v>78.39514731899001</v>
       </c>
       <c r="X5" t="n">
-        <v>76.65870506403094</v>
+        <v>76.24654622615523</v>
       </c>
       <c r="Y5" t="n">
-        <v>70.77783139002238</v>
+        <v>70.43513065103099</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.8030408573541</v>
+        <v>17.69210058951027</v>
       </c>
       <c r="AA5" t="n">
-        <v>63.39828820164858</v>
+        <v>63.5755133902956</v>
       </c>
       <c r="AB5" t="n">
-        <v>34.59822795670191</v>
+        <v>35.24090102951153</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.6196404332074</v>
+        <v>112.4002077300202</v>
       </c>
       <c r="C6" t="n">
-        <v>113.0758931429691</v>
+        <v>134.7710241872199</v>
       </c>
       <c r="D6" t="n">
-        <v>135.3923831051893</v>
+        <v>113.2281279187803</v>
       </c>
       <c r="E6" t="n">
-        <v>112.935476641339</v>
+        <v>134.6296547452925</v>
       </c>
       <c r="F6" t="n">
-        <v>114.2209297659099</v>
+        <v>135.9138224961723</v>
       </c>
       <c r="G6" t="n">
-        <v>136.7285304416979</v>
+        <v>114.5113590620265</v>
       </c>
       <c r="H6" t="n">
-        <v>136.544043792319</v>
+        <v>114.3834120396601</v>
       </c>
       <c r="I6" t="n">
-        <v>135.2729130997358</v>
+        <v>113.2068732036989</v>
       </c>
       <c r="J6" t="n">
-        <v>136.4300703138528</v>
+        <v>136.1776841795587</v>
       </c>
       <c r="K6" t="n">
-        <v>114.9775862437215</v>
+        <v>114.8837560916798</v>
       </c>
       <c r="L6" t="n">
-        <v>136.0767409274325</v>
+        <v>135.8332528231185</v>
       </c>
       <c r="M6" t="n">
-        <v>136.1108198116404</v>
+        <v>113.9599412792114</v>
       </c>
       <c r="N6" t="n">
-        <v>51.07886759202032</v>
+        <v>51.02917605539093</v>
       </c>
       <c r="O6" t="n">
-        <v>137.4384876522864</v>
+        <v>137.1788435050002</v>
       </c>
       <c r="P6" t="n">
-        <v>138.9061077776216</v>
+        <v>110.240146006147</v>
       </c>
       <c r="Q6" t="n">
-        <v>135.3521746606948</v>
+        <v>113.1897946881874</v>
       </c>
       <c r="R6" t="n">
-        <v>135.1937796911818</v>
+        <v>113.056233923372</v>
       </c>
       <c r="S6" t="n">
-        <v>136.8452826255528</v>
+        <v>136.5431478861085</v>
       </c>
       <c r="T6" t="n">
-        <v>114.6544403653516</v>
+        <v>114.5578713486995</v>
       </c>
       <c r="U6" t="n">
-        <v>136.9883404477054</v>
+        <v>136.754400989884</v>
       </c>
       <c r="V6" t="n">
-        <v>135.7870598155634</v>
+        <v>113.6205920105308</v>
       </c>
       <c r="W6" t="n">
-        <v>122.544100622681</v>
+        <v>122.3100922071639</v>
       </c>
       <c r="X6" t="n">
-        <v>116.8308839372989</v>
+        <v>138.5147076842882</v>
       </c>
       <c r="Y6" t="n">
-        <v>121.2097881211394</v>
+        <v>120.9798284724758</v>
       </c>
       <c r="Z6" t="n">
-        <v>113.544938874826</v>
+        <v>113.3277226948416</v>
       </c>
       <c r="AA6" t="n">
-        <v>115.9348485461645</v>
+        <v>137.6527997199513</v>
       </c>
       <c r="AB6" t="n">
-        <v>114.2191388131883</v>
+        <v>114.0431783720553</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.279347977044986</v>
+        <v>2.068931116953645</v>
       </c>
       <c r="C7" t="n">
-        <v>2.735600686806575</v>
+        <v>2.52122124188038</v>
       </c>
       <c r="D7" t="n">
-        <v>3.110215381559437</v>
+        <v>2.896851305713716</v>
       </c>
       <c r="E7" t="n">
-        <v>2.595184185176552</v>
+        <v>2.379851799952906</v>
       </c>
       <c r="F7" t="n">
-        <v>3.880637309747547</v>
+        <v>3.664019550832592</v>
       </c>
       <c r="G7" t="n">
-        <v>4.446362718068105</v>
+        <v>4.18008244895991</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2618760686891</v>
+        <v>4.052135426593559</v>
       </c>
       <c r="I7" t="n">
-        <v>2.990745376105931</v>
+        <v>2.875596590632395</v>
       </c>
       <c r="J7" t="n">
-        <v>4.147902590222872</v>
+        <v>3.927881234219081</v>
       </c>
       <c r="K7" t="n">
-        <v>4.637293787559081</v>
+        <v>4.55247947861329</v>
       </c>
       <c r="L7" t="n">
-        <v>3.794573203802714</v>
+        <v>3.583449877778927</v>
       </c>
       <c r="M7" t="n">
-        <v>3.828652088010463</v>
+        <v>3.628664666144978</v>
       </c>
       <c r="N7" t="n">
-        <v>51.07886759202032</v>
+        <v>51.02917605539093</v>
       </c>
       <c r="O7" t="n">
-        <v>5.082188460348599</v>
+        <v>4.866167462408574</v>
       </c>
       <c r="P7" t="n">
-        <v>6.550386505941489</v>
+        <v>6.333619100732516</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.070006937064967</v>
+        <v>2.858518075120942</v>
       </c>
       <c r="R7" t="n">
-        <v>2.911611967551887</v>
+        <v>2.724957310305454</v>
       </c>
       <c r="S7" t="n">
-        <v>4.563114901922916</v>
+        <v>4.293344940768876</v>
       </c>
       <c r="T7" t="n">
-        <v>4.314147909189166</v>
+        <v>4.226594735633061</v>
       </c>
       <c r="U7" t="n">
-        <v>4.693593347981378</v>
+        <v>4.497737764503388</v>
       </c>
       <c r="V7" t="n">
-        <v>3.504892091933493</v>
+        <v>3.28931539746446</v>
       </c>
       <c r="W7" t="n">
-        <v>6.517552015972271</v>
+        <v>6.293634174188148</v>
       </c>
       <c r="X7" t="n">
-        <v>6.490591481136536</v>
+        <v>6.2649047389486</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.987715754262078</v>
+        <v>5.767156916291156</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.204646418663575</v>
+        <v>2.996446081775126</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.594556090002101</v>
+        <v>5.402996774611657</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.871467165810772</v>
+        <v>3.702912380420011</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.528384029083981</v>
+        <v>2.29437484195759</v>
       </c>
       <c r="C8" t="n">
-        <v>3.822712537051417</v>
+        <v>3.544501671557816</v>
       </c>
       <c r="D8" t="n">
-        <v>4.19732723180427</v>
+        <v>3.920131735391155</v>
       </c>
       <c r="E8" t="n">
-        <v>3.23604539490969</v>
+        <v>2.978307719332815</v>
       </c>
       <c r="F8" t="n">
-        <v>4.260235776158989</v>
+        <v>4.013756909778369</v>
       </c>
       <c r="G8" t="n">
-        <v>5.707255044495099</v>
+        <v>5.368799516687153</v>
       </c>
       <c r="H8" t="n">
-        <v>5.34898791893391</v>
+        <v>5.075415856271001</v>
       </c>
       <c r="I8" t="n">
-        <v>4.077857226350766</v>
+        <v>3.898877020309832</v>
       </c>
       <c r="J8" t="n">
-        <v>5.235014440467666</v>
+        <v>4.951161663896512</v>
       </c>
       <c r="K8" t="n">
-        <v>5.724405637803904</v>
+        <v>5.575759908290721</v>
       </c>
       <c r="L8" t="n">
-        <v>4.881685054047529</v>
+        <v>4.606730307456363</v>
       </c>
       <c r="M8" t="n">
-        <v>4.915763938254546</v>
+        <v>4.651945095824143</v>
       </c>
       <c r="N8" t="n">
-        <v>51.07886759202032</v>
+        <v>51.02917605539093</v>
       </c>
       <c r="O8" t="n">
-        <v>5.698178211407238</v>
+        <v>5.440949186507822</v>
       </c>
       <c r="P8" t="n">
-        <v>7.122614443241813</v>
+        <v>6.866740176214325</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.154341967074261</v>
+        <v>2.927168678231381</v>
       </c>
       <c r="R8" t="n">
-        <v>3.998723817796718</v>
+        <v>3.748237739982889</v>
       </c>
       <c r="S8" t="n">
-        <v>5.650226752167741</v>
+        <v>5.316625370446313</v>
       </c>
       <c r="T8" t="n">
-        <v>5.401259759434003</v>
+        <v>5.249875165310503</v>
       </c>
       <c r="U8" t="n">
-        <v>5.37448045642188</v>
+        <v>5.133149163499981</v>
       </c>
       <c r="V8" t="n">
-        <v>4.352190666713055</v>
+        <v>4.088671783736465</v>
       </c>
       <c r="W8" t="n">
-        <v>7.604828570442178</v>
+        <v>7.317071400497662</v>
       </c>
       <c r="X8" t="n">
-        <v>6.651737822297208</v>
+        <v>6.406678660666175</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.891427016365726</v>
+        <v>7.574614326045966</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.438114782635904</v>
+        <v>3.20706958047906</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.681667940246918</v>
+        <v>6.426277204289103</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.834019264455215</v>
+        <v>5.559599961087687</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.589800640749739</v>
+        <v>3.696789236828527</v>
       </c>
       <c r="C9" t="n">
-        <v>4.704368540308464</v>
+        <v>4.884185055004945</v>
       </c>
       <c r="D9" t="n">
-        <v>5.078983235061288</v>
+        <v>5.259815118838284</v>
       </c>
       <c r="E9" t="n">
-        <v>4.412015912648728</v>
+        <v>4.573156518306461</v>
       </c>
       <c r="F9" t="n">
-        <v>4.331808411791503</v>
+        <v>4.332363601224333</v>
       </c>
       <c r="G9" t="n">
-        <v>6.415131006508741</v>
+        <v>6.543046653124371</v>
       </c>
       <c r="H9" t="n">
-        <v>6.230643922190944</v>
+        <v>6.415099239718132</v>
       </c>
       <c r="I9" t="n">
-        <v>4.959513229607801</v>
+        <v>5.238560403756959</v>
       </c>
       <c r="J9" t="n">
-        <v>6.116670443724743</v>
+        <v>6.290845047343657</v>
       </c>
       <c r="K9" t="n">
-        <v>6.606061641060947</v>
+        <v>6.915443291737864</v>
       </c>
       <c r="L9" t="n">
-        <v>5.76334105730457</v>
+        <v>5.946413690903499</v>
       </c>
       <c r="M9" t="n">
-        <v>5.797419941512308</v>
+        <v>5.991628479269538</v>
       </c>
       <c r="N9" t="n">
-        <v>51.07886759202032</v>
+        <v>51.02917605539093</v>
       </c>
       <c r="O9" t="n">
-        <v>7.26911936502737</v>
+        <v>7.472745744944564</v>
       </c>
       <c r="P9" t="n">
-        <v>8.784764541130517</v>
+        <v>8.993179073220285</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.038775225505687</v>
+        <v>5.221482279285412</v>
       </c>
       <c r="R9" t="n">
-        <v>4.880379821053765</v>
+        <v>5.087921123430022</v>
       </c>
       <c r="S9" t="n">
-        <v>6.531882755424811</v>
+        <v>6.656308753893445</v>
       </c>
       <c r="T9" t="n">
-        <v>6.282915762691047</v>
+        <v>6.589558548757628</v>
       </c>
       <c r="U9" t="n">
-        <v>6.674940577577411</v>
+        <v>6.867561857668972</v>
       </c>
       <c r="V9" t="n">
-        <v>6.233341685624834</v>
+        <v>6.500575504372739</v>
       </c>
       <c r="W9" t="n">
-        <v>8.486319869474125</v>
+        <v>8.656597987312713</v>
       </c>
       <c r="X9" t="n">
-        <v>8.459359334638364</v>
+        <v>8.627868552073167</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.956483607763943</v>
+        <v>8.130120729415722</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.776508925097907</v>
+        <v>4.916206685296476</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.563323943503962</v>
+        <v>7.765960587736236</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.840235019312605</v>
+        <v>6.065876193544578</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.83583034254409</v>
+        <v>39.6903050496308</v>
       </c>
       <c r="C2" t="n">
-        <v>42.57620033197401</v>
+        <v>42.45984275399571</v>
       </c>
       <c r="D2" t="n">
-        <v>39.75687580323839</v>
+        <v>39.6698047517094</v>
       </c>
       <c r="E2" t="n">
-        <v>39.75875694247251</v>
+        <v>39.627353116949</v>
       </c>
       <c r="F2" t="n">
-        <v>39.7274975577575</v>
+        <v>39.60705433032805</v>
       </c>
       <c r="G2" t="n">
-        <v>40.02371054570597</v>
+        <v>39.80048354084981</v>
       </c>
       <c r="H2" t="n">
-        <v>39.87588030914564</v>
+        <v>39.76151256340708</v>
       </c>
       <c r="I2" t="n">
-        <v>39.69891935782336</v>
+        <v>39.59700275437993</v>
       </c>
       <c r="J2" t="n">
-        <v>39.96711203454784</v>
+        <v>39.81279625376364</v>
       </c>
       <c r="K2" t="n">
-        <v>39.8394456210986</v>
+        <v>39.72485076381404</v>
       </c>
       <c r="L2" t="n">
-        <v>39.91430612455408</v>
+        <v>39.85223690284598</v>
       </c>
       <c r="M2" t="n">
-        <v>40.18603263417679</v>
+        <v>40.04309985702002</v>
       </c>
       <c r="N2" t="n">
-        <v>39.94100553575112</v>
+        <v>39.83144160389177</v>
       </c>
       <c r="O2" t="n">
-        <v>44.10986533167497</v>
+        <v>43.93394011868192</v>
       </c>
       <c r="P2" t="n">
-        <v>40.10131605824854</v>
+        <v>39.94141790205291</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.83429821919813</v>
+        <v>39.71341476273059</v>
       </c>
       <c r="R2" t="n">
-        <v>39.76733455105744</v>
+        <v>39.69006463219088</v>
       </c>
       <c r="S2" t="n">
-        <v>39.93607952856477</v>
+        <v>39.77486470857872</v>
       </c>
       <c r="T2" t="n">
-        <v>39.84303310872758</v>
+        <v>39.71832236506722</v>
       </c>
       <c r="U2" t="n">
-        <v>43.62596333629708</v>
+        <v>43.5235062423283</v>
       </c>
       <c r="V2" t="n">
-        <v>39.85806465648855</v>
+        <v>39.74335594036909</v>
       </c>
       <c r="W2" t="n">
-        <v>46.22015569850176</v>
+        <v>46.11587246602797</v>
       </c>
       <c r="X2" t="n">
-        <v>39.86668786766843</v>
+        <v>39.74677401895287</v>
       </c>
       <c r="Y2" t="n">
-        <v>40.17273335803421</v>
+        <v>40.04659684064932</v>
       </c>
       <c r="Z2" t="n">
-        <v>41.26705004001864</v>
+        <v>41.1347173026514</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.83541872336389</v>
+        <v>39.71434570010576</v>
       </c>
       <c r="AB2" t="n">
-        <v>40.08947407011924</v>
+        <v>40.08853650961267</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.30875722035805</v>
+        <v>40.98397737578973</v>
       </c>
       <c r="C3" t="n">
-        <v>44.60551818605671</v>
+        <v>44.5095278598393</v>
       </c>
       <c r="D3" t="n">
-        <v>40.7605416080492</v>
+        <v>40.85247912703068</v>
       </c>
       <c r="E3" t="n">
-        <v>40.76797108579633</v>
+        <v>40.54301391569398</v>
       </c>
       <c r="F3" t="n">
-        <v>40.55052032249613</v>
+        <v>40.40353494337915</v>
       </c>
       <c r="G3" t="n">
-        <v>42.64860126311739</v>
+        <v>41.77062670286247</v>
       </c>
       <c r="H3" t="n">
-        <v>41.6183620262259</v>
+        <v>41.5148419968041</v>
       </c>
       <c r="I3" t="n">
-        <v>40.34659609729727</v>
+        <v>40.33230818934931</v>
       </c>
       <c r="J3" t="n">
-        <v>42.25124184202211</v>
+        <v>41.86354944364408</v>
       </c>
       <c r="K3" t="n">
-        <v>41.34193391811797</v>
+        <v>41.2368515463349</v>
       </c>
       <c r="L3" t="n">
-        <v>41.87814452987799</v>
+        <v>42.14791532600908</v>
       </c>
       <c r="M3" t="n">
-        <v>43.8311979030587</v>
+        <v>43.52270002283092</v>
       </c>
       <c r="N3" t="n">
-        <v>42.07328736623685</v>
+        <v>42.00417329841487</v>
       </c>
       <c r="O3" t="n">
-        <v>48.90131237565587</v>
+        <v>48.66406773612817</v>
       </c>
       <c r="P3" t="n">
-        <v>43.19977630585956</v>
+        <v>42.7725039734116</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.31115783314782</v>
+        <v>41.16113703514658</v>
       </c>
       <c r="R3" t="n">
-        <v>40.83815380859927</v>
+        <v>41.00061806913153</v>
       </c>
       <c r="S3" t="n">
-        <v>42.02552661064609</v>
+        <v>41.58874944795009</v>
       </c>
       <c r="T3" t="n">
-        <v>41.37713875922042</v>
+        <v>41.19962922059545</v>
       </c>
       <c r="U3" t="n">
-        <v>48.68191698440832</v>
+        <v>48.63796270395698</v>
       </c>
       <c r="V3" t="n">
-        <v>41.46419901786849</v>
+        <v>41.35838378466143</v>
       </c>
       <c r="W3" t="n">
-        <v>53.53154669496217</v>
+        <v>53.45454435368649</v>
       </c>
       <c r="X3" t="n">
-        <v>41.54394240877477</v>
+        <v>41.40082194051622</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.72166871237663</v>
+        <v>43.53427001332758</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.06818751551228</v>
+        <v>43.89546824493318</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.31618144587265</v>
+        <v>41.16488803295975</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.14507458427327</v>
+        <v>43.84278935280047</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.155242207961414</v>
+        <v>4.998758963970971</v>
       </c>
       <c r="C4" t="n">
-        <v>3.601623120848047</v>
+        <v>2.819671564423511</v>
       </c>
       <c r="D4" t="n">
-        <v>5.263414365621415</v>
+        <v>4.767198668346336</v>
       </c>
       <c r="E4" t="n">
-        <v>5.284662698637454</v>
+        <v>4.287687925010482</v>
       </c>
       <c r="F4" t="n">
-        <v>4.931573568254043</v>
+        <v>4.058403792223663</v>
       </c>
       <c r="G4" t="n">
-        <v>8.27743553183867</v>
+        <v>6.243275706900105</v>
       </c>
       <c r="H4" t="n">
-        <v>6.607625004621114</v>
+        <v>5.803080589148545</v>
       </c>
       <c r="I4" t="n">
-        <v>4.608769653376616</v>
+        <v>3.944866617936117</v>
       </c>
       <c r="J4" t="n">
-        <v>7.638275330465388</v>
+        <v>6.382946804849491</v>
       </c>
       <c r="K4" t="n">
-        <v>6.196078442345472</v>
+        <v>5.388968697484375</v>
       </c>
       <c r="L4" t="n">
-        <v>7.041662266407846</v>
+        <v>6.827853738369088</v>
       </c>
       <c r="M4" t="n">
-        <v>10.1044635693253</v>
+        <v>8.97645773632274</v>
       </c>
       <c r="N4" t="n">
-        <v>7.343244398214406</v>
+        <v>97.07504839063225</v>
       </c>
       <c r="O4" t="n">
-        <v>7.276350903003609</v>
+        <v>6.40488626355739</v>
       </c>
       <c r="P4" t="n">
-        <v>9.154025496306616</v>
+        <v>7.83519414969831</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.137936169957607</v>
+        <v>5.259793804426328</v>
       </c>
       <c r="R4" t="n">
-        <v>5.38155073349914</v>
+        <v>4.996043338389542</v>
       </c>
       <c r="S4" t="n">
-        <v>7.28760288096931</v>
+        <v>5.95389921115299</v>
       </c>
       <c r="T4" t="n">
-        <v>6.236600765440564</v>
+        <v>5.315227430427348</v>
       </c>
       <c r="U4" t="n">
-        <v>8.4253624617625</v>
+        <v>7.722120340241931</v>
       </c>
       <c r="V4" t="n">
-        <v>6.407071747987708</v>
+        <v>5.60169409601161</v>
       </c>
       <c r="W4" t="n">
-        <v>9.600089767962334</v>
+        <v>8.815665015626106</v>
       </c>
       <c r="X4" t="n">
-        <v>6.503792149404055</v>
+        <v>5.636601949472797</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.941029358292703</v>
+        <v>9.022774145663739</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.969048291614241</v>
+        <v>6.082490486442802</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.150592779967139</v>
+        <v>5.270309170331008</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.006820148384733</v>
+        <v>9.459995658735762</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.11922411012932</v>
+        <v>59.75916157411471</v>
       </c>
       <c r="C5" t="n">
-        <v>24.80227628112808</v>
+        <v>23.94081642223514</v>
       </c>
       <c r="D5" t="n">
-        <v>58.75845602341119</v>
+        <v>63.61934709755231</v>
       </c>
       <c r="E5" t="n">
-        <v>55.82535797624919</v>
+        <v>50.94572384981467</v>
       </c>
       <c r="F5" t="n">
-        <v>52.29089969682666</v>
+        <v>49.61059341298865</v>
       </c>
       <c r="G5" t="n">
-        <v>106.6524090997544</v>
+        <v>83.45717907507584</v>
       </c>
       <c r="H5" t="n">
-        <v>88.89045917693485</v>
+        <v>87.56574024233809</v>
       </c>
       <c r="I5" t="n">
-        <v>46.2094958614974</v>
+        <v>47.7485068919657</v>
       </c>
       <c r="J5" t="n">
-        <v>98.22797490666004</v>
+        <v>88.89394962873634</v>
       </c>
       <c r="K5" t="n">
-        <v>71.99257109178687</v>
+        <v>70.65191769043112</v>
       </c>
       <c r="L5" t="n">
-        <v>89.05275421052424</v>
+        <v>98.91632886210277</v>
       </c>
       <c r="M5" t="n">
-        <v>156.5550439487519</v>
+        <v>148.7418659276117</v>
       </c>
       <c r="N5" t="n">
-        <v>111.9211976713965</v>
+        <v>97.07504839063225</v>
       </c>
       <c r="O5" t="n">
-        <v>84.390272189987</v>
+        <v>82.01789368333692</v>
       </c>
       <c r="P5" t="n">
-        <v>121.7256282579155</v>
+        <v>111.3444853587977</v>
       </c>
       <c r="Q5" t="n">
-        <v>74.20854568279309</v>
+        <v>71.4934582141549</v>
       </c>
       <c r="R5" t="n">
-        <v>62.64260237080197</v>
+        <v>69.91685952017758</v>
       </c>
       <c r="S5" t="n">
-        <v>89.24497670546508</v>
+        <v>78.52271219999845</v>
       </c>
       <c r="T5" t="n">
-        <v>78.09824929713852</v>
+        <v>74.46942858685074</v>
       </c>
       <c r="U5" t="n">
-        <v>113.0230031276185</v>
+        <v>113.2713157601275</v>
       </c>
       <c r="V5" t="n">
-        <v>70.06351359425261</v>
+        <v>68.74591693129861</v>
       </c>
       <c r="W5" t="n">
-        <v>138.4161708713941</v>
+        <v>137.5269006219988</v>
       </c>
       <c r="X5" t="n">
-        <v>82.02599208764545</v>
+        <v>79.50697023362554</v>
       </c>
       <c r="Y5" t="n">
-        <v>143.754393615054</v>
+        <v>139.9804907889937</v>
       </c>
       <c r="Z5" t="n">
-        <v>83.43141489361498</v>
+        <v>80.71747058623902</v>
       </c>
       <c r="AA5" t="n">
-        <v>72.79414729917991</v>
+        <v>70.08325061634876</v>
       </c>
       <c r="AB5" t="n">
-        <v>139.5865900320194</v>
+        <v>164.5232504725333</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.670541972539</v>
+        <v>124.5175939116262</v>
       </c>
       <c r="C6" t="n">
-        <v>147.0595217928449</v>
+        <v>146.2029713567362</v>
       </c>
       <c r="D6" t="n">
-        <v>148.7213130376183</v>
+        <v>124.2860336160015</v>
       </c>
       <c r="E6" t="n">
-        <v>124.7999624632151</v>
+        <v>147.670987717323</v>
       </c>
       <c r="F6" t="n">
-        <v>124.4468733328317</v>
+        <v>123.577238739879</v>
       </c>
       <c r="G6" t="n">
-        <v>127.7927352964164</v>
+        <v>149.6265754992127</v>
       </c>
       <c r="H6" t="n">
-        <v>150.065523676618</v>
+        <v>149.1863803814612</v>
       </c>
       <c r="I6" t="n">
-        <v>124.1240694179543</v>
+        <v>147.3281664102487</v>
       </c>
       <c r="J6" t="n">
-        <v>151.0961740024621</v>
+        <v>149.7662465971622</v>
       </c>
       <c r="K6" t="n">
-        <v>149.6539771143424</v>
+        <v>124.9078036451396</v>
       </c>
       <c r="L6" t="n">
-        <v>126.5569620309855</v>
+        <v>150.2111535306817</v>
       </c>
       <c r="M6" t="n">
-        <v>129.6197633339029</v>
+        <v>152.3597575286353</v>
       </c>
       <c r="N6" t="n">
-        <v>126.8684907339696</v>
+        <v>97.07504839063225</v>
       </c>
       <c r="O6" t="n">
-        <v>150.8003070305168</v>
+        <v>125.9348709339256</v>
       </c>
       <c r="P6" t="n">
-        <v>152.67787975775</v>
+        <v>151.2767421989857</v>
       </c>
       <c r="Q6" t="n">
-        <v>149.5958348419544</v>
+        <v>124.7786287520816</v>
       </c>
       <c r="R6" t="n">
-        <v>148.8394494054959</v>
+        <v>148.3793431307021</v>
       </c>
       <c r="S6" t="n">
-        <v>150.7455015529661</v>
+        <v>125.4727341588081</v>
       </c>
       <c r="T6" t="n">
-        <v>125.7519005300183</v>
+        <v>124.8340623780825</v>
       </c>
       <c r="U6" t="n">
-        <v>127.9603496190142</v>
+        <v>127.2414197880801</v>
       </c>
       <c r="V6" t="n">
-        <v>149.8649704199845</v>
+        <v>125.1205290436668</v>
       </c>
       <c r="W6" t="n">
-        <v>153.1240718382445</v>
+        <v>134.4539689499464</v>
       </c>
       <c r="X6" t="n">
-        <v>149.9616908214009</v>
+        <v>149.0199017417854</v>
       </c>
       <c r="Y6" t="n">
-        <v>134.7290106129945</v>
+        <v>133.7973000142053</v>
       </c>
       <c r="Z6" t="n">
-        <v>150.426946963611</v>
+        <v>125.6013254340981</v>
       </c>
       <c r="AA6" t="n">
-        <v>125.6658925445448</v>
+        <v>148.6536089626437</v>
       </c>
       <c r="AB6" t="n">
-        <v>128.544399401284</v>
+        <v>129.0101184996722</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.407376619283772</v>
+        <v>6.199319933310755</v>
       </c>
       <c r="C7" t="n">
-        <v>4.853757532170413</v>
+        <v>4.020232533763326</v>
       </c>
       <c r="D7" t="n">
-        <v>6.515548776943779</v>
+        <v>5.967759637686151</v>
       </c>
       <c r="E7" t="n">
-        <v>6.53679710995982</v>
+        <v>5.488248894350293</v>
       </c>
       <c r="F7" t="n">
-        <v>6.183707979576412</v>
+        <v>5.25896476156348</v>
       </c>
       <c r="G7" t="n">
-        <v>9.529569943161038</v>
+        <v>7.443836676239901</v>
       </c>
       <c r="H7" t="n">
-        <v>7.859759415943484</v>
+        <v>7.003641558488363</v>
       </c>
       <c r="I7" t="n">
-        <v>5.860904064698983</v>
+        <v>5.145427587275927</v>
       </c>
       <c r="J7" t="n">
-        <v>8.890409741787757</v>
+        <v>7.58350777418929</v>
       </c>
       <c r="K7" t="n">
-        <v>7.448212853667836</v>
+        <v>6.589529666824182</v>
       </c>
       <c r="L7" t="n">
-        <v>8.293796677730212</v>
+        <v>8.028414707708997</v>
       </c>
       <c r="M7" t="n">
-        <v>11.35659798064766</v>
+        <v>10.17701870566254</v>
       </c>
       <c r="N7" t="n">
-        <v>8.595378809536779</v>
+        <v>97.07504839063225</v>
       </c>
       <c r="O7" t="n">
-        <v>8.528472717512841</v>
+        <v>7.605433544493497</v>
       </c>
       <c r="P7" t="n">
-        <v>10.40614731081585</v>
+        <v>9.035741430634404</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.390070581279968</v>
+        <v>6.460354773766135</v>
       </c>
       <c r="R7" t="n">
-        <v>6.633685144821509</v>
+        <v>6.196604307729345</v>
       </c>
       <c r="S7" t="n">
-        <v>8.539737292291676</v>
+        <v>7.154460180492803</v>
       </c>
       <c r="T7" t="n">
-        <v>7.488735176762928</v>
+        <v>6.515788399767155</v>
       </c>
       <c r="U7" t="n">
-        <v>9.696607934016987</v>
+        <v>8.92455931287534</v>
       </c>
       <c r="V7" t="n">
-        <v>7.659206159310072</v>
+        <v>6.802255065351323</v>
       </c>
       <c r="W7" t="n">
-        <v>10.8522241792847</v>
+        <v>10.0162259849659</v>
       </c>
       <c r="X7" t="n">
-        <v>7.755926560726422</v>
+        <v>6.837162918812627</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.21285116228903</v>
+        <v>10.22379961518641</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.221182702936607</v>
+        <v>7.283051455782626</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.402727191289508</v>
+        <v>6.470870139670816</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.2589545597071</v>
+        <v>10.66055662807557</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.936062956553231</v>
+        <v>6.692309605011204</v>
       </c>
       <c r="C8" t="n">
-        <v>6.742687830372969</v>
+        <v>5.793697037257528</v>
       </c>
       <c r="D8" t="n">
-        <v>8.404479075146336</v>
+        <v>7.741224141180355</v>
       </c>
       <c r="E8" t="n">
-        <v>7.701437624061382</v>
+        <v>6.579898321928355</v>
       </c>
       <c r="F8" t="n">
-        <v>6.924304428220567</v>
+        <v>5.951437446619869</v>
       </c>
       <c r="G8" t="n">
-        <v>11.70055568767426</v>
+        <v>9.482815977484385</v>
       </c>
       <c r="H8" t="n">
-        <v>9.748689714146032</v>
+        <v>8.777106061982561</v>
       </c>
       <c r="I8" t="n">
-        <v>7.749834362901531</v>
+        <v>6.918892090770139</v>
       </c>
       <c r="J8" t="n">
-        <v>10.77934003999031</v>
+        <v>9.356972277683496</v>
       </c>
       <c r="K8" t="n">
-        <v>9.337143151870404</v>
+        <v>8.362994170318395</v>
       </c>
       <c r="L8" t="n">
-        <v>10.18272697593276</v>
+        <v>9.801879211203097</v>
       </c>
       <c r="M8" t="n">
-        <v>13.24552827885002</v>
+        <v>11.9504832091579</v>
       </c>
       <c r="N8" t="n">
-        <v>9.429892473643235</v>
+        <v>97.07504839063225</v>
       </c>
       <c r="O8" t="n">
-        <v>9.652761823784246</v>
+        <v>8.659099732382975</v>
       </c>
       <c r="P8" t="n">
-        <v>11.45940854215058</v>
+        <v>10.02254504913183</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.651437934722538</v>
+        <v>6.7017019161036</v>
       </c>
       <c r="R8" t="n">
-        <v>8.522615443024051</v>
+        <v>7.970068811223555</v>
       </c>
       <c r="S8" t="n">
-        <v>10.42866759049423</v>
+        <v>8.927924683987003</v>
       </c>
       <c r="T8" t="n">
-        <v>9.377665474965479</v>
+        <v>8.28925290326136</v>
       </c>
       <c r="U8" t="n">
-        <v>10.92176075966978</v>
+        <v>10.07273367546312</v>
       </c>
       <c r="V8" t="n">
-        <v>9.175879405146745</v>
+        <v>8.226966416988974</v>
       </c>
       <c r="W8" t="n">
-        <v>12.74142180238525</v>
+        <v>11.78994213662408</v>
       </c>
       <c r="X8" t="n">
-        <v>8.141962974794543</v>
+        <v>7.195868122700462</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.45349369330803</v>
+        <v>13.27230320782256</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.724601810459863</v>
+        <v>7.75225565024544</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.291657489492055</v>
+        <v>8.244334643165027</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.56877341496663</v>
+        <v>13.77158416323512</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.89463911861166</v>
+        <v>9.415613836367594</v>
       </c>
       <c r="C9" t="n">
-        <v>9.751279912490292</v>
+        <v>8.547001032044472</v>
       </c>
       <c r="D9" t="n">
-        <v>11.41307115726365</v>
+        <v>10.4945281359673</v>
       </c>
       <c r="E9" t="n">
-        <v>11.10883756904192</v>
+        <v>9.71256538658551</v>
       </c>
       <c r="F9" t="n">
-        <v>7.83019591690352</v>
+        <v>6.764731341128192</v>
       </c>
       <c r="G9" t="n">
-        <v>14.42709272252951</v>
+        <v>11.97060541529365</v>
       </c>
       <c r="H9" t="n">
-        <v>12.75728179626335</v>
+        <v>11.53041005676952</v>
       </c>
       <c r="I9" t="n">
-        <v>10.75842644501885</v>
+        <v>9.672196085557077</v>
       </c>
       <c r="J9" t="n">
-        <v>13.78793212210762</v>
+        <v>12.11027627247045</v>
       </c>
       <c r="K9" t="n">
-        <v>12.34573523398771</v>
+        <v>11.11629816510534</v>
       </c>
       <c r="L9" t="n">
-        <v>13.1913190580501</v>
+        <v>12.55518320599011</v>
       </c>
       <c r="M9" t="n">
-        <v>16.25412036096753</v>
+        <v>14.70378720394369</v>
       </c>
       <c r="N9" t="n">
-        <v>13.49290118985665</v>
+        <v>97.07504839063225</v>
       </c>
       <c r="O9" t="n">
-        <v>13.8933665039217</v>
+        <v>12.56650561667998</v>
       </c>
       <c r="P9" t="n">
-        <v>15.87268353292926</v>
+        <v>14.09126404939405</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.28759336064845</v>
+        <v>10.98712351281987</v>
       </c>
       <c r="R9" t="n">
-        <v>11.53120752514138</v>
+        <v>10.72337280601049</v>
       </c>
       <c r="S9" t="n">
-        <v>13.43725967261155</v>
+        <v>11.68122867877394</v>
       </c>
       <c r="T9" t="n">
-        <v>12.3862575570828</v>
+        <v>11.04255689804829</v>
       </c>
       <c r="U9" t="n">
-        <v>14.59470664607871</v>
+        <v>13.44991430804574</v>
       </c>
       <c r="V9" t="n">
-        <v>14.18413687408953</v>
+        <v>12.84128167927154</v>
       </c>
       <c r="W9" t="n">
-        <v>15.74974655960459</v>
+        <v>14.54299448324706</v>
       </c>
       <c r="X9" t="n">
-        <v>12.65344894104629</v>
+        <v>11.36393141709377</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.11037354260891</v>
+        <v>14.75056811346757</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.26844393867772</v>
+        <v>11.01972040069948</v>
       </c>
       <c r="AA9" t="n">
-        <v>12.30024957160938</v>
+        <v>10.99763863795197</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.15647694002699</v>
+        <v>15.18732512635671</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.68111959773678</v>
+        <v>39.52516644115882</v>
       </c>
       <c r="C2" t="n">
-        <v>42.5337564981287</v>
+        <v>42.39139325379595</v>
       </c>
       <c r="D2" t="n">
-        <v>39.70815636860006</v>
+        <v>39.60418783679205</v>
       </c>
       <c r="E2" t="n">
-        <v>39.62761023782725</v>
+        <v>39.485007659783</v>
       </c>
       <c r="F2" t="n">
-        <v>39.62962587686292</v>
+        <v>39.506473242957</v>
       </c>
       <c r="G2" t="n">
-        <v>39.90543497987802</v>
+        <v>39.66964391663458</v>
       </c>
       <c r="H2" t="n">
-        <v>39.74577652075353</v>
+        <v>39.62048311942833</v>
       </c>
       <c r="I2" t="n">
-        <v>39.65284841847644</v>
+        <v>39.51926893015051</v>
       </c>
       <c r="J2" t="n">
-        <v>39.84135810699775</v>
+        <v>39.67245924222181</v>
       </c>
       <c r="K2" t="n">
-        <v>39.69258601115406</v>
+        <v>39.53152046818629</v>
       </c>
       <c r="L2" t="n">
-        <v>39.7713695322193</v>
+        <v>39.68375781275456</v>
       </c>
       <c r="M2" t="n">
-        <v>40.02567265297897</v>
+        <v>39.86749633953338</v>
       </c>
       <c r="N2" t="n">
-        <v>39.76732752906171</v>
+        <v>39.63287865255444</v>
       </c>
       <c r="O2" t="n">
-        <v>43.92218381852712</v>
+        <v>43.70955152745518</v>
       </c>
       <c r="P2" t="n">
-        <v>39.9897621004166</v>
+        <v>39.81152916748575</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.69551760920189</v>
+        <v>39.55947358515913</v>
       </c>
       <c r="R2" t="n">
-        <v>39.63589320337469</v>
+        <v>39.5450656074475</v>
       </c>
       <c r="S2" t="n">
-        <v>39.81426140833879</v>
+        <v>39.63907735223471</v>
       </c>
       <c r="T2" t="n">
-        <v>39.75362163601464</v>
+        <v>39.60770542464211</v>
       </c>
       <c r="U2" t="n">
-        <v>43.36364630624847</v>
+        <v>43.23484248841925</v>
       </c>
       <c r="V2" t="n">
-        <v>39.75376133676419</v>
+        <v>39.62192646670736</v>
       </c>
       <c r="W2" t="n">
-        <v>45.99988190814985</v>
+        <v>45.86388887633561</v>
       </c>
       <c r="X2" t="n">
-        <v>39.83644516998643</v>
+        <v>39.69865880047913</v>
       </c>
       <c r="Y2" t="n">
-        <v>40.07623016177872</v>
+        <v>39.92315568933982</v>
       </c>
       <c r="Z2" t="n">
-        <v>41.06033236737353</v>
+        <v>40.90444163275986</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.74460360177577</v>
+        <v>39.59853119700507</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.96428634312679</v>
+        <v>39.93359475512397</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.81075123235858</v>
+        <v>40.49942246415425</v>
       </c>
       <c r="C3" t="n">
-        <v>44.88551156421227</v>
+        <v>44.74370672329611</v>
       </c>
       <c r="D3" t="n">
-        <v>41.01545750182927</v>
+        <v>41.07480583361782</v>
       </c>
       <c r="E3" t="n">
-        <v>40.4350867665943</v>
+        <v>40.21833999158858</v>
       </c>
       <c r="F3" t="n">
-        <v>40.45340211753515</v>
+        <v>40.37547609442456</v>
       </c>
       <c r="G3" t="n">
-        <v>42.40489207698049</v>
+        <v>41.52603339898883</v>
       </c>
       <c r="H3" t="n">
-        <v>41.29214227361586</v>
+        <v>41.19894458725358</v>
       </c>
       <c r="I3" t="n">
-        <v>40.62143190072882</v>
+        <v>40.46887711326898</v>
       </c>
       <c r="J3" t="n">
-        <v>41.95577353184598</v>
+        <v>41.55235983617516</v>
       </c>
       <c r="K3" t="n">
-        <v>40.89244244678287</v>
+        <v>40.54478440945382</v>
       </c>
       <c r="L3" t="n">
-        <v>41.46014815372749</v>
+        <v>41.6357193828505</v>
       </c>
       <c r="M3" t="n">
-        <v>43.28910149021417</v>
+        <v>42.95989297352914</v>
       </c>
       <c r="N3" t="n">
-        <v>41.43602945871062</v>
+        <v>41.27737279615113</v>
       </c>
       <c r="O3" t="n">
-        <v>48.59679525210935</v>
+        <v>48.29608536876131</v>
       </c>
       <c r="P3" t="n">
-        <v>43.00420837162478</v>
+        <v>42.53457282655433</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.92066492364867</v>
+        <v>40.75067464390095</v>
       </c>
       <c r="R3" t="n">
-        <v>40.50160942478644</v>
+        <v>40.65549875103913</v>
       </c>
       <c r="S3" t="n">
-        <v>41.75814733851809</v>
+        <v>41.3099920838601</v>
       </c>
       <c r="T3" t="n">
-        <v>41.34216866471559</v>
+        <v>41.10131768761416</v>
       </c>
       <c r="U3" t="n">
-        <v>47.78053818712729</v>
+        <v>47.71731550893127</v>
       </c>
       <c r="V3" t="n">
-        <v>41.32128833027398</v>
+        <v>41.18156431810392</v>
       </c>
       <c r="W3" t="n">
-        <v>52.9650630291626</v>
+        <v>52.84887097790757</v>
       </c>
       <c r="X3" t="n">
-        <v>41.93092341075095</v>
+        <v>41.748383424414</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.63640715648477</v>
+        <v>43.34492498688849</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.52048994471277</v>
+        <v>43.31074594526349</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.27112562375426</v>
+        <v>41.02954439578259</v>
       </c>
       <c r="AB3" t="n">
-        <v>42.8528277032967</v>
+        <v>43.42720124401605</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.303407180493443</v>
+        <v>4.222964260526822</v>
       </c>
       <c r="C4" t="n">
-        <v>3.981369745139888</v>
+        <v>3.205721481322426</v>
       </c>
       <c r="D4" t="n">
-        <v>5.608799944922935</v>
+        <v>5.115547275841649</v>
       </c>
       <c r="E4" t="n">
-        <v>4.698994344793723</v>
+        <v>3.769352350934473</v>
       </c>
       <c r="F4" t="n">
-        <v>4.721761914941345</v>
+        <v>4.011815987541216</v>
       </c>
       <c r="G4" t="n">
-        <v>7.837152611952563</v>
+        <v>5.854903808947751</v>
       </c>
       <c r="H4" t="n">
-        <v>6.03373686962181</v>
+        <v>5.299609989419555</v>
       </c>
       <c r="I4" t="n">
-        <v>4.984071205362687</v>
+        <v>4.156349160698782</v>
       </c>
       <c r="J4" t="n">
-        <v>7.113621360476093</v>
+        <v>5.887368782488545</v>
       </c>
       <c r="K4" t="n">
-        <v>5.432925594852524</v>
+        <v>4.294735918798994</v>
       </c>
       <c r="L4" t="n">
-        <v>6.322821707494127</v>
+        <v>6.014326758335875</v>
       </c>
       <c r="M4" t="n">
-        <v>9.190345647715064</v>
+        <v>8.083912710864411</v>
       </c>
       <c r="N4" t="n">
-        <v>6.277165422416345</v>
+        <v>72.47327460659885</v>
       </c>
       <c r="O4" t="n">
-        <v>6.94365754289305</v>
+        <v>6.078298835548317</v>
       </c>
       <c r="P4" t="n">
-        <v>8.78966623082805</v>
+        <v>7.457562987751585</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.466039343404093</v>
+        <v>4.610479234076273</v>
       </c>
       <c r="R4" t="n">
-        <v>4.79255425100419</v>
+        <v>4.447734497826158</v>
       </c>
       <c r="S4" t="n">
-        <v>6.807305179501916</v>
+        <v>5.509640402737286</v>
       </c>
       <c r="T4" t="n">
-        <v>6.122351055427131</v>
+        <v>5.155280048778729</v>
       </c>
       <c r="U4" t="n">
-        <v>7.11834221433744</v>
+        <v>6.463778170151759</v>
       </c>
       <c r="V4" t="n">
-        <v>6.125293606505565</v>
+        <v>5.32009295074772</v>
       </c>
       <c r="W4" t="n">
-        <v>8.837149125368445</v>
+        <v>8.092112008827675</v>
       </c>
       <c r="X4" t="n">
-        <v>7.057880972346396</v>
+        <v>6.18264026947787</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.747410671462731</v>
+        <v>8.705071365199748</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.21190976178495</v>
+        <v>5.340965215343582</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.020488210198542</v>
+        <v>5.051652927265338</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.486410897611501</v>
+        <v>8.799741183182974</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.47037193772577</v>
+        <v>46.18547807401734</v>
       </c>
       <c r="C5" t="n">
-        <v>32.13369303971807</v>
+        <v>30.85201588081559</v>
       </c>
       <c r="D5" t="n">
-        <v>63.957512192511</v>
+        <v>67.88197560390931</v>
       </c>
       <c r="E5" t="n">
-        <v>45.01120712379123</v>
+        <v>41.02981161290825</v>
       </c>
       <c r="F5" t="n">
-        <v>47.45032282716662</v>
+        <v>47.35748105973634</v>
       </c>
       <c r="G5" t="n">
-        <v>93.75513491715274</v>
+        <v>72.70042241616659</v>
       </c>
       <c r="H5" t="n">
-        <v>75.71637942294825</v>
+        <v>75.19953727905462</v>
       </c>
       <c r="I5" t="n">
-        <v>53.27609107100969</v>
+        <v>50.9904323411649</v>
       </c>
       <c r="J5" t="n">
-        <v>85.20428884989265</v>
+        <v>76.49378877420121</v>
       </c>
       <c r="K5" t="n">
-        <v>54.68589863134866</v>
+        <v>47.46158288944374</v>
       </c>
       <c r="L5" t="n">
-        <v>73.23592144138341</v>
+        <v>80.16047329118092</v>
       </c>
       <c r="M5" t="n">
-        <v>132.5900536488056</v>
+        <v>125.0496486823745</v>
       </c>
       <c r="N5" t="n">
-        <v>84.24513619444382</v>
+        <v>72.47327460659885</v>
       </c>
       <c r="O5" t="n">
-        <v>75.6239350863664</v>
+        <v>72.99219570800994</v>
       </c>
       <c r="P5" t="n">
-        <v>109.2905069869414</v>
+        <v>98.91998404192509</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.05435896091251</v>
+        <v>56.35615611456873</v>
       </c>
       <c r="R5" t="n">
-        <v>50.50431361954506</v>
+        <v>57.44453000296306</v>
       </c>
       <c r="S5" t="n">
-        <v>77.59564863053762</v>
+        <v>67.6892816833</v>
       </c>
       <c r="T5" t="n">
-        <v>74.19267102930549</v>
+        <v>69.31367815220433</v>
       </c>
       <c r="U5" t="n">
-        <v>85.10526507608829</v>
+        <v>85.81299546139728</v>
       </c>
       <c r="V5" t="n">
-        <v>62.88454372217106</v>
+        <v>61.14682529939419</v>
       </c>
       <c r="W5" t="n">
-        <v>118.9341906060658</v>
+        <v>118.2070701463302</v>
       </c>
       <c r="X5" t="n">
-        <v>89.51556147916206</v>
+        <v>86.40993805747203</v>
       </c>
       <c r="Y5" t="n">
-        <v>134.3756378548456</v>
+        <v>128.3037535659287</v>
       </c>
       <c r="Z5" t="n">
-        <v>64.3011239087877</v>
+        <v>61.57923341187643</v>
       </c>
       <c r="AA5" t="n">
-        <v>68.92886110351424</v>
+        <v>64.21792624486309</v>
       </c>
       <c r="AB5" t="n">
-        <v>124.0650383520079</v>
+        <v>144.0771113602306</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116.6559632266844</v>
+        <v>137.7415479045756</v>
       </c>
       <c r="C6" t="n">
-        <v>115.3339257913309</v>
+        <v>114.551516707449</v>
       </c>
       <c r="D6" t="n">
-        <v>139.2205232765123</v>
+        <v>138.6341309198903</v>
       </c>
       <c r="E6" t="n">
-        <v>116.0515503909847</v>
+        <v>137.2879359949832</v>
       </c>
       <c r="F6" t="n">
-        <v>138.3334852465308</v>
+        <v>115.3576112136677</v>
       </c>
       <c r="G6" t="n">
-        <v>119.1897086581436</v>
+        <v>117.2006990350743</v>
       </c>
       <c r="H6" t="n">
-        <v>117.3862929158128</v>
+        <v>116.645405215546</v>
       </c>
       <c r="I6" t="n">
-        <v>116.3366272515536</v>
+        <v>115.5021443868253</v>
       </c>
       <c r="J6" t="n">
-        <v>140.7253446920655</v>
+        <v>139.4059524265373</v>
       </c>
       <c r="K6" t="n">
-        <v>139.0446489264419</v>
+        <v>137.8133195628477</v>
       </c>
       <c r="L6" t="n">
-        <v>117.6753777536851</v>
+        <v>139.5329104023846</v>
       </c>
       <c r="M6" t="n">
-        <v>142.8020689793044</v>
+        <v>119.4297079369908</v>
       </c>
       <c r="N6" t="n">
-        <v>117.6391302138932</v>
+        <v>72.47327460659885</v>
       </c>
       <c r="O6" t="n">
-        <v>118.3056223343699</v>
+        <v>139.6536832176089</v>
       </c>
       <c r="P6" t="n">
-        <v>142.4646413033337</v>
+        <v>141.0324233384162</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.0777626749935</v>
+        <v>138.129062878125</v>
       </c>
       <c r="R6" t="n">
-        <v>138.4042775825936</v>
+        <v>115.7935297239527</v>
       </c>
       <c r="S6" t="n">
-        <v>118.1598612256929</v>
+        <v>139.028224046786</v>
       </c>
       <c r="T6" t="n">
-        <v>117.4749071016181</v>
+        <v>116.5010752749052</v>
       </c>
       <c r="U6" t="n">
-        <v>118.4898503502518</v>
+        <v>117.8229379339088</v>
       </c>
       <c r="V6" t="n">
-        <v>139.7370169380949</v>
+        <v>138.8386765947964</v>
       </c>
       <c r="W6" t="n">
-        <v>125.8891788411457</v>
+        <v>141.6676766907504</v>
       </c>
       <c r="X6" t="n">
-        <v>118.4104370185374</v>
+        <v>117.5284354956044</v>
       </c>
       <c r="Y6" t="n">
-        <v>126.0127404354664</v>
+        <v>124.9595312422339</v>
       </c>
       <c r="Z6" t="n">
-        <v>117.5644658079759</v>
+        <v>138.8595488593922</v>
       </c>
       <c r="AA6" t="n">
-        <v>139.632211541788</v>
+        <v>138.570236571314</v>
       </c>
       <c r="AB6" t="n">
-        <v>119.8600615887886</v>
+        <v>120.1744589613083</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.39726414428253</v>
+        <v>5.274665268894043</v>
       </c>
       <c r="C7" t="n">
-        <v>5.075226708928978</v>
+        <v>4.257422489689623</v>
       </c>
       <c r="D7" t="n">
-        <v>6.702656908712026</v>
+        <v>6.167248284208876</v>
       </c>
       <c r="E7" t="n">
-        <v>5.792851308582811</v>
+        <v>4.821053359301692</v>
       </c>
       <c r="F7" t="n">
-        <v>5.815618878730431</v>
+        <v>5.063516995908437</v>
       </c>
       <c r="G7" t="n">
-        <v>8.931009575741649</v>
+        <v>6.906604817314974</v>
       </c>
       <c r="H7" t="n">
-        <v>7.127593833410899</v>
+        <v>6.351310997786772</v>
       </c>
       <c r="I7" t="n">
-        <v>6.077928169151776</v>
+        <v>5.208050169066006</v>
       </c>
       <c r="J7" t="n">
-        <v>8.20747832426518</v>
+        <v>6.939069790855779</v>
       </c>
       <c r="K7" t="n">
-        <v>6.526782558641611</v>
+        <v>5.346436927166213</v>
       </c>
       <c r="L7" t="n">
-        <v>7.416678671283207</v>
+        <v>7.066027766703098</v>
       </c>
       <c r="M7" t="n">
-        <v>10.28420261150415</v>
+        <v>9.135613719231626</v>
       </c>
       <c r="N7" t="n">
-        <v>7.371022386205438</v>
+        <v>72.47327460659885</v>
       </c>
       <c r="O7" t="n">
-        <v>8.037507084590281</v>
+        <v>7.129991789409327</v>
       </c>
       <c r="P7" t="n">
-        <v>9.883515772525289</v>
+        <v>8.509255941612611</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.559896307193183</v>
+        <v>5.662180242443502</v>
       </c>
       <c r="R7" t="n">
-        <v>5.886411214793282</v>
+        <v>5.499435506193375</v>
       </c>
       <c r="S7" t="n">
-        <v>7.901162143291002</v>
+        <v>6.561341411104507</v>
       </c>
       <c r="T7" t="n">
-        <v>7.216208019216221</v>
+        <v>6.206981057145945</v>
       </c>
       <c r="U7" t="n">
-        <v>8.225994639174642</v>
+        <v>7.526174835888036</v>
       </c>
       <c r="V7" t="n">
-        <v>7.219150570294652</v>
+        <v>6.371793959114944</v>
       </c>
       <c r="W7" t="n">
-        <v>9.931006089157538</v>
+        <v>9.143813017194896</v>
       </c>
       <c r="X7" t="n">
-        <v>8.151737936135477</v>
+        <v>7.234341277845094</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.86021972497514</v>
+        <v>9.770136911197469</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.305766725574037</v>
+        <v>6.392666223710803</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.114345173987624</v>
+        <v>6.103353935632557</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.580267861400587</v>
+        <v>9.851442191550207</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.845444930273979</v>
+        <v>5.681570041596081</v>
       </c>
       <c r="C8" t="n">
-        <v>6.701681640551943</v>
+        <v>5.761092330973075</v>
       </c>
       <c r="D8" t="n">
-        <v>8.329111840334994</v>
+        <v>7.670918125492311</v>
       </c>
       <c r="E8" t="n">
-        <v>6.791910014949115</v>
+        <v>5.740728154408778</v>
       </c>
       <c r="F8" t="n">
-        <v>6.447361005620422</v>
+        <v>5.641284947962646</v>
       </c>
       <c r="G8" t="n">
-        <v>10.80178732706023</v>
+        <v>8.637696040217282</v>
       </c>
       <c r="H8" t="n">
-        <v>8.754048765033863</v>
+        <v>7.854980839070216</v>
       </c>
       <c r="I8" t="n">
-        <v>7.70438310077474</v>
+        <v>6.711720010349448</v>
       </c>
       <c r="J8" t="n">
-        <v>9.833933255888139</v>
+        <v>8.442739632139221</v>
       </c>
       <c r="K8" t="n">
-        <v>8.153237490264578</v>
+        <v>6.850106768449656</v>
       </c>
       <c r="L8" t="n">
-        <v>9.043133602906178</v>
+        <v>8.569697607986537</v>
       </c>
       <c r="M8" t="n">
-        <v>11.91065754312686</v>
+        <v>10.63928356051739</v>
       </c>
       <c r="N8" t="n">
-        <v>8.08411773352117</v>
+        <v>72.47327460659885</v>
       </c>
       <c r="O8" t="n">
-        <v>9.00160899737037</v>
+        <v>8.017129131452087</v>
       </c>
       <c r="P8" t="n">
-        <v>10.78609173037625</v>
+        <v>9.339123489118469</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.776519331284332</v>
+        <v>5.853545647127707</v>
       </c>
       <c r="R8" t="n">
-        <v>7.512866146416256</v>
+        <v>7.003105347476818</v>
       </c>
       <c r="S8" t="n">
-        <v>9.527617074913975</v>
+        <v>8.065011252387947</v>
       </c>
       <c r="T8" t="n">
-        <v>8.842662950839182</v>
+        <v>7.710650898429419</v>
       </c>
       <c r="U8" t="n">
-        <v>9.2785158054345</v>
+        <v>8.49513509030006</v>
       </c>
       <c r="V8" t="n">
-        <v>8.519163996291667</v>
+        <v>7.57342696109253</v>
       </c>
       <c r="W8" t="n">
-        <v>11.55769258355431</v>
+        <v>10.64769840277129</v>
       </c>
       <c r="X8" t="n">
-        <v>8.47635212579681</v>
+        <v>7.526227379466722</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.65137922046073</v>
+        <v>12.36076768601975</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.732060464552713</v>
+        <v>6.779198022314164</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.740800105610592</v>
+        <v>7.607023776915995</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.43752866206957</v>
+        <v>12.50077485559916</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.20210858574997</v>
+        <v>7.844202432299347</v>
       </c>
       <c r="C9" t="n">
-        <v>9.044666148474043</v>
+        <v>7.902417344358104</v>
       </c>
       <c r="D9" t="n">
-        <v>10.6720963482571</v>
+        <v>9.812243138877363</v>
       </c>
       <c r="E9" t="n">
-        <v>9.493507213714873</v>
+        <v>8.217837098546957</v>
       </c>
       <c r="F9" t="n">
-        <v>7.1003485908793</v>
+        <v>6.229288126259824</v>
       </c>
       <c r="G9" t="n">
-        <v>12.90044932839838</v>
+        <v>10.55159984490016</v>
       </c>
       <c r="H9" t="n">
-        <v>11.09703327295597</v>
+        <v>9.996305852455251</v>
       </c>
       <c r="I9" t="n">
-        <v>10.04736760869684</v>
+        <v>8.853045023734476</v>
       </c>
       <c r="J9" t="n">
-        <v>12.17691776381024</v>
+        <v>10.58406464552425</v>
       </c>
       <c r="K9" t="n">
-        <v>10.49622199818668</v>
+        <v>8.991431781834685</v>
       </c>
       <c r="L9" t="n">
-        <v>11.38611811082828</v>
+        <v>10.71102262137156</v>
       </c>
       <c r="M9" t="n">
-        <v>14.25364205104922</v>
+        <v>12.7806085739001</v>
       </c>
       <c r="N9" t="n">
-        <v>11.34046182575051</v>
+        <v>72.47327460659885</v>
       </c>
       <c r="O9" t="n">
-        <v>12.39289962055963</v>
+        <v>11.13140019949808</v>
       </c>
       <c r="P9" t="n">
-        <v>14.32284480285294</v>
+        <v>12.58817639565523</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.52933605984991</v>
+        <v>9.307175270028678</v>
       </c>
       <c r="R9" t="n">
-        <v>9.855850654338354</v>
+        <v>9.144430360861843</v>
       </c>
       <c r="S9" t="n">
-        <v>11.87060158283608</v>
+        <v>10.20633626577299</v>
       </c>
       <c r="T9" t="n">
-        <v>11.18564745876128</v>
+        <v>9.851975911814435</v>
       </c>
       <c r="U9" t="n">
-        <v>12.20059070739491</v>
+        <v>11.17383857081797</v>
       </c>
       <c r="V9" t="n">
-        <v>12.53250651738466</v>
+        <v>11.25784266605121</v>
       </c>
       <c r="W9" t="n">
-        <v>13.90044552870261</v>
+        <v>12.78880787186337</v>
       </c>
       <c r="X9" t="n">
-        <v>12.12117737568054</v>
+        <v>10.87933613251356</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.82965916452021</v>
+        <v>13.41513176586595</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.57305906543934</v>
+        <v>9.38925579264019</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.08378461353269</v>
+        <v>9.748348790301025</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.54970730094565</v>
+        <v>13.49643704621867</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.55116932215855</v>
+        <v>39.402299847149</v>
       </c>
       <c r="C2" t="n">
-        <v>42.43075787621281</v>
+        <v>42.28684474596508</v>
       </c>
       <c r="D2" t="n">
-        <v>39.53128712652673</v>
+        <v>39.42617232903942</v>
       </c>
       <c r="E2" t="n">
-        <v>39.42625125518245</v>
+        <v>39.29138089092763</v>
       </c>
       <c r="F2" t="n">
-        <v>39.58787257764134</v>
+        <v>39.4655521286383</v>
       </c>
       <c r="G2" t="n">
-        <v>39.75269807471044</v>
+        <v>39.53549423107177</v>
       </c>
       <c r="H2" t="n">
-        <v>39.61498358583808</v>
+        <v>39.49145730862973</v>
       </c>
       <c r="I2" t="n">
-        <v>39.60190185692144</v>
+        <v>39.46297730189157</v>
       </c>
       <c r="J2" t="n">
-        <v>39.70016934504865</v>
+        <v>39.54147872806413</v>
       </c>
       <c r="K2" t="n">
-        <v>39.68535783760336</v>
+        <v>39.52047775178141</v>
       </c>
       <c r="L2" t="n">
-        <v>39.67922359995873</v>
+        <v>39.58532508912367</v>
       </c>
       <c r="M2" t="n">
-        <v>39.86384971178415</v>
+        <v>39.71387402801867</v>
       </c>
       <c r="N2" t="n">
-        <v>39.61629221261319</v>
+        <v>39.48768476427374</v>
       </c>
       <c r="O2" t="n">
-        <v>43.62495850344184</v>
+        <v>43.41806553734951</v>
       </c>
       <c r="P2" t="n">
-        <v>39.81935787910052</v>
+        <v>39.64963022905432</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.62009535857244</v>
+        <v>39.48469457574317</v>
       </c>
       <c r="R2" t="n">
-        <v>39.55521311781044</v>
+        <v>39.45743895266394</v>
       </c>
       <c r="S2" t="n">
-        <v>39.72322564010339</v>
+        <v>39.55638604481052</v>
       </c>
       <c r="T2" t="n">
-        <v>39.65819676459633</v>
+        <v>39.52131729496416</v>
       </c>
       <c r="U2" t="n">
-        <v>43.1682663035269</v>
+        <v>43.05025252167518</v>
       </c>
       <c r="V2" t="n">
-        <v>39.62449604503279</v>
+        <v>39.49127146467</v>
       </c>
       <c r="W2" t="n">
-        <v>45.79118644628656</v>
+        <v>45.66318568060088</v>
       </c>
       <c r="X2" t="n">
-        <v>39.74966954506557</v>
+        <v>39.61507622412886</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.93352490983062</v>
+        <v>39.75994225623116</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.7791816155399</v>
+        <v>40.62662872427284</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.67061542956782</v>
+        <v>39.52231334501175</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.81014102105216</v>
+        <v>39.77089343814573</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.5822230821711</v>
+        <v>40.30124512816919</v>
       </c>
       <c r="C3" t="n">
-        <v>44.8571240498696</v>
+        <v>44.71793318064569</v>
       </c>
       <c r="D3" t="n">
-        <v>40.44950655511339</v>
+        <v>40.47988096236728</v>
       </c>
       <c r="E3" t="n">
-        <v>39.69672993112596</v>
+        <v>39.51501993812769</v>
       </c>
       <c r="F3" t="n">
-        <v>40.85659501484559</v>
+        <v>40.7641907599165</v>
       </c>
       <c r="G3" t="n">
-        <v>42.01185205618046</v>
+        <v>41.24597166631295</v>
       </c>
       <c r="H3" t="n">
-        <v>41.05928582903898</v>
+        <v>40.9582811647505</v>
       </c>
       <c r="I3" t="n">
-        <v>40.95821766083093</v>
+        <v>40.74703925526349</v>
       </c>
       <c r="J3" t="n">
-        <v>41.64716176518153</v>
+        <v>41.29641051968193</v>
       </c>
       <c r="K3" t="n">
-        <v>41.53929934674007</v>
+        <v>41.14419714785204</v>
       </c>
       <c r="L3" t="n">
-        <v>41.4981727962768</v>
+        <v>41.60804604227712</v>
       </c>
       <c r="M3" t="n">
-        <v>42.82246766158296</v>
+        <v>42.53176198817277</v>
       </c>
       <c r="N3" t="n">
-        <v>41.05912685884305</v>
+        <v>40.92180345759621</v>
       </c>
       <c r="O3" t="n">
-        <v>47.78407740531494</v>
+        <v>47.51320536996576</v>
       </c>
       <c r="P3" t="n">
-        <v>42.48460025668007</v>
+        <v>42.05568971529614</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.08049865903088</v>
+        <v>40.89482327658003</v>
       </c>
       <c r="R3" t="n">
-        <v>40.62778121384375</v>
+        <v>40.71139875658389</v>
       </c>
       <c r="S3" t="n">
-        <v>41.80707490881449</v>
+        <v>41.39817085342352</v>
       </c>
       <c r="T3" t="n">
-        <v>41.36267734720845</v>
+        <v>41.16607100481946</v>
       </c>
       <c r="U3" t="n">
-        <v>47.41737746166492</v>
+        <v>47.38021251318573</v>
       </c>
       <c r="V3" t="n">
-        <v>41.09970158398836</v>
+        <v>40.92989612387462</v>
       </c>
       <c r="W3" t="n">
-        <v>52.54985921731285</v>
+        <v>52.44283611820787</v>
       </c>
       <c r="X3" t="n">
-        <v>42.00760416207025</v>
+        <v>41.82760056191835</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.32387751521102</v>
+        <v>42.86529197923265</v>
       </c>
       <c r="Z3" t="n">
-        <v>42.68647310280201</v>
+        <v>42.47594924501569</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.44504503996515</v>
+        <v>41.16710224143095</v>
       </c>
       <c r="AB3" t="n">
-        <v>42.44683482887154</v>
+        <v>42.94003094605219</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.908881428121434</v>
+        <v>3.930747573369445</v>
       </c>
       <c r="C4" t="n">
-        <v>3.905124512575779</v>
+        <v>3.204394642325339</v>
       </c>
       <c r="D4" t="n">
-        <v>4.684302882198168</v>
+        <v>4.200398238205871</v>
       </c>
       <c r="E4" t="n">
-        <v>3.497874396476591</v>
+        <v>2.677866937608297</v>
       </c>
       <c r="F4" t="n">
-        <v>5.323461583131252</v>
+        <v>4.645211190278198</v>
       </c>
       <c r="G4" t="n">
-        <v>7.185241396001478</v>
+        <v>5.435239412220853</v>
       </c>
       <c r="H4" t="n">
-        <v>5.629692892393518</v>
+        <v>4.937822115253064</v>
       </c>
       <c r="I4" t="n">
-        <v>5.481928746387342</v>
+        <v>4.616127337695107</v>
       </c>
       <c r="J4" t="n">
-        <v>6.592293479170472</v>
+        <v>5.503575795815068</v>
       </c>
       <c r="K4" t="n">
-        <v>6.424602439837448</v>
+        <v>5.265621370714713</v>
       </c>
       <c r="L4" t="n">
-        <v>6.355313403752726</v>
+        <v>5.998101877244233</v>
       </c>
       <c r="M4" t="n">
-        <v>8.432144432076075</v>
+        <v>7.440231396765194</v>
       </c>
       <c r="N4" t="n">
-        <v>5.644474433816235</v>
+        <v>64.43378084464523</v>
       </c>
       <c r="O4" t="n">
-        <v>5.902772749089438</v>
+        <v>5.144031728307157</v>
       </c>
       <c r="P4" t="n">
-        <v>7.93819455161263</v>
+        <v>6.724458014586252</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.687432716959751</v>
+        <v>4.861433936288478</v>
       </c>
       <c r="R4" t="n">
-        <v>4.954557960247466</v>
+        <v>4.553569135402076</v>
       </c>
       <c r="S4" t="n">
-        <v>6.852336689124948</v>
+        <v>5.671222059109096</v>
       </c>
       <c r="T4" t="n">
-        <v>6.117805625512105</v>
+        <v>5.275104397172402</v>
       </c>
       <c r="U4" t="n">
-        <v>6.671590264895596</v>
+        <v>6.082722699711867</v>
       </c>
       <c r="V4" t="n">
-        <v>5.739482595945782</v>
+        <v>4.940410224956171</v>
       </c>
       <c r="W4" t="n">
-        <v>8.320826982752314</v>
+        <v>7.631763321457398</v>
       </c>
       <c r="X4" t="n">
-        <v>7.151032760470227</v>
+        <v>6.334154633326357</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.206008395569516</v>
+        <v>7.93837764809187</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.082019077658915</v>
+        <v>4.261965478384359</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.258080159233048</v>
+        <v>5.286355240665872</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.814968749032301</v>
+        <v>8.056251124908069</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46.85342314777831</v>
+        <v>41.59129830237004</v>
       </c>
       <c r="C5" t="n">
-        <v>33.00738281984992</v>
+        <v>32.16568100909707</v>
       </c>
       <c r="D5" t="n">
-        <v>47.64059801691015</v>
+        <v>50.63936213967539</v>
       </c>
       <c r="E5" t="n">
-        <v>25.03441544797996</v>
+        <v>22.23507786872351</v>
       </c>
       <c r="F5" t="n">
-        <v>60.62177328492977</v>
+        <v>60.19302235405964</v>
       </c>
       <c r="G5" t="n">
-        <v>82.61031081006145</v>
+        <v>65.14919456733892</v>
       </c>
       <c r="H5" t="n">
-        <v>70.80471206960985</v>
+        <v>70.13798840306715</v>
       </c>
       <c r="I5" t="n">
-        <v>64.19926228258871</v>
+        <v>60.3135357147242</v>
       </c>
       <c r="J5" t="n">
-        <v>77.40757712602141</v>
+        <v>70.34993495718466</v>
       </c>
       <c r="K5" t="n">
-        <v>73.3329686279844</v>
+        <v>64.94703320071307</v>
       </c>
       <c r="L5" t="n">
-        <v>73.4827472156969</v>
+        <v>78.4360425080349</v>
       </c>
       <c r="M5" t="n">
-        <v>116.0630057734272</v>
+        <v>109.9689854470565</v>
       </c>
       <c r="N5" t="n">
-        <v>76.20402381635041</v>
+        <v>64.43378084464523</v>
       </c>
       <c r="O5" t="n">
-        <v>61.61922948273353</v>
+        <v>59.88610886641754</v>
       </c>
       <c r="P5" t="n">
-        <v>94.36967050829188</v>
+        <v>85.42415542791959</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.91256921487511</v>
+        <v>60.91410622992888</v>
       </c>
       <c r="R5" t="n">
-        <v>56.31427226494922</v>
+        <v>61.2214174888584</v>
       </c>
       <c r="S5" t="n">
-        <v>79.60838040355601</v>
+        <v>70.92594642637465</v>
       </c>
       <c r="T5" t="n">
-        <v>76.83470050976216</v>
+        <v>73.34519813266147</v>
       </c>
       <c r="U5" t="n">
-        <v>77.25289493499766</v>
+        <v>78.42634863372024</v>
       </c>
       <c r="V5" t="n">
-        <v>58.46914647366135</v>
+        <v>56.08308095878163</v>
       </c>
       <c r="W5" t="n">
-        <v>112.4409806183878</v>
+        <v>111.8260152093259</v>
       </c>
       <c r="X5" t="n">
-        <v>91.00521677933935</v>
+        <v>88.12085034749744</v>
       </c>
       <c r="Y5" t="n">
-        <v>129.854365326311</v>
+        <v>119.0184858133738</v>
       </c>
       <c r="Z5" t="n">
-        <v>46.33755602986308</v>
+        <v>43.74303094989111</v>
       </c>
       <c r="AA5" t="n">
-        <v>76.0690415086507</v>
+        <v>70.39461404088425</v>
       </c>
       <c r="AB5" t="n">
-        <v>112.0913311035705</v>
+        <v>129.4428369150716</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>138.4378398939894</v>
+        <v>115.2459428385959</v>
       </c>
       <c r="C6" t="n">
-        <v>115.2350651311596</v>
+        <v>114.5195899075518</v>
       </c>
       <c r="D6" t="n">
-        <v>116.0142435007818</v>
+        <v>137.6284709290134</v>
       </c>
       <c r="E6" t="n">
-        <v>137.0268328623446</v>
+        <v>136.1059396284157</v>
       </c>
       <c r="F6" t="n">
-        <v>116.6534022017149</v>
+        <v>115.9604064555047</v>
       </c>
       <c r="G6" t="n">
-        <v>140.7141998618694</v>
+        <v>116.7504346774474</v>
       </c>
       <c r="H6" t="n">
-        <v>116.9596335109772</v>
+        <v>138.3658948060603</v>
       </c>
       <c r="I6" t="n">
-        <v>116.811869364971</v>
+        <v>115.9313226029218</v>
       </c>
       <c r="J6" t="n">
-        <v>140.1212519450384</v>
+        <v>138.9316484866223</v>
       </c>
       <c r="K6" t="n">
-        <v>139.9535609057054</v>
+        <v>138.6936940615221</v>
       </c>
       <c r="L6" t="n">
-        <v>139.8842718696208</v>
+        <v>117.3132971424709</v>
       </c>
       <c r="M6" t="n">
-        <v>119.7620850506598</v>
+        <v>118.7554266619916</v>
       </c>
       <c r="N6" t="n">
-        <v>116.9882118780725</v>
+        <v>64.43378084464523</v>
       </c>
       <c r="O6" t="n">
-        <v>139.4984921617417</v>
+        <v>116.4740280460592</v>
       </c>
       <c r="P6" t="n">
-        <v>112.8362687667971</v>
+        <v>140.2126421602463</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.2163911828277</v>
+        <v>138.2895066270958</v>
       </c>
       <c r="R6" t="n">
-        <v>138.4835164261153</v>
+        <v>137.9816418262093</v>
       </c>
       <c r="S6" t="n">
-        <v>140.3812951549929</v>
+        <v>116.9864173243354</v>
       </c>
       <c r="T6" t="n">
-        <v>139.6467640913801</v>
+        <v>138.7031770879799</v>
       </c>
       <c r="U6" t="n">
-        <v>118.0232861710479</v>
+        <v>139.5429008500159</v>
       </c>
       <c r="V6" t="n">
-        <v>117.0694232145294</v>
+        <v>116.2556054901827</v>
       </c>
       <c r="W6" t="n">
-        <v>141.9165939528989</v>
+        <v>124.6474803346835</v>
       </c>
       <c r="X6" t="n">
-        <v>118.4809733790539</v>
+        <v>117.6493498985528</v>
       </c>
       <c r="Y6" t="n">
-        <v>125.4549995899929</v>
+        <v>124.1834837702463</v>
       </c>
       <c r="Z6" t="n">
-        <v>138.6109775435268</v>
+        <v>115.5771607436109</v>
       </c>
       <c r="AA6" t="n">
-        <v>139.7870386251011</v>
+        <v>138.7144279314734</v>
       </c>
       <c r="AB6" t="n">
-        <v>119.1688620537379</v>
+        <v>119.4025757292696</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.951033477717178</v>
+        <v>4.9365805659043</v>
       </c>
       <c r="C7" t="n">
-        <v>4.947276562171521</v>
+        <v>4.210227634860185</v>
       </c>
       <c r="D7" t="n">
-        <v>5.726454931793911</v>
+        <v>5.206231230740717</v>
       </c>
       <c r="E7" t="n">
-        <v>4.540026446072333</v>
+        <v>3.683699930143151</v>
       </c>
       <c r="F7" t="n">
-        <v>6.365613632726999</v>
+        <v>5.651044182813046</v>
       </c>
       <c r="G7" t="n">
-        <v>8.227393445597224</v>
+        <v>6.441072404755707</v>
       </c>
       <c r="H7" t="n">
-        <v>6.671844941989257</v>
+        <v>5.943655107787913</v>
       </c>
       <c r="I7" t="n">
-        <v>6.524080795983087</v>
+        <v>5.62196033022995</v>
       </c>
       <c r="J7" t="n">
-        <v>7.634445528766215</v>
+        <v>6.509408788349919</v>
       </c>
       <c r="K7" t="n">
-        <v>7.46675448943319</v>
+        <v>6.271454363249569</v>
       </c>
       <c r="L7" t="n">
-        <v>7.397465453348472</v>
+        <v>7.003934869779075</v>
       </c>
       <c r="M7" t="n">
-        <v>9.474296481671821</v>
+        <v>8.446064389300041</v>
       </c>
       <c r="N7" t="n">
-        <v>6.686626483411975</v>
+        <v>64.43378084464523</v>
       </c>
       <c r="O7" t="n">
-        <v>6.944923404402116</v>
+        <v>6.149861281732564</v>
       </c>
       <c r="P7" t="n">
-        <v>8.980345206925323</v>
+        <v>7.730287568011649</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.729584766555494</v>
+        <v>5.86726692882333</v>
       </c>
       <c r="R7" t="n">
-        <v>5.996710009843209</v>
+        <v>5.559402127936923</v>
       </c>
       <c r="S7" t="n">
-        <v>7.894488738720691</v>
+        <v>6.677055051643945</v>
       </c>
       <c r="T7" t="n">
-        <v>7.159957675107845</v>
+        <v>6.280937389707258</v>
       </c>
       <c r="U7" t="n">
-        <v>7.721822846118717</v>
+        <v>7.112648820737459</v>
       </c>
       <c r="V7" t="n">
-        <v>6.781634645541519</v>
+        <v>5.946243217491022</v>
       </c>
       <c r="W7" t="n">
-        <v>9.362979032348058</v>
+        <v>8.637596313992255</v>
       </c>
       <c r="X7" t="n">
-        <v>8.193184810065963</v>
+        <v>7.339987625861196</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.26991573273376</v>
+        <v>8.97631610012345</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.124171127254654</v>
+        <v>5.267798470919209</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.300232208828787</v>
+        <v>6.292188233200727</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.857120798628044</v>
+        <v>9.062084117442932</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.366536651011295</v>
+        <v>5.308581705033971</v>
       </c>
       <c r="C8" t="n">
-        <v>6.477694738397123</v>
+        <v>5.615070040427171</v>
       </c>
       <c r="D8" t="n">
-        <v>7.256873108019517</v>
+        <v>6.611073636307712</v>
       </c>
       <c r="E8" t="n">
-        <v>5.476785271544111</v>
+        <v>4.538584828510301</v>
       </c>
       <c r="F8" t="n">
-        <v>6.954807532985662</v>
+        <v>6.183949920031103</v>
       </c>
       <c r="G8" t="n">
-        <v>9.988996510534667</v>
+        <v>8.060081175153627</v>
       </c>
       <c r="H8" t="n">
-        <v>8.20226311821486</v>
+        <v>7.348497513354915</v>
       </c>
       <c r="I8" t="n">
-        <v>8.054498972208689</v>
+        <v>7.02680273579694</v>
       </c>
       <c r="J8" t="n">
-        <v>9.164863704991815</v>
+        <v>7.914251193916919</v>
       </c>
       <c r="K8" t="n">
-        <v>8.997172665658795</v>
+        <v>7.676296768816547</v>
       </c>
       <c r="L8" t="n">
-        <v>8.927883629574074</v>
+        <v>8.408777275346067</v>
       </c>
       <c r="M8" t="n">
-        <v>11.00471465789699</v>
+        <v>9.850906794869823</v>
       </c>
       <c r="N8" t="n">
-        <v>7.352799010687123</v>
+        <v>64.43378084464523</v>
       </c>
       <c r="O8" t="n">
-        <v>7.848599533466212</v>
+        <v>6.974100992485423</v>
       </c>
       <c r="P8" t="n">
-        <v>9.825803806169795</v>
+        <v>8.500595394147396</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.925981695581441</v>
+        <v>6.036291186003554</v>
       </c>
       <c r="R8" t="n">
-        <v>7.527128186068814</v>
+        <v>6.964244533503911</v>
       </c>
       <c r="S8" t="n">
-        <v>9.4249069149463</v>
+        <v>8.081897457210939</v>
       </c>
       <c r="T8" t="n">
-        <v>8.690375851333451</v>
+        <v>7.685779795274263</v>
       </c>
       <c r="U8" t="n">
-        <v>8.71114412524647</v>
+        <v>8.015180824938087</v>
       </c>
       <c r="V8" t="n">
-        <v>7.995642088478673</v>
+        <v>7.061948728286136</v>
       </c>
       <c r="W8" t="n">
-        <v>10.89361631949784</v>
+        <v>10.04264170114479</v>
       </c>
       <c r="X8" t="n">
-        <v>8.491765913360236</v>
+        <v>7.60367383658698</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.8907409566832</v>
+        <v>11.39747121888713</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.518964182137343</v>
+        <v>5.620614053379152</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.83065038505439</v>
+        <v>7.697030638767729</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.55216092137846</v>
+        <v>11.54581558935894</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.333701108453983</v>
+        <v>7.128513639403406</v>
       </c>
       <c r="C9" t="n">
-        <v>8.359244102637659</v>
+        <v>7.355019958714097</v>
       </c>
       <c r="D9" t="n">
-        <v>9.138422472260041</v>
+        <v>8.351023554594631</v>
       </c>
       <c r="E9" t="n">
-        <v>7.714435864747705</v>
+        <v>6.608576226095277</v>
       </c>
       <c r="F9" t="n">
-        <v>7.404763790781602</v>
+        <v>6.599235873893186</v>
       </c>
       <c r="G9" t="n">
-        <v>11.63936111468572</v>
+        <v>9.585864729178946</v>
       </c>
       <c r="H9" t="n">
-        <v>10.08381248245539</v>
+        <v>9.088447431641839</v>
       </c>
       <c r="I9" t="n">
-        <v>9.936048336449209</v>
+        <v>8.766752654083863</v>
       </c>
       <c r="J9" t="n">
-        <v>11.04641306923235</v>
+        <v>9.654201112203834</v>
       </c>
       <c r="K9" t="n">
-        <v>10.87872202989931</v>
+        <v>9.41624668710347</v>
       </c>
       <c r="L9" t="n">
-        <v>10.8094329938146</v>
+        <v>10.14872719363301</v>
       </c>
       <c r="M9" t="n">
-        <v>12.88626402213795</v>
+        <v>11.59085671315397</v>
       </c>
       <c r="N9" t="n">
-        <v>10.09859402387811</v>
+        <v>64.43378084464523</v>
       </c>
       <c r="O9" t="n">
-        <v>10.69800115273011</v>
+        <v>9.610433353358879</v>
       </c>
       <c r="P9" t="n">
-        <v>12.80760824179191</v>
+        <v>11.25953556883929</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.141552435644</v>
+        <v>9.012059253246582</v>
       </c>
       <c r="R9" t="n">
-        <v>9.408677550309335</v>
+        <v>8.704194451790823</v>
       </c>
       <c r="S9" t="n">
-        <v>11.30645627918682</v>
+        <v>9.821847375497851</v>
       </c>
       <c r="T9" t="n">
-        <v>10.57192521557398</v>
+        <v>9.425729713561179</v>
       </c>
       <c r="U9" t="n">
-        <v>11.14746514252598</v>
+        <v>10.26545347559735</v>
       </c>
       <c r="V9" t="n">
-        <v>11.38139098678458</v>
+        <v>10.19061334638346</v>
       </c>
       <c r="W9" t="n">
-        <v>12.77494657281419</v>
+        <v>11.78238863784616</v>
       </c>
       <c r="X9" t="n">
-        <v>11.6051523505321</v>
+        <v>10.48477994971513</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.68188327319989</v>
+        <v>12.12110842397734</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.915562402147739</v>
+        <v>7.838101398585822</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.71219974929492</v>
+        <v>9.436980557054589</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.26908833909418</v>
+        <v>12.20687644129683</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.18428935884818</v>
+        <v>39.11736658890637</v>
       </c>
       <c r="C2" t="n">
-        <v>42.11067217972031</v>
+        <v>42.02797194376195</v>
       </c>
       <c r="D2" t="n">
-        <v>39.2230456278509</v>
+        <v>39.1608036036755</v>
       </c>
       <c r="E2" t="n">
-        <v>39.28580122762036</v>
+        <v>39.21948685685311</v>
       </c>
       <c r="F2" t="n">
-        <v>39.19987902857061</v>
+        <v>39.13020642708545</v>
       </c>
       <c r="G2" t="n">
-        <v>39.37446243682649</v>
+        <v>39.28102999772727</v>
       </c>
       <c r="H2" t="n">
-        <v>39.32727036990335</v>
+        <v>39.26314347483206</v>
       </c>
       <c r="I2" t="n">
-        <v>39.22699230665016</v>
+        <v>39.17361499248705</v>
       </c>
       <c r="J2" t="n">
-        <v>39.39689074180662</v>
+        <v>39.32285351237701</v>
       </c>
       <c r="K2" t="n">
-        <v>39.29773907873348</v>
+        <v>39.235289834655</v>
       </c>
       <c r="L2" t="n">
-        <v>39.33416971523593</v>
+        <v>39.28028845189268</v>
       </c>
       <c r="M2" t="n">
-        <v>39.43879060460084</v>
+        <v>39.36596206362762</v>
       </c>
       <c r="N2" t="n">
-        <v>39.47612306361044</v>
+        <v>39.41180800365764</v>
       </c>
       <c r="O2" t="n">
-        <v>43.47489660471769</v>
+        <v>43.34806907907063</v>
       </c>
       <c r="P2" t="n">
-        <v>39.62282653277428</v>
+        <v>39.55076069222365</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.32152504135554</v>
+        <v>39.25629382556941</v>
       </c>
       <c r="R2" t="n">
-        <v>39.23324489577472</v>
+        <v>39.18348549480662</v>
       </c>
       <c r="S2" t="n">
-        <v>39.31595280438703</v>
+        <v>39.23772672031196</v>
       </c>
       <c r="T2" t="n">
-        <v>39.3579967768711</v>
+        <v>39.29886347308049</v>
       </c>
       <c r="U2" t="n">
-        <v>42.96143257781124</v>
+        <v>42.93372024172582</v>
       </c>
       <c r="V2" t="n">
-        <v>39.40468589340645</v>
+        <v>39.34021300478311</v>
       </c>
       <c r="W2" t="n">
-        <v>45.76828661384928</v>
+        <v>45.73909729389908</v>
       </c>
       <c r="X2" t="n">
-        <v>39.3434546665473</v>
+        <v>39.27876989296981</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.68166985031174</v>
+        <v>39.61701814569647</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.63564754479187</v>
+        <v>40.54740950882406</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.33900175919523</v>
+        <v>39.28214032850569</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.51112839294409</v>
+        <v>39.47046598589613</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.17579494363216</v>
+        <v>39.09851126817938</v>
       </c>
       <c r="C3" t="n">
-        <v>43.82058047715417</v>
+        <v>43.73385497219596</v>
       </c>
       <c r="D3" t="n">
-        <v>39.45631807161678</v>
+        <v>39.41234968690484</v>
       </c>
       <c r="E3" t="n">
-        <v>39.902071836312</v>
+        <v>39.82904093019614</v>
       </c>
       <c r="F3" t="n">
-        <v>39.29061120712934</v>
+        <v>39.19350034175886</v>
       </c>
       <c r="G3" t="n">
-        <v>40.52142186608597</v>
+        <v>40.25646173507602</v>
       </c>
       <c r="H3" t="n">
-        <v>40.20612971455659</v>
+        <v>40.14866627241047</v>
       </c>
       <c r="I3" t="n">
-        <v>39.48522363255683</v>
+        <v>39.50471976634628</v>
       </c>
       <c r="J3" t="n">
-        <v>40.68679193706646</v>
+        <v>40.55917616614581</v>
       </c>
       <c r="K3" t="n">
-        <v>39.98431832124754</v>
+        <v>39.93877108411315</v>
       </c>
       <c r="L3" t="n">
-        <v>40.23813893362328</v>
+        <v>40.25329726222846</v>
       </c>
       <c r="M3" t="n">
-        <v>40.99468606358708</v>
+        <v>40.87504495995085</v>
       </c>
       <c r="N3" t="n">
-        <v>41.25967458473046</v>
+        <v>41.20089366479755</v>
       </c>
       <c r="O3" t="n">
-        <v>47.95746887826532</v>
+        <v>47.79578674571333</v>
       </c>
       <c r="P3" t="n">
-        <v>42.29419639823596</v>
+        <v>42.18033331979595</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.15581996594847</v>
+        <v>40.0905024685784</v>
       </c>
       <c r="R3" t="n">
-        <v>39.53118093370376</v>
+        <v>39.57673413638651</v>
       </c>
       <c r="S3" t="n">
-        <v>40.10467573837732</v>
+        <v>39.94756562308105</v>
       </c>
       <c r="T3" t="n">
-        <v>40.41793166182626</v>
+        <v>40.39609659291508</v>
       </c>
       <c r="U3" t="n">
-        <v>47.07717340577697</v>
+        <v>47.13309323991088</v>
       </c>
       <c r="V3" t="n">
-        <v>40.73952621563056</v>
+        <v>40.67962323046163</v>
       </c>
       <c r="W3" t="n">
-        <v>53.49401191863946</v>
+        <v>53.5010306029148</v>
       </c>
       <c r="X3" t="n">
-        <v>40.31623096302911</v>
+        <v>40.25479894124494</v>
       </c>
       <c r="Y3" t="n">
-        <v>42.72596232396103</v>
+        <v>42.66477735407192</v>
       </c>
       <c r="Z3" t="n">
-        <v>42.65128754865604</v>
+        <v>42.55096646972071</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.28236775632566</v>
+        <v>40.27679357414519</v>
       </c>
       <c r="AB3" t="n">
-        <v>41.51148110694145</v>
+        <v>41.61910138895006</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.622885273735148</v>
+        <v>2.137486654210915</v>
       </c>
       <c r="C4" t="n">
-        <v>2.231487405948784</v>
+        <v>1.780623843169178</v>
       </c>
       <c r="D4" t="n">
-        <v>3.060655160885275</v>
+        <v>2.628127718041996</v>
       </c>
       <c r="E4" t="n">
-        <v>3.769508529283285</v>
+        <v>3.290982058313427</v>
       </c>
       <c r="F4" t="n">
-        <v>2.798977764852082</v>
+        <v>2.282518533060522</v>
       </c>
       <c r="G4" t="n">
-        <v>4.770977673438043</v>
+        <v>3.98614014573068</v>
       </c>
       <c r="H4" t="n">
-        <v>4.237921568117756</v>
+        <v>3.784103641422236</v>
       </c>
       <c r="I4" t="n">
-        <v>3.105234713485113</v>
+        <v>2.772838248198469</v>
       </c>
       <c r="J4" t="n">
-        <v>5.025454513683464</v>
+        <v>4.459836548051166</v>
       </c>
       <c r="K4" t="n">
-        <v>3.904352049289397</v>
+        <v>3.469483962314976</v>
       </c>
       <c r="L4" t="n">
-        <v>4.315852847504843</v>
+        <v>3.977764044400845</v>
       </c>
       <c r="M4" t="n">
-        <v>5.506668469557567</v>
+        <v>4.95421388959941</v>
       </c>
       <c r="N4" t="n">
-        <v>5.919281219161554</v>
+        <v>77.8704513900648</v>
       </c>
       <c r="O4" t="n">
-        <v>6.152745714155576</v>
+        <v>5.697376256515186</v>
       </c>
       <c r="P4" t="n">
-        <v>7.576364390297489</v>
+        <v>7.032872422317194</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.173025439188516</v>
+        <v>3.706733702006168</v>
       </c>
       <c r="R4" t="n">
-        <v>3.175860583980136</v>
+        <v>2.884330112553215</v>
       </c>
       <c r="S4" t="n">
-        <v>4.110084459273415</v>
+        <v>3.497009706833172</v>
       </c>
       <c r="T4" t="n">
-        <v>4.584990469664277</v>
+        <v>4.187577453649173</v>
       </c>
       <c r="U4" t="n">
-        <v>6.065473812257299</v>
+        <v>5.710551923315727</v>
       </c>
       <c r="V4" t="n">
-        <v>5.119768461504913</v>
+        <v>4.662983138289819</v>
       </c>
       <c r="W4" t="n">
-        <v>9.719192398537981</v>
+        <v>9.279321442946616</v>
       </c>
       <c r="X4" t="n">
-        <v>4.420730643855429</v>
+        <v>3.960611222795122</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.241642754259628</v>
+        <v>7.770740791669954</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.865024908868838</v>
+        <v>4.404801143124926</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.370433006875511</v>
+        <v>3.998681842650484</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.298995271585133</v>
+        <v>6.10487535780852</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.58503908685091</v>
+        <v>14.46315729707665</v>
       </c>
       <c r="C5" t="n">
-        <v>9.619013544519589</v>
+        <v>9.079443809083482</v>
       </c>
       <c r="D5" t="n">
-        <v>26.0411902307263</v>
+        <v>25.8681453043075</v>
       </c>
       <c r="E5" t="n">
-        <v>38.25613668992637</v>
+        <v>37.21446953508685</v>
       </c>
       <c r="F5" t="n">
-        <v>20.89003940679322</v>
+        <v>19.06879900669963</v>
       </c>
       <c r="G5" t="n">
-        <v>49.72300619029629</v>
+        <v>43.78714658443634</v>
       </c>
       <c r="H5" t="n">
-        <v>51.612419101363</v>
+        <v>51.01310147078894</v>
       </c>
       <c r="I5" t="n">
-        <v>27.29449068908505</v>
+        <v>29.12407518216418</v>
       </c>
       <c r="J5" t="n">
-        <v>57.46080876755175</v>
+        <v>55.06662753162171</v>
       </c>
       <c r="K5" t="n">
-        <v>39.16256346053849</v>
+        <v>38.88969466038919</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50245832494169</v>
+        <v>44.81225111692601</v>
       </c>
       <c r="M5" t="n">
-        <v>68.76136433427685</v>
+        <v>66.36113379817192</v>
       </c>
       <c r="N5" t="n">
-        <v>77.58574341552196</v>
+        <v>77.8704513900648</v>
       </c>
       <c r="O5" t="n">
-        <v>73.83897369452239</v>
+        <v>73.22910656333866</v>
       </c>
       <c r="P5" t="n">
-        <v>102.8713233508487</v>
+        <v>100.7216206812503</v>
       </c>
       <c r="Q5" t="n">
-        <v>45.21034347712395</v>
+        <v>44.39048686592097</v>
       </c>
       <c r="R5" t="n">
-        <v>29.37081778201476</v>
+        <v>32.10425667764091</v>
       </c>
       <c r="S5" t="n">
-        <v>37.6940882269982</v>
+        <v>34.62855449390882</v>
       </c>
       <c r="T5" t="n">
-        <v>54.00698700841747</v>
+        <v>54.46797435564463</v>
       </c>
       <c r="U5" t="n">
-        <v>77.73131998550427</v>
+        <v>79.1129138600414</v>
       </c>
       <c r="V5" t="n">
-        <v>57.51900950121725</v>
+        <v>56.86332771979509</v>
       </c>
       <c r="W5" t="n">
-        <v>151.6222898607922</v>
+        <v>151.3072684032783</v>
       </c>
       <c r="X5" t="n">
-        <v>52.06190521791065</v>
+        <v>51.35068456921951</v>
       </c>
       <c r="Y5" t="n">
-        <v>122.0003103866014</v>
+        <v>121.3022906786877</v>
       </c>
       <c r="Z5" t="n">
-        <v>52.81859288136538</v>
+        <v>52.12797686575188</v>
       </c>
       <c r="AA5" t="n">
-        <v>49.95264799383916</v>
+        <v>50.92466107485146</v>
       </c>
       <c r="AB5" t="n">
-        <v>91.51217370702426</v>
+        <v>96.11245607556023</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>122.0937777272173</v>
+        <v>121.5961304938028</v>
       </c>
       <c r="C6" t="n">
-        <v>145.3852007234095</v>
+        <v>121.2392676827611</v>
       </c>
       <c r="D6" t="n">
-        <v>122.5315476143673</v>
+        <v>145.7195658738991</v>
       </c>
       <c r="E6" t="n">
-        <v>123.2404009827654</v>
+        <v>146.3824202141705</v>
       </c>
       <c r="F6" t="n">
-        <v>145.9526910823127</v>
+        <v>121.7411623726524</v>
       </c>
       <c r="G6" t="n">
-        <v>147.9246909908986</v>
+        <v>123.4447839853226</v>
       </c>
       <c r="H6" t="n">
-        <v>123.7088140216</v>
+        <v>146.8755417972793</v>
       </c>
       <c r="I6" t="n">
-        <v>122.5761271669672</v>
+        <v>145.8642764040556</v>
       </c>
       <c r="J6" t="n">
-        <v>124.4963469671656</v>
+        <v>123.918480387643</v>
       </c>
       <c r="K6" t="n">
-        <v>123.3752445027715</v>
+        <v>146.5609221181722</v>
       </c>
       <c r="L6" t="n">
-        <v>123.786745300987</v>
+        <v>123.4364078839927</v>
       </c>
       <c r="M6" t="n">
-        <v>148.6603817870182</v>
+        <v>148.0456520454565</v>
       </c>
       <c r="N6" t="n">
-        <v>125.3974748298761</v>
+        <v>77.8704513900648</v>
       </c>
       <c r="O6" t="n">
-        <v>149.3782131115473</v>
+        <v>148.8605749472365</v>
       </c>
       <c r="P6" t="n">
-        <v>120.1396462748172</v>
+        <v>150.1957853888397</v>
       </c>
       <c r="Q6" t="n">
-        <v>147.326738756649</v>
+        <v>146.7981718578633</v>
       </c>
       <c r="R6" t="n">
-        <v>122.6467530374623</v>
+        <v>145.9757682684104</v>
       </c>
       <c r="S6" t="n">
-        <v>123.5809769127556</v>
+        <v>122.9556535464251</v>
       </c>
       <c r="T6" t="n">
-        <v>147.738703787125</v>
+        <v>123.646221293241</v>
       </c>
       <c r="U6" t="n">
-        <v>125.5357502426261</v>
+        <v>125.1797358104647</v>
       </c>
       <c r="V6" t="n">
-        <v>148.2734817789655</v>
+        <v>147.754421294147</v>
       </c>
       <c r="W6" t="n">
-        <v>135.31338191068</v>
+        <v>152.4427039774117</v>
       </c>
       <c r="X6" t="n">
-        <v>123.8916230973376</v>
+        <v>123.4192550623869</v>
       </c>
       <c r="Y6" t="n">
-        <v>132.9617126097449</v>
+        <v>132.4897462443676</v>
       </c>
       <c r="Z6" t="n">
-        <v>148.0187382263294</v>
+        <v>123.8634449827169</v>
       </c>
       <c r="AA6" t="n">
-        <v>147.5241463243361</v>
+        <v>147.0901199985076</v>
       </c>
       <c r="AB6" t="n">
-        <v>125.7850413728566</v>
+        <v>125.5813486657625</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.667376928909054</v>
+        <v>3.156768276269891</v>
       </c>
       <c r="C7" t="n">
-        <v>3.275979061122681</v>
+        <v>2.799905465228166</v>
       </c>
       <c r="D7" t="n">
-        <v>4.105146816059175</v>
+        <v>3.647409340100982</v>
       </c>
       <c r="E7" t="n">
-        <v>4.814000184457182</v>
+        <v>4.310263680372414</v>
       </c>
       <c r="F7" t="n">
-        <v>3.843469420025967</v>
+        <v>3.301800155119517</v>
       </c>
       <c r="G7" t="n">
-        <v>5.815469328611941</v>
+        <v>5.005421767789674</v>
       </c>
       <c r="H7" t="n">
-        <v>5.282413223291649</v>
+        <v>4.803385263481225</v>
       </c>
       <c r="I7" t="n">
-        <v>4.149726368659008</v>
+        <v>3.792119870257456</v>
       </c>
       <c r="J7" t="n">
-        <v>6.069946168857356</v>
+        <v>5.479118170110159</v>
       </c>
       <c r="K7" t="n">
-        <v>4.948843704463291</v>
+        <v>4.488765584373958</v>
       </c>
       <c r="L7" t="n">
-        <v>5.360344502678739</v>
+        <v>4.997045666459836</v>
       </c>
       <c r="M7" t="n">
-        <v>6.551160124731457</v>
+        <v>5.973495511658413</v>
       </c>
       <c r="N7" t="n">
-        <v>6.963772874335449</v>
+        <v>77.8704513900648</v>
       </c>
       <c r="O7" t="n">
-        <v>7.197232513451041</v>
+        <v>6.716652933257324</v>
       </c>
       <c r="P7" t="n">
-        <v>8.620851189592965</v>
+        <v>8.052149099059324</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.217517094362417</v>
+        <v>4.726015324065148</v>
       </c>
       <c r="R7" t="n">
-        <v>4.220352239154034</v>
+        <v>3.903611734612195</v>
       </c>
       <c r="S7" t="n">
-        <v>5.154576114447313</v>
+        <v>4.516291328892168</v>
       </c>
       <c r="T7" t="n">
-        <v>5.629482124838176</v>
+        <v>5.206859075708165</v>
       </c>
       <c r="U7" t="n">
-        <v>7.102923599322109</v>
+        <v>6.735692807551778</v>
       </c>
       <c r="V7" t="n">
-        <v>6.164260116678809</v>
+        <v>5.68226476034882</v>
       </c>
       <c r="W7" t="n">
-        <v>10.76368405371188</v>
+        <v>10.29860306500561</v>
       </c>
       <c r="X7" t="n">
-        <v>5.465222299029325</v>
+        <v>4.979892844854103</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.285518386320222</v>
+        <v>8.800562461285985</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.909516564042738</v>
+        <v>5.42408276518391</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.414924662049412</v>
+        <v>5.017963464709465</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.343486926759006</v>
+        <v>7.124156979867497</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.029028263103317</v>
+        <v>3.49545233503515</v>
       </c>
       <c r="C8" t="n">
-        <v>4.712736585393814</v>
+        <v>4.162096297947442</v>
       </c>
       <c r="D8" t="n">
-        <v>5.5419043403303</v>
+        <v>5.00960017282026</v>
       </c>
       <c r="E8" t="n">
-        <v>5.678295376547164</v>
+        <v>5.127467347831594</v>
       </c>
       <c r="F8" t="n">
-        <v>4.372609733380584</v>
+        <v>3.799934607107208</v>
       </c>
       <c r="G8" t="n">
-        <v>7.475157124909916</v>
+        <v>6.579843397494376</v>
       </c>
       <c r="H8" t="n">
-        <v>6.719170747562786</v>
+        <v>6.165576096200495</v>
       </c>
       <c r="I8" t="n">
-        <v>5.58648389293014</v>
+        <v>5.154310702976735</v>
       </c>
       <c r="J8" t="n">
-        <v>7.50670369312849</v>
+        <v>6.841309002829429</v>
       </c>
       <c r="K8" t="n">
-        <v>6.385601228734419</v>
+        <v>5.850956417093241</v>
       </c>
       <c r="L8" t="n">
-        <v>6.797102026949875</v>
+        <v>6.35923649917912</v>
       </c>
       <c r="M8" t="n">
-        <v>7.987917649001752</v>
+        <v>7.335686344379144</v>
       </c>
       <c r="N8" t="n">
-        <v>7.567143239454971</v>
+        <v>77.8704513900648</v>
       </c>
       <c r="O8" t="n">
-        <v>8.029629760968238</v>
+        <v>7.503489911675901</v>
       </c>
       <c r="P8" t="n">
-        <v>9.397109604568548</v>
+        <v>8.78554161220714</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.367885524625741</v>
+        <v>4.863556941760503</v>
       </c>
       <c r="R8" t="n">
-        <v>5.657109763425167</v>
+        <v>5.265802567331475</v>
       </c>
       <c r="S8" t="n">
-        <v>6.591333638718449</v>
+        <v>5.878482161611436</v>
       </c>
       <c r="T8" t="n">
-        <v>7.066239649109301</v>
+        <v>6.569049908427438</v>
       </c>
       <c r="U8" t="n">
-        <v>8.016385876405725</v>
+        <v>7.599380767682236</v>
       </c>
       <c r="V8" t="n">
-        <v>7.301686404897199</v>
+        <v>6.760718965888589</v>
       </c>
       <c r="W8" t="n">
-        <v>12.20065286523119</v>
+        <v>11.66099504457729</v>
       </c>
       <c r="X8" t="n">
-        <v>5.714126346700644</v>
+        <v>5.211240891166762</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.78271684922955</v>
+        <v>11.17420375227185</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.251197248964061</v>
+        <v>5.743754660284424</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.85168218632054</v>
+        <v>6.380154297428741</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.903282763684359</v>
+        <v>9.555486220784475</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.331140906386927</v>
+        <v>5.730837826007509</v>
       </c>
       <c r="C9" t="n">
-        <v>7.044347316671105</v>
+        <v>6.437666769219256</v>
       </c>
       <c r="D9" t="n">
-        <v>7.8735150716076</v>
+        <v>7.285170644092075</v>
       </c>
       <c r="E9" t="n">
-        <v>8.327430627522933</v>
+        <v>7.702529586045971</v>
       </c>
       <c r="F9" t="n">
-        <v>5.065422746784447</v>
+        <v>4.487461113784883</v>
       </c>
       <c r="G9" t="n">
-        <v>9.583838038262492</v>
+        <v>8.643183487593054</v>
       </c>
       <c r="H9" t="n">
-        <v>9.050781478840083</v>
+        <v>8.441146567472302</v>
       </c>
       <c r="I9" t="n">
-        <v>7.918094624207439</v>
+        <v>7.429881174248553</v>
       </c>
       <c r="J9" t="n">
-        <v>9.838314424405779</v>
+        <v>9.116879474101268</v>
       </c>
       <c r="K9" t="n">
-        <v>8.717211960011717</v>
+        <v>8.126526888365058</v>
       </c>
       <c r="L9" t="n">
-        <v>9.128712758227175</v>
+        <v>8.634806970450922</v>
       </c>
       <c r="M9" t="n">
-        <v>10.31952838027988</v>
+        <v>9.611256815649508</v>
       </c>
       <c r="N9" t="n">
-        <v>10.73214112988388</v>
+        <v>77.8704513900648</v>
       </c>
       <c r="O9" t="n">
-        <v>11.33167064086556</v>
+        <v>10.70692579075126</v>
       </c>
       <c r="P9" t="n">
-        <v>12.83490207860745</v>
+        <v>12.11908600540689</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.985885804012961</v>
+        <v>8.363777043868513</v>
       </c>
       <c r="R9" t="n">
-        <v>7.988720494702465</v>
+        <v>7.541373038603297</v>
       </c>
       <c r="S9" t="n">
-        <v>8.922944369995742</v>
+        <v>8.154052632883259</v>
       </c>
       <c r="T9" t="n">
-        <v>9.397850380386606</v>
+        <v>8.844620379699279</v>
       </c>
       <c r="U9" t="n">
-        <v>10.87771769986633</v>
+        <v>10.37813489692286</v>
       </c>
       <c r="V9" t="n">
-        <v>11.20731787495555</v>
+        <v>10.54750337292384</v>
       </c>
       <c r="W9" t="n">
-        <v>14.53205230926032</v>
+        <v>13.9363643689967</v>
       </c>
       <c r="X9" t="n">
-        <v>9.233590554577761</v>
+        <v>8.617654148845189</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.05388664186864</v>
+        <v>12.43832376527709</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.011906845478435</v>
+        <v>8.420532693635945</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.183292917597843</v>
+        <v>8.655724768700564</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.11185518230747</v>
+        <v>10.76191828385859</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.89562720007466</v>
+        <v>38.84110052853848</v>
       </c>
       <c r="C2" t="n">
-        <v>41.88777994697603</v>
+        <v>41.81414835615186</v>
       </c>
       <c r="D2" t="n">
-        <v>38.91536827063065</v>
+        <v>38.85898391116448</v>
       </c>
       <c r="E2" t="n">
-        <v>38.94245682634143</v>
+        <v>38.88616051505189</v>
       </c>
       <c r="F2" t="n">
-        <v>38.97006941619556</v>
+        <v>38.91485707994927</v>
       </c>
       <c r="G2" t="n">
-        <v>39.07168208130361</v>
+        <v>39.01420647941357</v>
       </c>
       <c r="H2" t="n">
-        <v>39.05009854660324</v>
+        <v>38.99677271586012</v>
       </c>
       <c r="I2" t="n">
-        <v>38.95466883517148</v>
+        <v>38.91026805556009</v>
       </c>
       <c r="J2" t="n">
-        <v>39.05996851413012</v>
+        <v>39.004821729942</v>
       </c>
       <c r="K2" t="n">
-        <v>38.94641334617889</v>
+        <v>38.89475621558115</v>
       </c>
       <c r="L2" t="n">
-        <v>38.91408697639319</v>
+        <v>38.85890656493245</v>
       </c>
       <c r="M2" t="n">
-        <v>39.00561718719268</v>
+        <v>38.95219429021051</v>
       </c>
       <c r="N2" t="n">
-        <v>39.15146670145096</v>
+        <v>39.0971129590377</v>
       </c>
       <c r="O2" t="n">
-        <v>43.03876210519869</v>
+        <v>42.92789744264258</v>
       </c>
       <c r="P2" t="n">
-        <v>39.30755458514144</v>
+        <v>39.25366770777371</v>
       </c>
       <c r="Q2" t="n">
-        <v>38.96955331541702</v>
+        <v>38.91511037566391</v>
       </c>
       <c r="R2" t="n">
-        <v>38.92780611236685</v>
+        <v>38.87234752315268</v>
       </c>
       <c r="S2" t="n">
-        <v>39.0065863235838</v>
+        <v>38.94751390896919</v>
       </c>
       <c r="T2" t="n">
-        <v>39.04039400780258</v>
+        <v>38.99148373762932</v>
       </c>
       <c r="U2" t="n">
-        <v>42.42814202574775</v>
+        <v>42.3804492255433</v>
       </c>
       <c r="V2" t="n">
-        <v>39.08967739445885</v>
+        <v>39.03507686639818</v>
       </c>
       <c r="W2" t="n">
-        <v>45.14168873592195</v>
+        <v>45.09614561926234</v>
       </c>
       <c r="X2" t="n">
-        <v>39.21967913290131</v>
+        <v>39.16568290971051</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.32890419909682</v>
+        <v>39.27489114213399</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.12863726988346</v>
+        <v>40.04127110647178</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.14460104089242</v>
+        <v>39.09113099922038</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.14559980216777</v>
+        <v>39.09162841814024</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.62733251348433</v>
+        <v>38.57529510480502</v>
       </c>
       <c r="C3" t="n">
-        <v>43.73351846947249</v>
+        <v>43.65086226406356</v>
       </c>
       <c r="D3" t="n">
-        <v>38.76873454556972</v>
+        <v>38.70343242155413</v>
       </c>
       <c r="E3" t="n">
-        <v>38.96177029874116</v>
+        <v>38.89708806492249</v>
       </c>
       <c r="F3" t="n">
-        <v>39.15956899963252</v>
+        <v>39.10260324700612</v>
       </c>
       <c r="G3" t="n">
-        <v>39.87203269465704</v>
+        <v>39.79916025186783</v>
       </c>
       <c r="H3" t="n">
-        <v>39.73552803874095</v>
+        <v>39.69204202199644</v>
       </c>
       <c r="I3" t="n">
-        <v>39.05009248889358</v>
+        <v>39.07037350439629</v>
       </c>
       <c r="J3" t="n">
-        <v>39.79371168009627</v>
+        <v>39.73730962192535</v>
       </c>
       <c r="K3" t="n">
-        <v>38.98872369687607</v>
+        <v>38.95705668725853</v>
       </c>
       <c r="L3" t="n">
-        <v>38.75772870277306</v>
+        <v>38.70109405982084</v>
       </c>
       <c r="M3" t="n">
-        <v>39.41591659659809</v>
+        <v>39.37121282504133</v>
       </c>
       <c r="N3" t="n">
-        <v>40.45070480965078</v>
+        <v>40.39988210397265</v>
       </c>
       <c r="O3" t="n">
-        <v>47.15448346016359</v>
+        <v>47.01132543772426</v>
       </c>
       <c r="P3" t="n">
-        <v>41.55350935055395</v>
+        <v>41.50602030039156</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.15202169693153</v>
+        <v>39.10057810009462</v>
       </c>
       <c r="R3" t="n">
-        <v>38.85857953666049</v>
+        <v>38.79982902361593</v>
       </c>
       <c r="S3" t="n">
-        <v>39.41187866329317</v>
+        <v>39.32771038837743</v>
       </c>
       <c r="T3" t="n">
-        <v>39.65958767975933</v>
+        <v>39.6475417940892</v>
       </c>
       <c r="U3" t="n">
-        <v>45.41873041201069</v>
+        <v>45.38426018173618</v>
       </c>
       <c r="V3" t="n">
-        <v>40.00251510550866</v>
+        <v>39.94996343644586</v>
       </c>
       <c r="W3" t="n">
-        <v>51.26058970929781</v>
+        <v>51.2309068044022</v>
       </c>
       <c r="X3" t="n">
-        <v>40.93612196809782</v>
+        <v>40.88784280800522</v>
       </c>
       <c r="Y3" t="n">
-        <v>41.72072174588475</v>
+        <v>41.67232542786633</v>
       </c>
       <c r="Z3" t="n">
-        <v>41.22517503969029</v>
+        <v>41.11589823909303</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.40485856362697</v>
+        <v>40.36033886078661</v>
       </c>
       <c r="AB3" t="n">
-        <v>40.40486403137177</v>
+        <v>40.3563803275218</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.676670834219329</v>
+        <v>1.366664752831685</v>
       </c>
       <c r="C4" t="n">
-        <v>2.018678689634577</v>
+        <v>1.710632284997022</v>
       </c>
       <c r="D4" t="n">
-        <v>1.899655307490386</v>
+        <v>1.568665786354967</v>
       </c>
       <c r="E4" t="n">
-        <v>2.205633005595028</v>
+        <v>1.875638029118912</v>
       </c>
       <c r="F4" t="n">
-        <v>2.517529910415955</v>
+        <v>2.199778930706811</v>
       </c>
       <c r="G4" t="n">
-        <v>3.66529170694681</v>
+        <v>3.321976100637877</v>
       </c>
       <c r="H4" t="n">
-        <v>3.421495753589807</v>
+        <v>3.125053721373798</v>
       </c>
       <c r="I4" t="n">
-        <v>2.343573263131646</v>
+        <v>2.147943789175236</v>
       </c>
       <c r="J4" t="n">
-        <v>3.534129146187817</v>
+        <v>3.21717376337222</v>
       </c>
       <c r="K4" t="n">
-        <v>2.250323717247899</v>
+        <v>1.972730420814319</v>
       </c>
       <c r="L4" t="n">
-        <v>1.885182499653941</v>
+        <v>1.567792125083018</v>
       </c>
       <c r="M4" t="n">
-        <v>2.932996617772247</v>
+        <v>2.634567619952888</v>
       </c>
       <c r="N4" t="n">
-        <v>4.566495694249554</v>
+        <v>54.45687528540235</v>
       </c>
       <c r="O4" t="n">
-        <v>5.183371669679984</v>
+        <v>4.877241709584835</v>
       </c>
       <c r="P4" t="n">
-        <v>6.329580144507853</v>
+        <v>6.026800832572769</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.511700314704499</v>
+        <v>2.202640022325443</v>
       </c>
       <c r="R4" t="n">
-        <v>2.04014645159033</v>
+        <v>1.719613931326832</v>
       </c>
       <c r="S4" t="n">
-        <v>2.93000517797351</v>
+        <v>2.568652837369959</v>
       </c>
       <c r="T4" t="n">
-        <v>3.311878523527978</v>
+        <v>3.06531227920703</v>
       </c>
       <c r="U4" t="n">
-        <v>3.67535091921809</v>
+        <v>3.364229944919039</v>
       </c>
       <c r="V4" t="n">
-        <v>3.875995585856508</v>
+        <v>3.565499165397936</v>
       </c>
       <c r="W4" t="n">
-        <v>6.47793953856313</v>
+        <v>6.183516943497886</v>
       </c>
       <c r="X4" t="n">
-        <v>5.336986486749979</v>
+        <v>5.032972063442585</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.569367145723989</v>
+        <v>6.250970907607448</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.84550947627459</v>
+        <v>2.529182623260479</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.488944899881157</v>
+        <v>4.190873938882789</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.484206752492002</v>
+        <v>4.179785737821715</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.094531305758341</v>
+        <v>4.651384244607914</v>
       </c>
       <c r="C5" t="n">
-        <v>11.31911599411265</v>
+        <v>10.89657151340764</v>
       </c>
       <c r="D5" t="n">
-        <v>9.302170227551706</v>
+        <v>8.484629535882405</v>
       </c>
       <c r="E5" t="n">
-        <v>14.5601752525125</v>
+        <v>13.75581254426256</v>
       </c>
       <c r="F5" t="n">
-        <v>20.45295801246215</v>
+        <v>19.854836505477</v>
       </c>
       <c r="G5" t="n">
-        <v>34.14515645473797</v>
+        <v>33.22254676525253</v>
       </c>
       <c r="H5" t="n">
-        <v>38.92190269060191</v>
+        <v>38.70877636638067</v>
       </c>
       <c r="I5" t="n">
-        <v>17.60333566631864</v>
+        <v>19.20874282594662</v>
       </c>
       <c r="J5" t="n">
-        <v>34.54204371183124</v>
+        <v>34.00674311525294</v>
       </c>
       <c r="K5" t="n">
-        <v>14.68495438520135</v>
+        <v>14.758253601414</v>
       </c>
       <c r="L5" t="n">
-        <v>8.081684322918626</v>
+        <v>7.543453053581892</v>
       </c>
       <c r="M5" t="n">
-        <v>25.24551397522624</v>
+        <v>24.97593013280346</v>
       </c>
       <c r="N5" t="n">
-        <v>35.61009086146102</v>
+        <v>54.45687528540235</v>
       </c>
       <c r="O5" t="n">
-        <v>59.28774021241816</v>
+        <v>58.90945202956328</v>
       </c>
       <c r="P5" t="n">
-        <v>80.25324388726831</v>
+        <v>79.92864605312154</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.34750142652435</v>
+        <v>17.91912017091837</v>
       </c>
       <c r="R5" t="n">
-        <v>12.34433576628536</v>
+        <v>11.68290131646639</v>
       </c>
       <c r="S5" t="n">
-        <v>23.4400936860322</v>
+        <v>22.25065975730336</v>
       </c>
       <c r="T5" t="n">
-        <v>33.52213520700269</v>
+        <v>34.15282445381489</v>
       </c>
       <c r="U5" t="n">
-        <v>34.72031279614713</v>
+        <v>34.47439524510258</v>
       </c>
       <c r="V5" t="n">
-        <v>38.80950153773746</v>
+        <v>38.35860638633739</v>
       </c>
       <c r="W5" t="n">
-        <v>85.31993070859792</v>
+        <v>85.12979796509451</v>
       </c>
       <c r="X5" t="n">
-        <v>67.7679497015818</v>
+        <v>67.41647837430665</v>
       </c>
       <c r="Y5" t="n">
-        <v>92.20845178373352</v>
+        <v>91.85516460792024</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.0788230800197</v>
+        <v>22.54372592605191</v>
       </c>
       <c r="AA5" t="n">
-        <v>55.13861098970607</v>
+        <v>54.8943706005704</v>
       </c>
       <c r="AB5" t="n">
-        <v>55.87414138519355</v>
+        <v>55.51108754720269</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.9120644993154</v>
+        <v>134.5047971254061</v>
       </c>
       <c r="C6" t="n">
-        <v>113.2540723547306</v>
+        <v>112.9186152967066</v>
       </c>
       <c r="D6" t="n">
-        <v>113.1350489725864</v>
+        <v>112.7766487980647</v>
       </c>
       <c r="E6" t="n">
-        <v>135.4097152623695</v>
+        <v>113.0836210408287</v>
       </c>
       <c r="F6" t="n">
-        <v>135.7216121671904</v>
+        <v>135.3379113032813</v>
       </c>
       <c r="G6" t="n">
-        <v>114.9006853720429</v>
+        <v>136.4601084732124</v>
       </c>
       <c r="H6" t="n">
-        <v>114.6568894186858</v>
+        <v>136.2631860939482</v>
       </c>
       <c r="I6" t="n">
-        <v>113.5789669282277</v>
+        <v>135.2860761617496</v>
       </c>
       <c r="J6" t="n">
-        <v>114.7695228112839</v>
+        <v>136.3553061359466</v>
       </c>
       <c r="K6" t="n">
-        <v>113.485717382344</v>
+        <v>135.1108627933887</v>
       </c>
       <c r="L6" t="n">
-        <v>135.0892647564283</v>
+        <v>112.7757751367926</v>
       </c>
       <c r="M6" t="n">
-        <v>136.1370788745467</v>
+        <v>135.7726999925272</v>
       </c>
       <c r="N6" t="n">
-        <v>115.809564064449</v>
+        <v>54.45687528540235</v>
       </c>
       <c r="O6" t="n">
-        <v>116.4264400398796</v>
+        <v>138.0777453634841</v>
       </c>
       <c r="P6" t="n">
-        <v>111.1365297662524</v>
+        <v>110.8098592199405</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.7470939798005</v>
+        <v>135.3407723948999</v>
       </c>
       <c r="R6" t="n">
-        <v>135.2442287083648</v>
+        <v>112.9275969430365</v>
       </c>
       <c r="S6" t="n">
-        <v>114.1653988430696</v>
+        <v>135.7067852099443</v>
       </c>
       <c r="T6" t="n">
-        <v>136.5159607803024</v>
+        <v>114.2732952909167</v>
       </c>
       <c r="U6" t="n">
-        <v>114.9121112940318</v>
+        <v>114.5877713359555</v>
       </c>
       <c r="V6" t="n">
-        <v>137.0800778426309</v>
+        <v>114.7734821771076</v>
       </c>
       <c r="W6" t="n">
-        <v>123.4034938779567</v>
+        <v>123.0806657530047</v>
       </c>
       <c r="X6" t="n">
-        <v>116.5723801518461</v>
+        <v>138.171104436017</v>
       </c>
       <c r="Y6" t="n">
-        <v>122.6932694750022</v>
+        <v>122.3612402006163</v>
       </c>
       <c r="Z6" t="n">
-        <v>136.0495917330491</v>
+        <v>113.7371656349702</v>
       </c>
       <c r="AA6" t="n">
-        <v>137.6930271566555</v>
+        <v>137.3290063114572</v>
       </c>
       <c r="AB6" t="n">
-        <v>115.7322620934786</v>
+        <v>115.4022213659933</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.532394258583275</v>
+        <v>2.209618540268885</v>
       </c>
       <c r="C7" t="n">
-        <v>2.874402113998521</v>
+        <v>2.553586072434214</v>
       </c>
       <c r="D7" t="n">
-        <v>2.75537873185433</v>
+        <v>2.411619573792161</v>
       </c>
       <c r="E7" t="n">
-        <v>3.06135642995898</v>
+        <v>2.718591816556124</v>
       </c>
       <c r="F7" t="n">
-        <v>3.373253334779903</v>
+        <v>3.042732718144016</v>
       </c>
       <c r="G7" t="n">
-        <v>4.521015131310749</v>
+        <v>4.164929888075068</v>
       </c>
       <c r="H7" t="n">
-        <v>4.277219177953752</v>
+        <v>3.968007508810993</v>
       </c>
       <c r="I7" t="n">
-        <v>3.199296687495587</v>
+        <v>2.990897576612429</v>
       </c>
       <c r="J7" t="n">
-        <v>4.389852570551765</v>
+        <v>4.060127550809418</v>
       </c>
       <c r="K7" t="n">
-        <v>3.106047141611846</v>
+        <v>2.815684208251514</v>
       </c>
       <c r="L7" t="n">
-        <v>2.740905924017883</v>
+        <v>2.410745912520214</v>
       </c>
       <c r="M7" t="n">
-        <v>3.788720042136196</v>
+        <v>3.477521407390102</v>
       </c>
       <c r="N7" t="n">
-        <v>5.4222191186135</v>
+        <v>54.45687528540235</v>
       </c>
       <c r="O7" t="n">
-        <v>6.039093763208456</v>
+        <v>5.720192534476425</v>
       </c>
       <c r="P7" t="n">
-        <v>7.185302238036321</v>
+        <v>6.869751657464372</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.367423739068448</v>
+        <v>3.045593809762648</v>
       </c>
       <c r="R7" t="n">
-        <v>2.895869875954279</v>
+        <v>2.562567718764028</v>
       </c>
       <c r="S7" t="n">
-        <v>3.785728602337463</v>
+        <v>3.411606624807163</v>
       </c>
       <c r="T7" t="n">
-        <v>4.167601947891928</v>
+        <v>3.908266066644217</v>
       </c>
       <c r="U7" t="n">
-        <v>4.522896277220708</v>
+        <v>4.217597214673699</v>
       </c>
       <c r="V7" t="n">
-        <v>4.73171901022045</v>
+        <v>4.40845295283514</v>
       </c>
       <c r="W7" t="n">
-        <v>7.33366296292708</v>
+        <v>7.026470730935074</v>
       </c>
       <c r="X7" t="n">
-        <v>6.192709911113928</v>
+        <v>5.875925850879784</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.426457279805483</v>
+        <v>7.109483074371418</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.70123290063854</v>
+        <v>3.372136410697681</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.344668324245114</v>
+        <v>5.033827726319982</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.339930176855948</v>
+        <v>5.022739525258915</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.768372346919675</v>
+        <v>2.424807500793553</v>
       </c>
       <c r="C8" t="n">
-        <v>3.94518496358228</v>
+        <v>3.56192719495458</v>
       </c>
       <c r="D8" t="n">
-        <v>3.826161581438073</v>
+        <v>3.419960696312524</v>
       </c>
       <c r="E8" t="n">
-        <v>3.687630369702899</v>
+        <v>3.304602809565442</v>
       </c>
       <c r="F8" t="n">
-        <v>3.739284248166838</v>
+        <v>3.38148551561128</v>
       </c>
       <c r="G8" t="n">
-        <v>5.764900186261099</v>
+        <v>5.337736278204932</v>
       </c>
       <c r="H8" t="n">
-        <v>5.348002027537497</v>
+        <v>4.976348631331365</v>
       </c>
       <c r="I8" t="n">
-        <v>4.270079537079342</v>
+        <v>3.999238699132792</v>
       </c>
       <c r="J8" t="n">
-        <v>5.460635420135509</v>
+        <v>5.068468673329775</v>
       </c>
       <c r="K8" t="n">
-        <v>4.176829991195591</v>
+        <v>3.824025330771877</v>
       </c>
       <c r="L8" t="n">
-        <v>3.811688773601637</v>
+        <v>3.41908703504058</v>
       </c>
       <c r="M8" t="n">
-        <v>4.859502891717919</v>
+        <v>4.485862529910106</v>
       </c>
       <c r="N8" t="n">
-        <v>5.845888618026932</v>
+        <v>54.45687528540235</v>
       </c>
       <c r="O8" t="n">
-        <v>6.64059696004505</v>
+        <v>6.282670419732341</v>
       </c>
       <c r="P8" t="n">
-        <v>7.74321442487849</v>
+        <v>7.390813506923052</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.439343638769749</v>
+        <v>3.104910267944669</v>
       </c>
       <c r="R8" t="n">
-        <v>3.966652725538021</v>
+        <v>3.570908841284389</v>
       </c>
       <c r="S8" t="n">
-        <v>4.856511451921206</v>
+        <v>4.419947747327517</v>
       </c>
       <c r="T8" t="n">
-        <v>5.238384797475675</v>
+        <v>4.916607189164584</v>
       </c>
       <c r="U8" t="n">
-        <v>5.188370904190805</v>
+        <v>4.839971376361069</v>
       </c>
       <c r="V8" t="n">
-        <v>5.566179629553556</v>
+        <v>5.19561843124985</v>
       </c>
       <c r="W8" t="n">
-        <v>8.404609873964416</v>
+        <v>8.034967729454584</v>
       </c>
       <c r="X8" t="n">
-        <v>6.341141324979841</v>
+        <v>6.00793628003292</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.314615207346019</v>
+        <v>8.899620379656721</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.921704062088245</v>
+        <v>3.572592162704937</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.415451173828847</v>
+        <v>6.042168848840348</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.282736403297926</v>
+        <v>6.859594402242721</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.431180148562345</v>
+        <v>4.071502344645135</v>
       </c>
       <c r="C9" t="n">
-        <v>5.596397303961</v>
+        <v>5.216093641494158</v>
       </c>
       <c r="D9" t="n">
-        <v>5.477373921816796</v>
+        <v>5.074127142852103</v>
       </c>
       <c r="E9" t="n">
-        <v>5.593358564341633</v>
+        <v>5.196318958750522</v>
       </c>
       <c r="F9" t="n">
-        <v>4.197525915871415</v>
+        <v>3.859583536516266</v>
       </c>
       <c r="G9" t="n">
-        <v>7.243010702247252</v>
+        <v>6.827437811187469</v>
       </c>
       <c r="H9" t="n">
-        <v>6.999214367916217</v>
+        <v>6.630515077870936</v>
       </c>
       <c r="I9" t="n">
-        <v>5.921291877458067</v>
+        <v>5.653405145672364</v>
       </c>
       <c r="J9" t="n">
-        <v>7.111847760514229</v>
+        <v>6.722635119869363</v>
       </c>
       <c r="K9" t="n">
-        <v>5.828042331574303</v>
+        <v>5.478191777311457</v>
       </c>
       <c r="L9" t="n">
-        <v>5.462901113980362</v>
+        <v>5.073253481580154</v>
       </c>
       <c r="M9" t="n">
-        <v>6.510715232098653</v>
+        <v>6.140028976450042</v>
       </c>
       <c r="N9" t="n">
-        <v>8.144214308575958</v>
+        <v>54.45687528540235</v>
       </c>
       <c r="O9" t="n">
-        <v>9.033901275348587</v>
+        <v>8.648029204755716</v>
       </c>
       <c r="P9" t="n">
-        <v>10.23944137728976</v>
+        <v>9.855292133675004</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.089419310004935</v>
+        <v>5.708101732875048</v>
       </c>
       <c r="R9" t="n">
-        <v>5.617865065916737</v>
+        <v>5.225075287823965</v>
       </c>
       <c r="S9" t="n">
-        <v>6.507723792299919</v>
+        <v>6.074114193867111</v>
       </c>
       <c r="T9" t="n">
-        <v>6.889597137854391</v>
+        <v>6.570773635704164</v>
       </c>
       <c r="U9" t="n">
-        <v>7.254436243262049</v>
+        <v>6.885249680742952</v>
       </c>
       <c r="V9" t="n">
-        <v>8.403680377286818</v>
+        <v>7.994863448223679</v>
       </c>
       <c r="W9" t="n">
-        <v>10.05565815288955</v>
+        <v>9.688978299995025</v>
       </c>
       <c r="X9" t="n">
-        <v>8.914705101076382</v>
+        <v>8.538433419939725</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.14845246976795</v>
+        <v>9.771990643431362</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.92690623661869</v>
+        <v>5.55193918448662</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.066663514207564</v>
+        <v>7.696335295379923</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.061925366818414</v>
+        <v>7.685247094318862</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.74068069772322</v>
+        <v>38.69842104855333</v>
       </c>
       <c r="C2" t="n">
-        <v>41.71248924242067</v>
+        <v>41.65425171781188</v>
       </c>
       <c r="D2" t="n">
-        <v>38.7844508896471</v>
+        <v>38.74270031550378</v>
       </c>
       <c r="E2" t="n">
-        <v>38.74357278028446</v>
+        <v>38.69981335289958</v>
       </c>
       <c r="F2" t="n">
-        <v>38.85590356427711</v>
+        <v>38.81293843625948</v>
       </c>
       <c r="G2" t="n">
-        <v>38.83419627692015</v>
+        <v>38.79248497402523</v>
       </c>
       <c r="H2" t="n">
-        <v>38.89044966425656</v>
+        <v>38.84876433900499</v>
       </c>
       <c r="I2" t="n">
-        <v>38.7989300826057</v>
+        <v>38.76023842329506</v>
       </c>
       <c r="J2" t="n">
-        <v>38.85478055914814</v>
+        <v>38.81298169385913</v>
       </c>
       <c r="K2" t="n">
-        <v>38.80184700695997</v>
+        <v>38.76083091507994</v>
       </c>
       <c r="L2" t="n">
-        <v>38.76647434972877</v>
+        <v>38.72410660973708</v>
       </c>
       <c r="M2" t="n">
-        <v>38.85018683180314</v>
+        <v>38.80849534294823</v>
       </c>
       <c r="N2" t="n">
-        <v>38.91206937734496</v>
+        <v>38.87042065432787</v>
       </c>
       <c r="O2" t="n">
-        <v>42.68021168322561</v>
+        <v>42.59541677849833</v>
       </c>
       <c r="P2" t="n">
-        <v>39.09962847556432</v>
+        <v>39.05837101845326</v>
       </c>
       <c r="Q2" t="n">
-        <v>38.78569998408373</v>
+        <v>38.74402912500827</v>
       </c>
       <c r="R2" t="n">
-        <v>38.76825986985772</v>
+        <v>38.72451168362056</v>
       </c>
       <c r="S2" t="n">
-        <v>38.8914675905319</v>
+        <v>38.84877334002168</v>
       </c>
       <c r="T2" t="n">
-        <v>38.87179905617017</v>
+        <v>38.83193812908836</v>
       </c>
       <c r="U2" t="n">
-        <v>42.20499122205362</v>
+        <v>42.16541008459404</v>
       </c>
       <c r="V2" t="n">
-        <v>38.86935524433809</v>
+        <v>38.82723731838044</v>
       </c>
       <c r="W2" t="n">
-        <v>44.72133906469504</v>
+        <v>44.68189194366754</v>
       </c>
       <c r="X2" t="n">
-        <v>39.09878440562589</v>
+        <v>39.05783965819825</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.03926711571361</v>
+        <v>38.99777261879449</v>
       </c>
       <c r="Z2" t="n">
-        <v>39.84889497996843</v>
+        <v>39.78238877303494</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.00801313739743</v>
+        <v>38.96640004457797</v>
       </c>
       <c r="AB2" t="n">
-        <v>38.94913924149515</v>
+        <v>38.90954941972046</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.49968387431985</v>
+        <v>38.45664220738615</v>
       </c>
       <c r="C3" t="n">
-        <v>43.49977870817978</v>
+        <v>43.4316289726281</v>
       </c>
       <c r="D3" t="n">
-        <v>38.81272051926516</v>
+        <v>38.7732707502792</v>
       </c>
       <c r="E3" t="n">
-        <v>38.52057584316117</v>
+        <v>38.46685568599337</v>
       </c>
       <c r="F3" t="n">
-        <v>39.32438653225962</v>
+        <v>39.27625255319253</v>
       </c>
       <c r="G3" t="n">
-        <v>39.16256889983141</v>
+        <v>39.1234122638494</v>
       </c>
       <c r="H3" t="n">
-        <v>39.57353850901957</v>
+        <v>39.5345466454828</v>
       </c>
       <c r="I3" t="n">
-        <v>38.91710654636076</v>
+        <v>38.89953034607554</v>
       </c>
       <c r="J3" t="n">
-        <v>39.31159868139461</v>
+        <v>39.27182181862474</v>
       </c>
       <c r="K3" t="n">
-        <v>38.93583537375292</v>
+        <v>38.9016147875599</v>
       </c>
       <c r="L3" t="n">
-        <v>38.6824113800784</v>
+        <v>38.63859671391753</v>
       </c>
       <c r="M3" t="n">
-        <v>39.28400145698092</v>
+        <v>39.24460538121622</v>
       </c>
       <c r="N3" t="n">
-        <v>39.7229652008852</v>
+        <v>39.68425448073732</v>
       </c>
       <c r="O3" t="n">
-        <v>46.24609477104302</v>
+        <v>46.13625724628905</v>
       </c>
       <c r="P3" t="n">
-        <v>41.04592427454671</v>
+        <v>41.0099963155373</v>
       </c>
       <c r="Q3" t="n">
-        <v>38.82047759741132</v>
+        <v>38.7816064324024</v>
       </c>
       <c r="R3" t="n">
-        <v>38.69819061561837</v>
+        <v>38.64443434359795</v>
       </c>
       <c r="S3" t="n">
-        <v>39.5693333262345</v>
+        <v>39.52321042668263</v>
       </c>
       <c r="T3" t="n">
-        <v>39.43678185505664</v>
+        <v>39.41082596368875</v>
       </c>
       <c r="U3" t="n">
-        <v>45.18060488071941</v>
+        <v>45.1486240743874</v>
       </c>
       <c r="V3" t="n">
-        <v>39.41277602644663</v>
+        <v>39.37074134261197</v>
       </c>
       <c r="W3" t="n">
-        <v>49.71071054320632</v>
+        <v>49.67868304289981</v>
       </c>
       <c r="X3" t="n">
-        <v>41.04895462593347</v>
+        <v>41.01524680161313</v>
       </c>
       <c r="Y3" t="n">
-        <v>40.63324197074095</v>
+        <v>40.59563530420125</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.54908487687774</v>
+        <v>40.46533932466679</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.40870390993958</v>
+        <v>40.37024984125965</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.98293234464249</v>
+        <v>39.95854732514699</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.471978440301808</v>
+        <v>1.224580842304677</v>
       </c>
       <c r="C4" t="n">
-        <v>1.664970398176602</v>
+        <v>1.42025765823133</v>
       </c>
       <c r="D4" t="n">
-        <v>1.966382893365719</v>
+        <v>1.724735531979034</v>
       </c>
       <c r="E4" t="n">
-        <v>1.504645843255036</v>
+        <v>1.240307560387283</v>
       </c>
       <c r="F4" t="n">
-        <v>2.773473723165498</v>
+        <v>2.518107417046873</v>
       </c>
       <c r="G4" t="n">
-        <v>2.528279926623389</v>
+        <v>2.287076152053485</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1636878144247</v>
+        <v>2.922777469287057</v>
       </c>
       <c r="I4" t="n">
-        <v>2.129932038590559</v>
+        <v>1.922836527409639</v>
       </c>
       <c r="J4" t="n">
-        <v>2.761908279504509</v>
+        <v>2.519752479187896</v>
       </c>
       <c r="K4" t="n">
-        <v>2.162880041023635</v>
+        <v>1.929528994679816</v>
       </c>
       <c r="L4" t="n">
-        <v>1.763329605371085</v>
+        <v>1.514711071817332</v>
       </c>
       <c r="M4" t="n">
-        <v>2.714087037073951</v>
+        <v>2.472446060541167</v>
       </c>
       <c r="N4" t="n">
-        <v>3.407892419317595</v>
+        <v>38.78370947956876</v>
       </c>
       <c r="O4" t="n">
-        <v>4.053981984482212</v>
+        <v>3.813666532418742</v>
       </c>
       <c r="P4" t="n">
-        <v>5.526458715153376</v>
+        <v>5.290381337491404</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.980491989638682</v>
+        <v>1.739745046615182</v>
       </c>
       <c r="R4" t="n">
-        <v>1.783497876607498</v>
+        <v>1.519286567674058</v>
       </c>
       <c r="S4" t="n">
-        <v>3.175185759973957</v>
+        <v>2.922879139910888</v>
       </c>
       <c r="T4" t="n">
-        <v>2.953020616385223</v>
+        <v>2.732717687839296</v>
       </c>
       <c r="U4" t="n">
-        <v>3.470096145377476</v>
+        <v>3.219490641655679</v>
       </c>
       <c r="V4" t="n">
-        <v>2.932650841082727</v>
+        <v>2.687079676919175</v>
       </c>
       <c r="W4" t="n">
-        <v>4.235070673023951</v>
+        <v>4.000872446977704</v>
       </c>
       <c r="X4" t="n">
-        <v>5.516924556907252</v>
+        <v>5.284379378973166</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.84348461127623</v>
+        <v>4.5877133623995</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.930202164977502</v>
+        <v>1.681368780866386</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.491621325420159</v>
+        <v>4.251526878831707</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.807763176811534</v>
+        <v>3.589792881584773</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.814768462323481</v>
+        <v>4.399795140028123</v>
       </c>
       <c r="C5" t="n">
-        <v>8.52167043493354</v>
+        <v>8.134303562983806</v>
       </c>
       <c r="D5" t="n">
-        <v>13.89421275815065</v>
+        <v>13.55948948465483</v>
       </c>
       <c r="E5" t="n">
-        <v>5.522636068696096</v>
+        <v>4.821254366178272</v>
       </c>
       <c r="F5" t="n">
-        <v>29.05236976983163</v>
+        <v>28.46677567318033</v>
       </c>
       <c r="G5" t="n">
-        <v>21.14429474394046</v>
+        <v>20.8240773345567</v>
       </c>
       <c r="H5" t="n">
-        <v>37.29860766871434</v>
+        <v>36.97288839910661</v>
       </c>
       <c r="I5" t="n">
-        <v>17.32958863476034</v>
+        <v>17.62770673272152</v>
       </c>
       <c r="J5" t="n">
-        <v>26.35569817740623</v>
+        <v>26.02046572266422</v>
       </c>
       <c r="K5" t="n">
-        <v>16.82954608482108</v>
+        <v>16.63489570976331</v>
       </c>
       <c r="L5" t="n">
-        <v>9.261415756193053</v>
+        <v>8.824045110424004</v>
       </c>
       <c r="M5" t="n">
-        <v>26.75705297542314</v>
+        <v>26.41785059502678</v>
       </c>
       <c r="N5" t="n">
-        <v>35.64659257932351</v>
+        <v>38.78370947956874</v>
       </c>
       <c r="O5" t="n">
-        <v>44.97701191919835</v>
+        <v>44.67510350745133</v>
       </c>
       <c r="P5" t="n">
-        <v>68.4469679564538</v>
+        <v>68.21200750919101</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.54376984311921</v>
+        <v>13.22998503337264</v>
       </c>
       <c r="R5" t="n">
-        <v>11.19139770315963</v>
+        <v>10.43196967965567</v>
       </c>
       <c r="S5" t="n">
-        <v>31.55784091496636</v>
+        <v>31.06668715699228</v>
       </c>
       <c r="T5" t="n">
-        <v>31.68299023469863</v>
+        <v>31.72959900417787</v>
       </c>
       <c r="U5" t="n">
-        <v>35.70996108214897</v>
+        <v>35.5038905122187</v>
       </c>
       <c r="V5" t="n">
-        <v>27.80026082818735</v>
+        <v>27.41149308805948</v>
       </c>
       <c r="W5" t="n">
-        <v>52.01679403984667</v>
+        <v>51.81477758062961</v>
       </c>
       <c r="X5" t="n">
-        <v>72.9706166651298</v>
+        <v>72.7920709984185</v>
       </c>
       <c r="Y5" t="n">
-        <v>65.77813647616803</v>
+        <v>65.50258715389693</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.63640821232751</v>
+        <v>11.20478776676137</v>
       </c>
       <c r="AA5" t="n">
-        <v>58.76890761442368</v>
+        <v>58.46915888520294</v>
       </c>
       <c r="AB5" t="n">
-        <v>49.08669048141097</v>
+        <v>49.19134626438399</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.5408810361794</v>
+        <v>134.239994375785</v>
       </c>
       <c r="C6" t="n">
-        <v>134.7338729940543</v>
+        <v>134.4356711917115</v>
       </c>
       <c r="D6" t="n">
-        <v>135.0352854892432</v>
+        <v>134.7401490654595</v>
       </c>
       <c r="E6" t="n">
-        <v>134.5735484391325</v>
+        <v>112.3892781895615</v>
       </c>
       <c r="F6" t="n">
-        <v>135.8423763190431</v>
+        <v>135.5335209505272</v>
       </c>
       <c r="G6" t="n">
-        <v>135.597182522501</v>
+        <v>135.3024896855338</v>
       </c>
       <c r="H6" t="n">
-        <v>114.3375815907991</v>
+        <v>135.9381910027674</v>
       </c>
       <c r="I6" t="n">
-        <v>113.303825814965</v>
+        <v>134.9382500608898</v>
       </c>
       <c r="J6" t="n">
-        <v>113.935802055879</v>
+        <v>113.668723108362</v>
       </c>
       <c r="K6" t="n">
-        <v>135.2317826369012</v>
+        <v>113.078499623854</v>
       </c>
       <c r="L6" t="n">
-        <v>134.8322322012486</v>
+        <v>134.5301246052976</v>
       </c>
       <c r="M6" t="n">
-        <v>135.7829896329515</v>
+        <v>135.4878595940214</v>
       </c>
       <c r="N6" t="n">
-        <v>114.5898307252417</v>
+        <v>38.78370947956874</v>
       </c>
       <c r="O6" t="n">
-        <v>137.1772937572839</v>
+        <v>114.9714489261843</v>
       </c>
       <c r="P6" t="n">
-        <v>138.6496529676479</v>
+        <v>138.3614293710577</v>
       </c>
       <c r="Q6" t="n">
-        <v>135.0493945855163</v>
+        <v>134.7551585800955</v>
       </c>
       <c r="R6" t="n">
-        <v>112.9573916529819</v>
+        <v>134.5347001011543</v>
       </c>
       <c r="S6" t="n">
-        <v>114.3490795363484</v>
+        <v>135.9382926733912</v>
       </c>
       <c r="T6" t="n">
-        <v>136.0219232122628</v>
+        <v>113.8816883170135</v>
       </c>
       <c r="U6" t="n">
-        <v>136.5401635180206</v>
+        <v>136.2530853494409</v>
       </c>
       <c r="V6" t="n">
-        <v>114.1065446174573</v>
+        <v>113.8360503060934</v>
       </c>
       <c r="W6" t="n">
-        <v>137.3585221343325</v>
+        <v>137.0726080216405</v>
       </c>
       <c r="X6" t="n">
-        <v>116.6908183332818</v>
+        <v>116.4333500081473</v>
       </c>
       <c r="Y6" t="n">
-        <v>120.9019163506032</v>
+        <v>120.6386256537036</v>
       </c>
       <c r="Z6" t="n">
-        <v>113.104095941352</v>
+        <v>112.8303394100406</v>
       </c>
       <c r="AA6" t="n">
-        <v>115.6655151017947</v>
+        <v>137.2669404123119</v>
       </c>
       <c r="AB6" t="n">
-        <v>114.9944083536234</v>
+        <v>114.7536420441663</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.269847158840896</v>
+        <v>2.01253072044207</v>
       </c>
       <c r="C7" t="n">
-        <v>2.462839116715688</v>
+        <v>2.208207536368716</v>
       </c>
       <c r="D7" t="n">
-        <v>2.764251611904807</v>
+        <v>2.512685410116428</v>
       </c>
       <c r="E7" t="n">
-        <v>2.302514561794122</v>
+        <v>2.028257438524667</v>
       </c>
       <c r="F7" t="n">
-        <v>3.571342441704583</v>
+        <v>3.306057295184269</v>
       </c>
       <c r="G7" t="n">
-        <v>3.326148645162479</v>
+        <v>3.075026030190869</v>
       </c>
       <c r="H7" t="n">
-        <v>3.961556532963786</v>
+        <v>3.710727347424451</v>
       </c>
       <c r="I7" t="n">
-        <v>2.927800757129646</v>
+        <v>2.710786405547031</v>
       </c>
       <c r="J7" t="n">
-        <v>3.559776998043593</v>
+        <v>3.307702357325277</v>
       </c>
       <c r="K7" t="n">
-        <v>2.960748759562722</v>
+        <v>2.717478872817201</v>
       </c>
       <c r="L7" t="n">
-        <v>2.561198323910172</v>
+        <v>2.302660949954716</v>
       </c>
       <c r="M7" t="n">
-        <v>3.511955755613037</v>
+        <v>3.260395938678551</v>
       </c>
       <c r="N7" t="n">
-        <v>4.205761137856681</v>
+        <v>38.78370947956874</v>
       </c>
       <c r="O7" t="n">
-        <v>4.851850785460572</v>
+        <v>4.601615005116493</v>
       </c>
       <c r="P7" t="n">
-        <v>6.324327516131738</v>
+        <v>6.078329810189164</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.77836070817777</v>
+        <v>2.527694924752565</v>
       </c>
       <c r="R7" t="n">
-        <v>2.581366595146585</v>
+        <v>2.307236445811451</v>
       </c>
       <c r="S7" t="n">
-        <v>3.973054478513045</v>
+        <v>3.710829018048282</v>
       </c>
       <c r="T7" t="n">
-        <v>3.750889334924313</v>
+        <v>3.52066756597669</v>
       </c>
       <c r="U7" t="n">
-        <v>4.259182669104083</v>
+        <v>4.020131273374611</v>
       </c>
       <c r="V7" t="n">
-        <v>3.730519559621816</v>
+        <v>3.475029555056567</v>
       </c>
       <c r="W7" t="n">
-        <v>5.032939391563037</v>
+        <v>4.788822325115095</v>
       </c>
       <c r="X7" t="n">
-        <v>6.314793275446339</v>
+        <v>6.07232925711056</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.642518106580879</v>
+        <v>5.393844414841698</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.728070883516589</v>
+        <v>2.469318659003779</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.289490043959248</v>
+        <v>5.039476756969091</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.605631895350627</v>
+        <v>4.377742759722162</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.452891018910586</v>
+        <v>2.180242245445703</v>
       </c>
       <c r="C8" t="n">
-        <v>3.389265609349811</v>
+        <v>3.088247961100924</v>
       </c>
       <c r="D8" t="n">
-        <v>3.690678104538933</v>
+        <v>3.392725834848632</v>
       </c>
       <c r="E8" t="n">
-        <v>2.833111731275018</v>
+        <v>2.529003736732415</v>
       </c>
       <c r="F8" t="n">
-        <v>3.870196627677038</v>
+        <v>3.58474133748928</v>
       </c>
       <c r="G8" t="n">
-        <v>4.406720369242101</v>
+        <v>4.102772492600052</v>
       </c>
       <c r="H8" t="n">
-        <v>4.88798302559791</v>
+        <v>4.590767772156653</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85422724976377</v>
+        <v>3.590826830279222</v>
       </c>
       <c r="J8" t="n">
-        <v>4.486203490677717</v>
+        <v>4.18774278205748</v>
       </c>
       <c r="K8" t="n">
-        <v>3.887175252196842</v>
+        <v>3.597519297549399</v>
       </c>
       <c r="L8" t="n">
-        <v>3.487624816544295</v>
+        <v>3.182701374686924</v>
       </c>
       <c r="M8" t="n">
-        <v>4.43838224824451</v>
+        <v>4.140436363409494</v>
       </c>
       <c r="N8" t="n">
-        <v>4.555941724703841</v>
+        <v>38.78370947956874</v>
       </c>
       <c r="O8" t="n">
-        <v>5.360388667542582</v>
+        <v>5.081224995439359</v>
       </c>
       <c r="P8" t="n">
-        <v>6.79404817856905</v>
+        <v>6.520744113945131</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8153129144339</v>
+        <v>2.555417563104355</v>
       </c>
       <c r="R8" t="n">
-        <v>3.507793087780708</v>
+        <v>3.187276870543657</v>
       </c>
       <c r="S8" t="n">
-        <v>4.899480971147166</v>
+        <v>4.590869442780486</v>
       </c>
       <c r="T8" t="n">
-        <v>4.677315827558436</v>
+        <v>4.400707990708895</v>
       </c>
       <c r="U8" t="n">
-        <v>4.825012268698634</v>
+        <v>4.553730037548329</v>
       </c>
       <c r="V8" t="n">
-        <v>4.445265873617754</v>
+        <v>4.155687875934071</v>
       </c>
       <c r="W8" t="n">
-        <v>5.959511978842533</v>
+        <v>5.669002741926517</v>
       </c>
       <c r="X8" t="n">
-        <v>6.419877976274468</v>
+        <v>6.16533825395098</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.294885648234001</v>
+        <v>6.974860147363749</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.897306029651242</v>
+        <v>2.623798309066377</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.215916536593371</v>
+        <v>5.919517181701302</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.308583707087298</v>
+        <v>6.001870283305978</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.765776986822472</v>
+        <v>3.480306295189994</v>
       </c>
       <c r="C9" t="n">
-        <v>4.645414021518382</v>
+        <v>4.345565988007996</v>
       </c>
       <c r="D9" t="n">
-        <v>4.946826516707501</v>
+        <v>4.650043861755713</v>
       </c>
       <c r="E9" t="n">
-        <v>4.32661468968854</v>
+        <v>4.011078988422938</v>
       </c>
       <c r="F9" t="n">
-        <v>4.171012861259254</v>
+        <v>3.899844307763738</v>
       </c>
       <c r="G9" t="n">
-        <v>5.508723687832056</v>
+        <v>5.21238460542116</v>
       </c>
       <c r="H9" t="n">
-        <v>6.14413143776648</v>
+        <v>5.848085799063733</v>
       </c>
       <c r="I9" t="n">
-        <v>5.110375661932342</v>
+        <v>4.848144857186305</v>
       </c>
       <c r="J9" t="n">
-        <v>5.742351902846287</v>
+        <v>5.445060808964561</v>
       </c>
       <c r="K9" t="n">
-        <v>5.14332366436542</v>
+        <v>4.854837324456473</v>
       </c>
       <c r="L9" t="n">
-        <v>4.743773228712866</v>
+        <v>4.440019401593995</v>
       </c>
       <c r="M9" t="n">
-        <v>5.694530660415728</v>
+        <v>5.39775439031783</v>
       </c>
       <c r="N9" t="n">
-        <v>6.38833604265937</v>
+        <v>38.78370947956874</v>
       </c>
       <c r="O9" t="n">
-        <v>7.261979070753261</v>
+        <v>6.960873915402086</v>
       </c>
       <c r="P9" t="n">
-        <v>8.783944745467975</v>
+        <v>8.485847930521729</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.960935750847361</v>
+        <v>4.665053499982857</v>
       </c>
       <c r="R9" t="n">
-        <v>4.763941499949279</v>
+        <v>4.444594897450713</v>
       </c>
       <c r="S9" t="n">
-        <v>6.155629383315735</v>
+        <v>5.848187469687561</v>
       </c>
       <c r="T9" t="n">
-        <v>5.933464239727004</v>
+        <v>5.658026017615972</v>
       </c>
       <c r="U9" t="n">
-        <v>6.451704545484821</v>
+        <v>6.162980145737148</v>
       </c>
       <c r="V9" t="n">
-        <v>6.705468081326623</v>
+        <v>6.38507220861134</v>
       </c>
       <c r="W9" t="n">
-        <v>7.215514296365737</v>
+        <v>6.926180776754366</v>
       </c>
       <c r="X9" t="n">
-        <v>8.497368180249039</v>
+        <v>8.209687708749829</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.825093011383577</v>
+        <v>7.531202866480974</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.496659920604134</v>
+        <v>4.202978226586741</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.472064948761943</v>
+        <v>7.176835208608372</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.788206800153322</v>
+        <v>6.515101211361438</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.62780535359527</v>
+        <v>39.50161198220552</v>
       </c>
       <c r="C2" t="n">
-        <v>42.42897767731518</v>
+        <v>42.31579442056723</v>
       </c>
       <c r="D2" t="n">
-        <v>39.59970192145899</v>
+        <v>39.49937286404622</v>
       </c>
       <c r="E2" t="n">
-        <v>39.62452743273985</v>
+        <v>39.50271116731738</v>
       </c>
       <c r="F2" t="n">
-        <v>39.55369666745757</v>
+        <v>39.43872113188697</v>
       </c>
       <c r="G2" t="n">
-        <v>39.90855647702609</v>
+        <v>39.69589858493077</v>
       </c>
       <c r="H2" t="n">
-        <v>39.74035433896783</v>
+        <v>39.63050250492768</v>
       </c>
       <c r="I2" t="n">
-        <v>39.5826908363909</v>
+        <v>39.48405581143469</v>
       </c>
       <c r="J2" t="n">
-        <v>39.83123954765473</v>
+        <v>39.68529924066127</v>
       </c>
       <c r="K2" t="n">
-        <v>39.64474472730206</v>
+        <v>39.54161586553933</v>
       </c>
       <c r="L2" t="n">
-        <v>39.7739847279759</v>
+        <v>39.70869067461381</v>
       </c>
       <c r="M2" t="n">
-        <v>40.07409185397333</v>
+        <v>39.93673003181978</v>
       </c>
       <c r="N2" t="n">
-        <v>39.78703596940313</v>
+        <v>39.67136226013366</v>
       </c>
       <c r="O2" t="n">
-        <v>43.85666173165733</v>
+        <v>43.69262320170546</v>
       </c>
       <c r="P2" t="n">
-        <v>39.93554293972279</v>
+        <v>39.79529959856451</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.65497346321663</v>
+        <v>39.54218817462006</v>
       </c>
       <c r="R2" t="n">
-        <v>39.61178445983789</v>
+        <v>39.52555542170035</v>
       </c>
       <c r="S2" t="n">
-        <v>39.72578793775203</v>
+        <v>39.58878485052997</v>
       </c>
       <c r="T2" t="n">
-        <v>39.66646276315422</v>
+        <v>39.55630276920878</v>
       </c>
       <c r="U2" t="n">
-        <v>43.41411216989282</v>
+        <v>43.32606280497718</v>
       </c>
       <c r="V2" t="n">
-        <v>39.74794458217396</v>
+        <v>39.63799019691508</v>
       </c>
       <c r="W2" t="n">
-        <v>46.08165313274222</v>
+        <v>45.99177893188413</v>
       </c>
       <c r="X2" t="n">
-        <v>39.74822920439443</v>
+        <v>39.63327164810089</v>
       </c>
       <c r="Y2" t="n">
-        <v>40.06474610469418</v>
+        <v>39.94560221663026</v>
       </c>
       <c r="Z2" t="n">
-        <v>41.08666926668122</v>
+        <v>40.9584508168991</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.70590035324388</v>
+        <v>39.59232789510211</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.9417737817082</v>
+        <v>39.92976901715325</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.45097487424877</v>
+        <v>40.23583548145214</v>
       </c>
       <c r="C3" t="n">
-        <v>44.20048411866667</v>
+        <v>44.10135044444488</v>
       </c>
       <c r="D3" t="n">
-        <v>40.2614664790208</v>
+        <v>40.23049284379376</v>
       </c>
       <c r="E3" t="n">
-        <v>40.43402944583197</v>
+        <v>40.24958079296952</v>
       </c>
       <c r="F3" t="n">
-        <v>39.93170258396652</v>
+        <v>39.79589267948668</v>
       </c>
       <c r="G3" t="n">
-        <v>42.44331769283207</v>
+        <v>41.61442861533892</v>
       </c>
       <c r="H3" t="n">
-        <v>41.27343246382694</v>
+        <v>41.17424554904789</v>
       </c>
       <c r="I3" t="n">
-        <v>40.13977739801616</v>
+        <v>40.12091736366095</v>
       </c>
       <c r="J3" t="n">
-        <v>41.90036194552678</v>
+        <v>41.54507370092665</v>
       </c>
       <c r="K3" t="n">
-        <v>40.57424084885312</v>
+        <v>40.52292608171629</v>
       </c>
       <c r="L3" t="n">
-        <v>41.49586428993013</v>
+        <v>41.71408100572784</v>
       </c>
       <c r="M3" t="n">
-        <v>43.63075137593526</v>
+        <v>43.33518960710888</v>
       </c>
       <c r="N3" t="n">
-        <v>41.59770136167199</v>
+        <v>41.45697988186407</v>
       </c>
       <c r="O3" t="n">
-        <v>48.24570773055075</v>
+        <v>48.0425109997331</v>
       </c>
       <c r="P3" t="n">
-        <v>42.64196695305372</v>
+        <v>42.32672131967634</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.65212359622691</v>
+        <v>40.53206889628159</v>
       </c>
       <c r="R3" t="n">
-        <v>40.35009231198342</v>
+        <v>40.42028146602846</v>
       </c>
       <c r="S3" t="n">
-        <v>41.14385253628648</v>
+        <v>40.85222158725237</v>
       </c>
       <c r="T3" t="n">
-        <v>40.73915872486353</v>
+        <v>40.63780560346162</v>
       </c>
       <c r="U3" t="n">
-        <v>48.07784639508227</v>
+        <v>48.06288573934397</v>
       </c>
       <c r="V3" t="n">
-        <v>41.30222843024082</v>
+        <v>41.20242909498172</v>
       </c>
       <c r="W3" t="n">
-        <v>53.4698865609533</v>
+        <v>53.41549072243973</v>
       </c>
       <c r="X3" t="n">
-        <v>41.32205080410909</v>
+        <v>41.18640744070219</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.57413803159886</v>
+        <v>43.4087446252339</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.62922251472769</v>
+        <v>43.47338547490005</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.01558290507251</v>
+        <v>40.88991874506595</v>
       </c>
       <c r="AB3" t="n">
-        <v>42.71143754667674</v>
+        <v>43.30310449751923</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.746372723751751</v>
+        <v>3.845406853363641</v>
       </c>
       <c r="C4" t="n">
-        <v>2.925177343542077</v>
+        <v>2.220515250675768</v>
       </c>
       <c r="D4" t="n">
-        <v>4.428931529554637</v>
+        <v>3.820114983709513</v>
       </c>
       <c r="E4" t="n">
-        <v>4.709347099771519</v>
+        <v>3.857822654852331</v>
       </c>
       <c r="F4" t="n">
-        <v>3.909281022146371</v>
+        <v>3.135025767795646</v>
       </c>
       <c r="G4" t="n">
-        <v>7.917585814800378</v>
+        <v>6.03996340739857</v>
       </c>
       <c r="H4" t="n">
-        <v>6.017665288625948</v>
+        <v>5.301284600080431</v>
       </c>
       <c r="I4" t="n">
-        <v>4.236783498225046</v>
+        <v>3.647101828269578</v>
       </c>
       <c r="J4" t="n">
-        <v>7.044532879480929</v>
+        <v>5.920941186367607</v>
       </c>
       <c r="K4" t="n">
-        <v>4.937710742267075</v>
+        <v>4.297269118314722</v>
       </c>
       <c r="L4" t="n">
-        <v>6.397536003215518</v>
+        <v>6.184455945020431</v>
       </c>
       <c r="M4" t="n">
-        <v>9.773732465895261</v>
+        <v>8.746045268676991</v>
       </c>
       <c r="N4" t="n">
-        <v>6.544955779003386</v>
+        <v>82.2954463264056</v>
       </c>
       <c r="O4" t="n">
-        <v>6.440292482152731</v>
+        <v>5.693410042088381</v>
       </c>
       <c r="P4" t="n">
-        <v>8.222410325345503</v>
+        <v>7.162743583116864</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.053249019872773</v>
+        <v>4.30373361265665</v>
       </c>
       <c r="R4" t="n">
-        <v>4.56540935878639</v>
+        <v>4.115859016984149</v>
       </c>
       <c r="S4" t="n">
-        <v>5.853131086017848</v>
+        <v>4.830064502589005</v>
       </c>
       <c r="T4" t="n">
-        <v>5.183025948007162</v>
+        <v>4.463164451570476</v>
       </c>
       <c r="U4" t="n">
-        <v>7.561067205190528</v>
+        <v>6.954388735837731</v>
       </c>
       <c r="V4" t="n">
-        <v>6.104965153432207</v>
+        <v>5.390293861797739</v>
       </c>
       <c r="W4" t="n">
-        <v>9.600188775337829</v>
+        <v>8.907952153003142</v>
       </c>
       <c r="X4" t="n">
-        <v>6.106615516236651</v>
+        <v>5.332563346091012</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.664156839585539</v>
+        <v>8.853178416227172</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.339279982964381</v>
+        <v>5.568121405801566</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.628491670257715</v>
+        <v>4.870084820912655</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.278307523104615</v>
+        <v>8.646594949655574</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.96825481808193</v>
+        <v>40.68654123971744</v>
       </c>
       <c r="C5" t="n">
-        <v>14.72283998096817</v>
+        <v>13.80549844943336</v>
       </c>
       <c r="D5" t="n">
-        <v>45.12115575548403</v>
+        <v>46.12470615669341</v>
       </c>
       <c r="E5" t="n">
-        <v>47.85494617968625</v>
+        <v>44.20280352406026</v>
       </c>
       <c r="F5" t="n">
-        <v>34.50474735695848</v>
+        <v>32.21133701520109</v>
       </c>
       <c r="G5" t="n">
-        <v>98.5935930636778</v>
+        <v>77.70952324437798</v>
       </c>
       <c r="H5" t="n">
-        <v>79.67822275102421</v>
+        <v>78.5096188350587</v>
       </c>
       <c r="I5" t="n">
-        <v>41.33225040539546</v>
+        <v>42.71050771508791</v>
       </c>
       <c r="J5" t="n">
-        <v>87.00799539100908</v>
+        <v>78.94642732276844</v>
       </c>
       <c r="K5" t="n">
-        <v>49.9034803765491</v>
+        <v>50.10952568424191</v>
       </c>
       <c r="L5" t="n">
-        <v>77.07809899374961</v>
+        <v>85.08800873924966</v>
       </c>
       <c r="M5" t="n">
-        <v>141.1511220534268</v>
+        <v>134.2488616136515</v>
       </c>
       <c r="N5" t="n">
-        <v>98.15180889631944</v>
+        <v>82.29544632640558</v>
       </c>
       <c r="O5" t="n">
-        <v>72.25282103588934</v>
+        <v>70.64674414232996</v>
       </c>
       <c r="P5" t="n">
-        <v>107.7194212722257</v>
+        <v>100.5310488148327</v>
       </c>
       <c r="Q5" t="n">
-        <v>54.80195061849656</v>
+        <v>53.04489401416037</v>
       </c>
       <c r="R5" t="n">
-        <v>49.03206747086459</v>
+        <v>53.34190710855658</v>
       </c>
       <c r="S5" t="n">
-        <v>62.31927473206189</v>
+        <v>56.09479874762742</v>
       </c>
       <c r="T5" t="n">
-        <v>60.05622178795033</v>
+        <v>58.84023730228802</v>
       </c>
       <c r="U5" t="n">
-        <v>99.18558299300867</v>
+        <v>99.8872292014987</v>
       </c>
       <c r="V5" t="n">
-        <v>67.18795482484052</v>
+        <v>66.0667725696789</v>
       </c>
       <c r="W5" t="n">
-        <v>141.2410238348073</v>
+        <v>140.5774392600341</v>
       </c>
       <c r="X5" t="n">
-        <v>77.14168876995812</v>
+        <v>74.87337561874631</v>
       </c>
       <c r="Y5" t="n">
-        <v>140.8984765397742</v>
+        <v>137.8072701017039</v>
       </c>
       <c r="Z5" t="n">
-        <v>73.10010478856186</v>
+        <v>71.04800801837763</v>
       </c>
       <c r="AA5" t="n">
-        <v>65.6738875237471</v>
+        <v>63.75349986438302</v>
       </c>
       <c r="AB5" t="n">
-        <v>127.0568687080792</v>
+        <v>148.4464128117448</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>148.1402799793338</v>
+        <v>123.3453895203915</v>
       </c>
       <c r="C6" t="n">
-        <v>122.4252960494671</v>
+        <v>121.7204979177036</v>
       </c>
       <c r="D6" t="n">
-        <v>147.8228387851369</v>
+        <v>123.3200976507373</v>
       </c>
       <c r="E6" t="n">
-        <v>148.1032543553537</v>
+        <v>147.1729939398813</v>
       </c>
       <c r="F6" t="n">
-        <v>147.3031882777286</v>
+        <v>122.6350084348234</v>
       </c>
       <c r="G6" t="n">
-        <v>127.4177045207253</v>
+        <v>149.3551346924274</v>
       </c>
       <c r="H6" t="n">
-        <v>149.4115725442083</v>
+        <v>124.8012672671081</v>
       </c>
       <c r="I6" t="n">
-        <v>123.7369022041502</v>
+        <v>123.1470844952973</v>
       </c>
       <c r="J6" t="n">
-        <v>126.544651585406</v>
+        <v>125.4209238533954</v>
       </c>
       <c r="K6" t="n">
-        <v>124.437829448192</v>
+        <v>147.6124404033436</v>
       </c>
       <c r="L6" t="n">
-        <v>149.7914432587975</v>
+        <v>149.4996272300493</v>
       </c>
       <c r="M6" t="n">
-        <v>153.1676397214774</v>
+        <v>128.2460279357047</v>
       </c>
       <c r="N6" t="n">
-        <v>126.0549156754726</v>
+        <v>82.29544632640558</v>
       </c>
       <c r="O6" t="n">
-        <v>125.9502523786241</v>
+        <v>149.0728994979742</v>
       </c>
       <c r="P6" t="n">
-        <v>151.6864551055892</v>
+        <v>150.5419444011589</v>
       </c>
       <c r="Q6" t="n">
-        <v>148.4471562754548</v>
+        <v>123.8037162796844</v>
       </c>
       <c r="R6" t="n">
-        <v>147.9593166143687</v>
+        <v>147.431030302013</v>
       </c>
       <c r="S6" t="n">
-        <v>149.2470383416001</v>
+        <v>124.3300471696168</v>
       </c>
       <c r="T6" t="n">
-        <v>124.6831446539321</v>
+        <v>123.9631471185982</v>
       </c>
       <c r="U6" t="n">
-        <v>150.972637131276</v>
+        <v>150.2768624014292</v>
       </c>
       <c r="V6" t="n">
-        <v>149.4988724090146</v>
+        <v>124.8902765288256</v>
       </c>
       <c r="W6" t="n">
-        <v>135.2214215027482</v>
+        <v>134.5287220661517</v>
       </c>
       <c r="X6" t="n">
-        <v>125.606734222162</v>
+        <v>148.6477346311199</v>
       </c>
       <c r="Y6" t="n">
-        <v>134.4339108101659</v>
+        <v>133.6142541282171</v>
       </c>
       <c r="Z6" t="n">
-        <v>125.8393986888893</v>
+        <v>148.8832926908305</v>
       </c>
       <c r="AA6" t="n">
-        <v>149.02239892584</v>
+        <v>148.1852561059415</v>
       </c>
       <c r="AB6" t="n">
-        <v>127.7997777776382</v>
+        <v>128.1757216985619</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.928118753529976</v>
+        <v>4.98095906908649</v>
       </c>
       <c r="C7" t="n">
-        <v>4.106923373320439</v>
+        <v>3.35606746639861</v>
       </c>
       <c r="D7" t="n">
-        <v>5.610677559332926</v>
+        <v>4.955667199432368</v>
       </c>
       <c r="E7" t="n">
-        <v>5.891093129549884</v>
+        <v>4.993374870575179</v>
       </c>
       <c r="F7" t="n">
-        <v>5.091027051924674</v>
+        <v>4.270577983518491</v>
       </c>
       <c r="G7" t="n">
-        <v>9.099331844578726</v>
+        <v>7.175515623121424</v>
       </c>
       <c r="H7" t="n">
-        <v>7.199411318404335</v>
+        <v>6.436836815803272</v>
       </c>
       <c r="I7" t="n">
-        <v>5.418529528003451</v>
+        <v>4.782654043992426</v>
       </c>
       <c r="J7" t="n">
-        <v>8.226278909259314</v>
+        <v>7.056493402090453</v>
       </c>
       <c r="K7" t="n">
-        <v>6.119456772045408</v>
+        <v>5.432821334037573</v>
       </c>
       <c r="L7" t="n">
-        <v>7.579282032993814</v>
+        <v>7.320008160743281</v>
       </c>
       <c r="M7" t="n">
-        <v>10.95547849567361</v>
+        <v>9.881597484399844</v>
       </c>
       <c r="N7" t="n">
-        <v>7.726701808781836</v>
+        <v>82.29544632640558</v>
       </c>
       <c r="O7" t="n">
-        <v>7.622028175339821</v>
+        <v>6.828951694173324</v>
       </c>
       <c r="P7" t="n">
-        <v>9.404146018532742</v>
+        <v>8.298285235201822</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.23499504965103</v>
+        <v>5.439285828379491</v>
       </c>
       <c r="R7" t="n">
-        <v>5.74715538856455</v>
+        <v>5.251411232706992</v>
       </c>
       <c r="S7" t="n">
-        <v>7.034877115796426</v>
+        <v>5.965616718311853</v>
       </c>
       <c r="T7" t="n">
-        <v>6.36477197778555</v>
+        <v>5.598716667293317</v>
       </c>
       <c r="U7" t="n">
-        <v>8.758204090832157</v>
+        <v>8.096287813336371</v>
       </c>
       <c r="V7" t="n">
-        <v>7.286711183210641</v>
+        <v>6.525846077520585</v>
       </c>
       <c r="W7" t="n">
-        <v>10.78193480511618</v>
+        <v>10.04350436872599</v>
       </c>
       <c r="X7" t="n">
-        <v>7.288361546015049</v>
+        <v>6.468115561813854</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.86356553986812</v>
+        <v>9.996033012512704</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.521026012742729</v>
+        <v>6.703673621524409</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.810237700035798</v>
+        <v>6.005637036635507</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.460053552882954</v>
+        <v>9.78214716537842</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.403079327219016</v>
+        <v>5.421883819504566</v>
       </c>
       <c r="C8" t="n">
-        <v>5.849947282378585</v>
+        <v>4.989555372012898</v>
       </c>
       <c r="D8" t="n">
-        <v>7.353701468391072</v>
+        <v>6.589155105046625</v>
       </c>
       <c r="E8" t="n">
-        <v>6.958910718456579</v>
+        <v>5.991858074813727</v>
       </c>
       <c r="F8" t="n">
-        <v>5.763537072864409</v>
+        <v>4.897290135530701</v>
       </c>
       <c r="G8" t="n">
-        <v>11.10529694673455</v>
+        <v>9.0562892676557</v>
       </c>
       <c r="H8" t="n">
-        <v>8.942435227462342</v>
+        <v>8.07032472141753</v>
       </c>
       <c r="I8" t="n">
-        <v>7.161553437061593</v>
+        <v>6.416141949606711</v>
       </c>
       <c r="J8" t="n">
-        <v>9.969302818317438</v>
+        <v>8.68998130770472</v>
       </c>
       <c r="K8" t="n">
-        <v>7.862480681103536</v>
+        <v>7.066309239651847</v>
       </c>
       <c r="L8" t="n">
-        <v>9.322305942051853</v>
+        <v>8.95349606635755</v>
       </c>
       <c r="M8" t="n">
-        <v>12.69850240473114</v>
+        <v>11.51508539001502</v>
       </c>
       <c r="N8" t="n">
-        <v>8.486764490041718</v>
+        <v>82.29544632640558</v>
       </c>
       <c r="O8" t="n">
-        <v>8.652227472459559</v>
+        <v>7.792057233090911</v>
       </c>
       <c r="P8" t="n">
-        <v>10.36813083754851</v>
+        <v>9.199118689791167</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.460752236353633</v>
+        <v>5.645844700354006</v>
       </c>
       <c r="R8" t="n">
-        <v>7.490179297622854</v>
+        <v>6.884899138321268</v>
       </c>
       <c r="S8" t="n">
-        <v>8.77790102485425</v>
+        <v>7.599104623926131</v>
       </c>
       <c r="T8" t="n">
-        <v>8.107795886843627</v>
+        <v>7.232204572907602</v>
       </c>
       <c r="U8" t="n">
-        <v>9.882822434020726</v>
+        <v>9.147924760550673</v>
       </c>
       <c r="V8" t="n">
-        <v>8.681221206003094</v>
+        <v>7.832580765835655</v>
       </c>
       <c r="W8" t="n">
-        <v>12.52520792294854</v>
+        <v>11.67722664540335</v>
       </c>
       <c r="X8" t="n">
-        <v>7.630339255850597</v>
+        <v>6.783975215533515</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.86439778820229</v>
+        <v>12.81400653696415</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.972431659129762</v>
+        <v>7.122445899224899</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.55326160909406</v>
+        <v>7.63912494224977</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.52767564758815</v>
+        <v>12.66136700545767</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.290447625379665</v>
+        <v>8.086674170380393</v>
       </c>
       <c r="C9" t="n">
-        <v>8.819697494130635</v>
+        <v>7.71781116801345</v>
       </c>
       <c r="D9" t="n">
-        <v>10.32345168014308</v>
+        <v>9.317410901047197</v>
       </c>
       <c r="E9" t="n">
-        <v>10.29219014112949</v>
+        <v>9.065232336798962</v>
       </c>
       <c r="F9" t="n">
-        <v>6.690656054886064</v>
+        <v>5.736832886858974</v>
       </c>
       <c r="G9" t="n">
-        <v>13.81210615501812</v>
+        <v>11.53725937974847</v>
       </c>
       <c r="H9" t="n">
-        <v>11.91218543921443</v>
+        <v>10.7985805174181</v>
       </c>
       <c r="I9" t="n">
-        <v>10.13130364881357</v>
+        <v>9.144397745607259</v>
       </c>
       <c r="J9" t="n">
-        <v>12.93905303006953</v>
+        <v>11.41823710370527</v>
       </c>
       <c r="K9" t="n">
-        <v>10.83223089285558</v>
+        <v>9.794565035652409</v>
       </c>
       <c r="L9" t="n">
-        <v>12.29205615380386</v>
+        <v>11.68175186235812</v>
       </c>
       <c r="M9" t="n">
-        <v>15.66825261648381</v>
+        <v>14.24334118601468</v>
       </c>
       <c r="N9" t="n">
-        <v>12.43947592959186</v>
+        <v>82.29544632640558</v>
       </c>
       <c r="O9" t="n">
-        <v>12.78234867246207</v>
+        <v>11.60695226618652</v>
       </c>
       <c r="P9" t="n">
-        <v>14.66179788462744</v>
+        <v>13.16681222538732</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.94776936009058</v>
+        <v>9.801029585006543</v>
       </c>
       <c r="R9" t="n">
-        <v>10.45992950937497</v>
+        <v>9.613154934321836</v>
       </c>
       <c r="S9" t="n">
-        <v>11.74765123660653</v>
+        <v>10.32736041992669</v>
       </c>
       <c r="T9" t="n">
-        <v>11.07754609859577</v>
+        <v>9.960460368908148</v>
       </c>
       <c r="U9" t="n">
-        <v>13.47325002628225</v>
+        <v>12.45898703373811</v>
       </c>
       <c r="V9" t="n">
-        <v>13.55786871626831</v>
+        <v>12.33701830124237</v>
       </c>
       <c r="W9" t="n">
-        <v>15.49470892592636</v>
+        <v>14.40524807034082</v>
       </c>
       <c r="X9" t="n">
-        <v>12.00113566682532</v>
+        <v>10.82985926342869</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.57633966067801</v>
+        <v>14.35777671412754</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.41960181000639</v>
+        <v>10.3081437894115</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.52301182084623</v>
+        <v>10.36738073825033</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.17282767369318</v>
+        <v>14.14389086699326</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.12384717844137</v>
+        <v>39.0187125081626</v>
       </c>
       <c r="C2" t="n">
-        <v>42.11664454293246</v>
+        <v>41.99062466853402</v>
       </c>
       <c r="D2" t="n">
-        <v>39.17871795181073</v>
+        <v>39.07371954467347</v>
       </c>
       <c r="E2" t="n">
-        <v>39.21435283400169</v>
+        <v>39.10777567048267</v>
       </c>
       <c r="F2" t="n">
-        <v>39.19095885297659</v>
+        <v>39.0853011591717</v>
       </c>
       <c r="G2" t="n">
-        <v>39.52958573128264</v>
+        <v>39.33963741891905</v>
       </c>
       <c r="H2" t="n">
-        <v>39.3703157582039</v>
+        <v>39.26580842576393</v>
       </c>
       <c r="I2" t="n">
-        <v>39.15875948471034</v>
+        <v>39.06043877234021</v>
       </c>
       <c r="J2" t="n">
-        <v>39.37678748761559</v>
+        <v>39.24725053690528</v>
       </c>
       <c r="K2" t="n">
-        <v>39.22608729596774</v>
+        <v>39.13657750226416</v>
       </c>
       <c r="L2" t="n">
-        <v>39.23359523199597</v>
+        <v>39.13901068381963</v>
       </c>
       <c r="M2" t="n">
-        <v>39.34283996102673</v>
+        <v>39.23524961666045</v>
       </c>
       <c r="N2" t="n">
-        <v>39.36102472625001</v>
+        <v>39.25625326713715</v>
       </c>
       <c r="O2" t="n">
-        <v>43.32787534108692</v>
+        <v>43.15143214350103</v>
       </c>
       <c r="P2" t="n">
-        <v>39.55055949586473</v>
+        <v>39.4300247180154</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.23162263296408</v>
+        <v>39.12447186213479</v>
       </c>
       <c r="R2" t="n">
-        <v>39.17541807078084</v>
+        <v>39.074729819901</v>
       </c>
       <c r="S2" t="n">
-        <v>39.23846230477346</v>
+        <v>39.12821440292539</v>
       </c>
       <c r="T2" t="n">
-        <v>39.25961384981365</v>
+        <v>39.16531301169723</v>
       </c>
       <c r="U2" t="n">
-        <v>42.78391163673513</v>
+        <v>42.68781274326759</v>
       </c>
       <c r="V2" t="n">
-        <v>39.31740309458161</v>
+        <v>39.21176700222461</v>
       </c>
       <c r="W2" t="n">
-        <v>45.49802111322253</v>
+        <v>45.40451697426484</v>
       </c>
       <c r="X2" t="n">
-        <v>39.44842444762973</v>
+        <v>39.34147841588953</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.715705410342</v>
+        <v>39.60034607702796</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.42062655448035</v>
+        <v>40.29326346021569</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.28374330056511</v>
+        <v>39.18586238635397</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.54248256743843</v>
+        <v>39.48440145327064</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.83637666694629</v>
+        <v>38.74777594954757</v>
       </c>
       <c r="C3" t="n">
-        <v>43.91215837502723</v>
+        <v>43.78631752654078</v>
       </c>
       <c r="D3" t="n">
-        <v>39.2293570948769</v>
+        <v>39.14170253941413</v>
       </c>
       <c r="E3" t="n">
-        <v>39.48266164744251</v>
+        <v>39.38376258512962</v>
       </c>
       <c r="F3" t="n">
-        <v>39.31688747746517</v>
+        <v>39.22452036935286</v>
       </c>
       <c r="G3" t="n">
-        <v>41.71078385986696</v>
+        <v>41.02132524289379</v>
       </c>
       <c r="H3" t="n">
-        <v>40.60688493357185</v>
+        <v>40.52274674174684</v>
       </c>
       <c r="I3" t="n">
-        <v>39.08752321647422</v>
+        <v>39.04767757880217</v>
       </c>
       <c r="J3" t="n">
-        <v>40.63336446408849</v>
+        <v>40.37191703642478</v>
       </c>
       <c r="K3" t="n">
-        <v>39.56320877516188</v>
+        <v>39.58555040327733</v>
       </c>
       <c r="L3" t="n">
-        <v>39.61572485320136</v>
+        <v>39.60199944214133</v>
       </c>
       <c r="M3" t="n">
-        <v>40.40278972828034</v>
+        <v>40.2951258763574</v>
       </c>
       <c r="N3" t="n">
-        <v>40.53221691177359</v>
+        <v>40.44619355861509</v>
       </c>
       <c r="O3" t="n">
-        <v>47.35621740196849</v>
+        <v>47.14559291759005</v>
       </c>
       <c r="P3" t="n">
-        <v>41.86767326082254</v>
+        <v>41.66967258196713</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.60296573589877</v>
+        <v>39.5000175852224</v>
       </c>
       <c r="R3" t="n">
-        <v>39.20732980751938</v>
+        <v>39.1505631697971</v>
       </c>
       <c r="S3" t="n">
-        <v>39.64884978745268</v>
+        <v>39.52399591223465</v>
       </c>
       <c r="T3" t="n">
-        <v>39.80847848675855</v>
+        <v>39.79733477634767</v>
       </c>
       <c r="U3" t="n">
-        <v>46.19564927486729</v>
+        <v>46.12491588194153</v>
       </c>
       <c r="V3" t="n">
-        <v>40.20879768420931</v>
+        <v>40.11664025745112</v>
       </c>
       <c r="W3" t="n">
-        <v>51.99465384872513</v>
+        <v>51.92983134334995</v>
       </c>
       <c r="X3" t="n">
-        <v>41.15376353795585</v>
+        <v>41.05221252790591</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.05948968395287</v>
+        <v>42.89792710907309</v>
       </c>
       <c r="Z3" t="n">
-        <v>41.68845812591286</v>
+        <v>41.5570542253121</v>
       </c>
       <c r="AA3" t="n">
-        <v>39.97850103511615</v>
+        <v>39.94167000696316</v>
       </c>
       <c r="AB3" t="n">
-        <v>41.82123346035704</v>
+        <v>42.06362087464249</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.062176236610334</v>
+        <v>1.557468059291157</v>
       </c>
       <c r="C4" t="n">
-        <v>2.337681514150295</v>
+        <v>1.827563435435186</v>
       </c>
       <c r="D4" t="n">
-        <v>2.681966863619856</v>
+        <v>2.178797841168372</v>
       </c>
       <c r="E4" t="n">
-        <v>3.084479250822596</v>
+        <v>2.563477448774701</v>
       </c>
       <c r="F4" t="n">
-        <v>2.820233473381339</v>
+        <v>2.309617504731642</v>
       </c>
       <c r="G4" t="n">
-        <v>6.645179839908174</v>
+        <v>5.18246255903791</v>
       </c>
       <c r="H4" t="n">
-        <v>4.846152226176698</v>
+        <v>4.348530118336388</v>
       </c>
       <c r="I4" t="n">
-        <v>2.456526796372423</v>
+        <v>2.028785408206974</v>
       </c>
       <c r="J4" t="n">
-        <v>4.91944967197299</v>
+        <v>4.139469767718275</v>
       </c>
       <c r="K4" t="n">
-        <v>3.21702539684815</v>
+        <v>2.888807388244395</v>
       </c>
       <c r="L4" t="n">
-        <v>3.301830988108342</v>
+        <v>2.916291293232392</v>
       </c>
       <c r="M4" t="n">
-        <v>4.547238750367237</v>
+        <v>4.011945298599658</v>
       </c>
       <c r="N4" t="n">
-        <v>4.741205746170785</v>
+        <v>54.94422479630336</v>
       </c>
       <c r="O4" t="n">
-        <v>5.344334171310978</v>
+        <v>4.830670144207092</v>
       </c>
       <c r="P4" t="n">
-        <v>6.882088159271738</v>
+        <v>6.203428682542993</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.279549574602937</v>
+        <v>2.75206861411376</v>
       </c>
       <c r="R4" t="n">
-        <v>2.644693189366815</v>
+        <v>2.190209364613127</v>
       </c>
       <c r="S4" t="n">
-        <v>3.356806814094286</v>
+        <v>2.794342333997283</v>
       </c>
       <c r="T4" t="n">
-        <v>3.595723245514735</v>
+        <v>3.213388186278484</v>
       </c>
       <c r="U4" t="n">
-        <v>4.76996899301622</v>
+        <v>4.270697422438682</v>
       </c>
       <c r="V4" t="n">
-        <v>4.249474080606403</v>
+        <v>3.74153976634125</v>
       </c>
       <c r="W4" t="n">
-        <v>7.48717126002818</v>
+        <v>6.991915564715131</v>
       </c>
       <c r="X4" t="n">
-        <v>5.728425805013771</v>
+        <v>5.203257466719892</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.72572289057265</v>
+        <v>8.104817807344956</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.540261341893163</v>
+        <v>3.022856706839824</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.868276491848073</v>
+        <v>3.445502826205694</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.760856480985115</v>
+        <v>6.776402166398481</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.484116354749934</v>
+        <v>5.893835980786638</v>
       </c>
       <c r="C5" t="n">
-        <v>11.65828659160802</v>
+        <v>10.96118837917714</v>
       </c>
       <c r="D5" t="n">
-        <v>18.1535041931161</v>
+        <v>17.57678855422574</v>
       </c>
       <c r="E5" t="n">
-        <v>24.74226017259321</v>
+        <v>23.86214248900789</v>
       </c>
       <c r="F5" t="n">
-        <v>20.68524140521785</v>
+        <v>19.97308776589713</v>
       </c>
       <c r="G5" t="n">
-        <v>76.46811014776738</v>
+        <v>61.24580960465173</v>
       </c>
       <c r="H5" t="n">
-        <v>61.65685618088639</v>
+        <v>61.18422669648348</v>
       </c>
       <c r="I5" t="n">
-        <v>14.48270247170939</v>
+        <v>15.31771914766339</v>
       </c>
       <c r="J5" t="n">
-        <v>52.73600491698841</v>
+        <v>47.95175873081081</v>
       </c>
       <c r="K5" t="n">
-        <v>25.42704021389238</v>
+        <v>27.66124496265175</v>
       </c>
       <c r="L5" t="n">
-        <v>26.37327729980012</v>
+        <v>27.67228702861029</v>
       </c>
       <c r="M5" t="n">
-        <v>49.00417511835832</v>
+        <v>47.87819448533456</v>
       </c>
       <c r="N5" t="n">
-        <v>50.51609787791914</v>
+        <v>54.94422479630336</v>
       </c>
       <c r="O5" t="n">
-        <v>57.34748780083405</v>
+        <v>56.6164261974714</v>
       </c>
       <c r="P5" t="n">
-        <v>84.38871560201082</v>
+        <v>80.98682608218822</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.66294990810224</v>
+        <v>25.69144143946107</v>
       </c>
       <c r="R5" t="n">
-        <v>18.28409852971608</v>
+        <v>18.63381823344134</v>
       </c>
       <c r="S5" t="n">
-        <v>26.51044108750297</v>
+        <v>25.02313872002179</v>
       </c>
       <c r="T5" t="n">
-        <v>35.22859734494767</v>
+        <v>36.87285861911097</v>
       </c>
       <c r="U5" t="n">
-        <v>50.56662546835778</v>
+        <v>50.06866874284655</v>
       </c>
       <c r="V5" t="n">
-        <v>40.49091547332844</v>
+        <v>39.81428203785302</v>
       </c>
       <c r="W5" t="n">
-        <v>103.2313247846855</v>
+        <v>102.8023634016107</v>
       </c>
       <c r="X5" t="n">
-        <v>71.7748725567486</v>
+        <v>70.81105233405194</v>
       </c>
       <c r="Y5" t="n">
-        <v>124.2021452646122</v>
+        <v>121.5754496476911</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.30082650038933</v>
+        <v>28.51488006632844</v>
       </c>
       <c r="AA5" t="n">
-        <v>38.91395700791568</v>
+        <v>39.77244567059363</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.49816260224225</v>
+        <v>105.7676913237886</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>113.3144745113888</v>
+        <v>134.8467363179406</v>
       </c>
       <c r="C6" t="n">
-        <v>135.7208494335582</v>
+        <v>135.1168316940845</v>
       </c>
       <c r="D6" t="n">
-        <v>113.9342651383983</v>
+        <v>135.4680660998178</v>
       </c>
       <c r="E6" t="n">
-        <v>136.4676471702304</v>
+        <v>113.8003250080538</v>
       </c>
       <c r="F6" t="n">
-        <v>136.2034013927891</v>
+        <v>113.5464650640107</v>
       </c>
       <c r="G6" t="n">
-        <v>117.8974781146866</v>
+        <v>116.4193101183171</v>
       </c>
       <c r="H6" t="n">
-        <v>138.2293201455846</v>
+        <v>115.5853776776155</v>
       </c>
       <c r="I6" t="n">
-        <v>135.8396947157804</v>
+        <v>135.3180536668565</v>
       </c>
       <c r="J6" t="n">
-        <v>116.1717479467514</v>
+        <v>137.4287380263677</v>
       </c>
       <c r="K6" t="n">
-        <v>136.600193316256</v>
+        <v>114.1256549475235</v>
       </c>
       <c r="L6" t="n">
-        <v>114.5541292628868</v>
+        <v>136.2055595518819</v>
       </c>
       <c r="M6" t="n">
-        <v>137.930406669775</v>
+        <v>115.2487928578788</v>
       </c>
       <c r="N6" t="n">
-        <v>116.0007806945642</v>
+        <v>54.94422479630336</v>
       </c>
       <c r="O6" t="n">
-        <v>116.6039091197044</v>
+        <v>138.1828125638557</v>
       </c>
       <c r="P6" t="n">
-        <v>111.7019702560927</v>
+        <v>111.0104312199936</v>
       </c>
       <c r="Q6" t="n">
-        <v>136.6627174940109</v>
+        <v>113.9889161733929</v>
       </c>
       <c r="R6" t="n">
-        <v>136.0278611087747</v>
+        <v>135.4794776232626</v>
       </c>
       <c r="S6" t="n">
-        <v>114.6091050888728</v>
+        <v>114.0311898932764</v>
       </c>
       <c r="T6" t="n">
-        <v>114.8480215202932</v>
+        <v>114.4502357455576</v>
       </c>
       <c r="U6" t="n">
-        <v>116.044031611388</v>
+        <v>137.5824346580295</v>
       </c>
       <c r="V6" t="n">
-        <v>137.6326420000143</v>
+        <v>114.9783873256203</v>
       </c>
       <c r="W6" t="n">
-        <v>124.4335050355529</v>
+        <v>123.9213824398707</v>
       </c>
       <c r="X6" t="n">
-        <v>116.9807240797923</v>
+        <v>138.4925257253693</v>
       </c>
       <c r="Y6" t="n">
-        <v>124.8850989918215</v>
+        <v>124.2499301702555</v>
       </c>
       <c r="Z6" t="n">
-        <v>114.7925596166717</v>
+        <v>136.3121249654892</v>
       </c>
       <c r="AA6" t="n">
-        <v>137.251444411256</v>
+        <v>114.6823503854848</v>
       </c>
       <c r="AB6" t="n">
-        <v>118.0335777792342</v>
+        <v>118.0379162478261</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.005950187686247</v>
+        <v>2.471284658119616</v>
       </c>
       <c r="C7" t="n">
-        <v>3.281455465226207</v>
+        <v>2.741380034263653</v>
       </c>
       <c r="D7" t="n">
-        <v>3.625740814695766</v>
+        <v>3.092614439996836</v>
       </c>
       <c r="E7" t="n">
-        <v>4.028253201898508</v>
+        <v>3.477294047603169</v>
       </c>
       <c r="F7" t="n">
-        <v>3.764007424457248</v>
+        <v>3.223434103560115</v>
       </c>
       <c r="G7" t="n">
-        <v>7.588953790984073</v>
+        <v>6.096279157866382</v>
       </c>
       <c r="H7" t="n">
-        <v>5.789926177252609</v>
+        <v>5.26234671716486</v>
       </c>
       <c r="I7" t="n">
-        <v>3.400300747448336</v>
+        <v>2.942602007035445</v>
       </c>
       <c r="J7" t="n">
-        <v>5.863223623048897</v>
+        <v>5.053286366546746</v>
       </c>
       <c r="K7" t="n">
-        <v>4.160799347924064</v>
+        <v>3.802623987072853</v>
       </c>
       <c r="L7" t="n">
-        <v>4.245604939184252</v>
+        <v>3.830107892060856</v>
       </c>
       <c r="M7" t="n">
-        <v>5.49101270144315</v>
+        <v>4.925761897428128</v>
       </c>
       <c r="N7" t="n">
-        <v>5.684979697246693</v>
+        <v>54.94422479630336</v>
       </c>
       <c r="O7" t="n">
-        <v>6.288104219851236</v>
+        <v>5.744481841614486</v>
       </c>
       <c r="P7" t="n">
-        <v>7.825858207812002</v>
+        <v>7.117240379950386</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.223323525678849</v>
+        <v>3.665885212942229</v>
       </c>
       <c r="R7" t="n">
-        <v>3.588467140442728</v>
+        <v>3.104025963441586</v>
       </c>
       <c r="S7" t="n">
-        <v>4.300580765170197</v>
+        <v>3.708158932825742</v>
       </c>
       <c r="T7" t="n">
-        <v>4.539497196590648</v>
+        <v>4.127204785106949</v>
       </c>
       <c r="U7" t="n">
-        <v>5.72820279578742</v>
+        <v>5.203148309684133</v>
       </c>
       <c r="V7" t="n">
-        <v>5.193248031682316</v>
+        <v>4.655356365169717</v>
       </c>
       <c r="W7" t="n">
-        <v>8.430945211104092</v>
+        <v>7.905732163543586</v>
       </c>
       <c r="X7" t="n">
-        <v>6.672199756089682</v>
+        <v>6.117074065548367</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.691261185241832</v>
+        <v>9.041103383114754</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.484035292969074</v>
+        <v>3.93667330566829</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.812050442923984</v>
+        <v>4.359319425034162</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.704630432061029</v>
+        <v>7.690218765226948</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.334572972053858</v>
+        <v>2.765179260551403</v>
       </c>
       <c r="C8" t="n">
-        <v>4.590549981106368</v>
+        <v>3.947169998737124</v>
       </c>
       <c r="D8" t="n">
-        <v>4.934835330575929</v>
+        <v>4.298404404470308</v>
       </c>
       <c r="E8" t="n">
-        <v>4.815275443220981</v>
+        <v>4.197526631286538</v>
       </c>
       <c r="F8" t="n">
-        <v>4.245376245376391</v>
+        <v>3.659391345700274</v>
       </c>
       <c r="G8" t="n">
-        <v>9.101355507432489</v>
+        <v>7.491156566004625</v>
       </c>
       <c r="H8" t="n">
-        <v>7.099020693132772</v>
+        <v>6.468136681638327</v>
       </c>
       <c r="I8" t="n">
-        <v>4.709395263328495</v>
+        <v>4.148391971508916</v>
       </c>
       <c r="J8" t="n">
-        <v>7.172318138929057</v>
+        <v>6.25907633102021</v>
       </c>
       <c r="K8" t="n">
-        <v>5.469893863804223</v>
+        <v>5.008413951546324</v>
       </c>
       <c r="L8" t="n">
-        <v>5.554699455064416</v>
+        <v>5.035897856534325</v>
       </c>
       <c r="M8" t="n">
-        <v>6.800107217322461</v>
+        <v>6.131551861903075</v>
       </c>
       <c r="N8" t="n">
-        <v>6.234044591399478</v>
+        <v>54.94422479630336</v>
       </c>
       <c r="O8" t="n">
-        <v>7.046035754884761</v>
+        <v>6.437659659743441</v>
       </c>
       <c r="P8" t="n">
-        <v>8.532592438944047</v>
+        <v>7.762801747208059</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.359261237123375</v>
+        <v>3.780571564094848</v>
       </c>
       <c r="R8" t="n">
-        <v>4.897561656322886</v>
+        <v>4.309815927915062</v>
       </c>
       <c r="S8" t="n">
-        <v>5.609675281050354</v>
+        <v>4.913948897299218</v>
       </c>
       <c r="T8" t="n">
-        <v>5.84859171247081</v>
+        <v>5.332994749580418</v>
       </c>
       <c r="U8" t="n">
-        <v>6.560388859014745</v>
+        <v>5.964721015623345</v>
       </c>
       <c r="V8" t="n">
-        <v>6.228124475512439</v>
+        <v>5.608637969499948</v>
       </c>
       <c r="W8" t="n">
-        <v>9.740232415976035</v>
+        <v>9.111701340264849</v>
       </c>
       <c r="X8" t="n">
-        <v>6.897999648848183</v>
+        <v>6.315337437784333</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.96553761501535</v>
+        <v>11.14849278056514</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.794445311712317</v>
+        <v>4.213628983698382</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.121144958804144</v>
+        <v>5.565109389507629</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.03790965552778</v>
+        <v>9.848559685573521</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.377737821468171</v>
+        <v>4.658499571408434</v>
       </c>
       <c r="C9" t="n">
-        <v>6.645044002933218</v>
+        <v>5.849107617479237</v>
       </c>
       <c r="D9" t="n">
-        <v>6.989329352402781</v>
+        <v>6.200342023212416</v>
       </c>
       <c r="E9" t="n">
-        <v>7.162938533774889</v>
+        <v>6.37257134895455</v>
       </c>
       <c r="F9" t="n">
-        <v>4.841223516262607</v>
+        <v>4.209128262730345</v>
       </c>
       <c r="G9" t="n">
-        <v>10.95254284521598</v>
+        <v>9.204007115042661</v>
       </c>
       <c r="H9" t="n">
-        <v>9.153514714959625</v>
+        <v>8.370074300380438</v>
       </c>
       <c r="I9" t="n">
-        <v>6.76388928515534</v>
+        <v>6.050329590251029</v>
       </c>
       <c r="J9" t="n">
-        <v>9.226812160755916</v>
+        <v>8.161013949762316</v>
       </c>
       <c r="K9" t="n">
-        <v>7.524387885631072</v>
+        <v>6.910351570288437</v>
       </c>
       <c r="L9" t="n">
-        <v>7.609193476891269</v>
+        <v>6.937835475276431</v>
       </c>
       <c r="M9" t="n">
-        <v>8.854601239150167</v>
+        <v>8.033489480643704</v>
       </c>
       <c r="N9" t="n">
-        <v>9.0485682349537</v>
+        <v>54.94422479630336</v>
       </c>
       <c r="O9" t="n">
-        <v>9.980378868702751</v>
+        <v>9.15727151764713</v>
       </c>
       <c r="P9" t="n">
-        <v>11.58961548546369</v>
+        <v>10.59637467988171</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.586912579910756</v>
+        <v>6.773613170118503</v>
       </c>
       <c r="R9" t="n">
-        <v>6.952055678149741</v>
+        <v>6.211753546657172</v>
       </c>
       <c r="S9" t="n">
-        <v>7.664169302877212</v>
+        <v>6.815886516041322</v>
       </c>
       <c r="T9" t="n">
-        <v>7.90308573429766</v>
+        <v>7.234932368322527</v>
       </c>
       <c r="U9" t="n">
-        <v>9.099095825392411</v>
+        <v>8.314710581424061</v>
       </c>
       <c r="V9" t="n">
-        <v>9.701353636153257</v>
+        <v>8.825335750024292</v>
       </c>
       <c r="W9" t="n">
-        <v>11.7945337488111</v>
+        <v>11.01345974675917</v>
       </c>
       <c r="X9" t="n">
-        <v>10.03578829379669</v>
+        <v>9.22480164876395</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.05484972294884</v>
+        <v>12.14883096633033</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.249656285093059</v>
+        <v>6.489413752594052</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.175638980630996</v>
+        <v>7.467047008249741</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.06821896976804</v>
+        <v>10.79794634844252</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
@@ -798,7 +798,7 @@
         <v>9.841604237983002</v>
       </c>
       <c r="N4" t="n">
-        <v>112.7863197477354</v>
+        <v>7.171533386977773</v>
       </c>
       <c r="O4" t="n">
         <v>6.383930261660264</v>
@@ -974,7 +974,7 @@
         <v>163.1548092868801</v>
       </c>
       <c r="N6" t="n">
-        <v>112.7863197477354</v>
+        <v>134.9386897789306</v>
       </c>
       <c r="O6" t="n">
         <v>134.1510834482693</v>
@@ -1062,7 +1062,7 @@
         <v>11.18555173924851</v>
       </c>
       <c r="N7" t="n">
-        <v>112.7863197477354</v>
+        <v>8.515480888243264</v>
       </c>
       <c r="O7" t="n">
         <v>7.727862772552006</v>
@@ -1150,7 +1150,7 @@
         <v>13.21361175273829</v>
       </c>
       <c r="N8" t="n">
-        <v>112.7863197477354</v>
+        <v>9.416736327233748</v>
       </c>
       <c r="O8" t="n">
         <v>8.938788881777811</v>
@@ -1238,7 +1238,7 @@
         <v>16.95264576696825</v>
       </c>
       <c r="N9" t="n">
-        <v>112.7863197477354</v>
+        <v>14.282574915963</v>
       </c>
       <c r="O9" t="n">
         <v>14.03202860559393</v>
@@ -1658,7 +1658,7 @@
         <v>2.791647448925112</v>
       </c>
       <c r="N4" t="n">
-        <v>51.02917605539093</v>
+        <v>3.821390688380156</v>
       </c>
       <c r="O4" t="n">
         <v>4.029151129765974</v>
@@ -1834,7 +1834,7 @@
         <v>113.9599412792114</v>
       </c>
       <c r="N6" t="n">
-        <v>51.02917605539093</v>
+        <v>114.995445598669</v>
       </c>
       <c r="O6" t="n">
         <v>137.1788435050002</v>
@@ -1922,7 +1922,7 @@
         <v>3.628664666144978</v>
       </c>
       <c r="N7" t="n">
-        <v>51.02917605539093</v>
+        <v>4.658407905600011</v>
       </c>
       <c r="O7" t="n">
         <v>4.866167462408574</v>
@@ -2010,7 +2010,7 @@
         <v>4.651945095824143</v>
       </c>
       <c r="N8" t="n">
-        <v>51.02917605539093</v>
+        <v>5.063231413689012</v>
       </c>
       <c r="O8" t="n">
         <v>5.440949186507822</v>
@@ -2098,7 +2098,7 @@
         <v>5.991628479269538</v>
       </c>
       <c r="N9" t="n">
-        <v>51.02917605539093</v>
+        <v>7.021371718724583</v>
       </c>
       <c r="O9" t="n">
         <v>7.472745744944564</v>
@@ -2518,7 +2518,7 @@
         <v>8.97645773632274</v>
       </c>
       <c r="N4" t="n">
-        <v>97.07504839063225</v>
+        <v>6.592961270371503</v>
       </c>
       <c r="O4" t="n">
         <v>6.40488626355739</v>
@@ -2694,7 +2694,7 @@
         <v>152.3597575286353</v>
       </c>
       <c r="N6" t="n">
-        <v>97.07504839063225</v>
+        <v>126.1213177036418</v>
       </c>
       <c r="O6" t="n">
         <v>125.9348709339256</v>
@@ -2782,7 +2782,7 @@
         <v>10.17701870566254</v>
       </c>
       <c r="N7" t="n">
-        <v>97.07504839063225</v>
+        <v>7.79352223971131</v>
       </c>
       <c r="O7" t="n">
         <v>7.605433544493497</v>
@@ -2870,7 +2870,7 @@
         <v>11.9504832091579</v>
       </c>
       <c r="N8" t="n">
-        <v>97.07504839063225</v>
+        <v>8.574404529322035</v>
       </c>
       <c r="O8" t="n">
         <v>8.659099732382975</v>
@@ -2958,7 +2958,7 @@
         <v>14.70378720394369</v>
       </c>
       <c r="N9" t="n">
-        <v>97.07504839063225</v>
+        <v>12.32029073799246</v>
       </c>
       <c r="O9" t="n">
         <v>12.56650561667998</v>
@@ -3166,43 +3166,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.52516644115882</v>
+        <v>39.52516644115886</v>
       </c>
       <c r="C2" t="n">
-        <v>42.39139325379595</v>
+        <v>42.39139325379598</v>
       </c>
       <c r="D2" t="n">
         <v>39.60418783679205</v>
       </c>
       <c r="E2" t="n">
-        <v>39.485007659783</v>
+        <v>39.48500765978303</v>
       </c>
       <c r="F2" t="n">
-        <v>39.506473242957</v>
+        <v>39.50647324295704</v>
       </c>
       <c r="G2" t="n">
-        <v>39.66964391663458</v>
+        <v>39.6696439166346</v>
       </c>
       <c r="H2" t="n">
-        <v>39.62048311942833</v>
+        <v>39.62048311942835</v>
       </c>
       <c r="I2" t="n">
-        <v>39.51926893015051</v>
+        <v>39.51926893015055</v>
       </c>
       <c r="J2" t="n">
-        <v>39.67245924222181</v>
+        <v>39.67245924222184</v>
       </c>
       <c r="K2" t="n">
-        <v>39.53152046818629</v>
+        <v>39.53152046818633</v>
       </c>
       <c r="L2" t="n">
         <v>39.68375781275456</v>
       </c>
       <c r="M2" t="n">
-        <v>39.86749633953338</v>
+        <v>39.86749633953339</v>
       </c>
       <c r="N2" t="n">
-        <v>39.63287865255444</v>
+        <v>39.63287865255445</v>
       </c>
       <c r="O2" t="n">
         <v>43.70955152745518</v>
@@ -3211,40 +3211,40 @@
         <v>39.81152916748575</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.55947358515913</v>
+        <v>39.55947358515915</v>
       </c>
       <c r="R2" t="n">
-        <v>39.5450656074475</v>
+        <v>39.54506560744754</v>
       </c>
       <c r="S2" t="n">
-        <v>39.63907735223471</v>
+        <v>39.63907735223476</v>
       </c>
       <c r="T2" t="n">
-        <v>39.60770542464211</v>
+        <v>39.6077054246421</v>
       </c>
       <c r="U2" t="n">
-        <v>43.23484248841925</v>
+        <v>43.23484248841926</v>
       </c>
       <c r="V2" t="n">
-        <v>39.62192646670736</v>
+        <v>39.62192646670738</v>
       </c>
       <c r="W2" t="n">
         <v>45.86388887633561</v>
       </c>
       <c r="X2" t="n">
-        <v>39.69865880047913</v>
+        <v>39.69865880047916</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.92315568933982</v>
+        <v>39.92315568933986</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.90444163275986</v>
+        <v>40.9044416327599</v>
       </c>
       <c r="AA2" t="n">
         <v>39.59853119700507</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.93359475512397</v>
+        <v>39.93359475512396</v>
       </c>
     </row>
     <row r="3">
@@ -3254,82 +3254,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.49942246415425</v>
+        <v>40.49942246415424</v>
       </c>
       <c r="C3" t="n">
-        <v>44.74370672329611</v>
+        <v>44.74370672329614</v>
       </c>
       <c r="D3" t="n">
-        <v>41.07480583361782</v>
+        <v>41.07480583361777</v>
       </c>
       <c r="E3" t="n">
-        <v>40.21833999158858</v>
+        <v>40.21833999158861</v>
       </c>
       <c r="F3" t="n">
-        <v>40.37547609442456</v>
+        <v>40.37547609442451</v>
       </c>
       <c r="G3" t="n">
-        <v>41.52603339898883</v>
+        <v>41.52603339898886</v>
       </c>
       <c r="H3" t="n">
         <v>41.19894458725358</v>
       </c>
       <c r="I3" t="n">
-        <v>40.46887711326898</v>
+        <v>40.46887711326899</v>
       </c>
       <c r="J3" t="n">
-        <v>41.55235983617516</v>
+        <v>41.55235983617515</v>
       </c>
       <c r="K3" t="n">
         <v>40.54478440945382</v>
       </c>
       <c r="L3" t="n">
-        <v>41.6357193828505</v>
+        <v>41.63571938285051</v>
       </c>
       <c r="M3" t="n">
-        <v>42.95989297352914</v>
+        <v>42.95989297352913</v>
       </c>
       <c r="N3" t="n">
         <v>41.27737279615113</v>
       </c>
       <c r="O3" t="n">
-        <v>48.29608536876131</v>
+        <v>48.29608536876134</v>
       </c>
       <c r="P3" t="n">
-        <v>42.53457282655433</v>
+        <v>42.53457282655437</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.75067464390095</v>
+        <v>40.75067464390096</v>
       </c>
       <c r="R3" t="n">
-        <v>40.65549875103913</v>
+        <v>40.65549875103915</v>
       </c>
       <c r="S3" t="n">
-        <v>41.3099920838601</v>
+        <v>41.30999208386007</v>
       </c>
       <c r="T3" t="n">
         <v>41.10131768761416</v>
       </c>
       <c r="U3" t="n">
-        <v>47.71731550893127</v>
+        <v>47.71731550893129</v>
       </c>
       <c r="V3" t="n">
-        <v>41.18156431810392</v>
+        <v>41.18156431810397</v>
       </c>
       <c r="W3" t="n">
-        <v>52.84887097790757</v>
+        <v>52.84887097790752</v>
       </c>
       <c r="X3" t="n">
-        <v>41.748383424414</v>
+        <v>41.74838342441397</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.34492498688849</v>
+        <v>43.3449249868885</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.31074594526349</v>
+        <v>43.31074594526353</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.02954439578259</v>
+        <v>41.02954439578262</v>
       </c>
       <c r="AB3" t="n">
         <v>43.42720124401605</v>
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.222964260526822</v>
+        <v>4.222964260526798</v>
       </c>
       <c r="C4" t="n">
-        <v>3.205721481322426</v>
+        <v>3.205721481322386</v>
       </c>
       <c r="D4" t="n">
-        <v>5.115547275841649</v>
+        <v>5.115547275841614</v>
       </c>
       <c r="E4" t="n">
-        <v>3.769352350934473</v>
+        <v>3.769352350934441</v>
       </c>
       <c r="F4" t="n">
-        <v>4.011815987541216</v>
+        <v>4.011815987541197</v>
       </c>
       <c r="G4" t="n">
-        <v>5.854903808947751</v>
+        <v>5.85490380894772</v>
       </c>
       <c r="H4" t="n">
-        <v>5.299609989419555</v>
+        <v>5.299609989419528</v>
       </c>
       <c r="I4" t="n">
-        <v>4.156349160698782</v>
+        <v>4.156349160698746</v>
       </c>
       <c r="J4" t="n">
-        <v>5.887368782488545</v>
+        <v>5.887368782488527</v>
       </c>
       <c r="K4" t="n">
-        <v>4.294735918798994</v>
+        <v>4.294735918798962</v>
       </c>
       <c r="L4" t="n">
-        <v>6.014326758335875</v>
+        <v>6.014326758335825</v>
       </c>
       <c r="M4" t="n">
-        <v>8.083912710864411</v>
+        <v>8.08391271086438</v>
       </c>
       <c r="N4" t="n">
-        <v>72.47327460659885</v>
+        <v>5.439623238305315</v>
       </c>
       <c r="O4" t="n">
-        <v>6.078298835548317</v>
+        <v>6.078298835548283</v>
       </c>
       <c r="P4" t="n">
-        <v>7.457562987751585</v>
+        <v>7.457562987751565</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.610479234076273</v>
+        <v>4.610479234076251</v>
       </c>
       <c r="R4" t="n">
-        <v>4.447734497826158</v>
+        <v>4.447734497826127</v>
       </c>
       <c r="S4" t="n">
-        <v>5.509640402737286</v>
+        <v>5.509640402737253</v>
       </c>
       <c r="T4" t="n">
-        <v>5.155280048778729</v>
+        <v>5.155280048778716</v>
       </c>
       <c r="U4" t="n">
-        <v>6.463778170151759</v>
+        <v>6.46377817015175</v>
       </c>
       <c r="V4" t="n">
-        <v>5.32009295074772</v>
+        <v>5.320092950747717</v>
       </c>
       <c r="W4" t="n">
-        <v>8.092112008827675</v>
+        <v>8.092112008827653</v>
       </c>
       <c r="X4" t="n">
-        <v>6.18264026947787</v>
+        <v>6.182640269477827</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.705071365199748</v>
+        <v>8.705071365199736</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.340965215343582</v>
+        <v>5.340965215343543</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.051652927265338</v>
+        <v>5.0516529272653</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.799741183182974</v>
+        <v>8.799741183182942</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46.18547807401734</v>
+        <v>46.18547807401733</v>
       </c>
       <c r="C5" t="n">
-        <v>30.85201588081559</v>
+        <v>30.85201588081557</v>
       </c>
       <c r="D5" t="n">
-        <v>67.88197560390931</v>
+        <v>67.88197560390927</v>
       </c>
       <c r="E5" t="n">
-        <v>41.02981161290825</v>
+        <v>41.02981161290816</v>
       </c>
       <c r="F5" t="n">
-        <v>47.35748105973634</v>
+        <v>47.35748105973629</v>
       </c>
       <c r="G5" t="n">
-        <v>72.70042241616659</v>
+        <v>72.70042241616666</v>
       </c>
       <c r="H5" t="n">
-        <v>75.19953727905462</v>
+        <v>75.19953727905485</v>
       </c>
       <c r="I5" t="n">
-        <v>50.9904323411649</v>
+        <v>50.99043234116485</v>
       </c>
       <c r="J5" t="n">
-        <v>76.49378877420121</v>
+        <v>76.49378877420111</v>
       </c>
       <c r="K5" t="n">
-        <v>47.46158288944374</v>
+        <v>47.46158288944367</v>
       </c>
       <c r="L5" t="n">
-        <v>80.16047329118092</v>
+        <v>80.16047329118064</v>
       </c>
       <c r="M5" t="n">
-        <v>125.0496486823745</v>
+        <v>125.049648682374</v>
       </c>
       <c r="N5" t="n">
         <v>72.47327460659885</v>
       </c>
       <c r="O5" t="n">
-        <v>72.99219570800994</v>
+        <v>72.99219570801006</v>
       </c>
       <c r="P5" t="n">
-        <v>98.91998404192509</v>
+        <v>98.91998404192523</v>
       </c>
       <c r="Q5" t="n">
-        <v>56.35615611456873</v>
+        <v>56.35615611456862</v>
       </c>
       <c r="R5" t="n">
-        <v>57.44453000296306</v>
+        <v>57.44453000296301</v>
       </c>
       <c r="S5" t="n">
-        <v>67.6892816833</v>
+        <v>67.6892816832999</v>
       </c>
       <c r="T5" t="n">
-        <v>69.31367815220433</v>
+        <v>69.31367815220426</v>
       </c>
       <c r="U5" t="n">
-        <v>85.81299546139728</v>
+        <v>85.81299546139788</v>
       </c>
       <c r="V5" t="n">
-        <v>61.14682529939419</v>
+        <v>61.14682529939428</v>
       </c>
       <c r="W5" t="n">
-        <v>118.2070701463302</v>
+        <v>118.2070701463298</v>
       </c>
       <c r="X5" t="n">
-        <v>86.40993805747203</v>
+        <v>86.4099380574722</v>
       </c>
       <c r="Y5" t="n">
-        <v>128.3037535659287</v>
+        <v>128.3037535659286</v>
       </c>
       <c r="Z5" t="n">
-        <v>61.57923341187643</v>
+        <v>61.57923341187627</v>
       </c>
       <c r="AA5" t="n">
-        <v>64.21792624486309</v>
+        <v>64.21792624486305</v>
       </c>
       <c r="AB5" t="n">
-        <v>144.0771113602306</v>
+        <v>144.0771113602302</v>
       </c>
     </row>
     <row r="6">
@@ -3518,43 +3518,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>137.7415479045756</v>
+        <v>137.7415479045755</v>
       </c>
       <c r="C6" t="n">
-        <v>114.551516707449</v>
+        <v>114.5515167074489</v>
       </c>
       <c r="D6" t="n">
-        <v>138.6341309198903</v>
+        <v>138.6341309198902</v>
       </c>
       <c r="E6" t="n">
-        <v>137.2879359949832</v>
+        <v>137.287935994983</v>
       </c>
       <c r="F6" t="n">
-        <v>115.3576112136677</v>
+        <v>115.3576112136678</v>
       </c>
       <c r="G6" t="n">
-        <v>117.2006990350743</v>
+        <v>117.2006990350742</v>
       </c>
       <c r="H6" t="n">
-        <v>116.645405215546</v>
+        <v>116.6454052155461</v>
       </c>
       <c r="I6" t="n">
         <v>115.5021443868253</v>
       </c>
       <c r="J6" t="n">
-        <v>139.4059524265373</v>
+        <v>139.4059524265371</v>
       </c>
       <c r="K6" t="n">
-        <v>137.8133195628477</v>
+        <v>137.8133195628476</v>
       </c>
       <c r="L6" t="n">
-        <v>139.5329104023846</v>
+        <v>139.5329104023845</v>
       </c>
       <c r="M6" t="n">
-        <v>119.4297079369908</v>
+        <v>119.4297079369909</v>
       </c>
       <c r="N6" t="n">
-        <v>72.47327460659885</v>
+        <v>116.794252464057</v>
       </c>
       <c r="O6" t="n">
         <v>139.6536832176089</v>
@@ -3563,16 +3563,16 @@
         <v>141.0324233384162</v>
       </c>
       <c r="Q6" t="n">
-        <v>138.129062878125</v>
+        <v>138.1290628781248</v>
       </c>
       <c r="R6" t="n">
-        <v>115.7935297239527</v>
+        <v>115.7935297239526</v>
       </c>
       <c r="S6" t="n">
-        <v>139.028224046786</v>
+        <v>139.0282240467859</v>
       </c>
       <c r="T6" t="n">
-        <v>116.5010752749052</v>
+        <v>116.5010752749053</v>
       </c>
       <c r="U6" t="n">
         <v>117.8229379339088</v>
@@ -3590,10 +3590,10 @@
         <v>124.9595312422339</v>
       </c>
       <c r="Z6" t="n">
-        <v>138.8595488593922</v>
+        <v>138.8595488593921</v>
       </c>
       <c r="AA6" t="n">
-        <v>138.570236571314</v>
+        <v>138.5702365713138</v>
       </c>
       <c r="AB6" t="n">
         <v>120.1744589613083</v>
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.274665268894043</v>
+        <v>5.274665268894005</v>
       </c>
       <c r="C7" t="n">
-        <v>4.257422489689623</v>
+        <v>4.257422489689606</v>
       </c>
       <c r="D7" t="n">
-        <v>6.167248284208876</v>
+        <v>6.167248284208844</v>
       </c>
       <c r="E7" t="n">
-        <v>4.821053359301692</v>
+        <v>4.821053359301663</v>
       </c>
       <c r="F7" t="n">
-        <v>5.063516995908437</v>
+        <v>5.063516995908415</v>
       </c>
       <c r="G7" t="n">
-        <v>6.906604817314974</v>
+        <v>6.906604817314937</v>
       </c>
       <c r="H7" t="n">
-        <v>6.351310997786772</v>
+        <v>6.351310997786751</v>
       </c>
       <c r="I7" t="n">
-        <v>5.208050169066006</v>
+        <v>5.208050169065967</v>
       </c>
       <c r="J7" t="n">
-        <v>6.939069790855779</v>
+        <v>6.939069790855748</v>
       </c>
       <c r="K7" t="n">
-        <v>5.346436927166213</v>
+        <v>5.346436927166184</v>
       </c>
       <c r="L7" t="n">
-        <v>7.066027766703098</v>
+        <v>7.066027766703059</v>
       </c>
       <c r="M7" t="n">
-        <v>9.135613719231626</v>
+        <v>9.135613719231602</v>
       </c>
       <c r="N7" t="n">
-        <v>72.47327460659885</v>
+        <v>6.491324246672534</v>
       </c>
       <c r="O7" t="n">
-        <v>7.129991789409327</v>
+        <v>7.129991789409306</v>
       </c>
       <c r="P7" t="n">
-        <v>8.509255941612611</v>
+        <v>8.509255941612587</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.662180242443502</v>
+        <v>5.662180242443467</v>
       </c>
       <c r="R7" t="n">
-        <v>5.499435506193375</v>
+        <v>5.499435506193345</v>
       </c>
       <c r="S7" t="n">
-        <v>6.561341411104507</v>
+        <v>6.561341411104475</v>
       </c>
       <c r="T7" t="n">
-        <v>6.206981057145945</v>
+        <v>6.20698105714594</v>
       </c>
       <c r="U7" t="n">
-        <v>7.526174835888036</v>
+        <v>7.526174835888054</v>
       </c>
       <c r="V7" t="n">
-        <v>6.371793959114944</v>
+        <v>6.371793959114941</v>
       </c>
       <c r="W7" t="n">
-        <v>9.143813017194896</v>
+        <v>9.143813017194862</v>
       </c>
       <c r="X7" t="n">
-        <v>7.234341277845094</v>
+        <v>7.234341277845048</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.770136911197469</v>
+        <v>9.77013691119744</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.392666223710803</v>
+        <v>6.392666223710763</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.103353935632557</v>
+        <v>6.103353935632519</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.851442191550207</v>
+        <v>9.851442191550175</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.681570041596081</v>
+        <v>5.681570041596087</v>
       </c>
       <c r="C8" t="n">
-        <v>5.761092330973075</v>
+        <v>5.761092330973065</v>
       </c>
       <c r="D8" t="n">
-        <v>7.670918125492311</v>
+        <v>7.670918125492298</v>
       </c>
       <c r="E8" t="n">
-        <v>5.740728154408778</v>
+        <v>5.740728154408773</v>
       </c>
       <c r="F8" t="n">
-        <v>5.641284947962646</v>
+        <v>5.641284947962627</v>
       </c>
       <c r="G8" t="n">
-        <v>8.637696040217282</v>
+        <v>8.637696040217257</v>
       </c>
       <c r="H8" t="n">
-        <v>7.854980839070216</v>
+        <v>7.854980839070201</v>
       </c>
       <c r="I8" t="n">
-        <v>6.711720010349448</v>
+        <v>6.711720010349436</v>
       </c>
       <c r="J8" t="n">
-        <v>8.442739632139221</v>
+        <v>8.442739632139206</v>
       </c>
       <c r="K8" t="n">
-        <v>6.850106768449656</v>
+        <v>6.850106768449653</v>
       </c>
       <c r="L8" t="n">
-        <v>8.569697607986537</v>
+        <v>8.569697607986525</v>
       </c>
       <c r="M8" t="n">
-        <v>10.63928356051739</v>
+        <v>10.63928356051736</v>
       </c>
       <c r="N8" t="n">
-        <v>72.47327460659885</v>
+        <v>7.144817674629802</v>
       </c>
       <c r="O8" t="n">
-        <v>8.017129131452087</v>
+        <v>8.017129131452059</v>
       </c>
       <c r="P8" t="n">
-        <v>9.339123489118469</v>
+        <v>9.339123489118434</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.853545647127707</v>
+        <v>5.85354564712766</v>
       </c>
       <c r="R8" t="n">
-        <v>7.003105347476818</v>
+        <v>7.003105347476793</v>
       </c>
       <c r="S8" t="n">
-        <v>8.065011252387947</v>
+        <v>8.065011252387938</v>
       </c>
       <c r="T8" t="n">
-        <v>7.710650898429419</v>
+        <v>7.710650898429392</v>
       </c>
       <c r="U8" t="n">
-        <v>8.49513509030006</v>
+        <v>8.495135090300018</v>
       </c>
       <c r="V8" t="n">
-        <v>7.57342696109253</v>
+        <v>7.573426961092542</v>
       </c>
       <c r="W8" t="n">
-        <v>10.64769840277129</v>
+        <v>10.64769840277126</v>
       </c>
       <c r="X8" t="n">
-        <v>7.526227379466722</v>
+        <v>7.526227379466701</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.36076768601975</v>
+        <v>12.36076768601971</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.779198022314164</v>
+        <v>6.779198022314165</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.607023776915995</v>
+        <v>7.607023776915986</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.50077485559916</v>
+        <v>12.50077485559912</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.844202432299347</v>
+        <v>7.844202432299319</v>
       </c>
       <c r="C9" t="n">
-        <v>7.902417344358104</v>
+        <v>7.902417344358082</v>
       </c>
       <c r="D9" t="n">
-        <v>9.812243138877363</v>
+        <v>9.812243138877331</v>
       </c>
       <c r="E9" t="n">
-        <v>8.217837098546957</v>
+        <v>8.217837098546932</v>
       </c>
       <c r="F9" t="n">
-        <v>6.229288126259824</v>
+        <v>6.229288126259817</v>
       </c>
       <c r="G9" t="n">
-        <v>10.55159984490016</v>
+        <v>10.55159984490014</v>
       </c>
       <c r="H9" t="n">
-        <v>9.996305852455251</v>
+        <v>9.99630585245523</v>
       </c>
       <c r="I9" t="n">
-        <v>8.853045023734476</v>
+        <v>8.853045023734458</v>
       </c>
       <c r="J9" t="n">
-        <v>10.58406464552425</v>
+        <v>10.58406464552423</v>
       </c>
       <c r="K9" t="n">
-        <v>8.991431781834685</v>
+        <v>8.991431781834669</v>
       </c>
       <c r="L9" t="n">
-        <v>10.71102262137156</v>
+        <v>10.71102262137153</v>
       </c>
       <c r="M9" t="n">
-        <v>12.7806085739001</v>
+        <v>12.78060857390007</v>
       </c>
       <c r="N9" t="n">
-        <v>72.47327460659885</v>
+        <v>10.13631910134102</v>
       </c>
       <c r="O9" t="n">
-        <v>11.13140019949808</v>
+        <v>11.13140019949809</v>
       </c>
       <c r="P9" t="n">
-        <v>12.58817639565523</v>
+        <v>12.58817639565519</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.307175270028678</v>
+        <v>9.307175270028676</v>
       </c>
       <c r="R9" t="n">
-        <v>9.144430360861843</v>
+        <v>9.144430360861822</v>
       </c>
       <c r="S9" t="n">
-        <v>10.20633626577299</v>
+        <v>10.20633626577298</v>
       </c>
       <c r="T9" t="n">
-        <v>9.851975911814435</v>
+        <v>9.851975911814419</v>
       </c>
       <c r="U9" t="n">
-        <v>11.17383857081797</v>
+        <v>11.17383857081799</v>
       </c>
       <c r="V9" t="n">
-        <v>11.25784266605121</v>
+        <v>11.2578426660512</v>
       </c>
       <c r="W9" t="n">
-        <v>12.78880787186337</v>
+        <v>12.78880787186335</v>
       </c>
       <c r="X9" t="n">
-        <v>10.87933613251356</v>
+        <v>10.87933613251354</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.41513176586595</v>
+        <v>13.41513176586593</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.38925579264019</v>
+        <v>9.38925579264016</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.748348790301025</v>
+        <v>9.748348790301005</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.49643704621867</v>
+        <v>13.49643704621865</v>
       </c>
     </row>
   </sheetData>
@@ -4026,40 +4026,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.402299847149</v>
+        <v>39.40229984714902</v>
       </c>
       <c r="C2" t="n">
-        <v>42.28684474596508</v>
+        <v>42.28684474596504</v>
       </c>
       <c r="D2" t="n">
         <v>39.42617232903942</v>
       </c>
       <c r="E2" t="n">
-        <v>39.29138089092763</v>
+        <v>39.29138089092765</v>
       </c>
       <c r="F2" t="n">
-        <v>39.4655521286383</v>
+        <v>39.46555212863834</v>
       </c>
       <c r="G2" t="n">
         <v>39.53549423107177</v>
       </c>
       <c r="H2" t="n">
-        <v>39.49145730862973</v>
+        <v>39.49145730862976</v>
       </c>
       <c r="I2" t="n">
-        <v>39.46297730189157</v>
+        <v>39.46297730189158</v>
       </c>
       <c r="J2" t="n">
         <v>39.54147872806413</v>
       </c>
       <c r="K2" t="n">
-        <v>39.52047775178141</v>
+        <v>39.52047775178143</v>
       </c>
       <c r="L2" t="n">
-        <v>39.58532508912367</v>
+        <v>39.58532508912371</v>
       </c>
       <c r="M2" t="n">
-        <v>39.71387402801867</v>
+        <v>39.71387402801868</v>
       </c>
       <c r="N2" t="n">
         <v>39.48768476427374</v>
@@ -4068,43 +4068,43 @@
         <v>43.41806553734951</v>
       </c>
       <c r="P2" t="n">
-        <v>39.64963022905432</v>
+        <v>39.6496302290543</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.48469457574317</v>
+        <v>39.4846945757432</v>
       </c>
       <c r="R2" t="n">
         <v>39.45743895266394</v>
       </c>
       <c r="S2" t="n">
-        <v>39.55638604481052</v>
+        <v>39.55638604481057</v>
       </c>
       <c r="T2" t="n">
         <v>39.52131729496416</v>
       </c>
       <c r="U2" t="n">
-        <v>43.05025252167518</v>
+        <v>43.05025252167516</v>
       </c>
       <c r="V2" t="n">
-        <v>39.49127146467</v>
+        <v>39.49127146467002</v>
       </c>
       <c r="W2" t="n">
-        <v>45.66318568060088</v>
+        <v>45.66318568060087</v>
       </c>
       <c r="X2" t="n">
-        <v>39.61507622412886</v>
+        <v>39.61507622412887</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.75994225623116</v>
+        <v>39.75994225623113</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.62662872427284</v>
+        <v>40.62662872427285</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.52231334501175</v>
+        <v>39.52231334501177</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.77089343814573</v>
+        <v>39.77089343814576</v>
       </c>
     </row>
     <row r="3">
@@ -4114,43 +4114,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.30124512816919</v>
+        <v>40.30124512816918</v>
       </c>
       <c r="C3" t="n">
-        <v>44.71793318064569</v>
+        <v>44.71793318064572</v>
       </c>
       <c r="D3" t="n">
-        <v>40.47988096236728</v>
+        <v>40.47988096236729</v>
       </c>
       <c r="E3" t="n">
-        <v>39.51501993812769</v>
+        <v>39.51501993812767</v>
       </c>
       <c r="F3" t="n">
-        <v>40.7641907599165</v>
+        <v>40.76419075991652</v>
       </c>
       <c r="G3" t="n">
-        <v>41.24597166631295</v>
+        <v>41.24597166631301</v>
       </c>
       <c r="H3" t="n">
-        <v>40.9582811647505</v>
+        <v>40.95828116475045</v>
       </c>
       <c r="I3" t="n">
-        <v>40.74703925526349</v>
+        <v>40.74703925526352</v>
       </c>
       <c r="J3" t="n">
-        <v>41.29641051968193</v>
+        <v>41.29641051968188</v>
       </c>
       <c r="K3" t="n">
-        <v>41.14419714785204</v>
+        <v>41.14419714785205</v>
       </c>
       <c r="L3" t="n">
-        <v>41.60804604227712</v>
+        <v>41.60804604227714</v>
       </c>
       <c r="M3" t="n">
-        <v>42.53176198817277</v>
+        <v>42.53176198817276</v>
       </c>
       <c r="N3" t="n">
-        <v>40.92180345759621</v>
+        <v>40.92180345759623</v>
       </c>
       <c r="O3" t="n">
         <v>47.51320536996576</v>
@@ -4162,37 +4162,37 @@
         <v>40.89482327658003</v>
       </c>
       <c r="R3" t="n">
-        <v>40.71139875658389</v>
+        <v>40.71139875658387</v>
       </c>
       <c r="S3" t="n">
-        <v>41.39817085342352</v>
+        <v>41.39817085342358</v>
       </c>
       <c r="T3" t="n">
-        <v>41.16607100481946</v>
+        <v>41.16607100481951</v>
       </c>
       <c r="U3" t="n">
-        <v>47.38021251318573</v>
+        <v>47.38021251318575</v>
       </c>
       <c r="V3" t="n">
-        <v>40.92989612387462</v>
+        <v>40.92989612387466</v>
       </c>
       <c r="W3" t="n">
-        <v>52.44283611820787</v>
+        <v>52.44283611820788</v>
       </c>
       <c r="X3" t="n">
-        <v>41.82760056191835</v>
+        <v>41.8276005619184</v>
       </c>
       <c r="Y3" t="n">
-        <v>42.86529197923265</v>
+        <v>42.86529197923268</v>
       </c>
       <c r="Z3" t="n">
-        <v>42.47594924501569</v>
+        <v>42.47594924501568</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.16710224143095</v>
+        <v>41.16710224143096</v>
       </c>
       <c r="AB3" t="n">
-        <v>42.94003094605219</v>
+        <v>42.94003094605221</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.930747573369445</v>
+        <v>3.930747573369477</v>
       </c>
       <c r="C4" t="n">
-        <v>3.204394642325339</v>
+        <v>3.204394642325362</v>
       </c>
       <c r="D4" t="n">
-        <v>4.200398238205871</v>
+        <v>4.200398238205892</v>
       </c>
       <c r="E4" t="n">
-        <v>2.677866937608297</v>
+        <v>2.677866937608326</v>
       </c>
       <c r="F4" t="n">
-        <v>4.645211190278198</v>
+        <v>4.645211190278264</v>
       </c>
       <c r="G4" t="n">
-        <v>5.435239412220853</v>
+        <v>5.435239412220886</v>
       </c>
       <c r="H4" t="n">
-        <v>4.937822115253064</v>
+        <v>4.93782211525308</v>
       </c>
       <c r="I4" t="n">
-        <v>4.616127337695107</v>
+        <v>4.61612733769514</v>
       </c>
       <c r="J4" t="n">
-        <v>5.503575795815068</v>
+        <v>5.503575795815085</v>
       </c>
       <c r="K4" t="n">
-        <v>5.265621370714713</v>
+        <v>5.265621370714745</v>
       </c>
       <c r="L4" t="n">
-        <v>5.998101877244233</v>
+        <v>5.998101877244274</v>
       </c>
       <c r="M4" t="n">
-        <v>7.440231396765194</v>
+        <v>7.440231396765214</v>
       </c>
       <c r="N4" t="n">
-        <v>64.43378084464523</v>
+        <v>4.895209491295308</v>
       </c>
       <c r="O4" t="n">
-        <v>5.144031728307157</v>
+        <v>5.144031728307167</v>
       </c>
       <c r="P4" t="n">
-        <v>6.724458014586252</v>
+        <v>6.724458014586281</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.861433936288478</v>
+        <v>4.861433936288488</v>
       </c>
       <c r="R4" t="n">
-        <v>4.553569135402076</v>
+        <v>4.553569135402077</v>
       </c>
       <c r="S4" t="n">
-        <v>5.671222059109096</v>
+        <v>5.671222059109121</v>
       </c>
       <c r="T4" t="n">
-        <v>5.275104397172402</v>
+        <v>5.275104397172436</v>
       </c>
       <c r="U4" t="n">
-        <v>6.082722699711867</v>
+        <v>6.082722699711915</v>
       </c>
       <c r="V4" t="n">
-        <v>4.940410224956171</v>
+        <v>4.94041022495617</v>
       </c>
       <c r="W4" t="n">
         <v>7.631763321457398</v>
       </c>
       <c r="X4" t="n">
-        <v>6.334154633326357</v>
+        <v>6.334154633326384</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.93837764809187</v>
+        <v>7.9383776480919</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.261965478384359</v>
+        <v>4.261965478384379</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.286355240665872</v>
+        <v>5.286355240665894</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.056251124908069</v>
+        <v>8.056251124908107</v>
       </c>
     </row>
     <row r="5">
@@ -4290,55 +4290,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.59129830237004</v>
+        <v>41.59129830237009</v>
       </c>
       <c r="C5" t="n">
-        <v>32.16568100909707</v>
+        <v>32.16568100909713</v>
       </c>
       <c r="D5" t="n">
-        <v>50.63936213967539</v>
+        <v>50.63936213967523</v>
       </c>
       <c r="E5" t="n">
-        <v>22.23507786872351</v>
+        <v>22.23507786872354</v>
       </c>
       <c r="F5" t="n">
-        <v>60.19302235405964</v>
+        <v>60.19302235405959</v>
       </c>
       <c r="G5" t="n">
-        <v>65.14919456733892</v>
+        <v>65.14919456733884</v>
       </c>
       <c r="H5" t="n">
         <v>70.13798840306715</v>
       </c>
       <c r="I5" t="n">
-        <v>60.3135357147242</v>
+        <v>60.31353571472422</v>
       </c>
       <c r="J5" t="n">
-        <v>70.34993495718466</v>
+        <v>70.34993495718457</v>
       </c>
       <c r="K5" t="n">
-        <v>64.94703320071307</v>
+        <v>64.94703320071328</v>
       </c>
       <c r="L5" t="n">
-        <v>78.4360425080349</v>
+        <v>78.43604250803484</v>
       </c>
       <c r="M5" t="n">
         <v>109.9689854470565</v>
       </c>
       <c r="N5" t="n">
-        <v>64.43378084464523</v>
+        <v>64.43378084464527</v>
       </c>
       <c r="O5" t="n">
-        <v>59.88610886641754</v>
+        <v>59.88610886641747</v>
       </c>
       <c r="P5" t="n">
-        <v>85.42415542791959</v>
+        <v>85.42415542791922</v>
       </c>
       <c r="Q5" t="n">
-        <v>60.91410622992888</v>
+        <v>60.91410622992883</v>
       </c>
       <c r="R5" t="n">
-        <v>61.2214174888584</v>
+        <v>61.22141748885837</v>
       </c>
       <c r="S5" t="n">
         <v>70.92594642637465</v>
@@ -4347,7 +4347,7 @@
         <v>73.34519813266147</v>
       </c>
       <c r="U5" t="n">
-        <v>78.42634863372024</v>
+        <v>78.42634863372039</v>
       </c>
       <c r="V5" t="n">
         <v>56.08308095878163</v>
@@ -4356,7 +4356,7 @@
         <v>111.8260152093259</v>
       </c>
       <c r="X5" t="n">
-        <v>88.12085034749744</v>
+        <v>88.12085034749728</v>
       </c>
       <c r="Y5" t="n">
         <v>119.0184858133738</v>
@@ -4365,7 +4365,7 @@
         <v>43.74303094989111</v>
       </c>
       <c r="AA5" t="n">
-        <v>70.39461404088425</v>
+        <v>70.39461404088421</v>
       </c>
       <c r="AB5" t="n">
         <v>129.4428369150716</v>
@@ -4378,43 +4378,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115.2459428385959</v>
+        <v>115.2459428385958</v>
       </c>
       <c r="C6" t="n">
-        <v>114.5195899075518</v>
+        <v>114.5195899075517</v>
       </c>
       <c r="D6" t="n">
         <v>137.6284709290134</v>
       </c>
       <c r="E6" t="n">
-        <v>136.1059396284157</v>
+        <v>136.1059396284159</v>
       </c>
       <c r="F6" t="n">
-        <v>115.9604064555047</v>
+        <v>115.9604064555044</v>
       </c>
       <c r="G6" t="n">
-        <v>116.7504346774474</v>
+        <v>116.7504346774472</v>
       </c>
       <c r="H6" t="n">
-        <v>138.3658948060603</v>
+        <v>138.3658948060606</v>
       </c>
       <c r="I6" t="n">
-        <v>115.9313226029218</v>
+        <v>115.9313226029215</v>
       </c>
       <c r="J6" t="n">
-        <v>138.9316484866223</v>
+        <v>138.9316484866226</v>
       </c>
       <c r="K6" t="n">
-        <v>138.6936940615221</v>
+        <v>138.6936940615223</v>
       </c>
       <c r="L6" t="n">
-        <v>117.3132971424709</v>
+        <v>117.3132971424706</v>
       </c>
       <c r="M6" t="n">
         <v>118.7554266619916</v>
       </c>
       <c r="N6" t="n">
-        <v>64.43378084464523</v>
+        <v>116.2238134514062</v>
       </c>
       <c r="O6" t="n">
         <v>116.4740280460592</v>
@@ -4423,40 +4423,40 @@
         <v>140.2126421602463</v>
       </c>
       <c r="Q6" t="n">
-        <v>138.2895066270958</v>
+        <v>138.289506627096</v>
       </c>
       <c r="R6" t="n">
-        <v>137.9816418262093</v>
+        <v>137.9816418262096</v>
       </c>
       <c r="S6" t="n">
         <v>116.9864173243354</v>
       </c>
       <c r="T6" t="n">
-        <v>138.7031770879799</v>
+        <v>138.70317708798</v>
       </c>
       <c r="U6" t="n">
-        <v>139.5429008500159</v>
+        <v>139.5429008500162</v>
       </c>
       <c r="V6" t="n">
-        <v>116.2556054901827</v>
+        <v>116.2556054901825</v>
       </c>
       <c r="W6" t="n">
-        <v>124.6474803346835</v>
+        <v>124.6474803346834</v>
       </c>
       <c r="X6" t="n">
-        <v>117.6493498985528</v>
+        <v>117.6493498985527</v>
       </c>
       <c r="Y6" t="n">
         <v>124.1834837702463</v>
       </c>
       <c r="Z6" t="n">
-        <v>115.5771607436109</v>
+        <v>115.5771607436108</v>
       </c>
       <c r="AA6" t="n">
         <v>138.7144279314734</v>
       </c>
       <c r="AB6" t="n">
-        <v>119.4025757292696</v>
+        <v>119.4025757292698</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.9365805659043</v>
+        <v>4.936580565904308</v>
       </c>
       <c r="C7" t="n">
-        <v>4.210227634860185</v>
+        <v>4.210227634860211</v>
       </c>
       <c r="D7" t="n">
-        <v>5.206231230740717</v>
+        <v>5.206231230740738</v>
       </c>
       <c r="E7" t="n">
-        <v>3.683699930143151</v>
+        <v>3.683699930143176</v>
       </c>
       <c r="F7" t="n">
-        <v>5.651044182813046</v>
+        <v>5.651044182813097</v>
       </c>
       <c r="G7" t="n">
-        <v>6.441072404755707</v>
+        <v>6.441072404755733</v>
       </c>
       <c r="H7" t="n">
-        <v>5.943655107787913</v>
+        <v>5.943655107787924</v>
       </c>
       <c r="I7" t="n">
-        <v>5.62196033022995</v>
+        <v>5.621960330229987</v>
       </c>
       <c r="J7" t="n">
-        <v>6.509408788349919</v>
+        <v>6.509408788349929</v>
       </c>
       <c r="K7" t="n">
-        <v>6.271454363249569</v>
+        <v>6.271454363249587</v>
       </c>
       <c r="L7" t="n">
-        <v>7.003934869779075</v>
+        <v>7.003934869779114</v>
       </c>
       <c r="M7" t="n">
-        <v>8.446064389300041</v>
+        <v>8.446064389300062</v>
       </c>
       <c r="N7" t="n">
-        <v>64.43378084464523</v>
+        <v>5.901042483830173</v>
       </c>
       <c r="O7" t="n">
-        <v>6.149861281732564</v>
+        <v>6.149861281732581</v>
       </c>
       <c r="P7" t="n">
-        <v>7.730287568011649</v>
+        <v>7.730287568011638</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.86726692882333</v>
+        <v>5.867266928823348</v>
       </c>
       <c r="R7" t="n">
-        <v>5.559402127936923</v>
+        <v>5.559402127936927</v>
       </c>
       <c r="S7" t="n">
-        <v>6.677055051643945</v>
+        <v>6.677055051643965</v>
       </c>
       <c r="T7" t="n">
-        <v>6.280937389707258</v>
+        <v>6.280937389707284</v>
       </c>
       <c r="U7" t="n">
-        <v>7.112648820737459</v>
+        <v>7.112648820737484</v>
       </c>
       <c r="V7" t="n">
-        <v>5.946243217491022</v>
+        <v>5.946243217491014</v>
       </c>
       <c r="W7" t="n">
-        <v>8.637596313992255</v>
+        <v>8.637596313992271</v>
       </c>
       <c r="X7" t="n">
-        <v>7.339987625861196</v>
+        <v>7.339987625861208</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.97631610012345</v>
+        <v>8.976316100123464</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.267798470919209</v>
+        <v>5.267798470919229</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.292188233200727</v>
+        <v>6.292188233200739</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.062084117442932</v>
+        <v>9.062084117442987</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.308581705033971</v>
+        <v>5.308581705033991</v>
       </c>
       <c r="C8" t="n">
-        <v>5.615070040427171</v>
+        <v>5.615070040427188</v>
       </c>
       <c r="D8" t="n">
-        <v>6.611073636307712</v>
+        <v>6.611073636307738</v>
       </c>
       <c r="E8" t="n">
-        <v>4.538584828510301</v>
+        <v>4.5385848285103</v>
       </c>
       <c r="F8" t="n">
-        <v>6.183949920031103</v>
+        <v>6.183949920031139</v>
       </c>
       <c r="G8" t="n">
-        <v>8.060081175153627</v>
+        <v>8.060081175153645</v>
       </c>
       <c r="H8" t="n">
-        <v>7.348497513354915</v>
+        <v>7.348497513354899</v>
       </c>
       <c r="I8" t="n">
-        <v>7.02680273579694</v>
+        <v>7.026802735796955</v>
       </c>
       <c r="J8" t="n">
-        <v>7.914251193916919</v>
+        <v>7.914251193916937</v>
       </c>
       <c r="K8" t="n">
-        <v>7.676296768816547</v>
+        <v>7.676296768816566</v>
       </c>
       <c r="L8" t="n">
-        <v>8.408777275346067</v>
+        <v>8.408777275346093</v>
       </c>
       <c r="M8" t="n">
-        <v>9.850906794869823</v>
+        <v>9.850906794869845</v>
       </c>
       <c r="N8" t="n">
-        <v>64.43378084464523</v>
+        <v>6.505260116990532</v>
       </c>
       <c r="O8" t="n">
-        <v>6.974100992485423</v>
+        <v>6.974100992485435</v>
       </c>
       <c r="P8" t="n">
-        <v>8.500595394147396</v>
+        <v>8.500595394147407</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.036291186003554</v>
+        <v>6.036291186003598</v>
       </c>
       <c r="R8" t="n">
-        <v>6.964244533503911</v>
+        <v>6.964244533503956</v>
       </c>
       <c r="S8" t="n">
-        <v>8.081897457210939</v>
+        <v>8.081897457210969</v>
       </c>
       <c r="T8" t="n">
-        <v>7.685779795274263</v>
+        <v>7.685779795274289</v>
       </c>
       <c r="U8" t="n">
-        <v>8.015180824938087</v>
+        <v>8.01518082493808</v>
       </c>
       <c r="V8" t="n">
-        <v>7.061948728286136</v>
+        <v>7.061948728286137</v>
       </c>
       <c r="W8" t="n">
-        <v>10.04264170114479</v>
+        <v>10.04264170114482</v>
       </c>
       <c r="X8" t="n">
-        <v>7.60367383658698</v>
+        <v>7.603673836587013</v>
       </c>
       <c r="Y8" t="n">
         <v>11.39747121888713</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.620614053379152</v>
+        <v>5.620614053379176</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.697030638767729</v>
+        <v>7.69703063876773</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.54581558935894</v>
+        <v>11.54581558935898</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.128513639403406</v>
+        <v>7.128513639403428</v>
       </c>
       <c r="C9" t="n">
-        <v>7.355019958714097</v>
+        <v>7.355019958714127</v>
       </c>
       <c r="D9" t="n">
-        <v>8.351023554594631</v>
+        <v>8.351023554594684</v>
       </c>
       <c r="E9" t="n">
-        <v>6.608576226095277</v>
+        <v>6.608576226095283</v>
       </c>
       <c r="F9" t="n">
-        <v>6.599235873893186</v>
+        <v>6.599235873893225</v>
       </c>
       <c r="G9" t="n">
-        <v>9.585864729178946</v>
+        <v>9.585864729178994</v>
       </c>
       <c r="H9" t="n">
-        <v>9.088447431641839</v>
+        <v>9.08844743164185</v>
       </c>
       <c r="I9" t="n">
-        <v>8.766752654083863</v>
+        <v>8.766752654083881</v>
       </c>
       <c r="J9" t="n">
-        <v>9.654201112203834</v>
+        <v>9.654201112203848</v>
       </c>
       <c r="K9" t="n">
-        <v>9.41624668710347</v>
+        <v>9.416246687103509</v>
       </c>
       <c r="L9" t="n">
-        <v>10.14872719363301</v>
+        <v>10.14872719363303</v>
       </c>
       <c r="M9" t="n">
-        <v>11.59085671315397</v>
+        <v>11.59085671315398</v>
       </c>
       <c r="N9" t="n">
-        <v>64.43378084464523</v>
+        <v>9.045834807684095</v>
       </c>
       <c r="O9" t="n">
-        <v>9.610433353358879</v>
+        <v>9.610433353358911</v>
       </c>
       <c r="P9" t="n">
-        <v>11.25953556883929</v>
+        <v>11.25953556883932</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.012059253246582</v>
+        <v>9.012059253246594</v>
       </c>
       <c r="R9" t="n">
-        <v>8.704194451790823</v>
+        <v>8.704194451790833</v>
       </c>
       <c r="S9" t="n">
-        <v>9.821847375497851</v>
+        <v>9.821847375497864</v>
       </c>
       <c r="T9" t="n">
-        <v>9.425729713561179</v>
+        <v>9.425729713561237</v>
       </c>
       <c r="U9" t="n">
-        <v>10.26545347559735</v>
+        <v>10.2654534755974</v>
       </c>
       <c r="V9" t="n">
         <v>10.19061334638346</v>
       </c>
       <c r="W9" t="n">
-        <v>11.78238863784616</v>
+        <v>11.78238863784619</v>
       </c>
       <c r="X9" t="n">
-        <v>10.48477994971513</v>
+        <v>10.48477994971512</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.12110842397734</v>
+        <v>12.12110842397741</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.838101398585822</v>
+        <v>7.838101398585834</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.436980557054589</v>
+        <v>9.43698055705465</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.20687644129683</v>
+        <v>12.20687644129688</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>4.95421388959941</v>
       </c>
       <c r="N4" t="n">
-        <v>77.8704513900648</v>
+        <v>5.463337883569005</v>
       </c>
       <c r="O4" t="n">
         <v>5.697376256515186</v>
@@ -5274,7 +5274,7 @@
         <v>148.0456520454565</v>
       </c>
       <c r="N6" t="n">
-        <v>77.8704513900648</v>
+        <v>124.9278647443018</v>
       </c>
       <c r="O6" t="n">
         <v>148.8605749472365</v>
@@ -5362,7 +5362,7 @@
         <v>5.973495511658413</v>
       </c>
       <c r="N7" t="n">
-        <v>77.8704513900648</v>
+        <v>6.482619505627991</v>
       </c>
       <c r="O7" t="n">
         <v>6.716652933257324</v>
@@ -5450,7 +5450,7 @@
         <v>7.335686344379144</v>
       </c>
       <c r="N8" t="n">
-        <v>77.8704513900648</v>
+        <v>7.051421359175542</v>
       </c>
       <c r="O8" t="n">
         <v>7.503489911675901</v>
@@ -5538,7 +5538,7 @@
         <v>9.611256815649508</v>
       </c>
       <c r="N9" t="n">
-        <v>77.8704513900648</v>
+        <v>10.12038080961909</v>
       </c>
       <c r="O9" t="n">
         <v>10.70692579075126</v>
@@ -5958,7 +5958,7 @@
         <v>2.634567619952888</v>
       </c>
       <c r="N4" t="n">
-        <v>54.45687528540235</v>
+        <v>4.258442926857505</v>
       </c>
       <c r="O4" t="n">
         <v>4.877241709584835</v>
@@ -5985,7 +5985,7 @@
         <v>3.565499165397936</v>
       </c>
       <c r="W4" t="n">
-        <v>6.183516943497886</v>
+        <v>6.183516943497885</v>
       </c>
       <c r="X4" t="n">
         <v>5.032972063442585</v>
@@ -6073,7 +6073,7 @@
         <v>38.35860638633739</v>
       </c>
       <c r="W5" t="n">
-        <v>85.12979796509451</v>
+        <v>85.12979796509453</v>
       </c>
       <c r="X5" t="n">
         <v>67.41647837430665</v>
@@ -6088,7 +6088,7 @@
         <v>54.8943706005704</v>
       </c>
       <c r="AB5" t="n">
-        <v>55.51108754720269</v>
+        <v>55.51108754720268</v>
       </c>
     </row>
     <row r="6">
@@ -6134,7 +6134,7 @@
         <v>135.7726999925272</v>
       </c>
       <c r="N6" t="n">
-        <v>54.45687528540235</v>
+        <v>115.4729570504244</v>
       </c>
       <c r="O6" t="n">
         <v>138.0777453634841</v>
@@ -6222,7 +6222,7 @@
         <v>3.477521407390102</v>
       </c>
       <c r="N7" t="n">
-        <v>54.45687528540235</v>
+        <v>5.101396714294698</v>
       </c>
       <c r="O7" t="n">
         <v>5.720192534476425</v>
@@ -6292,7 +6292,7 @@
         <v>5.337736278204932</v>
       </c>
       <c r="H8" t="n">
-        <v>4.976348631331365</v>
+        <v>4.976348631331364</v>
       </c>
       <c r="I8" t="n">
         <v>3.999238699132792</v>
@@ -6310,7 +6310,7 @@
         <v>4.485862529910106</v>
       </c>
       <c r="N8" t="n">
-        <v>54.45687528540235</v>
+        <v>5.494912219511548</v>
       </c>
       <c r="O8" t="n">
         <v>6.282670419732341</v>
@@ -6328,7 +6328,7 @@
         <v>4.419947747327517</v>
       </c>
       <c r="T8" t="n">
-        <v>4.916607189164584</v>
+        <v>4.916607189164585</v>
       </c>
       <c r="U8" t="n">
         <v>4.839971376361069</v>
@@ -6377,7 +6377,7 @@
         <v>3.859583536516266</v>
       </c>
       <c r="G9" t="n">
-        <v>6.827437811187469</v>
+        <v>6.82743781118747</v>
       </c>
       <c r="H9" t="n">
         <v>6.630515077870936</v>
@@ -6398,7 +6398,7 @@
         <v>6.140028976450042</v>
       </c>
       <c r="N9" t="n">
-        <v>54.45687528540235</v>
+        <v>7.763904283354638</v>
       </c>
       <c r="O9" t="n">
         <v>8.648029204755716</v>
@@ -6416,7 +6416,7 @@
         <v>6.074114193867111</v>
       </c>
       <c r="T9" t="n">
-        <v>6.570773635704164</v>
+        <v>6.570773635704165</v>
       </c>
       <c r="U9" t="n">
         <v>6.885249680742952</v>
@@ -6818,7 +6818,7 @@
         <v>2.472446060541167</v>
       </c>
       <c r="N4" t="n">
-        <v>38.78370947956876</v>
+        <v>3.167395513256096</v>
       </c>
       <c r="O4" t="n">
         <v>3.813666532418742</v>
@@ -6906,7 +6906,7 @@
         <v>26.41785059502678</v>
       </c>
       <c r="N5" t="n">
-        <v>38.78370947956874</v>
+        <v>38.78370947956876</v>
       </c>
       <c r="O5" t="n">
         <v>44.67510350745133</v>
@@ -6994,7 +6994,7 @@
         <v>135.4878595940214</v>
       </c>
       <c r="N6" t="n">
-        <v>38.78370947956874</v>
+        <v>114.3234513064053</v>
       </c>
       <c r="O6" t="n">
         <v>114.9714489261843</v>
@@ -7082,7 +7082,7 @@
         <v>3.260395938678551</v>
       </c>
       <c r="N7" t="n">
-        <v>38.78370947956874</v>
+        <v>3.955345391393479</v>
       </c>
       <c r="O7" t="n">
         <v>4.601615005116493</v>
@@ -7170,7 +7170,7 @@
         <v>4.140436363409494</v>
       </c>
       <c r="N8" t="n">
-        <v>38.78370947956874</v>
+        <v>4.283211748559076</v>
       </c>
       <c r="O8" t="n">
         <v>5.081224995439359</v>
@@ -7258,7 +7258,7 @@
         <v>5.39775439031783</v>
       </c>
       <c r="N9" t="n">
-        <v>38.78370947956874</v>
+        <v>6.092703843032763</v>
       </c>
       <c r="O9" t="n">
         <v>6.960873915402086</v>
@@ -7678,7 +7678,7 @@
         <v>8.746045268676991</v>
       </c>
       <c r="N4" t="n">
-        <v>82.2954463264056</v>
+        <v>5.76281433154783</v>
       </c>
       <c r="O4" t="n">
         <v>5.693410042088381</v>
@@ -7766,7 +7766,7 @@
         <v>134.2488616136515</v>
       </c>
       <c r="N5" t="n">
-        <v>82.29544632640558</v>
+        <v>82.2954463264056</v>
       </c>
       <c r="O5" t="n">
         <v>70.64674414232996</v>
@@ -7854,7 +7854,7 @@
         <v>128.2460279357047</v>
       </c>
       <c r="N6" t="n">
-        <v>82.29544632640558</v>
+        <v>125.2720374782842</v>
       </c>
       <c r="O6" t="n">
         <v>149.0728994979742</v>
@@ -7942,7 +7942,7 @@
         <v>9.881597484399844</v>
       </c>
       <c r="N7" t="n">
-        <v>82.29544632640558</v>
+        <v>6.898366547270685</v>
       </c>
       <c r="O7" t="n">
         <v>6.828951694173324</v>
@@ -8030,7 +8030,7 @@
         <v>11.51508539001502</v>
       </c>
       <c r="N8" t="n">
-        <v>82.29544632640558</v>
+        <v>7.607418495682989</v>
       </c>
       <c r="O8" t="n">
         <v>7.792057233090911</v>
@@ -8118,7 +8118,7 @@
         <v>14.24334118601468</v>
       </c>
       <c r="N9" t="n">
-        <v>82.29544632640558</v>
+        <v>11.26011024888551</v>
       </c>
       <c r="O9" t="n">
         <v>11.60695226618652</v>
@@ -8538,7 +8538,7 @@
         <v>4.011945298599658</v>
       </c>
       <c r="N4" t="n">
-        <v>54.94422479630336</v>
+        <v>4.240600206056565</v>
       </c>
       <c r="O4" t="n">
         <v>4.830670144207092</v>
@@ -8714,7 +8714,7 @@
         <v>115.2487928578788</v>
       </c>
       <c r="N6" t="n">
-        <v>54.94422479630336</v>
+        <v>115.4833210917824</v>
       </c>
       <c r="O6" t="n">
         <v>138.1828125638557</v>
@@ -8802,7 +8802,7 @@
         <v>4.925761897428128</v>
       </c>
       <c r="N7" t="n">
-        <v>54.94422479630336</v>
+        <v>5.154416804885042</v>
       </c>
       <c r="O7" t="n">
         <v>5.744481841614486</v>
@@ -8890,7 +8890,7 @@
         <v>6.131551861903075</v>
       </c>
       <c r="N8" t="n">
-        <v>54.94422479630336</v>
+        <v>5.653335306666338</v>
       </c>
       <c r="O8" t="n">
         <v>6.437659659743441</v>
@@ -8978,7 +8978,7 @@
         <v>8.033489480643704</v>
       </c>
       <c r="N9" t="n">
-        <v>54.94422479630336</v>
+        <v>8.262144388100603</v>
       </c>
       <c r="O9" t="n">
         <v>9.15727151764713</v>

--- a/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
@@ -586,16 +586,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.86558020822903</v>
+        <v>39.86558020822908</v>
       </c>
       <c r="C2" t="n">
         <v>42.57319409382514</v>
       </c>
       <c r="D2" t="n">
-        <v>39.74379697887208</v>
+        <v>39.7437969788721</v>
       </c>
       <c r="E2" t="n">
-        <v>39.73571265549226</v>
+        <v>39.73571265549227</v>
       </c>
       <c r="F2" t="n">
         <v>39.74936597682419</v>
@@ -610,19 +610,19 @@
         <v>39.70996203503856</v>
       </c>
       <c r="J2" t="n">
-        <v>39.94209255405192</v>
+        <v>39.94209255405196</v>
       </c>
       <c r="K2" t="n">
-        <v>39.89178481684849</v>
+        <v>39.8917848168485</v>
       </c>
       <c r="L2" t="n">
         <v>40.0200402595998</v>
       </c>
       <c r="M2" t="n">
-        <v>40.2099958901585</v>
+        <v>40.20999589015852</v>
       </c>
       <c r="N2" t="n">
-        <v>39.97294740999753</v>
+        <v>39.97294740999754</v>
       </c>
       <c r="O2" t="n">
         <v>44.0647283889531</v>
@@ -634,37 +634,37 @@
         <v>39.84917345479597</v>
       </c>
       <c r="R2" t="n">
-        <v>39.76836775620612</v>
+        <v>39.76836775620614</v>
       </c>
       <c r="S2" t="n">
-        <v>39.91121268372182</v>
+        <v>39.91121268372184</v>
       </c>
       <c r="T2" t="n">
-        <v>39.8933557817838</v>
+        <v>39.89335578178382</v>
       </c>
       <c r="U2" t="n">
-        <v>43.74458627711367</v>
+        <v>43.7445862771137</v>
       </c>
       <c r="V2" t="n">
-        <v>39.87922973880492</v>
+        <v>39.87922973880493</v>
       </c>
       <c r="W2" t="n">
-        <v>46.24781264865615</v>
+        <v>46.24781264865614</v>
       </c>
       <c r="X2" t="n">
-        <v>39.83098976852254</v>
+        <v>39.83098976852255</v>
       </c>
       <c r="Y2" t="n">
         <v>40.15672860280745</v>
       </c>
       <c r="Z2" t="n">
-        <v>41.34106150211278</v>
+        <v>41.34106150211279</v>
       </c>
       <c r="AA2" t="n">
         <v>39.8731527723793</v>
       </c>
       <c r="AB2" t="n">
-        <v>40.21119741395757</v>
+        <v>40.21119741395758</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.59003225759685</v>
+        <v>41.68464360995331</v>
       </c>
       <c r="C3" t="n">
-        <v>44.66813516894263</v>
+        <v>44.69906058911023</v>
       </c>
       <c r="D3" t="n">
-        <v>40.73652099874683</v>
+        <v>40.80165196494996</v>
       </c>
       <c r="E3" t="n">
-        <v>40.6731996817472</v>
+        <v>40.7356727088629</v>
       </c>
       <c r="F3" t="n">
-        <v>40.77891345547659</v>
+        <v>40.84577391208072</v>
       </c>
       <c r="G3" t="n">
-        <v>42.02136842120964</v>
+        <v>42.13105574073995</v>
       </c>
       <c r="H3" t="n">
-        <v>42.02971977390121</v>
+        <v>42.14119200139852</v>
       </c>
       <c r="I3" t="n">
-        <v>40.49535967140321</v>
+        <v>40.5520004624561</v>
       </c>
       <c r="J3" t="n">
-        <v>42.14326094593921</v>
+        <v>42.25761912503599</v>
       </c>
       <c r="K3" t="n">
-        <v>41.79455978800009</v>
+        <v>41.89712834969509</v>
       </c>
       <c r="L3" t="n">
-        <v>42.70199130034279</v>
+        <v>42.83604901678688</v>
       </c>
       <c r="M3" t="n">
-        <v>44.07343409629516</v>
+        <v>44.25747223196537</v>
       </c>
       <c r="N3" t="n">
-        <v>42.37107455390974</v>
+        <v>42.49388558961201</v>
       </c>
       <c r="O3" t="n">
-        <v>48.72350244181498</v>
+        <v>48.82741405033485</v>
       </c>
       <c r="P3" t="n">
-        <v>42.79993913720786</v>
+        <v>42.93672410405776</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.48772405002578</v>
+        <v>41.57938553521385</v>
       </c>
       <c r="R3" t="n">
-        <v>40.91527871138069</v>
+        <v>40.98692259706485</v>
       </c>
       <c r="S3" t="n">
-        <v>41.9191675097569</v>
+        <v>42.02550960213564</v>
       </c>
       <c r="T3" t="n">
-        <v>41.8078274654559</v>
+        <v>41.91100126920853</v>
       </c>
       <c r="U3" t="n">
-        <v>49.32064072718993</v>
+        <v>49.47634540351032</v>
       </c>
       <c r="V3" t="n">
-        <v>41.6882860294765</v>
+        <v>41.78646823037803</v>
       </c>
       <c r="W3" t="n">
-        <v>53.49348608030591</v>
+        <v>53.6511702383715</v>
       </c>
       <c r="X3" t="n">
-        <v>41.35884397933955</v>
+        <v>41.44603483004561</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.67961306704692</v>
+        <v>43.84860942377318</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.45484910854751</v>
+        <v>44.56903934913453</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.65612642825275</v>
+        <v>41.75346220235117</v>
       </c>
       <c r="AB3" t="n">
-        <v>44.07810035166606</v>
+        <v>44.26124394299324</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.958771451649437</v>
+        <v>5.958771451649417</v>
       </c>
       <c r="C4" t="n">
-        <v>3.063154130162663</v>
+        <v>3.063154130162645</v>
       </c>
       <c r="D4" t="n">
-        <v>4.583173853009286</v>
+        <v>4.583173853009274</v>
       </c>
       <c r="E4" t="n">
-        <v>4.491857701461445</v>
+        <v>4.491857701461419</v>
       </c>
       <c r="F4" t="n">
-        <v>4.646078246743581</v>
+        <v>4.646078246743562</v>
       </c>
       <c r="G4" t="n">
-        <v>6.637159703831425</v>
+        <v>6.637159703831427</v>
       </c>
       <c r="H4" t="n">
-        <v>6.611718325599921</v>
+        <v>6.611718325599901</v>
       </c>
       <c r="I4" t="n">
-        <v>4.200992597566137</v>
+        <v>4.20099259756612</v>
       </c>
       <c r="J4" t="n">
-        <v>6.823608014778772</v>
+        <v>6.823608014778774</v>
       </c>
       <c r="K4" t="n">
-        <v>6.254764560721542</v>
+        <v>6.254764560721541</v>
       </c>
       <c r="L4" t="n">
-        <v>7.703468787016422</v>
+        <v>7.703468787016469</v>
       </c>
       <c r="M4" t="n">
-        <v>9.841604237983002</v>
+        <v>9.841604237982972</v>
       </c>
       <c r="N4" t="n">
-        <v>7.171533386977773</v>
+        <v>7.171533386977759</v>
       </c>
       <c r="O4" t="n">
-        <v>6.383930261660264</v>
+        <v>6.383930261660234</v>
       </c>
       <c r="P4" t="n">
-        <v>7.87607174604783</v>
+        <v>7.876071746047792</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.77344962414326</v>
+        <v>5.773449624143205</v>
       </c>
       <c r="R4" t="n">
-        <v>4.860712086113234</v>
+        <v>4.860712086113219</v>
       </c>
       <c r="S4" t="n">
-        <v>6.474211254316091</v>
+        <v>6.47421125431607</v>
       </c>
       <c r="T4" t="n">
-        <v>6.272509332345686</v>
+        <v>6.272509332345671</v>
       </c>
       <c r="U4" t="n">
-        <v>8.68009087306465</v>
+        <v>8.680090873064589</v>
       </c>
       <c r="V4" t="n">
-        <v>6.116671802223239</v>
+        <v>6.116671802223244</v>
       </c>
       <c r="W4" t="n">
-        <v>8.752498563223481</v>
+        <v>8.75249856322344</v>
       </c>
       <c r="X4" t="n">
-        <v>5.568056522775903</v>
+        <v>5.568056522775892</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.245363694056401</v>
+        <v>9.245363694056358</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.837684138097909</v>
+        <v>6.837684138097883</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.044307047278175</v>
+        <v>6.044307047278173</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.830662539209808</v>
+        <v>9.830662539209786</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.59295066876508</v>
+        <v>79.59295066876429</v>
       </c>
       <c r="C5" t="n">
-        <v>28.48735538111602</v>
+        <v>28.487355381116</v>
       </c>
       <c r="D5" t="n">
-        <v>61.19991272789832</v>
+        <v>61.19991272789805</v>
       </c>
       <c r="E5" t="n">
         <v>56.01891517752794</v>
       </c>
       <c r="F5" t="n">
-        <v>64.03946431738021</v>
+        <v>64.03946431738026</v>
       </c>
       <c r="G5" t="n">
-        <v>94.85644287227058</v>
+        <v>94.85644287227083</v>
       </c>
       <c r="H5" t="n">
         <v>108.8620019948882</v>
       </c>
       <c r="I5" t="n">
-        <v>53.69400632597093</v>
+        <v>53.69400632597106</v>
       </c>
       <c r="J5" t="n">
-        <v>101.2508451083561</v>
+        <v>101.2508451083562</v>
       </c>
       <c r="K5" t="n">
-        <v>95.95707232069437</v>
+        <v>95.95707232069428</v>
       </c>
       <c r="L5" t="n">
-        <v>120.4153028042077</v>
+        <v>120.4153028042078</v>
       </c>
       <c r="M5" t="n">
-        <v>175.2380915959088</v>
+        <v>175.2380915959084</v>
       </c>
       <c r="N5" t="n">
-        <v>112.7863197477354</v>
+        <v>112.7863197477355</v>
       </c>
       <c r="O5" t="n">
-        <v>85.48114031744191</v>
+        <v>85.48114031744151</v>
       </c>
       <c r="P5" t="n">
-        <v>117.2870097399863</v>
+        <v>117.2870097399864</v>
       </c>
       <c r="Q5" t="n">
-        <v>84.64997914673984</v>
+        <v>84.64997914673978</v>
       </c>
       <c r="R5" t="n">
-        <v>68.80666382409234</v>
+        <v>68.80666382409231</v>
       </c>
       <c r="S5" t="n">
-        <v>92.02568332854516</v>
+        <v>92.02568332854558</v>
       </c>
       <c r="T5" t="n">
-        <v>97.53617242777239</v>
+        <v>97.53617242777231</v>
       </c>
       <c r="U5" t="n">
         <v>137.315353078078</v>
       </c>
       <c r="V5" t="n">
-        <v>83.19859025623199</v>
+        <v>83.19859025623205</v>
       </c>
       <c r="W5" t="n">
-        <v>142.6623649242607</v>
+        <v>142.6623649242605</v>
       </c>
       <c r="X5" t="n">
-        <v>81.04741386160957</v>
+        <v>81.04741386160941</v>
       </c>
       <c r="Y5" t="n">
-        <v>152.7377409684672</v>
+        <v>152.7377409684669</v>
       </c>
       <c r="Z5" t="n">
-        <v>98.69762641940274</v>
+        <v>98.69762641940255</v>
       </c>
       <c r="AA5" t="n">
-        <v>88.47641829302817</v>
+        <v>88.47641829302843</v>
       </c>
       <c r="AB5" t="n">
-        <v>180.6103279895025</v>
+        <v>180.6103279895026</v>
       </c>
     </row>
     <row r="6">
@@ -938,22 +938,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>133.7113716979431</v>
+        <v>133.7113716979432</v>
       </c>
       <c r="C6" t="n">
-        <v>156.3763591790596</v>
+        <v>156.3763591790597</v>
       </c>
       <c r="D6" t="n">
         <v>157.8963789019063</v>
       </c>
       <c r="E6" t="n">
-        <v>157.8050627503584</v>
+        <v>157.8050627503586</v>
       </c>
       <c r="F6" t="n">
-        <v>132.3986784930372</v>
+        <v>132.3986784930374</v>
       </c>
       <c r="G6" t="n">
-        <v>159.9503647527284</v>
+        <v>159.9503647527286</v>
       </c>
       <c r="H6" t="n">
         <v>159.924923374497</v>
@@ -962,22 +962,22 @@
         <v>131.9535928438598</v>
       </c>
       <c r="J6" t="n">
-        <v>134.5762082610723</v>
+        <v>134.5762082610725</v>
       </c>
       <c r="K6" t="n">
-        <v>159.5679696096185</v>
+        <v>159.5679696096186</v>
       </c>
       <c r="L6" t="n">
-        <v>161.0166738359135</v>
+        <v>161.0166738359137</v>
       </c>
       <c r="M6" t="n">
-        <v>163.1548092868801</v>
+        <v>163.1548092868802</v>
       </c>
       <c r="N6" t="n">
         <v>134.9386897789306</v>
       </c>
       <c r="O6" t="n">
-        <v>134.1510834482693</v>
+        <v>134.1510834482694</v>
       </c>
       <c r="P6" t="n">
         <v>161.2542468551927</v>
@@ -986,34 +986,34 @@
         <v>159.0866546730404</v>
       </c>
       <c r="R6" t="n">
-        <v>158.1739171350102</v>
+        <v>158.1739171350106</v>
       </c>
       <c r="S6" t="n">
-        <v>134.2268115006097</v>
+        <v>134.2268115006098</v>
       </c>
       <c r="T6" t="n">
-        <v>134.0251095786393</v>
+        <v>134.0251095786395</v>
       </c>
       <c r="U6" t="n">
-        <v>136.4347539285932</v>
+        <v>136.4347539285933</v>
       </c>
       <c r="V6" t="n">
-        <v>159.4298768511202</v>
+        <v>159.4298768511203</v>
       </c>
       <c r="W6" t="n">
-        <v>162.1306688099944</v>
+        <v>162.1306688099945</v>
       </c>
       <c r="X6" t="n">
-        <v>158.881261571673</v>
+        <v>158.8812615716731</v>
       </c>
       <c r="Y6" t="n">
         <v>142.6207229350815</v>
       </c>
       <c r="Z6" t="n">
-        <v>134.5902843843916</v>
+        <v>134.5902843843917</v>
       </c>
       <c r="AA6" t="n">
-        <v>159.3575120961754</v>
+        <v>159.3575120961753</v>
       </c>
       <c r="AB6" t="n">
         <v>137.6174078246913</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.302718952914929</v>
+        <v>7.302718952914913</v>
       </c>
       <c r="C7" t="n">
-        <v>4.407101631428175</v>
+        <v>4.40710163142815</v>
       </c>
       <c r="D7" t="n">
-        <v>5.927121354274782</v>
+        <v>5.927121354274761</v>
       </c>
       <c r="E7" t="n">
-        <v>5.835805202726942</v>
+        <v>5.835805202726915</v>
       </c>
       <c r="F7" t="n">
-        <v>5.990025748009049</v>
+        <v>5.990025748009041</v>
       </c>
       <c r="G7" t="n">
-        <v>7.981107205096929</v>
+        <v>7.981107205096915</v>
       </c>
       <c r="H7" t="n">
-        <v>7.955665826865429</v>
+        <v>7.955665826865403</v>
       </c>
       <c r="I7" t="n">
-        <v>5.544940098831651</v>
+        <v>5.544940098831617</v>
       </c>
       <c r="J7" t="n">
-        <v>8.167555516044278</v>
+        <v>8.167555516044271</v>
       </c>
       <c r="K7" t="n">
-        <v>7.598712061987051</v>
+        <v>7.598712061987038</v>
       </c>
       <c r="L7" t="n">
         <v>9.047416288281962</v>
       </c>
       <c r="M7" t="n">
-        <v>11.18555173924851</v>
+        <v>11.18555173924846</v>
       </c>
       <c r="N7" t="n">
-        <v>8.515480888243264</v>
+        <v>8.515480888243252</v>
       </c>
       <c r="O7" t="n">
-        <v>7.727862772552006</v>
+        <v>7.727862772551969</v>
       </c>
       <c r="P7" t="n">
-        <v>9.220004256939564</v>
+        <v>9.220004256939523</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.117397125408734</v>
+        <v>7.117397125408763</v>
       </c>
       <c r="R7" t="n">
-        <v>6.204659587378751</v>
+        <v>6.20465958737872</v>
       </c>
       <c r="S7" t="n">
-        <v>7.81815875558158</v>
+        <v>7.818158755581569</v>
       </c>
       <c r="T7" t="n">
-        <v>7.6164568336112</v>
+        <v>7.616456833611169</v>
       </c>
       <c r="U7" t="n">
-        <v>10.02680514579375</v>
+        <v>10.02680514579377</v>
       </c>
       <c r="V7" t="n">
-        <v>7.460619303488736</v>
+        <v>7.460619303488739</v>
       </c>
       <c r="W7" t="n">
         <v>10.09644606448895</v>
       </c>
       <c r="X7" t="n">
-        <v>6.912004024041419</v>
+        <v>6.912004024041385</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.5913740045568</v>
+        <v>10.59137400455676</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.181631639363424</v>
+        <v>8.181631639363379</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.388254548543685</v>
+        <v>7.388254548543674</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.17461004047529</v>
+        <v>11.17461004047527</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.87715136980653</v>
+        <v>7.877151369806485</v>
       </c>
       <c r="C8" t="n">
-        <v>6.435161644917458</v>
+        <v>6.435161644917455</v>
       </c>
       <c r="D8" t="n">
-        <v>7.955181367764093</v>
+        <v>7.955181367764078</v>
       </c>
       <c r="E8" t="n">
-        <v>7.08985140078806</v>
+        <v>7.089851400788048</v>
       </c>
       <c r="F8" t="n">
-        <v>6.790916355302614</v>
+        <v>6.790916355302615</v>
       </c>
       <c r="G8" t="n">
-        <v>10.31058637009214</v>
+        <v>10.31058637009217</v>
       </c>
       <c r="H8" t="n">
-        <v>9.98372584035471</v>
+        <v>9.983725840354712</v>
       </c>
       <c r="I8" t="n">
-        <v>7.573000112320932</v>
+        <v>7.573000112320954</v>
       </c>
       <c r="J8" t="n">
         <v>10.19561552953358</v>
       </c>
       <c r="K8" t="n">
-        <v>9.626772075476334</v>
+        <v>9.626772075476357</v>
       </c>
       <c r="L8" t="n">
-        <v>11.07547630177124</v>
+        <v>11.07547630177126</v>
       </c>
       <c r="M8" t="n">
-        <v>13.21361175273829</v>
+        <v>13.21361175273828</v>
       </c>
       <c r="N8" t="n">
-        <v>9.416736327233748</v>
+        <v>9.416736327233746</v>
       </c>
       <c r="O8" t="n">
-        <v>8.938788881777811</v>
+        <v>8.93878888177778</v>
       </c>
       <c r="P8" t="n">
-        <v>10.3550262768174</v>
+        <v>10.35502627681734</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.406158542709045</v>
+        <v>7.406158542709055</v>
       </c>
       <c r="R8" t="n">
-        <v>8.232719600868032</v>
+        <v>8.232719600868025</v>
       </c>
       <c r="S8" t="n">
-        <v>9.846218769070877</v>
+        <v>9.846218769070845</v>
       </c>
       <c r="T8" t="n">
-        <v>9.644516847100498</v>
+        <v>9.644516847100476</v>
       </c>
       <c r="U8" t="n">
         <v>11.34522213786832</v>
       </c>
       <c r="V8" t="n">
-        <v>9.091995518424474</v>
+        <v>9.091995518424483</v>
       </c>
       <c r="W8" t="n">
-        <v>12.12479175534861</v>
+        <v>12.12479175534855</v>
       </c>
       <c r="X8" t="n">
-        <v>7.333993297679033</v>
+        <v>7.333993297679027</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.06569600687694</v>
+        <v>14.06569600687693</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.729062177538697</v>
+        <v>8.729062177538683</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.416314562032982</v>
+        <v>9.416314562032959</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.72110562700791</v>
+        <v>14.72110562700795</v>
       </c>
     </row>
     <row r="9">
@@ -1205,46 +1205,46 @@
         <v>11.4492379981237</v>
       </c>
       <c r="C9" t="n">
-        <v>10.17419565914791</v>
+        <v>10.17419565914792</v>
       </c>
       <c r="D9" t="n">
-        <v>11.69421538199454</v>
+        <v>11.69421538199452</v>
       </c>
       <c r="E9" t="n">
-        <v>11.22887735868203</v>
+        <v>11.22887735868207</v>
       </c>
       <c r="F9" t="n">
-        <v>8.021251764066756</v>
+        <v>8.021251764066744</v>
       </c>
       <c r="G9" t="n">
         <v>13.7482015240188</v>
       </c>
       <c r="H9" t="n">
-        <v>13.72275985458518</v>
+        <v>13.72275985458517</v>
       </c>
       <c r="I9" t="n">
         <v>11.31203412655138</v>
       </c>
       <c r="J9" t="n">
-        <v>13.93464954376402</v>
+        <v>13.93464954376404</v>
       </c>
       <c r="K9" t="n">
-        <v>13.36580608970679</v>
+        <v>13.36580608970681</v>
       </c>
       <c r="L9" t="n">
         <v>14.81451031600172</v>
       </c>
       <c r="M9" t="n">
-        <v>16.95264576696825</v>
+        <v>16.95264576696823</v>
       </c>
       <c r="N9" t="n">
-        <v>14.282574915963</v>
+        <v>14.28257491596302</v>
       </c>
       <c r="O9" t="n">
-        <v>14.03202860559393</v>
+        <v>14.03202860559394</v>
       </c>
       <c r="P9" t="n">
-        <v>15.64097066955822</v>
+        <v>15.64097066955823</v>
       </c>
       <c r="Q9" t="n">
         <v>12.88449144433062</v>
@@ -1253,16 +1253,16 @@
         <v>11.97175361509848</v>
       </c>
       <c r="S9" t="n">
-        <v>13.58525278330133</v>
+        <v>13.58525278330134</v>
       </c>
       <c r="T9" t="n">
-        <v>13.38355086133096</v>
+        <v>13.38355086133093</v>
       </c>
       <c r="U9" t="n">
         <v>15.7931952112848</v>
       </c>
       <c r="V9" t="n">
-        <v>15.09782041297532</v>
+        <v>15.09782041297534</v>
       </c>
       <c r="W9" t="n">
         <v>15.8635400922087</v>
@@ -1271,13 +1271,13 @@
         <v>12.67909805176116</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.35846803227654</v>
+        <v>16.35846803227653</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.97166317541233</v>
+        <v>12.9716631754123</v>
       </c>
       <c r="AA9" t="n">
-        <v>13.15534857626343</v>
+        <v>13.15534857626345</v>
       </c>
       <c r="AB9" t="n">
         <v>16.94170406819504</v>
@@ -1446,19 +1446,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.79767279880322</v>
+        <v>38.79767279880325</v>
       </c>
       <c r="C2" t="n">
         <v>41.7832252513118</v>
       </c>
       <c r="D2" t="n">
-        <v>38.87096952041478</v>
+        <v>38.87096952041477</v>
       </c>
       <c r="E2" t="n">
-        <v>38.82519896262243</v>
+        <v>38.82519896262247</v>
       </c>
       <c r="F2" t="n">
-        <v>38.93888780294378</v>
+        <v>38.9388878029438</v>
       </c>
       <c r="G2" t="n">
         <v>38.98457544179062</v>
@@ -1467,64 +1467,64 @@
         <v>38.97324814550442</v>
       </c>
       <c r="I2" t="n">
-        <v>38.86908781616912</v>
+        <v>38.86908781616911</v>
       </c>
       <c r="J2" t="n">
-        <v>38.96219847616745</v>
+        <v>38.96219847616747</v>
       </c>
       <c r="K2" t="n">
-        <v>39.01754417691996</v>
+        <v>39.01754417691997</v>
       </c>
       <c r="L2" t="n">
-        <v>38.93175487760107</v>
+        <v>38.93175487760108</v>
       </c>
       <c r="M2" t="n">
-        <v>38.93490611117453</v>
+        <v>38.93490611117451</v>
       </c>
       <c r="N2" t="n">
         <v>39.02692214176368</v>
       </c>
       <c r="O2" t="n">
-        <v>42.77805981120951</v>
+        <v>42.77805981120952</v>
       </c>
       <c r="P2" t="n">
-        <v>39.17523058394656</v>
+        <v>39.17523058394659</v>
       </c>
       <c r="Q2" t="n">
-        <v>38.86757583564978</v>
+        <v>38.8675758356498</v>
       </c>
       <c r="R2" t="n">
-        <v>38.85575154832134</v>
+        <v>38.85575154832132</v>
       </c>
       <c r="S2" t="n">
-        <v>38.99460269978464</v>
+        <v>38.99460269978466</v>
       </c>
       <c r="T2" t="n">
-        <v>38.98869322774883</v>
+        <v>38.98869322774885</v>
       </c>
       <c r="U2" t="n">
-        <v>42.36330489084965</v>
+        <v>42.36330489084967</v>
       </c>
       <c r="V2" t="n">
         <v>38.90541315723291</v>
       </c>
       <c r="W2" t="n">
-        <v>44.98574370532948</v>
+        <v>44.98574370532945</v>
       </c>
       <c r="X2" t="n">
-        <v>39.16914714456269</v>
+        <v>39.16914714456271</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.12508096030318</v>
+        <v>39.12508096030319</v>
       </c>
       <c r="Z2" t="n">
-        <v>39.95932211852326</v>
+        <v>39.9593221185233</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.09284144629075</v>
+        <v>39.09284144629076</v>
       </c>
       <c r="AB2" t="n">
-        <v>38.94229044815238</v>
+        <v>38.94229044815237</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.50376106155622</v>
+        <v>38.50835835811914</v>
       </c>
       <c r="C3" t="n">
-        <v>43.65229972366941</v>
+        <v>43.66710475996776</v>
       </c>
       <c r="D3" t="n">
-        <v>39.02715485099089</v>
+        <v>39.05042055939309</v>
       </c>
       <c r="E3" t="n">
-        <v>38.69966036024099</v>
+        <v>38.71116983592781</v>
       </c>
       <c r="F3" t="n">
-        <v>39.51330217221511</v>
+        <v>39.55400848344085</v>
       </c>
       <c r="G3" t="n">
-        <v>39.82897601903489</v>
+        <v>39.88033197460292</v>
       </c>
       <c r="H3" t="n">
-        <v>39.76281154299256</v>
+        <v>39.81237693666242</v>
       </c>
       <c r="I3" t="n">
-        <v>39.01501434053375</v>
+        <v>39.03784298479466</v>
       </c>
       <c r="J3" t="n">
-        <v>39.67439755717765</v>
+        <v>39.72044896339833</v>
       </c>
       <c r="K3" t="n">
-        <v>40.06584519772085</v>
+        <v>40.12624772183586</v>
       </c>
       <c r="L3" t="n">
-        <v>39.45598775250475</v>
+        <v>39.49434330814569</v>
       </c>
       <c r="M3" t="n">
-        <v>39.4894070050144</v>
+        <v>39.52927227035657</v>
       </c>
       <c r="N3" t="n">
-        <v>40.14283495315444</v>
+        <v>40.20544261218997</v>
       </c>
       <c r="O3" t="n">
-        <v>46.4213369137717</v>
+        <v>46.4877803174758</v>
       </c>
       <c r="P3" t="n">
-        <v>41.1823404403031</v>
+        <v>41.28114395946973</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.001853418548</v>
+        <v>39.02420286842224</v>
       </c>
       <c r="R3" t="n">
-        <v>38.92049835784486</v>
+        <v>38.93997224279192</v>
       </c>
       <c r="S3" t="n">
-        <v>39.90124493755184</v>
+        <v>39.95524349425948</v>
       </c>
       <c r="T3" t="n">
-        <v>39.87099168448707</v>
+        <v>39.92418509748044</v>
       </c>
       <c r="U3" t="n">
-        <v>45.5631726567054</v>
+        <v>45.62198907471274</v>
       </c>
       <c r="V3" t="n">
-        <v>39.26820899589327</v>
+        <v>39.29979459080548</v>
       </c>
       <c r="W3" t="n">
-        <v>50.77021166782205</v>
+        <v>50.86909970734636</v>
       </c>
       <c r="X3" t="n">
-        <v>41.15173433708225</v>
+        <v>41.25062471882522</v>
       </c>
       <c r="Y3" t="n">
-        <v>40.84300548747163</v>
+        <v>40.93028592195345</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.86708536001722</v>
+        <v>40.89224006294877</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.61210223970389</v>
+        <v>40.69118163318212</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.54120770839887</v>
+        <v>39.58260407167658</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.231913899733783</v>
+        <v>1.231913899733787</v>
       </c>
       <c r="C4" t="n">
-        <v>1.684204024660515</v>
+        <v>1.684204024660499</v>
       </c>
       <c r="D4" t="n">
-        <v>2.059834088493855</v>
+        <v>2.059834088493838</v>
       </c>
       <c r="E4" t="n">
-        <v>1.542834582733042</v>
+        <v>1.542834582733003</v>
       </c>
       <c r="F4" t="n">
-        <v>2.827002333612737</v>
+        <v>2.827002333612708</v>
       </c>
       <c r="G4" t="n">
-        <v>3.343065231740045</v>
+        <v>3.343065231739975</v>
       </c>
       <c r="H4" t="n">
-        <v>3.215118209373704</v>
+        <v>3.215118209373696</v>
       </c>
       <c r="I4" t="n">
-        <v>2.038579373412538</v>
+        <v>2.03857937341252</v>
       </c>
       <c r="J4" t="n">
-        <v>3.090864016999223</v>
+        <v>3.090864016999183</v>
       </c>
       <c r="K4" t="n">
-        <v>3.715462261393433</v>
+        <v>3.715462261393406</v>
       </c>
       <c r="L4" t="n">
-        <v>2.74643266055907</v>
+        <v>2.746432660559042</v>
       </c>
       <c r="M4" t="n">
-        <v>2.791647448925112</v>
+        <v>2.791647448925087</v>
       </c>
       <c r="N4" t="n">
-        <v>3.821390688380156</v>
+        <v>3.821390688380181</v>
       </c>
       <c r="O4" t="n">
-        <v>4.029151129765974</v>
+        <v>4.029151129765993</v>
       </c>
       <c r="P4" t="n">
-        <v>5.496602768089915</v>
+        <v>5.496602768089905</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.021500857901084</v>
+        <v>2.021500857901064</v>
       </c>
       <c r="R4" t="n">
-        <v>1.887940093085597</v>
+        <v>1.887940093085619</v>
       </c>
       <c r="S4" t="n">
-        <v>3.456327723549018</v>
+        <v>3.456327723549038</v>
       </c>
       <c r="T4" t="n">
         <v>3.389577518413202</v>
       </c>
       <c r="U4" t="n">
-        <v>3.634438463141649</v>
+        <v>3.634438463141597</v>
       </c>
       <c r="V4" t="n">
-        <v>2.452298180244605</v>
+        <v>2.452298180244587</v>
       </c>
       <c r="W4" t="n">
-        <v>5.456616956968288</v>
+        <v>5.456616956968305</v>
       </c>
       <c r="X4" t="n">
-        <v>5.427887521728737</v>
+        <v>5.427887521728715</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.896997334888393</v>
+        <v>4.896997334888399</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.159428864555268</v>
+        <v>2.159428864555252</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.565979557391797</v>
+        <v>4.5659795573918</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.865895163200152</v>
+        <v>2.865895163200133</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.72202285942897</v>
+        <v>3.722022859428923</v>
       </c>
       <c r="C5" t="n">
-        <v>11.77338069445656</v>
+        <v>11.7733806944566</v>
       </c>
       <c r="D5" t="n">
-        <v>18.50582101282184</v>
+        <v>18.50582101282183</v>
       </c>
       <c r="E5" t="n">
-        <v>8.932877360417882</v>
+        <v>8.932877360417905</v>
       </c>
       <c r="F5" t="n">
-        <v>32.80575164126046</v>
+        <v>32.80575164126043</v>
       </c>
       <c r="G5" t="n">
-        <v>36.54306407574137</v>
+        <v>36.54306407574139</v>
       </c>
       <c r="H5" t="n">
-        <v>41.88713106378827</v>
+        <v>41.88713106378819</v>
       </c>
       <c r="I5" t="n">
-        <v>18.79804677550249</v>
+        <v>18.79804677550246</v>
       </c>
       <c r="J5" t="n">
-        <v>34.73014416819943</v>
+        <v>34.73014416819941</v>
       </c>
       <c r="K5" t="n">
-        <v>43.94296308073689</v>
+        <v>43.94296308073685</v>
       </c>
       <c r="L5" t="n">
         <v>28.06080191001574</v>
       </c>
       <c r="M5" t="n">
-        <v>31.81537470788103</v>
+        <v>31.81537470788099</v>
       </c>
       <c r="N5" t="n">
-        <v>51.02917605539093</v>
+        <v>51.02917605539083</v>
       </c>
       <c r="O5" t="n">
-        <v>47.26739004629542</v>
+        <v>47.26739004629537</v>
       </c>
       <c r="P5" t="n">
-        <v>70.82254604826761</v>
+        <v>70.8225460482675</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.26787462422494</v>
+        <v>17.26787462422493</v>
       </c>
       <c r="R5" t="n">
-        <v>16.47868623370214</v>
+        <v>16.47868623370215</v>
       </c>
       <c r="S5" t="n">
-        <v>38.91106526482577</v>
+        <v>38.91106526482574</v>
       </c>
       <c r="T5" t="n">
-        <v>43.90924127135468</v>
+        <v>43.90924127135465</v>
       </c>
       <c r="U5" t="n">
-        <v>41.96417205804574</v>
+        <v>41.96417205804577</v>
       </c>
       <c r="V5" t="n">
-        <v>22.91746977870998</v>
+        <v>22.91746977870995</v>
       </c>
       <c r="W5" t="n">
-        <v>78.39514731899001</v>
+        <v>78.39514731898964</v>
       </c>
       <c r="X5" t="n">
-        <v>76.24654622615523</v>
+        <v>76.24654622615519</v>
       </c>
       <c r="Y5" t="n">
-        <v>70.43513065103099</v>
+        <v>70.43513065103107</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.69210058951027</v>
+        <v>17.69210058951026</v>
       </c>
       <c r="AA5" t="n">
-        <v>63.5755133902956</v>
+        <v>63.57551339029578</v>
       </c>
       <c r="AB5" t="n">
-        <v>35.24090102951153</v>
+        <v>35.24090102951156</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.4002077300202</v>
+        <v>112.4002077300201</v>
       </c>
       <c r="C6" t="n">
-        <v>134.7710241872199</v>
+        <v>134.77102418722</v>
       </c>
       <c r="D6" t="n">
-        <v>113.2281279187803</v>
+        <v>113.2281279187802</v>
       </c>
       <c r="E6" t="n">
         <v>134.6296547452925</v>
       </c>
       <c r="F6" t="n">
-        <v>135.9138224961723</v>
+        <v>135.9138224961722</v>
       </c>
       <c r="G6" t="n">
-        <v>114.5113590620265</v>
+        <v>114.5113590620263</v>
       </c>
       <c r="H6" t="n">
-        <v>114.3834120396601</v>
+        <v>114.38341203966</v>
       </c>
       <c r="I6" t="n">
-        <v>113.2068732036989</v>
+        <v>113.2068732036988</v>
       </c>
       <c r="J6" t="n">
         <v>136.1776841795587</v>
       </c>
       <c r="K6" t="n">
-        <v>114.8837560916798</v>
+        <v>114.8837560916797</v>
       </c>
       <c r="L6" t="n">
         <v>135.8332528231185</v>
       </c>
       <c r="M6" t="n">
-        <v>113.9599412792114</v>
+        <v>113.9599412792113</v>
       </c>
       <c r="N6" t="n">
         <v>114.995445598669</v>
       </c>
       <c r="O6" t="n">
-        <v>137.1788435050002</v>
+        <v>137.1788435050001</v>
       </c>
       <c r="P6" t="n">
-        <v>110.240146006147</v>
+        <v>110.2401460061469</v>
       </c>
       <c r="Q6" t="n">
         <v>113.1897946881874</v>
       </c>
       <c r="R6" t="n">
-        <v>113.056233923372</v>
+        <v>113.0562339233719</v>
       </c>
       <c r="S6" t="n">
-        <v>136.5431478861085</v>
+        <v>136.5431478861084</v>
       </c>
       <c r="T6" t="n">
-        <v>114.5578713486995</v>
+        <v>114.5578713486997</v>
       </c>
       <c r="U6" t="n">
-        <v>136.754400989884</v>
+        <v>136.7544009898841</v>
       </c>
       <c r="V6" t="n">
-        <v>113.6205920105308</v>
+        <v>113.6205920105307</v>
       </c>
       <c r="W6" t="n">
-        <v>122.3100922071639</v>
+        <v>122.3100922071635</v>
       </c>
       <c r="X6" t="n">
-        <v>138.5147076842882</v>
+        <v>138.5147076842881</v>
       </c>
       <c r="Y6" t="n">
-        <v>120.9798284724758</v>
+        <v>120.9798284724756</v>
       </c>
       <c r="Z6" t="n">
         <v>113.3277226948416</v>
       </c>
       <c r="AA6" t="n">
-        <v>137.6527997199513</v>
+        <v>137.6527997199514</v>
       </c>
       <c r="AB6" t="n">
-        <v>114.0431783720553</v>
+        <v>114.0431783720552</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.068931116953645</v>
+        <v>2.06893111695363</v>
       </c>
       <c r="C7" t="n">
-        <v>2.52122124188038</v>
+        <v>2.521221241880371</v>
       </c>
       <c r="D7" t="n">
-        <v>2.896851305713716</v>
+        <v>2.896851305713697</v>
       </c>
       <c r="E7" t="n">
-        <v>2.379851799952906</v>
+        <v>2.379851799952895</v>
       </c>
       <c r="F7" t="n">
-        <v>3.664019550832592</v>
+        <v>3.664019550832584</v>
       </c>
       <c r="G7" t="n">
-        <v>4.18008244895991</v>
+        <v>4.180082448959872</v>
       </c>
       <c r="H7" t="n">
-        <v>4.052135426593559</v>
+        <v>4.052135426593566</v>
       </c>
       <c r="I7" t="n">
-        <v>2.875596590632395</v>
+        <v>2.875596590632385</v>
       </c>
       <c r="J7" t="n">
-        <v>3.927881234219081</v>
+        <v>3.927881234219067</v>
       </c>
       <c r="K7" t="n">
-        <v>4.55247947861329</v>
+        <v>4.552479478613283</v>
       </c>
       <c r="L7" t="n">
-        <v>3.583449877778927</v>
+        <v>3.583449877778914</v>
       </c>
       <c r="M7" t="n">
-        <v>3.628664666144978</v>
+        <v>3.628664666144964</v>
       </c>
       <c r="N7" t="n">
-        <v>4.658407905600011</v>
+        <v>4.65840790560003</v>
       </c>
       <c r="O7" t="n">
-        <v>4.866167462408574</v>
+        <v>4.866167462408555</v>
       </c>
       <c r="P7" t="n">
-        <v>6.333619100732516</v>
+        <v>6.333619100732546</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.858518075120942</v>
+        <v>2.85851807512093</v>
       </c>
       <c r="R7" t="n">
-        <v>2.724957310305454</v>
+        <v>2.724957310305453</v>
       </c>
       <c r="S7" t="n">
-        <v>4.293344940768876</v>
+        <v>4.293344940768851</v>
       </c>
       <c r="T7" t="n">
-        <v>4.226594735633061</v>
+        <v>4.22659473563309</v>
       </c>
       <c r="U7" t="n">
-        <v>4.497737764503388</v>
+        <v>4.497737764503344</v>
       </c>
       <c r="V7" t="n">
-        <v>3.28931539746446</v>
+        <v>3.289315397464447</v>
       </c>
       <c r="W7" t="n">
-        <v>6.293634174188148</v>
+        <v>6.293634174188076</v>
       </c>
       <c r="X7" t="n">
         <v>6.2649047389486</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.767156916291156</v>
+        <v>5.767156916291106</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.996446081775126</v>
+        <v>2.996446081775121</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.402996774611657</v>
+        <v>5.402996774611659</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.702912380420011</v>
+        <v>3.702912380419999</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.29437484195759</v>
+        <v>2.294374841957577</v>
       </c>
       <c r="C8" t="n">
-        <v>3.544501671557816</v>
+        <v>3.544501671557799</v>
       </c>
       <c r="D8" t="n">
-        <v>3.920131735391155</v>
+        <v>3.92013173539114</v>
       </c>
       <c r="E8" t="n">
-        <v>2.978307719332815</v>
+        <v>2.978307719332816</v>
       </c>
       <c r="F8" t="n">
-        <v>4.013756909778369</v>
+        <v>4.013756909778367</v>
       </c>
       <c r="G8" t="n">
-        <v>5.368799516687153</v>
+        <v>5.368799516687149</v>
       </c>
       <c r="H8" t="n">
-        <v>5.075415856271001</v>
+        <v>5.075415856270996</v>
       </c>
       <c r="I8" t="n">
-        <v>3.898877020309832</v>
+        <v>3.898877020309815</v>
       </c>
       <c r="J8" t="n">
-        <v>4.951161663896512</v>
+        <v>4.951161663896483</v>
       </c>
       <c r="K8" t="n">
-        <v>5.575759908290721</v>
+        <v>5.575759908290705</v>
       </c>
       <c r="L8" t="n">
-        <v>4.606730307456363</v>
+        <v>4.606730307456347</v>
       </c>
       <c r="M8" t="n">
-        <v>4.651945095824143</v>
+        <v>4.651945095824139</v>
       </c>
       <c r="N8" t="n">
-        <v>5.063231413689012</v>
+        <v>5.063231413689024</v>
       </c>
       <c r="O8" t="n">
-        <v>5.440949186507822</v>
+        <v>5.440949186507813</v>
       </c>
       <c r="P8" t="n">
-        <v>6.866740176214325</v>
+        <v>6.866740176214361</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.927168678231381</v>
+        <v>2.927168678231376</v>
       </c>
       <c r="R8" t="n">
-        <v>3.748237739982889</v>
+        <v>3.748237739982921</v>
       </c>
       <c r="S8" t="n">
-        <v>5.316625370446313</v>
+        <v>5.316625370446326</v>
       </c>
       <c r="T8" t="n">
-        <v>5.249875165310503</v>
+        <v>5.249875165310494</v>
       </c>
       <c r="U8" t="n">
-        <v>5.133149163499981</v>
+        <v>5.133149163499974</v>
       </c>
       <c r="V8" t="n">
         <v>4.088671783736465</v>
       </c>
       <c r="W8" t="n">
-        <v>7.317071400497662</v>
+        <v>7.317071400497603</v>
       </c>
       <c r="X8" t="n">
-        <v>6.406678660666175</v>
+        <v>6.406678660666155</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.574614326045966</v>
+        <v>7.574614326045971</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.20706958047906</v>
+        <v>3.207069580479071</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.426277204289103</v>
+        <v>6.426277204289089</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.559599961087687</v>
+        <v>5.55959996108769</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.696789236828527</v>
+        <v>3.696789236828513</v>
       </c>
       <c r="C9" t="n">
-        <v>4.884185055004945</v>
+        <v>4.884185055004956</v>
       </c>
       <c r="D9" t="n">
-        <v>5.259815118838284</v>
+        <v>5.259815118838285</v>
       </c>
       <c r="E9" t="n">
-        <v>4.573156518306461</v>
+        <v>4.573156518306424</v>
       </c>
       <c r="F9" t="n">
-        <v>4.332363601224333</v>
+        <v>4.332363601224337</v>
       </c>
       <c r="G9" t="n">
-        <v>6.543046653124371</v>
+        <v>6.543046653124362</v>
       </c>
       <c r="H9" t="n">
-        <v>6.415099239718132</v>
+        <v>6.415099239718106</v>
       </c>
       <c r="I9" t="n">
-        <v>5.238560403756959</v>
+        <v>5.238560403756978</v>
       </c>
       <c r="J9" t="n">
-        <v>6.290845047343657</v>
+        <v>6.290845047343622</v>
       </c>
       <c r="K9" t="n">
-        <v>6.915443291737864</v>
+        <v>6.91544329173786</v>
       </c>
       <c r="L9" t="n">
-        <v>5.946413690903499</v>
+        <v>5.946413690903504</v>
       </c>
       <c r="M9" t="n">
-        <v>5.991628479269538</v>
+        <v>5.991628479269543</v>
       </c>
       <c r="N9" t="n">
-        <v>7.021371718724583</v>
+        <v>7.021371718724577</v>
       </c>
       <c r="O9" t="n">
-        <v>7.472745744944564</v>
+        <v>7.472745744944557</v>
       </c>
       <c r="P9" t="n">
-        <v>8.993179073220285</v>
+        <v>8.993179073220277</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.221482279285412</v>
+        <v>5.22148227928537</v>
       </c>
       <c r="R9" t="n">
-        <v>5.087921123430022</v>
+        <v>5.087921123429999</v>
       </c>
       <c r="S9" t="n">
-        <v>6.656308753893445</v>
+        <v>6.65630875389345</v>
       </c>
       <c r="T9" t="n">
-        <v>6.589558548757628</v>
+        <v>6.58955854875764</v>
       </c>
       <c r="U9" t="n">
-        <v>6.867561857668972</v>
+        <v>6.867561857668971</v>
       </c>
       <c r="V9" t="n">
-        <v>6.500575504372739</v>
+        <v>6.500575504372706</v>
       </c>
       <c r="W9" t="n">
-        <v>8.656597987312713</v>
+        <v>8.656597987312697</v>
       </c>
       <c r="X9" t="n">
-        <v>8.627868552073167</v>
+        <v>8.627868552073197</v>
       </c>
       <c r="Y9" t="n">
         <v>8.130120729415722</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.916206685296476</v>
+        <v>4.916206685296457</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.765960587736236</v>
+        <v>7.76596058773624</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.065876193544578</v>
+        <v>6.065876193544591</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.6903050496308</v>
+        <v>39.69030504963082</v>
       </c>
       <c r="C2" t="n">
-        <v>42.45984275399571</v>
+        <v>42.45984275399569</v>
       </c>
       <c r="D2" t="n">
-        <v>39.6698047517094</v>
+        <v>39.66980475170944</v>
       </c>
       <c r="E2" t="n">
         <v>39.627353116949</v>
       </c>
       <c r="F2" t="n">
-        <v>39.60705433032805</v>
+        <v>39.6070543303281</v>
       </c>
       <c r="G2" t="n">
-        <v>39.80048354084981</v>
+        <v>39.80048354084985</v>
       </c>
       <c r="H2" t="n">
-        <v>39.76151256340708</v>
+        <v>39.7615125634071</v>
       </c>
       <c r="I2" t="n">
-        <v>39.59700275437993</v>
+        <v>39.59700275437996</v>
       </c>
       <c r="J2" t="n">
         <v>39.81279625376364</v>
       </c>
       <c r="K2" t="n">
-        <v>39.72485076381404</v>
+        <v>39.72485076381408</v>
       </c>
       <c r="L2" t="n">
-        <v>39.85223690284598</v>
+        <v>39.85223690284602</v>
       </c>
       <c r="M2" t="n">
-        <v>40.04309985702002</v>
+        <v>40.04309985702001</v>
       </c>
       <c r="N2" t="n">
-        <v>39.83144160389177</v>
+        <v>39.83144160389178</v>
       </c>
       <c r="O2" t="n">
-        <v>43.93394011868192</v>
+        <v>43.93394011868196</v>
       </c>
       <c r="P2" t="n">
-        <v>39.94141790205291</v>
+        <v>39.94141790205292</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.71341476273059</v>
+        <v>39.71341476273062</v>
       </c>
       <c r="R2" t="n">
         <v>39.69006463219088</v>
       </c>
       <c r="S2" t="n">
-        <v>39.77486470857872</v>
+        <v>39.77486470857877</v>
       </c>
       <c r="T2" t="n">
-        <v>39.71832236506722</v>
+        <v>39.71832236506725</v>
       </c>
       <c r="U2" t="n">
         <v>43.5235062423283</v>
       </c>
       <c r="V2" t="n">
-        <v>39.74335594036909</v>
+        <v>39.74335594036912</v>
       </c>
       <c r="W2" t="n">
-        <v>46.11587246602797</v>
+        <v>46.11587246602799</v>
       </c>
       <c r="X2" t="n">
         <v>39.74677401895287</v>
       </c>
       <c r="Y2" t="n">
-        <v>40.04659684064932</v>
+        <v>40.04659684064935</v>
       </c>
       <c r="Z2" t="n">
-        <v>41.1347173026514</v>
+        <v>41.13471730265142</v>
       </c>
       <c r="AA2" t="n">
         <v>39.71434570010576</v>
       </c>
       <c r="AB2" t="n">
-        <v>40.08853650961267</v>
+        <v>40.08853650961272</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.98397737578973</v>
+        <v>41.05993713777683</v>
       </c>
       <c r="C3" t="n">
-        <v>44.5095278598393</v>
+        <v>44.53762426440774</v>
       </c>
       <c r="D3" t="n">
-        <v>40.85247912703068</v>
+        <v>40.92438899010937</v>
       </c>
       <c r="E3" t="n">
-        <v>40.54301391569398</v>
+        <v>40.60355741705251</v>
       </c>
       <c r="F3" t="n">
-        <v>40.40353494337915</v>
+        <v>40.45977435551195</v>
       </c>
       <c r="G3" t="n">
-        <v>41.77062670286247</v>
+        <v>41.8741904715806</v>
       </c>
       <c r="H3" t="n">
-        <v>41.5148419968041</v>
+        <v>41.61067225938323</v>
       </c>
       <c r="I3" t="n">
-        <v>40.33230818934931</v>
+        <v>40.38582711031605</v>
       </c>
       <c r="J3" t="n">
-        <v>41.86354944364408</v>
+        <v>41.97078270251544</v>
       </c>
       <c r="K3" t="n">
-        <v>41.2368515463349</v>
+        <v>41.32262106310456</v>
       </c>
       <c r="L3" t="n">
-        <v>42.14791532600908</v>
+        <v>42.26508468144787</v>
       </c>
       <c r="M3" t="n">
-        <v>43.52270002283092</v>
+        <v>43.68986675125159</v>
       </c>
       <c r="N3" t="n">
-        <v>42.00417329841487</v>
+        <v>42.11666188149272</v>
       </c>
       <c r="O3" t="n">
-        <v>48.66406773612817</v>
+        <v>48.77103814253582</v>
       </c>
       <c r="P3" t="n">
-        <v>42.7725039734116</v>
+        <v>42.91097887813096</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.16113703514658</v>
+        <v>41.24391480963056</v>
       </c>
       <c r="R3" t="n">
-        <v>41.00061806913153</v>
+        <v>41.07796930341223</v>
       </c>
       <c r="S3" t="n">
-        <v>41.58874944795009</v>
+        <v>41.68614569592016</v>
       </c>
       <c r="T3" t="n">
-        <v>41.19962922059545</v>
+        <v>41.28391177422549</v>
       </c>
       <c r="U3" t="n">
-        <v>48.63796270395698</v>
+        <v>48.77492749202005</v>
       </c>
       <c r="V3" t="n">
-        <v>41.35838378466143</v>
+        <v>41.44775136721492</v>
       </c>
       <c r="W3" t="n">
-        <v>53.45454435368649</v>
+        <v>53.61625847391646</v>
       </c>
       <c r="X3" t="n">
-        <v>41.40082194051622</v>
+        <v>41.49219135802793</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.53427001332758</v>
+        <v>43.70088125145937</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.89546824493318</v>
+        <v>43.99552512583695</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.16488803295975</v>
+        <v>41.24756302688999</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.84278935280047</v>
+        <v>44.02024029096869</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.998758963970971</v>
+        <v>4.998758963970896</v>
       </c>
       <c r="C4" t="n">
-        <v>2.819671564423511</v>
+        <v>2.819671564423493</v>
       </c>
       <c r="D4" t="n">
-        <v>4.767198668346336</v>
+        <v>4.767198668346331</v>
       </c>
       <c r="E4" t="n">
-        <v>4.287687925010482</v>
+        <v>4.287687925010466</v>
       </c>
       <c r="F4" t="n">
-        <v>4.058403792223663</v>
+        <v>4.058403792223646</v>
       </c>
       <c r="G4" t="n">
-        <v>6.243275706900105</v>
+        <v>6.243275706900095</v>
       </c>
       <c r="H4" t="n">
-        <v>5.803080589148545</v>
+        <v>5.803080589148532</v>
       </c>
       <c r="I4" t="n">
-        <v>3.944866617936117</v>
+        <v>3.944866617936116</v>
       </c>
       <c r="J4" t="n">
-        <v>6.382946804849491</v>
+        <v>6.382946804849484</v>
       </c>
       <c r="K4" t="n">
-        <v>5.388968697484375</v>
+        <v>5.388968697484345</v>
       </c>
       <c r="L4" t="n">
-        <v>6.827853738369088</v>
+        <v>6.827853738369232</v>
       </c>
       <c r="M4" t="n">
-        <v>8.97645773632274</v>
+        <v>8.976457736322727</v>
       </c>
       <c r="N4" t="n">
-        <v>6.592961270371503</v>
+        <v>6.59296127037147</v>
       </c>
       <c r="O4" t="n">
-        <v>6.40488626355739</v>
+        <v>6.404886263557379</v>
       </c>
       <c r="P4" t="n">
-        <v>7.83519414969831</v>
+        <v>7.835194149698291</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.259793804426328</v>
+        <v>5.259793804426317</v>
       </c>
       <c r="R4" t="n">
-        <v>4.996043338389542</v>
+        <v>4.99604333838953</v>
       </c>
       <c r="S4" t="n">
-        <v>5.95389921115299</v>
+        <v>5.953899211152952</v>
       </c>
       <c r="T4" t="n">
-        <v>5.315227430427348</v>
+        <v>5.315227430427331</v>
       </c>
       <c r="U4" t="n">
-        <v>7.722120340241931</v>
+        <v>7.72212034024189</v>
       </c>
       <c r="V4" t="n">
-        <v>5.60169409601161</v>
+        <v>5.601694096011593</v>
       </c>
       <c r="W4" t="n">
-        <v>8.815665015626106</v>
+        <v>8.815665015626072</v>
       </c>
       <c r="X4" t="n">
-        <v>5.636601949472797</v>
+        <v>5.636601949472804</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.022774145663739</v>
+        <v>9.022774145663721</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.082490486442802</v>
+        <v>6.08249048644281</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.270309170331008</v>
+        <v>5.270309170331006</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.459995658735762</v>
+        <v>9.459995658735735</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.75916157411471</v>
+        <v>59.75916157411613</v>
       </c>
       <c r="C5" t="n">
-        <v>23.94081642223514</v>
+        <v>23.94081642223509</v>
       </c>
       <c r="D5" t="n">
         <v>63.61934709755231</v>
       </c>
       <c r="E5" t="n">
-        <v>50.94572384981467</v>
+        <v>50.94572384981532</v>
       </c>
       <c r="F5" t="n">
-        <v>49.61059341298865</v>
+        <v>49.61059341298863</v>
       </c>
       <c r="G5" t="n">
-        <v>83.45717907507584</v>
+        <v>83.4571790750758</v>
       </c>
       <c r="H5" t="n">
-        <v>87.56574024233809</v>
+        <v>87.56574024233791</v>
       </c>
       <c r="I5" t="n">
-        <v>47.7485068919657</v>
+        <v>47.74850689196583</v>
       </c>
       <c r="J5" t="n">
-        <v>88.89394962873634</v>
+        <v>88.89394962873651</v>
       </c>
       <c r="K5" t="n">
-        <v>70.65191769043112</v>
+        <v>70.65191769043105</v>
       </c>
       <c r="L5" t="n">
-        <v>98.91632886210277</v>
+        <v>98.91632886210597</v>
       </c>
       <c r="M5" t="n">
-        <v>148.7418659276117</v>
+        <v>148.7418659276116</v>
       </c>
       <c r="N5" t="n">
-        <v>97.07504839063225</v>
+        <v>97.07504839063216</v>
       </c>
       <c r="O5" t="n">
-        <v>82.01789368333692</v>
+        <v>82.01789368333695</v>
       </c>
       <c r="P5" t="n">
         <v>111.3444853587977</v>
       </c>
       <c r="Q5" t="n">
-        <v>71.4934582141549</v>
+        <v>71.49345821415473</v>
       </c>
       <c r="R5" t="n">
         <v>69.91685952017758</v>
       </c>
       <c r="S5" t="n">
-        <v>78.52271219999845</v>
+        <v>78.52271219999821</v>
       </c>
       <c r="T5" t="n">
-        <v>74.46942858685074</v>
+        <v>74.46942858685057</v>
       </c>
       <c r="U5" t="n">
-        <v>113.2713157601275</v>
+        <v>113.2713157601273</v>
       </c>
       <c r="V5" t="n">
-        <v>68.74591693129861</v>
+        <v>68.74591693129872</v>
       </c>
       <c r="W5" t="n">
-        <v>137.5269006219988</v>
+        <v>137.5269006219986</v>
       </c>
       <c r="X5" t="n">
-        <v>79.50697023362554</v>
+        <v>79.50697023362569</v>
       </c>
       <c r="Y5" t="n">
-        <v>139.9804907889937</v>
+        <v>139.9804907889934</v>
       </c>
       <c r="Z5" t="n">
-        <v>80.71747058623902</v>
+        <v>80.71747058623957</v>
       </c>
       <c r="AA5" t="n">
-        <v>70.08325061634876</v>
+        <v>70.08325061634895</v>
       </c>
       <c r="AB5" t="n">
-        <v>164.5232504725333</v>
+        <v>164.5232504725329</v>
       </c>
     </row>
     <row r="6">
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>124.5175939116262</v>
+        <v>124.517593911626</v>
       </c>
       <c r="C6" t="n">
         <v>146.2029713567362</v>
@@ -2667,13 +2667,13 @@
         <v>124.2860336160015</v>
       </c>
       <c r="E6" t="n">
-        <v>147.670987717323</v>
+        <v>147.6709877173231</v>
       </c>
       <c r="F6" t="n">
-        <v>123.577238739879</v>
+        <v>123.5772387398788</v>
       </c>
       <c r="G6" t="n">
-        <v>149.6265754992127</v>
+        <v>149.6265754992128</v>
       </c>
       <c r="H6" t="n">
         <v>149.1863803814612</v>
@@ -2685,58 +2685,58 @@
         <v>149.7662465971622</v>
       </c>
       <c r="K6" t="n">
-        <v>124.9078036451396</v>
+        <v>124.9078036451395</v>
       </c>
       <c r="L6" t="n">
-        <v>150.2111535306817</v>
+        <v>150.2111535306819</v>
       </c>
       <c r="M6" t="n">
-        <v>152.3597575286353</v>
+        <v>152.3597575286355</v>
       </c>
       <c r="N6" t="n">
-        <v>126.1213177036418</v>
+        <v>126.1213177036417</v>
       </c>
       <c r="O6" t="n">
-        <v>125.9348709339256</v>
+        <v>125.9348709339254</v>
       </c>
       <c r="P6" t="n">
-        <v>151.2767421989857</v>
+        <v>151.2767421989856</v>
       </c>
       <c r="Q6" t="n">
-        <v>124.7786287520816</v>
+        <v>124.7786287520815</v>
       </c>
       <c r="R6" t="n">
-        <v>148.3793431307021</v>
+        <v>148.3793431307023</v>
       </c>
       <c r="S6" t="n">
-        <v>125.4727341588081</v>
+        <v>125.4727341588082</v>
       </c>
       <c r="T6" t="n">
         <v>124.8340623780825</v>
       </c>
       <c r="U6" t="n">
-        <v>127.2414197880801</v>
+        <v>127.24141978808</v>
       </c>
       <c r="V6" t="n">
         <v>125.1205290436668</v>
       </c>
       <c r="W6" t="n">
-        <v>134.4539689499464</v>
+        <v>134.4539689499463</v>
       </c>
       <c r="X6" t="n">
         <v>149.0199017417854</v>
       </c>
       <c r="Y6" t="n">
-        <v>133.7973000142053</v>
+        <v>133.7973000142051</v>
       </c>
       <c r="Z6" t="n">
-        <v>125.6013254340981</v>
+        <v>125.601325434098</v>
       </c>
       <c r="AA6" t="n">
         <v>148.6536089626437</v>
       </c>
       <c r="AB6" t="n">
-        <v>129.0101184996722</v>
+        <v>129.0101184996723</v>
       </c>
     </row>
     <row r="7">
@@ -2746,82 +2746,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.199319933310755</v>
+        <v>6.199319933310711</v>
       </c>
       <c r="C7" t="n">
-        <v>4.020232533763326</v>
+        <v>4.020232533763318</v>
       </c>
       <c r="D7" t="n">
-        <v>5.967759637686151</v>
+        <v>5.967759637686139</v>
       </c>
       <c r="E7" t="n">
-        <v>5.488248894350293</v>
+        <v>5.488248894350297</v>
       </c>
       <c r="F7" t="n">
-        <v>5.25896476156348</v>
+        <v>5.258964761563465</v>
       </c>
       <c r="G7" t="n">
-        <v>7.443836676239901</v>
+        <v>7.443836676239892</v>
       </c>
       <c r="H7" t="n">
-        <v>7.003641558488363</v>
+        <v>7.003641558488352</v>
       </c>
       <c r="I7" t="n">
-        <v>5.145427587275927</v>
+        <v>5.14542758727592</v>
       </c>
       <c r="J7" t="n">
-        <v>7.58350777418929</v>
+        <v>7.583507774189279</v>
       </c>
       <c r="K7" t="n">
-        <v>6.589529666824182</v>
+        <v>6.589529666824165</v>
       </c>
       <c r="L7" t="n">
-        <v>8.028414707708997</v>
+        <v>8.028414707708915</v>
       </c>
       <c r="M7" t="n">
-        <v>10.17701870566254</v>
+        <v>10.17701870566253</v>
       </c>
       <c r="N7" t="n">
-        <v>7.79352223971131</v>
+        <v>7.793522239711283</v>
       </c>
       <c r="O7" t="n">
-        <v>7.605433544493497</v>
+        <v>7.605433544493473</v>
       </c>
       <c r="P7" t="n">
-        <v>9.035741430634404</v>
+        <v>9.035741430634387</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.460354773766135</v>
+        <v>6.460354773766113</v>
       </c>
       <c r="R7" t="n">
-        <v>6.196604307729345</v>
+        <v>6.196604307729327</v>
       </c>
       <c r="S7" t="n">
-        <v>7.154460180492803</v>
+        <v>7.154460180492786</v>
       </c>
       <c r="T7" t="n">
-        <v>6.515788399767155</v>
+        <v>6.515788399767123</v>
       </c>
       <c r="U7" t="n">
-        <v>8.92455931287534</v>
+        <v>8.924559312875326</v>
       </c>
       <c r="V7" t="n">
-        <v>6.802255065351323</v>
+        <v>6.802255065351405</v>
       </c>
       <c r="W7" t="n">
-        <v>10.0162259849659</v>
+        <v>10.01622598496589</v>
       </c>
       <c r="X7" t="n">
-        <v>6.837162918812627</v>
+        <v>6.837162918812618</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.22379961518641</v>
+        <v>10.22379961518639</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.283051455782626</v>
+        <v>7.283051455782629</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.470870139670816</v>
+        <v>6.470870139670815</v>
       </c>
       <c r="AB7" t="n">
         <v>10.66055662807557</v>
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.692309605011204</v>
+        <v>6.692309605011165</v>
       </c>
       <c r="C8" t="n">
-        <v>5.793697037257528</v>
+        <v>5.793697037257509</v>
       </c>
       <c r="D8" t="n">
-        <v>7.741224141180355</v>
+        <v>7.741224141180332</v>
       </c>
       <c r="E8" t="n">
-        <v>6.579898321928355</v>
+        <v>6.579898321928354</v>
       </c>
       <c r="F8" t="n">
-        <v>5.951437446619869</v>
+        <v>5.951437446619845</v>
       </c>
       <c r="G8" t="n">
-        <v>9.482815977484385</v>
+        <v>9.482815977484382</v>
       </c>
       <c r="H8" t="n">
-        <v>8.777106061982561</v>
+        <v>8.777106061982536</v>
       </c>
       <c r="I8" t="n">
-        <v>6.918892090770139</v>
+        <v>6.918892090770111</v>
       </c>
       <c r="J8" t="n">
-        <v>9.356972277683496</v>
+        <v>9.356972277683493</v>
       </c>
       <c r="K8" t="n">
-        <v>8.362994170318395</v>
+        <v>8.362994170318364</v>
       </c>
       <c r="L8" t="n">
-        <v>9.801879211203097</v>
+        <v>9.801879211203181</v>
       </c>
       <c r="M8" t="n">
-        <v>11.9504832091579</v>
+        <v>11.95048320915789</v>
       </c>
       <c r="N8" t="n">
-        <v>8.574404529322035</v>
+        <v>8.574404529322026</v>
       </c>
       <c r="O8" t="n">
-        <v>8.659099732382975</v>
+        <v>8.659099732382982</v>
       </c>
       <c r="P8" t="n">
-        <v>10.02254504913183</v>
+        <v>10.02254504913182</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.7017019161036</v>
+        <v>6.701701916103593</v>
       </c>
       <c r="R8" t="n">
-        <v>7.970068811223555</v>
+        <v>7.97006881122353</v>
       </c>
       <c r="S8" t="n">
-        <v>8.927924683987003</v>
+        <v>8.927924683986983</v>
       </c>
       <c r="T8" t="n">
-        <v>8.28925290326136</v>
+        <v>8.289252903261328</v>
       </c>
       <c r="U8" t="n">
-        <v>10.07273367546312</v>
+        <v>10.07273367546311</v>
       </c>
       <c r="V8" t="n">
-        <v>8.226966416988974</v>
+        <v>8.226966416989029</v>
       </c>
       <c r="W8" t="n">
-        <v>11.78994213662408</v>
+        <v>11.78994213662407</v>
       </c>
       <c r="X8" t="n">
-        <v>7.195868122700462</v>
+        <v>7.195868122700471</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.27230320782256</v>
+        <v>13.27230320782255</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.75225565024544</v>
+        <v>7.752255650245425</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.244334643165027</v>
+        <v>8.244334643165013</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.77158416323512</v>
+        <v>13.77158416323511</v>
       </c>
     </row>
     <row r="9">
@@ -2922,28 +2922,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.415613836367594</v>
+        <v>9.415613836367598</v>
       </c>
       <c r="C9" t="n">
-        <v>8.547001032044472</v>
+        <v>8.547001032044477</v>
       </c>
       <c r="D9" t="n">
-        <v>10.4945281359673</v>
+        <v>10.49452813596731</v>
       </c>
       <c r="E9" t="n">
-        <v>9.71256538658551</v>
+        <v>9.712565386585524</v>
       </c>
       <c r="F9" t="n">
-        <v>6.764731341128192</v>
+        <v>6.764731341128183</v>
       </c>
       <c r="G9" t="n">
         <v>11.97060541529365</v>
       </c>
       <c r="H9" t="n">
-        <v>11.53041005676952</v>
+        <v>11.53041005676951</v>
       </c>
       <c r="I9" t="n">
-        <v>9.672196085557077</v>
+        <v>9.672196085557085</v>
       </c>
       <c r="J9" t="n">
         <v>12.11027627247045</v>
@@ -2952,52 +2952,52 @@
         <v>11.11629816510534</v>
       </c>
       <c r="L9" t="n">
-        <v>12.55518320599011</v>
+        <v>12.55518320599012</v>
       </c>
       <c r="M9" t="n">
-        <v>14.70378720394369</v>
+        <v>14.70378720394368</v>
       </c>
       <c r="N9" t="n">
-        <v>12.32029073799246</v>
+        <v>12.32029073799245</v>
       </c>
       <c r="O9" t="n">
-        <v>12.56650561667998</v>
+        <v>12.56650561667996</v>
       </c>
       <c r="P9" t="n">
         <v>14.09126404939405</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.98712351281987</v>
+        <v>10.98712351281988</v>
       </c>
       <c r="R9" t="n">
         <v>10.72337280601049</v>
       </c>
       <c r="S9" t="n">
-        <v>11.68122867877394</v>
+        <v>11.68122867877396</v>
       </c>
       <c r="T9" t="n">
-        <v>11.04255689804829</v>
+        <v>11.0425568980483</v>
       </c>
       <c r="U9" t="n">
-        <v>13.44991430804574</v>
+        <v>13.44991430804575</v>
       </c>
       <c r="V9" t="n">
-        <v>12.84128167927154</v>
+        <v>12.84128167927155</v>
       </c>
       <c r="W9" t="n">
-        <v>14.54299448324706</v>
+        <v>14.54299448324705</v>
       </c>
       <c r="X9" t="n">
-        <v>11.36393141709377</v>
+        <v>11.36393141709379</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.75056811346757</v>
+        <v>14.75056811346755</v>
       </c>
       <c r="Z9" t="n">
         <v>11.01972040069948</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.99763863795197</v>
+        <v>10.99763863795198</v>
       </c>
       <c r="AB9" t="n">
         <v>15.18732512635671</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.52516644115886</v>
+        <v>39.52516644115878</v>
       </c>
       <c r="C2" t="n">
-        <v>42.39139325379598</v>
+        <v>42.39139325379595</v>
       </c>
       <c r="D2" t="n">
-        <v>39.60418783679205</v>
+        <v>39.60418783679199</v>
       </c>
       <c r="E2" t="n">
-        <v>39.48500765978303</v>
+        <v>39.48500765978297</v>
       </c>
       <c r="F2" t="n">
-        <v>39.50647324295704</v>
+        <v>39.50647324295698</v>
       </c>
       <c r="G2" t="n">
-        <v>39.6696439166346</v>
+        <v>39.66964391663453</v>
       </c>
       <c r="H2" t="n">
-        <v>39.62048311942835</v>
+        <v>39.62048311942829</v>
       </c>
       <c r="I2" t="n">
-        <v>39.51926893015055</v>
+        <v>39.51926893015048</v>
       </c>
       <c r="J2" t="n">
-        <v>39.67245924222184</v>
+        <v>39.67245924222178</v>
       </c>
       <c r="K2" t="n">
-        <v>39.53152046818633</v>
+        <v>39.53152046818625</v>
       </c>
       <c r="L2" t="n">
-        <v>39.68375781275456</v>
+        <v>39.68375781275452</v>
       </c>
       <c r="M2" t="n">
-        <v>39.86749633953339</v>
+        <v>39.86749633953333</v>
       </c>
       <c r="N2" t="n">
-        <v>39.63287865255445</v>
+        <v>39.6328786525544</v>
       </c>
       <c r="O2" t="n">
-        <v>43.70955152745518</v>
+        <v>43.70955152745515</v>
       </c>
       <c r="P2" t="n">
-        <v>39.81152916748575</v>
+        <v>39.81152916748568</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.55947358515915</v>
+        <v>39.55947358515906</v>
       </c>
       <c r="R2" t="n">
-        <v>39.54506560744754</v>
+        <v>39.54506560744746</v>
       </c>
       <c r="S2" t="n">
-        <v>39.63907735223476</v>
+        <v>39.63907735223468</v>
       </c>
       <c r="T2" t="n">
-        <v>39.6077054246421</v>
+        <v>39.60770542464202</v>
       </c>
       <c r="U2" t="n">
-        <v>43.23484248841926</v>
+        <v>43.23484248841923</v>
       </c>
       <c r="V2" t="n">
-        <v>39.62192646670738</v>
+        <v>39.62192646670732</v>
       </c>
       <c r="W2" t="n">
         <v>45.86388887633561</v>
       </c>
       <c r="X2" t="n">
-        <v>39.69865880047916</v>
+        <v>39.6986588004791</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.92315568933986</v>
+        <v>39.92315568933978</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.9044416327599</v>
+        <v>40.90444163275985</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.59853119700507</v>
+        <v>39.59853119700502</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.93359475512396</v>
+        <v>39.93359475512392</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.49942246415424</v>
+        <v>40.56081419864737</v>
       </c>
       <c r="C3" t="n">
-        <v>44.74370672329614</v>
+        <v>44.7831194552462</v>
       </c>
       <c r="D3" t="n">
-        <v>41.07480583361777</v>
+        <v>41.15719800055791</v>
       </c>
       <c r="E3" t="n">
-        <v>40.21833999158861</v>
+        <v>40.2699623459028</v>
       </c>
       <c r="F3" t="n">
-        <v>40.37547609442451</v>
+        <v>40.43332875300746</v>
       </c>
       <c r="G3" t="n">
-        <v>41.52603339898886</v>
+        <v>41.62360168423522</v>
       </c>
       <c r="H3" t="n">
-        <v>41.19894458725358</v>
+        <v>41.28605068901371</v>
       </c>
       <c r="I3" t="n">
-        <v>40.46887711326899</v>
+        <v>40.52981597619915</v>
       </c>
       <c r="J3" t="n">
-        <v>41.55235983617515</v>
+        <v>41.6512606327146</v>
       </c>
       <c r="K3" t="n">
-        <v>40.54478440945382</v>
+        <v>40.60863541561754</v>
       </c>
       <c r="L3" t="n">
-        <v>41.63571938285051</v>
+        <v>41.73739058721923</v>
       </c>
       <c r="M3" t="n">
-        <v>42.95989297352913</v>
+        <v>43.1095799692376</v>
       </c>
       <c r="N3" t="n">
-        <v>41.27737279615113</v>
+        <v>41.36668004166498</v>
       </c>
       <c r="O3" t="n">
-        <v>48.29608536876134</v>
+        <v>48.39843565039105</v>
       </c>
       <c r="P3" t="n">
-        <v>42.53457282655437</v>
+        <v>42.66730374438484</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.75067464390096</v>
+        <v>40.8215352972128</v>
       </c>
       <c r="R3" t="n">
-        <v>40.65549875103915</v>
+        <v>40.72313730832976</v>
       </c>
       <c r="S3" t="n">
-        <v>41.30999208386007</v>
+        <v>41.40013767553663</v>
       </c>
       <c r="T3" t="n">
-        <v>41.10131768761416</v>
+        <v>41.18465493795557</v>
       </c>
       <c r="U3" t="n">
-        <v>47.71731550893129</v>
+        <v>47.82918593415469</v>
       </c>
       <c r="V3" t="n">
-        <v>41.18156431810397</v>
+        <v>41.26728727513191</v>
       </c>
       <c r="W3" t="n">
-        <v>52.84887097790752</v>
+        <v>52.99706918582411</v>
       </c>
       <c r="X3" t="n">
-        <v>41.74838342441397</v>
+        <v>41.8546647956043</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.3449249868885</v>
+        <v>43.50735740134522</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.31074594526353</v>
+        <v>43.3969784585508</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.02954439578262</v>
+        <v>41.10996730035229</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.42720124401605</v>
+        <v>43.59245689848139</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.222964260526798</v>
+        <v>4.222964260526822</v>
       </c>
       <c r="C4" t="n">
-        <v>3.205721481322386</v>
+        <v>3.205721481322415</v>
       </c>
       <c r="D4" t="n">
-        <v>5.115547275841614</v>
+        <v>5.115547275841636</v>
       </c>
       <c r="E4" t="n">
-        <v>3.769352350934441</v>
+        <v>3.769352350934442</v>
       </c>
       <c r="F4" t="n">
-        <v>4.011815987541197</v>
+        <v>4.011815987541173</v>
       </c>
       <c r="G4" t="n">
-        <v>5.85490380894772</v>
+        <v>5.854903808947761</v>
       </c>
       <c r="H4" t="n">
-        <v>5.299609989419528</v>
+        <v>5.299609989419545</v>
       </c>
       <c r="I4" t="n">
-        <v>4.156349160698746</v>
+        <v>4.156349160698763</v>
       </c>
       <c r="J4" t="n">
-        <v>5.887368782488527</v>
+        <v>5.887368782488537</v>
       </c>
       <c r="K4" t="n">
-        <v>4.294735918798962</v>
+        <v>4.294735918798986</v>
       </c>
       <c r="L4" t="n">
-        <v>6.014326758335825</v>
+        <v>6.014326758335862</v>
       </c>
       <c r="M4" t="n">
-        <v>8.08391271086438</v>
+        <v>8.08391271086442</v>
       </c>
       <c r="N4" t="n">
-        <v>5.439623238305315</v>
+        <v>5.439623238305294</v>
       </c>
       <c r="O4" t="n">
-        <v>6.078298835548283</v>
+        <v>6.078298835548265</v>
       </c>
       <c r="P4" t="n">
-        <v>7.457562987751565</v>
+        <v>7.457562987751545</v>
       </c>
       <c r="Q4" t="n">
         <v>4.610479234076251</v>
       </c>
       <c r="R4" t="n">
-        <v>4.447734497826127</v>
+        <v>4.447734497826151</v>
       </c>
       <c r="S4" t="n">
-        <v>5.509640402737253</v>
+        <v>5.509640402737293</v>
       </c>
       <c r="T4" t="n">
-        <v>5.155280048778716</v>
+        <v>5.155280048778736</v>
       </c>
       <c r="U4" t="n">
-        <v>6.46377817015175</v>
+        <v>6.463778170151773</v>
       </c>
       <c r="V4" t="n">
-        <v>5.320092950747717</v>
+        <v>5.320092950747713</v>
       </c>
       <c r="W4" t="n">
-        <v>8.092112008827653</v>
+        <v>8.092112008827666</v>
       </c>
       <c r="X4" t="n">
-        <v>6.182640269477827</v>
+        <v>6.182640269477832</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.705071365199736</v>
+        <v>8.705071365199782</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.340965215343543</v>
+        <v>5.340965215343584</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.0516529272653</v>
+        <v>5.051652927265315</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.799741183182942</v>
+        <v>8.799741183182938</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46.18547807401733</v>
+        <v>46.18547807401723</v>
       </c>
       <c r="C5" t="n">
-        <v>30.85201588081557</v>
+        <v>30.85201588081558</v>
       </c>
       <c r="D5" t="n">
-        <v>67.88197560390927</v>
+        <v>67.88197560390937</v>
       </c>
       <c r="E5" t="n">
-        <v>41.02981161290816</v>
+        <v>41.02981161290815</v>
       </c>
       <c r="F5" t="n">
-        <v>47.35748105973629</v>
+        <v>47.35748105973626</v>
       </c>
       <c r="G5" t="n">
-        <v>72.70042241616666</v>
+        <v>72.70042241616638</v>
       </c>
       <c r="H5" t="n">
-        <v>75.19953727905485</v>
+        <v>75.19953727905475</v>
       </c>
       <c r="I5" t="n">
-        <v>50.99043234116485</v>
+        <v>50.99043234116492</v>
       </c>
       <c r="J5" t="n">
-        <v>76.49378877420111</v>
+        <v>76.49378877420109</v>
       </c>
       <c r="K5" t="n">
-        <v>47.46158288944367</v>
+        <v>47.46158288944373</v>
       </c>
       <c r="L5" t="n">
-        <v>80.16047329118064</v>
+        <v>80.16047329118072</v>
       </c>
       <c r="M5" t="n">
-        <v>125.049648682374</v>
+        <v>125.0496486823742</v>
       </c>
       <c r="N5" t="n">
-        <v>72.47327460659885</v>
+        <v>72.47327460659888</v>
       </c>
       <c r="O5" t="n">
-        <v>72.99219570801006</v>
+        <v>72.99219570800983</v>
       </c>
       <c r="P5" t="n">
         <v>98.91998404192523</v>
       </c>
       <c r="Q5" t="n">
-        <v>56.35615611456862</v>
+        <v>56.35615611456861</v>
       </c>
       <c r="R5" t="n">
-        <v>57.44453000296301</v>
+        <v>57.44453000296297</v>
       </c>
       <c r="S5" t="n">
-        <v>67.6892816832999</v>
+        <v>67.68928168329984</v>
       </c>
       <c r="T5" t="n">
-        <v>69.31367815220426</v>
+        <v>69.31367815220443</v>
       </c>
       <c r="U5" t="n">
-        <v>85.81299546139788</v>
+        <v>85.81299546139743</v>
       </c>
       <c r="V5" t="n">
-        <v>61.14682529939428</v>
+        <v>61.14682529939416</v>
       </c>
       <c r="W5" t="n">
-        <v>118.2070701463298</v>
+        <v>118.2070701463302</v>
       </c>
       <c r="X5" t="n">
-        <v>86.4099380574722</v>
+        <v>86.40993805747196</v>
       </c>
       <c r="Y5" t="n">
-        <v>128.3037535659286</v>
+        <v>128.3037535659288</v>
       </c>
       <c r="Z5" t="n">
-        <v>61.57923341187627</v>
+        <v>61.57923341187642</v>
       </c>
       <c r="AA5" t="n">
-        <v>64.21792624486305</v>
+        <v>64.21792624486314</v>
       </c>
       <c r="AB5" t="n">
-        <v>144.0771113602302</v>
+        <v>144.0771113602304</v>
       </c>
     </row>
     <row r="6">
@@ -3518,40 +3518,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>137.7415479045755</v>
+        <v>137.7415479045754</v>
       </c>
       <c r="C6" t="n">
-        <v>114.5515167074489</v>
+        <v>114.551516707449</v>
       </c>
       <c r="D6" t="n">
-        <v>138.6341309198902</v>
+        <v>138.6341309198904</v>
       </c>
       <c r="E6" t="n">
-        <v>137.287935994983</v>
+        <v>137.2879359949831</v>
       </c>
       <c r="F6" t="n">
-        <v>115.3576112136678</v>
+        <v>115.3576112136677</v>
       </c>
       <c r="G6" t="n">
-        <v>117.2006990350742</v>
+        <v>117.2006990350743</v>
       </c>
       <c r="H6" t="n">
-        <v>116.6454052155461</v>
+        <v>116.645405215546</v>
       </c>
       <c r="I6" t="n">
-        <v>115.5021443868253</v>
+        <v>115.5021443868254</v>
       </c>
       <c r="J6" t="n">
         <v>139.4059524265371</v>
       </c>
       <c r="K6" t="n">
-        <v>137.8133195628476</v>
+        <v>137.8133195628477</v>
       </c>
       <c r="L6" t="n">
         <v>139.5329104023845</v>
       </c>
       <c r="M6" t="n">
-        <v>119.4297079369909</v>
+        <v>119.4297079369908</v>
       </c>
       <c r="N6" t="n">
         <v>116.794252464057</v>
@@ -3563,7 +3563,7 @@
         <v>141.0324233384162</v>
       </c>
       <c r="Q6" t="n">
-        <v>138.1290628781248</v>
+        <v>138.1290628781249</v>
       </c>
       <c r="R6" t="n">
         <v>115.7935297239526</v>
@@ -3575,7 +3575,7 @@
         <v>116.5010752749053</v>
       </c>
       <c r="U6" t="n">
-        <v>117.8229379339088</v>
+        <v>117.8229379339089</v>
       </c>
       <c r="V6" t="n">
         <v>138.8386765947964</v>
@@ -3590,10 +3590,10 @@
         <v>124.9595312422339</v>
       </c>
       <c r="Z6" t="n">
-        <v>138.8595488593921</v>
+        <v>138.8595488593922</v>
       </c>
       <c r="AA6" t="n">
-        <v>138.5702365713138</v>
+        <v>138.570236571314</v>
       </c>
       <c r="AB6" t="n">
         <v>120.1744589613083</v>
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.274665268894005</v>
+        <v>5.274665268894035</v>
       </c>
       <c r="C7" t="n">
-        <v>4.257422489689606</v>
+        <v>4.257422489689628</v>
       </c>
       <c r="D7" t="n">
-        <v>6.167248284208844</v>
+        <v>6.167248284208851</v>
       </c>
       <c r="E7" t="n">
-        <v>4.821053359301663</v>
+        <v>4.821053359301674</v>
       </c>
       <c r="F7" t="n">
-        <v>5.063516995908415</v>
+        <v>5.063516995908443</v>
       </c>
       <c r="G7" t="n">
-        <v>6.906604817314937</v>
+        <v>6.906604817314986</v>
       </c>
       <c r="H7" t="n">
-        <v>6.351310997786751</v>
+        <v>6.351310997786781</v>
       </c>
       <c r="I7" t="n">
-        <v>5.208050169065967</v>
+        <v>5.208050169065991</v>
       </c>
       <c r="J7" t="n">
-        <v>6.939069790855748</v>
+        <v>6.939069790855761</v>
       </c>
       <c r="K7" t="n">
-        <v>5.346436927166184</v>
+        <v>5.346436927166212</v>
       </c>
       <c r="L7" t="n">
-        <v>7.066027766703059</v>
+        <v>7.066027766703074</v>
       </c>
       <c r="M7" t="n">
-        <v>9.135613719231602</v>
+        <v>9.135613719231634</v>
       </c>
       <c r="N7" t="n">
-        <v>6.491324246672534</v>
+        <v>6.491324246672566</v>
       </c>
       <c r="O7" t="n">
-        <v>7.129991789409306</v>
+        <v>7.129991789409313</v>
       </c>
       <c r="P7" t="n">
-        <v>8.509255941612587</v>
+        <v>8.509255941612604</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.662180242443467</v>
+        <v>5.662180242443491</v>
       </c>
       <c r="R7" t="n">
-        <v>5.499435506193345</v>
+        <v>5.499435506193382</v>
       </c>
       <c r="S7" t="n">
-        <v>6.561341411104475</v>
+        <v>6.561341411104502</v>
       </c>
       <c r="T7" t="n">
-        <v>6.20698105714594</v>
+        <v>6.20698105714596</v>
       </c>
       <c r="U7" t="n">
-        <v>7.526174835888054</v>
+        <v>7.526174835888038</v>
       </c>
       <c r="V7" t="n">
-        <v>6.371793959114941</v>
+        <v>6.371793959114939</v>
       </c>
       <c r="W7" t="n">
-        <v>9.143813017194862</v>
+        <v>9.143813017194889</v>
       </c>
       <c r="X7" t="n">
-        <v>7.234341277845048</v>
+        <v>7.234341277845057</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.77013691119744</v>
+        <v>9.770136911197483</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.392666223710763</v>
+        <v>6.392666223710799</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.103353935632519</v>
+        <v>6.103353935632531</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.851442191550175</v>
+        <v>9.85144219155022</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.681570041596087</v>
+        <v>5.681570041596106</v>
       </c>
       <c r="C8" t="n">
-        <v>5.761092330973065</v>
+        <v>5.761092330973112</v>
       </c>
       <c r="D8" t="n">
-        <v>7.670918125492298</v>
+        <v>7.670918125492335</v>
       </c>
       <c r="E8" t="n">
-        <v>5.740728154408773</v>
+        <v>5.740728154408776</v>
       </c>
       <c r="F8" t="n">
-        <v>5.641284947962627</v>
+        <v>5.641284947962626</v>
       </c>
       <c r="G8" t="n">
-        <v>8.637696040217257</v>
+        <v>8.637696040217243</v>
       </c>
       <c r="H8" t="n">
-        <v>7.854980839070201</v>
+        <v>7.854980839070244</v>
       </c>
       <c r="I8" t="n">
-        <v>6.711720010349436</v>
+        <v>6.711720010349453</v>
       </c>
       <c r="J8" t="n">
-        <v>8.442739632139206</v>
+        <v>8.442739632139201</v>
       </c>
       <c r="K8" t="n">
-        <v>6.850106768449653</v>
+        <v>6.850106768449693</v>
       </c>
       <c r="L8" t="n">
-        <v>8.569697607986525</v>
+        <v>8.569697607986555</v>
       </c>
       <c r="M8" t="n">
-        <v>10.63928356051736</v>
+        <v>10.63928356051743</v>
       </c>
       <c r="N8" t="n">
-        <v>7.144817674629802</v>
+        <v>7.144817674629853</v>
       </c>
       <c r="O8" t="n">
-        <v>8.017129131452059</v>
+        <v>8.017129131452128</v>
       </c>
       <c r="P8" t="n">
-        <v>9.339123489118434</v>
+        <v>9.339123489118499</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.85354564712766</v>
+        <v>5.853545647127704</v>
       </c>
       <c r="R8" t="n">
-        <v>7.003105347476793</v>
+        <v>7.003105347476857</v>
       </c>
       <c r="S8" t="n">
-        <v>8.065011252387938</v>
+        <v>8.065011252387981</v>
       </c>
       <c r="T8" t="n">
-        <v>7.710650898429392</v>
+        <v>7.710650898429429</v>
       </c>
       <c r="U8" t="n">
-        <v>8.495135090300018</v>
+        <v>8.49513509030003</v>
       </c>
       <c r="V8" t="n">
-        <v>7.573426961092542</v>
+        <v>7.573426961092524</v>
       </c>
       <c r="W8" t="n">
         <v>10.64769840277126</v>
       </c>
       <c r="X8" t="n">
-        <v>7.526227379466701</v>
+        <v>7.526227379466692</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.36076768601971</v>
+        <v>12.36076768601975</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.779198022314165</v>
+        <v>6.779198022314201</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.607023776915986</v>
+        <v>7.607023776916013</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.50077485559912</v>
+        <v>12.50077485559918</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.844202432299319</v>
+        <v>7.84420243229932</v>
       </c>
       <c r="C9" t="n">
-        <v>7.902417344358082</v>
+        <v>7.902417344358112</v>
       </c>
       <c r="D9" t="n">
-        <v>9.812243138877331</v>
+        <v>9.812243138877353</v>
       </c>
       <c r="E9" t="n">
-        <v>8.217837098546932</v>
+        <v>8.217837098546964</v>
       </c>
       <c r="F9" t="n">
-        <v>6.229288126259817</v>
+        <v>6.229288126259822</v>
       </c>
       <c r="G9" t="n">
-        <v>10.55159984490014</v>
+        <v>10.55159984490018</v>
       </c>
       <c r="H9" t="n">
-        <v>9.99630585245523</v>
+        <v>9.996305852455258</v>
       </c>
       <c r="I9" t="n">
-        <v>8.853045023734458</v>
+        <v>8.85304502373447</v>
       </c>
       <c r="J9" t="n">
         <v>10.58406464552423</v>
       </c>
       <c r="K9" t="n">
-        <v>8.991431781834669</v>
+        <v>8.991431781834686</v>
       </c>
       <c r="L9" t="n">
-        <v>10.71102262137153</v>
+        <v>10.71102262137156</v>
       </c>
       <c r="M9" t="n">
-        <v>12.78060857390007</v>
+        <v>12.7806085739001</v>
       </c>
       <c r="N9" t="n">
-        <v>10.13631910134102</v>
+        <v>10.13631910134105</v>
       </c>
       <c r="O9" t="n">
-        <v>11.13140019949809</v>
+        <v>11.13140019949812</v>
       </c>
       <c r="P9" t="n">
-        <v>12.58817639565519</v>
+        <v>12.58817639565525</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.307175270028676</v>
+        <v>9.307175270028671</v>
       </c>
       <c r="R9" t="n">
-        <v>9.144430360861822</v>
+        <v>9.144430360861858</v>
       </c>
       <c r="S9" t="n">
-        <v>10.20633626577298</v>
+        <v>10.20633626577299</v>
       </c>
       <c r="T9" t="n">
-        <v>9.851975911814419</v>
+        <v>9.851975911814453</v>
       </c>
       <c r="U9" t="n">
-        <v>11.17383857081799</v>
+        <v>11.17383857081796</v>
       </c>
       <c r="V9" t="n">
-        <v>11.2578426660512</v>
+        <v>11.25784266605121</v>
       </c>
       <c r="W9" t="n">
-        <v>12.78880787186335</v>
+        <v>12.78880787186338</v>
       </c>
       <c r="X9" t="n">
-        <v>10.87933613251354</v>
+        <v>10.87933613251358</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.41513176586593</v>
+        <v>13.41513176586595</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.38925579264016</v>
+        <v>9.389255792640199</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.748348790301005</v>
+        <v>9.74834879030098</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.49643704621865</v>
+        <v>13.49643704621867</v>
       </c>
     </row>
   </sheetData>
@@ -4029,82 +4029,82 @@
         <v>39.40229984714902</v>
       </c>
       <c r="C2" t="n">
-        <v>42.28684474596504</v>
+        <v>42.28684474596503</v>
       </c>
       <c r="D2" t="n">
-        <v>39.42617232903942</v>
+        <v>39.42617232903944</v>
       </c>
       <c r="E2" t="n">
-        <v>39.29138089092765</v>
+        <v>39.29138089092767</v>
       </c>
       <c r="F2" t="n">
-        <v>39.46555212863834</v>
+        <v>39.46555212863831</v>
       </c>
       <c r="G2" t="n">
         <v>39.53549423107177</v>
       </c>
       <c r="H2" t="n">
-        <v>39.49145730862976</v>
+        <v>39.49145730862973</v>
       </c>
       <c r="I2" t="n">
-        <v>39.46297730189158</v>
+        <v>39.46297730189157</v>
       </c>
       <c r="J2" t="n">
         <v>39.54147872806413</v>
       </c>
       <c r="K2" t="n">
-        <v>39.52047775178143</v>
+        <v>39.52047775178144</v>
       </c>
       <c r="L2" t="n">
-        <v>39.58532508912371</v>
+        <v>39.58532508912372</v>
       </c>
       <c r="M2" t="n">
-        <v>39.71387402801868</v>
+        <v>39.71387402801867</v>
       </c>
       <c r="N2" t="n">
-        <v>39.48768476427374</v>
+        <v>39.48768476427372</v>
       </c>
       <c r="O2" t="n">
-        <v>43.41806553734951</v>
+        <v>43.4180655373495</v>
       </c>
       <c r="P2" t="n">
         <v>39.6496302290543</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.4846945757432</v>
+        <v>39.48469457574322</v>
       </c>
       <c r="R2" t="n">
-        <v>39.45743895266394</v>
+        <v>39.45743895266396</v>
       </c>
       <c r="S2" t="n">
-        <v>39.55638604481057</v>
+        <v>39.55638604481056</v>
       </c>
       <c r="T2" t="n">
-        <v>39.52131729496416</v>
+        <v>39.52131729496415</v>
       </c>
       <c r="U2" t="n">
-        <v>43.05025252167516</v>
+        <v>43.05025252167517</v>
       </c>
       <c r="V2" t="n">
-        <v>39.49127146467002</v>
+        <v>39.49127146467005</v>
       </c>
       <c r="W2" t="n">
-        <v>45.66318568060087</v>
+        <v>45.66318568060082</v>
       </c>
       <c r="X2" t="n">
-        <v>39.61507622412887</v>
+        <v>39.61507622412888</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.75994225623113</v>
+        <v>39.75994225623116</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.62662872427285</v>
+        <v>40.62662872427283</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.52231334501177</v>
+        <v>39.52231334501178</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.77089343814576</v>
+        <v>39.77089343814573</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.30124512816918</v>
+        <v>40.35790076754617</v>
       </c>
       <c r="C3" t="n">
-        <v>44.71793318064572</v>
+        <v>44.75907896670745</v>
       </c>
       <c r="D3" t="n">
-        <v>40.47988096236729</v>
+        <v>40.54346457138593</v>
       </c>
       <c r="E3" t="n">
-        <v>39.51501993812767</v>
+        <v>39.54407295269166</v>
       </c>
       <c r="F3" t="n">
-        <v>40.76419075991652</v>
+        <v>40.83812880740726</v>
       </c>
       <c r="G3" t="n">
-        <v>41.24597166631301</v>
+        <v>41.33597879236557</v>
       </c>
       <c r="H3" t="n">
-        <v>40.95828116475045</v>
+        <v>41.03897848388599</v>
       </c>
       <c r="I3" t="n">
-        <v>40.74703925526352</v>
+        <v>40.82010337805607</v>
       </c>
       <c r="J3" t="n">
-        <v>41.29641051968188</v>
+        <v>41.38860755227976</v>
       </c>
       <c r="K3" t="n">
-        <v>41.14419714785205</v>
+        <v>41.23160648565988</v>
       </c>
       <c r="L3" t="n">
-        <v>41.60804604227714</v>
+        <v>41.71110139903112</v>
       </c>
       <c r="M3" t="n">
-        <v>42.53176198817276</v>
+        <v>42.66869649945536</v>
       </c>
       <c r="N3" t="n">
-        <v>40.92180345759623</v>
+        <v>41.00067931153949</v>
       </c>
       <c r="O3" t="n">
-        <v>47.51320536996576</v>
+        <v>47.59662784990518</v>
       </c>
       <c r="P3" t="n">
-        <v>42.05568971529614</v>
+        <v>42.17395325340155</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.89482327658003</v>
+        <v>40.97307122392229</v>
       </c>
       <c r="R3" t="n">
-        <v>40.71139875658387</v>
+        <v>40.78319990753044</v>
       </c>
       <c r="S3" t="n">
-        <v>41.39817085342358</v>
+        <v>41.49364289648266</v>
       </c>
       <c r="T3" t="n">
-        <v>41.16607100481951</v>
+        <v>41.25387050654575</v>
       </c>
       <c r="U3" t="n">
-        <v>47.38021251318575</v>
+        <v>47.48576387959125</v>
       </c>
       <c r="V3" t="n">
-        <v>40.92989612387466</v>
+        <v>41.00892533745664</v>
       </c>
       <c r="W3" t="n">
-        <v>52.44283611820788</v>
+        <v>52.58251206842589</v>
       </c>
       <c r="X3" t="n">
-        <v>41.8276005619184</v>
+        <v>41.93904819926428</v>
       </c>
       <c r="Y3" t="n">
-        <v>42.86529197923268</v>
+        <v>43.01276152441245</v>
       </c>
       <c r="Z3" t="n">
-        <v>42.47594924501568</v>
+        <v>42.54000595246522</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.16710224143096</v>
+        <v>41.25451699188714</v>
       </c>
       <c r="AB3" t="n">
-        <v>42.94003094605221</v>
+        <v>43.09033386143857</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.930747573369477</v>
+        <v>3.930747573369468</v>
       </c>
       <c r="C4" t="n">
-        <v>3.204394642325362</v>
+        <v>3.204394642325351</v>
       </c>
       <c r="D4" t="n">
-        <v>4.200398238205892</v>
+        <v>4.200398238205881</v>
       </c>
       <c r="E4" t="n">
-        <v>2.677866937608326</v>
+        <v>2.67786693760833</v>
       </c>
       <c r="F4" t="n">
-        <v>4.645211190278264</v>
+        <v>4.645211190278227</v>
       </c>
       <c r="G4" t="n">
-        <v>5.435239412220886</v>
+        <v>5.435239412220872</v>
       </c>
       <c r="H4" t="n">
-        <v>4.93782211525308</v>
+        <v>4.937822115253078</v>
       </c>
       <c r="I4" t="n">
-        <v>4.61612733769514</v>
+        <v>4.61612733769512</v>
       </c>
       <c r="J4" t="n">
-        <v>5.503575795815085</v>
+        <v>5.50357579581507</v>
       </c>
       <c r="K4" t="n">
-        <v>5.265621370714745</v>
+        <v>5.265621370714739</v>
       </c>
       <c r="L4" t="n">
-        <v>5.998101877244274</v>
+        <v>5.998101877244266</v>
       </c>
       <c r="M4" t="n">
-        <v>7.440231396765214</v>
+        <v>7.44023139676522</v>
       </c>
       <c r="N4" t="n">
-        <v>4.895209491295308</v>
+        <v>4.895209491295321</v>
       </c>
       <c r="O4" t="n">
-        <v>5.144031728307167</v>
+        <v>5.144031728307166</v>
       </c>
       <c r="P4" t="n">
-        <v>6.724458014586281</v>
+        <v>6.72445801458626</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.861433936288488</v>
+        <v>4.861433936288487</v>
       </c>
       <c r="R4" t="n">
-        <v>4.553569135402077</v>
+        <v>4.553569135402092</v>
       </c>
       <c r="S4" t="n">
-        <v>5.671222059109121</v>
+        <v>5.671222059109105</v>
       </c>
       <c r="T4" t="n">
-        <v>5.275104397172436</v>
+        <v>5.275104397172438</v>
       </c>
       <c r="U4" t="n">
-        <v>6.082722699711915</v>
+        <v>6.082722699711881</v>
       </c>
       <c r="V4" t="n">
-        <v>4.94041022495617</v>
+        <v>4.940410224956167</v>
       </c>
       <c r="W4" t="n">
-        <v>7.631763321457398</v>
+        <v>7.631763321457415</v>
       </c>
       <c r="X4" t="n">
-        <v>6.334154633326384</v>
+        <v>6.334154633326368</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.9383776480919</v>
+        <v>7.938377648091889</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.261965478384379</v>
+        <v>4.261965478384383</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.286355240665894</v>
+        <v>5.286355240665879</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.056251124908107</v>
+        <v>8.056251124908087</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.59129830237009</v>
+        <v>41.5912983023702</v>
       </c>
       <c r="C5" t="n">
-        <v>32.16568100909713</v>
+        <v>32.16568100909711</v>
       </c>
       <c r="D5" t="n">
-        <v>50.63936213967523</v>
+        <v>50.63936213967515</v>
       </c>
       <c r="E5" t="n">
-        <v>22.23507786872354</v>
+        <v>22.23507786872355</v>
       </c>
       <c r="F5" t="n">
-        <v>60.19302235405959</v>
+        <v>60.1930223540597</v>
       </c>
       <c r="G5" t="n">
-        <v>65.14919456733884</v>
+        <v>65.14919456733878</v>
       </c>
       <c r="H5" t="n">
-        <v>70.13798840306715</v>
+        <v>70.13798840306725</v>
       </c>
       <c r="I5" t="n">
-        <v>60.31353571472422</v>
+        <v>60.31353571472419</v>
       </c>
       <c r="J5" t="n">
-        <v>70.34993495718457</v>
+        <v>70.3499349571846</v>
       </c>
       <c r="K5" t="n">
-        <v>64.94703320071328</v>
+        <v>64.94703320071308</v>
       </c>
       <c r="L5" t="n">
-        <v>78.43604250803484</v>
+        <v>78.43604250803497</v>
       </c>
       <c r="M5" t="n">
-        <v>109.9689854470565</v>
+        <v>109.9689854470566</v>
       </c>
       <c r="N5" t="n">
-        <v>64.43378084464527</v>
+        <v>64.4337808446451</v>
       </c>
       <c r="O5" t="n">
-        <v>59.88610886641747</v>
+        <v>59.88610886641739</v>
       </c>
       <c r="P5" t="n">
-        <v>85.42415542791922</v>
+        <v>85.42415542791954</v>
       </c>
       <c r="Q5" t="n">
-        <v>60.91410622992883</v>
+        <v>60.91410622992896</v>
       </c>
       <c r="R5" t="n">
-        <v>61.22141748885837</v>
+        <v>61.22141748885835</v>
       </c>
       <c r="S5" t="n">
-        <v>70.92594642637465</v>
+        <v>70.92594642637459</v>
       </c>
       <c r="T5" t="n">
-        <v>73.34519813266147</v>
+        <v>73.34519813266142</v>
       </c>
       <c r="U5" t="n">
-        <v>78.42634863372039</v>
+        <v>78.42634863372021</v>
       </c>
       <c r="V5" t="n">
-        <v>56.08308095878163</v>
+        <v>56.08308095878159</v>
       </c>
       <c r="W5" t="n">
         <v>111.8260152093259</v>
       </c>
       <c r="X5" t="n">
-        <v>88.12085034749728</v>
+        <v>88.12085034749735</v>
       </c>
       <c r="Y5" t="n">
-        <v>119.0184858133738</v>
+        <v>119.0184858133737</v>
       </c>
       <c r="Z5" t="n">
-        <v>43.74303094989111</v>
+        <v>43.74303094989112</v>
       </c>
       <c r="AA5" t="n">
-        <v>70.39461404088421</v>
+        <v>70.39461404088429</v>
       </c>
       <c r="AB5" t="n">
-        <v>129.4428369150716</v>
+        <v>129.4428369150715</v>
       </c>
     </row>
     <row r="6">
@@ -4378,46 +4378,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115.2459428385958</v>
+        <v>115.2459428385957</v>
       </c>
       <c r="C6" t="n">
         <v>114.5195899075517</v>
       </c>
       <c r="D6" t="n">
-        <v>137.6284709290134</v>
+        <v>137.6284709290133</v>
       </c>
       <c r="E6" t="n">
-        <v>136.1059396284159</v>
+        <v>136.1059396284157</v>
       </c>
       <c r="F6" t="n">
-        <v>115.9604064555044</v>
+        <v>115.9604064555045</v>
       </c>
       <c r="G6" t="n">
-        <v>116.7504346774472</v>
+        <v>116.7504346774473</v>
       </c>
       <c r="H6" t="n">
-        <v>138.3658948060606</v>
+        <v>138.3658948060605</v>
       </c>
       <c r="I6" t="n">
         <v>115.9313226029215</v>
       </c>
       <c r="J6" t="n">
-        <v>138.9316484866226</v>
+        <v>138.9316484866225</v>
       </c>
       <c r="K6" t="n">
-        <v>138.6936940615223</v>
+        <v>138.6936940615222</v>
       </c>
       <c r="L6" t="n">
-        <v>117.3132971424706</v>
+        <v>117.3132971424708</v>
       </c>
       <c r="M6" t="n">
-        <v>118.7554266619916</v>
+        <v>118.7554266619915</v>
       </c>
       <c r="N6" t="n">
-        <v>116.2238134514062</v>
+        <v>116.2238134514064</v>
       </c>
       <c r="O6" t="n">
-        <v>116.4740280460592</v>
+        <v>116.4740280460594</v>
       </c>
       <c r="P6" t="n">
         <v>140.2126421602463</v>
@@ -4429,34 +4429,34 @@
         <v>137.9816418262096</v>
       </c>
       <c r="S6" t="n">
-        <v>116.9864173243354</v>
+        <v>116.9864173243355</v>
       </c>
       <c r="T6" t="n">
         <v>138.70317708798</v>
       </c>
       <c r="U6" t="n">
-        <v>139.5429008500162</v>
+        <v>139.542900850016</v>
       </c>
       <c r="V6" t="n">
-        <v>116.2556054901825</v>
+        <v>116.2556054901826</v>
       </c>
       <c r="W6" t="n">
         <v>124.6474803346834</v>
       </c>
       <c r="X6" t="n">
-        <v>117.6493498985527</v>
+        <v>117.6493498985528</v>
       </c>
       <c r="Y6" t="n">
-        <v>124.1834837702463</v>
+        <v>124.1834837702464</v>
       </c>
       <c r="Z6" t="n">
         <v>115.5771607436108</v>
       </c>
       <c r="AA6" t="n">
-        <v>138.7144279314734</v>
+        <v>138.7144279314733</v>
       </c>
       <c r="AB6" t="n">
-        <v>119.4025757292698</v>
+        <v>119.4025757292697</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.936580565904308</v>
+        <v>4.936580565904306</v>
       </c>
       <c r="C7" t="n">
-        <v>4.210227634860211</v>
+        <v>4.210227634860197</v>
       </c>
       <c r="D7" t="n">
-        <v>5.206231230740738</v>
+        <v>5.206231230740723</v>
       </c>
       <c r="E7" t="n">
-        <v>3.683699930143176</v>
+        <v>3.683699930143173</v>
       </c>
       <c r="F7" t="n">
-        <v>5.651044182813097</v>
+        <v>5.651044182813088</v>
       </c>
       <c r="G7" t="n">
-        <v>6.441072404755733</v>
+        <v>6.441072404755725</v>
       </c>
       <c r="H7" t="n">
-        <v>5.943655107787924</v>
+        <v>5.943655107787921</v>
       </c>
       <c r="I7" t="n">
-        <v>5.621960330229987</v>
+        <v>5.621960330229975</v>
       </c>
       <c r="J7" t="n">
-        <v>6.509408788349929</v>
+        <v>6.509408788349933</v>
       </c>
       <c r="K7" t="n">
-        <v>6.271454363249587</v>
+        <v>6.271454363249586</v>
       </c>
       <c r="L7" t="n">
-        <v>7.003934869779114</v>
+        <v>7.00393486977911</v>
       </c>
       <c r="M7" t="n">
-        <v>8.446064389300062</v>
+        <v>8.446064389300085</v>
       </c>
       <c r="N7" t="n">
-        <v>5.901042483830173</v>
+        <v>5.901042483830157</v>
       </c>
       <c r="O7" t="n">
-        <v>6.149861281732581</v>
+        <v>6.149861281732549</v>
       </c>
       <c r="P7" t="n">
-        <v>7.730287568011638</v>
+        <v>7.73028756801163</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.867266928823348</v>
+        <v>5.86726692882334</v>
       </c>
       <c r="R7" t="n">
-        <v>5.559402127936927</v>
+        <v>5.559402127936931</v>
       </c>
       <c r="S7" t="n">
-        <v>6.677055051643965</v>
+        <v>6.677055051643944</v>
       </c>
       <c r="T7" t="n">
-        <v>6.280937389707284</v>
+        <v>6.28093738970729</v>
       </c>
       <c r="U7" t="n">
-        <v>7.112648820737484</v>
+        <v>7.112648820737467</v>
       </c>
       <c r="V7" t="n">
-        <v>5.946243217491014</v>
+        <v>5.946243217491013</v>
       </c>
       <c r="W7" t="n">
-        <v>8.637596313992271</v>
+        <v>8.637596313992248</v>
       </c>
       <c r="X7" t="n">
-        <v>7.339987625861208</v>
+        <v>7.339987625861218</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.976316100123464</v>
+        <v>8.976316100123459</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.267798470919229</v>
+        <v>5.267798470919217</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.292188233200739</v>
+        <v>6.292188233200733</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.062084117442987</v>
+        <v>9.062084117442962</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.308581705033991</v>
+        <v>5.30858170503399</v>
       </c>
       <c r="C8" t="n">
-        <v>5.615070040427188</v>
+        <v>5.615070040427169</v>
       </c>
       <c r="D8" t="n">
-        <v>6.611073636307738</v>
+        <v>6.611073636307696</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5385848285103</v>
+        <v>4.538584828510309</v>
       </c>
       <c r="F8" t="n">
-        <v>6.183949920031139</v>
+        <v>6.18394992003112</v>
       </c>
       <c r="G8" t="n">
-        <v>8.060081175153645</v>
+        <v>8.060081175153634</v>
       </c>
       <c r="H8" t="n">
-        <v>7.348497513354899</v>
+        <v>7.348497513354907</v>
       </c>
       <c r="I8" t="n">
-        <v>7.026802735796955</v>
+        <v>7.026802735796946</v>
       </c>
       <c r="J8" t="n">
-        <v>7.914251193916937</v>
+        <v>7.914251193916911</v>
       </c>
       <c r="K8" t="n">
-        <v>7.676296768816566</v>
+        <v>7.676296768816554</v>
       </c>
       <c r="L8" t="n">
-        <v>8.408777275346093</v>
+        <v>8.408777275346086</v>
       </c>
       <c r="M8" t="n">
-        <v>9.850906794869845</v>
+        <v>9.850906794869815</v>
       </c>
       <c r="N8" t="n">
-        <v>6.505260116990532</v>
+        <v>6.505260116990494</v>
       </c>
       <c r="O8" t="n">
-        <v>6.974100992485435</v>
+        <v>6.974100992485425</v>
       </c>
       <c r="P8" t="n">
-        <v>8.500595394147407</v>
+        <v>8.500595394147419</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.036291186003598</v>
+        <v>6.03629118600357</v>
       </c>
       <c r="R8" t="n">
-        <v>6.964244533503956</v>
+        <v>6.964244533503904</v>
       </c>
       <c r="S8" t="n">
-        <v>8.081897457210969</v>
+        <v>8.081897457210918</v>
       </c>
       <c r="T8" t="n">
-        <v>7.685779795274289</v>
+        <v>7.685779795274279</v>
       </c>
       <c r="U8" t="n">
-        <v>8.01518082493808</v>
+        <v>8.015180824938071</v>
       </c>
       <c r="V8" t="n">
-        <v>7.061948728286137</v>
+        <v>7.061948728286127</v>
       </c>
       <c r="W8" t="n">
-        <v>10.04264170114482</v>
+        <v>10.0426417011448</v>
       </c>
       <c r="X8" t="n">
-        <v>7.603673836587013</v>
+        <v>7.603673836586988</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.39747121888713</v>
+        <v>11.3974712188871</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.620614053379176</v>
+        <v>5.62061405337916</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.69703063876773</v>
+        <v>7.697030638767699</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.54581558935898</v>
+        <v>11.54581558935894</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.128513639403428</v>
+        <v>7.128513639403442</v>
       </c>
       <c r="C9" t="n">
-        <v>7.355019958714127</v>
+        <v>7.355019958714104</v>
       </c>
       <c r="D9" t="n">
-        <v>8.351023554594684</v>
+        <v>8.351023554594621</v>
       </c>
       <c r="E9" t="n">
-        <v>6.608576226095283</v>
+        <v>6.608576226095263</v>
       </c>
       <c r="F9" t="n">
-        <v>6.599235873893225</v>
+        <v>6.599235873893194</v>
       </c>
       <c r="G9" t="n">
-        <v>9.585864729178994</v>
+        <v>9.585864729178965</v>
       </c>
       <c r="H9" t="n">
-        <v>9.08844743164185</v>
+        <v>9.088447431641839</v>
       </c>
       <c r="I9" t="n">
-        <v>8.766752654083881</v>
+        <v>8.766752654083884</v>
       </c>
       <c r="J9" t="n">
-        <v>9.654201112203848</v>
+        <v>9.654201112203827</v>
       </c>
       <c r="K9" t="n">
-        <v>9.416246687103509</v>
+        <v>9.416246687103483</v>
       </c>
       <c r="L9" t="n">
-        <v>10.14872719363303</v>
+        <v>10.148727193633</v>
       </c>
       <c r="M9" t="n">
-        <v>11.59085671315398</v>
+        <v>11.59085671315397</v>
       </c>
       <c r="N9" t="n">
-        <v>9.045834807684095</v>
+        <v>9.045834807684058</v>
       </c>
       <c r="O9" t="n">
-        <v>9.610433353358911</v>
+        <v>9.610433353358852</v>
       </c>
       <c r="P9" t="n">
-        <v>11.25953556883932</v>
+        <v>11.25953556883929</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.012059253246594</v>
+        <v>9.012059253246589</v>
       </c>
       <c r="R9" t="n">
-        <v>8.704194451790833</v>
+        <v>8.704194451790826</v>
       </c>
       <c r="S9" t="n">
-        <v>9.821847375497864</v>
+        <v>9.821847375497837</v>
       </c>
       <c r="T9" t="n">
-        <v>9.425729713561237</v>
+        <v>9.425729713561198</v>
       </c>
       <c r="U9" t="n">
-        <v>10.2654534755974</v>
+        <v>10.26545347559736</v>
       </c>
       <c r="V9" t="n">
-        <v>10.19061334638346</v>
+        <v>10.19061334638345</v>
       </c>
       <c r="W9" t="n">
-        <v>11.78238863784619</v>
+        <v>11.78238863784617</v>
       </c>
       <c r="X9" t="n">
-        <v>10.48477994971512</v>
+        <v>10.48477994971511</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.12110842397741</v>
+        <v>12.12110842397736</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.838101398585834</v>
+        <v>7.838101398585816</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.43698055705465</v>
+        <v>9.436980557054618</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.20687644129688</v>
+        <v>12.20687644129684</v>
       </c>
     </row>
   </sheetData>
@@ -4889,19 +4889,19 @@
         <v>39.11736658890637</v>
       </c>
       <c r="C2" t="n">
-        <v>42.02797194376195</v>
+        <v>42.02797194376197</v>
       </c>
       <c r="D2" t="n">
         <v>39.1608036036755</v>
       </c>
       <c r="E2" t="n">
-        <v>39.21948685685311</v>
+        <v>39.21948685685314</v>
       </c>
       <c r="F2" t="n">
-        <v>39.13020642708545</v>
+        <v>39.13020642708544</v>
       </c>
       <c r="G2" t="n">
-        <v>39.28102999772727</v>
+        <v>39.28102999772729</v>
       </c>
       <c r="H2" t="n">
         <v>39.26314347483206</v>
@@ -4916,55 +4916,55 @@
         <v>39.235289834655</v>
       </c>
       <c r="L2" t="n">
-        <v>39.28028845189268</v>
+        <v>39.28028845189269</v>
       </c>
       <c r="M2" t="n">
-        <v>39.36596206362762</v>
+        <v>39.36596206362763</v>
       </c>
       <c r="N2" t="n">
-        <v>39.41180800365764</v>
+        <v>39.41180800365768</v>
       </c>
       <c r="O2" t="n">
-        <v>43.34806907907063</v>
+        <v>43.34806907907062</v>
       </c>
       <c r="P2" t="n">
-        <v>39.55076069222365</v>
+        <v>39.55076069222366</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.25629382556941</v>
+        <v>39.25629382556942</v>
       </c>
       <c r="R2" t="n">
-        <v>39.18348549480662</v>
+        <v>39.18348549480663</v>
       </c>
       <c r="S2" t="n">
-        <v>39.23772672031196</v>
+        <v>39.237726720312</v>
       </c>
       <c r="T2" t="n">
-        <v>39.29886347308049</v>
+        <v>39.29886347308052</v>
       </c>
       <c r="U2" t="n">
-        <v>42.93372024172582</v>
+        <v>42.93372024172584</v>
       </c>
       <c r="V2" t="n">
-        <v>39.34021300478311</v>
+        <v>39.34021300478312</v>
       </c>
       <c r="W2" t="n">
-        <v>45.73909729389908</v>
+        <v>45.7390972938991</v>
       </c>
       <c r="X2" t="n">
-        <v>39.27876989296981</v>
+        <v>39.27876989296984</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.61701814569647</v>
+        <v>39.61701814569649</v>
       </c>
       <c r="Z2" t="n">
         <v>40.54740950882406</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.28214032850569</v>
+        <v>39.2821403285057</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.47046598589613</v>
+        <v>39.47046598589616</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.09851126817938</v>
+        <v>39.11666510535525</v>
       </c>
       <c r="C3" t="n">
-        <v>43.73385497219596</v>
+        <v>43.74423726243271</v>
       </c>
       <c r="D3" t="n">
-        <v>39.41234968690484</v>
+        <v>39.44179549479142</v>
       </c>
       <c r="E3" t="n">
-        <v>39.82904093019614</v>
+        <v>39.87295828587961</v>
       </c>
       <c r="F3" t="n">
-        <v>39.19350034175886</v>
+        <v>39.21527562325257</v>
       </c>
       <c r="G3" t="n">
-        <v>40.25646173507602</v>
+        <v>40.31556789250311</v>
       </c>
       <c r="H3" t="n">
-        <v>40.14866627241047</v>
+        <v>40.20446677894596</v>
       </c>
       <c r="I3" t="n">
-        <v>39.50471976634628</v>
+        <v>39.53747752212328</v>
       </c>
       <c r="J3" t="n">
-        <v>40.55917616614581</v>
+        <v>40.62908625604871</v>
       </c>
       <c r="K3" t="n">
-        <v>39.93877108411315</v>
+        <v>39.98706538316052</v>
       </c>
       <c r="L3" t="n">
-        <v>40.25329726222846</v>
+        <v>40.31254880674874</v>
       </c>
       <c r="M3" t="n">
-        <v>40.87504495995085</v>
+        <v>40.95709054677619</v>
       </c>
       <c r="N3" t="n">
-        <v>41.20089366479755</v>
+        <v>41.29369263389965</v>
       </c>
       <c r="O3" t="n">
-        <v>47.79578674571333</v>
+        <v>47.89263543833231</v>
       </c>
       <c r="P3" t="n">
-        <v>42.18033331979595</v>
+        <v>42.30660039145364</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.0905024685784</v>
+        <v>40.14406363331618</v>
       </c>
       <c r="R3" t="n">
-        <v>39.57673413638651</v>
+        <v>39.61207336185215</v>
       </c>
       <c r="S3" t="n">
-        <v>39.94756562308105</v>
+        <v>39.99595772307121</v>
       </c>
       <c r="T3" t="n">
-        <v>40.39609659291508</v>
+        <v>40.46064120582579</v>
       </c>
       <c r="U3" t="n">
-        <v>47.13309323991088</v>
+        <v>47.2310809419453</v>
       </c>
       <c r="V3" t="n">
-        <v>40.67962323046163</v>
+        <v>40.75361421778827</v>
       </c>
       <c r="W3" t="n">
-        <v>53.5010306029148</v>
+        <v>53.67866810756919</v>
       </c>
       <c r="X3" t="n">
-        <v>40.25479894124494</v>
+        <v>40.31414522067115</v>
       </c>
       <c r="Y3" t="n">
-        <v>42.66477735407192</v>
+        <v>42.80922124320196</v>
       </c>
       <c r="Z3" t="n">
-        <v>42.55096646972071</v>
+        <v>42.61938189872311</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.27679357414519</v>
+        <v>40.33665596563864</v>
       </c>
       <c r="AB3" t="n">
-        <v>41.61910138895006</v>
+        <v>41.72673387889311</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.137486654210915</v>
+        <v>2.137486654210911</v>
       </c>
       <c r="C4" t="n">
-        <v>1.780623843169178</v>
+        <v>1.780623843169177</v>
       </c>
       <c r="D4" t="n">
         <v>2.628127718041996</v>
       </c>
       <c r="E4" t="n">
-        <v>3.290982058313427</v>
+        <v>3.290982058313429</v>
       </c>
       <c r="F4" t="n">
-        <v>2.282518533060522</v>
+        <v>2.282518533060518</v>
       </c>
       <c r="G4" t="n">
-        <v>3.98614014573068</v>
+        <v>3.986140145730695</v>
       </c>
       <c r="H4" t="n">
-        <v>3.784103641422236</v>
+        <v>3.784103641422231</v>
       </c>
       <c r="I4" t="n">
         <v>2.772838248198469</v>
       </c>
       <c r="J4" t="n">
-        <v>4.459836548051166</v>
+        <v>4.459836548051178</v>
       </c>
       <c r="K4" t="n">
-        <v>3.469483962314976</v>
+        <v>3.46948396231497</v>
       </c>
       <c r="L4" t="n">
-        <v>3.977764044400845</v>
+        <v>3.977764044400855</v>
       </c>
       <c r="M4" t="n">
-        <v>4.95421388959941</v>
+        <v>4.954213889599414</v>
       </c>
       <c r="N4" t="n">
-        <v>5.463337883569005</v>
+        <v>5.463337883569006</v>
       </c>
       <c r="O4" t="n">
-        <v>5.697376256515186</v>
+        <v>5.69737625651517</v>
       </c>
       <c r="P4" t="n">
-        <v>7.032872422317194</v>
+        <v>7.03287242231719</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.706733702006168</v>
+        <v>3.706733702006155</v>
       </c>
       <c r="R4" t="n">
-        <v>2.884330112553215</v>
+        <v>2.884330112553211</v>
       </c>
       <c r="S4" t="n">
-        <v>3.497009706833172</v>
+        <v>3.497009706833186</v>
       </c>
       <c r="T4" t="n">
-        <v>4.187577453649173</v>
+        <v>4.187577453649189</v>
       </c>
       <c r="U4" t="n">
-        <v>5.710551923315727</v>
+        <v>5.710551923315726</v>
       </c>
       <c r="V4" t="n">
-        <v>4.662983138289819</v>
+        <v>4.662983138289846</v>
       </c>
       <c r="W4" t="n">
-        <v>9.279321442946616</v>
+        <v>9.279321442946603</v>
       </c>
       <c r="X4" t="n">
-        <v>3.960611222795122</v>
+        <v>3.960611222795106</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.770740791669954</v>
+        <v>7.770740791669967</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.404801143124926</v>
+        <v>4.40480114312492</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.998681842650484</v>
+        <v>3.998681842650475</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.10487535780852</v>
+        <v>6.104875357808508</v>
       </c>
     </row>
     <row r="5">
@@ -5153,82 +5153,82 @@
         <v>14.46315729707665</v>
       </c>
       <c r="C5" t="n">
-        <v>9.079443809083482</v>
+        <v>9.079443809083481</v>
       </c>
       <c r="D5" t="n">
-        <v>25.8681453043075</v>
+        <v>25.86814530430741</v>
       </c>
       <c r="E5" t="n">
-        <v>37.21446953508685</v>
+        <v>37.21446953508688</v>
       </c>
       <c r="F5" t="n">
-        <v>19.06879900669963</v>
+        <v>19.06879900669958</v>
       </c>
       <c r="G5" t="n">
-        <v>43.78714658443634</v>
+        <v>43.78714658443658</v>
       </c>
       <c r="H5" t="n">
-        <v>51.01310147078894</v>
+        <v>51.01310147078883</v>
       </c>
       <c r="I5" t="n">
-        <v>29.12407518216418</v>
+        <v>29.12407518216413</v>
       </c>
       <c r="J5" t="n">
-        <v>55.06662753162171</v>
+        <v>55.06662753162173</v>
       </c>
       <c r="K5" t="n">
         <v>38.88969466038919</v>
       </c>
       <c r="L5" t="n">
-        <v>44.81225111692601</v>
+        <v>44.81225111692608</v>
       </c>
       <c r="M5" t="n">
-        <v>66.36113379817192</v>
+        <v>66.36113379817188</v>
       </c>
       <c r="N5" t="n">
-        <v>77.8704513900648</v>
+        <v>77.87045139006506</v>
       </c>
       <c r="O5" t="n">
-        <v>73.22910656333866</v>
+        <v>73.22910656333852</v>
       </c>
       <c r="P5" t="n">
-        <v>100.7216206812503</v>
+        <v>100.7216206812505</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.39048686592097</v>
+        <v>44.39048686592093</v>
       </c>
       <c r="R5" t="n">
-        <v>32.10425667764091</v>
+        <v>32.10425667764114</v>
       </c>
       <c r="S5" t="n">
-        <v>34.62855449390882</v>
+        <v>34.62855449390885</v>
       </c>
       <c r="T5" t="n">
-        <v>54.46797435564463</v>
+        <v>54.46797435564469</v>
       </c>
       <c r="U5" t="n">
-        <v>79.1129138600414</v>
+        <v>79.1129138600412</v>
       </c>
       <c r="V5" t="n">
-        <v>56.86332771979509</v>
+        <v>56.86332771979504</v>
       </c>
       <c r="W5" t="n">
-        <v>151.3072684032783</v>
+        <v>151.3072684032786</v>
       </c>
       <c r="X5" t="n">
-        <v>51.35068456921951</v>
+        <v>51.35068456921957</v>
       </c>
       <c r="Y5" t="n">
-        <v>121.3022906786877</v>
+        <v>121.3022906786879</v>
       </c>
       <c r="Z5" t="n">
-        <v>52.12797686575188</v>
+        <v>52.1279768657518</v>
       </c>
       <c r="AA5" t="n">
-        <v>50.92466107485146</v>
+        <v>50.92466107485143</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.11245607556023</v>
+        <v>96.11245607556026</v>
       </c>
     </row>
     <row r="6">
@@ -5241,7 +5241,7 @@
         <v>121.5961304938028</v>
       </c>
       <c r="C6" t="n">
-        <v>121.2392676827611</v>
+        <v>121.239267682761</v>
       </c>
       <c r="D6" t="n">
         <v>145.7195658738991</v>
@@ -5259,25 +5259,25 @@
         <v>146.8755417972793</v>
       </c>
       <c r="I6" t="n">
-        <v>145.8642764040556</v>
+        <v>145.8642764040557</v>
       </c>
       <c r="J6" t="n">
-        <v>123.918480387643</v>
+        <v>123.9184803876429</v>
       </c>
       <c r="K6" t="n">
-        <v>146.5609221181722</v>
+        <v>146.5609221181721</v>
       </c>
       <c r="L6" t="n">
         <v>123.4364078839927</v>
       </c>
       <c r="M6" t="n">
-        <v>148.0456520454565</v>
+        <v>148.0456520454564</v>
       </c>
       <c r="N6" t="n">
-        <v>124.9278647443018</v>
+        <v>124.9278647443021</v>
       </c>
       <c r="O6" t="n">
-        <v>148.8605749472365</v>
+        <v>148.8605749472366</v>
       </c>
       <c r="P6" t="n">
         <v>150.1957853888397</v>
@@ -5286,13 +5286,13 @@
         <v>146.7981718578633</v>
       </c>
       <c r="R6" t="n">
-        <v>145.9757682684104</v>
+        <v>145.9757682684103</v>
       </c>
       <c r="S6" t="n">
-        <v>122.9556535464251</v>
+        <v>122.955653546425</v>
       </c>
       <c r="T6" t="n">
-        <v>123.646221293241</v>
+        <v>123.6462212932411</v>
       </c>
       <c r="U6" t="n">
         <v>125.1797358104647</v>
@@ -5301,7 +5301,7 @@
         <v>147.754421294147</v>
       </c>
       <c r="W6" t="n">
-        <v>152.4427039774117</v>
+        <v>152.4427039774116</v>
       </c>
       <c r="X6" t="n">
         <v>123.4192550623869</v>
@@ -5310,13 +5310,13 @@
         <v>132.4897462443676</v>
       </c>
       <c r="Z6" t="n">
-        <v>123.8634449827169</v>
+        <v>123.8634449827168</v>
       </c>
       <c r="AA6" t="n">
         <v>147.0901199985076</v>
       </c>
       <c r="AB6" t="n">
-        <v>125.5813486657625</v>
+        <v>125.5813486657626</v>
       </c>
     </row>
     <row r="7">
@@ -5326,55 +5326,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.156768276269891</v>
+        <v>3.156768276269894</v>
       </c>
       <c r="C7" t="n">
-        <v>2.799905465228166</v>
+        <v>2.799905465228161</v>
       </c>
       <c r="D7" t="n">
-        <v>3.647409340100982</v>
+        <v>3.647409340100976</v>
       </c>
       <c r="E7" t="n">
-        <v>4.310263680372414</v>
+        <v>4.310263680372409</v>
       </c>
       <c r="F7" t="n">
-        <v>3.301800155119517</v>
+        <v>3.3018001551195</v>
       </c>
       <c r="G7" t="n">
-        <v>5.005421767789674</v>
+        <v>5.005421767789679</v>
       </c>
       <c r="H7" t="n">
-        <v>4.803385263481225</v>
+        <v>4.803385263481212</v>
       </c>
       <c r="I7" t="n">
-        <v>3.792119870257456</v>
+        <v>3.792119870257446</v>
       </c>
       <c r="J7" t="n">
-        <v>5.479118170110159</v>
+        <v>5.479118170110163</v>
       </c>
       <c r="K7" t="n">
-        <v>4.488765584373958</v>
+        <v>4.488765584373951</v>
       </c>
       <c r="L7" t="n">
-        <v>4.997045666459836</v>
+        <v>4.997045666459837</v>
       </c>
       <c r="M7" t="n">
-        <v>5.973495511658413</v>
+        <v>5.973495511658395</v>
       </c>
       <c r="N7" t="n">
-        <v>6.482619505627991</v>
+        <v>6.482619505627992</v>
       </c>
       <c r="O7" t="n">
-        <v>6.716652933257324</v>
+        <v>6.716652933257317</v>
       </c>
       <c r="P7" t="n">
-        <v>8.052149099059324</v>
+        <v>8.052149099059331</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.726015324065148</v>
+        <v>4.726015324065138</v>
       </c>
       <c r="R7" t="n">
-        <v>3.903611734612195</v>
+        <v>3.903611734612197</v>
       </c>
       <c r="S7" t="n">
         <v>4.516291328892168</v>
@@ -5383,28 +5383,28 @@
         <v>5.206859075708165</v>
       </c>
       <c r="U7" t="n">
-        <v>6.735692807551778</v>
+        <v>6.73569280755177</v>
       </c>
       <c r="V7" t="n">
-        <v>5.68226476034882</v>
+        <v>5.682264760348829</v>
       </c>
       <c r="W7" t="n">
-        <v>10.29860306500561</v>
+        <v>10.29860306500559</v>
       </c>
       <c r="X7" t="n">
-        <v>4.979892844854103</v>
+        <v>4.979892844854099</v>
       </c>
       <c r="Y7" t="n">
         <v>8.800562461285985</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.42408276518391</v>
+        <v>5.424082765183901</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.017963464709465</v>
+        <v>5.017963464709464</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.124156979867497</v>
+        <v>7.124156979867495</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.49545233503515</v>
+        <v>3.495452335035154</v>
       </c>
       <c r="C8" t="n">
-        <v>4.162096297947442</v>
+        <v>4.162096297947443</v>
       </c>
       <c r="D8" t="n">
-        <v>5.00960017282026</v>
+        <v>5.009600172820263</v>
       </c>
       <c r="E8" t="n">
-        <v>5.127467347831594</v>
+        <v>5.127467347831601</v>
       </c>
       <c r="F8" t="n">
-        <v>3.799934607107208</v>
+        <v>3.799934607107215</v>
       </c>
       <c r="G8" t="n">
-        <v>6.579843397494376</v>
+        <v>6.579843397494381</v>
       </c>
       <c r="H8" t="n">
-        <v>6.165576096200495</v>
+        <v>6.165576096200498</v>
       </c>
       <c r="I8" t="n">
-        <v>5.154310702976735</v>
+        <v>5.154310702976734</v>
       </c>
       <c r="J8" t="n">
-        <v>6.841309002829429</v>
+        <v>6.841309002829448</v>
       </c>
       <c r="K8" t="n">
-        <v>5.850956417093241</v>
+        <v>5.850956417093242</v>
       </c>
       <c r="L8" t="n">
-        <v>6.35923649917912</v>
+        <v>6.359236499179123</v>
       </c>
       <c r="M8" t="n">
-        <v>7.335686344379144</v>
+        <v>7.335686344379147</v>
       </c>
       <c r="N8" t="n">
-        <v>7.051421359175542</v>
+        <v>7.051421359175556</v>
       </c>
       <c r="O8" t="n">
         <v>7.503489911675901</v>
       </c>
       <c r="P8" t="n">
-        <v>8.78554161220714</v>
+        <v>8.785541612207153</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.863556941760503</v>
+        <v>4.863556941760507</v>
       </c>
       <c r="R8" t="n">
-        <v>5.265802567331475</v>
+        <v>5.265802567331471</v>
       </c>
       <c r="S8" t="n">
-        <v>5.878482161611436</v>
+        <v>5.878482161611454</v>
       </c>
       <c r="T8" t="n">
-        <v>6.569049908427438</v>
+        <v>6.569049908427449</v>
       </c>
       <c r="U8" t="n">
-        <v>7.599380767682236</v>
+        <v>7.599380767682246</v>
       </c>
       <c r="V8" t="n">
-        <v>6.760718965888589</v>
+        <v>6.760718965888604</v>
       </c>
       <c r="W8" t="n">
         <v>11.66099504457729</v>
       </c>
       <c r="X8" t="n">
-        <v>5.211240891166762</v>
+        <v>5.211240891166758</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.17420375227185</v>
+        <v>11.17420375227187</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.743754660284424</v>
+        <v>5.743754660284412</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.380154297428741</v>
+        <v>6.380154297428748</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.555486220784475</v>
+        <v>9.555486220784484</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.730837826007509</v>
+        <v>5.730837826007517</v>
       </c>
       <c r="C9" t="n">
-        <v>6.437666769219256</v>
+        <v>6.437666769219259</v>
       </c>
       <c r="D9" t="n">
-        <v>7.285170644092075</v>
+        <v>7.285170644092081</v>
       </c>
       <c r="E9" t="n">
-        <v>7.702529586045971</v>
+        <v>7.702529586045977</v>
       </c>
       <c r="F9" t="n">
-        <v>4.487461113784883</v>
+        <v>4.487461113784874</v>
       </c>
       <c r="G9" t="n">
-        <v>8.643183487593054</v>
+        <v>8.643183487593046</v>
       </c>
       <c r="H9" t="n">
-        <v>8.441146567472302</v>
+        <v>8.441146567472316</v>
       </c>
       <c r="I9" t="n">
-        <v>7.429881174248553</v>
+        <v>7.429881174248555</v>
       </c>
       <c r="J9" t="n">
-        <v>9.116879474101268</v>
+        <v>9.116879474101264</v>
       </c>
       <c r="K9" t="n">
-        <v>8.126526888365058</v>
+        <v>8.126526888365049</v>
       </c>
       <c r="L9" t="n">
-        <v>8.634806970450922</v>
+        <v>8.634806970450942</v>
       </c>
       <c r="M9" t="n">
-        <v>9.611256815649508</v>
+        <v>9.611256815649499</v>
       </c>
       <c r="N9" t="n">
         <v>10.12038080961909</v>
       </c>
       <c r="O9" t="n">
-        <v>10.70692579075126</v>
+        <v>10.70692579075125</v>
       </c>
       <c r="P9" t="n">
-        <v>12.11908600540689</v>
+        <v>12.11908600540688</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.363777043868513</v>
+        <v>8.363777043868517</v>
       </c>
       <c r="R9" t="n">
-        <v>7.541373038603297</v>
+        <v>7.541373038603295</v>
       </c>
       <c r="S9" t="n">
-        <v>8.154052632883259</v>
+        <v>8.154052632883262</v>
       </c>
       <c r="T9" t="n">
-        <v>8.844620379699279</v>
+        <v>8.844620379699265</v>
       </c>
       <c r="U9" t="n">
-        <v>10.37813489692286</v>
+        <v>10.37813489692285</v>
       </c>
       <c r="V9" t="n">
-        <v>10.54750337292384</v>
+        <v>10.54750337292385</v>
       </c>
       <c r="W9" t="n">
-        <v>13.9363643689967</v>
+        <v>13.93636436899669</v>
       </c>
       <c r="X9" t="n">
-        <v>8.617654148845189</v>
+        <v>8.617654148845192</v>
       </c>
       <c r="Y9" t="n">
         <v>12.43832376527709</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.420532693635945</v>
+        <v>8.420532693635936</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.655724768700564</v>
+        <v>8.655724768700571</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.76191828385859</v>
+        <v>10.7619182838586</v>
       </c>
     </row>
   </sheetData>
@@ -5746,19 +5746,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.84110052853848</v>
+        <v>38.84110052853845</v>
       </c>
       <c r="C2" t="n">
-        <v>41.81414835615186</v>
+        <v>41.81414835615188</v>
       </c>
       <c r="D2" t="n">
-        <v>38.85898391116448</v>
+        <v>38.85898391116445</v>
       </c>
       <c r="E2" t="n">
-        <v>38.88616051505189</v>
+        <v>38.88616051505191</v>
       </c>
       <c r="F2" t="n">
-        <v>38.91485707994927</v>
+        <v>38.91485707994928</v>
       </c>
       <c r="G2" t="n">
         <v>39.01420647941357</v>
@@ -5767,64 +5767,64 @@
         <v>38.99677271586012</v>
       </c>
       <c r="I2" t="n">
-        <v>38.91026805556009</v>
+        <v>38.91026805556008</v>
       </c>
       <c r="J2" t="n">
-        <v>39.004821729942</v>
+        <v>39.00482172994202</v>
       </c>
       <c r="K2" t="n">
-        <v>38.89475621558115</v>
+        <v>38.89475621558114</v>
       </c>
       <c r="L2" t="n">
-        <v>38.85890656493245</v>
+        <v>38.85890656493244</v>
       </c>
       <c r="M2" t="n">
-        <v>38.95219429021051</v>
+        <v>38.9521942902105</v>
       </c>
       <c r="N2" t="n">
-        <v>39.0971129590377</v>
+        <v>39.09711295903769</v>
       </c>
       <c r="O2" t="n">
-        <v>42.92789744264258</v>
+        <v>42.92789744264259</v>
       </c>
       <c r="P2" t="n">
-        <v>39.25366770777371</v>
+        <v>39.2536677077737</v>
       </c>
       <c r="Q2" t="n">
         <v>38.91511037566391</v>
       </c>
       <c r="R2" t="n">
-        <v>38.87234752315268</v>
+        <v>38.87234752315269</v>
       </c>
       <c r="S2" t="n">
-        <v>38.94751390896919</v>
+        <v>38.9475139089692</v>
       </c>
       <c r="T2" t="n">
-        <v>38.99148373762932</v>
+        <v>38.99148373762933</v>
       </c>
       <c r="U2" t="n">
-        <v>42.3804492255433</v>
+        <v>42.38044922554331</v>
       </c>
       <c r="V2" t="n">
-        <v>39.03507686639818</v>
+        <v>39.03507686639816</v>
       </c>
       <c r="W2" t="n">
         <v>45.09614561926234</v>
       </c>
       <c r="X2" t="n">
-        <v>39.16568290971051</v>
+        <v>39.1656829097105</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.27489114213399</v>
+        <v>39.27489114213397</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.04127110647178</v>
+        <v>40.04127110647179</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.09113099922038</v>
+        <v>39.09113099922037</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.09162841814024</v>
+        <v>39.09162841814025</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.57529510480502</v>
+        <v>38.58104633878914</v>
       </c>
       <c r="C3" t="n">
-        <v>43.65086226406356</v>
+        <v>43.66440508406306</v>
       </c>
       <c r="D3" t="n">
-        <v>38.70343242155413</v>
+        <v>38.71379808137281</v>
       </c>
       <c r="E3" t="n">
-        <v>38.89708806492249</v>
+        <v>38.91417131054752</v>
       </c>
       <c r="F3" t="n">
-        <v>39.10260324700612</v>
+        <v>39.12727239214819</v>
       </c>
       <c r="G3" t="n">
-        <v>39.79916025186783</v>
+        <v>39.84821930757423</v>
       </c>
       <c r="H3" t="n">
-        <v>39.69204202199644</v>
+        <v>39.73769821598665</v>
       </c>
       <c r="I3" t="n">
-        <v>39.07037350439629</v>
+        <v>39.09380403468889</v>
       </c>
       <c r="J3" t="n">
-        <v>39.73730962192535</v>
+        <v>39.78426182888731</v>
       </c>
       <c r="K3" t="n">
-        <v>38.95705668725853</v>
+        <v>38.97648030560801</v>
       </c>
       <c r="L3" t="n">
-        <v>38.70109405982084</v>
+        <v>38.71135492171033</v>
       </c>
       <c r="M3" t="n">
-        <v>39.37121282504133</v>
+        <v>39.40566820393833</v>
       </c>
       <c r="N3" t="n">
-        <v>40.39988210397265</v>
+        <v>40.47042403759911</v>
       </c>
       <c r="O3" t="n">
-        <v>47.01132543772426</v>
+        <v>47.09469427553079</v>
       </c>
       <c r="P3" t="n">
-        <v>41.50602030039156</v>
+        <v>41.61471154473141</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.10057810009462</v>
+        <v>39.12513639183388</v>
       </c>
       <c r="R3" t="n">
-        <v>38.79982902361593</v>
+        <v>38.81363839416771</v>
       </c>
       <c r="S3" t="n">
-        <v>39.32771038837743</v>
+        <v>39.36016471021549</v>
       </c>
       <c r="T3" t="n">
-        <v>39.6475417940892</v>
+        <v>39.69158155559605</v>
       </c>
       <c r="U3" t="n">
-        <v>45.38426018173618</v>
+        <v>45.43483376495034</v>
       </c>
       <c r="V3" t="n">
-        <v>39.94996343644586</v>
+        <v>40.00430172575084</v>
       </c>
       <c r="W3" t="n">
-        <v>51.2309068044022</v>
+        <v>51.34416991856178</v>
       </c>
       <c r="X3" t="n">
-        <v>40.88784280800522</v>
+        <v>40.97600739468345</v>
       </c>
       <c r="Y3" t="n">
-        <v>41.67232542786633</v>
+        <v>41.7876251810977</v>
       </c>
       <c r="Z3" t="n">
-        <v>41.11589823909303</v>
+        <v>41.1474157246798</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.36033886078661</v>
+        <v>40.42919684630458</v>
       </c>
       <c r="AB3" t="n">
-        <v>40.3563803275218</v>
+        <v>40.42546335242923</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.366664752831685</v>
+        <v>1.366664752831704</v>
       </c>
       <c r="C4" t="n">
-        <v>1.710632284997022</v>
+        <v>1.710632284997034</v>
       </c>
       <c r="D4" t="n">
-        <v>1.568665786354967</v>
+        <v>1.568665786354966</v>
       </c>
       <c r="E4" t="n">
-        <v>1.875638029118912</v>
+        <v>1.875638029118927</v>
       </c>
       <c r="F4" t="n">
-        <v>2.199778930706811</v>
+        <v>2.199778930706827</v>
       </c>
       <c r="G4" t="n">
-        <v>3.321976100637877</v>
+        <v>3.321976100637886</v>
       </c>
       <c r="H4" t="n">
-        <v>3.125053721373798</v>
+        <v>3.125053721373812</v>
       </c>
       <c r="I4" t="n">
-        <v>2.147943789175236</v>
+        <v>2.147943789175232</v>
       </c>
       <c r="J4" t="n">
-        <v>3.21717376337222</v>
+        <v>3.217173763372225</v>
       </c>
       <c r="K4" t="n">
-        <v>1.972730420814319</v>
+        <v>1.972730420814321</v>
       </c>
       <c r="L4" t="n">
         <v>1.567792125083018</v>
       </c>
       <c r="M4" t="n">
-        <v>2.634567619952888</v>
+        <v>2.634567619952904</v>
       </c>
       <c r="N4" t="n">
-        <v>4.258442926857505</v>
+        <v>4.258442926857497</v>
       </c>
       <c r="O4" t="n">
-        <v>4.877241709584835</v>
+        <v>4.877241709584853</v>
       </c>
       <c r="P4" t="n">
-        <v>6.026800832572769</v>
+        <v>6.026800832572782</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.202640022325443</v>
+        <v>2.202640022325459</v>
       </c>
       <c r="R4" t="n">
-        <v>1.719613931326832</v>
+        <v>1.719613931326839</v>
       </c>
       <c r="S4" t="n">
-        <v>2.568652837369959</v>
+        <v>2.568652837369981</v>
       </c>
       <c r="T4" t="n">
-        <v>3.06531227920703</v>
+        <v>3.065312279207033</v>
       </c>
       <c r="U4" t="n">
-        <v>3.364229944919039</v>
+        <v>3.364229944919048</v>
       </c>
       <c r="V4" t="n">
         <v>3.565499165397936</v>
       </c>
       <c r="W4" t="n">
-        <v>6.183516943497885</v>
+        <v>6.18351694349789</v>
       </c>
       <c r="X4" t="n">
-        <v>5.032972063442585</v>
+        <v>5.032972063442592</v>
       </c>
       <c r="Y4" t="n">
         <v>6.250970907607448</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.529182623260479</v>
+        <v>2.529182623260501</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.190873938882789</v>
+        <v>4.190873938882799</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.179785737821715</v>
+        <v>4.179785737821724</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.651384244607914</v>
+        <v>4.651384244607936</v>
       </c>
       <c r="C5" t="n">
-        <v>10.89657151340764</v>
+        <v>10.8965715134077</v>
       </c>
       <c r="D5" t="n">
-        <v>8.484629535882405</v>
+        <v>8.4846295358824</v>
       </c>
       <c r="E5" t="n">
-        <v>13.75581254426256</v>
+        <v>13.75581254426257</v>
       </c>
       <c r="F5" t="n">
-        <v>19.854836505477</v>
+        <v>19.85483650547708</v>
       </c>
       <c r="G5" t="n">
-        <v>33.22254676525253</v>
+        <v>33.22254676525257</v>
       </c>
       <c r="H5" t="n">
-        <v>38.70877636638067</v>
+        <v>38.70877636638075</v>
       </c>
       <c r="I5" t="n">
-        <v>19.20874282594662</v>
+        <v>19.20874282594666</v>
       </c>
       <c r="J5" t="n">
-        <v>34.00674311525294</v>
+        <v>34.00674311525297</v>
       </c>
       <c r="K5" t="n">
-        <v>14.758253601414</v>
+        <v>14.75825360141402</v>
       </c>
       <c r="L5" t="n">
         <v>7.543453053581892</v>
       </c>
       <c r="M5" t="n">
-        <v>24.97593013280346</v>
+        <v>24.97593013280345</v>
       </c>
       <c r="N5" t="n">
-        <v>54.45687528540235</v>
+        <v>54.45687528540254</v>
       </c>
       <c r="O5" t="n">
-        <v>58.90945202956328</v>
+        <v>58.90945202956339</v>
       </c>
       <c r="P5" t="n">
-        <v>79.92864605312154</v>
+        <v>79.9286460531217</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.91912017091837</v>
+        <v>17.91912017091838</v>
       </c>
       <c r="R5" t="n">
-        <v>11.68290131646639</v>
+        <v>11.68290131646641</v>
       </c>
       <c r="S5" t="n">
-        <v>22.25065975730336</v>
+        <v>22.25065975730334</v>
       </c>
       <c r="T5" t="n">
-        <v>34.15282445381489</v>
+        <v>34.15282445381492</v>
       </c>
       <c r="U5" t="n">
         <v>34.47439524510258</v>
       </c>
       <c r="V5" t="n">
-        <v>38.35860638633739</v>
+        <v>38.35860638633748</v>
       </c>
       <c r="W5" t="n">
-        <v>85.12979796509453</v>
+        <v>85.12979796509443</v>
       </c>
       <c r="X5" t="n">
-        <v>67.41647837430665</v>
+        <v>67.41647837430666</v>
       </c>
       <c r="Y5" t="n">
-        <v>91.85516460792024</v>
+        <v>91.8551646079203</v>
       </c>
       <c r="Z5" t="n">
         <v>22.54372592605191</v>
       </c>
       <c r="AA5" t="n">
-        <v>54.8943706005704</v>
+        <v>54.89437060057035</v>
       </c>
       <c r="AB5" t="n">
-        <v>55.51108754720268</v>
+        <v>55.51108754720265</v>
       </c>
     </row>
     <row r="6">
@@ -6098,40 +6098,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.5047971254061</v>
+        <v>134.5047971254062</v>
       </c>
       <c r="C6" t="n">
-        <v>112.9186152967066</v>
+        <v>112.9186152967068</v>
       </c>
       <c r="D6" t="n">
-        <v>112.7766487980647</v>
+        <v>112.7766487980648</v>
       </c>
       <c r="E6" t="n">
         <v>113.0836210408287</v>
       </c>
       <c r="F6" t="n">
-        <v>135.3379113032813</v>
+        <v>135.3379113032814</v>
       </c>
       <c r="G6" t="n">
-        <v>136.4601084732124</v>
+        <v>136.4601084732125</v>
       </c>
       <c r="H6" t="n">
-        <v>136.2631860939482</v>
+        <v>136.2631860939483</v>
       </c>
       <c r="I6" t="n">
-        <v>135.2860761617496</v>
+        <v>135.2860761617498</v>
       </c>
       <c r="J6" t="n">
         <v>136.3553061359466</v>
       </c>
       <c r="K6" t="n">
-        <v>135.1108627933887</v>
+        <v>135.1108627933889</v>
       </c>
       <c r="L6" t="n">
-        <v>112.7757751367926</v>
+        <v>112.7757751367927</v>
       </c>
       <c r="M6" t="n">
-        <v>135.7726999925272</v>
+        <v>135.7726999925274</v>
       </c>
       <c r="N6" t="n">
         <v>115.4729570504244</v>
@@ -6143,16 +6143,16 @@
         <v>110.8098592199405</v>
       </c>
       <c r="Q6" t="n">
-        <v>135.3407723948999</v>
+        <v>135.3407723949</v>
       </c>
       <c r="R6" t="n">
-        <v>112.9275969430365</v>
+        <v>112.9275969430366</v>
       </c>
       <c r="S6" t="n">
-        <v>135.7067852099443</v>
+        <v>135.7067852099445</v>
       </c>
       <c r="T6" t="n">
-        <v>114.2732952909167</v>
+        <v>114.2732952909168</v>
       </c>
       <c r="U6" t="n">
         <v>114.5877713359555</v>
@@ -6161,22 +6161,22 @@
         <v>114.7734821771076</v>
       </c>
       <c r="W6" t="n">
-        <v>123.0806657530047</v>
+        <v>123.0806657530048</v>
       </c>
       <c r="X6" t="n">
         <v>138.171104436017</v>
       </c>
       <c r="Y6" t="n">
-        <v>122.3612402006163</v>
+        <v>122.3612402006162</v>
       </c>
       <c r="Z6" t="n">
-        <v>113.7371656349702</v>
+        <v>113.7371656349703</v>
       </c>
       <c r="AA6" t="n">
-        <v>137.3290063114572</v>
+        <v>137.3290063114573</v>
       </c>
       <c r="AB6" t="n">
-        <v>115.4022213659933</v>
+        <v>115.4022213659932</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.209618540268885</v>
+        <v>2.209618540268901</v>
       </c>
       <c r="C7" t="n">
-        <v>2.553586072434214</v>
+        <v>2.553586072434232</v>
       </c>
       <c r="D7" t="n">
-        <v>2.411619573792161</v>
+        <v>2.411619573792173</v>
       </c>
       <c r="E7" t="n">
-        <v>2.718591816556124</v>
+        <v>2.718591816556128</v>
       </c>
       <c r="F7" t="n">
-        <v>3.042732718144016</v>
+        <v>3.042732718144037</v>
       </c>
       <c r="G7" t="n">
-        <v>4.164929888075068</v>
+        <v>4.16492988807508</v>
       </c>
       <c r="H7" t="n">
-        <v>3.968007508810993</v>
+        <v>3.968007508811008</v>
       </c>
       <c r="I7" t="n">
-        <v>2.990897576612429</v>
+        <v>2.990897576612445</v>
       </c>
       <c r="J7" t="n">
-        <v>4.060127550809418</v>
+        <v>4.060127550809426</v>
       </c>
       <c r="K7" t="n">
         <v>2.815684208251514</v>
       </c>
       <c r="L7" t="n">
-        <v>2.410745912520214</v>
+        <v>2.410745912520213</v>
       </c>
       <c r="M7" t="n">
-        <v>3.477521407390102</v>
+        <v>3.477521407390106</v>
       </c>
       <c r="N7" t="n">
-        <v>5.101396714294698</v>
+        <v>5.101396714294706</v>
       </c>
       <c r="O7" t="n">
-        <v>5.720192534476425</v>
+        <v>5.720192534476434</v>
       </c>
       <c r="P7" t="n">
-        <v>6.869751657464372</v>
+        <v>6.869751657464381</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.045593809762648</v>
+        <v>3.045593809762656</v>
       </c>
       <c r="R7" t="n">
-        <v>2.562567718764028</v>
+        <v>2.56256771876404</v>
       </c>
       <c r="S7" t="n">
-        <v>3.411606624807163</v>
+        <v>3.411606624807179</v>
       </c>
       <c r="T7" t="n">
-        <v>3.908266066644217</v>
+        <v>3.908266066644234</v>
       </c>
       <c r="U7" t="n">
         <v>4.217597214673699</v>
       </c>
       <c r="V7" t="n">
-        <v>4.40845295283514</v>
+        <v>4.408452952835143</v>
       </c>
       <c r="W7" t="n">
-        <v>7.026470730935074</v>
+        <v>7.026470730935093</v>
       </c>
       <c r="X7" t="n">
-        <v>5.875925850879784</v>
+        <v>5.875925850879788</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.109483074371418</v>
+        <v>7.109483074371424</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.372136410697681</v>
+        <v>3.372136410697698</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.033827726319982</v>
+        <v>5.033827726319993</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.022739525258915</v>
+        <v>5.022739525258924</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.424807500793553</v>
+        <v>2.424807500793571</v>
       </c>
       <c r="C8" t="n">
-        <v>3.56192719495458</v>
+        <v>3.561927194954589</v>
       </c>
       <c r="D8" t="n">
-        <v>3.419960696312524</v>
+        <v>3.419960696312522</v>
       </c>
       <c r="E8" t="n">
-        <v>3.304602809565442</v>
+        <v>3.304602809565457</v>
       </c>
       <c r="F8" t="n">
-        <v>3.38148551561128</v>
+        <v>3.3814855156113</v>
       </c>
       <c r="G8" t="n">
-        <v>5.337736278204932</v>
+        <v>5.337736278204934</v>
       </c>
       <c r="H8" t="n">
-        <v>4.976348631331364</v>
+        <v>4.976348631331367</v>
       </c>
       <c r="I8" t="n">
-        <v>3.999238699132792</v>
+        <v>3.999238699132791</v>
       </c>
       <c r="J8" t="n">
-        <v>5.068468673329775</v>
+        <v>5.068468673329784</v>
       </c>
       <c r="K8" t="n">
-        <v>3.824025330771877</v>
+        <v>3.824025330771883</v>
       </c>
       <c r="L8" t="n">
-        <v>3.41908703504058</v>
+        <v>3.419087035040569</v>
       </c>
       <c r="M8" t="n">
-        <v>4.485862529910106</v>
+        <v>4.485862529910112</v>
       </c>
       <c r="N8" t="n">
-        <v>5.494912219511548</v>
+        <v>5.494912219511568</v>
       </c>
       <c r="O8" t="n">
-        <v>6.282670419732341</v>
+        <v>6.28267041973236</v>
       </c>
       <c r="P8" t="n">
-        <v>7.390813506923052</v>
+        <v>7.390813506923066</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.104910267944669</v>
+        <v>3.104910267944686</v>
       </c>
       <c r="R8" t="n">
-        <v>3.570908841284389</v>
+        <v>3.5709088412844</v>
       </c>
       <c r="S8" t="n">
-        <v>4.419947747327517</v>
+        <v>4.419947747327538</v>
       </c>
       <c r="T8" t="n">
-        <v>4.916607189164585</v>
+        <v>4.916607189164597</v>
       </c>
       <c r="U8" t="n">
-        <v>4.839971376361069</v>
+        <v>4.839971376361081</v>
       </c>
       <c r="V8" t="n">
-        <v>5.19561843124985</v>
+        <v>5.195618431249846</v>
       </c>
       <c r="W8" t="n">
         <v>8.034967729454584</v>
       </c>
       <c r="X8" t="n">
-        <v>6.00793628003292</v>
+        <v>6.007936280032904</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.899620379656721</v>
+        <v>8.899620379656728</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.572592162704937</v>
+        <v>3.572592162704939</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.042168848840348</v>
+        <v>6.042168848840356</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.859594402242721</v>
+        <v>6.859594402242716</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.071502344645135</v>
+        <v>4.071502344645156</v>
       </c>
       <c r="C9" t="n">
-        <v>5.216093641494158</v>
+        <v>5.216093641494177</v>
       </c>
       <c r="D9" t="n">
-        <v>5.074127142852103</v>
+        <v>5.074127142852114</v>
       </c>
       <c r="E9" t="n">
-        <v>5.196318958750522</v>
+        <v>5.196318958750524</v>
       </c>
       <c r="F9" t="n">
-        <v>3.859583536516266</v>
+        <v>3.859583536516263</v>
       </c>
       <c r="G9" t="n">
         <v>6.82743781118747</v>
       </c>
       <c r="H9" t="n">
-        <v>6.630515077870936</v>
+        <v>6.630515077870959</v>
       </c>
       <c r="I9" t="n">
-        <v>5.653405145672364</v>
+        <v>5.653405145672385</v>
       </c>
       <c r="J9" t="n">
-        <v>6.722635119869363</v>
+        <v>6.722635119869372</v>
       </c>
       <c r="K9" t="n">
-        <v>5.478191777311457</v>
+        <v>5.478191777311475</v>
       </c>
       <c r="L9" t="n">
-        <v>5.073253481580154</v>
+        <v>5.073253481580165</v>
       </c>
       <c r="M9" t="n">
-        <v>6.140028976450042</v>
+        <v>6.140028976450061</v>
       </c>
       <c r="N9" t="n">
-        <v>7.763904283354638</v>
+        <v>7.763904283354657</v>
       </c>
       <c r="O9" t="n">
-        <v>8.648029204755716</v>
+        <v>8.64802920475573</v>
       </c>
       <c r="P9" t="n">
-        <v>9.855292133675004</v>
+        <v>9.85529213367502</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.708101732875048</v>
+        <v>5.70810173287505</v>
       </c>
       <c r="R9" t="n">
-        <v>5.225075287823965</v>
+        <v>5.225075287823986</v>
       </c>
       <c r="S9" t="n">
-        <v>6.074114193867111</v>
+        <v>6.074114193867122</v>
       </c>
       <c r="T9" t="n">
-        <v>6.570773635704165</v>
+        <v>6.570773635704187</v>
       </c>
       <c r="U9" t="n">
-        <v>6.885249680742952</v>
+        <v>6.885249680742965</v>
       </c>
       <c r="V9" t="n">
-        <v>7.994863448223679</v>
+        <v>7.994863448223683</v>
       </c>
       <c r="W9" t="n">
-        <v>9.688978299995025</v>
+        <v>9.688978299995036</v>
       </c>
       <c r="X9" t="n">
-        <v>8.538433419939725</v>
+        <v>8.538433419939734</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.771990643431362</v>
+        <v>9.771990643431367</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.55193918448662</v>
+        <v>5.551939184486632</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.696335295379923</v>
+        <v>7.696335295379946</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.685247094318862</v>
+        <v>7.68524709431887</v>
       </c>
     </row>
   </sheetData>
@@ -6609,34 +6609,34 @@
         <v>38.69842104855333</v>
       </c>
       <c r="C2" t="n">
-        <v>41.65425171781188</v>
+        <v>41.65425171781187</v>
       </c>
       <c r="D2" t="n">
         <v>38.74270031550378</v>
       </c>
       <c r="E2" t="n">
-        <v>38.69981335289958</v>
+        <v>38.69981335289957</v>
       </c>
       <c r="F2" t="n">
-        <v>38.81293843625948</v>
+        <v>38.81293843625946</v>
       </c>
       <c r="G2" t="n">
-        <v>38.79248497402523</v>
+        <v>38.79248497402524</v>
       </c>
       <c r="H2" t="n">
-        <v>38.84876433900499</v>
+        <v>38.84876433900502</v>
       </c>
       <c r="I2" t="n">
         <v>38.76023842329506</v>
       </c>
       <c r="J2" t="n">
-        <v>38.81298169385913</v>
+        <v>38.81298169385916</v>
       </c>
       <c r="K2" t="n">
-        <v>38.76083091507994</v>
+        <v>38.76083091507997</v>
       </c>
       <c r="L2" t="n">
-        <v>38.72410660973708</v>
+        <v>38.72410660973712</v>
       </c>
       <c r="M2" t="n">
         <v>38.80849534294823</v>
@@ -6648,43 +6648,43 @@
         <v>42.59541677849833</v>
       </c>
       <c r="P2" t="n">
-        <v>39.05837101845326</v>
+        <v>39.05837101845324</v>
       </c>
       <c r="Q2" t="n">
-        <v>38.74402912500827</v>
+        <v>38.7440291250083</v>
       </c>
       <c r="R2" t="n">
         <v>38.72451168362056</v>
       </c>
       <c r="S2" t="n">
-        <v>38.84877334002168</v>
+        <v>38.84877334002166</v>
       </c>
       <c r="T2" t="n">
         <v>38.83193812908836</v>
       </c>
       <c r="U2" t="n">
-        <v>42.16541008459404</v>
+        <v>42.16541008459403</v>
       </c>
       <c r="V2" t="n">
-        <v>38.82723731838044</v>
+        <v>38.82723731838043</v>
       </c>
       <c r="W2" t="n">
         <v>44.68189194366754</v>
       </c>
       <c r="X2" t="n">
-        <v>39.05783965819825</v>
+        <v>39.05783965819824</v>
       </c>
       <c r="Y2" t="n">
-        <v>38.99777261879449</v>
+        <v>38.99777261879451</v>
       </c>
       <c r="Z2" t="n">
-        <v>39.78238877303494</v>
+        <v>39.78238877303493</v>
       </c>
       <c r="AA2" t="n">
-        <v>38.96640004457797</v>
+        <v>38.966400044578</v>
       </c>
       <c r="AB2" t="n">
-        <v>38.90954941972046</v>
+        <v>38.90954941972044</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.45664220738615</v>
+        <v>38.46208257902781</v>
       </c>
       <c r="C3" t="n">
-        <v>43.4316289726281</v>
+        <v>43.44152909764196</v>
       </c>
       <c r="D3" t="n">
-        <v>38.7732707502792</v>
+        <v>38.79002642753736</v>
       </c>
       <c r="E3" t="n">
-        <v>38.46685568599337</v>
+        <v>38.47264146756982</v>
       </c>
       <c r="F3" t="n">
-        <v>39.27625255319253</v>
+        <v>39.31100963393195</v>
       </c>
       <c r="G3" t="n">
-        <v>39.1234122638494</v>
+        <v>39.15238675827867</v>
       </c>
       <c r="H3" t="n">
-        <v>39.5345466454828</v>
+        <v>39.57852661629561</v>
       </c>
       <c r="I3" t="n">
-        <v>38.89953034607554</v>
+        <v>38.92077772131859</v>
       </c>
       <c r="J3" t="n">
-        <v>39.27182181862474</v>
+        <v>39.30616973297796</v>
       </c>
       <c r="K3" t="n">
-        <v>38.9016147875599</v>
+        <v>38.92294555470206</v>
       </c>
       <c r="L3" t="n">
-        <v>38.63859671391753</v>
+        <v>38.65052841890061</v>
       </c>
       <c r="M3" t="n">
-        <v>39.24460538121622</v>
+        <v>39.278295143128</v>
       </c>
       <c r="N3" t="n">
-        <v>39.68425448073732</v>
+        <v>39.73323983631808</v>
       </c>
       <c r="O3" t="n">
-        <v>46.13625724628905</v>
+        <v>46.19894018647036</v>
       </c>
       <c r="P3" t="n">
-        <v>41.0099963155373</v>
+        <v>41.10524721207847</v>
       </c>
       <c r="Q3" t="n">
-        <v>38.7816064324024</v>
+        <v>38.79865823583329</v>
       </c>
       <c r="R3" t="n">
-        <v>38.64443434359795</v>
+        <v>38.65661569091349</v>
       </c>
       <c r="S3" t="n">
-        <v>39.52321042668263</v>
+        <v>39.5663734132351</v>
       </c>
       <c r="T3" t="n">
-        <v>39.41082596368875</v>
+        <v>39.45026704105788</v>
       </c>
       <c r="U3" t="n">
-        <v>45.1486240743874</v>
+        <v>45.19888537232022</v>
       </c>
       <c r="V3" t="n">
-        <v>39.37074134261197</v>
+        <v>39.40844987956142</v>
       </c>
       <c r="W3" t="n">
-        <v>49.67868304289981</v>
+        <v>49.74610488076205</v>
       </c>
       <c r="X3" t="n">
-        <v>41.01524680161313</v>
+        <v>41.11193636033402</v>
       </c>
       <c r="Y3" t="n">
-        <v>40.59563530420125</v>
+        <v>40.67668594209221</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.46533932466679</v>
+        <v>40.48090702732303</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.37024984125965</v>
+        <v>40.44332298763529</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.95854732514699</v>
+        <v>40.01724544692935</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.224580842304677</v>
+        <v>1.224580842304675</v>
       </c>
       <c r="C4" t="n">
-        <v>1.42025765823133</v>
+        <v>1.420257658231336</v>
       </c>
       <c r="D4" t="n">
-        <v>1.724735531979034</v>
+        <v>1.724735531979042</v>
       </c>
       <c r="E4" t="n">
-        <v>1.240307560387283</v>
+        <v>1.240307560387272</v>
       </c>
       <c r="F4" t="n">
-        <v>2.518107417046873</v>
+        <v>2.518107417046886</v>
       </c>
       <c r="G4" t="n">
-        <v>2.287076152053485</v>
+        <v>2.287076152053481</v>
       </c>
       <c r="H4" t="n">
-        <v>2.922777469287057</v>
+        <v>2.922777469287053</v>
       </c>
       <c r="I4" t="n">
-        <v>1.922836527409639</v>
+        <v>1.922836527409642</v>
       </c>
       <c r="J4" t="n">
-        <v>2.519752479187896</v>
+        <v>2.519752479187898</v>
       </c>
       <c r="K4" t="n">
-        <v>1.929528994679816</v>
+        <v>1.929528994679809</v>
       </c>
       <c r="L4" t="n">
-        <v>1.514711071817332</v>
+        <v>1.514711071817337</v>
       </c>
       <c r="M4" t="n">
-        <v>2.472446060541167</v>
+        <v>2.472446060541173</v>
       </c>
       <c r="N4" t="n">
-        <v>3.167395513256096</v>
+        <v>3.1673955132561</v>
       </c>
       <c r="O4" t="n">
-        <v>3.813666532418742</v>
+        <v>3.81366653241873</v>
       </c>
       <c r="P4" t="n">
-        <v>5.290381337491404</v>
+        <v>5.290381337491394</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.739745046615182</v>
+        <v>1.739745046615184</v>
       </c>
       <c r="R4" t="n">
-        <v>1.519286567674058</v>
+        <v>1.51928656767406</v>
       </c>
       <c r="S4" t="n">
-        <v>2.922879139910888</v>
+        <v>2.922879139910896</v>
       </c>
       <c r="T4" t="n">
-        <v>2.732717687839296</v>
+        <v>2.732717687839302</v>
       </c>
       <c r="U4" t="n">
-        <v>3.219490641655679</v>
+        <v>3.21949064165568</v>
       </c>
       <c r="V4" t="n">
-        <v>2.687079676919175</v>
+        <v>2.687079676919194</v>
       </c>
       <c r="W4" t="n">
-        <v>4.000872446977704</v>
+        <v>4.000872446977692</v>
       </c>
       <c r="X4" t="n">
-        <v>5.284379378973166</v>
+        <v>5.284379378973163</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.5877133623995</v>
+        <v>4.587713362399507</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.681368780866386</v>
+        <v>1.681368780866393</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.251526878831707</v>
+        <v>4.251526878831712</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.589792881584773</v>
+        <v>3.589792881584771</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.399795140028123</v>
+        <v>4.399795140028132</v>
       </c>
       <c r="C5" t="n">
-        <v>8.134303562983806</v>
+        <v>8.134303562983808</v>
       </c>
       <c r="D5" t="n">
-        <v>13.55948948465483</v>
+        <v>13.55948948465482</v>
       </c>
       <c r="E5" t="n">
-        <v>4.821254366178272</v>
+        <v>4.821254366178253</v>
       </c>
       <c r="F5" t="n">
         <v>28.46677567318033</v>
       </c>
       <c r="G5" t="n">
-        <v>20.8240773345567</v>
+        <v>20.82407733455672</v>
       </c>
       <c r="H5" t="n">
-        <v>36.97288839910661</v>
+        <v>36.97288839910659</v>
       </c>
       <c r="I5" t="n">
-        <v>17.62770673272152</v>
+        <v>17.62770673272154</v>
       </c>
       <c r="J5" t="n">
-        <v>26.02046572266422</v>
+        <v>26.02046572266424</v>
       </c>
       <c r="K5" t="n">
-        <v>16.63489570976331</v>
+        <v>16.63489570976335</v>
       </c>
       <c r="L5" t="n">
-        <v>8.824045110424004</v>
+        <v>8.824045110424002</v>
       </c>
       <c r="M5" t="n">
-        <v>26.41785059502678</v>
+        <v>26.41785059502683</v>
       </c>
       <c r="N5" t="n">
-        <v>38.78370947956876</v>
+        <v>38.78370947956882</v>
       </c>
       <c r="O5" t="n">
-        <v>44.67510350745133</v>
+        <v>44.67510350745137</v>
       </c>
       <c r="P5" t="n">
-        <v>68.21200750919101</v>
+        <v>68.21200750919114</v>
       </c>
       <c r="Q5" t="n">
         <v>13.22998503337264</v>
       </c>
       <c r="R5" t="n">
-        <v>10.43196967965567</v>
+        <v>10.43196967965569</v>
       </c>
       <c r="S5" t="n">
-        <v>31.06668715699228</v>
+        <v>31.06668715699229</v>
       </c>
       <c r="T5" t="n">
-        <v>31.72959900417787</v>
+        <v>31.7295990041779</v>
       </c>
       <c r="U5" t="n">
-        <v>35.5038905122187</v>
+        <v>35.50389051221875</v>
       </c>
       <c r="V5" t="n">
-        <v>27.41149308805948</v>
+        <v>27.41149308805946</v>
       </c>
       <c r="W5" t="n">
-        <v>51.81477758062961</v>
+        <v>51.81477758062956</v>
       </c>
       <c r="X5" t="n">
-        <v>72.7920709984185</v>
+        <v>72.79207099841845</v>
       </c>
       <c r="Y5" t="n">
-        <v>65.50258715389693</v>
+        <v>65.50258715389677</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.20478776676137</v>
+        <v>11.2047877667614</v>
       </c>
       <c r="AA5" t="n">
-        <v>58.46915888520294</v>
+        <v>58.46915888520304</v>
       </c>
       <c r="AB5" t="n">
-        <v>49.19134626438399</v>
+        <v>49.1913462643839</v>
       </c>
     </row>
     <row r="6">
@@ -6958,37 +6958,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.239994375785</v>
+        <v>134.2399943757851</v>
       </c>
       <c r="C6" t="n">
-        <v>134.4356711917115</v>
+        <v>134.4356711917117</v>
       </c>
       <c r="D6" t="n">
-        <v>134.7401490654595</v>
+        <v>134.7401490654594</v>
       </c>
       <c r="E6" t="n">
-        <v>112.3892781895615</v>
+        <v>112.3892781895614</v>
       </c>
       <c r="F6" t="n">
         <v>135.5335209505272</v>
       </c>
       <c r="G6" t="n">
-        <v>135.3024896855338</v>
+        <v>135.3024896855339</v>
       </c>
       <c r="H6" t="n">
         <v>135.9381910027674</v>
       </c>
       <c r="I6" t="n">
-        <v>134.9382500608898</v>
+        <v>134.9382500608899</v>
       </c>
       <c r="J6" t="n">
-        <v>113.668723108362</v>
+        <v>113.6687231083619</v>
       </c>
       <c r="K6" t="n">
         <v>113.078499623854</v>
       </c>
       <c r="L6" t="n">
-        <v>134.5301246052976</v>
+        <v>134.5301246052977</v>
       </c>
       <c r="M6" t="n">
         <v>135.4878595940214</v>
@@ -7000,43 +7000,43 @@
         <v>114.9714489261843</v>
       </c>
       <c r="P6" t="n">
-        <v>138.3614293710577</v>
+        <v>138.3614293710579</v>
       </c>
       <c r="Q6" t="n">
-        <v>134.7551585800955</v>
+        <v>134.7551585800956</v>
       </c>
       <c r="R6" t="n">
-        <v>134.5347001011543</v>
+        <v>134.5347001011545</v>
       </c>
       <c r="S6" t="n">
-        <v>135.9382926733912</v>
+        <v>135.9382926733913</v>
       </c>
       <c r="T6" t="n">
         <v>113.8816883170135</v>
       </c>
       <c r="U6" t="n">
-        <v>136.2530853494409</v>
+        <v>136.2530853494408</v>
       </c>
       <c r="V6" t="n">
-        <v>113.8360503060934</v>
+        <v>113.8360503060933</v>
       </c>
       <c r="W6" t="n">
         <v>137.0726080216405</v>
       </c>
       <c r="X6" t="n">
-        <v>116.4333500081473</v>
+        <v>116.4333500081472</v>
       </c>
       <c r="Y6" t="n">
-        <v>120.6386256537036</v>
+        <v>120.6386256537035</v>
       </c>
       <c r="Z6" t="n">
         <v>112.8303394100406</v>
       </c>
       <c r="AA6" t="n">
-        <v>137.2669404123119</v>
+        <v>137.2669404123122</v>
       </c>
       <c r="AB6" t="n">
-        <v>114.7536420441663</v>
+        <v>114.7536420441664</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.01253072044207</v>
+        <v>2.012530720442063</v>
       </c>
       <c r="C7" t="n">
-        <v>2.208207536368716</v>
+        <v>2.208207536368719</v>
       </c>
       <c r="D7" t="n">
-        <v>2.512685410116428</v>
+        <v>2.512685410116424</v>
       </c>
       <c r="E7" t="n">
-        <v>2.028257438524667</v>
+        <v>2.028257438524687</v>
       </c>
       <c r="F7" t="n">
         <v>3.306057295184269</v>
       </c>
       <c r="G7" t="n">
-        <v>3.075026030190869</v>
+        <v>3.07502603019088</v>
       </c>
       <c r="H7" t="n">
-        <v>3.710727347424451</v>
+        <v>3.71072734742446</v>
       </c>
       <c r="I7" t="n">
-        <v>2.710786405547031</v>
+        <v>2.710786405547023</v>
       </c>
       <c r="J7" t="n">
-        <v>3.307702357325277</v>
+        <v>3.307702357325289</v>
       </c>
       <c r="K7" t="n">
-        <v>2.717478872817201</v>
+        <v>2.717478872817204</v>
       </c>
       <c r="L7" t="n">
-        <v>2.302660949954716</v>
+        <v>2.302660949954714</v>
       </c>
       <c r="M7" t="n">
-        <v>3.260395938678551</v>
+        <v>3.260395938678556</v>
       </c>
       <c r="N7" t="n">
-        <v>3.955345391393479</v>
+        <v>3.955345391393489</v>
       </c>
       <c r="O7" t="n">
-        <v>4.601615005116493</v>
+        <v>4.601615005116502</v>
       </c>
       <c r="P7" t="n">
-        <v>6.078329810189164</v>
+        <v>6.078329810189159</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.527694924752565</v>
+        <v>2.527694924752571</v>
       </c>
       <c r="R7" t="n">
-        <v>2.307236445811451</v>
+        <v>2.307236445811452</v>
       </c>
       <c r="S7" t="n">
-        <v>3.710829018048282</v>
+        <v>3.71082901804828</v>
       </c>
       <c r="T7" t="n">
-        <v>3.52066756597669</v>
+        <v>3.520667565976698</v>
       </c>
       <c r="U7" t="n">
-        <v>4.020131273374611</v>
+        <v>4.020131273374624</v>
       </c>
       <c r="V7" t="n">
-        <v>3.475029555056567</v>
+        <v>3.475029555056598</v>
       </c>
       <c r="W7" t="n">
-        <v>4.788822325115095</v>
+        <v>4.788822325115093</v>
       </c>
       <c r="X7" t="n">
-        <v>6.07232925711056</v>
+        <v>6.072329257110549</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.393844414841698</v>
+        <v>5.3938444148417</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.469318659003779</v>
+        <v>2.469318659003771</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.039476756969091</v>
+        <v>5.039476756969098</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.377742759722162</v>
+        <v>4.377742759722159</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.180242245445703</v>
+        <v>2.180242245445704</v>
       </c>
       <c r="C8" t="n">
-        <v>3.088247961100924</v>
+        <v>3.08824796110093</v>
       </c>
       <c r="D8" t="n">
-        <v>3.392725834848632</v>
+        <v>3.392725834848638</v>
       </c>
       <c r="E8" t="n">
-        <v>2.529003736732415</v>
+        <v>2.529003736732423</v>
       </c>
       <c r="F8" t="n">
-        <v>3.58474133748928</v>
+        <v>3.584741337489278</v>
       </c>
       <c r="G8" t="n">
-        <v>4.102772492600052</v>
+        <v>4.102772492600059</v>
       </c>
       <c r="H8" t="n">
-        <v>4.590767772156653</v>
+        <v>4.590767772156658</v>
       </c>
       <c r="I8" t="n">
-        <v>3.590826830279222</v>
+        <v>3.590826830279237</v>
       </c>
       <c r="J8" t="n">
-        <v>4.18774278205748</v>
+        <v>4.187742782057491</v>
       </c>
       <c r="K8" t="n">
-        <v>3.597519297549399</v>
+        <v>3.597519297549397</v>
       </c>
       <c r="L8" t="n">
-        <v>3.182701374686924</v>
+        <v>3.182701374686921</v>
       </c>
       <c r="M8" t="n">
-        <v>4.140436363409494</v>
+        <v>4.140436363409496</v>
       </c>
       <c r="N8" t="n">
-        <v>4.283211748559076</v>
+        <v>4.283211748559074</v>
       </c>
       <c r="O8" t="n">
-        <v>5.081224995439359</v>
+        <v>5.081224995439372</v>
       </c>
       <c r="P8" t="n">
-        <v>6.520744113945131</v>
+        <v>6.520744113945126</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.555417563104355</v>
+        <v>2.555417563104347</v>
       </c>
       <c r="R8" t="n">
-        <v>3.187276870543657</v>
+        <v>3.187276870543651</v>
       </c>
       <c r="S8" t="n">
-        <v>4.590869442780486</v>
+        <v>4.590869442780485</v>
       </c>
       <c r="T8" t="n">
-        <v>4.400707990708895</v>
+        <v>4.400707990708891</v>
       </c>
       <c r="U8" t="n">
-        <v>4.553730037548329</v>
+        <v>4.553730037548331</v>
       </c>
       <c r="V8" t="n">
-        <v>4.155687875934071</v>
+        <v>4.155687875934069</v>
       </c>
       <c r="W8" t="n">
-        <v>5.669002741926517</v>
+        <v>5.669002741926525</v>
       </c>
       <c r="X8" t="n">
-        <v>6.16533825395098</v>
+        <v>6.165338253950986</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.974860147363749</v>
+        <v>6.974860147363751</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.623798309066377</v>
+        <v>2.62379830906638</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.919517181701302</v>
+        <v>5.919517181701304</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.001870283305978</v>
+        <v>6.00187028330599</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.480306295189994</v>
+        <v>3.480306295189993</v>
       </c>
       <c r="C9" t="n">
-        <v>4.345565988007996</v>
+        <v>4.345565988008</v>
       </c>
       <c r="D9" t="n">
-        <v>4.650043861755713</v>
+        <v>4.650043861755704</v>
       </c>
       <c r="E9" t="n">
-        <v>4.011078988422938</v>
+        <v>4.011078988422953</v>
       </c>
       <c r="F9" t="n">
-        <v>3.899844307763738</v>
+        <v>3.899844307763732</v>
       </c>
       <c r="G9" t="n">
-        <v>5.21238460542116</v>
+        <v>5.212384605421158</v>
       </c>
       <c r="H9" t="n">
-        <v>5.848085799063733</v>
+        <v>5.848085799063734</v>
       </c>
       <c r="I9" t="n">
-        <v>4.848144857186305</v>
+        <v>4.848144857186304</v>
       </c>
       <c r="J9" t="n">
-        <v>5.445060808964561</v>
+        <v>5.445060808964564</v>
       </c>
       <c r="K9" t="n">
-        <v>4.854837324456473</v>
+        <v>4.854837324456481</v>
       </c>
       <c r="L9" t="n">
-        <v>4.440019401593995</v>
+        <v>4.440019401593993</v>
       </c>
       <c r="M9" t="n">
-        <v>5.39775439031783</v>
+        <v>5.397754390317833</v>
       </c>
       <c r="N9" t="n">
-        <v>6.092703843032763</v>
+        <v>6.092703843032767</v>
       </c>
       <c r="O9" t="n">
-        <v>6.960873915402086</v>
+        <v>6.960873915402088</v>
       </c>
       <c r="P9" t="n">
-        <v>8.485847930521729</v>
+        <v>8.485847930521743</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.665053499982857</v>
+        <v>4.665053499982863</v>
       </c>
       <c r="R9" t="n">
-        <v>4.444594897450713</v>
+        <v>4.444594897450728</v>
       </c>
       <c r="S9" t="n">
-        <v>5.848187469687561</v>
+        <v>5.848187469687566</v>
       </c>
       <c r="T9" t="n">
-        <v>5.658026017615972</v>
+        <v>5.658026017615974</v>
       </c>
       <c r="U9" t="n">
-        <v>6.162980145737148</v>
+        <v>6.162980145737157</v>
       </c>
       <c r="V9" t="n">
-        <v>6.38507220861134</v>
+        <v>6.385072208611373</v>
       </c>
       <c r="W9" t="n">
-        <v>6.926180776754366</v>
+        <v>6.926180776754373</v>
       </c>
       <c r="X9" t="n">
-        <v>8.209687708749829</v>
+        <v>8.209687708749827</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.531202866480974</v>
+        <v>7.53120286648097</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.202978226586741</v>
+        <v>4.202978226586737</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.176835208608372</v>
+        <v>7.176835208608374</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.515101211361438</v>
+        <v>6.51510121136144</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.50161198220552</v>
+        <v>39.50161198220548</v>
       </c>
       <c r="C2" t="n">
-        <v>42.31579442056723</v>
+        <v>42.31579442056726</v>
       </c>
       <c r="D2" t="n">
         <v>39.49937286404622</v>
       </c>
       <c r="E2" t="n">
-        <v>39.50271116731738</v>
+        <v>39.50271116731734</v>
       </c>
       <c r="F2" t="n">
-        <v>39.43872113188697</v>
+        <v>39.43872113188691</v>
       </c>
       <c r="G2" t="n">
         <v>39.69589858493077</v>
       </c>
       <c r="H2" t="n">
-        <v>39.63050250492768</v>
+        <v>39.6305025049277</v>
       </c>
       <c r="I2" t="n">
-        <v>39.48405581143469</v>
+        <v>39.48405581143466</v>
       </c>
       <c r="J2" t="n">
-        <v>39.68529924066127</v>
+        <v>39.68529924066124</v>
       </c>
       <c r="K2" t="n">
-        <v>39.54161586553933</v>
+        <v>39.54161586553931</v>
       </c>
       <c r="L2" t="n">
-        <v>39.70869067461381</v>
+        <v>39.70869067461378</v>
       </c>
       <c r="M2" t="n">
-        <v>39.93673003181978</v>
+        <v>39.93673003181979</v>
       </c>
       <c r="N2" t="n">
-        <v>39.67136226013366</v>
+        <v>39.67136226013364</v>
       </c>
       <c r="O2" t="n">
-        <v>43.69262320170546</v>
+        <v>43.69262320170547</v>
       </c>
       <c r="P2" t="n">
-        <v>39.79529959856451</v>
+        <v>39.79529959856449</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.54218817462006</v>
+        <v>39.54218817462007</v>
       </c>
       <c r="R2" t="n">
-        <v>39.52555542170035</v>
+        <v>39.52555542170033</v>
       </c>
       <c r="S2" t="n">
-        <v>39.58878485052997</v>
+        <v>39.58878485052995</v>
       </c>
       <c r="T2" t="n">
-        <v>39.55630276920878</v>
+        <v>39.55630276920873</v>
       </c>
       <c r="U2" t="n">
-        <v>43.32606280497718</v>
+        <v>43.32606280497719</v>
       </c>
       <c r="V2" t="n">
-        <v>39.63799019691508</v>
+        <v>39.6379901969151</v>
       </c>
       <c r="W2" t="n">
-        <v>45.99177893188413</v>
+        <v>45.99177893188414</v>
       </c>
       <c r="X2" t="n">
         <v>39.63327164810089</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.94560221663026</v>
+        <v>39.94560221663027</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.9584508168991</v>
+        <v>40.95845081689911</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.59232789510211</v>
+        <v>39.59232789510214</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.92976901715325</v>
+        <v>39.92976901715327</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.23583548145214</v>
+        <v>40.2876928885891</v>
       </c>
       <c r="C3" t="n">
-        <v>44.10135044444488</v>
+        <v>44.11744372677872</v>
       </c>
       <c r="D3" t="n">
-        <v>40.23049284379376</v>
+        <v>40.28256400418926</v>
       </c>
       <c r="E3" t="n">
-        <v>40.24958079296952</v>
+        <v>40.30198849687172</v>
       </c>
       <c r="F3" t="n">
-        <v>39.79589267948668</v>
+        <v>39.83273276111571</v>
       </c>
       <c r="G3" t="n">
-        <v>41.61442861533892</v>
+        <v>41.71491773647937</v>
       </c>
       <c r="H3" t="n">
-        <v>41.17424554904789</v>
+        <v>41.26018263454409</v>
       </c>
       <c r="I3" t="n">
-        <v>40.12091736366095</v>
+        <v>40.16918582183413</v>
       </c>
       <c r="J3" t="n">
-        <v>41.54507370092665</v>
+        <v>41.64342308290877</v>
       </c>
       <c r="K3" t="n">
-        <v>40.52292608171629</v>
+        <v>40.58563808792589</v>
       </c>
       <c r="L3" t="n">
-        <v>41.71408100572784</v>
+        <v>41.81835642585462</v>
       </c>
       <c r="M3" t="n">
-        <v>43.33518960710888</v>
+        <v>43.49861611934784</v>
       </c>
       <c r="N3" t="n">
-        <v>41.45697988186407</v>
+        <v>41.55233022808011</v>
       </c>
       <c r="O3" t="n">
-        <v>48.0425109997331</v>
+        <v>48.13517538171416</v>
       </c>
       <c r="P3" t="n">
-        <v>42.32672131967634</v>
+        <v>42.45176483203726</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.53206889628159</v>
+        <v>40.59485670221273</v>
       </c>
       <c r="R3" t="n">
-        <v>40.42028146602846</v>
+        <v>40.47922635402565</v>
       </c>
       <c r="S3" t="n">
-        <v>40.85222158725237</v>
+        <v>40.92609692778093</v>
       </c>
       <c r="T3" t="n">
-        <v>40.63780560346162</v>
+        <v>40.70437455624945</v>
       </c>
       <c r="U3" t="n">
-        <v>48.06288573934397</v>
+        <v>48.18435462098865</v>
       </c>
       <c r="V3" t="n">
-        <v>41.20242909498172</v>
+        <v>41.28852356916565</v>
       </c>
       <c r="W3" t="n">
-        <v>53.41549072243973</v>
+        <v>53.58070447141183</v>
       </c>
       <c r="X3" t="n">
-        <v>41.18640744070219</v>
+        <v>41.27239971566848</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.4087446252339</v>
+        <v>43.57316170126413</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.47338547490005</v>
+        <v>43.56347320393159</v>
       </c>
       <c r="AA3" t="n">
-        <v>40.88991874506595</v>
+        <v>40.96509845179933</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.30310449751923</v>
+        <v>43.46371832737399</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.845406853363641</v>
+        <v>3.845406853363588</v>
       </c>
       <c r="C4" t="n">
-        <v>2.220515250675768</v>
+        <v>2.220515250675771</v>
       </c>
       <c r="D4" t="n">
-        <v>3.820114983709513</v>
+        <v>3.8201149837095</v>
       </c>
       <c r="E4" t="n">
-        <v>3.857822654852331</v>
+        <v>3.85782265485232</v>
       </c>
       <c r="F4" t="n">
-        <v>3.135025767795646</v>
+        <v>3.135025767795639</v>
       </c>
       <c r="G4" t="n">
-        <v>6.03996340739857</v>
+        <v>6.039963407398578</v>
       </c>
       <c r="H4" t="n">
-        <v>5.301284600080431</v>
+        <v>5.301284600080405</v>
       </c>
       <c r="I4" t="n">
-        <v>3.647101828269578</v>
+        <v>3.647101828269581</v>
       </c>
       <c r="J4" t="n">
-        <v>5.920941186367607</v>
+        <v>5.920941186367584</v>
       </c>
       <c r="K4" t="n">
-        <v>4.297269118314722</v>
+        <v>4.297269118314718</v>
       </c>
       <c r="L4" t="n">
-        <v>6.184455945020431</v>
+        <v>6.184455945020298</v>
       </c>
       <c r="M4" t="n">
-        <v>8.746045268676991</v>
+        <v>8.746045268676994</v>
       </c>
       <c r="N4" t="n">
         <v>5.76281433154783</v>
       </c>
       <c r="O4" t="n">
-        <v>5.693410042088381</v>
+        <v>5.693410042088384</v>
       </c>
       <c r="P4" t="n">
-        <v>7.162743583116864</v>
+        <v>7.162743583116842</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.30373361265665</v>
+        <v>4.303733612656631</v>
       </c>
       <c r="R4" t="n">
-        <v>4.115859016984149</v>
+        <v>4.115859016984152</v>
       </c>
       <c r="S4" t="n">
-        <v>4.830064502589005</v>
+        <v>4.830064502589008</v>
       </c>
       <c r="T4" t="n">
-        <v>4.463164451570476</v>
+        <v>4.463164451570472</v>
       </c>
       <c r="U4" t="n">
-        <v>6.954388735837731</v>
+        <v>6.954388735837727</v>
       </c>
       <c r="V4" t="n">
-        <v>5.390293861797739</v>
+        <v>5.39029386179774</v>
       </c>
       <c r="W4" t="n">
-        <v>8.907952153003142</v>
+        <v>8.907952153003134</v>
       </c>
       <c r="X4" t="n">
-        <v>5.332563346091012</v>
+        <v>5.332563346090981</v>
       </c>
       <c r="Y4" t="n">
         <v>8.853178416227172</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.568121405801566</v>
+        <v>5.56812140580155</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.870084820912655</v>
+        <v>4.87008482091264</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.646594949655574</v>
+        <v>8.646594949655579</v>
       </c>
     </row>
     <row r="5">
@@ -7730,37 +7730,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.68654123971744</v>
+        <v>40.68654123971691</v>
       </c>
       <c r="C5" t="n">
-        <v>13.80549844943336</v>
+        <v>13.80549844943339</v>
       </c>
       <c r="D5" t="n">
-        <v>46.12470615669341</v>
+        <v>46.12470615669322</v>
       </c>
       <c r="E5" t="n">
-        <v>44.20280352406026</v>
+        <v>44.20280352406017</v>
       </c>
       <c r="F5" t="n">
-        <v>32.21133701520109</v>
+        <v>32.21133701520105</v>
       </c>
       <c r="G5" t="n">
-        <v>77.70952324437798</v>
+        <v>77.709523244378</v>
       </c>
       <c r="H5" t="n">
-        <v>78.5096188350587</v>
+        <v>78.50961883505902</v>
       </c>
       <c r="I5" t="n">
-        <v>42.71050771508791</v>
+        <v>42.71050771508792</v>
       </c>
       <c r="J5" t="n">
-        <v>78.94642732276844</v>
+        <v>78.94642732276836</v>
       </c>
       <c r="K5" t="n">
-        <v>50.10952568424191</v>
+        <v>50.10952568424192</v>
       </c>
       <c r="L5" t="n">
-        <v>85.08800873924966</v>
+        <v>85.08800873924767</v>
       </c>
       <c r="M5" t="n">
         <v>134.2488616136515</v>
@@ -7769,46 +7769,46 @@
         <v>82.2954463264056</v>
       </c>
       <c r="O5" t="n">
-        <v>70.64674414232996</v>
+        <v>70.64674414232999</v>
       </c>
       <c r="P5" t="n">
-        <v>100.5310488148327</v>
+        <v>100.5310488148328</v>
       </c>
       <c r="Q5" t="n">
-        <v>53.04489401416037</v>
+        <v>53.04489401416015</v>
       </c>
       <c r="R5" t="n">
-        <v>53.34190710855658</v>
+        <v>53.34190710855696</v>
       </c>
       <c r="S5" t="n">
-        <v>56.09479874762742</v>
+        <v>56.09479874762719</v>
       </c>
       <c r="T5" t="n">
-        <v>58.84023730228802</v>
+        <v>58.84023730228785</v>
       </c>
       <c r="U5" t="n">
-        <v>99.8872292014987</v>
+        <v>99.88722920149867</v>
       </c>
       <c r="V5" t="n">
-        <v>66.0667725696789</v>
+        <v>66.06677256967905</v>
       </c>
       <c r="W5" t="n">
-        <v>140.5774392600341</v>
+        <v>140.5774392600339</v>
       </c>
       <c r="X5" t="n">
-        <v>74.87337561874631</v>
+        <v>74.87337561874618</v>
       </c>
       <c r="Y5" t="n">
-        <v>137.8072701017039</v>
+        <v>137.8072701017038</v>
       </c>
       <c r="Z5" t="n">
-        <v>71.04800801837763</v>
+        <v>71.04800801837705</v>
       </c>
       <c r="AA5" t="n">
-        <v>63.75349986438302</v>
+        <v>63.75349986438292</v>
       </c>
       <c r="AB5" t="n">
-        <v>148.4464128117448</v>
+        <v>148.4464128117446</v>
       </c>
     </row>
     <row r="6">
@@ -7824,40 +7824,40 @@
         <v>121.7204979177036</v>
       </c>
       <c r="D6" t="n">
-        <v>123.3200976507373</v>
+        <v>123.3200976507375</v>
       </c>
       <c r="E6" t="n">
-        <v>147.1729939398813</v>
+        <v>147.1729939398812</v>
       </c>
       <c r="F6" t="n">
-        <v>122.6350084348234</v>
+        <v>122.6350084348235</v>
       </c>
       <c r="G6" t="n">
         <v>149.3551346924274</v>
       </c>
       <c r="H6" t="n">
-        <v>124.8012672671081</v>
+        <v>124.8012672671084</v>
       </c>
       <c r="I6" t="n">
-        <v>123.1470844952973</v>
+        <v>123.1470844952975</v>
       </c>
       <c r="J6" t="n">
-        <v>125.4209238533954</v>
+        <v>125.4209238533955</v>
       </c>
       <c r="K6" t="n">
-        <v>147.6124404033436</v>
+        <v>147.6124404033435</v>
       </c>
       <c r="L6" t="n">
-        <v>149.4996272300493</v>
+        <v>149.4996272300491</v>
       </c>
       <c r="M6" t="n">
-        <v>128.2460279357047</v>
+        <v>128.2460279357049</v>
       </c>
       <c r="N6" t="n">
-        <v>125.2720374782842</v>
+        <v>125.2720374782841</v>
       </c>
       <c r="O6" t="n">
-        <v>149.0728994979742</v>
+        <v>149.0728994979743</v>
       </c>
       <c r="P6" t="n">
         <v>150.5419444011589</v>
@@ -7869,22 +7869,22 @@
         <v>147.431030302013</v>
       </c>
       <c r="S6" t="n">
-        <v>124.3300471696168</v>
+        <v>124.3300471696169</v>
       </c>
       <c r="T6" t="n">
-        <v>123.9631471185982</v>
+        <v>123.9631471185984</v>
       </c>
       <c r="U6" t="n">
         <v>150.2768624014292</v>
       </c>
       <c r="V6" t="n">
-        <v>124.8902765288256</v>
+        <v>124.8902765288257</v>
       </c>
       <c r="W6" t="n">
-        <v>134.5287220661517</v>
+        <v>134.5287220661518</v>
       </c>
       <c r="X6" t="n">
-        <v>148.6477346311199</v>
+        <v>148.6477346311198</v>
       </c>
       <c r="Y6" t="n">
         <v>133.6142541282171</v>
@@ -7893,7 +7893,7 @@
         <v>148.8832926908305</v>
       </c>
       <c r="AA6" t="n">
-        <v>148.1852561059415</v>
+        <v>148.1852561059414</v>
       </c>
       <c r="AB6" t="n">
         <v>128.1757216985619</v>
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.98095906908649</v>
+        <v>4.980959069086447</v>
       </c>
       <c r="C7" t="n">
-        <v>3.35606746639861</v>
+        <v>3.356067466398619</v>
       </c>
       <c r="D7" t="n">
         <v>4.955667199432368</v>
       </c>
       <c r="E7" t="n">
-        <v>4.993374870575179</v>
+        <v>4.993374870575163</v>
       </c>
       <c r="F7" t="n">
-        <v>4.270577983518491</v>
+        <v>4.270577983518492</v>
       </c>
       <c r="G7" t="n">
-        <v>7.175515623121424</v>
+        <v>7.175515623121425</v>
       </c>
       <c r="H7" t="n">
-        <v>6.436836815803272</v>
+        <v>6.436836815803254</v>
       </c>
       <c r="I7" t="n">
-        <v>4.782654043992426</v>
+        <v>4.782654043992425</v>
       </c>
       <c r="J7" t="n">
-        <v>7.056493402090453</v>
+        <v>7.056493402090428</v>
       </c>
       <c r="K7" t="n">
-        <v>5.432821334037573</v>
+        <v>5.432821334037563</v>
       </c>
       <c r="L7" t="n">
-        <v>7.320008160743281</v>
+        <v>7.32000816074308</v>
       </c>
       <c r="M7" t="n">
-        <v>9.881597484399844</v>
+        <v>9.881597484399842</v>
       </c>
       <c r="N7" t="n">
-        <v>6.898366547270685</v>
+        <v>6.89836654727067</v>
       </c>
       <c r="O7" t="n">
-        <v>6.828951694173324</v>
+        <v>6.828951694173318</v>
       </c>
       <c r="P7" t="n">
-        <v>8.298285235201822</v>
+        <v>8.298285235201782</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.439285828379491</v>
+        <v>5.43928582837947</v>
       </c>
       <c r="R7" t="n">
-        <v>5.251411232706992</v>
+        <v>5.251411232706996</v>
       </c>
       <c r="S7" t="n">
         <v>5.965616718311853</v>
       </c>
       <c r="T7" t="n">
-        <v>5.598716667293317</v>
+        <v>5.598716667293319</v>
       </c>
       <c r="U7" t="n">
-        <v>8.096287813336371</v>
+        <v>8.096287813336357</v>
       </c>
       <c r="V7" t="n">
-        <v>6.525846077520585</v>
+        <v>6.52584607752058</v>
       </c>
       <c r="W7" t="n">
-        <v>10.04350436872599</v>
+        <v>10.04350436872598</v>
       </c>
       <c r="X7" t="n">
-        <v>6.468115561813854</v>
+        <v>6.46811556181382</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.996033012512704</v>
+        <v>9.996033012512699</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.703673621524409</v>
+        <v>6.703673621524404</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.005637036635507</v>
+        <v>6.005637036635494</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.78214716537842</v>
+        <v>9.782147165378426</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.421883819504566</v>
+        <v>5.42188381950451</v>
       </c>
       <c r="C8" t="n">
-        <v>4.989555372012898</v>
+        <v>4.989555372012888</v>
       </c>
       <c r="D8" t="n">
-        <v>6.589155105046625</v>
+        <v>6.589155105046618</v>
       </c>
       <c r="E8" t="n">
-        <v>5.991858074813727</v>
+        <v>5.991858074813713</v>
       </c>
       <c r="F8" t="n">
-        <v>4.897290135530701</v>
+        <v>4.897290135530692</v>
       </c>
       <c r="G8" t="n">
-        <v>9.0562892676557</v>
+        <v>9.056289267655723</v>
       </c>
       <c r="H8" t="n">
-        <v>8.07032472141753</v>
+        <v>8.070324721417524</v>
       </c>
       <c r="I8" t="n">
-        <v>6.416141949606711</v>
+        <v>6.416141949606697</v>
       </c>
       <c r="J8" t="n">
-        <v>8.68998130770472</v>
+        <v>8.689981307704713</v>
       </c>
       <c r="K8" t="n">
-        <v>7.066309239651847</v>
+        <v>7.066309239651835</v>
       </c>
       <c r="L8" t="n">
-        <v>8.95349606635755</v>
+        <v>8.953496066357447</v>
       </c>
       <c r="M8" t="n">
-        <v>11.51508539001502</v>
+        <v>11.51508539001501</v>
       </c>
       <c r="N8" t="n">
-        <v>7.607418495682989</v>
+        <v>7.607418495682976</v>
       </c>
       <c r="O8" t="n">
-        <v>7.792057233090911</v>
+        <v>7.792057233090896</v>
       </c>
       <c r="P8" t="n">
-        <v>9.199118689791167</v>
+        <v>9.19911868979117</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.645844700354006</v>
+        <v>5.645844700353994</v>
       </c>
       <c r="R8" t="n">
-        <v>6.884899138321268</v>
+        <v>6.884899138321257</v>
       </c>
       <c r="S8" t="n">
         <v>7.599104623926131</v>
       </c>
       <c r="T8" t="n">
-        <v>7.232204572907602</v>
+        <v>7.232204572907588</v>
       </c>
       <c r="U8" t="n">
         <v>9.147924760550673</v>
       </c>
       <c r="V8" t="n">
-        <v>7.832580765835655</v>
+        <v>7.832580765835649</v>
       </c>
       <c r="W8" t="n">
         <v>11.67722664540335</v>
       </c>
       <c r="X8" t="n">
-        <v>6.783975215533515</v>
+        <v>6.783975215533485</v>
       </c>
       <c r="Y8" t="n">
         <v>12.81400653696415</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.122445899224899</v>
+        <v>7.122445899224877</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.63912494224977</v>
+        <v>7.639124942249749</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.66136700545767</v>
+        <v>12.66136700545765</v>
       </c>
     </row>
     <row r="9">
@@ -8082,82 +8082,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.086674170380393</v>
+        <v>8.086674170380341</v>
       </c>
       <c r="C9" t="n">
-        <v>7.71781116801345</v>
+        <v>7.717811168013449</v>
       </c>
       <c r="D9" t="n">
-        <v>9.317410901047197</v>
+        <v>9.317410901047218</v>
       </c>
       <c r="E9" t="n">
-        <v>9.065232336798962</v>
+        <v>9.065232336798939</v>
       </c>
       <c r="F9" t="n">
-        <v>5.736832886858974</v>
+        <v>5.73683288685895</v>
       </c>
       <c r="G9" t="n">
-        <v>11.53725937974847</v>
+        <v>11.53725937974845</v>
       </c>
       <c r="H9" t="n">
-        <v>10.7985805174181</v>
+        <v>10.79858051741808</v>
       </c>
       <c r="I9" t="n">
-        <v>9.144397745607259</v>
+        <v>9.144397745607245</v>
       </c>
       <c r="J9" t="n">
         <v>11.41823710370527</v>
       </c>
       <c r="K9" t="n">
-        <v>9.794565035652409</v>
+        <v>9.794565035652404</v>
       </c>
       <c r="L9" t="n">
-        <v>11.68175186235812</v>
+        <v>11.6817518623579</v>
       </c>
       <c r="M9" t="n">
-        <v>14.24334118601468</v>
+        <v>14.24334118601466</v>
       </c>
       <c r="N9" t="n">
-        <v>11.26011024888551</v>
+        <v>11.26011024888549</v>
       </c>
       <c r="O9" t="n">
         <v>11.60695226618652</v>
       </c>
       <c r="P9" t="n">
-        <v>13.16681222538732</v>
+        <v>13.16681222538729</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.801029585006543</v>
+        <v>9.801029585006514</v>
       </c>
       <c r="R9" t="n">
-        <v>9.613154934321836</v>
+        <v>9.613154934321809</v>
       </c>
       <c r="S9" t="n">
-        <v>10.32736041992669</v>
+        <v>10.32736041992668</v>
       </c>
       <c r="T9" t="n">
-        <v>9.960460368908148</v>
+        <v>9.960460368908127</v>
       </c>
       <c r="U9" t="n">
-        <v>12.45898703373811</v>
+        <v>12.4589870337381</v>
       </c>
       <c r="V9" t="n">
-        <v>12.33701830124237</v>
+        <v>12.33701830124238</v>
       </c>
       <c r="W9" t="n">
-        <v>14.40524807034082</v>
+        <v>14.40524807034081</v>
       </c>
       <c r="X9" t="n">
-        <v>10.82985926342869</v>
+        <v>10.82985926342863</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.35777671412754</v>
+        <v>14.35777671412758</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.3081437894115</v>
+        <v>10.30814378941147</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.36738073825033</v>
+        <v>10.36738073825032</v>
       </c>
       <c r="AB9" t="n">
         <v>14.14389086699326</v>
@@ -8326,46 +8326,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.0187125081626</v>
+        <v>39.01871250816259</v>
       </c>
       <c r="C2" t="n">
-        <v>41.99062466853402</v>
+        <v>41.99062466853401</v>
       </c>
       <c r="D2" t="n">
-        <v>39.07371954467347</v>
+        <v>39.07371954467345</v>
       </c>
       <c r="E2" t="n">
-        <v>39.10777567048267</v>
+        <v>39.10777567048262</v>
       </c>
       <c r="F2" t="n">
-        <v>39.0853011591717</v>
+        <v>39.08530115917169</v>
       </c>
       <c r="G2" t="n">
-        <v>39.33963741891905</v>
+        <v>39.33963741891903</v>
       </c>
       <c r="H2" t="n">
-        <v>39.26580842576393</v>
+        <v>39.26580842576391</v>
       </c>
       <c r="I2" t="n">
-        <v>39.06043877234021</v>
+        <v>39.06043877234018</v>
       </c>
       <c r="J2" t="n">
-        <v>39.24725053690528</v>
+        <v>39.24725053690531</v>
       </c>
       <c r="K2" t="n">
-        <v>39.13657750226416</v>
+        <v>39.13657750226415</v>
       </c>
       <c r="L2" t="n">
-        <v>39.13901068381963</v>
+        <v>39.13901068381962</v>
       </c>
       <c r="M2" t="n">
         <v>39.23524961666045</v>
       </c>
       <c r="N2" t="n">
-        <v>39.25625326713715</v>
+        <v>39.25625326713717</v>
       </c>
       <c r="O2" t="n">
-        <v>43.15143214350103</v>
+        <v>43.15143214350107</v>
       </c>
       <c r="P2" t="n">
         <v>39.4300247180154</v>
@@ -8374,7 +8374,7 @@
         <v>39.12447186213479</v>
       </c>
       <c r="R2" t="n">
-        <v>39.074729819901</v>
+        <v>39.07472981990102</v>
       </c>
       <c r="S2" t="n">
         <v>39.12821440292539</v>
@@ -8383,28 +8383,28 @@
         <v>39.16531301169723</v>
       </c>
       <c r="U2" t="n">
-        <v>42.68781274326759</v>
+        <v>42.68781274326762</v>
       </c>
       <c r="V2" t="n">
-        <v>39.21176700222461</v>
+        <v>39.2117670022246</v>
       </c>
       <c r="W2" t="n">
-        <v>45.40451697426484</v>
+        <v>45.40451697426487</v>
       </c>
       <c r="X2" t="n">
         <v>39.34147841588953</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.60034607702796</v>
+        <v>39.60034607702794</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.29326346021569</v>
+        <v>40.29326346021568</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.18586238635397</v>
+        <v>39.18586238635399</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.48440145327064</v>
+        <v>39.48440145327065</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.74777594954757</v>
+        <v>38.75535258159161</v>
       </c>
       <c r="C3" t="n">
-        <v>43.78631752654078</v>
+        <v>43.80004883210559</v>
       </c>
       <c r="D3" t="n">
-        <v>39.14170253941413</v>
+        <v>39.16334442758865</v>
       </c>
       <c r="E3" t="n">
-        <v>39.38376258512962</v>
+        <v>39.41374989671581</v>
       </c>
       <c r="F3" t="n">
-        <v>39.22452036935286</v>
+        <v>39.24921702619869</v>
       </c>
       <c r="G3" t="n">
-        <v>41.02132524289379</v>
+        <v>41.10918981444478</v>
       </c>
       <c r="H3" t="n">
-        <v>40.52274674174684</v>
+        <v>40.59363611836631</v>
       </c>
       <c r="I3" t="n">
-        <v>39.04767757880217</v>
+        <v>39.06597862857644</v>
       </c>
       <c r="J3" t="n">
-        <v>40.37191703642478</v>
+        <v>40.43699630067492</v>
       </c>
       <c r="K3" t="n">
-        <v>39.58555040327733</v>
+        <v>39.62310308114754</v>
       </c>
       <c r="L3" t="n">
-        <v>39.60199944214133</v>
+        <v>39.63988289363628</v>
       </c>
       <c r="M3" t="n">
-        <v>40.2951258763574</v>
+        <v>40.35821377812643</v>
       </c>
       <c r="N3" t="n">
-        <v>40.44619355861509</v>
+        <v>40.51390719983003</v>
       </c>
       <c r="O3" t="n">
-        <v>47.14559291759005</v>
+        <v>47.22553688791123</v>
       </c>
       <c r="P3" t="n">
-        <v>41.66967258196713</v>
+        <v>41.77987307683051</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.5000175852224</v>
+        <v>39.53446291460379</v>
       </c>
       <c r="R3" t="n">
-        <v>39.1505631697971</v>
+        <v>39.17254274894896</v>
       </c>
       <c r="S3" t="n">
-        <v>39.52399591223465</v>
+        <v>39.55905492706219</v>
       </c>
       <c r="T3" t="n">
-        <v>39.79733477634767</v>
+        <v>39.84226342913849</v>
       </c>
       <c r="U3" t="n">
-        <v>46.12491588194153</v>
+        <v>46.19340217856685</v>
       </c>
       <c r="V3" t="n">
-        <v>40.11664025745112</v>
+        <v>40.17257570685127</v>
       </c>
       <c r="W3" t="n">
-        <v>51.92983134334995</v>
+        <v>52.05871187065684</v>
       </c>
       <c r="X3" t="n">
-        <v>41.05221252790591</v>
+        <v>41.14176390505195</v>
       </c>
       <c r="Y3" t="n">
-        <v>42.89792710907309</v>
+        <v>43.05238743707029</v>
       </c>
       <c r="Z3" t="n">
-        <v>41.5570542253121</v>
+        <v>41.59711031947275</v>
       </c>
       <c r="AA3" t="n">
-        <v>39.94167000696316</v>
+        <v>39.99146166181088</v>
       </c>
       <c r="AB3" t="n">
-        <v>42.06362087464249</v>
+        <v>42.18865194526651</v>
       </c>
     </row>
     <row r="4">
@@ -8505,82 +8505,82 @@
         <v>1.557468059291157</v>
       </c>
       <c r="C4" t="n">
-        <v>1.827563435435186</v>
+        <v>1.827563435435184</v>
       </c>
       <c r="D4" t="n">
-        <v>2.178797841168372</v>
+        <v>2.178797841168366</v>
       </c>
       <c r="E4" t="n">
-        <v>2.563477448774701</v>
+        <v>2.5634774487747</v>
       </c>
       <c r="F4" t="n">
-        <v>2.309617504731642</v>
+        <v>2.309617504731653</v>
       </c>
       <c r="G4" t="n">
-        <v>5.18246255903791</v>
+        <v>5.182462559037917</v>
       </c>
       <c r="H4" t="n">
-        <v>4.348530118336388</v>
+        <v>4.34853011833639</v>
       </c>
       <c r="I4" t="n">
-        <v>2.028785408206974</v>
+        <v>2.028785408206972</v>
       </c>
       <c r="J4" t="n">
-        <v>4.139469767718275</v>
+        <v>4.139469767718277</v>
       </c>
       <c r="K4" t="n">
-        <v>2.888807388244395</v>
+        <v>2.888807388244385</v>
       </c>
       <c r="L4" t="n">
-        <v>2.916291293232392</v>
+        <v>2.916291293232388</v>
       </c>
       <c r="M4" t="n">
-        <v>4.011945298599658</v>
+        <v>4.011945298599657</v>
       </c>
       <c r="N4" t="n">
-        <v>4.240600206056565</v>
+        <v>4.24060020605657</v>
       </c>
       <c r="O4" t="n">
-        <v>4.830670144207092</v>
+        <v>4.830670144207103</v>
       </c>
       <c r="P4" t="n">
-        <v>6.203428682542993</v>
+        <v>6.203428682542997</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75206861411376</v>
+        <v>2.752068614113768</v>
       </c>
       <c r="R4" t="n">
-        <v>2.190209364613127</v>
+        <v>2.190209364613121</v>
       </c>
       <c r="S4" t="n">
-        <v>2.794342333997283</v>
+        <v>2.794342333997274</v>
       </c>
       <c r="T4" t="n">
-        <v>3.213388186278484</v>
+        <v>3.21338818627848</v>
       </c>
       <c r="U4" t="n">
-        <v>4.270697422438682</v>
+        <v>4.270697422438691</v>
       </c>
       <c r="V4" t="n">
-        <v>3.74153976634125</v>
+        <v>3.741539766341247</v>
       </c>
       <c r="W4" t="n">
-        <v>6.991915564715131</v>
+        <v>6.991915564715122</v>
       </c>
       <c r="X4" t="n">
-        <v>5.203257466719892</v>
+        <v>5.203257466719912</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.104817807344956</v>
+        <v>8.104817807344954</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.022856706839824</v>
+        <v>3.022856706839819</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.445502826205694</v>
+        <v>3.445502826205693</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.776402166398481</v>
+        <v>6.776402166398487</v>
       </c>
     </row>
     <row r="5">
@@ -8590,49 +8590,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.893835980786638</v>
+        <v>5.893835980786628</v>
       </c>
       <c r="C5" t="n">
         <v>10.96118837917714</v>
       </c>
       <c r="D5" t="n">
-        <v>17.57678855422574</v>
+        <v>17.57678855422573</v>
       </c>
       <c r="E5" t="n">
-        <v>23.86214248900789</v>
+        <v>23.86214248900791</v>
       </c>
       <c r="F5" t="n">
-        <v>19.97308776589713</v>
+        <v>19.97308776589712</v>
       </c>
       <c r="G5" t="n">
-        <v>61.24580960465173</v>
+        <v>61.24580960465164</v>
       </c>
       <c r="H5" t="n">
-        <v>61.18422669648348</v>
+        <v>61.18422669648346</v>
       </c>
       <c r="I5" t="n">
         <v>15.31771914766339</v>
       </c>
       <c r="J5" t="n">
-        <v>47.95175873081081</v>
+        <v>47.95175873081077</v>
       </c>
       <c r="K5" t="n">
-        <v>27.66124496265175</v>
+        <v>27.66124496265171</v>
       </c>
       <c r="L5" t="n">
-        <v>27.67228702861029</v>
+        <v>27.67228702861038</v>
       </c>
       <c r="M5" t="n">
-        <v>47.87819448533456</v>
+        <v>47.87819448533459</v>
       </c>
       <c r="N5" t="n">
-        <v>54.94422479630336</v>
+        <v>54.94422479630322</v>
       </c>
       <c r="O5" t="n">
-        <v>56.6164261974714</v>
+        <v>56.61642619747145</v>
       </c>
       <c r="P5" t="n">
-        <v>80.98682608218822</v>
+        <v>80.98682608218814</v>
       </c>
       <c r="Q5" t="n">
         <v>25.69144143946107</v>
@@ -8641,34 +8641,34 @@
         <v>18.63381823344134</v>
       </c>
       <c r="S5" t="n">
-        <v>25.02313872002179</v>
+        <v>25.02313872002181</v>
       </c>
       <c r="T5" t="n">
-        <v>36.87285861911097</v>
+        <v>36.87285861911114</v>
       </c>
       <c r="U5" t="n">
-        <v>50.06866874284655</v>
+        <v>50.06866874284667</v>
       </c>
       <c r="V5" t="n">
-        <v>39.81428203785302</v>
+        <v>39.81428203785299</v>
       </c>
       <c r="W5" t="n">
-        <v>102.8023634016107</v>
+        <v>102.8023634016106</v>
       </c>
       <c r="X5" t="n">
-        <v>70.81105233405194</v>
+        <v>70.81105233405198</v>
       </c>
       <c r="Y5" t="n">
-        <v>121.5754496476911</v>
+        <v>121.575449647691</v>
       </c>
       <c r="Z5" t="n">
-        <v>28.51488006632844</v>
+        <v>28.51488006632845</v>
       </c>
       <c r="AA5" t="n">
-        <v>39.77244567059363</v>
+        <v>39.7724456705936</v>
       </c>
       <c r="AB5" t="n">
-        <v>105.7676913237886</v>
+        <v>105.7676913237887</v>
       </c>
     </row>
     <row r="6">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.8467363179406</v>
+        <v>134.8467363179407</v>
       </c>
       <c r="C6" t="n">
         <v>135.1168316940845</v>
@@ -8687,34 +8687,34 @@
         <v>135.4680660998178</v>
       </c>
       <c r="E6" t="n">
-        <v>113.8003250080538</v>
+        <v>113.8003250080537</v>
       </c>
       <c r="F6" t="n">
         <v>113.5464650640107</v>
       </c>
       <c r="G6" t="n">
-        <v>116.4193101183171</v>
+        <v>116.419310118317</v>
       </c>
       <c r="H6" t="n">
-        <v>115.5853776776155</v>
+        <v>115.5853776776154</v>
       </c>
       <c r="I6" t="n">
-        <v>135.3180536668565</v>
+        <v>135.3180536668564</v>
       </c>
       <c r="J6" t="n">
         <v>137.4287380263677</v>
       </c>
       <c r="K6" t="n">
-        <v>114.1256549475235</v>
+        <v>114.1256549475234</v>
       </c>
       <c r="L6" t="n">
-        <v>136.2055595518819</v>
+        <v>136.2055595518818</v>
       </c>
       <c r="M6" t="n">
-        <v>115.2487928578788</v>
+        <v>115.2487928578787</v>
       </c>
       <c r="N6" t="n">
-        <v>115.4833210917824</v>
+        <v>115.4833210917823</v>
       </c>
       <c r="O6" t="n">
         <v>138.1828125638557</v>
@@ -8726,7 +8726,7 @@
         <v>113.9889161733929</v>
       </c>
       <c r="R6" t="n">
-        <v>135.4794776232626</v>
+        <v>135.4794776232625</v>
       </c>
       <c r="S6" t="n">
         <v>114.0311898932764</v>
@@ -8735,19 +8735,19 @@
         <v>114.4502357455576</v>
       </c>
       <c r="U6" t="n">
-        <v>137.5824346580295</v>
+        <v>137.5824346580294</v>
       </c>
       <c r="V6" t="n">
         <v>114.9783873256203</v>
       </c>
       <c r="W6" t="n">
-        <v>123.9213824398707</v>
+        <v>123.9213824398705</v>
       </c>
       <c r="X6" t="n">
         <v>138.4925257253693</v>
       </c>
       <c r="Y6" t="n">
-        <v>124.2499301702555</v>
+        <v>124.2499301702554</v>
       </c>
       <c r="Z6" t="n">
         <v>136.3121249654892</v>
@@ -8756,7 +8756,7 @@
         <v>114.6823503854848</v>
       </c>
       <c r="AB6" t="n">
-        <v>118.0379162478261</v>
+        <v>118.0379162478262</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.471284658119616</v>
+        <v>2.471284658119621</v>
       </c>
       <c r="C7" t="n">
-        <v>2.741380034263653</v>
+        <v>2.741380034263658</v>
       </c>
       <c r="D7" t="n">
-        <v>3.092614439996836</v>
+        <v>3.092614439996842</v>
       </c>
       <c r="E7" t="n">
-        <v>3.477294047603169</v>
+        <v>3.477294047603173</v>
       </c>
       <c r="F7" t="n">
-        <v>3.223434103560115</v>
+        <v>3.223434103560114</v>
       </c>
       <c r="G7" t="n">
-        <v>6.096279157866382</v>
+        <v>6.096279157866372</v>
       </c>
       <c r="H7" t="n">
-        <v>5.26234671716486</v>
+        <v>5.262346717164861</v>
       </c>
       <c r="I7" t="n">
-        <v>2.942602007035445</v>
+        <v>2.942602007035446</v>
       </c>
       <c r="J7" t="n">
-        <v>5.053286366546746</v>
+        <v>5.053286366546745</v>
       </c>
       <c r="K7" t="n">
-        <v>3.802623987072853</v>
+        <v>3.802623987072855</v>
       </c>
       <c r="L7" t="n">
-        <v>3.830107892060856</v>
+        <v>3.830107892060864</v>
       </c>
       <c r="M7" t="n">
-        <v>4.925761897428128</v>
+        <v>4.925761897428125</v>
       </c>
       <c r="N7" t="n">
-        <v>5.154416804885042</v>
+        <v>5.154416804885041</v>
       </c>
       <c r="O7" t="n">
-        <v>5.744481841614486</v>
+        <v>5.744481841614494</v>
       </c>
       <c r="P7" t="n">
-        <v>7.117240379950386</v>
+        <v>7.11724037995039</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.665885212942229</v>
+        <v>3.665885212942228</v>
       </c>
       <c r="R7" t="n">
-        <v>3.104025963441586</v>
+        <v>3.104025963441595</v>
       </c>
       <c r="S7" t="n">
-        <v>3.708158932825742</v>
+        <v>3.708158932825751</v>
       </c>
       <c r="T7" t="n">
-        <v>4.127204785106949</v>
+        <v>4.127204785106953</v>
       </c>
       <c r="U7" t="n">
-        <v>5.203148309684133</v>
+        <v>5.203148309684131</v>
       </c>
       <c r="V7" t="n">
-        <v>4.655356365169717</v>
+        <v>4.655356365169716</v>
       </c>
       <c r="W7" t="n">
-        <v>7.905732163543586</v>
+        <v>7.905732163543594</v>
       </c>
       <c r="X7" t="n">
-        <v>6.117074065548367</v>
+        <v>6.117074065548374</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.041103383114754</v>
+        <v>9.041103383114752</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.93667330566829</v>
+        <v>3.936673305668292</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.359319425034162</v>
+        <v>4.359319425034155</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.690218765226948</v>
+        <v>7.690218765226949</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.765179260551403</v>
+        <v>2.765179260551399</v>
       </c>
       <c r="C8" t="n">
-        <v>3.947169998737124</v>
+        <v>3.947169998737119</v>
       </c>
       <c r="D8" t="n">
-        <v>4.298404404470308</v>
+        <v>4.298404404470301</v>
       </c>
       <c r="E8" t="n">
-        <v>4.197526631286538</v>
+        <v>4.197526631286539</v>
       </c>
       <c r="F8" t="n">
-        <v>3.659391345700274</v>
+        <v>3.659391345700268</v>
       </c>
       <c r="G8" t="n">
-        <v>7.491156566004625</v>
+        <v>7.491156566004609</v>
       </c>
       <c r="H8" t="n">
-        <v>6.468136681638327</v>
+        <v>6.468136681638321</v>
       </c>
       <c r="I8" t="n">
-        <v>4.148391971508916</v>
+        <v>4.148391971508907</v>
       </c>
       <c r="J8" t="n">
         <v>6.25907633102021</v>
       </c>
       <c r="K8" t="n">
-        <v>5.008413951546324</v>
+        <v>5.008413951546316</v>
       </c>
       <c r="L8" t="n">
-        <v>5.035897856534325</v>
+        <v>5.035897856534321</v>
       </c>
       <c r="M8" t="n">
-        <v>6.131551861903075</v>
+        <v>6.131551861903079</v>
       </c>
       <c r="N8" t="n">
-        <v>5.653335306666338</v>
+        <v>5.653335306666339</v>
       </c>
       <c r="O8" t="n">
-        <v>6.437659659743441</v>
+        <v>6.437659659743444</v>
       </c>
       <c r="P8" t="n">
-        <v>7.762801747208059</v>
+        <v>7.762801747208055</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.780571564094848</v>
+        <v>3.78057156409485</v>
       </c>
       <c r="R8" t="n">
-        <v>4.309815927915062</v>
+        <v>4.309815927915055</v>
       </c>
       <c r="S8" t="n">
-        <v>4.913948897299218</v>
+        <v>4.913948897299212</v>
       </c>
       <c r="T8" t="n">
-        <v>5.332994749580418</v>
+        <v>5.332994749580414</v>
       </c>
       <c r="U8" t="n">
-        <v>5.964721015623345</v>
+        <v>5.964721015623338</v>
       </c>
       <c r="V8" t="n">
-        <v>5.608637969499948</v>
+        <v>5.608637969499946</v>
       </c>
       <c r="W8" t="n">
-        <v>9.111701340264849</v>
+        <v>9.111701340264844</v>
       </c>
       <c r="X8" t="n">
-        <v>6.315337437784333</v>
+        <v>6.315337437784347</v>
       </c>
       <c r="Y8" t="n">
         <v>11.14849278056514</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.213628983698382</v>
+        <v>4.21362898369838</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.565109389507629</v>
+        <v>5.565109389507632</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.848559685573521</v>
+        <v>9.848559685573512</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.658499571408434</v>
+        <v>4.658499571408438</v>
       </c>
       <c r="C9" t="n">
-        <v>5.849107617479237</v>
+        <v>5.84910761747923</v>
       </c>
       <c r="D9" t="n">
-        <v>6.200342023212416</v>
+        <v>6.200342023212411</v>
       </c>
       <c r="E9" t="n">
-        <v>6.37257134895455</v>
+        <v>6.372571348954553</v>
       </c>
       <c r="F9" t="n">
-        <v>4.209128262730345</v>
+        <v>4.209128262730351</v>
       </c>
       <c r="G9" t="n">
-        <v>9.204007115042661</v>
+        <v>9.20400711504265</v>
       </c>
       <c r="H9" t="n">
-        <v>8.370074300380438</v>
+        <v>8.370074300380434</v>
       </c>
       <c r="I9" t="n">
-        <v>6.050329590251029</v>
+        <v>6.050329590251018</v>
       </c>
       <c r="J9" t="n">
-        <v>8.161013949762316</v>
+        <v>8.161013949762323</v>
       </c>
       <c r="K9" t="n">
-        <v>6.910351570288437</v>
+        <v>6.910351570288431</v>
       </c>
       <c r="L9" t="n">
-        <v>6.937835475276431</v>
+        <v>6.937835475276441</v>
       </c>
       <c r="M9" t="n">
-        <v>8.033489480643704</v>
+        <v>8.033489480643709</v>
       </c>
       <c r="N9" t="n">
-        <v>8.262144388100603</v>
+        <v>8.262144388100621</v>
       </c>
       <c r="O9" t="n">
-        <v>9.15727151764713</v>
+        <v>9.157271517647152</v>
       </c>
       <c r="P9" t="n">
-        <v>10.59637467988171</v>
+        <v>10.59637467988173</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.773613170118503</v>
+        <v>6.773613170118502</v>
       </c>
       <c r="R9" t="n">
-        <v>6.211753546657172</v>
+        <v>6.211753546657167</v>
       </c>
       <c r="S9" t="n">
-        <v>6.815886516041322</v>
+        <v>6.815886516041326</v>
       </c>
       <c r="T9" t="n">
-        <v>7.234932368322527</v>
+        <v>7.234932368322528</v>
       </c>
       <c r="U9" t="n">
-        <v>8.314710581424061</v>
+        <v>8.314710581424062</v>
       </c>
       <c r="V9" t="n">
-        <v>8.825335750024292</v>
+        <v>8.825335750024308</v>
       </c>
       <c r="W9" t="n">
         <v>11.01345974675917</v>
       </c>
       <c r="X9" t="n">
-        <v>9.22480164876395</v>
+        <v>9.224801648763947</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.14883096633033</v>
+        <v>12.14883096633032</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.489413752594052</v>
+        <v>6.48941375259405</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.467047008249741</v>
+        <v>7.467047008249737</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.79794634844252</v>
+        <v>10.79794634844253</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.86558020822907</v>
+        <v>39.86558020822909</v>
       </c>
       <c r="C2" t="n">
-        <v>42.57319409382511</v>
+        <v>42.57319409382512</v>
       </c>
       <c r="D2" t="n">
-        <v>39.7437969788721</v>
+        <v>39.74379697887208</v>
       </c>
       <c r="E2" t="n">
-        <v>39.73571265549228</v>
+        <v>39.73571265549229</v>
       </c>
       <c r="F2" t="n">
-        <v>39.74936597682419</v>
+        <v>39.7493659768242</v>
       </c>
       <c r="G2" t="n">
-        <v>39.92563869640193</v>
+        <v>39.92563869640195</v>
       </c>
       <c r="H2" t="n">
-        <v>39.92338634207723</v>
+        <v>39.92338634207724</v>
       </c>
       <c r="I2" t="n">
         <v>39.70996203503856</v>
@@ -613,25 +613,25 @@
         <v>39.94209255405194</v>
       </c>
       <c r="K2" t="n">
-        <v>39.89178481684849</v>
+        <v>39.8917848168485</v>
       </c>
       <c r="L2" t="n">
         <v>40.02004025959982</v>
       </c>
       <c r="M2" t="n">
-        <v>40.20999589015849</v>
+        <v>40.20999589015851</v>
       </c>
       <c r="N2" t="n">
-        <v>39.97294740999754</v>
+        <v>39.97294740999752</v>
       </c>
       <c r="O2" t="n">
-        <v>44.06472838895306</v>
+        <v>44.06472838895309</v>
       </c>
       <c r="P2" t="n">
         <v>40.03532099705399</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.84917345479597</v>
+        <v>39.84917345479596</v>
       </c>
       <c r="R2" t="n">
         <v>39.76836775620612</v>
@@ -643,7 +643,7 @@
         <v>39.89335578178382</v>
       </c>
       <c r="U2" t="n">
-        <v>43.7445862771137</v>
+        <v>43.74458627711368</v>
       </c>
       <c r="V2" t="n">
         <v>39.87922973880493</v>
@@ -652,10 +652,10 @@
         <v>46.24781264865616</v>
       </c>
       <c r="X2" t="n">
-        <v>39.83098976852255</v>
+        <v>39.83098976852256</v>
       </c>
       <c r="Y2" t="n">
-        <v>40.15672860280745</v>
+        <v>40.15672860280746</v>
       </c>
       <c r="Z2" t="n">
         <v>41.34106150211277</v>
@@ -664,7 +664,7 @@
         <v>39.87315277237932</v>
       </c>
       <c r="AB2" t="n">
-        <v>40.21119741395761</v>
+        <v>40.21119741395758</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48.56881647219996</v>
+        <v>42.88019592920203</v>
       </c>
       <c r="C3" t="n">
-        <v>45.6637639783474</v>
+        <v>43.88850980624331</v>
       </c>
       <c r="D3" t="n">
-        <v>45.84464715645986</v>
+        <v>42.02790355245748</v>
       </c>
       <c r="E3" t="n">
-        <v>44.33154455751356</v>
+        <v>40.64272470475404</v>
       </c>
       <c r="F3" t="n">
-        <v>45.99920850645695</v>
+        <v>42.09313087302122</v>
       </c>
       <c r="G3" t="n">
-        <v>49.96020271212512</v>
+        <v>43.38084939560386</v>
       </c>
       <c r="H3" t="n">
-        <v>50.09663445345607</v>
+        <v>43.55289918469403</v>
       </c>
       <c r="I3" t="n">
-        <v>45.06284193739049</v>
+        <v>41.75988737746479</v>
       </c>
       <c r="J3" t="n">
-        <v>50.38285831164182</v>
+        <v>43.54725718476409</v>
       </c>
       <c r="K3" t="n">
-        <v>49.288525439903</v>
+        <v>43.22537867363683</v>
       </c>
       <c r="L3" t="n">
-        <v>52.19689088598886</v>
+        <v>44.18896866025123</v>
       </c>
       <c r="M3" t="n">
-        <v>56.76624906439133</v>
+        <v>45.85766719017522</v>
       </c>
       <c r="N3" t="n">
-        <v>51.15329783873284</v>
+        <v>43.85300359778919</v>
       </c>
       <c r="O3" t="n">
-        <v>53.58580498802323</v>
+        <v>47.30803227171348</v>
       </c>
       <c r="P3" t="n">
-        <v>52.4617149114215</v>
+        <v>44.22460053482314</v>
       </c>
       <c r="Q3" t="n">
-        <v>48.28582377986699</v>
+        <v>42.86370281741779</v>
       </c>
       <c r="R3" t="n">
-        <v>46.44027066169782</v>
+        <v>42.25075730614255</v>
       </c>
       <c r="S3" t="n">
-        <v>49.64666981514187</v>
+        <v>43.2717522143173</v>
       </c>
       <c r="T3" t="n">
-        <v>49.34162882711638</v>
+        <v>43.25395116598436</v>
       </c>
       <c r="U3" t="n">
-        <v>57.82632216533825</v>
+        <v>48.48326169329845</v>
       </c>
       <c r="V3" t="n">
-        <v>48.89535677512899</v>
+        <v>42.9959141930757</v>
       </c>
       <c r="W3" t="n">
-        <v>60.50298892505275</v>
+        <v>51.08114926391568</v>
       </c>
       <c r="X3" t="n">
-        <v>47.87282471654713</v>
+        <v>42.7253458505488</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.40328552949973</v>
+        <v>45.29839051961841</v>
       </c>
       <c r="Z3" t="n">
-        <v>51.77128686694764</v>
+        <v>44.91797366741964</v>
       </c>
       <c r="AA3" t="n">
-        <v>48.81345482713558</v>
+        <v>43.03394427226744</v>
       </c>
       <c r="AB3" t="n">
-        <v>56.70994314267389</v>
+        <v>45.92285545318845</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79.59295066876496</v>
+        <v>79.59295066876504</v>
       </c>
       <c r="C4" t="n">
-        <v>28.48735538111599</v>
+        <v>28.48735538111602</v>
       </c>
       <c r="D4" t="n">
-        <v>61.19991272789819</v>
+        <v>61.19991272789822</v>
       </c>
       <c r="E4" t="n">
-        <v>56.01891517752794</v>
+        <v>56.01891517752797</v>
       </c>
       <c r="F4" t="n">
-        <v>64.03946431738024</v>
+        <v>64.03946431738014</v>
       </c>
       <c r="G4" t="n">
-        <v>94.85644287227075</v>
+        <v>94.85644287227068</v>
       </c>
       <c r="H4" t="n">
         <v>108.862001994888</v>
       </c>
       <c r="I4" t="n">
-        <v>53.69400632597102</v>
+        <v>53.69400632597092</v>
       </c>
       <c r="J4" t="n">
         <v>101.2508451083562</v>
       </c>
       <c r="K4" t="n">
-        <v>95.95707232069458</v>
+        <v>95.95707232069434</v>
       </c>
       <c r="L4" t="n">
-        <v>120.4153028042084</v>
+        <v>120.4153028042078</v>
       </c>
       <c r="M4" t="n">
-        <v>175.2380915959086</v>
+        <v>175.2380915959087</v>
       </c>
       <c r="N4" t="n">
-        <v>112.7863197477355</v>
+        <v>112.7863197477356</v>
       </c>
       <c r="O4" t="n">
-        <v>85.48114031744142</v>
+        <v>85.48114031744134</v>
       </c>
       <c r="P4" t="n">
         <v>117.2870097399863</v>
       </c>
       <c r="Q4" t="n">
-        <v>84.64997914673987</v>
+        <v>84.64997914673988</v>
       </c>
       <c r="R4" t="n">
-        <v>68.80666382409237</v>
+        <v>68.80666382409238</v>
       </c>
       <c r="S4" t="n">
-        <v>92.02568332854545</v>
+        <v>92.02568332854558</v>
       </c>
       <c r="T4" t="n">
-        <v>97.53617242777247</v>
+        <v>97.53617242777229</v>
       </c>
       <c r="U4" t="n">
-        <v>137.315353078078</v>
+        <v>137.3153530780779</v>
       </c>
       <c r="V4" t="n">
-        <v>83.19859025623197</v>
+        <v>83.19859025623187</v>
       </c>
       <c r="W4" t="n">
-        <v>142.6623649242606</v>
+        <v>142.6623649242607</v>
       </c>
       <c r="X4" t="n">
-        <v>81.04741386160963</v>
+        <v>81.04741386160946</v>
       </c>
       <c r="Y4" t="n">
         <v>152.7377409684667</v>
       </c>
       <c r="Z4" t="n">
-        <v>98.6976264194026</v>
+        <v>98.69762641940272</v>
       </c>
       <c r="AA4" t="n">
-        <v>88.4764182930284</v>
+        <v>88.47641829302827</v>
       </c>
       <c r="AB4" t="n">
-        <v>180.6103279895026</v>
+        <v>180.6103279895025</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.877151369806509</v>
+        <v>7.877151369806453</v>
       </c>
       <c r="C5" t="n">
-        <v>6.435161644917459</v>
+        <v>6.435161644917423</v>
       </c>
       <c r="D5" t="n">
-        <v>7.95518136776408</v>
+        <v>7.955181367764069</v>
       </c>
       <c r="E5" t="n">
-        <v>7.089851400788042</v>
+        <v>7.089851400788021</v>
       </c>
       <c r="F5" t="n">
-        <v>6.790916355302604</v>
+        <v>6.790916355302572</v>
       </c>
       <c r="G5" t="n">
-        <v>10.31058637009213</v>
+        <v>10.3105863700921</v>
       </c>
       <c r="H5" t="n">
-        <v>9.983725840354712</v>
+        <v>9.983725840354687</v>
       </c>
       <c r="I5" t="n">
-        <v>7.573000112320931</v>
+        <v>7.573000112320907</v>
       </c>
       <c r="J5" t="n">
-        <v>10.19561552953357</v>
+        <v>10.19561552953356</v>
       </c>
       <c r="K5" t="n">
-        <v>9.626772075476339</v>
+        <v>9.626772075476367</v>
       </c>
       <c r="L5" t="n">
-        <v>11.07547630177126</v>
+        <v>11.07547630177123</v>
       </c>
       <c r="M5" t="n">
-        <v>13.21361175273827</v>
+        <v>13.21361175273828</v>
       </c>
       <c r="N5" t="n">
-        <v>112.7863197477355</v>
+        <v>9.416736327233723</v>
       </c>
       <c r="O5" t="n">
-        <v>8.938788881777823</v>
+        <v>8.938788881777784</v>
       </c>
       <c r="P5" t="n">
-        <v>10.35502627681738</v>
+        <v>10.35502627681733</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.406158542709056</v>
+        <v>7.406158542709035</v>
       </c>
       <c r="R5" t="n">
-        <v>8.23271960086803</v>
+        <v>8.232719600868016</v>
       </c>
       <c r="S5" t="n">
-        <v>9.846218769070871</v>
+        <v>9.846218769070864</v>
       </c>
       <c r="T5" t="n">
-        <v>9.64451684710048</v>
+        <v>9.644516847100508</v>
       </c>
       <c r="U5" t="n">
-        <v>11.34522213786831</v>
+        <v>11.34522213786829</v>
       </c>
       <c r="V5" t="n">
-        <v>9.091995518424474</v>
+        <v>9.091995518424467</v>
       </c>
       <c r="W5" t="n">
-        <v>12.12479175534858</v>
+        <v>12.12479175534854</v>
       </c>
       <c r="X5" t="n">
-        <v>7.333993297679035</v>
+        <v>7.333993297678995</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.06569600687691</v>
+        <v>14.06569600687692</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.729062177538694</v>
+        <v>8.729062177538678</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.416314562032984</v>
+        <v>9.416314562032998</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.72110562700791</v>
+        <v>14.72110562700789</v>
       </c>
     </row>
     <row r="6">
@@ -938,22 +938,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.44923799812371</v>
+        <v>11.4492379981237</v>
       </c>
       <c r="C6" t="n">
-        <v>10.17419565914793</v>
+        <v>10.1741956591479</v>
       </c>
       <c r="D6" t="n">
-        <v>11.69421538199455</v>
+        <v>11.69421538199451</v>
       </c>
       <c r="E6" t="n">
-        <v>11.22887735868206</v>
+        <v>11.22887735868207</v>
       </c>
       <c r="F6" t="n">
-        <v>8.021251764066747</v>
+        <v>8.021251764066742</v>
       </c>
       <c r="G6" t="n">
-        <v>13.74820152401882</v>
+        <v>13.74820152401878</v>
       </c>
       <c r="H6" t="n">
         <v>13.72275985458519</v>
@@ -962,61 +962,61 @@
         <v>11.31203412655141</v>
       </c>
       <c r="J6" t="n">
-        <v>13.93464954376404</v>
+        <v>13.934649543764</v>
       </c>
       <c r="K6" t="n">
         <v>13.36580608970681</v>
       </c>
       <c r="L6" t="n">
-        <v>14.81451031600174</v>
+        <v>14.81451031600168</v>
       </c>
       <c r="M6" t="n">
-        <v>16.95264576696827</v>
+        <v>16.95264576696823</v>
       </c>
       <c r="N6" t="n">
-        <v>112.7863197477355</v>
+        <v>14.28257491596299</v>
       </c>
       <c r="O6" t="n">
-        <v>14.03202860559395</v>
+        <v>14.03202860559394</v>
       </c>
       <c r="P6" t="n">
-        <v>15.64097066955823</v>
+        <v>15.64097066955821</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.88449144433065</v>
+        <v>12.88449144433058</v>
       </c>
       <c r="R6" t="n">
-        <v>11.97175361509851</v>
+        <v>11.97175361509846</v>
       </c>
       <c r="S6" t="n">
-        <v>13.58525278330135</v>
+        <v>13.58525278330134</v>
       </c>
       <c r="T6" t="n">
-        <v>13.38355086133094</v>
+        <v>13.38355086133092</v>
       </c>
       <c r="U6" t="n">
-        <v>15.7931952112848</v>
+        <v>15.79319521128482</v>
       </c>
       <c r="V6" t="n">
-        <v>15.09782041297534</v>
+        <v>15.09782041297532</v>
       </c>
       <c r="W6" t="n">
-        <v>15.86354009220873</v>
+        <v>15.86354009220872</v>
       </c>
       <c r="X6" t="n">
-        <v>12.67909805176118</v>
+        <v>12.67909805176115</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.35846803227654</v>
+        <v>16.35846803227648</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.97166317541233</v>
+        <v>12.97166317541227</v>
       </c>
       <c r="AA6" t="n">
-        <v>13.15534857626345</v>
+        <v>13.15534857626343</v>
       </c>
       <c r="AB6" t="n">
-        <v>16.94170406819504</v>
+        <v>16.94170406819502</v>
       </c>
     </row>
   </sheetData>
@@ -1182,85 +1182,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.7976727988032</v>
+        <v>38.79767279880323</v>
       </c>
       <c r="C2" t="n">
-        <v>41.7832252513118</v>
+        <v>41.78322525131183</v>
       </c>
       <c r="D2" t="n">
-        <v>38.87096952041476</v>
+        <v>38.87096952041481</v>
       </c>
       <c r="E2" t="n">
-        <v>38.82519896262244</v>
+        <v>38.82519896262249</v>
       </c>
       <c r="F2" t="n">
-        <v>38.93888780294377</v>
+        <v>38.9388878029438</v>
       </c>
       <c r="G2" t="n">
-        <v>38.98457544179061</v>
+        <v>38.98457544179062</v>
       </c>
       <c r="H2" t="n">
-        <v>38.9732481455044</v>
+        <v>38.97324814550444</v>
       </c>
       <c r="I2" t="n">
-        <v>38.86908781616912</v>
+        <v>38.86908781616915</v>
       </c>
       <c r="J2" t="n">
-        <v>38.96219847616753</v>
+        <v>38.96219847616751</v>
       </c>
       <c r="K2" t="n">
-        <v>39.01754417691991</v>
+        <v>39.01754417691998</v>
       </c>
       <c r="L2" t="n">
-        <v>38.93175487760108</v>
+        <v>38.93175487760111</v>
       </c>
       <c r="M2" t="n">
-        <v>38.93490611117451</v>
+        <v>38.93490611117456</v>
       </c>
       <c r="N2" t="n">
-        <v>39.02692214176369</v>
+        <v>39.0269221417637</v>
       </c>
       <c r="O2" t="n">
-        <v>42.77805981120949</v>
+        <v>42.77805981120954</v>
       </c>
       <c r="P2" t="n">
         <v>39.17523058394661</v>
       </c>
       <c r="Q2" t="n">
-        <v>38.86757583564976</v>
+        <v>38.86757583564982</v>
       </c>
       <c r="R2" t="n">
-        <v>38.85575154832135</v>
+        <v>38.85575154832136</v>
       </c>
       <c r="S2" t="n">
-        <v>38.99460269978464</v>
+        <v>38.99460269978467</v>
       </c>
       <c r="T2" t="n">
-        <v>38.9886932277488</v>
+        <v>38.98869322774885</v>
       </c>
       <c r="U2" t="n">
         <v>42.36330489084968</v>
       </c>
       <c r="V2" t="n">
-        <v>38.9054131572329</v>
+        <v>38.90541315723294</v>
       </c>
       <c r="W2" t="n">
-        <v>44.98574370532947</v>
+        <v>44.98574370532948</v>
       </c>
       <c r="X2" t="n">
-        <v>39.16914714456266</v>
+        <v>39.1691471445627</v>
       </c>
       <c r="Y2" t="n">
         <v>39.1250809603032</v>
       </c>
       <c r="Z2" t="n">
-        <v>39.9593221185233</v>
+        <v>39.95932211852339</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.09284144629073</v>
+        <v>39.09284144629076</v>
       </c>
       <c r="AB2" t="n">
-        <v>38.94229044815238</v>
+        <v>38.94229044815241</v>
       </c>
     </row>
     <row r="3">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.7266974364069</v>
+        <v>39.466144553656</v>
       </c>
       <c r="C3" t="n">
-        <v>43.60903646262867</v>
+        <v>42.73274531394303</v>
       </c>
       <c r="D3" t="n">
-        <v>41.44056658732662</v>
+        <v>40.05454874176392</v>
       </c>
       <c r="E3" t="n">
-        <v>39.17855254689407</v>
+        <v>38.49770496609973</v>
       </c>
       <c r="F3" t="n">
-        <v>43.0397510825397</v>
+        <v>40.60884716168667</v>
       </c>
       <c r="G3" t="n">
-        <v>44.02857903449934</v>
+        <v>40.89341760538867</v>
       </c>
       <c r="H3" t="n">
-        <v>43.85485022020345</v>
+        <v>40.91651711907542</v>
       </c>
       <c r="I3" t="n">
-        <v>41.40080975720224</v>
+        <v>40.04939890323112</v>
       </c>
       <c r="J3" t="n">
-        <v>43.5381222872029</v>
+        <v>40.75415092533486</v>
       </c>
       <c r="K3" t="n">
-        <v>44.84627335724307</v>
+        <v>41.17014737711993</v>
       </c>
       <c r="L3" t="n">
-        <v>42.82930259911465</v>
+        <v>40.50207161129416</v>
       </c>
       <c r="M3" t="n">
-        <v>42.96195488503025</v>
+        <v>40.57751368472917</v>
       </c>
       <c r="N3" t="n">
-        <v>45.06277504352627</v>
+        <v>41.3216168621762</v>
       </c>
       <c r="O3" t="n">
-        <v>49.1519160299905</v>
+        <v>45.09068446025572</v>
       </c>
       <c r="P3" t="n">
-        <v>48.40093684652955</v>
+        <v>42.36072271710884</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.35652213420347</v>
+        <v>40.01907584976047</v>
       </c>
       <c r="R3" t="n">
-        <v>41.0926159161459</v>
+        <v>39.94786030699133</v>
       </c>
       <c r="S3" t="n">
-        <v>44.26990556818061</v>
+        <v>40.97913979614598</v>
       </c>
       <c r="T3" t="n">
-        <v>44.19253923148629</v>
+        <v>41.02393137812133</v>
       </c>
       <c r="U3" t="n">
-        <v>48.05962880668618</v>
+        <v>44.46877605961728</v>
       </c>
       <c r="V3" t="n">
-        <v>42.20936514515489</v>
+        <v>40.2929610619243</v>
       </c>
       <c r="W3" t="n">
-        <v>54.21705202880918</v>
+        <v>48.26990363439174</v>
       </c>
       <c r="X3" t="n">
-        <v>48.38575936916538</v>
+        <v>42.41237750364635</v>
       </c>
       <c r="Y3" t="n">
-        <v>47.33433432213594</v>
+        <v>42.10331224942893</v>
       </c>
       <c r="Z3" t="n">
-        <v>42.6963625197758</v>
+        <v>41.16614385929125</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.58051669188256</v>
+        <v>41.83926393920775</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.11055709966977</v>
+        <v>40.6617788793673</v>
       </c>
     </row>
     <row r="4">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.722022859428983</v>
+        <v>3.722022859428969</v>
       </c>
       <c r="C4" t="n">
         <v>11.77338069445657</v>
       </c>
       <c r="D4" t="n">
-        <v>18.50582101282181</v>
+        <v>18.50582101282186</v>
       </c>
       <c r="E4" t="n">
-        <v>8.932877360417899</v>
+        <v>8.932877360417891</v>
       </c>
       <c r="F4" t="n">
-        <v>32.80575164126046</v>
+        <v>32.80575164126044</v>
       </c>
       <c r="G4" t="n">
-        <v>36.54306407574146</v>
+        <v>36.54306407574137</v>
       </c>
       <c r="H4" t="n">
-        <v>41.8871310637882</v>
+        <v>41.88713106378831</v>
       </c>
       <c r="I4" t="n">
-        <v>18.79804677550251</v>
+        <v>18.79804677550244</v>
       </c>
       <c r="J4" t="n">
-        <v>34.73014416819943</v>
+        <v>34.73014416819942</v>
       </c>
       <c r="K4" t="n">
-        <v>43.94296308073687</v>
+        <v>43.9429630807369</v>
       </c>
       <c r="L4" t="n">
-        <v>28.06080191001575</v>
+        <v>28.06080191001576</v>
       </c>
       <c r="M4" t="n">
-        <v>31.81537470788108</v>
+        <v>31.81537470788106</v>
       </c>
       <c r="N4" t="n">
-        <v>51.02917605539085</v>
+        <v>51.0291760553908</v>
       </c>
       <c r="O4" t="n">
-        <v>47.26739004629547</v>
+        <v>47.26739004629546</v>
       </c>
       <c r="P4" t="n">
-        <v>70.82254604826755</v>
+        <v>70.82254604826754</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.26787462422495</v>
+        <v>17.26787462422493</v>
       </c>
       <c r="R4" t="n">
-        <v>16.47868623370213</v>
+        <v>16.47868623370212</v>
       </c>
       <c r="S4" t="n">
-        <v>38.91106526482579</v>
+        <v>38.91106526482575</v>
       </c>
       <c r="T4" t="n">
-        <v>43.90924127135472</v>
+        <v>43.90924127135477</v>
       </c>
       <c r="U4" t="n">
-        <v>41.96417205804578</v>
+        <v>41.96417205804568</v>
       </c>
       <c r="V4" t="n">
-        <v>22.91746977870996</v>
+        <v>22.91746977870997</v>
       </c>
       <c r="W4" t="n">
-        <v>78.39514731898979</v>
+        <v>78.39514731898984</v>
       </c>
       <c r="X4" t="n">
-        <v>76.24654622615513</v>
+        <v>76.24654622615523</v>
       </c>
       <c r="Y4" t="n">
-        <v>70.43513065103102</v>
+        <v>70.43513065103096</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.69210058951026</v>
+        <v>17.6921005895103</v>
       </c>
       <c r="AA4" t="n">
-        <v>63.57551339029569</v>
+        <v>63.57551339029566</v>
       </c>
       <c r="AB4" t="n">
-        <v>35.24090102951155</v>
+        <v>35.24090102951154</v>
       </c>
     </row>
     <row r="5">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.2943748419576</v>
+        <v>2.294374841957591</v>
       </c>
       <c r="C5" t="n">
-        <v>3.544501671557815</v>
+        <v>3.544501671557814</v>
       </c>
       <c r="D5" t="n">
-        <v>3.920131735391153</v>
+        <v>3.920131735391149</v>
       </c>
       <c r="E5" t="n">
-        <v>2.978307719332813</v>
+        <v>2.97830771933281</v>
       </c>
       <c r="F5" t="n">
-        <v>4.013756909778385</v>
+        <v>4.013756909778372</v>
       </c>
       <c r="G5" t="n">
-        <v>5.368799516687149</v>
+        <v>5.36879951668714</v>
       </c>
       <c r="H5" t="n">
-        <v>5.075415856271003</v>
+        <v>5.075415856271001</v>
       </c>
       <c r="I5" t="n">
-        <v>3.89887702030984</v>
+        <v>3.89887702030983</v>
       </c>
       <c r="J5" t="n">
-        <v>4.951161663896519</v>
+        <v>4.951161663896506</v>
       </c>
       <c r="K5" t="n">
-        <v>5.575759908290728</v>
+        <v>5.575759908290723</v>
       </c>
       <c r="L5" t="n">
-        <v>4.606730307456361</v>
+        <v>4.606730307456363</v>
       </c>
       <c r="M5" t="n">
-        <v>4.651945095824139</v>
+        <v>4.651945095824138</v>
       </c>
       <c r="N5" t="n">
-        <v>51.02917605539085</v>
+        <v>5.063231413689008</v>
       </c>
       <c r="O5" t="n">
-        <v>5.440949186507833</v>
+        <v>5.440949186507829</v>
       </c>
       <c r="P5" t="n">
-        <v>6.866740176214329</v>
+        <v>6.866740176214321</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.927168678231384</v>
+        <v>2.927168678231379</v>
       </c>
       <c r="R5" t="n">
-        <v>3.748237739982891</v>
+        <v>3.748237739982892</v>
       </c>
       <c r="S5" t="n">
-        <v>5.316625370446319</v>
+        <v>5.316625370446309</v>
       </c>
       <c r="T5" t="n">
-        <v>5.249875165310495</v>
+        <v>5.249875165310496</v>
       </c>
       <c r="U5" t="n">
-        <v>5.133149163499985</v>
+        <v>5.133149163499974</v>
       </c>
       <c r="V5" t="n">
-        <v>4.088671783736463</v>
+        <v>4.088671783736448</v>
       </c>
       <c r="W5" t="n">
-        <v>7.317071400497658</v>
+        <v>7.31707140049765</v>
       </c>
       <c r="X5" t="n">
-        <v>6.406678660666175</v>
+        <v>6.40667866066617</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.574614326045968</v>
+        <v>7.574614326045966</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.207069580479076</v>
+        <v>3.207069580479057</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.426277204289105</v>
+        <v>6.4262772042891</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.5595999610877</v>
+        <v>5.559599961087687</v>
       </c>
     </row>
     <row r="6">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.696789236828528</v>
+        <v>3.696789236828527</v>
       </c>
       <c r="C6" t="n">
-        <v>4.884185055004955</v>
+        <v>4.884185055004949</v>
       </c>
       <c r="D6" t="n">
-        <v>5.25981511883829</v>
+        <v>5.259815118838286</v>
       </c>
       <c r="E6" t="n">
-        <v>4.573156518306458</v>
+        <v>4.573156518306457</v>
       </c>
       <c r="F6" t="n">
-        <v>4.332363601224341</v>
+        <v>4.332363601224332</v>
       </c>
       <c r="G6" t="n">
-        <v>6.543046653124382</v>
+        <v>6.543046653124378</v>
       </c>
       <c r="H6" t="n">
-        <v>6.415099239718137</v>
+        <v>6.415099239718133</v>
       </c>
       <c r="I6" t="n">
-        <v>5.238560403756973</v>
+        <v>5.238560403756964</v>
       </c>
       <c r="J6" t="n">
         <v>6.290845047343642</v>
       </c>
       <c r="K6" t="n">
-        <v>6.915443291737862</v>
+        <v>6.915443291737857</v>
       </c>
       <c r="L6" t="n">
-        <v>5.946413690903503</v>
+        <v>5.946413690903498</v>
       </c>
       <c r="M6" t="n">
-        <v>5.991628479269544</v>
+        <v>5.99162847926954</v>
       </c>
       <c r="N6" t="n">
-        <v>51.02917605539085</v>
+        <v>7.021371718724594</v>
       </c>
       <c r="O6" t="n">
-        <v>7.472745744944572</v>
+        <v>7.47274574494457</v>
       </c>
       <c r="P6" t="n">
-        <v>8.993179073220304</v>
+        <v>8.993179073220293</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.22148227928542</v>
+        <v>5.221482279285417</v>
       </c>
       <c r="R6" t="n">
-        <v>5.08792112343003</v>
+        <v>5.087921123430025</v>
       </c>
       <c r="S6" t="n">
-        <v>6.656308753893442</v>
+        <v>6.656308753893444</v>
       </c>
       <c r="T6" t="n">
-        <v>6.589558548757636</v>
+        <v>6.589558548757632</v>
       </c>
       <c r="U6" t="n">
-        <v>6.867561857668981</v>
+        <v>6.867561857668978</v>
       </c>
       <c r="V6" t="n">
-        <v>6.500575504372708</v>
+        <v>6.500575504372699</v>
       </c>
       <c r="W6" t="n">
-        <v>8.65659798731272</v>
+        <v>8.656597987312713</v>
       </c>
       <c r="X6" t="n">
-        <v>8.627868552073172</v>
+        <v>8.627868552073167</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.130120729415722</v>
+        <v>8.130120729415724</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.916206685296493</v>
+        <v>4.916206685296486</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.765960587736243</v>
+        <v>7.765960587736238</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.06587619354459</v>
+        <v>6.065876193544583</v>
       </c>
     </row>
   </sheetData>
@@ -1778,85 +1778,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.69030504963083</v>
+        <v>39.6903050496308</v>
       </c>
       <c r="C2" t="n">
-        <v>42.45984275399574</v>
+        <v>42.45984275399572</v>
       </c>
       <c r="D2" t="n">
-        <v>39.66980475170945</v>
+        <v>39.66980475170942</v>
       </c>
       <c r="E2" t="n">
-        <v>39.62735311694904</v>
+        <v>39.627353116949</v>
       </c>
       <c r="F2" t="n">
-        <v>39.60705433032811</v>
+        <v>39.60705433032807</v>
       </c>
       <c r="G2" t="n">
-        <v>39.80048354084985</v>
+        <v>39.80048354084981</v>
       </c>
       <c r="H2" t="n">
-        <v>39.76151256340712</v>
+        <v>39.7615125634071</v>
       </c>
       <c r="I2" t="n">
         <v>39.59700275437996</v>
       </c>
       <c r="J2" t="n">
-        <v>39.81279625376366</v>
+        <v>39.81279625376364</v>
       </c>
       <c r="K2" t="n">
-        <v>39.72485076381408</v>
+        <v>39.72485076381405</v>
       </c>
       <c r="L2" t="n">
-        <v>39.85223690284602</v>
+        <v>39.852236902846</v>
       </c>
       <c r="M2" t="n">
-        <v>40.04309985702004</v>
+        <v>40.04309985702003</v>
       </c>
       <c r="N2" t="n">
-        <v>39.83144160389184</v>
+        <v>39.83144160389178</v>
       </c>
       <c r="O2" t="n">
-        <v>43.93394011868197</v>
+        <v>43.93394011868195</v>
       </c>
       <c r="P2" t="n">
-        <v>39.94141790205296</v>
+        <v>39.94141790205293</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.71341476273064</v>
+        <v>39.71341476273061</v>
       </c>
       <c r="R2" t="n">
-        <v>39.6900646321909</v>
+        <v>39.69006463219088</v>
       </c>
       <c r="S2" t="n">
-        <v>39.77486470857878</v>
+        <v>39.77486470857876</v>
       </c>
       <c r="T2" t="n">
-        <v>39.71832236506725</v>
+        <v>39.71832236506722</v>
       </c>
       <c r="U2" t="n">
-        <v>43.52350624232832</v>
+        <v>43.5235062423283</v>
       </c>
       <c r="V2" t="n">
-        <v>39.74335594036914</v>
+        <v>39.7433559403691</v>
       </c>
       <c r="W2" t="n">
-        <v>46.11587246602799</v>
+        <v>46.11587246602795</v>
       </c>
       <c r="X2" t="n">
-        <v>39.74677401895288</v>
+        <v>39.74677401895286</v>
       </c>
       <c r="Y2" t="n">
-        <v>40.04659684064936</v>
+        <v>40.04659684064931</v>
       </c>
       <c r="Z2" t="n">
         <v>41.13471730265141</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.7143457001058</v>
+        <v>39.71434570010577</v>
       </c>
       <c r="AB2" t="n">
-        <v>40.08853650961274</v>
+        <v>40.08853650961273</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46.77117968928006</v>
+        <v>42.20706232500933</v>
       </c>
       <c r="C3" t="n">
-        <v>45.32190131957065</v>
+        <v>43.70214066216602</v>
       </c>
       <c r="D3" t="n">
-        <v>46.38850143789354</v>
+        <v>42.15792945236565</v>
       </c>
       <c r="E3" t="n">
-        <v>44.09070946895452</v>
+        <v>40.50783559882143</v>
       </c>
       <c r="F3" t="n">
-        <v>44.9421451705604</v>
+        <v>41.64812603943404</v>
       </c>
       <c r="G3" t="n">
-        <v>49.31534815641449</v>
+        <v>43.08999657954369</v>
       </c>
       <c r="H3" t="n">
-        <v>48.57965746550971</v>
+        <v>42.95223734728891</v>
       </c>
       <c r="I3" t="n">
-        <v>44.6964646726369</v>
+        <v>41.57137135471926</v>
       </c>
       <c r="J3" t="n">
-        <v>49.6455030047546</v>
+        <v>43.22783046785959</v>
       </c>
       <c r="K3" t="n">
-        <v>47.65572786373002</v>
+        <v>42.53321489978988</v>
       </c>
       <c r="L3" t="n">
-        <v>50.56282827674899</v>
+        <v>43.56510328744708</v>
       </c>
       <c r="M3" t="n">
-        <v>55.1352857707215</v>
+        <v>45.21603208238513</v>
       </c>
       <c r="N3" t="n">
-        <v>50.12431698608388</v>
+        <v>43.43538858100827</v>
       </c>
       <c r="O3" t="n">
-        <v>53.74433941893253</v>
+        <v>47.2615631108937</v>
       </c>
       <c r="P3" t="n">
-        <v>52.53754833804316</v>
+        <v>44.18549287470233</v>
       </c>
       <c r="Q3" t="n">
-        <v>47.38875376552171</v>
+        <v>42.4866573295276</v>
       </c>
       <c r="R3" t="n">
-        <v>46.88533375800782</v>
+        <v>42.34747152952098</v>
       </c>
       <c r="S3" t="n">
-        <v>48.74233809912019</v>
+        <v>42.89298989107483</v>
       </c>
       <c r="T3" t="n">
-        <v>47.52474511740981</v>
+        <v>42.55276225412488</v>
       </c>
       <c r="U3" t="n">
-        <v>55.9756668787747</v>
+        <v>47.75506069804872</v>
       </c>
       <c r="V3" t="n">
-        <v>47.99997784018409</v>
+        <v>42.59907799136072</v>
       </c>
       <c r="W3" t="n">
-        <v>60.74724521652018</v>
+        <v>51.07415110228883</v>
       </c>
       <c r="X3" t="n">
-        <v>48.17689861480098</v>
+        <v>42.76585597692635</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.10169925321767</v>
+        <v>45.11366215519746</v>
       </c>
       <c r="Z3" t="n">
-        <v>50.3398596551964</v>
+        <v>44.32890426918345</v>
       </c>
       <c r="AA3" t="n">
-        <v>47.38389628619856</v>
+        <v>42.47149686311309</v>
       </c>
       <c r="AB3" t="n">
-        <v>56.10745239385599</v>
+        <v>45.65119566822173</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59.75916157411455</v>
+        <v>59.75916157411284</v>
       </c>
       <c r="C4" t="n">
-        <v>23.94081642223509</v>
+        <v>23.94081642223511</v>
       </c>
       <c r="D4" t="n">
-        <v>63.61934709755246</v>
+        <v>63.61934709755218</v>
       </c>
       <c r="E4" t="n">
-        <v>50.94572384981508</v>
+        <v>50.94572384981539</v>
       </c>
       <c r="F4" t="n">
-        <v>49.61059341298858</v>
+        <v>49.61059341298864</v>
       </c>
       <c r="G4" t="n">
-        <v>83.45717907507586</v>
+        <v>83.45717907507569</v>
       </c>
       <c r="H4" t="n">
-        <v>87.56574024233797</v>
+        <v>87.56574024233809</v>
       </c>
       <c r="I4" t="n">
-        <v>47.74850689196569</v>
+        <v>47.74850689196577</v>
       </c>
       <c r="J4" t="n">
-        <v>88.89394962873641</v>
+        <v>88.89394962873654</v>
       </c>
       <c r="K4" t="n">
-        <v>70.65191769043109</v>
+        <v>70.65191769043125</v>
       </c>
       <c r="L4" t="n">
-        <v>98.91632886210381</v>
+        <v>98.91632886210601</v>
       </c>
       <c r="M4" t="n">
-        <v>148.7418659276115</v>
+        <v>148.7418659276119</v>
       </c>
       <c r="N4" t="n">
-        <v>97.07504839063225</v>
+        <v>97.07504839063222</v>
       </c>
       <c r="O4" t="n">
-        <v>82.01789368333691</v>
+        <v>82.01789368333712</v>
       </c>
       <c r="P4" t="n">
-        <v>111.3444853587979</v>
+        <v>111.3444853587981</v>
       </c>
       <c r="Q4" t="n">
-        <v>71.49345821415483</v>
+        <v>71.49345821415434</v>
       </c>
       <c r="R4" t="n">
-        <v>69.9168595201777</v>
+        <v>69.91685952017758</v>
       </c>
       <c r="S4" t="n">
-        <v>78.52271219999851</v>
+        <v>78.5227121999984</v>
       </c>
       <c r="T4" t="n">
-        <v>74.46942858685064</v>
+        <v>74.46942858685063</v>
       </c>
       <c r="U4" t="n">
         <v>113.2713157601275</v>
       </c>
       <c r="V4" t="n">
-        <v>68.74591693129877</v>
+        <v>68.74591693129864</v>
       </c>
       <c r="W4" t="n">
-        <v>137.5269006219985</v>
+        <v>137.5269006219987</v>
       </c>
       <c r="X4" t="n">
-        <v>79.50697023362545</v>
+        <v>79.50697023362518</v>
       </c>
       <c r="Y4" t="n">
-        <v>139.9804907889937</v>
+        <v>139.980490788994</v>
       </c>
       <c r="Z4" t="n">
-        <v>80.717470586239</v>
+        <v>80.71747058623897</v>
       </c>
       <c r="AA4" t="n">
-        <v>70.08325061634893</v>
+        <v>70.08325061634901</v>
       </c>
       <c r="AB4" t="n">
-        <v>164.5232504725325</v>
+        <v>164.5232504725336</v>
       </c>
     </row>
     <row r="5">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.692309605011153</v>
+        <v>6.692309605011128</v>
       </c>
       <c r="C5" t="n">
-        <v>5.793697037257532</v>
+        <v>5.79369703725755</v>
       </c>
       <c r="D5" t="n">
-        <v>7.741224141180358</v>
+        <v>7.741224141180367</v>
       </c>
       <c r="E5" t="n">
-        <v>6.579898321928352</v>
+        <v>6.579898321928416</v>
       </c>
       <c r="F5" t="n">
-        <v>5.951437446619874</v>
+        <v>5.951437446619881</v>
       </c>
       <c r="G5" t="n">
-        <v>9.482815977484403</v>
+        <v>9.482815977484414</v>
       </c>
       <c r="H5" t="n">
-        <v>8.777106061982572</v>
+        <v>8.777106061982584</v>
       </c>
       <c r="I5" t="n">
-        <v>6.918892090770141</v>
+        <v>6.918892090770153</v>
       </c>
       <c r="J5" t="n">
-        <v>9.356972277683505</v>
+        <v>9.356972277683512</v>
       </c>
       <c r="K5" t="n">
-        <v>8.362994170318398</v>
+        <v>8.362994170318409</v>
       </c>
       <c r="L5" t="n">
-        <v>9.801879211203191</v>
+        <v>9.801879211203422</v>
       </c>
       <c r="M5" t="n">
-        <v>11.95048320915791</v>
+        <v>11.95048320915795</v>
       </c>
       <c r="N5" t="n">
-        <v>97.07504839063225</v>
+        <v>8.574404529322051</v>
       </c>
       <c r="O5" t="n">
-        <v>8.659099732382982</v>
+        <v>8.659099732382986</v>
       </c>
       <c r="P5" t="n">
-        <v>10.02254504913184</v>
+        <v>10.02254504913188</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.701701916103609</v>
+        <v>6.70170191610363</v>
       </c>
       <c r="R5" t="n">
-        <v>7.970068811223558</v>
+        <v>7.970068811223569</v>
       </c>
       <c r="S5" t="n">
-        <v>8.927924683986999</v>
+        <v>8.927924683987005</v>
       </c>
       <c r="T5" t="n">
-        <v>8.289252903261344</v>
+        <v>8.289252903261371</v>
       </c>
       <c r="U5" t="n">
-        <v>10.07273367546312</v>
+        <v>10.07273367546313</v>
       </c>
       <c r="V5" t="n">
-        <v>8.226966416989027</v>
+        <v>8.226966416989042</v>
       </c>
       <c r="W5" t="n">
-        <v>11.78994213662408</v>
+        <v>11.7899421366241</v>
       </c>
       <c r="X5" t="n">
-        <v>7.195868122700461</v>
+        <v>7.195868122700491</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.27230320782256</v>
+        <v>13.27230320782257</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.752255650245431</v>
+        <v>7.752255650245443</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.244334643165029</v>
+        <v>8.244334643165059</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.77158416323516</v>
+        <v>13.77158416323522</v>
       </c>
     </row>
     <row r="6">
@@ -2130,52 +2130,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.415613836367598</v>
+        <v>9.415613836367536</v>
       </c>
       <c r="C6" t="n">
-        <v>8.547001032044484</v>
+        <v>8.547001032044488</v>
       </c>
       <c r="D6" t="n">
-        <v>10.4945281359673</v>
+        <v>10.49452813596731</v>
       </c>
       <c r="E6" t="n">
-        <v>9.712565386585524</v>
+        <v>9.712565386585554</v>
       </c>
       <c r="F6" t="n">
         <v>6.764731341128199</v>
       </c>
       <c r="G6" t="n">
-        <v>11.97060541529365</v>
+        <v>11.97060541529364</v>
       </c>
       <c r="H6" t="n">
-        <v>11.53041005676952</v>
+        <v>11.53041005676951</v>
       </c>
       <c r="I6" t="n">
-        <v>9.672196085557093</v>
+        <v>9.672196085557106</v>
       </c>
       <c r="J6" t="n">
         <v>12.11027627247046</v>
       </c>
       <c r="K6" t="n">
-        <v>11.11629816510535</v>
+        <v>11.11629816510537</v>
       </c>
       <c r="L6" t="n">
-        <v>12.55518320599014</v>
+        <v>12.55518320598998</v>
       </c>
       <c r="M6" t="n">
-        <v>14.7037872039437</v>
+        <v>14.70378720394369</v>
       </c>
       <c r="N6" t="n">
-        <v>97.07504839063225</v>
+        <v>12.32029073799248</v>
       </c>
       <c r="O6" t="n">
-        <v>12.56650561667999</v>
+        <v>12.56650561667998</v>
       </c>
       <c r="P6" t="n">
-        <v>14.09126404939406</v>
+        <v>14.09126404939409</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.98712351281989</v>
+        <v>10.98712351281986</v>
       </c>
       <c r="R6" t="n">
         <v>10.72337280601051</v>
@@ -2184,31 +2184,31 @@
         <v>11.68122867877395</v>
       </c>
       <c r="T6" t="n">
-        <v>11.04255689804831</v>
+        <v>11.0425568980483</v>
       </c>
       <c r="U6" t="n">
-        <v>13.44991430804576</v>
+        <v>13.44991430804577</v>
       </c>
       <c r="V6" t="n">
-        <v>12.84128167927154</v>
+        <v>12.84128167927155</v>
       </c>
       <c r="W6" t="n">
         <v>14.54299448324706</v>
       </c>
       <c r="X6" t="n">
-        <v>11.36393141709378</v>
+        <v>11.36393141709386</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.75056811346758</v>
+        <v>14.75056811346759</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.01972040069949</v>
+        <v>11.0197204006995</v>
       </c>
       <c r="AA6" t="n">
         <v>10.99763863795199</v>
       </c>
       <c r="AB6" t="n">
-        <v>15.18732512635674</v>
+        <v>15.1873251263568</v>
       </c>
     </row>
   </sheetData>
@@ -2374,16 +2374,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.52516644115882</v>
+        <v>39.52516644115886</v>
       </c>
       <c r="C2" t="n">
         <v>42.39139325379597</v>
       </c>
       <c r="D2" t="n">
-        <v>39.60418783679202</v>
+        <v>39.60418783679204</v>
       </c>
       <c r="E2" t="n">
-        <v>39.48500765978298</v>
+        <v>39.48500765978302</v>
       </c>
       <c r="F2" t="n">
         <v>39.50647324295703</v>
@@ -2392,67 +2392,67 @@
         <v>39.66964391663461</v>
       </c>
       <c r="H2" t="n">
-        <v>39.62048311942832</v>
+        <v>39.62048311942834</v>
       </c>
       <c r="I2" t="n">
-        <v>39.51926893015052</v>
+        <v>39.51926893015054</v>
       </c>
       <c r="J2" t="n">
-        <v>39.67245924222181</v>
+        <v>39.67245924222184</v>
       </c>
       <c r="K2" t="n">
-        <v>39.53152046818625</v>
+        <v>39.53152046818632</v>
       </c>
       <c r="L2" t="n">
-        <v>39.68375781275456</v>
+        <v>39.68375781275458</v>
       </c>
       <c r="M2" t="n">
         <v>39.86749633953338</v>
       </c>
       <c r="N2" t="n">
-        <v>39.63287865255445</v>
+        <v>39.63287865255447</v>
       </c>
       <c r="O2" t="n">
-        <v>43.70955152745519</v>
+        <v>43.70955152745521</v>
       </c>
       <c r="P2" t="n">
-        <v>39.81152916748574</v>
+        <v>39.81152916748572</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.55947358515914</v>
+        <v>39.55947358515915</v>
       </c>
       <c r="R2" t="n">
-        <v>39.5450656074475</v>
+        <v>39.54506560744752</v>
       </c>
       <c r="S2" t="n">
-        <v>39.63907735223473</v>
+        <v>39.63907735223474</v>
       </c>
       <c r="T2" t="n">
-        <v>39.60770542464208</v>
+        <v>39.60770542464211</v>
       </c>
       <c r="U2" t="n">
-        <v>43.23484248841925</v>
+        <v>43.23484248841929</v>
       </c>
       <c r="V2" t="n">
-        <v>39.62192646670737</v>
+        <v>39.62192646670739</v>
       </c>
       <c r="W2" t="n">
-        <v>45.86388887633559</v>
+        <v>45.86388887633564</v>
       </c>
       <c r="X2" t="n">
-        <v>39.69865880047913</v>
+        <v>39.69865880047917</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.92315568933981</v>
+        <v>39.92315568933984</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.90444163275991</v>
+        <v>40.9044416327599</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.59853119700507</v>
+        <v>39.59853119700508</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.93359475512392</v>
+        <v>39.93359475512393</v>
       </c>
     </row>
     <row r="3">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.35968631903486</v>
+        <v>41.67258349582362</v>
       </c>
       <c r="C3" t="n">
-        <v>46.28252578376542</v>
+        <v>43.94909787855291</v>
       </c>
       <c r="D3" t="n">
-        <v>47.27953893581466</v>
+        <v>42.39308802429265</v>
       </c>
       <c r="E3" t="n">
-        <v>43.21613665612701</v>
+        <v>40.15201590854297</v>
       </c>
       <c r="F3" t="n">
-        <v>45.01744045806227</v>
+        <v>41.59720456643971</v>
       </c>
       <c r="G3" t="n">
-        <v>48.6894973394387</v>
+        <v>42.79276992964694</v>
       </c>
       <c r="H3" t="n">
-        <v>47.7076891739888</v>
+        <v>42.58412988577659</v>
       </c>
       <c r="I3" t="n">
-        <v>45.30660275874202</v>
+        <v>41.71514092576124</v>
       </c>
       <c r="J3" t="n">
-        <v>48.80452239808229</v>
+        <v>42.86381500302637</v>
       </c>
       <c r="K3" t="n">
-        <v>45.56695718237799</v>
+        <v>41.72483504797582</v>
       </c>
       <c r="L3" t="n">
-        <v>49.0639009917828</v>
+        <v>42.97478795376414</v>
       </c>
       <c r="M3" t="n">
-        <v>53.45817606382957</v>
+        <v>44.56508154664726</v>
       </c>
       <c r="N3" t="n">
-        <v>47.92070562353807</v>
+        <v>42.60519052756916</v>
       </c>
       <c r="O3" t="n">
-        <v>53.14712688946556</v>
+        <v>46.9168350033877</v>
       </c>
       <c r="P3" t="n">
-        <v>51.93445282430341</v>
+        <v>43.8949384869122</v>
       </c>
       <c r="Q3" t="n">
-        <v>46.2191848544029</v>
+        <v>41.99700227801007</v>
       </c>
       <c r="R3" t="n">
-        <v>45.92124248958837</v>
+        <v>41.94084893005857</v>
       </c>
       <c r="S3" t="n">
-        <v>48.00231074909963</v>
+        <v>42.56495139015852</v>
       </c>
       <c r="T3" t="n">
-        <v>47.36661544186572</v>
+        <v>42.4320357802601</v>
       </c>
       <c r="U3" t="n">
-        <v>53.51052393664802</v>
+        <v>46.77500070130579</v>
       </c>
       <c r="V3" t="n">
-        <v>47.59149850377341</v>
+        <v>42.38173273870053</v>
       </c>
       <c r="W3" t="n">
-        <v>59.34048355013549</v>
+        <v>50.46105024122031</v>
       </c>
       <c r="X3" t="n">
-        <v>49.47547841937535</v>
+        <v>43.14344854720244</v>
       </c>
       <c r="Y3" t="n">
-        <v>54.64653408905434</v>
+        <v>44.8941659273555</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.91980363183801</v>
+        <v>43.67958905526797</v>
       </c>
       <c r="AA3" t="n">
-        <v>47.1055042392442</v>
+        <v>42.30970139818176</v>
       </c>
       <c r="AB3" t="n">
-        <v>54.91484849172561</v>
+        <v>45.16758669754338</v>
       </c>
     </row>
     <row r="4">
@@ -2550,82 +2550,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46.18547807401716</v>
+        <v>46.18547807401761</v>
       </c>
       <c r="C4" t="n">
-        <v>30.85201588081555</v>
+        <v>30.85201588081556</v>
       </c>
       <c r="D4" t="n">
-        <v>67.8819756039092</v>
+        <v>67.88197560390945</v>
       </c>
       <c r="E4" t="n">
-        <v>41.02981161290818</v>
+        <v>41.02981161290815</v>
       </c>
       <c r="F4" t="n">
-        <v>47.35748105973624</v>
+        <v>47.35748105973632</v>
       </c>
       <c r="G4" t="n">
-        <v>72.70042241616662</v>
+        <v>72.70042241616679</v>
       </c>
       <c r="H4" t="n">
-        <v>75.19953727905479</v>
+        <v>75.19953727905498</v>
       </c>
       <c r="I4" t="n">
-        <v>50.99043234116484</v>
+        <v>50.99043234116486</v>
       </c>
       <c r="J4" t="n">
-        <v>76.49378877420112</v>
+        <v>76.49378877420119</v>
       </c>
       <c r="K4" t="n">
-        <v>47.46158288944368</v>
+        <v>47.46158288944378</v>
       </c>
       <c r="L4" t="n">
-        <v>80.16047329118098</v>
+        <v>80.16047329118085</v>
       </c>
       <c r="M4" t="n">
-        <v>125.0496486823744</v>
+        <v>125.0496486823743</v>
       </c>
       <c r="N4" t="n">
-        <v>72.47327460659888</v>
+        <v>72.47327460659899</v>
       </c>
       <c r="O4" t="n">
-        <v>72.99219570800977</v>
+        <v>72.99219570800997</v>
       </c>
       <c r="P4" t="n">
-        <v>98.91998404192503</v>
+        <v>98.9199840419253</v>
       </c>
       <c r="Q4" t="n">
-        <v>56.35615611456842</v>
+        <v>56.35615611456848</v>
       </c>
       <c r="R4" t="n">
-        <v>57.44453000296296</v>
+        <v>57.44453000296286</v>
       </c>
       <c r="S4" t="n">
-        <v>67.68928168329978</v>
+        <v>67.68928168329987</v>
       </c>
       <c r="T4" t="n">
-        <v>69.31367815220423</v>
+        <v>69.31367815220449</v>
       </c>
       <c r="U4" t="n">
-        <v>85.81299546139726</v>
+        <v>85.81299546139731</v>
       </c>
       <c r="V4" t="n">
-        <v>61.14682529939407</v>
+        <v>61.14682529939402</v>
       </c>
       <c r="W4" t="n">
-        <v>118.20707014633</v>
+        <v>118.2070701463295</v>
       </c>
       <c r="X4" t="n">
-        <v>86.40993805747189</v>
+        <v>86.40993805747208</v>
       </c>
       <c r="Y4" t="n">
-        <v>128.3037535659284</v>
+        <v>128.3037535659288</v>
       </c>
       <c r="Z4" t="n">
-        <v>61.57923341187635</v>
+        <v>61.5792334118763</v>
       </c>
       <c r="AA4" t="n">
-        <v>64.21792624486308</v>
+        <v>64.21792624486324</v>
       </c>
       <c r="AB4" t="n">
         <v>144.0771113602307</v>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.681570041596066</v>
+        <v>5.681570041596119</v>
       </c>
       <c r="C5" t="n">
-        <v>5.761092330973048</v>
+        <v>5.761092330973071</v>
       </c>
       <c r="D5" t="n">
-        <v>7.670918125492266</v>
+        <v>7.670918125492318</v>
       </c>
       <c r="E5" t="n">
-        <v>5.740728154408747</v>
+        <v>5.740728154408774</v>
       </c>
       <c r="F5" t="n">
-        <v>5.641284947962601</v>
+        <v>5.64128494796263</v>
       </c>
       <c r="G5" t="n">
-        <v>8.637696040217255</v>
+        <v>8.63769604021727</v>
       </c>
       <c r="H5" t="n">
-        <v>7.854980839070206</v>
+        <v>7.854980839070217</v>
       </c>
       <c r="I5" t="n">
-        <v>6.711720010349419</v>
+        <v>6.711720010349445</v>
       </c>
       <c r="J5" t="n">
-        <v>8.442739632139192</v>
+        <v>8.44273963213921</v>
       </c>
       <c r="K5" t="n">
-        <v>6.850106768449638</v>
+        <v>6.850106768449646</v>
       </c>
       <c r="L5" t="n">
-        <v>8.569697607986495</v>
+        <v>8.569697607986534</v>
       </c>
       <c r="M5" t="n">
-        <v>10.63928356051734</v>
+        <v>10.63928356051737</v>
       </c>
       <c r="N5" t="n">
-        <v>72.47327460659888</v>
+        <v>7.14481767462981</v>
       </c>
       <c r="O5" t="n">
-        <v>8.017129131452045</v>
+        <v>8.017129131452073</v>
       </c>
       <c r="P5" t="n">
-        <v>9.339123489118418</v>
+        <v>9.339123489118464</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.853545647127666</v>
+        <v>5.853545647127678</v>
       </c>
       <c r="R5" t="n">
-        <v>7.003105347476787</v>
+        <v>7.00310534747681</v>
       </c>
       <c r="S5" t="n">
-        <v>8.065011252387913</v>
+        <v>8.065011252387951</v>
       </c>
       <c r="T5" t="n">
-        <v>7.710650898429366</v>
+        <v>7.710650898429405</v>
       </c>
       <c r="U5" t="n">
-        <v>8.495135090300014</v>
+        <v>8.495135090300035</v>
       </c>
       <c r="V5" t="n">
-        <v>7.573426961092514</v>
+        <v>7.573426961092536</v>
       </c>
       <c r="W5" t="n">
-        <v>10.64769840277125</v>
+        <v>10.64769840277126</v>
       </c>
       <c r="X5" t="n">
-        <v>7.526227379466677</v>
+        <v>7.526227379466701</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.3607676860197</v>
+        <v>12.36076768601974</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.779198022314161</v>
+        <v>6.779198022314167</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.607023776915972</v>
+        <v>7.607023776915995</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.50077485559913</v>
+        <v>12.50077485559914</v>
       </c>
     </row>
     <row r="6">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.844202432299306</v>
+        <v>7.844202432299355</v>
       </c>
       <c r="C6" t="n">
-        <v>7.902417344358074</v>
+        <v>7.902417344358098</v>
       </c>
       <c r="D6" t="n">
-        <v>9.81224313887731</v>
+        <v>9.81224313887734</v>
       </c>
       <c r="E6" t="n">
-        <v>8.217837098546934</v>
+        <v>8.217837098546948</v>
       </c>
       <c r="F6" t="n">
-        <v>6.229288126259821</v>
+        <v>6.229288126259822</v>
       </c>
       <c r="G6" t="n">
-        <v>10.55159984490011</v>
+        <v>10.55159984490016</v>
       </c>
       <c r="H6" t="n">
-        <v>9.996305852455237</v>
+        <v>9.996305852455242</v>
       </c>
       <c r="I6" t="n">
-        <v>8.853045023734458</v>
+        <v>8.853045023734468</v>
       </c>
       <c r="J6" t="n">
-        <v>10.58406464552422</v>
+        <v>10.58406464552424</v>
       </c>
       <c r="K6" t="n">
-        <v>8.991431781834665</v>
+        <v>8.991431781834676</v>
       </c>
       <c r="L6" t="n">
-        <v>10.71102262137154</v>
+        <v>10.71102262137156</v>
       </c>
       <c r="M6" t="n">
-        <v>12.78060857390006</v>
+        <v>12.78060857390009</v>
       </c>
       <c r="N6" t="n">
-        <v>72.47327460659888</v>
+        <v>10.13631910134104</v>
       </c>
       <c r="O6" t="n">
-        <v>11.13140019949808</v>
+        <v>11.1314001994981</v>
       </c>
       <c r="P6" t="n">
-        <v>12.58817639565519</v>
+        <v>12.58817639565523</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.307175270028671</v>
+        <v>9.30717527002869</v>
       </c>
       <c r="R6" t="n">
-        <v>9.144430360861831</v>
+        <v>9.144430360861833</v>
       </c>
       <c r="S6" t="n">
-        <v>10.20633626577295</v>
+        <v>10.20633626577298</v>
       </c>
       <c r="T6" t="n">
-        <v>9.85197591181441</v>
+        <v>9.851975911814435</v>
       </c>
       <c r="U6" t="n">
-        <v>11.17383857081795</v>
+        <v>11.17383857081796</v>
       </c>
       <c r="V6" t="n">
-        <v>11.2578426660512</v>
+        <v>11.25784266605123</v>
       </c>
       <c r="W6" t="n">
-        <v>12.78880787186334</v>
+        <v>12.78880787186336</v>
       </c>
       <c r="X6" t="n">
-        <v>10.87933613251355</v>
+        <v>10.87933613251356</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.41513176586591</v>
+        <v>13.41513176586596</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.389255792640165</v>
+        <v>9.389255792640183</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.748348790300998</v>
+        <v>9.748348790301026</v>
       </c>
       <c r="AB6" t="n">
-        <v>13.49643704621865</v>
+        <v>13.49643704621867</v>
       </c>
     </row>
   </sheetData>
@@ -2970,58 +2970,58 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.40229984714903</v>
+        <v>39.402299847149</v>
       </c>
       <c r="C2" t="n">
         <v>42.28684474596504</v>
       </c>
       <c r="D2" t="n">
-        <v>39.42617232903944</v>
+        <v>39.42617232903939</v>
       </c>
       <c r="E2" t="n">
-        <v>39.29138089092766</v>
+        <v>39.29138089092764</v>
       </c>
       <c r="F2" t="n">
-        <v>39.46555212863839</v>
+        <v>39.46555212863829</v>
       </c>
       <c r="G2" t="n">
-        <v>39.53549423107179</v>
+        <v>39.53549423107176</v>
       </c>
       <c r="H2" t="n">
-        <v>39.49145730862978</v>
+        <v>39.49145730862975</v>
       </c>
       <c r="I2" t="n">
-        <v>39.4629773018916</v>
+        <v>39.46297730189153</v>
       </c>
       <c r="J2" t="n">
-        <v>39.54147872806415</v>
+        <v>39.54147872806411</v>
       </c>
       <c r="K2" t="n">
         <v>39.52047775178142</v>
       </c>
       <c r="L2" t="n">
-        <v>39.58532508912371</v>
+        <v>39.58532508912367</v>
       </c>
       <c r="M2" t="n">
-        <v>39.71387402801871</v>
+        <v>39.71387402801868</v>
       </c>
       <c r="N2" t="n">
-        <v>39.48768476427374</v>
+        <v>39.4876847642737</v>
       </c>
       <c r="O2" t="n">
-        <v>43.41806553734956</v>
+        <v>43.41806553734948</v>
       </c>
       <c r="P2" t="n">
-        <v>39.64963022905432</v>
+        <v>39.64963022905429</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.4846945757432</v>
+        <v>39.48469457574319</v>
       </c>
       <c r="R2" t="n">
-        <v>39.45743895266399</v>
+        <v>39.45743895266396</v>
       </c>
       <c r="S2" t="n">
-        <v>39.55638604481056</v>
+        <v>39.55638604481051</v>
       </c>
       <c r="T2" t="n">
         <v>39.52131729496416</v>
@@ -3030,22 +3030,22 @@
         <v>43.05025252167518</v>
       </c>
       <c r="V2" t="n">
-        <v>39.49127146467005</v>
+        <v>39.49127146467003</v>
       </c>
       <c r="W2" t="n">
-        <v>45.66318568060084</v>
+        <v>45.66318568060087</v>
       </c>
       <c r="X2" t="n">
-        <v>39.61507622412891</v>
+        <v>39.61507622412886</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.75994225623116</v>
+        <v>39.75994225623112</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.62662872427287</v>
+        <v>40.62662872427283</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.52231334501177</v>
+        <v>39.52231334501174</v>
       </c>
       <c r="AB2" t="n">
         <v>39.77089343814576</v>
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.8616973650749</v>
+        <v>41.42459523753416</v>
       </c>
       <c r="C3" t="n">
-        <v>46.37435180071644</v>
+        <v>43.91077381091618</v>
       </c>
       <c r="D3" t="n">
-        <v>45.4872499308226</v>
+        <v>41.67988869655568</v>
       </c>
       <c r="E3" t="n">
-        <v>41.08389860024037</v>
+        <v>39.3443061613406</v>
       </c>
       <c r="F3" t="n">
-        <v>46.43381862055186</v>
+        <v>42.02024323771404</v>
       </c>
       <c r="G3" t="n">
-        <v>47.92976595930082</v>
+        <v>42.44425158697193</v>
       </c>
       <c r="H3" t="n">
-        <v>47.05991938393017</v>
+        <v>42.29794190254182</v>
       </c>
       <c r="I3" t="n">
-        <v>46.3596190619517</v>
+        <v>42.00864952220623</v>
       </c>
       <c r="J3" t="n">
-        <v>48.1238820373846</v>
+        <v>42.55212440691483</v>
       </c>
       <c r="K3" t="n">
-        <v>47.66975140003831</v>
+        <v>42.36724842889514</v>
       </c>
       <c r="L3" t="n">
-        <v>49.12607883956819</v>
+        <v>42.89248056445566</v>
       </c>
       <c r="M3" t="n">
-        <v>52.21848046893108</v>
+        <v>44.00553652719233</v>
       </c>
       <c r="N3" t="n">
-        <v>46.90208637157084</v>
+        <v>42.19352822909084</v>
       </c>
       <c r="O3" t="n">
-        <v>51.23389536197095</v>
+        <v>46.14468396602596</v>
       </c>
       <c r="P3" t="n">
-        <v>50.53646878863888</v>
+        <v>43.3187938411424</v>
       </c>
       <c r="Q3" t="n">
-        <v>46.83587285689695</v>
+        <v>42.12679767151796</v>
       </c>
       <c r="R3" t="n">
-        <v>46.24433169761532</v>
+        <v>41.99423254999627</v>
       </c>
       <c r="S3" t="n">
-        <v>48.43133432458484</v>
+        <v>42.63520011179178</v>
       </c>
       <c r="T3" t="n">
-        <v>47.71757155348195</v>
+        <v>42.49540807153754</v>
       </c>
       <c r="U3" t="n">
-        <v>52.80877084395329</v>
+        <v>46.39898991796476</v>
       </c>
       <c r="V3" t="n">
-        <v>46.91528262671462</v>
+        <v>42.0874686002627</v>
       </c>
       <c r="W3" t="n">
-        <v>58.43418701146225</v>
+        <v>50.04851894467205</v>
       </c>
       <c r="X3" t="n">
-        <v>49.88572926424559</v>
+        <v>43.18683244792719</v>
       </c>
       <c r="Y3" t="n">
-        <v>53.21523183928389</v>
+        <v>44.37310567353511</v>
       </c>
       <c r="Z3" t="n">
-        <v>46.73038920349786</v>
+        <v>42.79949894869445</v>
       </c>
       <c r="AA3" t="n">
-        <v>47.6902087725018</v>
+        <v>42.45600353951443</v>
       </c>
       <c r="AB3" t="n">
-        <v>53.47611910915843</v>
+        <v>44.56975301117571</v>
       </c>
     </row>
     <row r="4">
@@ -3146,37 +3146,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.59129830237012</v>
+        <v>41.59129830237014</v>
       </c>
       <c r="C4" t="n">
-        <v>32.16568100909707</v>
+        <v>32.16568100909711</v>
       </c>
       <c r="D4" t="n">
-        <v>50.63936213967522</v>
+        <v>50.63936213967534</v>
       </c>
       <c r="E4" t="n">
-        <v>22.23507786872353</v>
+        <v>22.23507786872352</v>
       </c>
       <c r="F4" t="n">
-        <v>60.19302235405971</v>
+        <v>60.19302235405972</v>
       </c>
       <c r="G4" t="n">
-        <v>65.14919456733895</v>
+        <v>65.14919456733865</v>
       </c>
       <c r="H4" t="n">
-        <v>70.13798840306731</v>
+        <v>70.13798840306727</v>
       </c>
       <c r="I4" t="n">
-        <v>60.31353571472421</v>
+        <v>60.31353571472424</v>
       </c>
       <c r="J4" t="n">
-        <v>70.34993495718464</v>
+        <v>70.34993495718463</v>
       </c>
       <c r="K4" t="n">
-        <v>64.94703320071328</v>
+        <v>64.94703320071325</v>
       </c>
       <c r="L4" t="n">
-        <v>78.43604250803487</v>
+        <v>78.43604250803489</v>
       </c>
       <c r="M4" t="n">
         <v>109.9689854470566</v>
@@ -3185,46 +3185,46 @@
         <v>64.43378084464533</v>
       </c>
       <c r="O4" t="n">
-        <v>59.88610886641756</v>
+        <v>59.88610886641752</v>
       </c>
       <c r="P4" t="n">
-        <v>85.42415542791949</v>
+        <v>85.42415542791959</v>
       </c>
       <c r="Q4" t="n">
-        <v>60.91410622992889</v>
+        <v>60.91410622992885</v>
       </c>
       <c r="R4" t="n">
-        <v>61.22141748885845</v>
+        <v>61.22141748885846</v>
       </c>
       <c r="S4" t="n">
-        <v>70.92594642637475</v>
+        <v>70.92594642637469</v>
       </c>
       <c r="T4" t="n">
-        <v>73.34519813266149</v>
+        <v>73.34519813266152</v>
       </c>
       <c r="U4" t="n">
-        <v>78.42634863372048</v>
+        <v>78.42634863372025</v>
       </c>
       <c r="V4" t="n">
-        <v>56.08308095878168</v>
+        <v>56.08308095878176</v>
       </c>
       <c r="W4" t="n">
-        <v>111.8260152093261</v>
+        <v>111.826015209326</v>
       </c>
       <c r="X4" t="n">
-        <v>88.12085034749745</v>
+        <v>88.1208503474974</v>
       </c>
       <c r="Y4" t="n">
-        <v>119.0184858133741</v>
+        <v>119.0184858133739</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.74303094989114</v>
+        <v>43.74303094989109</v>
       </c>
       <c r="AA4" t="n">
-        <v>70.39461404088416</v>
+        <v>70.39461404088428</v>
       </c>
       <c r="AB4" t="n">
-        <v>129.4428369150716</v>
+        <v>129.4428369150715</v>
       </c>
     </row>
     <row r="5">
@@ -3234,85 +3234,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.308581705033968</v>
+        <v>5.308581705033983</v>
       </c>
       <c r="C5" t="n">
-        <v>5.61507004042719</v>
+        <v>5.615070040427197</v>
       </c>
       <c r="D5" t="n">
-        <v>6.611073636307697</v>
+        <v>6.611073636307728</v>
       </c>
       <c r="E5" t="n">
-        <v>4.538584828510337</v>
+        <v>4.538584828510306</v>
       </c>
       <c r="F5" t="n">
-        <v>6.183949920031102</v>
+        <v>6.183949920031123</v>
       </c>
       <c r="G5" t="n">
-        <v>8.060081175153634</v>
+        <v>8.060081175153647</v>
       </c>
       <c r="H5" t="n">
-        <v>7.348497513354909</v>
+        <v>7.348497513354911</v>
       </c>
       <c r="I5" t="n">
-        <v>7.026802735796965</v>
+        <v>7.026802735796958</v>
       </c>
       <c r="J5" t="n">
-        <v>7.914251193916879</v>
+        <v>7.914251193916922</v>
       </c>
       <c r="K5" t="n">
-        <v>7.676296768816566</v>
+        <v>7.676296768816575</v>
       </c>
       <c r="L5" t="n">
         <v>8.408777275346102</v>
       </c>
       <c r="M5" t="n">
-        <v>9.850906794869829</v>
+        <v>9.850906794869839</v>
       </c>
       <c r="N5" t="n">
-        <v>64.43378084464533</v>
+        <v>6.50526011699051</v>
       </c>
       <c r="O5" t="n">
-        <v>6.974100992485468</v>
+        <v>6.974100992485434</v>
       </c>
       <c r="P5" t="n">
-        <v>8.500595394147432</v>
+        <v>8.500595394147409</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.036291186003615</v>
+        <v>6.036291186003583</v>
       </c>
       <c r="R5" t="n">
-        <v>6.964244533503939</v>
+        <v>6.964244533503917</v>
       </c>
       <c r="S5" t="n">
-        <v>8.081897457210967</v>
+        <v>8.081897457210937</v>
       </c>
       <c r="T5" t="n">
-        <v>7.685779795274277</v>
+        <v>7.685779795274289</v>
       </c>
       <c r="U5" t="n">
-        <v>8.015180824938065</v>
+        <v>8.015180824938081</v>
       </c>
       <c r="V5" t="n">
         <v>7.061948728286142</v>
       </c>
       <c r="W5" t="n">
-        <v>10.04264170114486</v>
+        <v>10.0426417011448</v>
       </c>
       <c r="X5" t="n">
-        <v>7.603673836586981</v>
+        <v>7.603673836587008</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.39747121888711</v>
+        <v>11.39747121888713</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.620614053379189</v>
+        <v>5.620614053379164</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.697030638767694</v>
+        <v>7.697030638767724</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.545815589359</v>
+        <v>11.54581558935894</v>
       </c>
     </row>
     <row r="6">
@@ -3322,61 +3322,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.128513639403465</v>
+        <v>7.128513639403434</v>
       </c>
       <c r="C6" t="n">
-        <v>7.355019958714119</v>
+        <v>7.355019958714111</v>
       </c>
       <c r="D6" t="n">
-        <v>8.351023554594663</v>
+        <v>8.351023554594645</v>
       </c>
       <c r="E6" t="n">
-        <v>6.608576226095287</v>
+        <v>6.608576226095274</v>
       </c>
       <c r="F6" t="n">
-        <v>6.599235873893238</v>
+        <v>6.599235873893209</v>
       </c>
       <c r="G6" t="n">
-        <v>9.585864729178983</v>
+        <v>9.585864729178974</v>
       </c>
       <c r="H6" t="n">
-        <v>9.088447431641832</v>
+        <v>9.088447431641837</v>
       </c>
       <c r="I6" t="n">
-        <v>8.766752654083879</v>
+        <v>8.766752654083884</v>
       </c>
       <c r="J6" t="n">
-        <v>9.654201112203836</v>
+        <v>9.654201112203843</v>
       </c>
       <c r="K6" t="n">
-        <v>9.416246687103481</v>
+        <v>9.416246687103511</v>
       </c>
       <c r="L6" t="n">
-        <v>10.148727193633</v>
+        <v>10.14872719363302</v>
       </c>
       <c r="M6" t="n">
-        <v>11.59085671315396</v>
+        <v>11.59085671315398</v>
       </c>
       <c r="N6" t="n">
-        <v>64.43378084464533</v>
+        <v>9.045834807684081</v>
       </c>
       <c r="O6" t="n">
-        <v>9.610433353358903</v>
+        <v>9.610433353358879</v>
       </c>
       <c r="P6" t="n">
-        <v>11.25953556883934</v>
+        <v>11.25953556883931</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.012059253246612</v>
+        <v>9.012059253246596</v>
       </c>
       <c r="R6" t="n">
-        <v>8.704194451790855</v>
+        <v>8.704194451790841</v>
       </c>
       <c r="S6" t="n">
-        <v>9.82184737549783</v>
+        <v>9.821847375497859</v>
       </c>
       <c r="T6" t="n">
-        <v>9.4257297135612</v>
+        <v>9.425729713561202</v>
       </c>
       <c r="U6" t="n">
         <v>10.26545347559737</v>
@@ -3385,22 +3385,22 @@
         <v>10.19061334638347</v>
       </c>
       <c r="W6" t="n">
-        <v>11.78238863784617</v>
+        <v>11.78238863784618</v>
       </c>
       <c r="X6" t="n">
-        <v>10.48477994971512</v>
+        <v>10.48477994971514</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.12110842397738</v>
+        <v>12.12110842397739</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.83810139858586</v>
+        <v>7.83810139858584</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.436980557054634</v>
+        <v>9.436980557054637</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.20687644129688</v>
+        <v>12.20687644129685</v>
       </c>
     </row>
   </sheetData>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.11736658890638</v>
+        <v>39.11736658890639</v>
       </c>
       <c r="C2" t="n">
         <v>42.02797194376198</v>
@@ -3575,22 +3575,22 @@
         <v>39.16080360367553</v>
       </c>
       <c r="E2" t="n">
-        <v>39.21948685685312</v>
+        <v>39.21948685685314</v>
       </c>
       <c r="F2" t="n">
-        <v>39.13020642708543</v>
+        <v>39.13020642708545</v>
       </c>
       <c r="G2" t="n">
         <v>39.2810299977273</v>
       </c>
       <c r="H2" t="n">
-        <v>39.26314347483208</v>
+        <v>39.26314347483207</v>
       </c>
       <c r="I2" t="n">
-        <v>39.17361499248706</v>
+        <v>39.17361499248708</v>
       </c>
       <c r="J2" t="n">
-        <v>39.32285351237704</v>
+        <v>39.32285351237702</v>
       </c>
       <c r="K2" t="n">
         <v>39.23528983465501</v>
@@ -3599,49 +3599,49 @@
         <v>39.28028845189269</v>
       </c>
       <c r="M2" t="n">
-        <v>39.36596206362768</v>
+        <v>39.36596206362766</v>
       </c>
       <c r="N2" t="n">
         <v>39.41180800365768</v>
       </c>
       <c r="O2" t="n">
-        <v>43.34806907907065</v>
+        <v>43.34806907907062</v>
       </c>
       <c r="P2" t="n">
-        <v>39.55076069222368</v>
+        <v>39.55076069222367</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.25629382556942</v>
+        <v>39.25629382556946</v>
       </c>
       <c r="R2" t="n">
-        <v>39.18348549480665</v>
+        <v>39.18348549480663</v>
       </c>
       <c r="S2" t="n">
-        <v>39.23772672031199</v>
+        <v>39.237726720312</v>
       </c>
       <c r="T2" t="n">
-        <v>39.29886347308049</v>
+        <v>39.2988634730805</v>
       </c>
       <c r="U2" t="n">
-        <v>42.93372024172585</v>
+        <v>42.93372024172584</v>
       </c>
       <c r="V2" t="n">
         <v>39.34021300478314</v>
       </c>
       <c r="W2" t="n">
-        <v>45.73909729389911</v>
+        <v>45.73909729389908</v>
       </c>
       <c r="X2" t="n">
-        <v>39.27876989296983</v>
+        <v>39.27876989296981</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.61701814569648</v>
+        <v>39.6170181456965</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.5474095088241</v>
+        <v>40.54740950882408</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.28214032850572</v>
+        <v>39.28214032850574</v>
       </c>
       <c r="AB2" t="n">
         <v>39.47046598589618</v>
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.2106369375872</v>
+        <v>40.14063808005611</v>
       </c>
       <c r="C3" t="n">
-        <v>43.43581869929746</v>
+        <v>42.84924830731952</v>
       </c>
       <c r="D3" t="n">
-        <v>42.24594106070192</v>
+        <v>40.51766165693556</v>
       </c>
       <c r="E3" t="n">
-        <v>42.36148590293067</v>
+        <v>39.74894672702297</v>
       </c>
       <c r="F3" t="n">
-        <v>41.53868620584002</v>
+        <v>40.26946421601249</v>
       </c>
       <c r="G3" t="n">
-        <v>44.97566504870083</v>
+        <v>41.37146905685767</v>
       </c>
       <c r="H3" t="n">
-        <v>44.66463097521348</v>
+        <v>41.38188163225063</v>
       </c>
       <c r="I3" t="n">
-        <v>42.54980815673969</v>
+        <v>40.62735264670748</v>
       </c>
       <c r="J3" t="n">
-        <v>45.9682637888757</v>
+        <v>41.73845204512639</v>
       </c>
       <c r="K3" t="n">
-        <v>43.97357869816518</v>
+        <v>41.07371751362363</v>
       </c>
       <c r="L3" t="n">
-        <v>44.98379847057984</v>
+        <v>41.38229807492464</v>
       </c>
       <c r="M3" t="n">
-        <v>47.06380202694158</v>
+        <v>42.11660681919624</v>
       </c>
       <c r="N3" t="n">
-        <v>48.07099888197543</v>
+        <v>42.50262549094771</v>
       </c>
       <c r="O3" t="n">
-        <v>52.36894551766598</v>
+        <v>46.45760798515536</v>
       </c>
       <c r="P3" t="n">
-        <v>51.17306271196018</v>
+        <v>43.51751342792466</v>
       </c>
       <c r="Q3" t="n">
-        <v>44.46067521609002</v>
+        <v>41.25552961070112</v>
       </c>
       <c r="R3" t="n">
-        <v>42.78684945391319</v>
+        <v>40.71838078412162</v>
       </c>
       <c r="S3" t="n">
-        <v>43.98544985750901</v>
+        <v>41.02679530683206</v>
       </c>
       <c r="T3" t="n">
-        <v>45.46753123430535</v>
+        <v>41.60980764538076</v>
       </c>
       <c r="U3" t="n">
-        <v>52.053541175787</v>
+        <v>46.13346778580092</v>
       </c>
       <c r="V3" t="n">
-        <v>46.34686325202973</v>
+        <v>41.85047315051732</v>
       </c>
       <c r="W3" t="n">
-        <v>61.87671824103472</v>
+        <v>51.21028402030421</v>
       </c>
       <c r="X3" t="n">
-        <v>44.99425148081787</v>
+        <v>41.4650501053862</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.82449807972147</v>
+        <v>44.137788331617</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.06314163784131</v>
+        <v>42.90290141312997</v>
       </c>
       <c r="AA3" t="n">
-        <v>45.04708937232439</v>
+        <v>41.47575410974102</v>
       </c>
       <c r="AB3" t="n">
-        <v>49.43736527687696</v>
+        <v>43.0432446798908</v>
       </c>
     </row>
     <row r="4">
@@ -3742,85 +3742,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.46315729707665</v>
+        <v>14.46315729707666</v>
       </c>
       <c r="C4" t="n">
-        <v>9.07944380908347</v>
+        <v>9.079443809083495</v>
       </c>
       <c r="D4" t="n">
-        <v>25.86814530430744</v>
+        <v>25.86814530430746</v>
       </c>
       <c r="E4" t="n">
-        <v>37.21446953508682</v>
+        <v>37.21446953508678</v>
       </c>
       <c r="F4" t="n">
         <v>19.06879900669961</v>
       </c>
       <c r="G4" t="n">
-        <v>43.78714658443644</v>
+        <v>43.78714658443634</v>
       </c>
       <c r="H4" t="n">
-        <v>51.01310147078889</v>
+        <v>51.01310147078881</v>
       </c>
       <c r="I4" t="n">
-        <v>29.12407518216412</v>
+        <v>29.12407518216415</v>
       </c>
       <c r="J4" t="n">
-        <v>55.06662753162171</v>
+        <v>55.06662753162169</v>
       </c>
       <c r="K4" t="n">
-        <v>38.88969466038913</v>
+        <v>38.88969466038915</v>
       </c>
       <c r="L4" t="n">
-        <v>44.81225111692608</v>
+        <v>44.81225111692609</v>
       </c>
       <c r="M4" t="n">
         <v>66.36113379817189</v>
       </c>
       <c r="N4" t="n">
-        <v>77.87045139006486</v>
+        <v>77.8704513900648</v>
       </c>
       <c r="O4" t="n">
-        <v>73.22910656333853</v>
+        <v>73.22910656333855</v>
       </c>
       <c r="P4" t="n">
-        <v>100.7216206812504</v>
+        <v>100.7216206812506</v>
       </c>
       <c r="Q4" t="n">
-        <v>44.39048686592095</v>
+        <v>44.39048686592086</v>
       </c>
       <c r="R4" t="n">
         <v>32.10425667764093</v>
       </c>
       <c r="S4" t="n">
-        <v>34.62855449390884</v>
+        <v>34.62855449390889</v>
       </c>
       <c r="T4" t="n">
-        <v>54.46797435564463</v>
+        <v>54.4679743556446</v>
       </c>
       <c r="U4" t="n">
-        <v>79.11291386004123</v>
+        <v>79.11291386004152</v>
       </c>
       <c r="V4" t="n">
-        <v>56.86332771979501</v>
+        <v>56.86332771979498</v>
       </c>
       <c r="W4" t="n">
-        <v>151.3072684032783</v>
+        <v>151.3072684032782</v>
       </c>
       <c r="X4" t="n">
-        <v>51.35068456921948</v>
+        <v>51.35068456921959</v>
       </c>
       <c r="Y4" t="n">
-        <v>121.3022906786878</v>
+        <v>121.3022906786877</v>
       </c>
       <c r="Z4" t="n">
-        <v>52.12797686575178</v>
+        <v>52.1279768657518</v>
       </c>
       <c r="AA4" t="n">
-        <v>50.92466107485147</v>
+        <v>50.92466107485139</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.11245607556032</v>
+        <v>96.11245607556029</v>
       </c>
     </row>
     <row r="5">
@@ -3830,85 +3830,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.495452335035148</v>
+        <v>3.495452335035157</v>
       </c>
       <c r="C5" t="n">
-        <v>4.162096297947445</v>
+        <v>4.162096297947443</v>
       </c>
       <c r="D5" t="n">
-        <v>5.009600172820272</v>
+        <v>5.009600172820262</v>
       </c>
       <c r="E5" t="n">
-        <v>5.127467347831608</v>
+        <v>5.127467347831598</v>
       </c>
       <c r="F5" t="n">
-        <v>3.79993460710721</v>
+        <v>3.799934607107219</v>
       </c>
       <c r="G5" t="n">
-        <v>6.579843397494376</v>
+        <v>6.579843397494374</v>
       </c>
       <c r="H5" t="n">
-        <v>6.165576096200506</v>
+        <v>6.165576096200493</v>
       </c>
       <c r="I5" t="n">
-        <v>5.154310702976742</v>
+        <v>5.154310702976732</v>
       </c>
       <c r="J5" t="n">
-        <v>6.84130900282944</v>
+        <v>6.841309002829445</v>
       </c>
       <c r="K5" t="n">
-        <v>5.850956417093241</v>
+        <v>5.850956417093245</v>
       </c>
       <c r="L5" t="n">
-        <v>6.359236499179134</v>
+        <v>6.359236499179121</v>
       </c>
       <c r="M5" t="n">
-        <v>7.335686344379159</v>
+        <v>7.335686344379144</v>
       </c>
       <c r="N5" t="n">
-        <v>77.87045139006486</v>
+        <v>7.051421359175551</v>
       </c>
       <c r="O5" t="n">
-        <v>7.503489911675898</v>
+        <v>7.503489911675906</v>
       </c>
       <c r="P5" t="n">
-        <v>8.785541612207137</v>
+        <v>8.785541612207155</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.8635569417605</v>
+        <v>4.863556941760502</v>
       </c>
       <c r="R5" t="n">
-        <v>5.265802567331471</v>
+        <v>5.265802567331475</v>
       </c>
       <c r="S5" t="n">
-        <v>5.878482161611453</v>
+        <v>5.878482161611447</v>
       </c>
       <c r="T5" t="n">
-        <v>6.569049908427436</v>
+        <v>6.569049908427445</v>
       </c>
       <c r="U5" t="n">
-        <v>7.599380767682263</v>
+        <v>7.599380767682238</v>
       </c>
       <c r="V5" t="n">
         <v>6.760718965888596</v>
       </c>
       <c r="W5" t="n">
-        <v>11.66099504457728</v>
+        <v>11.6609950445773</v>
       </c>
       <c r="X5" t="n">
-        <v>5.211240891166754</v>
+        <v>5.211240891166756</v>
       </c>
       <c r="Y5" t="n">
         <v>11.17420375227185</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.743754660284417</v>
+        <v>5.743754660284418</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.380154297428773</v>
+        <v>6.380154297428748</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.555486220784495</v>
+        <v>9.55548622078449</v>
       </c>
     </row>
     <row r="6">
@@ -3918,82 +3918,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.730837826007539</v>
+        <v>5.730837826007521</v>
       </c>
       <c r="C6" t="n">
-        <v>6.437666769219241</v>
+        <v>6.437666769219261</v>
       </c>
       <c r="D6" t="n">
-        <v>7.285170644092071</v>
+        <v>7.285170644092084</v>
       </c>
       <c r="E6" t="n">
-        <v>7.702529586045961</v>
+        <v>7.702529586045973</v>
       </c>
       <c r="F6" t="n">
-        <v>4.487461113784894</v>
+        <v>4.487461113784881</v>
       </c>
       <c r="G6" t="n">
-        <v>8.643183487593028</v>
+        <v>8.643183487593046</v>
       </c>
       <c r="H6" t="n">
-        <v>8.441146567472309</v>
+        <v>8.441146567472323</v>
       </c>
       <c r="I6" t="n">
-        <v>7.429881174248543</v>
+        <v>7.429881174248552</v>
       </c>
       <c r="J6" t="n">
-        <v>9.116879474101257</v>
+        <v>9.116879474101262</v>
       </c>
       <c r="K6" t="n">
-        <v>8.126526888365074</v>
+        <v>8.126526888365063</v>
       </c>
       <c r="L6" t="n">
-        <v>8.63480697045093</v>
+        <v>8.634806970450942</v>
       </c>
       <c r="M6" t="n">
-        <v>9.611256815649496</v>
+        <v>9.611256815649501</v>
       </c>
       <c r="N6" t="n">
-        <v>77.87045139006486</v>
+        <v>10.12038080961909</v>
       </c>
       <c r="O6" t="n">
         <v>10.70692579075125</v>
       </c>
       <c r="P6" t="n">
-        <v>12.11908600540687</v>
+        <v>12.11908600540688</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.363777043868499</v>
+        <v>8.363777043868515</v>
       </c>
       <c r="R6" t="n">
-        <v>7.54137303860329</v>
+        <v>7.541373038603295</v>
       </c>
       <c r="S6" t="n">
-        <v>8.154052632883252</v>
+        <v>8.154052632883271</v>
       </c>
       <c r="T6" t="n">
-        <v>8.844620379699263</v>
+        <v>8.844620379699268</v>
       </c>
       <c r="U6" t="n">
         <v>10.37813489692285</v>
       </c>
       <c r="V6" t="n">
-        <v>10.54750337292385</v>
+        <v>10.54750337292386</v>
       </c>
       <c r="W6" t="n">
-        <v>13.93636436899667</v>
+        <v>13.93636436899669</v>
       </c>
       <c r="X6" t="n">
-        <v>8.617654148845183</v>
+        <v>8.617654148845196</v>
       </c>
       <c r="Y6" t="n">
         <v>12.43832376527709</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.420532693635916</v>
+        <v>8.420532693635945</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.655724768700566</v>
+        <v>8.655724768700569</v>
       </c>
       <c r="AB6" t="n">
         <v>10.76191828385859</v>
@@ -4162,73 +4162,73 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.84110052853847</v>
+        <v>38.84110052853843</v>
       </c>
       <c r="C2" t="n">
-        <v>41.81414835615186</v>
+        <v>41.81414835615185</v>
       </c>
       <c r="D2" t="n">
         <v>38.85898391116449</v>
       </c>
       <c r="E2" t="n">
-        <v>38.88616051505191</v>
+        <v>38.88616051505192</v>
       </c>
       <c r="F2" t="n">
-        <v>38.91485707994929</v>
+        <v>38.9148570799493</v>
       </c>
       <c r="G2" t="n">
-        <v>39.01420647941357</v>
+        <v>39.01420647941355</v>
       </c>
       <c r="H2" t="n">
-        <v>38.99677271586014</v>
+        <v>38.99677271586013</v>
       </c>
       <c r="I2" t="n">
         <v>38.91026805556011</v>
       </c>
       <c r="J2" t="n">
-        <v>39.00482172994202</v>
+        <v>39.00482172994201</v>
       </c>
       <c r="K2" t="n">
         <v>38.89475621558115</v>
       </c>
       <c r="L2" t="n">
-        <v>38.85890656493245</v>
+        <v>38.85890656493242</v>
       </c>
       <c r="M2" t="n">
         <v>38.95219429021051</v>
       </c>
       <c r="N2" t="n">
-        <v>39.09711295903774</v>
+        <v>39.09711295903769</v>
       </c>
       <c r="O2" t="n">
-        <v>42.92789744264259</v>
+        <v>42.92789744264266</v>
       </c>
       <c r="P2" t="n">
-        <v>39.25366770777371</v>
+        <v>39.25366770777376</v>
       </c>
       <c r="Q2" t="n">
-        <v>38.91511037566392</v>
+        <v>38.91511037566393</v>
       </c>
       <c r="R2" t="n">
-        <v>38.8723475231527</v>
+        <v>38.87234752315271</v>
       </c>
       <c r="S2" t="n">
-        <v>38.94751390896922</v>
+        <v>38.94751390896918</v>
       </c>
       <c r="T2" t="n">
-        <v>38.99148373762934</v>
+        <v>38.99148373762932</v>
       </c>
       <c r="U2" t="n">
-        <v>42.38044922554329</v>
+        <v>42.3804492255433</v>
       </c>
       <c r="V2" t="n">
-        <v>39.03507686639818</v>
+        <v>39.03507686639819</v>
       </c>
       <c r="W2" t="n">
         <v>45.09614561926234</v>
       </c>
       <c r="X2" t="n">
-        <v>39.16568290971053</v>
+        <v>39.16568290971052</v>
       </c>
       <c r="Y2" t="n">
         <v>39.27489114213396</v>
@@ -4237,7 +4237,7 @@
         <v>40.04127110647179</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.09113099922039</v>
+        <v>39.09113099922038</v>
       </c>
       <c r="AB2" t="n">
         <v>39.09162841814027</v>
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.87751262996458</v>
+        <v>39.54789980716631</v>
       </c>
       <c r="C3" t="n">
-        <v>43.53479521483842</v>
+        <v>42.73652815159126</v>
       </c>
       <c r="D3" t="n">
-        <v>40.30026975860277</v>
+        <v>39.69488620064779</v>
       </c>
       <c r="E3" t="n">
-        <v>39.73048163397942</v>
+        <v>38.71904786449582</v>
       </c>
       <c r="F3" t="n">
-        <v>41.61200667501521</v>
+        <v>40.14501645565738</v>
       </c>
       <c r="G3" t="n">
-        <v>43.85836778814091</v>
+        <v>40.84291812621593</v>
       </c>
       <c r="H3" t="n">
-        <v>43.54052513364462</v>
+        <v>40.83713201686547</v>
       </c>
       <c r="I3" t="n">
-        <v>41.50036917882323</v>
+        <v>40.11218198046995</v>
       </c>
       <c r="J3" t="n">
-        <v>43.6638815511487</v>
+        <v>40.80741990656596</v>
       </c>
       <c r="K3" t="n">
-        <v>41.13119450514137</v>
+        <v>39.96811033049053</v>
       </c>
       <c r="L3" t="n">
-        <v>40.29073416803393</v>
+        <v>39.68050524013245</v>
       </c>
       <c r="M3" t="n">
-        <v>42.50457021642227</v>
+        <v>40.41393306672215</v>
       </c>
       <c r="N3" t="n">
-        <v>45.83126374872273</v>
+        <v>41.57547246845595</v>
       </c>
       <c r="O3" t="n">
-        <v>50.79688608147455</v>
+        <v>45.69236248688139</v>
       </c>
       <c r="P3" t="n">
-        <v>49.35974127730786</v>
+        <v>42.73965562341445</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.60185257730791</v>
+        <v>40.11752454623473</v>
       </c>
       <c r="R3" t="n">
-        <v>40.61651212055183</v>
+        <v>39.80963127945918</v>
       </c>
       <c r="S3" t="n">
-        <v>42.33035294511722</v>
+        <v>40.34463886859117</v>
       </c>
       <c r="T3" t="n">
-        <v>43.39131791572366</v>
+        <v>40.74288295685909</v>
       </c>
       <c r="U3" t="n">
-        <v>47.35432340583995</v>
+        <v>44.24869381802084</v>
       </c>
       <c r="V3" t="n">
-        <v>44.34557292922745</v>
+        <v>41.02392782954735</v>
       </c>
       <c r="W3" t="n">
-        <v>55.58987429159787</v>
+        <v>48.71664481083171</v>
       </c>
       <c r="X3" t="n">
-        <v>47.44396801978226</v>
+        <v>42.11336067162136</v>
       </c>
       <c r="Y3" t="n">
-        <v>49.95473829881146</v>
+        <v>43.02448435230468</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.34454941893271</v>
+        <v>41.42845542499575</v>
       </c>
       <c r="AA3" t="n">
-        <v>45.68336675799861</v>
+        <v>41.55140169661241</v>
       </c>
       <c r="AB3" t="n">
-        <v>45.69666284438541</v>
+        <v>41.55774238131877</v>
       </c>
     </row>
     <row r="4">
@@ -4338,58 +4338,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.651384244607909</v>
+        <v>4.651384244607917</v>
       </c>
       <c r="C4" t="n">
-        <v>10.89657151340767</v>
+        <v>10.89657151340766</v>
       </c>
       <c r="D4" t="n">
-        <v>8.484629535882394</v>
+        <v>8.484629535882384</v>
       </c>
       <c r="E4" t="n">
-        <v>13.75581254426255</v>
+        <v>13.75581254426257</v>
       </c>
       <c r="F4" t="n">
-        <v>19.85483650547702</v>
+        <v>19.85483650547701</v>
       </c>
       <c r="G4" t="n">
         <v>33.22254676525259</v>
       </c>
       <c r="H4" t="n">
-        <v>38.70877636638071</v>
+        <v>38.70877636638072</v>
       </c>
       <c r="I4" t="n">
-        <v>19.20874282594664</v>
+        <v>19.2087428259466</v>
       </c>
       <c r="J4" t="n">
-        <v>34.00674311525297</v>
+        <v>34.00674311525295</v>
       </c>
       <c r="K4" t="n">
-        <v>14.75825360141401</v>
+        <v>14.75825360141402</v>
       </c>
       <c r="L4" t="n">
-        <v>7.543453053581895</v>
+        <v>7.543453053581887</v>
       </c>
       <c r="M4" t="n">
         <v>24.97593013280341</v>
       </c>
       <c r="N4" t="n">
-        <v>54.45687528540243</v>
+        <v>54.45687528540247</v>
       </c>
       <c r="O4" t="n">
-        <v>58.90945202956329</v>
+        <v>58.9094520295633</v>
       </c>
       <c r="P4" t="n">
-        <v>79.9286460531217</v>
+        <v>79.92864605312177</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.91912017091835</v>
+        <v>17.91912017091838</v>
       </c>
       <c r="R4" t="n">
-        <v>11.68290131646638</v>
+        <v>11.68290131646639</v>
       </c>
       <c r="S4" t="n">
-        <v>22.25065975730334</v>
+        <v>22.25065975730335</v>
       </c>
       <c r="T4" t="n">
         <v>34.1528244538149</v>
@@ -4398,25 +4398,25 @@
         <v>34.47439524510256</v>
       </c>
       <c r="V4" t="n">
-        <v>38.35860638633738</v>
+        <v>38.35860638633735</v>
       </c>
       <c r="W4" t="n">
-        <v>85.12979796509448</v>
+        <v>85.12979796509445</v>
       </c>
       <c r="X4" t="n">
-        <v>67.41647837430664</v>
+        <v>67.41647837430675</v>
       </c>
       <c r="Y4" t="n">
-        <v>91.85516460792026</v>
+        <v>91.8551646079201</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.54372592605191</v>
+        <v>22.54372592605186</v>
       </c>
       <c r="AA4" t="n">
-        <v>54.89437060057029</v>
+        <v>54.89437060057035</v>
       </c>
       <c r="AB4" t="n">
-        <v>55.51108754720261</v>
+        <v>55.51108754720272</v>
       </c>
     </row>
     <row r="5">
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.424807500793552</v>
+        <v>2.424807500793553</v>
       </c>
       <c r="C5" t="n">
-        <v>3.561927194954585</v>
+        <v>3.561927194954577</v>
       </c>
       <c r="D5" t="n">
-        <v>3.419960696312538</v>
+        <v>3.419960696312522</v>
       </c>
       <c r="E5" t="n">
-        <v>3.304602809565455</v>
+        <v>3.30460280956545</v>
       </c>
       <c r="F5" t="n">
-        <v>3.38148551561129</v>
+        <v>3.38148551561128</v>
       </c>
       <c r="G5" t="n">
-        <v>5.337736278204945</v>
+        <v>5.337736278204936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.976348631331371</v>
+        <v>4.976348631331353</v>
       </c>
       <c r="I5" t="n">
-        <v>3.999238699132798</v>
+        <v>3.999238699132788</v>
       </c>
       <c r="J5" t="n">
-        <v>5.068468673329781</v>
+        <v>5.068468673329777</v>
       </c>
       <c r="K5" t="n">
-        <v>3.82402533077189</v>
+        <v>3.824025330771873</v>
       </c>
       <c r="L5" t="n">
-        <v>3.419087035040588</v>
+        <v>3.41908703504057</v>
       </c>
       <c r="M5" t="n">
-        <v>4.485862529910105</v>
+        <v>4.485862529910098</v>
       </c>
       <c r="N5" t="n">
-        <v>54.45687528540243</v>
+        <v>5.494912219511558</v>
       </c>
       <c r="O5" t="n">
-        <v>6.282670419732347</v>
+        <v>6.282670419732337</v>
       </c>
       <c r="P5" t="n">
-        <v>7.390813506923063</v>
+        <v>7.390813506923058</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.104910267944688</v>
+        <v>3.104910267944677</v>
       </c>
       <c r="R5" t="n">
-        <v>3.570908841284393</v>
+        <v>3.570908841284385</v>
       </c>
       <c r="S5" t="n">
-        <v>4.41994774732753</v>
+        <v>4.419947747327525</v>
       </c>
       <c r="T5" t="n">
-        <v>4.916607189164597</v>
+        <v>4.916607189164582</v>
       </c>
       <c r="U5" t="n">
-        <v>4.839971376361068</v>
+        <v>4.839971376361059</v>
       </c>
       <c r="V5" t="n">
-        <v>5.195618431249855</v>
+        <v>5.195618431249848</v>
       </c>
       <c r="W5" t="n">
-        <v>8.034967729454594</v>
+        <v>8.034967729454584</v>
       </c>
       <c r="X5" t="n">
-        <v>6.007936280032918</v>
+        <v>6.007936280032911</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.899620379656728</v>
+        <v>8.899620379656724</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.572592162704945</v>
+        <v>3.572592162704934</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.042168848840356</v>
+        <v>6.042168848840343</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.859594402242729</v>
+        <v>6.859594402242724</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.071502344645141</v>
+        <v>4.071502344645134</v>
       </c>
       <c r="C6" t="n">
-        <v>5.216093641494163</v>
+        <v>5.21609364149416</v>
       </c>
       <c r="D6" t="n">
-        <v>5.074127142852104</v>
+        <v>5.074127142852102</v>
       </c>
       <c r="E6" t="n">
         <v>5.196318958750513</v>
       </c>
       <c r="F6" t="n">
-        <v>3.859583536516256</v>
+        <v>3.85958353651626</v>
       </c>
       <c r="G6" t="n">
-        <v>6.827437811187479</v>
+        <v>6.827437811187461</v>
       </c>
       <c r="H6" t="n">
-        <v>6.630515077870941</v>
+        <v>6.63051507787094</v>
       </c>
       <c r="I6" t="n">
-        <v>5.653405145672371</v>
+        <v>5.65340514567237</v>
       </c>
       <c r="J6" t="n">
-        <v>6.722635119869364</v>
+        <v>6.722635119869357</v>
       </c>
       <c r="K6" t="n">
-        <v>5.478191777311457</v>
+        <v>5.478191777311455</v>
       </c>
       <c r="L6" t="n">
-        <v>5.073253481580155</v>
+        <v>5.07325348158015</v>
       </c>
       <c r="M6" t="n">
-        <v>6.140028976450033</v>
+        <v>6.140028976450036</v>
       </c>
       <c r="N6" t="n">
-        <v>54.45687528540243</v>
+        <v>7.763904283354639</v>
       </c>
       <c r="O6" t="n">
-        <v>8.648029204755723</v>
+        <v>8.648029204755709</v>
       </c>
       <c r="P6" t="n">
-        <v>9.855292133675018</v>
+        <v>9.855292133675004</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.708101732875047</v>
+        <v>5.708101732875037</v>
       </c>
       <c r="R6" t="n">
-        <v>5.225075287823972</v>
+        <v>5.225075287823965</v>
       </c>
       <c r="S6" t="n">
-        <v>6.074114193867112</v>
+        <v>6.074114193867109</v>
       </c>
       <c r="T6" t="n">
-        <v>6.570773635704159</v>
+        <v>6.570773635704166</v>
       </c>
       <c r="U6" t="n">
-        <v>6.885249680742944</v>
+        <v>6.885249680742952</v>
       </c>
       <c r="V6" t="n">
-        <v>7.994863448223681</v>
+        <v>7.994863448223674</v>
       </c>
       <c r="W6" t="n">
-        <v>9.688978299995025</v>
+        <v>9.688978299995016</v>
       </c>
       <c r="X6" t="n">
-        <v>8.538433419939734</v>
+        <v>8.53843341993973</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.771990643431369</v>
+        <v>9.771990643431355</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.551939184486626</v>
+        <v>5.551939184486617</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.696335295379928</v>
+        <v>7.696335295379931</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.685247094318848</v>
+        <v>7.685247094318855</v>
       </c>
     </row>
   </sheetData>
@@ -4758,85 +4758,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.69842104855337</v>
+        <v>38.69842104855334</v>
       </c>
       <c r="C2" t="n">
-        <v>41.65425171781188</v>
+        <v>41.6542517178119</v>
       </c>
       <c r="D2" t="n">
-        <v>38.74270031550382</v>
+        <v>38.7427003155038</v>
       </c>
       <c r="E2" t="n">
-        <v>38.69981335289961</v>
+        <v>38.69981335289958</v>
       </c>
       <c r="F2" t="n">
-        <v>38.81293843625952</v>
+        <v>38.81293843625949</v>
       </c>
       <c r="G2" t="n">
-        <v>38.79248497402528</v>
+        <v>38.79248497402523</v>
       </c>
       <c r="H2" t="n">
-        <v>38.84876433900504</v>
+        <v>38.84876433900503</v>
       </c>
       <c r="I2" t="n">
-        <v>38.76023842329508</v>
+        <v>38.76023842329506</v>
       </c>
       <c r="J2" t="n">
-        <v>38.81298169385916</v>
+        <v>38.81298169385913</v>
       </c>
       <c r="K2" t="n">
-        <v>38.76083091508</v>
+        <v>38.76083091507998</v>
       </c>
       <c r="L2" t="n">
-        <v>38.72410660973714</v>
+        <v>38.72410660973712</v>
       </c>
       <c r="M2" t="n">
-        <v>38.80849534294827</v>
+        <v>38.80849534294826</v>
       </c>
       <c r="N2" t="n">
-        <v>38.87042065432789</v>
+        <v>38.8704206543279</v>
       </c>
       <c r="O2" t="n">
-        <v>42.59541677849839</v>
+        <v>42.59541677849835</v>
       </c>
       <c r="P2" t="n">
-        <v>39.0583710184533</v>
+        <v>39.05837101845326</v>
       </c>
       <c r="Q2" t="n">
-        <v>38.74402912500834</v>
+        <v>38.7440291250083</v>
       </c>
       <c r="R2" t="n">
-        <v>38.72451168362059</v>
+        <v>38.7245116836206</v>
       </c>
       <c r="S2" t="n">
-        <v>38.8487733400217</v>
+        <v>38.84877334002167</v>
       </c>
       <c r="T2" t="n">
-        <v>38.83193812908843</v>
+        <v>38.83193812908838</v>
       </c>
       <c r="U2" t="n">
         <v>42.16541008459404</v>
       </c>
       <c r="V2" t="n">
-        <v>38.82723731838049</v>
+        <v>38.82723731838046</v>
       </c>
       <c r="W2" t="n">
         <v>44.68189194366754</v>
       </c>
       <c r="X2" t="n">
-        <v>39.05783965819829</v>
+        <v>39.05783965819825</v>
       </c>
       <c r="Y2" t="n">
-        <v>38.99777261879453</v>
+        <v>38.99777261879451</v>
       </c>
       <c r="Z2" t="n">
-        <v>39.78238877303496</v>
+        <v>39.78238877303492</v>
       </c>
       <c r="AA2" t="n">
-        <v>38.96640004457803</v>
+        <v>38.96640004457801</v>
       </c>
       <c r="AB2" t="n">
-        <v>38.90954941972047</v>
+        <v>38.90954941972043</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.7274488922892</v>
+        <v>39.40841065885533</v>
       </c>
       <c r="C3" t="n">
-        <v>43.07476990490462</v>
+        <v>42.48959951940503</v>
       </c>
       <c r="D3" t="n">
-        <v>40.76587571698736</v>
+        <v>39.76729671434425</v>
       </c>
       <c r="E3" t="n">
-        <v>38.58942164696582</v>
+        <v>38.25143183300437</v>
       </c>
       <c r="F3" t="n">
-        <v>42.41747503409124</v>
+        <v>40.34222370508142</v>
       </c>
       <c r="G3" t="n">
-        <v>41.89241454017123</v>
+        <v>40.12534660870676</v>
       </c>
       <c r="H3" t="n">
-        <v>43.26450151889761</v>
+        <v>40.64882319221284</v>
       </c>
       <c r="I3" t="n">
-        <v>41.17871858100126</v>
+        <v>39.91594099133966</v>
       </c>
       <c r="J3" t="n">
-        <v>42.38441245015363</v>
+        <v>40.30575002187811</v>
       </c>
       <c r="K3" t="n">
-        <v>41.18571284296001</v>
+        <v>39.90421585639022</v>
       </c>
       <c r="L3" t="n">
-        <v>40.3230461637884</v>
+        <v>39.60339026216608</v>
       </c>
       <c r="M3" t="n">
-        <v>42.31753740800933</v>
+        <v>40.2911518104471</v>
       </c>
       <c r="N3" t="n">
-        <v>43.7303154909745</v>
+        <v>40.78422340987657</v>
       </c>
       <c r="O3" t="n">
-        <v>48.66395569788062</v>
+        <v>44.82677302818536</v>
       </c>
       <c r="P3" t="n">
-        <v>47.99668916456819</v>
+        <v>42.165652608179</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.79283946330347</v>
+        <v>39.76910081872377</v>
       </c>
       <c r="R3" t="n">
-        <v>40.3456886068839</v>
+        <v>39.62934129368362</v>
       </c>
       <c r="S3" t="n">
-        <v>43.19611506588501</v>
+        <v>40.56062935035848</v>
       </c>
       <c r="T3" t="n">
-        <v>42.84980684696177</v>
+        <v>40.48612107315864</v>
       </c>
       <c r="U3" t="n">
-        <v>47.13426057466091</v>
+        <v>44.05569195349857</v>
       </c>
       <c r="V3" t="n">
-        <v>42.69596415548269</v>
+        <v>40.39782014526169</v>
       </c>
       <c r="W3" t="n">
-        <v>51.16485743093788</v>
+        <v>47.08643299658884</v>
       </c>
       <c r="X3" t="n">
-        <v>48.10319536732388</v>
+        <v>42.23286956159869</v>
       </c>
       <c r="Y3" t="n">
-        <v>46.68424237973832</v>
+        <v>41.82117951126367</v>
       </c>
       <c r="Z3" t="n">
-        <v>41.7019082809753</v>
+        <v>40.75640779347721</v>
       </c>
       <c r="AA3" t="n">
-        <v>45.95021475266629</v>
+        <v>41.55896202432405</v>
       </c>
       <c r="AB3" t="n">
-        <v>44.62516773286922</v>
+        <v>41.12863065644919</v>
       </c>
     </row>
     <row r="4">
@@ -4934,61 +4934,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.399795140028138</v>
+        <v>4.399795140028139</v>
       </c>
       <c r="C4" t="n">
-        <v>8.134303562983805</v>
+        <v>8.13430356298379</v>
       </c>
       <c r="D4" t="n">
-        <v>13.55948948465485</v>
+        <v>13.55948948465483</v>
       </c>
       <c r="E4" t="n">
-        <v>4.821254366178275</v>
+        <v>4.821254366178263</v>
       </c>
       <c r="F4" t="n">
-        <v>28.46677567318032</v>
+        <v>28.46677567318033</v>
       </c>
       <c r="G4" t="n">
-        <v>20.82407733455664</v>
+        <v>20.82407733455677</v>
       </c>
       <c r="H4" t="n">
-        <v>36.97288839910665</v>
+        <v>36.97288839910669</v>
       </c>
       <c r="I4" t="n">
-        <v>17.62770673272155</v>
+        <v>17.62770673272157</v>
       </c>
       <c r="J4" t="n">
-        <v>26.02046572266424</v>
+        <v>26.02046572266423</v>
       </c>
       <c r="K4" t="n">
-        <v>16.63489570976336</v>
+        <v>16.63489570976335</v>
       </c>
       <c r="L4" t="n">
-        <v>8.824045110424011</v>
+        <v>8.824045110424018</v>
       </c>
       <c r="M4" t="n">
-        <v>26.41785059502683</v>
+        <v>26.41785059502684</v>
       </c>
       <c r="N4" t="n">
-        <v>38.78370947956872</v>
+        <v>38.78370947956876</v>
       </c>
       <c r="O4" t="n">
-        <v>44.67510350745129</v>
+        <v>44.67510350745135</v>
       </c>
       <c r="P4" t="n">
-        <v>68.212007509191</v>
+        <v>68.21200750919094</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.22998503337263</v>
+        <v>13.22998503337264</v>
       </c>
       <c r="R4" t="n">
-        <v>10.43196967965579</v>
+        <v>10.43196967965568</v>
       </c>
       <c r="S4" t="n">
-        <v>31.0666871569923</v>
+        <v>31.06668715699234</v>
       </c>
       <c r="T4" t="n">
-        <v>31.72959900417788</v>
+        <v>31.7295990041779</v>
       </c>
       <c r="U4" t="n">
         <v>35.50389051221872</v>
@@ -4997,22 +4997,22 @@
         <v>27.41149308805947</v>
       </c>
       <c r="W4" t="n">
-        <v>51.81477758062948</v>
+        <v>51.81477758062956</v>
       </c>
       <c r="X4" t="n">
-        <v>72.79207099841851</v>
+        <v>72.79207099841847</v>
       </c>
       <c r="Y4" t="n">
-        <v>65.50258715389677</v>
+        <v>65.50258715389683</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.20478776676138</v>
+        <v>11.20478776676137</v>
       </c>
       <c r="AA4" t="n">
         <v>58.46915888520287</v>
       </c>
       <c r="AB4" t="n">
-        <v>49.19134626438401</v>
+        <v>49.19134626438398</v>
       </c>
     </row>
     <row r="5">
@@ -5025,79 +5025,79 @@
         <v>2.180242245445707</v>
       </c>
       <c r="C5" t="n">
-        <v>3.088247961100926</v>
+        <v>3.088247961100924</v>
       </c>
       <c r="D5" t="n">
-        <v>3.392725834848632</v>
+        <v>3.392725834848628</v>
       </c>
       <c r="E5" t="n">
-        <v>2.529003736732418</v>
+        <v>2.529003736732421</v>
       </c>
       <c r="F5" t="n">
-        <v>3.584741337489284</v>
+        <v>3.58474133748927</v>
       </c>
       <c r="G5" t="n">
-        <v>4.102772492600055</v>
+        <v>4.102772492600066</v>
       </c>
       <c r="H5" t="n">
-        <v>4.59076777215666</v>
+        <v>4.590767772156655</v>
       </c>
       <c r="I5" t="n">
-        <v>3.590826830279233</v>
+        <v>3.590826830279251</v>
       </c>
       <c r="J5" t="n">
-        <v>4.187742782057485</v>
+        <v>4.187742782057494</v>
       </c>
       <c r="K5" t="n">
-        <v>3.597519297549404</v>
+        <v>3.59751929754941</v>
       </c>
       <c r="L5" t="n">
-        <v>3.182701374686927</v>
+        <v>3.182701374686936</v>
       </c>
       <c r="M5" t="n">
-        <v>4.140436363409494</v>
+        <v>4.140436363409504</v>
       </c>
       <c r="N5" t="n">
-        <v>38.78370947956873</v>
+        <v>4.283211748559072</v>
       </c>
       <c r="O5" t="n">
-        <v>5.081224995439364</v>
+        <v>5.081224995439359</v>
       </c>
       <c r="P5" t="n">
-        <v>6.520744113945129</v>
+        <v>6.520744113945121</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.555417563104355</v>
+        <v>2.555417563104369</v>
       </c>
       <c r="R5" t="n">
-        <v>3.187276870543655</v>
+        <v>3.187276870543652</v>
       </c>
       <c r="S5" t="n">
-        <v>4.59086944278049</v>
+        <v>4.590869442780496</v>
       </c>
       <c r="T5" t="n">
-        <v>4.400707990708894</v>
+        <v>4.400707990708888</v>
       </c>
       <c r="U5" t="n">
-        <v>4.553730037548339</v>
+        <v>4.553730037548315</v>
       </c>
       <c r="V5" t="n">
-        <v>4.155687875934072</v>
+        <v>4.155687875934076</v>
       </c>
       <c r="W5" t="n">
-        <v>5.669002741926522</v>
+        <v>5.669002741926508</v>
       </c>
       <c r="X5" t="n">
-        <v>6.165338253950986</v>
+        <v>6.165338253950988</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.974860147363754</v>
+        <v>6.97486014736374</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.62379830906638</v>
+        <v>2.623798309066378</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.919517181701296</v>
+        <v>5.919517181701284</v>
       </c>
       <c r="AB5" t="n">
         <v>6.001870283305982</v>
@@ -5110,85 +5110,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.480306295189998</v>
+        <v>3.480306295189981</v>
       </c>
       <c r="C6" t="n">
-        <v>4.345565988008005</v>
+        <v>4.345565988008003</v>
       </c>
       <c r="D6" t="n">
-        <v>4.650043861755712</v>
+        <v>4.650043861755696</v>
       </c>
       <c r="E6" t="n">
-        <v>4.011078988422953</v>
+        <v>4.011078988422949</v>
       </c>
       <c r="F6" t="n">
-        <v>3.899844307763744</v>
+        <v>3.899844307763728</v>
       </c>
       <c r="G6" t="n">
-        <v>5.212384605421159</v>
+        <v>5.212384605421147</v>
       </c>
       <c r="H6" t="n">
-        <v>5.848085799063742</v>
+        <v>5.848085799063747</v>
       </c>
       <c r="I6" t="n">
-        <v>4.848144857186311</v>
+        <v>4.848144857186302</v>
       </c>
       <c r="J6" t="n">
         <v>5.445060808964564</v>
       </c>
       <c r="K6" t="n">
-        <v>4.854837324456486</v>
+        <v>4.85483732445649</v>
       </c>
       <c r="L6" t="n">
-        <v>4.440019401594006</v>
+        <v>4.440019401593998</v>
       </c>
       <c r="M6" t="n">
-        <v>5.397754390317842</v>
+        <v>5.397754390317835</v>
       </c>
       <c r="N6" t="n">
-        <v>38.78370947956872</v>
+        <v>6.092703843032779</v>
       </c>
       <c r="O6" t="n">
-        <v>6.960873915402093</v>
+        <v>6.96087391540208</v>
       </c>
       <c r="P6" t="n">
-        <v>8.485847930521736</v>
+        <v>8.485847930521745</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.66505349998286</v>
+        <v>4.66505349998284</v>
       </c>
       <c r="R6" t="n">
-        <v>4.444594897450735</v>
+        <v>4.444594897450719</v>
       </c>
       <c r="S6" t="n">
-        <v>5.848187469687569</v>
+        <v>5.848187469687562</v>
       </c>
       <c r="T6" t="n">
-        <v>5.658026017615972</v>
+        <v>5.658026017615962</v>
       </c>
       <c r="U6" t="n">
-        <v>6.162980145737151</v>
+        <v>6.162980145737144</v>
       </c>
       <c r="V6" t="n">
-        <v>6.385072208611345</v>
+        <v>6.385072208611344</v>
       </c>
       <c r="W6" t="n">
-        <v>6.926180776754378</v>
+        <v>6.926180776754363</v>
       </c>
       <c r="X6" t="n">
-        <v>8.209687708749836</v>
+        <v>8.209687708749831</v>
       </c>
       <c r="Y6" t="n">
         <v>7.531202866480982</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.202978226586748</v>
+        <v>4.202978226586737</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.176835208608377</v>
+        <v>7.176835208608382</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.515101211361445</v>
+        <v>6.51510121136142</v>
       </c>
     </row>
   </sheetData>
@@ -5354,82 +5354,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.50161198220553</v>
+        <v>39.5016119822055</v>
       </c>
       <c r="C2" t="n">
-        <v>42.31579442056722</v>
+        <v>42.31579442056724</v>
       </c>
       <c r="D2" t="n">
-        <v>39.49937286404624</v>
+        <v>39.49937286404622</v>
       </c>
       <c r="E2" t="n">
-        <v>39.50271116731739</v>
+        <v>39.50271116731738</v>
       </c>
       <c r="F2" t="n">
-        <v>39.43872113188699</v>
+        <v>39.43872113188696</v>
       </c>
       <c r="G2" t="n">
-        <v>39.69589858493075</v>
+        <v>39.69589858493078</v>
       </c>
       <c r="H2" t="n">
-        <v>39.63050250492766</v>
+        <v>39.6305025049277</v>
       </c>
       <c r="I2" t="n">
-        <v>39.48405581143469</v>
+        <v>39.48405581143471</v>
       </c>
       <c r="J2" t="n">
-        <v>39.68529924066126</v>
+        <v>39.68529924066124</v>
       </c>
       <c r="K2" t="n">
-        <v>39.54161586553933</v>
+        <v>39.54161586553932</v>
       </c>
       <c r="L2" t="n">
-        <v>39.70869067461381</v>
+        <v>39.70869067461382</v>
       </c>
       <c r="M2" t="n">
-        <v>39.93673003181983</v>
+        <v>39.93673003181981</v>
       </c>
       <c r="N2" t="n">
-        <v>39.67136226013363</v>
+        <v>39.67136226013368</v>
       </c>
       <c r="O2" t="n">
-        <v>43.69262320170545</v>
+        <v>43.69262320170547</v>
       </c>
       <c r="P2" t="n">
-        <v>39.79529959856448</v>
+        <v>39.7952995985645</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.54218817462003</v>
+        <v>39.54218817462009</v>
       </c>
       <c r="R2" t="n">
-        <v>39.52555542170036</v>
+        <v>39.52555542170039</v>
       </c>
       <c r="S2" t="n">
-        <v>39.58878485052999</v>
+        <v>39.58878485052998</v>
       </c>
       <c r="T2" t="n">
-        <v>39.55630276920873</v>
+        <v>39.55630276920876</v>
       </c>
       <c r="U2" t="n">
-        <v>43.32606280497718</v>
+        <v>43.32606280497721</v>
       </c>
       <c r="V2" t="n">
-        <v>39.6379901969151</v>
+        <v>39.63799019691508</v>
       </c>
       <c r="W2" t="n">
-        <v>45.99177893188418</v>
+        <v>45.99177893188416</v>
       </c>
       <c r="X2" t="n">
-        <v>39.63327164810089</v>
+        <v>39.63327164810092</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.94560221663027</v>
+        <v>39.94560221663026</v>
       </c>
       <c r="Z2" t="n">
         <v>40.9584508168991</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.59232789510212</v>
+        <v>39.59232789510214</v>
       </c>
       <c r="AB2" t="n">
         <v>39.92976901715325</v>
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.48875855178483</v>
+        <v>41.38069670686276</v>
       </c>
       <c r="C3" t="n">
-        <v>44.15162414314503</v>
+        <v>43.2420683730638</v>
       </c>
       <c r="D3" t="n">
-        <v>44.50178549423192</v>
+        <v>41.44517891267439</v>
       </c>
       <c r="E3" t="n">
-        <v>43.28976024785151</v>
+        <v>40.18546043906762</v>
       </c>
       <c r="F3" t="n">
-        <v>43.09721668476443</v>
+        <v>40.94717385943422</v>
       </c>
       <c r="G3" t="n">
-        <v>48.96341389076409</v>
+        <v>42.87220166294103</v>
       </c>
       <c r="H3" t="n">
-        <v>47.60797798914995</v>
+        <v>42.55495150622811</v>
       </c>
       <c r="I3" t="n">
-        <v>44.15030887154475</v>
+        <v>41.3208460056985</v>
       </c>
       <c r="J3" t="n">
-        <v>48.76099906496373</v>
+        <v>42.83630559329222</v>
       </c>
       <c r="K3" t="n">
-        <v>45.47206523822159</v>
+        <v>41.71381488669078</v>
       </c>
       <c r="L3" t="n">
-        <v>49.30771543797364</v>
+        <v>43.03910159274112</v>
       </c>
       <c r="M3" t="n">
-        <v>54.70926822403237</v>
+        <v>44.86663605031629</v>
       </c>
       <c r="N3" t="n">
-        <v>48.48498632630045</v>
+        <v>42.81246688243711</v>
       </c>
       <c r="O3" t="n">
-        <v>52.27189524515244</v>
+        <v>46.64716282757218</v>
       </c>
       <c r="P3" t="n">
-        <v>51.23692479817857</v>
+        <v>43.68799412690275</v>
       </c>
       <c r="Q3" t="n">
-        <v>45.48561890616669</v>
+        <v>41.75687275641489</v>
       </c>
       <c r="R3" t="n">
-        <v>45.13114804703697</v>
+        <v>41.67724338448793</v>
       </c>
       <c r="S3" t="n">
-        <v>46.50810115660448</v>
+        <v>42.03371298776359</v>
       </c>
       <c r="T3" t="n">
-        <v>45.83360289216214</v>
+        <v>41.90822177024896</v>
       </c>
       <c r="U3" t="n">
-        <v>54.44197232244174</v>
+        <v>47.138997028017</v>
       </c>
       <c r="V3" t="n">
-        <v>47.63561607815286</v>
+        <v>42.4194083358966</v>
       </c>
       <c r="W3" t="n">
-        <v>60.96086563563798</v>
+        <v>51.06389868426078</v>
       </c>
       <c r="X3" t="n">
-        <v>47.6197301968677</v>
+        <v>42.51808556821322</v>
       </c>
       <c r="Y3" t="n">
-        <v>54.83638072601867</v>
+        <v>44.96304883756478</v>
       </c>
       <c r="Z3" t="n">
-        <v>49.31182627922746</v>
+        <v>43.87374510149126</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.63140650313783</v>
+        <v>42.15736814081412</v>
       </c>
       <c r="AB3" t="n">
-        <v>54.49437255893038</v>
+        <v>45.01770386346085</v>
       </c>
     </row>
     <row r="4">
@@ -5530,85 +5530,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.68654123971736</v>
+        <v>40.68654123971749</v>
       </c>
       <c r="C4" t="n">
-        <v>13.80549844943339</v>
+        <v>13.80549844943341</v>
       </c>
       <c r="D4" t="n">
-        <v>46.12470615669334</v>
+        <v>46.1247061566934</v>
       </c>
       <c r="E4" t="n">
-        <v>44.20280352406015</v>
+        <v>44.20280352406026</v>
       </c>
       <c r="F4" t="n">
-        <v>32.21133701520109</v>
+        <v>32.21133701520108</v>
       </c>
       <c r="G4" t="n">
-        <v>77.70952324437792</v>
+        <v>77.70952324437783</v>
       </c>
       <c r="H4" t="n">
-        <v>78.50961883505876</v>
+        <v>78.50961883505877</v>
       </c>
       <c r="I4" t="n">
-        <v>42.71050771508786</v>
+        <v>42.71050771508785</v>
       </c>
       <c r="J4" t="n">
-        <v>78.94642732276833</v>
+        <v>78.94642732276837</v>
       </c>
       <c r="K4" t="n">
         <v>50.10952568424197</v>
       </c>
       <c r="L4" t="n">
-        <v>85.08800873924903</v>
+        <v>85.08800873924973</v>
       </c>
       <c r="M4" t="n">
         <v>134.2488616136513</v>
       </c>
       <c r="N4" t="n">
-        <v>82.29544632640572</v>
+        <v>82.29544632640571</v>
       </c>
       <c r="O4" t="n">
-        <v>70.64674414232994</v>
+        <v>70.64674414232987</v>
       </c>
       <c r="P4" t="n">
-        <v>100.5310488148328</v>
+        <v>100.5310488148327</v>
       </c>
       <c r="Q4" t="n">
-        <v>53.04489401416044</v>
+        <v>53.04489401416042</v>
       </c>
       <c r="R4" t="n">
-        <v>53.34190710855668</v>
+        <v>53.34190710855657</v>
       </c>
       <c r="S4" t="n">
-        <v>56.09479874762743</v>
+        <v>56.09479874762742</v>
       </c>
       <c r="T4" t="n">
-        <v>58.8402373022879</v>
+        <v>58.84023730228795</v>
       </c>
       <c r="U4" t="n">
-        <v>99.88722920149866</v>
+        <v>99.88722920149885</v>
       </c>
       <c r="V4" t="n">
-        <v>66.0667725696791</v>
+        <v>66.06677256967912</v>
       </c>
       <c r="W4" t="n">
-        <v>140.5774392600341</v>
+        <v>140.5774392600343</v>
       </c>
       <c r="X4" t="n">
-        <v>74.87337561874629</v>
+        <v>74.87337561874632</v>
       </c>
       <c r="Y4" t="n">
-        <v>137.8072701017039</v>
+        <v>137.807270101704</v>
       </c>
       <c r="Z4" t="n">
-        <v>71.04800801837764</v>
+        <v>71.0480080183775</v>
       </c>
       <c r="AA4" t="n">
-        <v>63.75349986438304</v>
+        <v>63.75349986438317</v>
       </c>
       <c r="AB4" t="n">
-        <v>148.446412811745</v>
+        <v>148.4464128117447</v>
       </c>
     </row>
     <row r="5">
@@ -5621,61 +5621,61 @@
         <v>5.421883819504566</v>
       </c>
       <c r="C5" t="n">
-        <v>4.989555372012896</v>
+        <v>4.989555372012903</v>
       </c>
       <c r="D5" t="n">
-        <v>6.589155105046634</v>
+        <v>6.58915510504664</v>
       </c>
       <c r="E5" t="n">
-        <v>5.991858074813733</v>
+        <v>5.99185807481374</v>
       </c>
       <c r="F5" t="n">
-        <v>4.897290135530694</v>
+        <v>4.897290135530699</v>
       </c>
       <c r="G5" t="n">
-        <v>9.056289267655719</v>
+        <v>9.056289267655725</v>
       </c>
       <c r="H5" t="n">
-        <v>8.070324721417531</v>
+        <v>8.070324721417542</v>
       </c>
       <c r="I5" t="n">
-        <v>6.416141949606709</v>
+        <v>6.416141949606708</v>
       </c>
       <c r="J5" t="n">
-        <v>8.689981307704718</v>
+        <v>8.689981307704725</v>
       </c>
       <c r="K5" t="n">
-        <v>7.066309239651845</v>
+        <v>7.066309239651849</v>
       </c>
       <c r="L5" t="n">
-        <v>8.95349606635755</v>
+        <v>8.953496066357562</v>
       </c>
       <c r="M5" t="n">
-        <v>11.515085390015</v>
+        <v>11.51508539001502</v>
       </c>
       <c r="N5" t="n">
-        <v>82.29544632640572</v>
+        <v>7.607418495682983</v>
       </c>
       <c r="O5" t="n">
-        <v>7.792057233090895</v>
+        <v>7.792057233090899</v>
       </c>
       <c r="P5" t="n">
-        <v>9.199118689791174</v>
+        <v>9.199118689791177</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.645844700354004</v>
+        <v>5.645844700354007</v>
       </c>
       <c r="R5" t="n">
-        <v>6.884899138321275</v>
+        <v>6.884899138321272</v>
       </c>
       <c r="S5" t="n">
-        <v>7.599104623926138</v>
+        <v>7.599104623926141</v>
       </c>
       <c r="T5" t="n">
         <v>7.2322045729076</v>
       </c>
       <c r="U5" t="n">
-        <v>9.147924760550673</v>
+        <v>9.147924760550699</v>
       </c>
       <c r="V5" t="n">
         <v>7.832580765835655</v>
@@ -5684,16 +5684,16 @@
         <v>11.67722664540337</v>
       </c>
       <c r="X5" t="n">
-        <v>6.783975215533505</v>
+        <v>6.783975215533521</v>
       </c>
       <c r="Y5" t="n">
         <v>12.81400653696416</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.122445899224898</v>
+        <v>7.122445899224905</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.639124942249769</v>
+        <v>7.639124942249774</v>
       </c>
       <c r="AB5" t="n">
         <v>12.66136700545766</v>
@@ -5706,43 +5706,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.086674170380407</v>
+        <v>8.086674170380414</v>
       </c>
       <c r="C6" t="n">
-        <v>7.717811168013453</v>
+        <v>7.71781116801346</v>
       </c>
       <c r="D6" t="n">
-        <v>9.317410901047197</v>
+        <v>9.317410901047202</v>
       </c>
       <c r="E6" t="n">
-        <v>9.065232336798964</v>
+        <v>9.065232336798974</v>
       </c>
       <c r="F6" t="n">
-        <v>5.736832886858969</v>
+        <v>5.73683288685897</v>
       </c>
       <c r="G6" t="n">
-        <v>11.53725937974846</v>
+        <v>11.53725937974847</v>
       </c>
       <c r="H6" t="n">
-        <v>10.79858051741809</v>
+        <v>10.79858051741811</v>
       </c>
       <c r="I6" t="n">
-        <v>9.144397745607268</v>
+        <v>9.144397745607277</v>
       </c>
       <c r="J6" t="n">
         <v>11.41823710370528</v>
       </c>
       <c r="K6" t="n">
-        <v>9.794565035652399</v>
+        <v>9.794565035652402</v>
       </c>
       <c r="L6" t="n">
-        <v>11.68175186235812</v>
+        <v>11.68175186235813</v>
       </c>
       <c r="M6" t="n">
         <v>14.24334118601468</v>
       </c>
       <c r="N6" t="n">
-        <v>82.29544632640572</v>
+        <v>11.26011024888551</v>
       </c>
       <c r="O6" t="n">
         <v>11.60695226618652</v>
@@ -5751,31 +5751,31 @@
         <v>13.16681222538731</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.801029585006528</v>
+        <v>9.801029585006535</v>
       </c>
       <c r="R6" t="n">
-        <v>9.613154934321836</v>
+        <v>9.613154934321834</v>
       </c>
       <c r="S6" t="n">
         <v>10.32736041992671</v>
       </c>
       <c r="T6" t="n">
-        <v>9.960460368908169</v>
+        <v>9.960460368908164</v>
       </c>
       <c r="U6" t="n">
-        <v>12.4589870337381</v>
+        <v>12.45898703373812</v>
       </c>
       <c r="V6" t="n">
         <v>12.33701830124237</v>
       </c>
       <c r="W6" t="n">
-        <v>14.40524807034083</v>
+        <v>14.40524807034082</v>
       </c>
       <c r="X6" t="n">
         <v>10.82985926342871</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.35777671412754</v>
+        <v>14.35777671412755</v>
       </c>
       <c r="Z6" t="n">
         <v>10.3081437894115</v>
@@ -5950,70 +5950,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.01871250816259</v>
+        <v>39.01871250816258</v>
       </c>
       <c r="C2" t="n">
         <v>41.99062466853402</v>
       </c>
       <c r="D2" t="n">
-        <v>39.07371954467348</v>
+        <v>39.07371954467344</v>
       </c>
       <c r="E2" t="n">
-        <v>39.10777567048267</v>
+        <v>39.10777567048263</v>
       </c>
       <c r="F2" t="n">
-        <v>39.08530115917172</v>
+        <v>39.08530115917168</v>
       </c>
       <c r="G2" t="n">
-        <v>39.33963741891907</v>
+        <v>39.33963741891905</v>
       </c>
       <c r="H2" t="n">
-        <v>39.2658084257639</v>
+        <v>39.26580842576395</v>
       </c>
       <c r="I2" t="n">
-        <v>39.06043877234021</v>
+        <v>39.0604387723402</v>
       </c>
       <c r="J2" t="n">
         <v>39.24725053690528</v>
       </c>
       <c r="K2" t="n">
-        <v>39.13657750226416</v>
+        <v>39.13657750226415</v>
       </c>
       <c r="L2" t="n">
-        <v>39.13901068381963</v>
+        <v>39.13901068381962</v>
       </c>
       <c r="M2" t="n">
-        <v>39.23524961666047</v>
+        <v>39.23524961666043</v>
       </c>
       <c r="N2" t="n">
-        <v>39.25625326713715</v>
+        <v>39.25625326713712</v>
       </c>
       <c r="O2" t="n">
         <v>43.15143214350103</v>
       </c>
       <c r="P2" t="n">
-        <v>39.43002471801542</v>
+        <v>39.43002471801535</v>
       </c>
       <c r="Q2" t="n">
-        <v>39.1244718621348</v>
+        <v>39.12447186213475</v>
       </c>
       <c r="R2" t="n">
-        <v>39.07472981990102</v>
+        <v>39.074729819901</v>
       </c>
       <c r="S2" t="n">
-        <v>39.12821440292542</v>
+        <v>39.12821440292534</v>
       </c>
       <c r="T2" t="n">
-        <v>39.16531301169724</v>
+        <v>39.16531301169721</v>
       </c>
       <c r="U2" t="n">
-        <v>42.6878127432676</v>
+        <v>42.68781274326761</v>
       </c>
       <c r="V2" t="n">
-        <v>39.2117670022246</v>
+        <v>39.21176700222456</v>
       </c>
       <c r="W2" t="n">
-        <v>45.40451697426484</v>
+        <v>45.40451697426476</v>
       </c>
       <c r="X2" t="n">
         <v>39.34147841588953</v>
@@ -6022,13 +6022,13 @@
         <v>39.60034607702796</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.29326346021568</v>
+        <v>40.29326346021563</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.18586238635399</v>
+        <v>39.18586238635395</v>
       </c>
       <c r="AB2" t="n">
-        <v>39.48440145327064</v>
+        <v>39.4844014532706</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.16533303257849</v>
+        <v>39.73998253730126</v>
       </c>
       <c r="C3" t="n">
-        <v>43.67737419724039</v>
+        <v>42.88363917956014</v>
       </c>
       <c r="D3" t="n">
-        <v>41.45652741318605</v>
+        <v>40.19030796844825</v>
       </c>
       <c r="E3" t="n">
-        <v>41.02270911466112</v>
+        <v>39.24851386280304</v>
       </c>
       <c r="F3" t="n">
-        <v>41.73478076291318</v>
+        <v>40.28433488861235</v>
       </c>
       <c r="G3" t="n">
-        <v>47.55003381768807</v>
+        <v>42.17592895771629</v>
       </c>
       <c r="H3" t="n">
-        <v>45.98001251897178</v>
+        <v>41.80444802291719</v>
       </c>
       <c r="I3" t="n">
-        <v>41.14971103303417</v>
+        <v>40.08993734044328</v>
       </c>
       <c r="J3" t="n">
-        <v>45.45212645460251</v>
+        <v>41.51405671576702</v>
       </c>
       <c r="K3" t="n">
-        <v>42.91440067087344</v>
+        <v>40.65657104171139</v>
       </c>
       <c r="L3" t="n">
-        <v>42.95019662694577</v>
+        <v>40.66858653482862</v>
       </c>
       <c r="M3" t="n">
-        <v>45.25361184471868</v>
+        <v>41.45673590448162</v>
       </c>
       <c r="N3" t="n">
-        <v>45.69645932963104</v>
+        <v>41.66308263096853</v>
       </c>
       <c r="O3" t="n">
-        <v>50.66874866296188</v>
+        <v>45.79319380613654</v>
       </c>
       <c r="P3" t="n">
-        <v>49.61859362999606</v>
+        <v>42.92268296129699</v>
       </c>
       <c r="Q3" t="n">
-        <v>42.63056821361661</v>
+        <v>40.56629951764008</v>
       </c>
       <c r="R3" t="n">
-        <v>41.48740821602634</v>
+        <v>40.21110614685522</v>
       </c>
       <c r="S3" t="n">
-        <v>42.69162892489275</v>
+        <v>40.57485747703004</v>
       </c>
       <c r="T3" t="n">
-        <v>43.59689267185988</v>
+        <v>40.93762632049658</v>
       </c>
       <c r="U3" t="n">
-        <v>49.19215478861572</v>
+        <v>45.04110248217999</v>
       </c>
       <c r="V3" t="n">
-        <v>44.61306897678426</v>
+        <v>41.21456091383292</v>
       </c>
       <c r="W3" t="n">
-        <v>57.23333335572202</v>
+        <v>49.50305217428522</v>
       </c>
       <c r="X3" t="n">
-        <v>47.69585281230199</v>
+        <v>42.32797577135357</v>
       </c>
       <c r="Y3" t="n">
-        <v>53.67459186049704</v>
+        <v>44.38314907225429</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.29749522343079</v>
+        <v>41.87316921521614</v>
       </c>
       <c r="AA3" t="n">
-        <v>44.04909778481265</v>
+        <v>41.08367545459091</v>
       </c>
       <c r="AB3" t="n">
-        <v>50.96985466954656</v>
+        <v>43.55074961521316</v>
       </c>
     </row>
     <row r="4">
@@ -6126,82 +6126,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.893835980786641</v>
+        <v>5.893835980786569</v>
       </c>
       <c r="C4" t="n">
         <v>10.96118837917713</v>
       </c>
       <c r="D4" t="n">
-        <v>17.57678855422571</v>
+        <v>17.57678855422573</v>
       </c>
       <c r="E4" t="n">
-        <v>23.86214248900785</v>
+        <v>23.86214248900792</v>
       </c>
       <c r="F4" t="n">
         <v>19.97308776589714</v>
       </c>
       <c r="G4" t="n">
-        <v>61.2458096046516</v>
+        <v>61.24580960464401</v>
       </c>
       <c r="H4" t="n">
-        <v>61.1842266964835</v>
+        <v>61.18422669648351</v>
       </c>
       <c r="I4" t="n">
-        <v>15.31771914766337</v>
+        <v>15.31771914766347</v>
       </c>
       <c r="J4" t="n">
-        <v>47.95175873081079</v>
+        <v>47.95175873081149</v>
       </c>
       <c r="K4" t="n">
-        <v>27.66124496265172</v>
+        <v>27.6612449626518</v>
       </c>
       <c r="L4" t="n">
-        <v>27.67228702861033</v>
+        <v>27.67228702861032</v>
       </c>
       <c r="M4" t="n">
-        <v>47.87819448533457</v>
+        <v>47.87819448533447</v>
       </c>
       <c r="N4" t="n">
         <v>54.94422479630326</v>
       </c>
       <c r="O4" t="n">
-        <v>56.61642619747143</v>
+        <v>56.61642619747161</v>
       </c>
       <c r="P4" t="n">
-        <v>80.98682608218807</v>
+        <v>80.98682608218819</v>
       </c>
       <c r="Q4" t="n">
-        <v>25.69144143946107</v>
+        <v>25.69144143946112</v>
       </c>
       <c r="R4" t="n">
-        <v>18.63381823344136</v>
+        <v>18.63381823344147</v>
       </c>
       <c r="S4" t="n">
-        <v>25.02313872002182</v>
+        <v>25.02313872002183</v>
       </c>
       <c r="T4" t="n">
-        <v>36.8728586191111</v>
+        <v>36.87285861911136</v>
       </c>
       <c r="U4" t="n">
-        <v>50.06866874284657</v>
+        <v>50.06866874284663</v>
       </c>
       <c r="V4" t="n">
         <v>39.81428203785303</v>
       </c>
       <c r="W4" t="n">
-        <v>102.8023634016106</v>
+        <v>102.8023634016105</v>
       </c>
       <c r="X4" t="n">
-        <v>70.81105233405204</v>
+        <v>70.81105233405157</v>
       </c>
       <c r="Y4" t="n">
-        <v>121.575449647691</v>
+        <v>121.5754496476909</v>
       </c>
       <c r="Z4" t="n">
-        <v>28.51488006632844</v>
+        <v>28.51488006632829</v>
       </c>
       <c r="AA4" t="n">
-        <v>39.77244567059364</v>
+        <v>39.77244567059321</v>
       </c>
       <c r="AB4" t="n">
         <v>105.7676913237885</v>
@@ -6214,85 +6214,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.765179260551395</v>
+        <v>2.765179260551396</v>
       </c>
       <c r="C5" t="n">
-        <v>3.947169998737118</v>
+        <v>3.947169998737092</v>
       </c>
       <c r="D5" t="n">
-        <v>4.298404404470286</v>
+        <v>4.298404404470303</v>
       </c>
       <c r="E5" t="n">
-        <v>4.197526631286534</v>
+        <v>4.197526631286529</v>
       </c>
       <c r="F5" t="n">
-        <v>3.65939134570027</v>
+        <v>3.659391345700289</v>
       </c>
       <c r="G5" t="n">
-        <v>7.491156566004594</v>
+        <v>7.491156566004477</v>
       </c>
       <c r="H5" t="n">
-        <v>6.46813668163833</v>
+        <v>6.46813668163828</v>
       </c>
       <c r="I5" t="n">
-        <v>4.14839197150891</v>
+        <v>4.148391971508948</v>
       </c>
       <c r="J5" t="n">
-        <v>6.259076331020184</v>
+        <v>6.25907633102031</v>
       </c>
       <c r="K5" t="n">
-        <v>5.008413951546325</v>
+        <v>5.008413951546339</v>
       </c>
       <c r="L5" t="n">
-        <v>5.035897856534325</v>
+        <v>5.035897856534286</v>
       </c>
       <c r="M5" t="n">
-        <v>6.131551861903075</v>
+        <v>6.131551861903058</v>
       </c>
       <c r="N5" t="n">
-        <v>54.94422479630326</v>
+        <v>5.653335306666348</v>
       </c>
       <c r="O5" t="n">
-        <v>6.437659659743439</v>
+        <v>6.437659659743426</v>
       </c>
       <c r="P5" t="n">
-        <v>7.762801747208048</v>
+        <v>7.762801747208034</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.780571564094834</v>
+        <v>3.780571564094848</v>
       </c>
       <c r="R5" t="n">
-        <v>4.309815927915045</v>
+        <v>4.309815927914999</v>
       </c>
       <c r="S5" t="n">
-        <v>4.913948897299216</v>
+        <v>4.913948897299267</v>
       </c>
       <c r="T5" t="n">
-        <v>5.332994749580418</v>
+        <v>5.332994749580362</v>
       </c>
       <c r="U5" t="n">
-        <v>5.964721015623342</v>
+        <v>5.964721015623319</v>
       </c>
       <c r="V5" t="n">
-        <v>5.608637969499941</v>
+        <v>5.608637969499922</v>
       </c>
       <c r="W5" t="n">
-        <v>9.11170134026484</v>
+        <v>9.111701340264897</v>
       </c>
       <c r="X5" t="n">
-        <v>6.315337437784337</v>
+        <v>6.315337437784296</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.14849278056511</v>
+        <v>11.14849278056522</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.213628983698364</v>
+        <v>4.213628983698331</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.565109389507624</v>
+        <v>5.565109389507525</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.848559685573505</v>
+        <v>9.848559685573482</v>
       </c>
     </row>
     <row r="6">
@@ -6302,85 +6302,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.658499571408433</v>
+        <v>4.658499571408421</v>
       </c>
       <c r="C6" t="n">
-        <v>5.849107617479218</v>
+        <v>5.849107617479215</v>
       </c>
       <c r="D6" t="n">
-        <v>6.200342023212416</v>
+        <v>6.200342023212291</v>
       </c>
       <c r="E6" t="n">
-        <v>6.372571348954544</v>
+        <v>6.372571348954595</v>
       </c>
       <c r="F6" t="n">
-        <v>4.209128262730331</v>
+        <v>4.209128262730325</v>
       </c>
       <c r="G6" t="n">
-        <v>9.204007115042645</v>
+        <v>9.204007115042607</v>
       </c>
       <c r="H6" t="n">
-        <v>8.370074300380409</v>
+        <v>8.37007430038042</v>
       </c>
       <c r="I6" t="n">
-        <v>6.050329590251013</v>
+        <v>6.050329590250905</v>
       </c>
       <c r="J6" t="n">
-        <v>8.1610139497623</v>
+        <v>8.161013949762175</v>
       </c>
       <c r="K6" t="n">
-        <v>6.910351570288435</v>
+        <v>6.910351570288554</v>
       </c>
       <c r="L6" t="n">
-        <v>6.937835475276444</v>
+        <v>6.937835475276504</v>
       </c>
       <c r="M6" t="n">
-        <v>8.033489480643691</v>
+        <v>8.033489480643377</v>
       </c>
       <c r="N6" t="n">
-        <v>54.94422479630326</v>
+        <v>8.262144388100698</v>
       </c>
       <c r="O6" t="n">
-        <v>9.157271517647134</v>
+        <v>9.157271517647191</v>
       </c>
       <c r="P6" t="n">
-        <v>10.59637467988171</v>
+        <v>10.59637467988158</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.773613170118494</v>
+        <v>6.773613170118375</v>
       </c>
       <c r="R6" t="n">
-        <v>6.211753546657159</v>
+        <v>6.211753546657063</v>
       </c>
       <c r="S6" t="n">
-        <v>6.815886516041331</v>
+        <v>6.815886516041131</v>
       </c>
       <c r="T6" t="n">
-        <v>7.234932368322525</v>
+        <v>7.234932368322315</v>
       </c>
       <c r="U6" t="n">
-        <v>8.31471058142407</v>
+        <v>8.314710581423995</v>
       </c>
       <c r="V6" t="n">
-        <v>8.825335750024283</v>
+        <v>8.825335750024292</v>
       </c>
       <c r="W6" t="n">
-        <v>11.01345974675917</v>
+        <v>11.01345974675905</v>
       </c>
       <c r="X6" t="n">
-        <v>9.224801648763956</v>
+        <v>9.224801648764117</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.14883096633031</v>
+        <v>12.14883096633023</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.489413752594041</v>
+        <v>6.489413752594196</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.467047008249734</v>
+        <v>7.467047008249876</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.79794634844252</v>
+        <v>10.79794634844237</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use fossils results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.88019592920203</v>
+        <v>42.05478845800965</v>
       </c>
       <c r="C3" t="n">
-        <v>43.88850980624331</v>
+        <v>43.60081790943063</v>
       </c>
       <c r="D3" t="n">
-        <v>42.02790355245748</v>
+        <v>41.39230207359547</v>
       </c>
       <c r="E3" t="n">
-        <v>40.64272470475404</v>
+        <v>40.06389157701422</v>
       </c>
       <c r="F3" t="n">
-        <v>42.09313087302122</v>
+        <v>41.42655973798635</v>
       </c>
       <c r="G3" t="n">
-        <v>43.38084939560386</v>
+        <v>42.39276527780363</v>
       </c>
       <c r="H3" t="n">
-        <v>43.55289918469403</v>
+        <v>42.40831867731377</v>
       </c>
       <c r="I3" t="n">
-        <v>41.75988737746479</v>
+        <v>41.20374119230885</v>
       </c>
       <c r="J3" t="n">
-        <v>43.54725718476409</v>
+        <v>42.4899319336673</v>
       </c>
       <c r="K3" t="n">
-        <v>43.22537867363683</v>
+        <v>42.22075346924623</v>
       </c>
       <c r="L3" t="n">
-        <v>44.18896866025123</v>
+        <v>42.92770403909326</v>
       </c>
       <c r="M3" t="n">
-        <v>45.85766719017522</v>
+        <v>44.00877818445542</v>
       </c>
       <c r="N3" t="n">
-        <v>43.85300359778919</v>
+        <v>42.6708967198614</v>
       </c>
       <c r="O3" t="n">
-        <v>47.30803227171348</v>
+        <v>46.42169225316893</v>
       </c>
       <c r="P3" t="n">
-        <v>44.22460053482314</v>
+        <v>43.00015283986993</v>
       </c>
       <c r="Q3" t="n">
-        <v>42.86370281741779</v>
+        <v>41.97982418476601</v>
       </c>
       <c r="R3" t="n">
-        <v>42.25075730614255</v>
+        <v>41.53340860252145</v>
       </c>
       <c r="S3" t="n">
-        <v>43.2717522143173</v>
+        <v>42.3134238366227</v>
       </c>
       <c r="T3" t="n">
-        <v>43.25395116598436</v>
+        <v>42.23191120397655</v>
       </c>
       <c r="U3" t="n">
-        <v>48.48326169329845</v>
+        <v>47.04441627889754</v>
       </c>
       <c r="V3" t="n">
-        <v>42.9959141930757</v>
+        <v>42.13205196288347</v>
       </c>
       <c r="W3" t="n">
-        <v>51.08114926391568</v>
+        <v>49.58344993321501</v>
       </c>
       <c r="X3" t="n">
-        <v>42.7253458505488</v>
+        <v>41.87935797141161</v>
       </c>
       <c r="Y3" t="n">
-        <v>45.29839051961841</v>
+        <v>43.69383455109169</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.91797366741964</v>
+        <v>43.88928303643306</v>
       </c>
       <c r="AA3" t="n">
-        <v>43.03394427226744</v>
+        <v>42.11040804695175</v>
       </c>
       <c r="AB3" t="n">
-        <v>45.92285545318845</v>
+        <v>44.01392454697334</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.466144553656</v>
+        <v>39.43181948505671</v>
       </c>
       <c r="C3" t="n">
-        <v>42.73274531394303</v>
+        <v>42.60121270340325</v>
       </c>
       <c r="D3" t="n">
-        <v>40.05454874176392</v>
+        <v>39.84169959043268</v>
       </c>
       <c r="E3" t="n">
-        <v>38.49770496609973</v>
+        <v>38.40069977142583</v>
       </c>
       <c r="F3" t="n">
-        <v>40.60884716168667</v>
+        <v>40.22288643705025</v>
       </c>
       <c r="G3" t="n">
-        <v>40.89341760538867</v>
+        <v>40.46625054316564</v>
       </c>
       <c r="H3" t="n">
-        <v>40.91651711907542</v>
+        <v>40.41935186079613</v>
       </c>
       <c r="I3" t="n">
-        <v>40.04939890323112</v>
+        <v>39.8325396985812</v>
       </c>
       <c r="J3" t="n">
-        <v>40.75415092533486</v>
+        <v>40.34694863163021</v>
       </c>
       <c r="K3" t="n">
-        <v>41.17014737711993</v>
+        <v>40.65308426197751</v>
       </c>
       <c r="L3" t="n">
-        <v>40.50207161129416</v>
+        <v>40.17577780073594</v>
       </c>
       <c r="M3" t="n">
-        <v>40.57751368472917</v>
+        <v>40.20376963579481</v>
       </c>
       <c r="N3" t="n">
-        <v>41.3216168621762</v>
+        <v>40.71526170111309</v>
       </c>
       <c r="O3" t="n">
-        <v>45.09068446025572</v>
+        <v>44.53510787727495</v>
       </c>
       <c r="P3" t="n">
-        <v>42.36072271710884</v>
+        <v>41.52259944153241</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.01907584976047</v>
+        <v>39.821572192221</v>
       </c>
       <c r="R3" t="n">
-        <v>39.94786030699133</v>
+        <v>39.75874346114438</v>
       </c>
       <c r="S3" t="n">
-        <v>40.97913979614598</v>
+        <v>40.52313003704987</v>
       </c>
       <c r="T3" t="n">
-        <v>41.02393137812133</v>
+        <v>40.50313090443641</v>
       </c>
       <c r="U3" t="n">
-        <v>44.46877605961728</v>
+        <v>43.97641320797823</v>
       </c>
       <c r="V3" t="n">
-        <v>40.2929610619243</v>
+        <v>40.02869835860447</v>
       </c>
       <c r="W3" t="n">
-        <v>48.26990363439174</v>
+        <v>47.33439987659499</v>
       </c>
       <c r="X3" t="n">
-        <v>42.41237750364635</v>
+        <v>41.50399121879834</v>
       </c>
       <c r="Y3" t="n">
-        <v>42.10331224942893</v>
+        <v>41.26289858972541</v>
       </c>
       <c r="Z3" t="n">
-        <v>41.16614385929125</v>
+        <v>40.96497786817569</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.83926393920775</v>
+        <v>41.08194039587257</v>
       </c>
       <c r="AB3" t="n">
-        <v>40.6617788793673</v>
+        <v>40.24516515638781</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.20706232500933</v>
+        <v>41.55050198522026</v>
       </c>
       <c r="C3" t="n">
-        <v>43.70214066216602</v>
+        <v>43.44654899424856</v>
       </c>
       <c r="D3" t="n">
-        <v>42.15792945236565</v>
+        <v>41.45259687453295</v>
       </c>
       <c r="E3" t="n">
-        <v>40.50783559882143</v>
+        <v>39.94785275288655</v>
       </c>
       <c r="F3" t="n">
-        <v>41.64812603943404</v>
+        <v>41.10132451061057</v>
       </c>
       <c r="G3" t="n">
-        <v>43.08999657954369</v>
+        <v>42.16579804024063</v>
       </c>
       <c r="H3" t="n">
-        <v>42.95223734728891</v>
+        <v>41.97381915844135</v>
       </c>
       <c r="I3" t="n">
-        <v>41.57137135471926</v>
+        <v>41.04541194775305</v>
       </c>
       <c r="J3" t="n">
-        <v>43.22783046785959</v>
+        <v>42.24049227936553</v>
       </c>
       <c r="K3" t="n">
-        <v>42.53321489978988</v>
+        <v>41.75146772902522</v>
       </c>
       <c r="L3" t="n">
-        <v>43.56510328744708</v>
+        <v>42.46360484083341</v>
       </c>
       <c r="M3" t="n">
-        <v>45.21603208238513</v>
+        <v>43.54624058151442</v>
       </c>
       <c r="N3" t="n">
-        <v>43.43538858100827</v>
+        <v>42.35303774071244</v>
       </c>
       <c r="O3" t="n">
-        <v>47.2615631108937</v>
+        <v>46.35644671445361</v>
       </c>
       <c r="P3" t="n">
-        <v>44.18549287470233</v>
+        <v>42.94786213018973</v>
       </c>
       <c r="Q3" t="n">
-        <v>42.4866573295276</v>
+        <v>41.69333955651312</v>
       </c>
       <c r="R3" t="n">
-        <v>42.34747152952098</v>
+        <v>41.56980246713509</v>
       </c>
       <c r="S3" t="n">
-        <v>42.89298989107483</v>
+        <v>42.02415927141602</v>
       </c>
       <c r="T3" t="n">
-        <v>42.55276225412488</v>
+        <v>41.72463266245801</v>
       </c>
       <c r="U3" t="n">
-        <v>47.75506069804872</v>
+        <v>46.4931205160882</v>
       </c>
       <c r="V3" t="n">
-        <v>42.59907799136072</v>
+        <v>41.84258532590503</v>
       </c>
       <c r="W3" t="n">
-        <v>51.07415110228883</v>
+        <v>49.5361216317414</v>
       </c>
       <c r="X3" t="n">
-        <v>42.76585597692635</v>
+        <v>41.88151125460902</v>
       </c>
       <c r="Y3" t="n">
-        <v>45.11366215519746</v>
+        <v>43.54886092070733</v>
       </c>
       <c r="Z3" t="n">
-        <v>44.32890426918345</v>
+        <v>43.43544563042742</v>
       </c>
       <c r="AA3" t="n">
-        <v>42.47149686311309</v>
+        <v>41.695113631403</v>
       </c>
       <c r="AB3" t="n">
-        <v>45.65119566822173</v>
+        <v>43.79905896556672</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.67258349582362</v>
+        <v>41.13237532027939</v>
       </c>
       <c r="C3" t="n">
-        <v>43.94909787855291</v>
+        <v>43.5920232862595</v>
       </c>
       <c r="D3" t="n">
-        <v>42.39308802429265</v>
+        <v>41.58675544114317</v>
       </c>
       <c r="E3" t="n">
-        <v>40.15201590854297</v>
+        <v>39.67195658052326</v>
       </c>
       <c r="F3" t="n">
-        <v>41.59720456643971</v>
+        <v>41.03930307125157</v>
       </c>
       <c r="G3" t="n">
-        <v>42.79276992964694</v>
+        <v>41.93425747989843</v>
       </c>
       <c r="H3" t="n">
-        <v>42.58412988577659</v>
+        <v>41.68654533252451</v>
       </c>
       <c r="I3" t="n">
-        <v>41.71514092576124</v>
+        <v>41.11261546319943</v>
       </c>
       <c r="J3" t="n">
-        <v>42.86381500302637</v>
+        <v>41.95719297023239</v>
       </c>
       <c r="K3" t="n">
-        <v>41.72483504797582</v>
+        <v>41.16922100024426</v>
       </c>
       <c r="L3" t="n">
-        <v>42.97478795376414</v>
+        <v>42.02288561431524</v>
       </c>
       <c r="M3" t="n">
-        <v>44.56508154664726</v>
+        <v>43.06542951012651</v>
       </c>
       <c r="N3" t="n">
-        <v>42.60519052756916</v>
+        <v>41.74427147691116</v>
       </c>
       <c r="O3" t="n">
-        <v>46.9168350033877</v>
+        <v>46.05744785646058</v>
       </c>
       <c r="P3" t="n">
-        <v>43.8949384869122</v>
+        <v>42.72152575355684</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.99700227801007</v>
+        <v>41.33164753575183</v>
       </c>
       <c r="R3" t="n">
-        <v>41.94084893005857</v>
+        <v>41.25948983426416</v>
       </c>
       <c r="S3" t="n">
-        <v>42.56495139015852</v>
+        <v>41.76612500759921</v>
       </c>
       <c r="T3" t="n">
-        <v>42.4320357802601</v>
+        <v>41.60789707069087</v>
       </c>
       <c r="U3" t="n">
-        <v>46.77500070130579</v>
+        <v>45.7567114569943</v>
       </c>
       <c r="V3" t="n">
-        <v>42.38173273870053</v>
+        <v>41.66417299107628</v>
       </c>
       <c r="W3" t="n">
-        <v>50.46105024122031</v>
+        <v>49.0490335961752</v>
       </c>
       <c r="X3" t="n">
-        <v>43.14344854720244</v>
+        <v>42.11375590659642</v>
       </c>
       <c r="Y3" t="n">
-        <v>44.8941659273555</v>
+        <v>43.3610041095213</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.67958905526797</v>
+        <v>42.95676492657496</v>
       </c>
       <c r="AA3" t="n">
-        <v>42.30970139818176</v>
+        <v>41.54942212479649</v>
       </c>
       <c r="AB3" t="n">
-        <v>45.16758669754338</v>
+        <v>43.43369159095916</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.42459523753416</v>
+        <v>40.9396716453329</v>
       </c>
       <c r="C3" t="n">
-        <v>43.91077381091618</v>
+        <v>43.53713151500065</v>
       </c>
       <c r="D3" t="n">
-        <v>41.67988869655568</v>
+        <v>41.08267133369885</v>
       </c>
       <c r="E3" t="n">
-        <v>39.3443061613406</v>
+        <v>39.09096112979988</v>
       </c>
       <c r="F3" t="n">
-        <v>42.02024323771404</v>
+        <v>41.30650517967982</v>
       </c>
       <c r="G3" t="n">
-        <v>42.44425158697193</v>
+        <v>41.67722006818465</v>
       </c>
       <c r="H3" t="n">
-        <v>42.29794190254182</v>
+        <v>41.46073057760972</v>
       </c>
       <c r="I3" t="n">
-        <v>42.00864952220623</v>
+        <v>41.2929978113483</v>
       </c>
       <c r="J3" t="n">
-        <v>42.55212440691483</v>
+        <v>41.71943899521241</v>
       </c>
       <c r="K3" t="n">
-        <v>42.36724842889514</v>
+        <v>41.60063320546962</v>
       </c>
       <c r="L3" t="n">
-        <v>42.89248056445566</v>
+        <v>41.96268337506734</v>
       </c>
       <c r="M3" t="n">
-        <v>44.00553652719233</v>
+        <v>42.69081659213442</v>
       </c>
       <c r="N3" t="n">
-        <v>42.19352822909084</v>
+        <v>41.42874022607632</v>
       </c>
       <c r="O3" t="n">
-        <v>46.14468396602596</v>
+        <v>45.4412528860424</v>
       </c>
       <c r="P3" t="n">
-        <v>43.3187938411424</v>
+        <v>42.30889603832604</v>
       </c>
       <c r="Q3" t="n">
-        <v>42.12679767151796</v>
+        <v>41.4066014121191</v>
       </c>
       <c r="R3" t="n">
-        <v>41.99423254999627</v>
+        <v>41.26616693676137</v>
       </c>
       <c r="S3" t="n">
-        <v>42.63520011179178</v>
+        <v>41.79729087798469</v>
       </c>
       <c r="T3" t="n">
-        <v>42.49540807153754</v>
+        <v>41.62148453355785</v>
       </c>
       <c r="U3" t="n">
-        <v>46.39898991796476</v>
+        <v>45.47080989967063</v>
       </c>
       <c r="V3" t="n">
-        <v>42.0874686002627</v>
+        <v>41.43008125384667</v>
       </c>
       <c r="W3" t="n">
-        <v>50.04851894467205</v>
+        <v>48.7124939025833</v>
       </c>
       <c r="X3" t="n">
-        <v>43.18683244792719</v>
+        <v>42.13744565405993</v>
       </c>
       <c r="Y3" t="n">
-        <v>44.37310567353511</v>
+        <v>42.94940720945581</v>
       </c>
       <c r="Z3" t="n">
-        <v>42.79949894869445</v>
+        <v>42.2912872677517</v>
       </c>
       <c r="AA3" t="n">
-        <v>42.45600353951443</v>
+        <v>41.61996789840248</v>
       </c>
       <c r="AB3" t="n">
-        <v>44.56975301117571</v>
+        <v>43.01380302794691</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.14063808005611</v>
+        <v>39.99070608595439</v>
       </c>
       <c r="C3" t="n">
-        <v>42.84924830731952</v>
+        <v>42.7592346875908</v>
       </c>
       <c r="D3" t="n">
-        <v>40.51766165693556</v>
+        <v>40.23763430726854</v>
       </c>
       <c r="E3" t="n">
-        <v>39.74894672702297</v>
+        <v>39.34157599883917</v>
       </c>
       <c r="F3" t="n">
-        <v>40.26946421601249</v>
+        <v>40.06636324854186</v>
       </c>
       <c r="G3" t="n">
-        <v>41.37146905685767</v>
+        <v>40.8940402736057</v>
       </c>
       <c r="H3" t="n">
-        <v>41.38188163225063</v>
+        <v>40.81591368251296</v>
       </c>
       <c r="I3" t="n">
-        <v>40.62735264670748</v>
+        <v>40.31024060572729</v>
       </c>
       <c r="J3" t="n">
-        <v>41.73845204512639</v>
+        <v>41.13222193369453</v>
       </c>
       <c r="K3" t="n">
-        <v>41.07371751362363</v>
+        <v>40.64850634655078</v>
       </c>
       <c r="L3" t="n">
-        <v>41.38229807492464</v>
+        <v>40.89255054908327</v>
       </c>
       <c r="M3" t="n">
-        <v>42.11660681919624</v>
+        <v>41.38164279267674</v>
       </c>
       <c r="N3" t="n">
-        <v>42.50262549094771</v>
+        <v>41.6365428455286</v>
       </c>
       <c r="O3" t="n">
-        <v>46.45760798515536</v>
+        <v>45.64963827257299</v>
       </c>
       <c r="P3" t="n">
-        <v>43.51751342792466</v>
+        <v>42.39776083280663</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.25552961070112</v>
+        <v>40.76757878250356</v>
       </c>
       <c r="R3" t="n">
-        <v>40.71838078412162</v>
+        <v>40.36707492472038</v>
       </c>
       <c r="S3" t="n">
-        <v>41.02679530683206</v>
+        <v>40.6527035992638</v>
       </c>
       <c r="T3" t="n">
-        <v>41.60980764538076</v>
+        <v>41.00746804194879</v>
       </c>
       <c r="U3" t="n">
-        <v>46.13346778580092</v>
+        <v>45.25564774667099</v>
       </c>
       <c r="V3" t="n">
-        <v>41.85047315051732</v>
+        <v>41.22524841457777</v>
       </c>
       <c r="W3" t="n">
-        <v>51.21028402030421</v>
+        <v>49.51434438665689</v>
       </c>
       <c r="X3" t="n">
-        <v>41.4650501053862</v>
+        <v>40.89716218950004</v>
       </c>
       <c r="Y3" t="n">
-        <v>44.137788331617</v>
+        <v>42.78164182897869</v>
       </c>
       <c r="Z3" t="n">
-        <v>42.90290141312997</v>
+        <v>42.33104302862147</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.47575410974102</v>
+        <v>40.91339804006781</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.0432446798908</v>
+        <v>41.9673703674267</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.54789980716631</v>
+        <v>39.50344912627246</v>
       </c>
       <c r="C3" t="n">
-        <v>42.73652815159126</v>
+        <v>42.61658885986606</v>
       </c>
       <c r="D3" t="n">
-        <v>39.69488620064779</v>
+        <v>39.60398451524289</v>
       </c>
       <c r="E3" t="n">
-        <v>38.71904786449582</v>
+        <v>38.56464382003723</v>
       </c>
       <c r="F3" t="n">
-        <v>40.14501645565738</v>
+        <v>39.91673990359182</v>
       </c>
       <c r="G3" t="n">
-        <v>40.84291812621593</v>
+        <v>40.45799653917027</v>
       </c>
       <c r="H3" t="n">
-        <v>40.83713201686547</v>
+        <v>40.37951134941105</v>
       </c>
       <c r="I3" t="n">
-        <v>40.11218198046995</v>
+        <v>39.89150720456423</v>
       </c>
       <c r="J3" t="n">
-        <v>40.80741990656596</v>
+        <v>40.41112621698426</v>
       </c>
       <c r="K3" t="n">
-        <v>39.96811033049053</v>
+        <v>39.80212503399873</v>
       </c>
       <c r="L3" t="n">
-        <v>39.68050524013245</v>
+        <v>39.60163194155062</v>
       </c>
       <c r="M3" t="n">
-        <v>40.41393306672215</v>
+        <v>40.12570913674215</v>
       </c>
       <c r="N3" t="n">
-        <v>41.57547246845595</v>
+        <v>40.93089991932013</v>
       </c>
       <c r="O3" t="n">
-        <v>45.69236248688139</v>
+        <v>44.99874811495967</v>
       </c>
       <c r="P3" t="n">
-        <v>42.73965562341445</v>
+        <v>41.79186818163406</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.11752454623473</v>
+        <v>39.91404634492069</v>
       </c>
       <c r="R3" t="n">
-        <v>39.80963127945918</v>
+        <v>39.67974812271913</v>
       </c>
       <c r="S3" t="n">
-        <v>40.34463886859117</v>
+        <v>40.09043350907208</v>
       </c>
       <c r="T3" t="n">
-        <v>40.74288295685909</v>
+        <v>40.34277797218955</v>
       </c>
       <c r="U3" t="n">
-        <v>44.24869381802084</v>
+        <v>43.84849807710722</v>
       </c>
       <c r="V3" t="n">
-        <v>41.02392782954735</v>
+        <v>40.57642074245904</v>
       </c>
       <c r="W3" t="n">
-        <v>48.71664481083171</v>
+        <v>47.70432876851719</v>
       </c>
       <c r="X3" t="n">
-        <v>42.11336067162136</v>
+        <v>41.31291622708262</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.02448435230468</v>
+        <v>41.92719907971431</v>
       </c>
       <c r="Z3" t="n">
-        <v>41.42845542499575</v>
+        <v>41.16999624834846</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.55140169661241</v>
+        <v>40.90036834711225</v>
       </c>
       <c r="AB3" t="n">
-        <v>41.55774238131877</v>
+        <v>40.89867812624531</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.40841065885533</v>
+        <v>39.3656770114818</v>
       </c>
       <c r="C3" t="n">
-        <v>42.48959951940503</v>
+        <v>42.40159701340516</v>
       </c>
       <c r="D3" t="n">
-        <v>39.76729671434425</v>
+        <v>39.61378993054043</v>
       </c>
       <c r="E3" t="n">
-        <v>38.25143183300437</v>
+        <v>38.2035080410896</v>
       </c>
       <c r="F3" t="n">
-        <v>40.34222370508142</v>
+        <v>40.00817123213009</v>
       </c>
       <c r="G3" t="n">
-        <v>40.12534660870676</v>
+        <v>39.88610444215016</v>
       </c>
       <c r="H3" t="n">
-        <v>40.64882319221284</v>
+        <v>40.21113677908296</v>
       </c>
       <c r="I3" t="n">
-        <v>39.91594099133966</v>
+        <v>39.71292754404826</v>
       </c>
       <c r="J3" t="n">
-        <v>40.30575002187811</v>
+        <v>40.0030118757152</v>
       </c>
       <c r="K3" t="n">
-        <v>39.90421585639022</v>
+        <v>39.71398809296859</v>
       </c>
       <c r="L3" t="n">
-        <v>39.60339026216608</v>
+        <v>39.50777280937988</v>
       </c>
       <c r="M3" t="n">
-        <v>40.2911518104471</v>
+        <v>39.98272515761857</v>
       </c>
       <c r="N3" t="n">
-        <v>40.78422340987657</v>
+        <v>40.32650207231057</v>
       </c>
       <c r="O3" t="n">
-        <v>44.82677302818536</v>
+        <v>44.30195589225242</v>
       </c>
       <c r="P3" t="n">
-        <v>42.165652608179</v>
+        <v>41.35864075463611</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.76910081872377</v>
+        <v>39.62000106971275</v>
       </c>
       <c r="R3" t="n">
-        <v>39.62934129368362</v>
+        <v>39.51321374304838</v>
       </c>
       <c r="S3" t="n">
-        <v>40.56062935035848</v>
+        <v>40.19849657222787</v>
       </c>
       <c r="T3" t="n">
-        <v>40.48612107315864</v>
+        <v>40.11307575132144</v>
       </c>
       <c r="U3" t="n">
-        <v>44.05569195349857</v>
+        <v>43.6408251526852</v>
       </c>
       <c r="V3" t="n">
-        <v>40.39782014526169</v>
+        <v>40.07942838343052</v>
       </c>
       <c r="W3" t="n">
-        <v>47.08643299658884</v>
+        <v>46.47267964296423</v>
       </c>
       <c r="X3" t="n">
-        <v>42.23286956159869</v>
+        <v>41.36719259723417</v>
       </c>
       <c r="Y3" t="n">
-        <v>41.82117951126367</v>
+        <v>41.04007067910908</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.75640779347721</v>
+        <v>40.6324676880204</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.55896202432405</v>
+        <v>40.86329197087482</v>
       </c>
       <c r="AB3" t="n">
-        <v>41.12863065644919</v>
+        <v>40.5431777843853</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.38069670686276</v>
+        <v>40.93798174862003</v>
       </c>
       <c r="C3" t="n">
-        <v>43.2420683730638</v>
+        <v>43.10039826761894</v>
       </c>
       <c r="D3" t="n">
-        <v>41.44517891267439</v>
+        <v>40.93734138164208</v>
       </c>
       <c r="E3" t="n">
-        <v>40.18546043906762</v>
+        <v>39.70098080572371</v>
       </c>
       <c r="F3" t="n">
-        <v>40.94717385943422</v>
+        <v>40.59701298916411</v>
       </c>
       <c r="G3" t="n">
-        <v>42.87220166294103</v>
+        <v>42.01434355263661</v>
       </c>
       <c r="H3" t="n">
-        <v>42.55495150622811</v>
+        <v>41.67875172110972</v>
       </c>
       <c r="I3" t="n">
-        <v>41.3208460056985</v>
+        <v>40.85164231638331</v>
       </c>
       <c r="J3" t="n">
-        <v>42.83630559329222</v>
+        <v>41.96228529619291</v>
       </c>
       <c r="K3" t="n">
-        <v>41.71381488669078</v>
+        <v>41.16416716042963</v>
       </c>
       <c r="L3" t="n">
-        <v>43.03910159274112</v>
+        <v>42.09501671222213</v>
       </c>
       <c r="M3" t="n">
-        <v>44.86663605031629</v>
+        <v>43.36710357479669</v>
       </c>
       <c r="N3" t="n">
-        <v>42.81246688243711</v>
+        <v>41.89664258278576</v>
       </c>
       <c r="O3" t="n">
-        <v>46.64716282757218</v>
+        <v>45.86935987584103</v>
       </c>
       <c r="P3" t="n">
-        <v>43.68799412690275</v>
+        <v>42.57149424791639</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.75687275641489</v>
+        <v>41.17231347860766</v>
       </c>
       <c r="R3" t="n">
-        <v>41.67724338448793</v>
+        <v>41.08690440801659</v>
       </c>
       <c r="S3" t="n">
-        <v>42.03371298776359</v>
+        <v>41.41907355599278</v>
       </c>
       <c r="T3" t="n">
-        <v>41.90822177024896</v>
+        <v>41.25648430598525</v>
       </c>
       <c r="U3" t="n">
-        <v>47.138997028017</v>
+        <v>46.0277747849415</v>
       </c>
       <c r="V3" t="n">
-        <v>42.4194083358966</v>
+        <v>41.69258406624834</v>
       </c>
       <c r="W3" t="n">
-        <v>51.06389868426078</v>
+        <v>49.49086156117916</v>
       </c>
       <c r="X3" t="n">
-        <v>42.51808556821322</v>
+        <v>41.68560141502463</v>
       </c>
       <c r="Y3" t="n">
-        <v>44.96304883756478</v>
+        <v>43.42246535925917</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.87374510149126</v>
+        <v>43.08966582038637</v>
       </c>
       <c r="AA3" t="n">
-        <v>42.15736814081412</v>
+        <v>41.45191658876249</v>
       </c>
       <c r="AB3" t="n">
-        <v>45.01770386346085</v>
+        <v>43.34775592419129</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.73998253730126</v>
+        <v>39.6816018055897</v>
       </c>
       <c r="C3" t="n">
-        <v>42.88363917956014</v>
+        <v>42.76389176696356</v>
       </c>
       <c r="D3" t="n">
-        <v>40.19030796844825</v>
+        <v>39.99042656817286</v>
       </c>
       <c r="E3" t="n">
-        <v>39.24851386280304</v>
+        <v>38.97315082859325</v>
       </c>
       <c r="F3" t="n">
-        <v>40.28433488861235</v>
+        <v>40.05547339412153</v>
       </c>
       <c r="G3" t="n">
-        <v>42.17592895771629</v>
+        <v>41.45585488617814</v>
       </c>
       <c r="H3" t="n">
-        <v>41.80444802291719</v>
+        <v>41.07449402894113</v>
       </c>
       <c r="I3" t="n">
-        <v>40.08993734044328</v>
+        <v>39.91703507129782</v>
       </c>
       <c r="J3" t="n">
-        <v>41.51405671576702</v>
+        <v>40.95069861095072</v>
       </c>
       <c r="K3" t="n">
-        <v>40.65657104171139</v>
+        <v>40.33677138682792</v>
       </c>
       <c r="L3" t="n">
-        <v>40.66858653482862</v>
+        <v>40.3489972045294</v>
       </c>
       <c r="M3" t="n">
-        <v>41.45673590448162</v>
+        <v>40.89268753858278</v>
       </c>
       <c r="N3" t="n">
-        <v>41.66308263096853</v>
+        <v>41.01157031795732</v>
       </c>
       <c r="O3" t="n">
-        <v>45.79319380613654</v>
+        <v>45.12783882931585</v>
       </c>
       <c r="P3" t="n">
-        <v>42.92268296129699</v>
+        <v>41.96314134593107</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.56629951764008</v>
+        <v>40.26994849162414</v>
       </c>
       <c r="R3" t="n">
-        <v>40.21110614685522</v>
+        <v>39.99784916228339</v>
       </c>
       <c r="S3" t="n">
-        <v>40.57485747703004</v>
+        <v>40.28759616986691</v>
       </c>
       <c r="T3" t="n">
-        <v>40.93762632049658</v>
+        <v>40.50414342810701</v>
       </c>
       <c r="U3" t="n">
-        <v>45.04110248217999</v>
+        <v>44.4526308826178</v>
       </c>
       <c r="V3" t="n">
-        <v>41.21456091383292</v>
+        <v>40.75020736303872</v>
       </c>
       <c r="W3" t="n">
-        <v>49.50305217428522</v>
+        <v>48.27453178872784</v>
       </c>
       <c r="X3" t="n">
-        <v>42.32797577135357</v>
+        <v>41.48580878693146</v>
       </c>
       <c r="Y3" t="n">
-        <v>44.38314907225429</v>
+        <v>42.9290064145206</v>
       </c>
       <c r="Z3" t="n">
-        <v>41.87316921521614</v>
+        <v>41.5441645936115</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.08367545459091</v>
+        <v>40.6160701611104</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.55074961521316</v>
+        <v>42.28153979539038</v>
       </c>
     </row>
     <row r="4">
